--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A73D2B04-8432-4F51-8E5D-7F8682CC962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{396A5B0D-60F6-40E8-B27B-0D0CB3D00B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="40" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1144,27 +1144,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1173,19 +1161,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1202,6 +1193,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1494,7 +1494,7 @@
                   <c:v>247.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>287.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -1616,7 +1616,7 @@
                   <c:v>248.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>287.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -1738,7 +1738,7 @@
                   <c:v>169.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -1860,7 +1860,7 @@
                   <c:v>212.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#N/A</c:v>
+                  <c:v>233.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -5053,7 +5053,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5690,7 +5690,7 @@
   <dimension ref="A1:Z129"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.7109375" customWidth="1"/>
@@ -5704,26 +5704,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105" t="s">
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="105"/>
+      <c r="D1" s="101"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="99" t="s">
+      <c r="F1" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5738,13 +5738,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="93">
+      <c r="A2" s="92">
         <v>1</v>
       </c>
-      <c r="B2" s="93">
+      <c r="B2" s="92">
         <v>25</v>
       </c>
-      <c r="C2" s="93">
+      <c r="C2" s="92">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5782,26 +5782,26 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="99" t="s">
+      <c r="R2" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
+      <c r="U2" s="98"/>
+      <c r="V2" s="98"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="93">
+      <c r="A3" s="92">
         <v>2</v>
       </c>
-      <c r="B3" s="93">
+      <c r="B3" s="92">
         <v>18</v>
       </c>
-      <c r="C3" s="93">
+      <c r="C3" s="92">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -5870,13 +5870,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="93">
+      <c r="A4" s="92">
         <v>3</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="92">
         <v>15</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="92">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -5939,13 +5939,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="93">
+      <c r="A5" s="92">
         <v>4</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="92">
         <v>12</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="92">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -5961,9 +5961,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
+      <c r="J5" s="5"/>
       <c r="K5" s="3"/>
       <c r="L5" s="5"/>
       <c r="M5" s="3"/>
@@ -5995,9 +5993,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="3"/>
       <c r="L6" s="5"/>
       <c r="M6" s="3"/>
@@ -6005,17 +6001,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="99" t="s">
+      <c r="R6" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="99"/>
-      <c r="T6" s="99"/>
-      <c r="U6" s="99"/>
-      <c r="V6" s="99"/>
-      <c r="W6" s="99"/>
-      <c r="X6" s="99"/>
-      <c r="Y6" s="99"/>
-      <c r="Z6" s="99"/>
+      <c r="S6" s="98"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="98"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="98"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6037,9 +6033,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
+      <c r="J7" s="5"/>
       <c r="K7" s="3"/>
       <c r="L7" s="5"/>
       <c r="M7" s="3"/>
@@ -6079,26 +6073,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="104">
+      <c r="G8" s="103">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104">
+      <c r="H8" s="100"/>
+      <c r="I8" s="103">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="103"/>
-      <c r="K8" s="104">
+      <c r="J8" s="100"/>
+      <c r="K8" s="103">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="103"/>
-      <c r="M8" s="104">
+      <c r="L8" s="100"/>
+      <c r="M8" s="103">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="103"/>
+      <c r="N8" s="100"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1">
@@ -6136,17 +6130,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="99" t="s">
+      <c r="R9" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6157,26 +6151,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="102">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106">
+      <c r="H10" s="102"/>
+      <c r="I10" s="102">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106">
+      <c r="J10" s="102"/>
+      <c r="K10" s="102">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106">
+      <c r="L10" s="102"/>
+      <c r="M10" s="102">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="106"/>
+      <c r="N10" s="102"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6209,26 +6203,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="97">
+      <c r="G11" s="94">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="98"/>
-      <c r="I11" s="97">
+      <c r="H11" s="95"/>
+      <c r="I11" s="94">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="98"/>
-      <c r="K11" s="97">
+      <c r="J11" s="95"/>
+      <c r="K11" s="94">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="98"/>
-      <c r="M11" s="97">
+      <c r="L11" s="95"/>
+      <c r="M11" s="94">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="98"/>
+      <c r="N11" s="95"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6251,40 +6245,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="97">
+      <c r="G12" s="94">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="98"/>
-      <c r="I12" s="97">
+      <c r="H12" s="95"/>
+      <c r="I12" s="94">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="98"/>
-      <c r="K12" s="97">
+      <c r="J12" s="95"/>
+      <c r="K12" s="94">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="98"/>
-      <c r="M12" s="97">
+      <c r="L12" s="95"/>
+      <c r="M12" s="94">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="98"/>
+      <c r="N12" s="95"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="99" t="s">
+      <c r="R12" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="99"/>
-      <c r="T12" s="99"/>
-      <c r="U12" s="99"/>
-      <c r="V12" s="99"/>
-      <c r="W12" s="99"/>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="99"/>
-      <c r="Z12" s="99"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6330,17 +6324,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="99" t="s">
+      <c r="F14" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="98"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6569,26 +6563,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="104">
+      <c r="G21" s="103">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="103"/>
-      <c r="I21" s="102">
+      <c r="H21" s="100"/>
+      <c r="I21" s="99">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="103"/>
-      <c r="K21" s="102">
+      <c r="J21" s="100"/>
+      <c r="K21" s="99">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="103"/>
-      <c r="M21" s="102">
+      <c r="L21" s="100"/>
+      <c r="M21" s="99">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="103"/>
+      <c r="N21" s="100"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1">
@@ -6624,26 +6618,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="100">
+      <c r="G23" s="96">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="101"/>
-      <c r="I23" s="100">
+      <c r="H23" s="97"/>
+      <c r="I23" s="96">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="101"/>
-      <c r="K23" s="100">
+      <c r="J23" s="97"/>
+      <c r="K23" s="96">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="101"/>
-      <c r="M23" s="100">
+      <c r="L23" s="97"/>
+      <c r="M23" s="96">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="101"/>
+      <c r="N23" s="97"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6657,26 +6651,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="97">
+      <c r="G24" s="94">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="98"/>
-      <c r="I24" s="97">
+      <c r="H24" s="95"/>
+      <c r="I24" s="94">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="98"/>
-      <c r="K24" s="97">
+      <c r="J24" s="95"/>
+      <c r="K24" s="94">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="98"/>
-      <c r="M24" s="97">
+      <c r="L24" s="95"/>
+      <c r="M24" s="94">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="98"/>
+      <c r="N24" s="95"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6690,26 +6684,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="97">
+      <c r="G25" s="94">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="98"/>
-      <c r="I25" s="97">
+      <c r="H25" s="95"/>
+      <c r="I25" s="94">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="98"/>
-      <c r="K25" s="97">
+      <c r="J25" s="95"/>
+      <c r="K25" s="94">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="98"/>
-      <c r="M25" s="97">
+      <c r="L25" s="95"/>
+      <c r="M25" s="94">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="98"/>
+      <c r="N25" s="95"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6739,17 +6733,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="99" t="s">
+      <c r="F27" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="99"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="98"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="98"/>
+      <c r="N27" s="98"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -6925,7 +6919,7 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="6:17">
+    <row r="33" spans="6:23">
       <c r="F33" s="11" t="s">
         <v>16</v>
       </c>
@@ -6942,39 +6936,51 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="6:17" ht="15.75" thickBot="1">
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" spans="6:23" ht="15.75" thickBot="1">
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="102">
+      <c r="G34" s="99">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="103"/>
-      <c r="I34" s="102">
+      <c r="H34" s="100"/>
+      <c r="I34" s="99">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="103"/>
-      <c r="K34" s="102">
+      <c r="J34" s="100"/>
+      <c r="K34" s="99">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="103"/>
-      <c r="M34" s="102">
+      <c r="L34" s="100"/>
+      <c r="M34" s="99">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="103"/>
+      <c r="N34" s="100"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1">
         <f>+SUM(I34-G34)+Q21</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="6:17" ht="15.75" thickTop="1">
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+    <row r="35" spans="6:23" ht="15.75" thickTop="1">
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -6987,108 +6993,161 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="6:17">
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="6:23">
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="100">
+      <c r="G36" s="96">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="101"/>
-      <c r="I36" s="100">
+      <c r="H36" s="97"/>
+      <c r="I36" s="96">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="101"/>
-      <c r="K36" s="100">
+      <c r="J36" s="97"/>
+      <c r="K36" s="96">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="101"/>
-      <c r="M36" s="100">
+      <c r="L36" s="97"/>
+      <c r="M36" s="96">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="101"/>
+      <c r="N36" s="97"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="6:17">
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="6:23">
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="97">
+      <c r="G37" s="94">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="98"/>
-      <c r="I37" s="97">
+      <c r="H37" s="95"/>
+      <c r="I37" s="94">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="98"/>
-      <c r="K37" s="97">
+      <c r="J37" s="95"/>
+      <c r="K37" s="94">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="98"/>
-      <c r="M37" s="97">
+      <c r="L37" s="95"/>
+      <c r="M37" s="94">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="98"/>
+      <c r="N37" s="95"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="6:17">
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="6:23">
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="97">
+      <c r="G38" s="94">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="98"/>
-      <c r="I38" s="97">
+      <c r="H38" s="95"/>
+      <c r="I38" s="94">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="98"/>
-      <c r="K38" s="97">
+      <c r="J38" s="95"/>
+      <c r="K38" s="94">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="98"/>
-      <c r="M38" s="97">
+      <c r="L38" s="95"/>
+      <c r="M38" s="94">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="98"/>
+      <c r="N38" s="95"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="40" spans="6:17" ht="15.75" thickBot="1">
-      <c r="F40" s="99" t="s">
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="6:23">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1">
+        <f>+SUM(J29*0.7)</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="40" spans="6:23" ht="15.75" thickBot="1">
+      <c r="F40" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="99"/>
-      <c r="N40" s="99"/>
+      <c r="G40" s="98"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="98"/>
+      <c r="J40" s="98"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="98"/>
+      <c r="N40" s="98"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="6:17" ht="16.5" thickTop="1" thickBot="1">
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="6:23" ht="16.5" thickTop="1" thickBot="1">
       <c r="F41" s="13" t="s">
         <v>24</v>
       </c>
@@ -7119,8 +7178,14 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="6:17" ht="15.75" thickTop="1">
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="6:23" ht="15.75" thickTop="1">
       <c r="F42" s="14" t="s">
         <v>9</v>
       </c>
@@ -7155,8 +7220,14 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="6:17">
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="6:23">
       <c r="F43" s="11" t="s">
         <v>11</v>
       </c>
@@ -7191,8 +7262,14 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="6:17">
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="6:23">
       <c r="F44" s="11" t="s">
         <v>13</v>
       </c>
@@ -7209,8 +7286,14 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="6:17">
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="6:23">
       <c r="F45" s="11" t="s">
         <v>14</v>
       </c>
@@ -7227,8 +7310,14 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="6:17">
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="6:23">
       <c r="F46" s="11" t="s">
         <v>16</v>
       </c>
@@ -7247,39 +7336,51 @@
       <c r="Q46" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="6:17" ht="15.75" thickBot="1">
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="6:23" ht="15.75" thickBot="1">
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="102">
+      <c r="G47" s="99">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="103"/>
-      <c r="I47" s="102">
+      <c r="H47" s="100"/>
+      <c r="I47" s="99">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="103"/>
-      <c r="K47" s="102">
+      <c r="J47" s="100"/>
+      <c r="K47" s="99">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="103"/>
-      <c r="M47" s="102">
+      <c r="L47" s="100"/>
+      <c r="M47" s="99">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="103"/>
+      <c r="N47" s="100"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1">
         <f>+SUM(I47-G47)+Q34</f>
         <v>6.75</v>
       </c>
-    </row>
-    <row r="48" spans="6:17" ht="15.75" thickTop="1">
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="6:23" ht="15.75" thickTop="1">
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -7292,81 +7393,87 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
     </row>
     <row r="49" spans="6:14">
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="100">
+      <c r="G49" s="96">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="101"/>
-      <c r="I49" s="100">
+      <c r="H49" s="97"/>
+      <c r="I49" s="96">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="101"/>
-      <c r="K49" s="100">
+      <c r="J49" s="97"/>
+      <c r="K49" s="96">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="101"/>
-      <c r="M49" s="100">
+      <c r="L49" s="97"/>
+      <c r="M49" s="96">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="101"/>
+      <c r="N49" s="97"/>
     </row>
     <row r="50" spans="6:14">
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="97">
+      <c r="G50" s="94">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="98"/>
-      <c r="I50" s="97">
+      <c r="H50" s="95"/>
+      <c r="I50" s="94">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="98"/>
-      <c r="K50" s="97">
+      <c r="J50" s="95"/>
+      <c r="K50" s="94">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="98"/>
-      <c r="M50" s="97">
+      <c r="L50" s="95"/>
+      <c r="M50" s="94">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="98"/>
+      <c r="N50" s="95"/>
     </row>
     <row r="51" spans="6:14">
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="97">
+      <c r="G51" s="94">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="98"/>
-      <c r="I51" s="97">
+      <c r="H51" s="95"/>
+      <c r="I51" s="94">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="98"/>
-      <c r="K51" s="97">
+      <c r="J51" s="95"/>
+      <c r="K51" s="94">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="98"/>
-      <c r="M51" s="97">
+      <c r="L51" s="95"/>
+      <c r="M51" s="94">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="98"/>
+      <c r="N51" s="95"/>
     </row>
     <row r="52" spans="6:14">
       <c r="F52" s="27"/>
@@ -7380,17 +7487,17 @@
       <c r="N52" s="28"/>
     </row>
     <row r="53" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F53" s="99" t="s">
+      <c r="F53" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="99"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="99"/>
-      <c r="M53" s="99"/>
-      <c r="N53" s="99"/>
+      <c r="G53" s="98"/>
+      <c r="H53" s="98"/>
+      <c r="I53" s="98"/>
+      <c r="J53" s="98"/>
+      <c r="K53" s="98"/>
+      <c r="L53" s="98"/>
+      <c r="M53" s="98"/>
+      <c r="N53" s="98"/>
     </row>
     <row r="54" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F54" s="13" t="s">
@@ -7536,26 +7643,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="102">
+      <c r="G60" s="99">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="103"/>
-      <c r="I60" s="102">
+      <c r="H60" s="100"/>
+      <c r="I60" s="99">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="103"/>
-      <c r="K60" s="102">
+      <c r="J60" s="100"/>
+      <c r="K60" s="99">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="103"/>
-      <c r="M60" s="102">
+      <c r="L60" s="100"/>
+      <c r="M60" s="99">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="103"/>
+      <c r="N60" s="100"/>
     </row>
     <row r="61" spans="6:14" ht="15.75" thickTop="1">
       <c r="F61" s="1"/>
@@ -7572,89 +7679,89 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="100">
+      <c r="G62" s="96">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="101"/>
-      <c r="I62" s="100">
+      <c r="H62" s="97"/>
+      <c r="I62" s="96">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="101"/>
-      <c r="K62" s="100">
+      <c r="J62" s="97"/>
+      <c r="K62" s="96">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="101"/>
-      <c r="M62" s="100">
+      <c r="L62" s="97"/>
+      <c r="M62" s="96">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="101"/>
+      <c r="N62" s="97"/>
     </row>
     <row r="63" spans="6:14">
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="97">
+      <c r="G63" s="94">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="98"/>
-      <c r="I63" s="97">
+      <c r="H63" s="95"/>
+      <c r="I63" s="94">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="98"/>
-      <c r="K63" s="97">
+      <c r="J63" s="95"/>
+      <c r="K63" s="94">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="98"/>
-      <c r="M63" s="97">
+      <c r="L63" s="95"/>
+      <c r="M63" s="94">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="98"/>
+      <c r="N63" s="95"/>
     </row>
     <row r="64" spans="6:14">
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="97">
+      <c r="G64" s="94">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="98"/>
-      <c r="I64" s="97">
+      <c r="H64" s="95"/>
+      <c r="I64" s="94">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="98"/>
-      <c r="K64" s="97">
+      <c r="J64" s="95"/>
+      <c r="K64" s="94">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="98"/>
-      <c r="M64" s="97">
+      <c r="L64" s="95"/>
+      <c r="M64" s="94">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="98"/>
+      <c r="N64" s="95"/>
     </row>
     <row r="66" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F66" s="99" t="s">
+      <c r="F66" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="G66" s="99"/>
-      <c r="H66" s="99"/>
-      <c r="I66" s="99"/>
-      <c r="J66" s="99"/>
-      <c r="K66" s="99"/>
-      <c r="L66" s="99"/>
-      <c r="M66" s="99"/>
-      <c r="N66" s="99"/>
+      <c r="G66" s="98"/>
+      <c r="H66" s="98"/>
+      <c r="I66" s="98"/>
+      <c r="J66" s="98"/>
+      <c r="K66" s="98"/>
+      <c r="L66" s="98"/>
+      <c r="M66" s="98"/>
+      <c r="N66" s="98"/>
     </row>
     <row r="67" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F67" s="13" t="s">
@@ -7800,35 +7907,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="102">
+      <c r="G73" s="99">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="103">
+      <c r="H73" s="100">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="102">
+      <c r="I73" s="99">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="103">
+      <c r="J73" s="100">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="102">
+      <c r="K73" s="99">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="103">
+      <c r="L73" s="100">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="102">
+      <c r="M73" s="99">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="103">
+      <c r="N73" s="100">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -7848,89 +7955,89 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="100">
+      <c r="G75" s="96">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="101"/>
-      <c r="I75" s="100">
+      <c r="H75" s="97"/>
+      <c r="I75" s="96">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="101"/>
-      <c r="K75" s="100">
+      <c r="J75" s="97"/>
+      <c r="K75" s="96">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="101"/>
-      <c r="M75" s="100">
+      <c r="L75" s="97"/>
+      <c r="M75" s="96">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="101"/>
+      <c r="N75" s="97"/>
     </row>
     <row r="76" spans="6:14">
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="97">
+      <c r="G76" s="94">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="98"/>
-      <c r="I76" s="97">
+      <c r="H76" s="95"/>
+      <c r="I76" s="94">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="98"/>
-      <c r="K76" s="97">
+      <c r="J76" s="95"/>
+      <c r="K76" s="94">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="98"/>
-      <c r="M76" s="97">
+      <c r="L76" s="95"/>
+      <c r="M76" s="94">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="98"/>
+      <c r="N76" s="95"/>
     </row>
     <row r="77" spans="6:14">
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="97">
+      <c r="G77" s="94">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="98"/>
-      <c r="I77" s="97">
+      <c r="H77" s="95"/>
+      <c r="I77" s="94">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="98"/>
-      <c r="K77" s="97">
+      <c r="J77" s="95"/>
+      <c r="K77" s="94">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="98"/>
-      <c r="M77" s="97">
+      <c r="L77" s="95"/>
+      <c r="M77" s="94">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="98"/>
+      <c r="N77" s="95"/>
     </row>
     <row r="79" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F79" s="99" t="s">
+      <c r="F79" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="G79" s="99"/>
-      <c r="H79" s="99"/>
-      <c r="I79" s="99"/>
-      <c r="J79" s="99"/>
-      <c r="K79" s="99"/>
-      <c r="L79" s="99"/>
-      <c r="M79" s="99"/>
-      <c r="N79" s="99"/>
+      <c r="G79" s="98"/>
+      <c r="H79" s="98"/>
+      <c r="I79" s="98"/>
+      <c r="J79" s="98"/>
+      <c r="K79" s="98"/>
+      <c r="L79" s="98"/>
+      <c r="M79" s="98"/>
+      <c r="N79" s="98"/>
     </row>
     <row r="80" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F80" s="13" t="s">
@@ -8076,35 +8183,35 @@
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="102">
+      <c r="G86" s="99">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="103">
+      <c r="H86" s="100">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="102">
+      <c r="I86" s="99">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="103">
+      <c r="J86" s="100">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="102">
+      <c r="K86" s="99">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="L86" s="103">
+      <c r="L86" s="100">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="M86" s="102">
+      <c r="M86" s="99">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
-      <c r="N86" s="103">
+      <c r="N86" s="100">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
@@ -8124,89 +8231,89 @@
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="100">
+      <c r="G88" s="96">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="101"/>
-      <c r="I88" s="100">
+      <c r="H88" s="97"/>
+      <c r="I88" s="96">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="101"/>
-      <c r="K88" s="100">
+      <c r="J88" s="97"/>
+      <c r="K88" s="96">
         <f>+SUM(K86,K75)</f>
         <v>169.75</v>
       </c>
-      <c r="L88" s="101"/>
-      <c r="M88" s="100">
+      <c r="L88" s="97"/>
+      <c r="M88" s="96">
         <f>+SUM(M86,M75)</f>
         <v>212.25</v>
       </c>
-      <c r="N88" s="101"/>
+      <c r="N88" s="97"/>
     </row>
     <row r="89" spans="6:14">
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="97">
+      <c r="G89" s="94">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="98"/>
-      <c r="I89" s="97">
+      <c r="H89" s="95"/>
+      <c r="I89" s="94">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="98"/>
-      <c r="K89" s="97">
+      <c r="J89" s="95"/>
+      <c r="K89" s="94">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L89" s="98"/>
-      <c r="M89" s="97">
+      <c r="L89" s="95"/>
+      <c r="M89" s="94">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N89" s="98"/>
+      <c r="N89" s="95"/>
     </row>
     <row r="90" spans="6:14">
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="97">
+      <c r="G90" s="94">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="98"/>
-      <c r="I90" s="97">
+      <c r="H90" s="95"/>
+      <c r="I90" s="94">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="98"/>
-      <c r="K90" s="97">
+      <c r="J90" s="95"/>
+      <c r="K90" s="94">
         <f>+SUM(K89+K77-K50)</f>
         <v>0</v>
       </c>
-      <c r="L90" s="98"/>
-      <c r="M90" s="97">
+      <c r="L90" s="95"/>
+      <c r="M90" s="94">
         <f>+SUM(M89+M77-M50)</f>
         <v>70</v>
       </c>
-      <c r="N90" s="98"/>
-    </row>
-    <row r="92" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F92" s="99"/>
-      <c r="G92" s="99"/>
-      <c r="H92" s="99"/>
-      <c r="I92" s="99"/>
-      <c r="J92" s="99"/>
-      <c r="K92" s="99"/>
-      <c r="L92" s="99"/>
-      <c r="M92" s="99"/>
-      <c r="N92" s="99"/>
-    </row>
-    <row r="93" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="N90" s="95"/>
+    </row>
+    <row r="92" spans="6:14">
+      <c r="F92" s="98"/>
+      <c r="G92" s="98"/>
+      <c r="H92" s="98"/>
+      <c r="I92" s="98"/>
+      <c r="J92" s="98"/>
+      <c r="K92" s="98"/>
+      <c r="L92" s="98"/>
+      <c r="M92" s="98"/>
+      <c r="N92" s="98"/>
+    </row>
+    <row r="93" spans="6:14" ht="16.5" customHeight="1">
       <c r="F93" s="13" t="s">
         <v>32</v>
       </c>
@@ -8235,54 +8342,70 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="6:14" ht="15.75" thickTop="1">
+    <row r="94" spans="6:14" ht="15.75" customHeight="1">
       <c r="F94" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G94" s="9"/>
-      <c r="H94" s="6" t="str">
+      <c r="G94" s="9">
+        <v>2</v>
+      </c>
+      <c r="H94" s="6">
         <f>+IF(G94=1,$B$2,IF($G94=2,$B$3,IF($G94=3,$B$4,IF($G94=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="I94" s="9"/>
-      <c r="J94" s="6" t="str">
+        <v>18</v>
+      </c>
+      <c r="I94" s="9">
+        <v>1</v>
+      </c>
+      <c r="J94" s="6">
         <f>+IF(I94=1,$B$2,IF($I94=2,$B$3,IF($I94=3,$B$4,IF($I94=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="K94" s="9"/>
-      <c r="L94" s="6" t="str">
+        <v>25</v>
+      </c>
+      <c r="K94" s="9">
+        <v>3</v>
+      </c>
+      <c r="L94" s="6">
         <f>+IF(K94=1,$B$2,IF($K94=2,$B$3,IF($K94=3,$B$4,IF($K94=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="M94" s="9"/>
-      <c r="N94" s="6" t="str">
+        <v>15</v>
+      </c>
+      <c r="M94" s="9">
+        <v>4</v>
+      </c>
+      <c r="N94" s="6">
         <f>+IF(M94=1,$B$2,IF($M94=2,$B$3,IF($M94=3,$B$4,IF($M94=4,$B$5,""))))</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="6:14">
       <c r="F95" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G95" s="10"/>
-      <c r="H95" s="5" t="str">
+      <c r="G95" s="10">
+        <v>1</v>
+      </c>
+      <c r="H95" s="5">
         <f>+IF(G95=1,$D$2,IF($G95=2,$D$3,IF($G95=3,$D$4,IF($G95=4,$D$5,""))))</f>
-        <v/>
-      </c>
-      <c r="I95" s="10"/>
-      <c r="J95" s="5" t="str">
+        <v>18.75</v>
+      </c>
+      <c r="I95" s="10">
+        <v>2</v>
+      </c>
+      <c r="J95" s="5">
         <f>+IF(I95=1,$D$2,IF($I95=2,$D$3,IF($I95=3,$D$4,IF($I95=4,$D$5,""))))</f>
-        <v/>
-      </c>
-      <c r="K95" s="10"/>
-      <c r="L95" s="5" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="K95" s="10">
+        <v>3</v>
+      </c>
+      <c r="L95" s="5">
         <f>+IF(K95=1,$D$2,IF($K95=2,$D$3,IF($K95=3,$D$4,IF($K95=4,$D$5,""))))</f>
-        <v/>
-      </c>
-      <c r="M95" s="10"/>
-      <c r="N95" s="5" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="M95" s="10">
+        <v>4</v>
+      </c>
+      <c r="N95" s="5">
         <f>+IF(M95=1,$D$2,IF($M95=2,$D$3,IF($M95=3,$D$4,IF($M95=4,$D$5,""))))</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="6:14">
@@ -8290,7 +8413,9 @@
         <v>13</v>
       </c>
       <c r="G96" s="10"/>
-      <c r="H96" s="5"/>
+      <c r="H96" s="5">
+        <v>1</v>
+      </c>
       <c r="I96" s="10"/>
       <c r="J96" s="5"/>
       <c r="K96" s="10"/>
@@ -8303,7 +8428,9 @@
         <v>14</v>
       </c>
       <c r="G97" s="10"/>
-      <c r="H97" s="5"/>
+      <c r="H97" s="5">
+        <v>1</v>
+      </c>
       <c r="I97" s="10"/>
       <c r="J97" s="5"/>
       <c r="K97" s="10"/>
@@ -8316,7 +8443,9 @@
         <v>16</v>
       </c>
       <c r="G98" s="10"/>
-      <c r="H98" s="5"/>
+      <c r="H98" s="5">
+        <v>1</v>
+      </c>
       <c r="I98" s="10"/>
       <c r="J98" s="5"/>
       <c r="K98" s="10"/>
@@ -8324,32 +8453,44 @@
       <c r="M98" s="10"/>
       <c r="N98" s="5"/>
     </row>
-    <row r="99" spans="6:14" ht="15.75" thickBot="1">
+    <row r="99" spans="6:14" ht="15.75" customHeight="1">
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="102"/>
-      <c r="H99" s="103">
+      <c r="G99" s="99">
         <f>+SUM(H94:H98)</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="102"/>
-      <c r="J99" s="103">
+        <v>39.75</v>
+      </c>
+      <c r="H99" s="100">
+        <f>+SUM(H94:H98)</f>
+        <v>39.75</v>
+      </c>
+      <c r="I99" s="99">
         <f>+SUM(J94:J98)</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="102"/>
-      <c r="L99" s="103">
-        <f>+SUM(L94:L98)</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="102"/>
-      <c r="N99" s="103">
-        <f>+SUM(N94:N98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="6:14" ht="15.75" thickTop="1">
+        <v>38.5</v>
+      </c>
+      <c r="J99" s="100">
+        <f>+SUM(J94:J98)</f>
+        <v>38.5</v>
+      </c>
+      <c r="K99" s="99">
+        <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
+        <v>26.25</v>
+      </c>
+      <c r="L99" s="100">
+        <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
+        <v>26.25</v>
+      </c>
+      <c r="M99" s="99">
+        <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
+        <v>21</v>
+      </c>
+      <c r="N99" s="100">
+        <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="6:14">
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -8364,69 +8505,87 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="100"/>
-      <c r="H101" s="101"/>
-      <c r="I101" s="100"/>
-      <c r="J101" s="101"/>
-      <c r="K101" s="100"/>
-      <c r="L101" s="101"/>
-      <c r="M101" s="100"/>
-      <c r="N101" s="101"/>
+      <c r="G101" s="96">
+        <f>+SUM(G99,G88)</f>
+        <v>287.5</v>
+      </c>
+      <c r="H101" s="97"/>
+      <c r="I101" s="96">
+        <f>+SUM(I99,I88)</f>
+        <v>287.25</v>
+      </c>
+      <c r="J101" s="97"/>
+      <c r="K101" s="96">
+        <f>+SUM(K99,K88)</f>
+        <v>196</v>
+      </c>
+      <c r="L101" s="97"/>
+      <c r="M101" s="96">
+        <f>+SUM(M99,M88)</f>
+        <v>233.25</v>
+      </c>
+      <c r="N101" s="97"/>
     </row>
     <row r="102" spans="6:14">
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="97" t="str">
+      <c r="G102" s="94">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="H102" s="98"/>
-      <c r="I102" s="97" t="str">
+        <v>20</v>
+      </c>
+      <c r="H102" s="95"/>
+      <c r="I102" s="94">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="J102" s="98"/>
-      <c r="K102" s="100"/>
-      <c r="L102" s="101"/>
-      <c r="M102" s="100"/>
-      <c r="N102" s="101"/>
+        <v>40</v>
+      </c>
+      <c r="J102" s="95"/>
+      <c r="K102" s="94">
+        <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
+        <v>10</v>
+      </c>
+      <c r="L102" s="95"/>
+      <c r="M102" s="94">
+        <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="95"/>
     </row>
     <row r="103" spans="6:14">
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="97" t="e">
+      <c r="G103" s="94">
         <f>+SUM(G102+G90-G63)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H103" s="98"/>
-      <c r="I103" s="97" t="e">
+        <v>70</v>
+      </c>
+      <c r="H103" s="95"/>
+      <c r="I103" s="94">
         <f>+SUM(I102+I90-I63)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J103" s="98"/>
-      <c r="K103" s="100" t="str">
-        <f>+IF($K94=1,"40Kg",IF($K94=2,"20Kg",IF($K94=3,"10Kg",IF($K94=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="L103" s="101"/>
-      <c r="M103" s="100" t="str">
-        <f>+IF($M94=1,"40Kg",IF($M94=2,"20Kg",IF($M94=3,"10Kg",IF($M94=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="N103" s="101"/>
+        <v>100</v>
+      </c>
+      <c r="J103" s="95"/>
+      <c r="K103" s="94">
+        <f>+SUM(K102+K90-K63)</f>
+        <v>10</v>
+      </c>
+      <c r="L103" s="95"/>
+      <c r="M103" s="94">
+        <f>+SUM(M102+M90-M63)</f>
+        <v>30</v>
+      </c>
+      <c r="N103" s="95"/>
     </row>
     <row r="105" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F105" s="99"/>
-      <c r="G105" s="99"/>
-      <c r="H105" s="99"/>
-      <c r="I105" s="99"/>
-      <c r="J105" s="99"/>
-      <c r="K105" s="99"/>
-      <c r="L105" s="99"/>
-      <c r="M105" s="99"/>
-      <c r="N105" s="99"/>
+      <c r="F105" s="98"/>
+      <c r="G105" s="98"/>
+      <c r="H105" s="98"/>
+      <c r="I105" s="98"/>
+      <c r="J105" s="98"/>
+      <c r="K105" s="98"/>
+      <c r="L105" s="98"/>
+      <c r="M105" s="98"/>
+      <c r="N105" s="98"/>
     </row>
     <row r="106" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F106" s="13" t="s">
@@ -8550,23 +8709,23 @@
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="102"/>
-      <c r="H112" s="103">
+      <c r="G112" s="99"/>
+      <c r="H112" s="100">
         <f>+SUM(H107:H111)</f>
         <v>0</v>
       </c>
-      <c r="I112" s="102"/>
-      <c r="J112" s="103">
+      <c r="I112" s="99"/>
+      <c r="J112" s="100">
         <f>+SUM(J107:J111)</f>
         <v>0</v>
       </c>
-      <c r="K112" s="102"/>
-      <c r="L112" s="103">
+      <c r="K112" s="99"/>
+      <c r="L112" s="100">
         <f>+SUM(L107:L111)</f>
         <v>0</v>
       </c>
-      <c r="M112" s="102"/>
-      <c r="N112" s="103">
+      <c r="M112" s="99"/>
+      <c r="N112" s="100">
         <f>+SUM(N107:N111)</f>
         <v>0</v>
       </c>
@@ -8586,81 +8745,81 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="100">
+      <c r="G114" s="96">
         <f>H112</f>
         <v>0</v>
       </c>
-      <c r="H114" s="101"/>
-      <c r="I114" s="100">
+      <c r="H114" s="97"/>
+      <c r="I114" s="96">
         <f>J112</f>
         <v>0</v>
       </c>
-      <c r="J114" s="101"/>
-      <c r="K114" s="100">
+      <c r="J114" s="97"/>
+      <c r="K114" s="96">
         <f>L112</f>
         <v>0</v>
       </c>
-      <c r="L114" s="101"/>
-      <c r="M114" s="100">
+      <c r="L114" s="97"/>
+      <c r="M114" s="96">
         <f>N112</f>
         <v>0</v>
       </c>
-      <c r="N114" s="101"/>
+      <c r="N114" s="97"/>
     </row>
     <row r="115" spans="6:14">
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="97" t="str">
+      <c r="G115" s="94" t="str">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H115" s="98"/>
-      <c r="I115" s="97" t="str">
+      <c r="H115" s="95"/>
+      <c r="I115" s="94" t="str">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J115" s="98"/>
-      <c r="K115" s="100"/>
-      <c r="L115" s="101"/>
-      <c r="M115" s="100"/>
-      <c r="N115" s="101"/>
+      <c r="J115" s="95"/>
+      <c r="K115" s="96"/>
+      <c r="L115" s="97"/>
+      <c r="M115" s="96"/>
+      <c r="N115" s="97"/>
     </row>
     <row r="116" spans="6:14">
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="97" t="e">
+      <c r="G116" s="94" t="e">
         <f>+SUM(G115+G103-G76)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H116" s="98"/>
-      <c r="I116" s="97" t="e">
+      <c r="H116" s="95"/>
+      <c r="I116" s="94" t="e">
         <f>+SUM(I115+I103-I76)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J116" s="98"/>
-      <c r="K116" s="100" t="str">
+      <c r="J116" s="95"/>
+      <c r="K116" s="96" t="str">
         <f>+IF($K107=1,"40Kg",IF($K107=2,"20Kg",IF($K107=3,"10Kg",IF($K107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L116" s="101"/>
-      <c r="M116" s="100" t="str">
+      <c r="L116" s="97"/>
+      <c r="M116" s="96" t="str">
         <f>+IF($M107=1,"40Kg",IF($M107=2,"20Kg",IF($M107=3,"10Kg",IF($M107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N116" s="101"/>
+      <c r="N116" s="97"/>
     </row>
     <row r="118" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F118" s="99"/>
-      <c r="G118" s="99"/>
-      <c r="H118" s="99"/>
-      <c r="I118" s="99"/>
-      <c r="J118" s="99"/>
-      <c r="K118" s="99"/>
-      <c r="L118" s="99"/>
-      <c r="M118" s="99"/>
-      <c r="N118" s="99"/>
+      <c r="F118" s="98"/>
+      <c r="G118" s="98"/>
+      <c r="H118" s="98"/>
+      <c r="I118" s="98"/>
+      <c r="J118" s="98"/>
+      <c r="K118" s="98"/>
+      <c r="L118" s="98"/>
+      <c r="M118" s="98"/>
+      <c r="N118" s="98"/>
     </row>
     <row r="119" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F119" s="13" t="s">
@@ -8784,23 +8943,23 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="102"/>
-      <c r="H125" s="103">
+      <c r="G125" s="99"/>
+      <c r="H125" s="100">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="102"/>
-      <c r="J125" s="103">
+      <c r="I125" s="99"/>
+      <c r="J125" s="100">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="102"/>
-      <c r="L125" s="103">
+      <c r="K125" s="99"/>
+      <c r="L125" s="100">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="102"/>
-      <c r="N125" s="103">
+      <c r="M125" s="99"/>
+      <c r="N125" s="100">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -8820,177 +8979,121 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="100">
+      <c r="G127" s="96">
         <f>H125</f>
         <v>0</v>
       </c>
-      <c r="H127" s="101"/>
-      <c r="I127" s="100">
+      <c r="H127" s="97"/>
+      <c r="I127" s="96">
         <f>J125</f>
         <v>0</v>
       </c>
-      <c r="J127" s="101"/>
-      <c r="K127" s="100">
+      <c r="J127" s="97"/>
+      <c r="K127" s="96">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="101"/>
-      <c r="M127" s="100">
+      <c r="L127" s="97"/>
+      <c r="M127" s="96">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="101"/>
+      <c r="N127" s="97"/>
     </row>
     <row r="128" spans="6:14">
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="97" t="str">
+      <c r="G128" s="94" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="98"/>
-      <c r="I128" s="97" t="str">
+      <c r="H128" s="95"/>
+      <c r="I128" s="94" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J128" s="98"/>
-      <c r="K128" s="100"/>
-      <c r="L128" s="101"/>
-      <c r="M128" s="100"/>
-      <c r="N128" s="101"/>
+      <c r="J128" s="95"/>
+      <c r="K128" s="96"/>
+      <c r="L128" s="97"/>
+      <c r="M128" s="96"/>
+      <c r="N128" s="97"/>
     </row>
     <row r="129" spans="6:14">
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="97" t="e">
+      <c r="G129" s="94" t="e">
         <f>+SUM(G128+G116-G89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H129" s="98"/>
-      <c r="I129" s="97" t="e">
+      <c r="H129" s="95"/>
+      <c r="I129" s="94" t="e">
         <f>+SUM(I128+I116-I89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J129" s="98"/>
-      <c r="K129" s="100" t="str">
+      <c r="J129" s="95"/>
+      <c r="K129" s="96" t="str">
         <f>+IF($K120=1,"40Kg",IF($K120=2,"20Kg",IF($K120=3,"10Kg",IF($K120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L129" s="101"/>
-      <c r="M129" s="100" t="str">
+      <c r="L129" s="97"/>
+      <c r="M129" s="96" t="str">
         <f>+IF($M120=1,"40Kg",IF($M120=2,"20Kg",IF($M120=3,"10Kg",IF($M120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N129" s="101"/>
+      <c r="N129" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="176">
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="R2:Z2"/>
+    <mergeCell ref="R6:Z6"/>
+    <mergeCell ref="R9:Z9"/>
+    <mergeCell ref="R12:Z12"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="F66:N66"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="I11:J11"/>
@@ -9015,54 +9118,110 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="R2:Z2"/>
-    <mergeCell ref="R6:Z6"/>
-    <mergeCell ref="R9:Z9"/>
-    <mergeCell ref="R12:Z12"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="F66:N66"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9137,7 +9296,7 @@
       </c>
       <c r="C2" s="25">
         <f>INDEX(Hoja1!$G$1:$G$250, (COUNTIF(DATOS!$J$4:$S$4, "&gt;0")-1)*13 + 12)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1">
         <f>_xlfn.RANK.EQ(B2, $B$2:$B$5) + COUNTIF($B$2:B2, B2) - 1</f>
@@ -9145,7 +9304,7 @@
       </c>
       <c r="E2" s="1">
         <f>+AVERAGEIF(DATOS!C$3:C$22, "&gt;0")</f>
-        <v>2</v>
+        <v>1.9375</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="29"/>
@@ -9162,16 +9321,16 @@
       </c>
       <c r="K2" s="43">
         <f>INDEX($C$2:$C$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L2" s="29"/>
       <c r="M2" s="47">
         <f>INDEX($E$2:$E$5, MATCH(I2, $A$2:$A$5, 0))</f>
-        <v>1.9285714285714286</v>
+        <v>1.875</v>
       </c>
       <c r="N2" s="48">
         <f>J2 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.76012223071046603</v>
+        <v>0.6651069518716578</v>
       </c>
       <c r="O2" s="49">
         <f>SUM(DATOS!D27:D46)</f>
@@ -9197,7 +9356,7 @@
       </c>
       <c r="C3" s="25">
         <f>INDEX(Hoja1!$I$1:$I$250, (COUNTIF(DATOS!$J$5:$S$5, "&gt;0")-1)*13 + 12)</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1">
         <f>_xlfn.RANK.EQ(B3, $B$2:$B$5) + COUNTIF($B$2:B3, B3) - 1</f>
@@ -9205,7 +9364,7 @@
       </c>
       <c r="E3" s="1">
         <f>+AVERAGEIF(DATOS!D$3:D$22, "&gt;0")</f>
-        <v>1.9285714285714286</v>
+        <v>1.875</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="29"/>
@@ -9222,20 +9381,20 @@
       </c>
       <c r="K3" s="43">
         <f t="shared" ref="K3:K5" si="2">INDEX($C$2:$C$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L3" s="29"/>
       <c r="M3" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I3, $A$2:$A$5, 0))</f>
-        <v>2</v>
+        <v>1.9375</v>
       </c>
       <c r="N3" s="39">
         <f>J3 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.75706646294881585</v>
+        <v>0.66243315508021394</v>
       </c>
       <c r="O3" s="41">
         <f>+SUM(DATOS!C27:C46)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="29"/>
       <c r="Q3" s="29"/>
@@ -9257,7 +9416,7 @@
       </c>
       <c r="C4" s="25">
         <f>INDEX(Hoja1!$K$1:$K$250, (COUNTIF(DATOS!$J$6:$S$6, "&gt;0")-1)*13 + 12)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1">
         <f>_xlfn.RANK.EQ(B4, $B$2:$B$5) + COUNTIF($B$2:B4, B4) - 1</f>
@@ -9265,7 +9424,7 @@
       </c>
       <c r="E4" s="1">
         <f>+AVERAGEIF(DATOS!E$3:E$22, "&gt;0")</f>
-        <v>3.5</v>
+        <v>3.4375</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="29"/>
@@ -9282,16 +9441,16 @@
       </c>
       <c r="K4" s="43">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I4, $A$2:$A$5, 0))</f>
-        <v>2.5714285714285716</v>
+        <v>2.75</v>
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.64858670741023683</v>
+        <v>0.56751336898395721</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -9317,7 +9476,7 @@
       </c>
       <c r="C5" s="26">
         <f>INDEX(Hoja1!$M$1:$M$250, (COUNTIF(DATOS!$J$7:$S$7, "&gt;0")-1)*13 + 12)</f>
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1">
         <f>_xlfn.RANK.EQ(B5, $B$2:$B$5) + COUNTIF($B$2:B5, B5) - 1</f>
@@ -9325,7 +9484,7 @@
       </c>
       <c r="E5" s="1">
         <f>+AVERAGEIF(DATOS!F$3:F$22, "&gt;0")</f>
-        <v>2.5714285714285716</v>
+        <v>2.75</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="29"/>
@@ -9342,16 +9501,16 @@
       </c>
       <c r="K5" s="44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L5" s="29"/>
       <c r="M5" s="46">
         <f>INDEX($E$2:$E$5, MATCH(I5, $A$2:$A$5, 0))</f>
-        <v>3.5</v>
+        <v>3.4375</v>
       </c>
       <c r="N5" s="40">
         <f>J5 / (COUNTIFS(DATOS!F3:F22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.51871657754010692</v>
+        <v>0.45387700534759357</v>
       </c>
       <c r="O5" s="42">
         <f>+SUM(DATOS!F27:F46)</f>
@@ -10036,25 +10195,25 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="105"/>
+      <c r="B2" s="101"/>
       <c r="C2" s="1" t="s">
         <v>44</v>
       </c>
@@ -10069,20 +10228,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="104" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10139,7 +10298,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="107"/>
+      <c r="A4" s="104"/>
       <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
@@ -10192,9 +10351,9 @@
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(G1)-1)*13 + 10))</f>
         <v>247.75</v>
       </c>
-      <c r="Q4" s="1" t="e">
+      <c r="Q4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>287.5</v>
       </c>
       <c r="R4" s="1" t="e">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10206,7 +10365,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="104" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -10261,9 +10420,9 @@
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(G1)-1)*13 + 10))</f>
         <v>248.75</v>
       </c>
-      <c r="Q5" s="1" t="e">
+      <c r="Q5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>287.25</v>
       </c>
       <c r="R5" s="1" t="e">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10275,7 +10434,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="107"/>
+      <c r="A6" s="104"/>
       <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
@@ -10328,9 +10487,9 @@
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(G1)-1)*13 + 10))</f>
         <v>169.75</v>
       </c>
-      <c r="Q6" s="1" t="e">
+      <c r="Q6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>196</v>
       </c>
       <c r="R6" s="1" t="e">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10342,7 +10501,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="104" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10397,9 +10556,9 @@
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(G1)-1)*13 + 10))</f>
         <v>212.25</v>
       </c>
-      <c r="Q7" s="1" t="e">
+      <c r="Q7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>233.25</v>
       </c>
       <c r="R7" s="1" t="e">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10411,7 +10570,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="107"/>
+      <c r="A8" s="104"/>
       <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
@@ -10446,7 +10605,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="104" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10483,7 +10642,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="107"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="1" t="s">
         <v>59</v>
       </c>
@@ -10518,7 +10677,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="104" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10555,7 +10714,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="107"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="1" t="s">
         <v>59</v>
       </c>
@@ -10590,7 +10749,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="104" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10627,7 +10786,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="107"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
@@ -10662,7 +10821,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="104" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10699,7 +10858,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="107"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="1" t="s">
         <v>59</v>
       </c>
@@ -10734,53 +10893,53 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="107"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="1">
         <f>Hoja1!G94</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1">
         <f>Hoja1!I94</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
         <f>Hoja1!K94</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1">
         <f>Hoja1!M94</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="107"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="1">
         <f>Hoja1!G95</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1">
         <f>Hoja1!I95</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1">
         <f>Hoja1!K95</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1">
         <f>Hoja1!M95</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="107"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
@@ -10803,7 +10962,7 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="107"/>
+      <c r="A20" s="104"/>
       <c r="B20" s="1" t="s">
         <v>59</v>
       </c>
@@ -10826,7 +10985,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="107"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
@@ -10849,7 +11008,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="107"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
@@ -10878,11 +11037,11 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1">
         <f>+COUNTIF(C3:C22,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" ref="D24:F24" si="0">+COUNTIF(D3:D22,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
@@ -10895,350 +11054,350 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="92" t="s">
+      <c r="B26" s="101"/>
+      <c r="C26" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="92" t="s">
+      <c r="D26" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="92" t="s">
+      <c r="E26" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="93" t="s">
         <v>47</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="107" t="s">
+      <c r="A27" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="105">
+      <c r="C27" s="101">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="105">
+      <c r="D27" s="101">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="105">
+      <c r="E27" s="101">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="105">
+      <c r="F27" s="101">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="105"/>
+      <c r="G27" s="101"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="104"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="101"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="107" t="s">
+      <c r="B29" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="105">
+      <c r="C29" s="101">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="105">
+      <c r="D29" s="101">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="105">
+      <c r="E29" s="101">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="105">
+      <c r="F29" s="101">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="105"/>
+      <c r="G29" s="101"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="107"/>
-      <c r="B30" s="107"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="104"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="107" t="s">
+      <c r="A31" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="105">
+      <c r="C31" s="101">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="105">
+      <c r="D31" s="101">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="105">
+      <c r="E31" s="101">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="105">
+      <c r="F31" s="101">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="105"/>
+      <c r="G31" s="101"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="107"/>
-      <c r="B32" s="107"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="101"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="107" t="s">
+      <c r="A33" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="105">
+      <c r="C33" s="101">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="105">
+      <c r="D33" s="101">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="105">
+      <c r="E33" s="101">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="105">
+      <c r="F33" s="101">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="105"/>
+      <c r="G33" s="101"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="107"/>
-      <c r="B34" s="107"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="101"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="107" t="s">
+      <c r="A35" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="105">
+      <c r="C35" s="101">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="105">
+      <c r="D35" s="101">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="105">
+      <c r="E35" s="101">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="105">
+      <c r="F35" s="101">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="105"/>
+      <c r="G35" s="101"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="107"/>
-      <c r="B36" s="107"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
+      <c r="A36" s="104"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="101"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="107" t="s">
+      <c r="A37" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="107" t="s">
+      <c r="B37" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="105">
+      <c r="C37" s="101">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="105">
+      <c r="D37" s="101">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="105">
+      <c r="E37" s="101">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="105">
+      <c r="F37" s="101">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="105"/>
+      <c r="G37" s="101"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="107"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
+      <c r="A38" s="104"/>
+      <c r="B38" s="104"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="F38" s="101"/>
+      <c r="G38" s="101"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="107" t="s">
+      <c r="A39" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="107" t="s">
+      <c r="B39" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="105">
+      <c r="C39" s="101">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="105">
+      <c r="D39" s="101">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="105">
+      <c r="E39" s="101">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="105">
+      <c r="F39" s="101">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="105"/>
+      <c r="G39" s="101"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="107"/>
-      <c r="B40" s="107"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
+      <c r="A40" s="104"/>
+      <c r="B40" s="104"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="101"/>
+      <c r="F40" s="101"/>
+      <c r="G40" s="101"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="107"/>
-      <c r="B41" s="107" t="s">
+      <c r="A41" s="104"/>
+      <c r="B41" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C41" s="101">
         <f>Hoja1!H96</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="105">
+        <v>1</v>
+      </c>
+      <c r="D41" s="101">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="105">
+      <c r="E41" s="101">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="105">
+      <c r="F41" s="101">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="105"/>
+      <c r="G41" s="101"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
+      <c r="A42" s="104"/>
+      <c r="B42" s="104"/>
+      <c r="C42" s="101"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="101"/>
+      <c r="F42" s="101"/>
+      <c r="G42" s="101"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="107"/>
-      <c r="B43" s="107" t="s">
+      <c r="A43" s="104"/>
+      <c r="B43" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="105">
+      <c r="C43" s="101">
         <f>Hoja1!H109</f>
         <v>0</v>
       </c>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="107"/>
-      <c r="B45" s="107" t="s">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="105">
+      <c r="C45" s="101">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="101"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="101"/>
+      <c r="F46" s="101"/>
+      <c r="G46" s="101"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -11247,7 +11406,7 @@
       <c r="B47" s="1"/>
       <c r="C47" s="1">
         <f>+SUM(C27:C46)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" ref="D47:F47" si="1">+SUM(D27:D46)</f>
@@ -11265,12 +11424,68 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
@@ -11287,68 +11502,12 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12187,33 +12346,33 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="105"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C30" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A29)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 6, CHOOSE(MOD(ROW(A29)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A29)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A29)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A29)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G30" s="1" t="str">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A29)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A29)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="105"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
@@ -12229,17 +12388,17 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A30)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="1" t="str">
+      <c r="F31" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A30)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A30)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G31" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A30)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A30)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="105"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -12255,17 +12414,17 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A31)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F32" s="1" t="str">
+      <c r="F32" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G32" s="1" t="str">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="105"/>
+      <c r="A33" s="101"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -12281,17 +12440,17 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A32)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="1" t="str">
+      <c r="F33" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G33" s="1" t="str">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="105"/>
+      <c r="A34" s="101"/>
       <c r="B34" s="1" t="s">
         <v>4</v>
       </c>
@@ -12317,7 +12476,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="105"/>
+      <c r="A35" s="101"/>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
@@ -12343,7 +12502,7 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="105"/>
+      <c r="A36" s="101"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -12369,7 +12528,7 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="105"/>
+      <c r="A37" s="101"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -12395,7 +12554,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="105"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -12421,7 +12580,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="105"/>
+      <c r="A39" s="101"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -12447,7 +12606,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="105"/>
+      <c r="A40" s="101"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -12473,7 +12632,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="105"/>
+      <c r="A41" s="101"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -12537,16 +12696,16 @@
       <c r="A3" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="D3" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="E3" s="93" t="s">
         <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -12672,7 +12831,7 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="104" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -12695,7 +12854,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="107"/>
+      <c r="A3" s="104"/>
       <c r="B3" s="1" t="s">
         <v>76</v>
       </c>
@@ -12718,7 +12877,7 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="107"/>
+      <c r="A4" s="104"/>
       <c r="B4" s="1" t="s">
         <v>77</v>
       </c>
@@ -12741,7 +12900,7 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="104" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -12758,7 +12917,7 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="107"/>
+      <c r="A6" s="104"/>
       <c r="B6" s="1" t="s">
         <v>76</v>
       </c>
@@ -12773,7 +12932,7 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="107"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="1" t="s">
         <v>77</v>
       </c>
@@ -12788,7 +12947,7 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="104" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -12805,7 +12964,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="107"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="1" t="s">
         <v>76</v>
       </c>
@@ -12820,7 +12979,7 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="107"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="1" t="s">
         <v>77</v>
       </c>
@@ -12843,7 +13002,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="104" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -12868,7 +13027,7 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="107"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="1" t="s">
         <v>76</v>
       </c>
@@ -12883,7 +13042,7 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="107"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
@@ -12898,7 +13057,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="107" t="s">
+      <c r="A14" s="104" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -12935,7 +13094,7 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="107"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="1" t="s">
         <v>76</v>
       </c>
@@ -12968,7 +13127,7 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="107"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="1" t="s">
         <v>77</v>
       </c>
@@ -13001,7 +13160,7 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="107" t="s">
+      <c r="A17" s="104" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -13031,7 +13190,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="107"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="1" t="s">
         <v>76</v>
       </c>
@@ -13059,7 +13218,7 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="107"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="1" t="s">
         <v>77</v>
       </c>
@@ -13087,7 +13246,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="107" t="s">
+      <c r="A20" s="104" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -13117,7 +13276,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="107"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
@@ -13143,7 +13302,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="107"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="1" t="s">
         <v>77</v>
       </c>
@@ -13169,7 +13328,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="107" t="s">
+      <c r="A23" s="104" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="1"/>
@@ -13189,7 +13348,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="107"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="1"/>
       <c r="C24" s="58"/>
       <c r="D24" s="58"/>
@@ -13207,7 +13366,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="107"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="1"/>
       <c r="C25" s="58"/>
       <c r="D25" s="58"/>
@@ -13225,7 +13384,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="104" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="1"/>
@@ -13245,7 +13404,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="107"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="1"/>
       <c r="C27" s="58"/>
       <c r="D27" s="58"/>
@@ -13263,7 +13422,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="107"/>
+      <c r="A28" s="104"/>
       <c r="B28" s="1"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
@@ -13281,7 +13440,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="104" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="1"/>
@@ -13301,7 +13460,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="107"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -13319,7 +13478,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="107"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -13397,7 +13556,7 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="106" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
@@ -13442,7 +13601,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="110"/>
+      <c r="A3" s="107"/>
       <c r="B3" s="62" t="s">
         <v>76</v>
       </c>
@@ -13485,7 +13644,7 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="110"/>
+      <c r="A4" s="107"/>
       <c r="B4" s="62" t="s">
         <v>77</v>
       </c>
@@ -13528,7 +13687,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="106" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
@@ -13550,7 +13709,7 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="110"/>
+      <c r="A6" s="107"/>
       <c r="B6" s="62" t="s">
         <v>76</v>
       </c>
@@ -13570,7 +13729,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="111"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="66" t="s">
         <v>77</v>
       </c>
@@ -13590,7 +13749,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="107" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
@@ -13612,7 +13771,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="110"/>
+      <c r="A9" s="107"/>
       <c r="B9" s="62" t="s">
         <v>76</v>
       </c>
@@ -13632,7 +13791,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="111"/>
+      <c r="A10" s="108"/>
       <c r="B10" s="66" t="s">
         <v>77</v>
       </c>
@@ -13664,7 +13823,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="107" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
@@ -13698,7 +13857,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="110"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="62" t="s">
         <v>76</v>
       </c>
@@ -13718,7 +13877,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="110"/>
+      <c r="A13" s="107"/>
       <c r="B13" s="62" t="s">
         <v>77</v>
       </c>
@@ -13738,7 +13897,7 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="109" t="s">
+      <c r="A14" s="106" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="64" t="s">
@@ -13772,7 +13931,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="110"/>
+      <c r="A15" s="107"/>
       <c r="B15" s="62" t="s">
         <v>76</v>
       </c>
@@ -13804,7 +13963,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="111"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="66" t="s">
         <v>77</v>
       </c>
@@ -13836,7 +13995,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="110" t="s">
+      <c r="A17" s="107" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="62" t="s">
@@ -13870,7 +14029,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="110"/>
+      <c r="A18" s="107"/>
       <c r="B18" s="62" t="s">
         <v>76</v>
       </c>
@@ -13902,7 +14061,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="110"/>
+      <c r="A19" s="107"/>
       <c r="B19" s="62" t="s">
         <v>77</v>
       </c>
@@ -13934,7 +14093,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="109" t="s">
+      <c r="A20" s="106" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="64" t="s">
@@ -13968,7 +14127,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="110"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="62" t="s">
         <v>76</v>
       </c>
@@ -14000,7 +14159,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="110"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="62" t="s">
         <v>77</v>
       </c>
@@ -14032,7 +14191,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="106" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -14066,7 +14225,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="110"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="62" t="s">
         <v>76</v>
       </c>
@@ -14098,7 +14257,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="111"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="66" t="s">
         <v>77</v>
       </c>
@@ -14130,7 +14289,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="110" t="s">
+      <c r="A26" s="107" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="62" t="s">
@@ -14164,7 +14323,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="110"/>
+      <c r="A27" s="107"/>
       <c r="B27" s="62" t="s">
         <v>76</v>
       </c>
@@ -14196,7 +14355,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="110"/>
+      <c r="A28" s="107"/>
       <c r="B28" s="62" t="s">
         <v>77</v>
       </c>
@@ -14228,7 +14387,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="109" t="s">
+      <c r="A29" s="106" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="64" t="s">
@@ -14262,7 +14421,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="110"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="62" t="s">
         <v>76</v>
       </c>
@@ -14294,7 +14453,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="111"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="66" t="s">
         <v>77</v>
       </c>
@@ -14412,16 +14571,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="96" t="s">
+      <c r="K1" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1"/>
@@ -14434,22 +14593,22 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="94" t="s">
+      <c r="K2" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="94" t="s">
+      <c r="L2" s="110"/>
+      <c r="M2" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="N2" s="95"/>
-      <c r="O2" s="94" t="s">
+      <c r="N2" s="110"/>
+      <c r="O2" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="94" t="s">
+      <c r="P2" s="110"/>
+      <c r="Q2" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="R2" s="95"/>
+      <c r="R2" s="110"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1"/>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{396A5B0D-60F6-40E8-B27B-0D0CB3D00B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{739B303C-CD1E-47B5-98D1-713E60938BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="99">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>FECHA 7</t>
+  </si>
+  <si>
+    <t>Rosario</t>
   </si>
   <si>
     <t>FECHA 8</t>
@@ -8303,7 +8306,9 @@
       <c r="N90" s="95"/>
     </row>
     <row r="92" spans="6:14">
-      <c r="F92" s="98"/>
+      <c r="F92" s="98" t="s">
+        <v>32</v>
+      </c>
       <c r="G92" s="98"/>
       <c r="H92" s="98"/>
       <c r="I92" s="98"/>
@@ -8315,7 +8320,7 @@
     </row>
     <row r="93" spans="6:14" ht="16.5" customHeight="1">
       <c r="F93" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>4</v>
@@ -8589,7 +8594,7 @@
     </row>
     <row r="106" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F106" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>4</v>
@@ -8823,7 +8828,7 @@
     </row>
     <row r="119" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F119" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>4</v>
@@ -9244,13 +9249,13 @@
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="A1" s="24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -9258,23 +9263,23 @@
       <c r="G1" s="29"/>
       <c r="H1" s="34"/>
       <c r="I1" s="35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L1" s="29"/>
       <c r="M1" s="50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N1" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O1" s="52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
@@ -9567,7 +9572,7 @@
       <c r="L7" s="29"/>
       <c r="M7" s="29"/>
       <c r="N7" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O7" s="29"/>
       <c r="P7" s="29"/>
@@ -10196,7 +10201,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="105"/>
       <c r="K1" s="105"/>
@@ -10211,20 +10216,20 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="101" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="101"/>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -10245,7 +10250,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1">
         <f>Hoja1!G3</f>
@@ -10267,40 +10272,40 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="104"/>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1">
         <f>Hoja1!G4</f>
@@ -10321,7 +10326,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10369,7 +10374,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1">
         <f>Hoja1!G16</f>
@@ -10390,7 +10395,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10436,7 +10441,7 @@
     <row r="6" spans="1:19">
       <c r="A6" s="104"/>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1">
         <f>Hoja1!G17</f>
@@ -10457,7 +10462,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10505,7 +10510,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <f>Hoja1!G29</f>
@@ -10526,7 +10531,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10572,7 +10577,7 @@
     <row r="8" spans="1:19">
       <c r="A8" s="104"/>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1">
         <f>Hoja1!G30</f>
@@ -10609,7 +10614,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1">
         <f>Hoja1!G42</f>
@@ -10644,7 +10649,7 @@
     <row r="10" spans="1:19">
       <c r="A10" s="104"/>
       <c r="B10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="1">
         <f>Hoja1!G43</f>
@@ -10678,10 +10683,10 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1">
         <f>Hoja1!G55</f>
@@ -10716,7 +10721,7 @@
     <row r="12" spans="1:19">
       <c r="A12" s="104"/>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1">
         <f>Hoja1!G56</f>
@@ -10750,10 +10755,10 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="104" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1">
         <f>Hoja1!G68</f>
@@ -10788,7 +10793,7 @@
     <row r="14" spans="1:19">
       <c r="A14" s="104"/>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1">
         <f>Hoja1!G69</f>
@@ -10822,10 +10827,10 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1">
         <f>Hoja1!G81</f>
@@ -10860,7 +10865,7 @@
     <row r="16" spans="1:19">
       <c r="A16" s="104"/>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1">
         <f>Hoja1!G82</f>
@@ -10895,7 +10900,7 @@
     <row r="17" spans="1:7">
       <c r="A17" s="104"/>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1">
         <f>Hoja1!G94</f>
@@ -10918,7 +10923,7 @@
     <row r="18" spans="1:7">
       <c r="A18" s="104"/>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1">
         <f>Hoja1!G95</f>
@@ -10941,7 +10946,7 @@
     <row r="19" spans="1:7">
       <c r="A19" s="104"/>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1">
         <f>Hoja1!G109</f>
@@ -10964,7 +10969,7 @@
     <row r="20" spans="1:7">
       <c r="A20" s="104"/>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1">
         <f>Hoja1!G110</f>
@@ -10987,7 +10992,7 @@
     <row r="21" spans="1:7">
       <c r="A21" s="104"/>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1">
         <f>Hoja1!G122</f>
@@ -11010,7 +11015,7 @@
     <row r="22" spans="1:7">
       <c r="A22" s="104"/>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1">
         <f>Hoja1!G123</f>
@@ -11032,7 +11037,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -11055,7 +11060,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="101" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="101"/>
       <c r="C25" s="101"/>
@@ -11066,20 +11071,20 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="101" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="101"/>
       <c r="C26" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" s="93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="93" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F26" s="93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -11088,7 +11093,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="101">
         <f>Hoja1!H5</f>
@@ -11122,7 +11127,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="101">
         <f>Hoja1!H18</f>
@@ -11156,7 +11161,7 @@
         <v>18</v>
       </c>
       <c r="B31" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" s="101">
         <f>Hoja1!H31</f>
@@ -11190,7 +11195,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" s="101">
         <f>Hoja1!H44</f>
@@ -11221,10 +11226,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B35" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" s="101">
         <f>Hoja1!H57</f>
@@ -11255,10 +11260,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="104" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C37" s="101">
         <f>Hoja1!H70</f>
@@ -11289,10 +11294,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B39" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" s="101">
         <f>Hoja1!H83</f>
@@ -11324,7 +11329,7 @@
     <row r="41" spans="1:7">
       <c r="A41" s="104"/>
       <c r="B41" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C41" s="101">
         <f>Hoja1!H96</f>
@@ -11356,7 +11361,7 @@
     <row r="43" spans="1:7">
       <c r="A43" s="104"/>
       <c r="B43" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C43" s="101">
         <f>Hoja1!H109</f>
@@ -11379,7 +11384,7 @@
     <row r="45" spans="1:7">
       <c r="A45" s="104"/>
       <c r="B45" s="104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45" s="101">
         <f>Hoja1!H122</f>
@@ -11524,25 +11529,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -12011,7 +12016,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
@@ -12039,7 +12044,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -12067,7 +12072,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -12095,7 +12100,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -12123,7 +12128,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>4</v>
@@ -12151,7 +12156,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -12179,7 +12184,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -12207,7 +12212,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -12235,7 +12240,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>4</v>
@@ -12263,7 +12268,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -12291,7 +12296,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -12319,7 +12324,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -12682,10 +12687,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -12694,22 +12699,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="93" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -12835,7 +12840,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="58">
         <v>1.0631828703703704E-3</v>
@@ -12856,7 +12861,7 @@
     <row r="3" spans="1:11">
       <c r="A3" s="104"/>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="58">
         <v>1.0327314814814815E-3</v>
@@ -12879,7 +12884,7 @@
     <row r="4" spans="1:11">
       <c r="A4" s="104"/>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="58">
         <v>1.0267824074074075E-3</v>
@@ -12904,7 +12909,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
@@ -12919,7 +12924,7 @@
     <row r="6" spans="1:11">
       <c r="A6" s="104"/>
       <c r="B6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -12934,7 +12939,7 @@
     <row r="7" spans="1:11">
       <c r="A7" s="104"/>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
@@ -12951,7 +12956,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -12966,7 +12971,7 @@
     <row r="9" spans="1:11">
       <c r="A9" s="104"/>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="58"/>
       <c r="D9" s="58"/>
@@ -12981,7 +12986,7 @@
     <row r="10" spans="1:11">
       <c r="A10" s="104"/>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="58">
         <v>8.9045138888888887E-4</v>
@@ -13006,7 +13011,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="58">
         <v>8.6745370370370383E-4</v>
@@ -13029,7 +13034,7 @@
     <row r="12" spans="1:11">
       <c r="A12" s="104"/>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -13044,7 +13049,7 @@
     <row r="13" spans="1:11">
       <c r="A13" s="104"/>
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -13058,10 +13063,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="58">
         <v>8.2178240740740736E-4</v>
@@ -13096,7 +13101,7 @@
     <row r="15" spans="1:11">
       <c r="A15" s="104"/>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" s="58">
         <v>8.1365740740740736E-4</v>
@@ -13129,7 +13134,7 @@
     <row r="16" spans="1:11">
       <c r="A16" s="104"/>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="58">
         <v>8.0902777777777787E-4</v>
@@ -13161,10 +13166,10 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="104" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="58">
         <v>9.2799768518518524E-4</v>
@@ -13192,7 +13197,7 @@
     <row r="18" spans="1:16">
       <c r="A18" s="104"/>
       <c r="B18" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="58">
         <v>9.2737268518518516E-4</v>
@@ -13220,7 +13225,7 @@
     <row r="19" spans="1:16">
       <c r="A19" s="104"/>
       <c r="B19" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="58">
         <v>9.2612268518518521E-4</v>
@@ -13247,10 +13252,10 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" s="58">
         <v>1.2464004629629628E-3</v>
@@ -13278,7 +13283,7 @@
     <row r="21" spans="1:16">
       <c r="A21" s="104"/>
       <c r="B21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="58">
         <v>1.2324652777777779E-3</v>
@@ -13304,7 +13309,7 @@
     <row r="22" spans="1:16">
       <c r="A22" s="104"/>
       <c r="B22" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" s="58">
         <v>1.2377777777777777E-3</v>
@@ -13329,7 +13334,7 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="104" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="58"/>
@@ -13385,7 +13390,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="58"/>
@@ -13441,7 +13446,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="58"/>
@@ -13539,7 +13544,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -13560,7 +13565,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="69">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -13581,7 +13586,7 @@
       <c r="G2" s="58"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="1">
         <f>IF('Carga Tiempos'!H14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!H14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
@@ -13603,7 +13608,7 @@
     <row r="3" spans="1:16">
       <c r="A3" s="107"/>
       <c r="B3" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="69">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -13624,7 +13629,7 @@
       <c r="G3" s="58"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" s="1">
         <f>IF('Carga Tiempos'!H15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!H15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
@@ -13646,7 +13651,7 @@
     <row r="4" spans="1:16">
       <c r="A4" s="107"/>
       <c r="B4" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="69">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -13667,7 +13672,7 @@
       <c r="G4" s="58"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="1">
         <f>IF('Carga Tiempos'!H16=MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16),0,'Carga Tiempos'!H16-MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16))</f>
@@ -13691,7 +13696,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="60"/>
@@ -13711,7 +13716,7 @@
     <row r="6" spans="1:16">
       <c r="A6" s="107"/>
       <c r="B6" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
@@ -13731,7 +13736,7 @@
     <row r="7" spans="1:16">
       <c r="A7" s="108"/>
       <c r="B7" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="61"/>
@@ -13753,7 +13758,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
@@ -13773,7 +13778,7 @@
     <row r="9" spans="1:16">
       <c r="A9" s="107"/>
       <c r="B9" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="68"/>
@@ -13793,7 +13798,7 @@
     <row r="10" spans="1:16">
       <c r="A10" s="108"/>
       <c r="B10" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="71">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -13827,7 +13832,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="69">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -13859,7 +13864,7 @@
     <row r="12" spans="1:16">
       <c r="A12" s="107"/>
       <c r="B12" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="68"/>
@@ -13879,7 +13884,7 @@
     <row r="13" spans="1:16">
       <c r="A13" s="107"/>
       <c r="B13" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="68"/>
@@ -13898,10 +13903,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="70">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -13933,7 +13938,7 @@
     <row r="15" spans="1:16">
       <c r="A15" s="107"/>
       <c r="B15" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" s="69">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -13965,7 +13970,7 @@
     <row r="16" spans="1:16">
       <c r="A16" s="108"/>
       <c r="B16" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="71">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -13996,10 +14001,10 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="107" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="69">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -14031,7 +14036,7 @@
     <row r="18" spans="1:16">
       <c r="A18" s="107"/>
       <c r="B18" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="69">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -14063,7 +14068,7 @@
     <row r="19" spans="1:16">
       <c r="A19" s="107"/>
       <c r="B19" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="69">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -14094,10 +14099,10 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="106" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" s="70">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -14129,7 +14134,7 @@
     <row r="21" spans="1:16">
       <c r="A21" s="107"/>
       <c r="B21" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="69">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -14161,7 +14166,7 @@
     <row r="22" spans="1:16">
       <c r="A22" s="107"/>
       <c r="B22" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" s="69">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -14192,10 +14197,10 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="106" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="70">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
@@ -14227,7 +14232,7 @@
     <row r="24" spans="1:16">
       <c r="A24" s="107"/>
       <c r="B24" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" s="69">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
@@ -14259,7 +14264,7 @@
     <row r="25" spans="1:16">
       <c r="A25" s="108"/>
       <c r="B25" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="71">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
@@ -14290,10 +14295,10 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="69">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
@@ -14325,7 +14330,7 @@
     <row r="27" spans="1:16">
       <c r="A27" s="107"/>
       <c r="B27" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -14357,7 +14362,7 @@
     <row r="28" spans="1:16">
       <c r="A28" s="107"/>
       <c r="B28" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" s="69">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -14388,10 +14393,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="70">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -14423,7 +14428,7 @@
     <row r="30" spans="1:16">
       <c r="A30" s="107"/>
       <c r="B30" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" s="69">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -14455,7 +14460,7 @@
     <row r="31" spans="1:16">
       <c r="A31" s="108"/>
       <c r="B31" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="71">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -14572,7 +14577,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="34.5">
       <c r="K1" s="111" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L1" s="111"/>
       <c r="M1" s="111"/>
@@ -14594,19 +14599,19 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" s="110"/>
       <c r="M2" s="109" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" s="110"/>
       <c r="O2" s="109" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2" s="110"/>
       <c r="Q2" s="109" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R2" s="110"/>
     </row>
@@ -14628,19 +14633,19 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="M3" s="83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
       <c r="O3" s="86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P3" s="77">
         <v>1.2796759259259259E-3</v>
       </c>
       <c r="Q3" s="86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R3" s="77">
         <v>1.2796759259259259E-3</v>
@@ -14664,19 +14669,19 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
       <c r="O4" s="83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P4" s="77">
         <v>1.2429976851851853E-3</v>
       </c>
       <c r="Q4" s="83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R4" s="77">
         <v>1.2429976851851853E-3</v>
@@ -14700,19 +14705,19 @@
         <v>1.2545601851851852E-3</v>
       </c>
       <c r="M5" s="83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
       <c r="O5" s="87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P5" s="77">
         <v>1.2377777777777777E-3</v>
       </c>
       <c r="Q5" s="87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R5" s="77">
         <v>1.2377777777777777E-3</v>
@@ -14736,19 +14741,19 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P6" s="77">
         <v>1.3249884259259259E-3</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R6" s="77">
         <v>1.3249884259259259E-3</v>
@@ -14772,19 +14777,19 @@
         <v>1.260300925925926E-3</v>
       </c>
       <c r="M7" s="83" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
       <c r="O7" s="87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P7" s="77">
         <v>1.2426273148148149E-3</v>
       </c>
       <c r="Q7" s="87" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R7" s="77">
         <v>1.2426273148148149E-3</v>
@@ -14808,19 +14813,19 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P8" s="77">
         <v>1.2478472222222222E-3</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R8" s="77">
         <v>1.2478472222222222E-3</v>
@@ -14844,19 +14849,19 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P9" s="77">
         <v>1.248275462962963E-3</v>
       </c>
       <c r="Q9" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R9" s="77">
         <v>1.248275462962963E-3</v>
@@ -14880,19 +14885,19 @@
         <v>1.2430787037037037E-3</v>
       </c>
       <c r="M10" s="83" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
       <c r="O10" s="87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P10" s="77">
         <v>1.2653240740740741E-3</v>
       </c>
       <c r="Q10" s="87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R10" s="77">
         <v>1.2653240740740741E-3</v>
@@ -14916,19 +14921,19 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
       <c r="O11" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P11" s="77">
         <v>1.6837615740740741E-3</v>
       </c>
       <c r="Q11" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R11" s="77">
         <v>1.6837615740740741E-3</v>
@@ -14952,19 +14957,19 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
       <c r="O12" s="83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P12" s="77">
         <v>1.543287037037037E-3</v>
       </c>
       <c r="Q12" s="83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R12" s="77">
         <v>1.543287037037037E-3</v>
@@ -14988,19 +14993,19 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
       <c r="O13" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P13" s="77">
         <v>1.9202893518518521E-3</v>
       </c>
       <c r="Q13" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R13" s="77">
         <v>1.9202893518518521E-3</v>
@@ -15024,19 +15029,19 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
       <c r="O14" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P14" s="77">
         <v>1.2480787037037037E-3</v>
       </c>
       <c r="Q14" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R14" s="77">
         <v>1.2480787037037037E-3</v>
@@ -15060,19 +15065,19 @@
         <v>1.236238425925926E-3</v>
       </c>
       <c r="M15" s="83" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
       <c r="O15" s="87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P15" s="77">
         <v>1.241701388888889E-3</v>
       </c>
       <c r="Q15" s="87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R15" s="77">
         <v>1.241701388888889E-3</v>
@@ -15096,19 +15101,19 @@
         <v>1.2310648148148148E-3</v>
       </c>
       <c r="M16" s="83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
       <c r="O16" s="88" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P16" s="77">
         <v>1.2480208333333334E-3</v>
       </c>
       <c r="Q16" s="88" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R16" s="77">
         <v>1.2480208333333334E-3</v>
@@ -15132,19 +15137,19 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
       <c r="O17" s="85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P17" s="80">
         <v>1.2779629629629629E-3</v>
       </c>
       <c r="Q17" s="85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R17" s="80">
         <v>1.2779629629629629E-3</v>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{739B303C-CD1E-47B5-98D1-713E60938BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A00ABAB9-1C6E-42EF-9443-BBADE8AD419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -9239,10 +9239,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="1" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="12" width="11.42578125"/>
     <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -9296,8 +9296,8 @@
         <v>4</v>
       </c>
       <c r="B2" s="17">
-        <f>+SUM(Hoja1!$G8,Hoja1!$G21,Hoja1!$G34,Hoja1!$G47,Hoja1!$G60,Hoja1!G73,Hoja1!G86)</f>
-        <v>247.75</v>
+        <f>+SUM(Hoja1!$G8,Hoja1!$G21,Hoja1!$G34,Hoja1!$G47,Hoja1!$G60,Hoja1!G73,Hoja1!G86,Hoja1!G99)</f>
+        <v>287.5</v>
       </c>
       <c r="C2" s="25">
         <f>INDEX(Hoja1!$G$1:$G$250, (COUNTIF(DATOS!$J$4:$S$4, "&gt;0")-1)*13 + 12)</f>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="D2" s="1">
         <f>_xlfn.RANK.EQ(B2, $B$2:$B$5) + COUNTIF($B$2:B2, B2) - 1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <f>+AVERAGEIF(DATOS!C$3:C$22, "&gt;0")</f>
@@ -9318,24 +9318,24 @@
       </c>
       <c r="I2" s="31" t="str">
         <f>INDEX($A$2:$A$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>Pablo</v>
+        <v>Agus</v>
       </c>
       <c r="J2" s="31">
         <f>INDEX($B$2:$B$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>248.75</v>
+        <v>287.5</v>
       </c>
       <c r="K2" s="43">
         <f>INDEX($C$2:$C$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L2" s="29"/>
       <c r="M2" s="47">
         <f>INDEX($E$2:$E$5, MATCH(I2, $A$2:$A$5, 0))</f>
-        <v>1.875</v>
+        <v>1.9375</v>
       </c>
       <c r="N2" s="48">
         <f>J2 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.6651069518716578</v>
+        <v>0.76871657754010692</v>
       </c>
       <c r="O2" s="49">
         <f>SUM(DATOS!D27:D46)</f>
@@ -9356,8 +9356,8 @@
         <v>6</v>
       </c>
       <c r="B3" s="21">
-        <f>+SUM(Hoja1!$I8,Hoja1!$I21,Hoja1!$I34,Hoja1!$I47,Hoja1!$I60,Hoja1!I73,Hoja1!I86)</f>
-        <v>248.75</v>
+        <f>+SUM(Hoja1!$I8,Hoja1!$I21,Hoja1!$I34,Hoja1!$I47,Hoja1!$I60,Hoja1!I73,Hoja1!I86,Hoja1!I99)</f>
+        <v>287.25</v>
       </c>
       <c r="C3" s="25">
         <f>INDEX(Hoja1!$I$1:$I$250, (COUNTIF(DATOS!$J$5:$S$5, "&gt;0")-1)*13 + 12)</f>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D3" s="1">
         <f>_xlfn.RANK.EQ(B3, $B$2:$B$5) + COUNTIF($B$2:B3, B3) - 1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <f>+AVERAGEIF(DATOS!D$3:D$22, "&gt;0")</f>
@@ -9378,24 +9378,24 @@
       </c>
       <c r="I3" s="31" t="str">
         <f t="shared" ref="I3:I5" si="0">INDEX($A$2:$A$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>Agus</v>
+        <v>Pablo</v>
       </c>
       <c r="J3" s="31">
         <f t="shared" ref="J3:J5" si="1">INDEX($B$2:$B$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>247.75</v>
+        <v>287.25</v>
       </c>
       <c r="K3" s="43">
         <f t="shared" ref="K3:K5" si="2">INDEX($C$2:$C$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L3" s="29"/>
       <c r="M3" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I3, $A$2:$A$5, 0))</f>
-        <v>1.9375</v>
+        <v>1.875</v>
       </c>
       <c r="N3" s="39">
         <f>J3 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.66243315508021394</v>
+        <v>0.76804812834224601</v>
       </c>
       <c r="O3" s="41">
         <f>+SUM(DATOS!C27:C46)</f>
@@ -9416,8 +9416,8 @@
         <v>7</v>
       </c>
       <c r="B4" s="21">
-        <f>+SUM(Hoja1!K8,Hoja1!K21,Hoja1!K34,Hoja1!K47,Hoja1!K60,Hoja1!K73,Hoja1!K86)</f>
-        <v>169.75</v>
+        <f>+SUM(Hoja1!K8,Hoja1!K21,Hoja1!K34,Hoja1!K47,Hoja1!K60,Hoja1!K73,Hoja1!K86,Hoja1!K99)</f>
+        <v>196</v>
       </c>
       <c r="C4" s="25">
         <f>INDEX(Hoja1!$K$1:$K$250, (COUNTIF(DATOS!$J$6:$S$6, "&gt;0")-1)*13 + 12)</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="J4" s="31">
         <f t="shared" si="1"/>
-        <v>212.25</v>
+        <v>233.25</v>
       </c>
       <c r="K4" s="43">
         <f t="shared" si="2"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.56751336898395721</v>
+        <v>0.62366310160427807</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -9476,8 +9476,8 @@
         <v>8</v>
       </c>
       <c r="B5" s="20">
-        <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86)</f>
-        <v>212.25</v>
+        <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86,Hoja1!M99)</f>
+        <v>233.25</v>
       </c>
       <c r="C5" s="26">
         <f>INDEX(Hoja1!$M$1:$M$250, (COUNTIF(DATOS!$J$7:$S$7, "&gt;0")-1)*13 + 12)</f>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="J5" s="33">
         <f t="shared" si="1"/>
-        <v>169.75</v>
+        <v>196</v>
       </c>
       <c r="K5" s="44">
         <f t="shared" si="2"/>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="N5" s="40">
         <f>J5 / (COUNTIFS(DATOS!F3:F22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.45387700534759357</v>
+        <v>0.52406417112299464</v>
       </c>
       <c r="O5" s="42">
         <f>+SUM(DATOS!F27:F46)</f>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A00ABAB9-1C6E-42EF-9443-BBADE8AD419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B76A17BE-6EA0-4506-951E-9FEFEA8AAF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId9"/>
+    <pivotCache cacheId="138" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="106">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -273,6 +273,9 @@
     <t>TERMAS</t>
   </si>
   <si>
+    <t>ROSARIO</t>
+  </si>
+  <si>
     <t>Total victorias</t>
   </si>
   <si>
@@ -324,13 +327,13 @@
     <t>Pablo C2</t>
   </si>
   <si>
-    <t>Eze C2</t>
-  </si>
-  <si>
     <t>Agus C2</t>
   </si>
   <si>
     <t>Juandi C2</t>
+  </si>
+  <si>
+    <t>Eze C2</t>
   </si>
   <si>
     <t>1</t>
@@ -377,6 +380,24 @@
   <si>
     <t>15</t>
   </si>
+  <si>
+    <t>ROSARIO C1</t>
+  </si>
+  <si>
+    <t>ROSARIO C2</t>
+  </si>
+  <si>
+    <t>Pablo C1</t>
+  </si>
+  <si>
+    <t>Agus C1</t>
+  </si>
+  <si>
+    <t>Juandi C1</t>
+  </si>
+  <si>
+    <t>Eze C1</t>
+  </si>
 </sst>
 </file>
 
@@ -388,12 +409,18 @@
     <numFmt numFmtId="166" formatCode="mm:ss.000"/>
     <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -435,6 +462,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -456,7 +490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -963,11 +997,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCDFE5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1127,30 +1170,40 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="47" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="47" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1185,7 +1238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1197,15 +1250,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1741,7 +1803,7 @@
                   <c:v>169.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>196</c:v>
+                  <c:v>193.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -1863,7 +1925,7 @@
                   <c:v>212.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>233.25</c:v>
+                  <c:v>235.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>#N/A</c:v>
@@ -5056,7 +5118,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5707,26 +5769,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101" t="s">
+      <c r="A1" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="101"/>
+      <c r="D1" s="105"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="98" t="s">
+      <c r="F1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5785,17 +5847,17 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="98" t="s">
+      <c r="R2" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
+      <c r="S2" s="102"/>
+      <c r="T2" s="102"/>
+      <c r="U2" s="102"/>
+      <c r="V2" s="102"/>
+      <c r="W2" s="102"/>
+      <c r="X2" s="102"/>
+      <c r="Y2" s="102"/>
+      <c r="Z2" s="102"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="92">
@@ -6004,17 +6066,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="98" t="s">
+      <c r="R6" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="98"/>
-      <c r="T6" s="98"/>
-      <c r="U6" s="98"/>
-      <c r="V6" s="98"/>
-      <c r="W6" s="98"/>
-      <c r="X6" s="98"/>
-      <c r="Y6" s="98"/>
-      <c r="Z6" s="98"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="102"/>
+      <c r="U6" s="102"/>
+      <c r="V6" s="102"/>
+      <c r="W6" s="102"/>
+      <c r="X6" s="102"/>
+      <c r="Y6" s="102"/>
+      <c r="Z6" s="102"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6076,26 +6138,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="103">
+      <c r="G8" s="107">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="100"/>
-      <c r="I8" s="103">
+      <c r="H8" s="104"/>
+      <c r="I8" s="107">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="100"/>
-      <c r="K8" s="103">
+      <c r="J8" s="104"/>
+      <c r="K8" s="107">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="100"/>
-      <c r="M8" s="103">
+      <c r="L8" s="104"/>
+      <c r="M8" s="107">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="100"/>
+      <c r="N8" s="104"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1">
@@ -6133,17 +6195,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="98" t="s">
+      <c r="R9" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
+      <c r="S9" s="102"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="102"/>
+      <c r="V9" s="102"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="102"/>
+      <c r="Y9" s="102"/>
+      <c r="Z9" s="102"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6154,26 +6216,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="102">
+      <c r="G10" s="106">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102">
+      <c r="H10" s="106"/>
+      <c r="I10" s="106">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102">
+      <c r="J10" s="106"/>
+      <c r="K10" s="106">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102">
+      <c r="L10" s="106"/>
+      <c r="M10" s="106">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="102"/>
+      <c r="N10" s="106"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6206,26 +6268,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="94">
+      <c r="G11" s="98">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="94">
+      <c r="H11" s="99"/>
+      <c r="I11" s="98">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="94">
+      <c r="J11" s="99"/>
+      <c r="K11" s="98">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="95"/>
-      <c r="M11" s="94">
+      <c r="L11" s="99"/>
+      <c r="M11" s="98">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="95"/>
+      <c r="N11" s="99"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6248,40 +6310,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="94">
+      <c r="G12" s="98">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="95"/>
-      <c r="I12" s="94">
+      <c r="H12" s="99"/>
+      <c r="I12" s="98">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="95"/>
-      <c r="K12" s="94">
+      <c r="J12" s="99"/>
+      <c r="K12" s="98">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="95"/>
-      <c r="M12" s="94">
+      <c r="L12" s="99"/>
+      <c r="M12" s="98">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="95"/>
+      <c r="N12" s="99"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="98" t="s">
+      <c r="R12" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="102"/>
+      <c r="U12" s="102"/>
+      <c r="V12" s="102"/>
+      <c r="W12" s="102"/>
+      <c r="X12" s="102"/>
+      <c r="Y12" s="102"/>
+      <c r="Z12" s="102"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6327,17 +6389,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6566,26 +6628,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="103">
+      <c r="G21" s="107">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="100"/>
-      <c r="I21" s="99">
+      <c r="H21" s="104"/>
+      <c r="I21" s="103">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="100"/>
-      <c r="K21" s="99">
+      <c r="J21" s="104"/>
+      <c r="K21" s="103">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="100"/>
-      <c r="M21" s="99">
+      <c r="L21" s="104"/>
+      <c r="M21" s="103">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="100"/>
+      <c r="N21" s="104"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1">
@@ -6621,26 +6683,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="96">
+      <c r="G23" s="100">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="97"/>
-      <c r="I23" s="96">
+      <c r="H23" s="101"/>
+      <c r="I23" s="100">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="97"/>
-      <c r="K23" s="96">
+      <c r="J23" s="101"/>
+      <c r="K23" s="100">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="97"/>
-      <c r="M23" s="96">
+      <c r="L23" s="101"/>
+      <c r="M23" s="100">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="97"/>
+      <c r="N23" s="101"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6654,26 +6716,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="94">
+      <c r="G24" s="98">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="95"/>
-      <c r="I24" s="94">
+      <c r="H24" s="99"/>
+      <c r="I24" s="98">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="95"/>
-      <c r="K24" s="94">
+      <c r="J24" s="99"/>
+      <c r="K24" s="98">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="95"/>
-      <c r="M24" s="94">
+      <c r="L24" s="99"/>
+      <c r="M24" s="98">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="95"/>
+      <c r="N24" s="99"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6687,26 +6749,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="94">
+      <c r="G25" s="98">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="95"/>
-      <c r="I25" s="94">
+      <c r="H25" s="99"/>
+      <c r="I25" s="98">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="95"/>
-      <c r="K25" s="94">
+      <c r="J25" s="99"/>
+      <c r="K25" s="98">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="95"/>
-      <c r="M25" s="94">
+      <c r="L25" s="99"/>
+      <c r="M25" s="98">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="95"/>
+      <c r="N25" s="99"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6736,17 +6798,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="98" t="s">
+      <c r="F27" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
-      <c r="N27" s="98"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="102"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="102"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -6950,26 +7012,26 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="99">
+      <c r="G34" s="103">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="100"/>
-      <c r="I34" s="99">
+      <c r="H34" s="104"/>
+      <c r="I34" s="103">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="100"/>
-      <c r="K34" s="99">
+      <c r="J34" s="104"/>
+      <c r="K34" s="103">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="100"/>
-      <c r="M34" s="99">
+      <c r="L34" s="104"/>
+      <c r="M34" s="103">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="100"/>
+      <c r="N34" s="104"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1">
@@ -7007,26 +7069,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="96">
+      <c r="G36" s="100">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="97"/>
-      <c r="I36" s="96">
+      <c r="H36" s="101"/>
+      <c r="I36" s="100">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="97"/>
-      <c r="K36" s="96">
+      <c r="J36" s="101"/>
+      <c r="K36" s="100">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="97"/>
-      <c r="M36" s="96">
+      <c r="L36" s="101"/>
+      <c r="M36" s="100">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="97"/>
+      <c r="N36" s="101"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7041,26 +7103,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="94">
+      <c r="G37" s="98">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="95"/>
-      <c r="I37" s="94">
+      <c r="H37" s="99"/>
+      <c r="I37" s="98">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="95"/>
-      <c r="K37" s="94">
+      <c r="J37" s="99"/>
+      <c r="K37" s="98">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="95"/>
-      <c r="M37" s="94">
+      <c r="L37" s="99"/>
+      <c r="M37" s="98">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="95"/>
+      <c r="N37" s="99"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7075,26 +7137,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="94">
+      <c r="G38" s="98">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="95"/>
-      <c r="I38" s="94">
+      <c r="H38" s="99"/>
+      <c r="I38" s="98">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="95"/>
-      <c r="K38" s="94">
+      <c r="J38" s="99"/>
+      <c r="K38" s="98">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="95"/>
-      <c r="M38" s="94">
+      <c r="L38" s="99"/>
+      <c r="M38" s="98">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="95"/>
+      <c r="N38" s="99"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7123,23 +7185,20 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="1">
-        <f>+SUM(J29*0.7)</f>
-        <v>17.5</v>
-      </c>
+      <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="98" t="s">
+      <c r="F40" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="98"/>
-      <c r="H40" s="98"/>
-      <c r="I40" s="98"/>
-      <c r="J40" s="98"/>
-      <c r="K40" s="98"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="98"/>
-      <c r="N40" s="98"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="102"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -7350,26 +7409,26 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="99">
+      <c r="G47" s="103">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="100"/>
-      <c r="I47" s="99">
+      <c r="H47" s="104"/>
+      <c r="I47" s="103">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="100"/>
-      <c r="K47" s="99">
+      <c r="J47" s="104"/>
+      <c r="K47" s="103">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="100"/>
-      <c r="M47" s="99">
+      <c r="L47" s="104"/>
+      <c r="M47" s="103">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="100"/>
+      <c r="N47" s="104"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1">
@@ -7407,76 +7466,76 @@
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="96">
+      <c r="G49" s="100">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="97"/>
-      <c r="I49" s="96">
+      <c r="H49" s="101"/>
+      <c r="I49" s="100">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="97"/>
-      <c r="K49" s="96">
+      <c r="J49" s="101"/>
+      <c r="K49" s="100">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="97"/>
-      <c r="M49" s="96">
+      <c r="L49" s="101"/>
+      <c r="M49" s="100">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="97"/>
+      <c r="N49" s="101"/>
     </row>
     <row r="50" spans="6:14">
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="94">
+      <c r="G50" s="98">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="95"/>
-      <c r="I50" s="94">
+      <c r="H50" s="99"/>
+      <c r="I50" s="98">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="95"/>
-      <c r="K50" s="94">
+      <c r="J50" s="99"/>
+      <c r="K50" s="98">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="95"/>
-      <c r="M50" s="94">
+      <c r="L50" s="99"/>
+      <c r="M50" s="98">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="95"/>
+      <c r="N50" s="99"/>
     </row>
     <row r="51" spans="6:14">
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="94">
+      <c r="G51" s="98">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="95"/>
-      <c r="I51" s="94">
+      <c r="H51" s="99"/>
+      <c r="I51" s="98">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="95"/>
-      <c r="K51" s="94">
+      <c r="J51" s="99"/>
+      <c r="K51" s="98">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="95"/>
-      <c r="M51" s="94">
+      <c r="L51" s="99"/>
+      <c r="M51" s="98">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="95"/>
+      <c r="N51" s="99"/>
     </row>
     <row r="52" spans="6:14">
       <c r="F52" s="27"/>
@@ -7490,17 +7549,17 @@
       <c r="N52" s="28"/>
     </row>
     <row r="53" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F53" s="98" t="s">
+      <c r="F53" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="98"/>
-      <c r="H53" s="98"/>
-      <c r="I53" s="98"/>
-      <c r="J53" s="98"/>
-      <c r="K53" s="98"/>
-      <c r="L53" s="98"/>
-      <c r="M53" s="98"/>
-      <c r="N53" s="98"/>
+      <c r="G53" s="102"/>
+      <c r="H53" s="102"/>
+      <c r="I53" s="102"/>
+      <c r="J53" s="102"/>
+      <c r="K53" s="102"/>
+      <c r="L53" s="102"/>
+      <c r="M53" s="102"/>
+      <c r="N53" s="102"/>
     </row>
     <row r="54" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F54" s="13" t="s">
@@ -7646,26 +7705,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="99">
+      <c r="G60" s="103">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="100"/>
-      <c r="I60" s="99">
+      <c r="H60" s="104"/>
+      <c r="I60" s="103">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="100"/>
-      <c r="K60" s="99">
+      <c r="J60" s="104"/>
+      <c r="K60" s="103">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="100"/>
-      <c r="M60" s="99">
+      <c r="L60" s="104"/>
+      <c r="M60" s="103">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="100"/>
+      <c r="N60" s="104"/>
     </row>
     <row r="61" spans="6:14" ht="15.75" thickTop="1">
       <c r="F61" s="1"/>
@@ -7682,89 +7741,89 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="96">
+      <c r="G62" s="100">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="97"/>
-      <c r="I62" s="96">
+      <c r="H62" s="101"/>
+      <c r="I62" s="100">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="97"/>
-      <c r="K62" s="96">
+      <c r="J62" s="101"/>
+      <c r="K62" s="100">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="97"/>
-      <c r="M62" s="96">
+      <c r="L62" s="101"/>
+      <c r="M62" s="100">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="97"/>
+      <c r="N62" s="101"/>
     </row>
     <row r="63" spans="6:14">
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="94">
+      <c r="G63" s="98">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="95"/>
-      <c r="I63" s="94">
+      <c r="H63" s="99"/>
+      <c r="I63" s="98">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="95"/>
-      <c r="K63" s="94">
+      <c r="J63" s="99"/>
+      <c r="K63" s="98">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="95"/>
-      <c r="M63" s="94">
+      <c r="L63" s="99"/>
+      <c r="M63" s="98">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="95"/>
+      <c r="N63" s="99"/>
     </row>
     <row r="64" spans="6:14">
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="94">
+      <c r="G64" s="98">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="95"/>
-      <c r="I64" s="94">
+      <c r="H64" s="99"/>
+      <c r="I64" s="98">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="95"/>
-      <c r="K64" s="94">
+      <c r="J64" s="99"/>
+      <c r="K64" s="98">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="95"/>
-      <c r="M64" s="94">
+      <c r="L64" s="99"/>
+      <c r="M64" s="98">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="95"/>
+      <c r="N64" s="99"/>
     </row>
     <row r="66" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F66" s="98" t="s">
+      <c r="F66" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="G66" s="98"/>
-      <c r="H66" s="98"/>
-      <c r="I66" s="98"/>
-      <c r="J66" s="98"/>
-      <c r="K66" s="98"/>
-      <c r="L66" s="98"/>
-      <c r="M66" s="98"/>
-      <c r="N66" s="98"/>
+      <c r="G66" s="102"/>
+      <c r="H66" s="102"/>
+      <c r="I66" s="102"/>
+      <c r="J66" s="102"/>
+      <c r="K66" s="102"/>
+      <c r="L66" s="102"/>
+      <c r="M66" s="102"/>
+      <c r="N66" s="102"/>
     </row>
     <row r="67" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F67" s="13" t="s">
@@ -7910,35 +7969,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="99">
+      <c r="G73" s="103">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="100">
+      <c r="H73" s="104">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="99">
+      <c r="I73" s="103">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="100">
+      <c r="J73" s="104">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="99">
+      <c r="K73" s="103">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="100">
+      <c r="L73" s="104">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="99">
+      <c r="M73" s="103">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="100">
+      <c r="N73" s="104">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -7958,89 +8017,89 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="96">
+      <c r="G75" s="100">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="97"/>
-      <c r="I75" s="96">
+      <c r="H75" s="101"/>
+      <c r="I75" s="100">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="97"/>
-      <c r="K75" s="96">
+      <c r="J75" s="101"/>
+      <c r="K75" s="100">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="97"/>
-      <c r="M75" s="96">
+      <c r="L75" s="101"/>
+      <c r="M75" s="100">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="97"/>
+      <c r="N75" s="101"/>
     </row>
     <row r="76" spans="6:14">
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="94">
+      <c r="G76" s="98">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="95"/>
-      <c r="I76" s="94">
+      <c r="H76" s="99"/>
+      <c r="I76" s="98">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="95"/>
-      <c r="K76" s="94">
+      <c r="J76" s="99"/>
+      <c r="K76" s="98">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="95"/>
-      <c r="M76" s="94">
+      <c r="L76" s="99"/>
+      <c r="M76" s="98">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="95"/>
+      <c r="N76" s="99"/>
     </row>
     <row r="77" spans="6:14">
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="94">
+      <c r="G77" s="98">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="95"/>
-      <c r="I77" s="94">
+      <c r="H77" s="99"/>
+      <c r="I77" s="98">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="95"/>
-      <c r="K77" s="94">
+      <c r="J77" s="99"/>
+      <c r="K77" s="98">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="95"/>
-      <c r="M77" s="94">
+      <c r="L77" s="99"/>
+      <c r="M77" s="98">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="95"/>
+      <c r="N77" s="99"/>
     </row>
     <row r="79" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F79" s="98" t="s">
+      <c r="F79" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="G79" s="98"/>
-      <c r="H79" s="98"/>
-      <c r="I79" s="98"/>
-      <c r="J79" s="98"/>
-      <c r="K79" s="98"/>
-      <c r="L79" s="98"/>
-      <c r="M79" s="98"/>
-      <c r="N79" s="98"/>
+      <c r="G79" s="102"/>
+      <c r="H79" s="102"/>
+      <c r="I79" s="102"/>
+      <c r="J79" s="102"/>
+      <c r="K79" s="102"/>
+      <c r="L79" s="102"/>
+      <c r="M79" s="102"/>
+      <c r="N79" s="102"/>
     </row>
     <row r="80" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F80" s="13" t="s">
@@ -8071,7 +8130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="6:14" ht="15.75" thickTop="1">
+    <row r="81" spans="6:24" ht="15.75" thickTop="1">
       <c r="F81" s="14" t="s">
         <v>9</v>
       </c>
@@ -8103,8 +8162,18 @@
         <f>+IF(M81=1,$B$2,IF($M81=2,$B$3,IF($M81=3,$B$4,IF($M81=4,$B$5,""))))</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="82" spans="6:14">
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+    </row>
+    <row r="82" spans="6:24">
       <c r="F82" s="11" t="s">
         <v>11</v>
       </c>
@@ -8136,8 +8205,18 @@
         <f>+IF(M82=1,$D$2,IF($M82=2,$D$3,IF($M82=3,$D$4,IF($M82=4,$D$5,""))))</f>
         <v>18.75</v>
       </c>
-    </row>
-    <row r="83" spans="6:14">
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+    </row>
+    <row r="83" spans="6:24">
       <c r="F83" s="11" t="s">
         <v>13</v>
       </c>
@@ -8151,8 +8230,18 @@
       <c r="L83" s="5"/>
       <c r="M83" s="10"/>
       <c r="N83" s="5"/>
-    </row>
-    <row r="84" spans="6:14">
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+    </row>
+    <row r="84" spans="6:24">
       <c r="F84" s="11" t="s">
         <v>14</v>
       </c>
@@ -8166,8 +8255,18 @@
       <c r="L84" s="5"/>
       <c r="M84" s="10"/>
       <c r="N84" s="5"/>
-    </row>
-    <row r="85" spans="6:14">
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+    </row>
+    <row r="85" spans="6:24">
       <c r="F85" s="11" t="s">
         <v>16</v>
       </c>
@@ -8181,45 +8280,65 @@
       <c r="L85" s="5"/>
       <c r="M85" s="10"/>
       <c r="N85" s="5"/>
-    </row>
-    <row r="86" spans="6:14" ht="15.75" thickBot="1">
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+    </row>
+    <row r="86" spans="6:24" ht="15.75" thickBot="1">
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="99">
+      <c r="G86" s="103">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="100">
+      <c r="H86" s="104">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="99">
+      <c r="I86" s="103">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="100">
+      <c r="J86" s="104">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="99">
+      <c r="K86" s="103">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="L86" s="100">
+      <c r="L86" s="104">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="M86" s="99">
+      <c r="M86" s="103">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
-      <c r="N86" s="100">
+      <c r="N86" s="104">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
-    </row>
-    <row r="87" spans="6:14">
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+    </row>
+    <row r="87" spans="6:24">
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -8229,96 +8348,146 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
-    </row>
-    <row r="88" spans="6:14">
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="1"/>
+      <c r="V87" s="1"/>
+      <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+    </row>
+    <row r="88" spans="6:24">
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="96">
+      <c r="G88" s="100">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="97"/>
-      <c r="I88" s="96">
+      <c r="H88" s="101"/>
+      <c r="I88" s="100">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="97"/>
-      <c r="K88" s="96">
+      <c r="J88" s="101"/>
+      <c r="K88" s="100">
         <f>+SUM(K86,K75)</f>
         <v>169.75</v>
       </c>
-      <c r="L88" s="97"/>
-      <c r="M88" s="96">
+      <c r="L88" s="101"/>
+      <c r="M88" s="100">
         <f>+SUM(M86,M75)</f>
         <v>212.25</v>
       </c>
-      <c r="N88" s="97"/>
-    </row>
-    <row r="89" spans="6:14">
+      <c r="N88" s="101"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+    </row>
+    <row r="89" spans="6:24">
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="94">
+      <c r="G89" s="98">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="95"/>
-      <c r="I89" s="94">
+      <c r="H89" s="99"/>
+      <c r="I89" s="98">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="95"/>
-      <c r="K89" s="94">
+      <c r="J89" s="99"/>
+      <c r="K89" s="98">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L89" s="95"/>
-      <c r="M89" s="94">
+      <c r="L89" s="99"/>
+      <c r="M89" s="98">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N89" s="95"/>
-    </row>
-    <row r="90" spans="6:14">
+      <c r="N89" s="99"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
+      <c r="V89" s="1"/>
+      <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+    </row>
+    <row r="90" spans="6:24">
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="94">
+      <c r="G90" s="98">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="95"/>
-      <c r="I90" s="94">
+      <c r="H90" s="99"/>
+      <c r="I90" s="98">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="95"/>
-      <c r="K90" s="94">
+      <c r="J90" s="99"/>
+      <c r="K90" s="98">
         <f>+SUM(K89+K77-K50)</f>
         <v>0</v>
       </c>
-      <c r="L90" s="95"/>
-      <c r="M90" s="94">
+      <c r="L90" s="99"/>
+      <c r="M90" s="98">
         <f>+SUM(M89+M77-M50)</f>
         <v>70</v>
       </c>
-      <c r="N90" s="95"/>
-    </row>
-    <row r="92" spans="6:14">
-      <c r="F92" s="98" t="s">
+      <c r="N90" s="99"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+    </row>
+    <row r="92" spans="6:24">
+      <c r="F92" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="G92" s="98"/>
-      <c r="H92" s="98"/>
-      <c r="I92" s="98"/>
-      <c r="J92" s="98"/>
-      <c r="K92" s="98"/>
-      <c r="L92" s="98"/>
-      <c r="M92" s="98"/>
-      <c r="N92" s="98"/>
-    </row>
-    <row r="93" spans="6:14" ht="16.5" customHeight="1">
+      <c r="G92" s="102"/>
+      <c r="H92" s="102"/>
+      <c r="I92" s="102"/>
+      <c r="J92" s="102"/>
+      <c r="K92" s="102"/>
+      <c r="L92" s="102"/>
+      <c r="M92" s="102"/>
+      <c r="N92" s="102"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+    </row>
+    <row r="93" spans="6:24" ht="16.5" customHeight="1">
       <c r="F93" s="13" t="s">
         <v>33</v>
       </c>
@@ -8346,8 +8515,18 @@
       <c r="N93" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="6:14" ht="15.75" customHeight="1">
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+    </row>
+    <row r="94" spans="6:24" ht="15.75" customHeight="1">
       <c r="F94" s="14" t="s">
         <v>9</v>
       </c>
@@ -8379,8 +8558,18 @@
         <f>+IF(M94=1,$B$2,IF($M94=2,$B$3,IF($M94=3,$B$4,IF($M94=4,$B$5,""))))</f>
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="6:14">
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+    </row>
+    <row r="95" spans="6:24">
       <c r="F95" s="11" t="s">
         <v>11</v>
       </c>
@@ -8399,21 +8588,31 @@
         <v>13.5</v>
       </c>
       <c r="K95" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" s="5">
         <f>+IF(K95=1,$D$2,IF($K95=2,$D$3,IF($K95=3,$D$4,IF($K95=4,$D$5,""))))</f>
-        <v>11.25</v>
+        <v>9</v>
       </c>
       <c r="M95" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N95" s="5">
         <f>+IF(M95=1,$D$2,IF($M95=2,$D$3,IF($M95=3,$D$4,IF($M95=4,$D$5,""))))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="6:14">
+        <v>11.25</v>
+      </c>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1"/>
+      <c r="V95" s="1"/>
+      <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+    </row>
+    <row r="96" spans="6:24">
       <c r="F96" s="11" t="s">
         <v>13</v>
       </c>
@@ -8427,6 +8626,16 @@
       <c r="L96" s="5"/>
       <c r="M96" s="10"/>
       <c r="N96" s="5"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1"/>
+      <c r="V96" s="1"/>
+      <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
     </row>
     <row r="97" spans="6:14">
       <c r="F97" s="11" t="s">
@@ -8462,37 +8671,37 @@
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="99">
+      <c r="G99" s="103">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="100">
+      <c r="H99" s="104">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="99">
+      <c r="I99" s="103">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="100">
+      <c r="J99" s="104">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="99">
+      <c r="K99" s="103">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
-        <v>26.25</v>
-      </c>
-      <c r="L99" s="100">
+        <v>24</v>
+      </c>
+      <c r="L99" s="104">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
-        <v>26.25</v>
-      </c>
-      <c r="M99" s="99">
+        <v>24</v>
+      </c>
+      <c r="M99" s="103">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
-        <v>21</v>
-      </c>
-      <c r="N99" s="100">
+        <v>23.25</v>
+      </c>
+      <c r="N99" s="104">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
-        <v>21</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="100" spans="6:14">
@@ -8510,87 +8719,87 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="96">
+      <c r="G101" s="100">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="97"/>
-      <c r="I101" s="96">
+      <c r="H101" s="101"/>
+      <c r="I101" s="100">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="97"/>
-      <c r="K101" s="96">
+      <c r="J101" s="101"/>
+      <c r="K101" s="100">
         <f>+SUM(K99,K88)</f>
-        <v>196</v>
-      </c>
-      <c r="L101" s="97"/>
-      <c r="M101" s="96">
+        <v>193.75</v>
+      </c>
+      <c r="L101" s="101"/>
+      <c r="M101" s="100">
         <f>+SUM(M99,M88)</f>
-        <v>233.25</v>
-      </c>
-      <c r="N101" s="97"/>
+        <v>235.5</v>
+      </c>
+      <c r="N101" s="101"/>
     </row>
     <row r="102" spans="6:14">
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="94">
+      <c r="G102" s="98">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="95"/>
-      <c r="I102" s="94">
+      <c r="H102" s="99"/>
+      <c r="I102" s="98">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="95"/>
-      <c r="K102" s="94">
+      <c r="J102" s="99"/>
+      <c r="K102" s="98">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="95"/>
-      <c r="M102" s="94">
+      <c r="L102" s="99"/>
+      <c r="M102" s="98">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="95"/>
+      <c r="N102" s="99"/>
     </row>
     <row r="103" spans="6:14">
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="94">
+      <c r="G103" s="98">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="95"/>
-      <c r="I103" s="94">
+      <c r="H103" s="99"/>
+      <c r="I103" s="98">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="95"/>
-      <c r="K103" s="94">
+      <c r="J103" s="99"/>
+      <c r="K103" s="98">
         <f>+SUM(K102+K90-K63)</f>
         <v>10</v>
       </c>
-      <c r="L103" s="95"/>
-      <c r="M103" s="94">
+      <c r="L103" s="99"/>
+      <c r="M103" s="98">
         <f>+SUM(M102+M90-M63)</f>
         <v>30</v>
       </c>
-      <c r="N103" s="95"/>
+      <c r="N103" s="99"/>
     </row>
     <row r="105" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F105" s="98"/>
-      <c r="G105" s="98"/>
-      <c r="H105" s="98"/>
-      <c r="I105" s="98"/>
-      <c r="J105" s="98"/>
-      <c r="K105" s="98"/>
-      <c r="L105" s="98"/>
-      <c r="M105" s="98"/>
-      <c r="N105" s="98"/>
+      <c r="F105" s="102"/>
+      <c r="G105" s="102"/>
+      <c r="H105" s="102"/>
+      <c r="I105" s="102"/>
+      <c r="J105" s="102"/>
+      <c r="K105" s="102"/>
+      <c r="L105" s="102"/>
+      <c r="M105" s="102"/>
+      <c r="N105" s="102"/>
     </row>
     <row r="106" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F106" s="13" t="s">
@@ -8710,32 +8919,26 @@
       <c r="M111" s="10"/>
       <c r="N111" s="5"/>
     </row>
-    <row r="112" spans="6:14" ht="15.75" thickBot="1">
+    <row r="112" spans="6:14" ht="15.75" customHeight="1">
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="99"/>
-      <c r="H112" s="100">
-        <f>+SUM(H107:H111)</f>
-        <v>0</v>
-      </c>
-      <c r="I112" s="99"/>
-      <c r="J112" s="100">
-        <f>+SUM(J107:J111)</f>
-        <v>0</v>
-      </c>
-      <c r="K112" s="99"/>
-      <c r="L112" s="100">
+      <c r="G112" s="103"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="103"/>
+      <c r="J112" s="104"/>
+      <c r="K112" s="103"/>
+      <c r="L112" s="104">
         <f>+SUM(L107:L111)</f>
         <v>0</v>
       </c>
-      <c r="M112" s="99"/>
-      <c r="N112" s="100">
+      <c r="M112" s="103"/>
+      <c r="N112" s="104">
         <f>+SUM(N107:N111)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="6:14" ht="15.75" thickTop="1">
+    <row r="113" spans="6:14">
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
@@ -8750,81 +8953,63 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="96">
-        <f>H112</f>
-        <v>0</v>
-      </c>
-      <c r="H114" s="97"/>
-      <c r="I114" s="96">
-        <f>J112</f>
-        <v>0</v>
-      </c>
-      <c r="J114" s="97"/>
-      <c r="K114" s="96">
-        <f>L112</f>
-        <v>0</v>
-      </c>
-      <c r="L114" s="97"/>
-      <c r="M114" s="96">
-        <f>N112</f>
-        <v>0</v>
-      </c>
-      <c r="N114" s="97"/>
+      <c r="G114" s="100"/>
+      <c r="H114" s="101"/>
+      <c r="I114" s="100"/>
+      <c r="J114" s="101"/>
+      <c r="K114" s="100"/>
+      <c r="L114" s="101"/>
+      <c r="M114" s="100"/>
+      <c r="N114" s="101"/>
     </row>
     <row r="115" spans="6:14">
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="94" t="str">
+      <c r="G115" s="98" t="str">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H115" s="95"/>
-      <c r="I115" s="94" t="str">
+      <c r="H115" s="99"/>
+      <c r="I115" s="98" t="str">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J115" s="95"/>
-      <c r="K115" s="96"/>
-      <c r="L115" s="97"/>
-      <c r="M115" s="96"/>
-      <c r="N115" s="97"/>
+      <c r="J115" s="99"/>
+      <c r="K115" s="100"/>
+      <c r="L115" s="101"/>
+      <c r="M115" s="100"/>
+      <c r="N115" s="101"/>
     </row>
     <row r="116" spans="6:14">
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="94" t="e">
-        <f>+SUM(G115+G103-G76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H116" s="95"/>
-      <c r="I116" s="94" t="e">
-        <f>+SUM(I115+I103-I76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J116" s="95"/>
-      <c r="K116" s="96" t="str">
+      <c r="G116" s="98"/>
+      <c r="H116" s="99"/>
+      <c r="I116" s="98"/>
+      <c r="J116" s="99"/>
+      <c r="K116" s="100" t="str">
         <f>+IF($K107=1,"40Kg",IF($K107=2,"20Kg",IF($K107=3,"10Kg",IF($K107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L116" s="97"/>
-      <c r="M116" s="96" t="str">
+      <c r="L116" s="101"/>
+      <c r="M116" s="100" t="str">
         <f>+IF($M107=1,"40Kg",IF($M107=2,"20Kg",IF($M107=3,"10Kg",IF($M107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N116" s="97"/>
+      <c r="N116" s="101"/>
     </row>
     <row r="118" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F118" s="98"/>
-      <c r="G118" s="98"/>
-      <c r="H118" s="98"/>
-      <c r="I118" s="98"/>
-      <c r="J118" s="98"/>
-      <c r="K118" s="98"/>
-      <c r="L118" s="98"/>
-      <c r="M118" s="98"/>
-      <c r="N118" s="98"/>
+      <c r="F118" s="102"/>
+      <c r="G118" s="102"/>
+      <c r="H118" s="102"/>
+      <c r="I118" s="102"/>
+      <c r="J118" s="102"/>
+      <c r="K118" s="102"/>
+      <c r="L118" s="102"/>
+      <c r="M118" s="102"/>
+      <c r="N118" s="102"/>
     </row>
     <row r="119" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F119" s="13" t="s">
@@ -8948,23 +9133,23 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="99"/>
-      <c r="H125" s="100">
+      <c r="G125" s="103"/>
+      <c r="H125" s="104">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="99"/>
-      <c r="J125" s="100">
+      <c r="I125" s="103"/>
+      <c r="J125" s="104">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="99"/>
-      <c r="L125" s="100">
+      <c r="K125" s="103"/>
+      <c r="L125" s="104">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="99"/>
-      <c r="N125" s="100">
+      <c r="M125" s="103"/>
+      <c r="N125" s="104">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -8984,70 +9169,70 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="96">
+      <c r="G127" s="100">
         <f>H125</f>
         <v>0</v>
       </c>
-      <c r="H127" s="97"/>
-      <c r="I127" s="96">
+      <c r="H127" s="101"/>
+      <c r="I127" s="100">
         <f>J125</f>
         <v>0</v>
       </c>
-      <c r="J127" s="97"/>
-      <c r="K127" s="96">
+      <c r="J127" s="101"/>
+      <c r="K127" s="100">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="97"/>
-      <c r="M127" s="96">
+      <c r="L127" s="101"/>
+      <c r="M127" s="100">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="97"/>
+      <c r="N127" s="101"/>
     </row>
     <row r="128" spans="6:14">
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="94" t="str">
+      <c r="G128" s="98" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="95"/>
-      <c r="I128" s="94" t="str">
+      <c r="H128" s="99"/>
+      <c r="I128" s="98" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J128" s="95"/>
-      <c r="K128" s="96"/>
-      <c r="L128" s="97"/>
-      <c r="M128" s="96"/>
-      <c r="N128" s="97"/>
+      <c r="J128" s="99"/>
+      <c r="K128" s="100"/>
+      <c r="L128" s="101"/>
+      <c r="M128" s="100"/>
+      <c r="N128" s="101"/>
     </row>
     <row r="129" spans="6:14">
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="94" t="e">
+      <c r="G129" s="98" t="e">
         <f>+SUM(G128+G116-G89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H129" s="95"/>
-      <c r="I129" s="94" t="e">
+      <c r="H129" s="99"/>
+      <c r="I129" s="98" t="e">
         <f>+SUM(I128+I116-I89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J129" s="95"/>
-      <c r="K129" s="96" t="str">
+      <c r="J129" s="99"/>
+      <c r="K129" s="100" t="str">
         <f>+IF($K120=1,"40Kg",IF($K120=2,"20Kg",IF($K120=3,"10Kg",IF($K120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L129" s="97"/>
-      <c r="M129" s="96" t="str">
+      <c r="L129" s="101"/>
+      <c r="M129" s="100" t="str">
         <f>+IF($M120=1,"40Kg",IF($M120=2,"20Kg",IF($M120=3,"10Kg",IF($M120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N129" s="97"/>
+      <c r="N129" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="176">
@@ -9417,7 +9602,7 @@
       </c>
       <c r="B4" s="21">
         <f>+SUM(Hoja1!K8,Hoja1!K21,Hoja1!K34,Hoja1!K47,Hoja1!K60,Hoja1!K73,Hoja1!K86,Hoja1!K99)</f>
-        <v>196</v>
+        <v>193.75</v>
       </c>
       <c r="C4" s="25">
         <f>INDEX(Hoja1!$K$1:$K$250, (COUNTIF(DATOS!$J$6:$S$6, "&gt;0")-1)*13 + 12)</f>
@@ -9429,7 +9614,7 @@
       </c>
       <c r="E4" s="1">
         <f>+AVERAGEIF(DATOS!E$3:E$22, "&gt;0")</f>
-        <v>3.4375</v>
+        <v>3.5</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="29"/>
@@ -9442,7 +9627,7 @@
       </c>
       <c r="J4" s="31">
         <f t="shared" si="1"/>
-        <v>233.25</v>
+        <v>235.5</v>
       </c>
       <c r="K4" s="43">
         <f t="shared" si="2"/>
@@ -9451,11 +9636,11 @@
       <c r="L4" s="1"/>
       <c r="M4" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I4, $A$2:$A$5, 0))</f>
-        <v>2.75</v>
+        <v>2.6875</v>
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.62366310160427807</v>
+        <v>0.6296791443850267</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -9477,7 +9662,7 @@
       </c>
       <c r="B5" s="20">
         <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86,Hoja1!M99)</f>
-        <v>233.25</v>
+        <v>235.5</v>
       </c>
       <c r="C5" s="26">
         <f>INDEX(Hoja1!$M$1:$M$250, (COUNTIF(DATOS!$J$7:$S$7, "&gt;0")-1)*13 + 12)</f>
@@ -9489,7 +9674,7 @@
       </c>
       <c r="E5" s="1">
         <f>+AVERAGEIF(DATOS!F$3:F$22, "&gt;0")</f>
-        <v>2.75</v>
+        <v>2.6875</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="29"/>
@@ -9502,7 +9687,7 @@
       </c>
       <c r="J5" s="33">
         <f t="shared" si="1"/>
-        <v>196</v>
+        <v>193.75</v>
       </c>
       <c r="K5" s="44">
         <f t="shared" si="2"/>
@@ -9511,11 +9696,11 @@
       <c r="L5" s="29"/>
       <c r="M5" s="46">
         <f>INDEX($E$2:$E$5, MATCH(I5, $A$2:$A$5, 0))</f>
-        <v>3.4375</v>
+        <v>3.5</v>
       </c>
       <c r="N5" s="40">
         <f>J5 / (COUNTIFS(DATOS!F3:F22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.52406417112299464</v>
+        <v>0.51804812834224601</v>
       </c>
       <c r="O5" s="42">
         <f>+SUM(DATOS!F27:F46)</f>
@@ -10200,25 +10385,25 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="101"/>
+      <c r="B2" s="105"/>
       <c r="C2" s="1" t="s">
         <v>45</v>
       </c>
@@ -10233,20 +10418,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="109"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10303,7 +10488,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="104"/>
+      <c r="A4" s="108"/>
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
@@ -10370,7 +10555,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="108" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -10439,7 +10624,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="104"/>
+      <c r="A6" s="108"/>
       <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
@@ -10494,7 +10679,7 @@
       </c>
       <c r="Q6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>196</v>
+        <v>193.75</v>
       </c>
       <c r="R6" s="1" t="e">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10506,7 +10691,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="108" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10563,7 +10748,7 @@
       </c>
       <c r="Q7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>233.25</v>
+        <v>235.5</v>
       </c>
       <c r="R7" s="1" t="e">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10))</f>
@@ -10575,7 +10760,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="104"/>
+      <c r="A8" s="108"/>
       <c r="B8" s="1" t="s">
         <v>60</v>
       </c>
@@ -10610,7 +10795,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="108" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10647,7 +10832,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="104"/>
+      <c r="A10" s="108"/>
       <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
@@ -10682,7 +10867,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="108" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10719,7 +10904,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="104"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="1" t="s">
         <v>60</v>
       </c>
@@ -10754,7 +10939,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="108" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10791,7 +10976,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="104"/>
+      <c r="A14" s="108"/>
       <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
@@ -10826,7 +11011,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="108" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10863,7 +11048,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="104"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="1" t="s">
         <v>60</v>
       </c>
@@ -10898,7 +11083,9 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="104"/>
+      <c r="A17" s="108" t="s">
+        <v>64</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
       </c>
@@ -10921,7 +11108,7 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="104"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="1" t="s">
         <v>60</v>
       </c>
@@ -10935,16 +11122,16 @@
       </c>
       <c r="E18" s="1">
         <f>Hoja1!K95</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1">
         <f>Hoja1!M95</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="104"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
@@ -10967,7 +11154,7 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="104"/>
+      <c r="A20" s="108"/>
       <c r="B20" s="1" t="s">
         <v>60</v>
       </c>
@@ -10990,7 +11177,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="104"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
@@ -11013,7 +11200,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="104"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="1" t="s">
         <v>60</v>
       </c>
@@ -11037,7 +11224,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -11059,21 +11246,21 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="101"/>
+      <c r="B26" s="105"/>
       <c r="C26" s="93" t="s">
         <v>45</v>
       </c>
@@ -11089,320 +11276,322 @@
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="104" t="s">
+      <c r="A27" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="101">
+      <c r="B27" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="105">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="101">
+      <c r="D27" s="105">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="101">
+      <c r="E27" s="105">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="101">
+      <c r="F27" s="105">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="101"/>
+      <c r="G27" s="105"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="104"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
+      <c r="A28" s="108"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="104" t="s">
+      <c r="A29" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="101">
+      <c r="B29" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="105">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="101">
+      <c r="D29" s="105">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="101">
+      <c r="E29" s="105">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="101">
+      <c r="F29" s="105">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="101"/>
+      <c r="G29" s="105"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="104"/>
-      <c r="B30" s="104"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="101"/>
+      <c r="A30" s="108"/>
+      <c r="B30" s="108"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="104" t="s">
+      <c r="A31" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="101">
+      <c r="B31" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="105">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="101">
+      <c r="D31" s="105">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="101">
+      <c r="E31" s="105">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="101">
+      <c r="F31" s="105">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="101"/>
+      <c r="G31" s="105"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="104"/>
-      <c r="B32" s="104"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="101"/>
+      <c r="A32" s="108"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="104" t="s">
+      <c r="A33" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="101">
+      <c r="B33" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="105">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="101">
+      <c r="D33" s="105">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="101">
+      <c r="E33" s="105">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="101">
+      <c r="F33" s="105">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="101"/>
+      <c r="G33" s="105"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="104"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="101"/>
+      <c r="A34" s="108"/>
+      <c r="B34" s="108"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="104" t="s">
+      <c r="A35" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="101">
+      <c r="B35" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="105">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="101">
+      <c r="D35" s="105">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="101">
+      <c r="E35" s="105">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="101">
+      <c r="F35" s="105">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="101"/>
+      <c r="G35" s="105"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="104"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="101"/>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="101"/>
+      <c r="A36" s="108"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="105"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="104" t="s">
+      <c r="A37" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="101">
+      <c r="B37" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="105">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="101">
+      <c r="D37" s="105">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="101">
+      <c r="E37" s="105">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="101">
+      <c r="F37" s="105">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="101"/>
+      <c r="G37" s="105"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="104"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="101"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="101"/>
-      <c r="G38" s="101"/>
+      <c r="A38" s="108"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="105"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="104" t="s">
+      <c r="A39" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="101">
+      <c r="B39" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="105">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="101">
+      <c r="D39" s="105">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="101">
+      <c r="E39" s="105">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="101">
+      <c r="F39" s="105">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="101"/>
+      <c r="G39" s="105"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="104"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="101"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="101"/>
-      <c r="F40" s="101"/>
-      <c r="G40" s="101"/>
+      <c r="A40" s="108"/>
+      <c r="B40" s="108"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="104"/>
-      <c r="B41" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="101">
+      <c r="A41" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="105">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="101">
+      <c r="D41" s="105">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="101">
+      <c r="E41" s="105">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="101">
+      <c r="F41" s="105">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="101"/>
+      <c r="G41" s="105"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="104"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="101"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="101"/>
-      <c r="F42" s="101"/>
-      <c r="G42" s="101"/>
+      <c r="A42" s="108"/>
+      <c r="B42" s="108"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="104"/>
-      <c r="B43" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="101">
+      <c r="A43" s="108"/>
+      <c r="B43" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="105">
         <f>Hoja1!H109</f>
         <v>0</v>
       </c>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="104"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="101"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="101"/>
-      <c r="F44" s="101"/>
-      <c r="G44" s="101"/>
+      <c r="A44" s="108"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="104"/>
-      <c r="B45" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="101">
+      <c r="A45" s="108"/>
+      <c r="B45" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="105">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="101"/>
-      <c r="E45" s="101"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="104"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="101"/>
-      <c r="D46" s="101"/>
-      <c r="E46" s="101"/>
-      <c r="F46" s="101"/>
-      <c r="G46" s="101"/>
+      <c r="A46" s="108"/>
+      <c r="B46" s="108"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -11535,19 +11724,19 @@
         <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -12351,7 +12540,9 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="101"/>
+      <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
       </c>
@@ -12377,7 +12568,9 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="101"/>
+      <c r="A31" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
@@ -12403,7 +12596,9 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="101"/>
+      <c r="A32" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
@@ -12425,11 +12620,13 @@
       </c>
       <c r="G32" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A31)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="101"/>
+      <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
@@ -12451,11 +12648,11 @@
       </c>
       <c r="G33" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A32)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="101"/>
+      <c r="A34" s="105"/>
       <c r="B34" s="1" t="s">
         <v>4</v>
       </c>
@@ -12481,7 +12678,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="101"/>
+      <c r="A35" s="105"/>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
@@ -12507,7 +12704,7 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="101"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -12533,7 +12730,7 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="101"/>
+      <c r="A37" s="105"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -12559,7 +12756,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="101"/>
+      <c r="A38" s="105"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -12585,7 +12782,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="101"/>
+      <c r="A39" s="105"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -12611,7 +12808,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="101"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -12637,7 +12834,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="101"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -12663,8 +12860,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A30:A33"/>
+  <mergeCells count="2">
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A38:A41"/>
   </mergeCells>
@@ -12690,7 +12886,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -12699,22 +12895,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="93" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="93" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -12836,11 +13032,11 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="108" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="58">
         <v>1.0631828703703704E-3</v>
@@ -12859,9 +13055,9 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="104"/>
+      <c r="A3" s="108"/>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="58">
         <v>1.0327314814814815E-3</v>
@@ -12882,9 +13078,9 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="104"/>
+      <c r="A4" s="108"/>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="58">
         <v>1.0267824074074075E-3</v>
@@ -12905,11 +13101,11 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="108" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
@@ -12922,9 +13118,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="104"/>
+      <c r="A6" s="108"/>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -12937,9 +13133,9 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="104"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
@@ -12952,11 +13148,11 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="108" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -12969,9 +13165,9 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="104"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" s="58"/>
       <c r="D9" s="58"/>
@@ -12984,9 +13180,9 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="104"/>
+      <c r="A10" s="108"/>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" s="58">
         <v>8.9045138888888887E-4</v>
@@ -13007,11 +13203,11 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="108" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="58">
         <v>8.6745370370370383E-4</v>
@@ -13032,9 +13228,9 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="104"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -13047,9 +13243,9 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="104"/>
+      <c r="A13" s="108"/>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -13062,11 +13258,11 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="108" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="58">
         <v>8.2178240740740736E-4</v>
@@ -13083,25 +13279,25 @@
       <c r="G14" s="58"/>
       <c r="H14" s="1" cm="1">
         <f t="array" ref="H14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>9.8536342592592599E-4</v>
+        <v>1.0041454475308643E-3</v>
       </c>
       <c r="I14" s="1" cm="1">
         <f t="array" ref="I14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
-        <v>9.8469444444444451E-4</v>
+        <v>1.0054070216049384E-3</v>
       </c>
       <c r="J14" s="1">
         <f t="array" ref="J14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(E$2:E$46&gt;0),E$2:E$46)),0)</f>
-        <v>1.0002633101851852E-3</v>
+        <v>1.0265000000000001E-3</v>
       </c>
       <c r="K14" s="1">
         <f t="array" ref="K14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>1.0084814814814815E-3</v>
+        <v>1.0336226851851852E-3</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="104"/>
+      <c r="A15" s="108"/>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" s="58">
         <v>8.1365740740740736E-4</v>
@@ -13132,9 +13328,9 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="104"/>
+      <c r="A16" s="108"/>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="58">
         <v>8.0902777777777787E-4</v>
@@ -13165,11 +13361,11 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="108" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="58">
         <v>9.2799768518518524E-4</v>
@@ -13195,9 +13391,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="104"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="58">
         <v>9.2737268518518516E-4</v>
@@ -13223,9 +13419,9 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="104"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="58">
         <v>9.2612268518518521E-4</v>
@@ -13251,11 +13447,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="108" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="58">
         <v>1.2464004629629628E-3</v>
@@ -13281,9 +13477,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="104"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" s="58">
         <v>1.2324652777777779E-3</v>
@@ -13307,9 +13503,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="104"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="58">
         <v>1.2377777777777777E-3</v>
@@ -13333,14 +13529,24 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="104" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
+      <c r="A23" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="58">
+        <v>1.0980555555555555E-3</v>
+      </c>
+      <c r="D23" s="58">
+        <v>1.1089699074074075E-3</v>
+      </c>
+      <c r="E23" s="58">
+        <v>1.1314467592592593E-3</v>
+      </c>
+      <c r="F23" s="58">
+        <v>1.1593287037037036E-3</v>
+      </c>
       <c r="G23" s="58"/>
       <c r="H23" s="58"/>
       <c r="I23" s="58"/>
@@ -13353,8 +13559,10 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="104"/>
-      <c r="B24" s="1"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="C24" s="58"/>
       <c r="D24" s="58"/>
       <c r="E24" s="58"/>
@@ -13371,8 +13579,10 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="104"/>
-      <c r="B25" s="1"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="C25" s="58"/>
       <c r="D25" s="58"/>
       <c r="E25" s="58"/>
@@ -13389,7 +13599,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="104" t="s">
+      <c r="A26" s="108" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="1"/>
@@ -13409,7 +13619,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="104"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="1"/>
       <c r="C27" s="58"/>
       <c r="D27" s="58"/>
@@ -13427,7 +13637,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="104"/>
+      <c r="A28" s="108"/>
       <c r="B28" s="1"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
@@ -13445,7 +13655,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="104" t="s">
+      <c r="A29" s="108" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="1"/>
@@ -13465,7 +13675,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="104"/>
+      <c r="A30" s="108"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -13483,7 +13693,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="104"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -13544,7 +13754,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -13561,11 +13771,11 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="110" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="69">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -13590,15 +13800,15 @@
       </c>
       <c r="J2" s="1">
         <f>IF('Carga Tiempos'!H14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!H14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>6.6898148148148394E-7</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
         <f>IF('Carga Tiempos'!I14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!I14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>0</v>
+        <v>1.261574074074099E-6</v>
       </c>
       <c r="L2" s="1">
         <f>IF('Carga Tiempos'!K14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!K14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>2.3787037037037006E-5</v>
+        <v>2.9477237654320894E-5</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -13606,9 +13816,9 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="107"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="69">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -13649,9 +13859,9 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="107"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="69">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -13692,11 +13902,11 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="110" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="60"/>
@@ -13714,9 +13924,9 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="107"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
@@ -13734,9 +13944,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="108"/>
+      <c r="A7" s="112"/>
       <c r="B7" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="61"/>
@@ -13754,11 +13964,11 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="111" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
@@ -13776,9 +13986,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="107"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="68"/>
@@ -13796,9 +14006,9 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="108"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" s="71">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -13828,11 +14038,11 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="111" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="69">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -13862,9 +14072,9 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="107"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="68"/>
@@ -13882,9 +14092,9 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="107"/>
+      <c r="A13" s="111"/>
       <c r="B13" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="68"/>
@@ -13902,11 +14112,11 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="106" t="s">
+      <c r="A14" s="110" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="70">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -13936,9 +14146,9 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="107"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" s="69">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -13968,9 +14178,9 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="108"/>
+      <c r="A16" s="112"/>
       <c r="B16" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="71">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -14000,11 +14210,11 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="107" t="s">
+      <c r="A17" s="111" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="69">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -14034,9 +14244,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="107"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="69">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -14066,9 +14276,9 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="107"/>
+      <c r="A19" s="111"/>
       <c r="B19" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="69">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -14098,11 +14308,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="110" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="70">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -14132,9 +14342,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="107"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" s="69">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -14164,9 +14374,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="107"/>
+      <c r="A22" s="111"/>
       <c r="B22" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="69">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -14196,27 +14406,27 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="106" t="s">
+      <c r="A23" s="110" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="70">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
-        <v>0</v>
+        <v>1.0980555555555555E-3</v>
       </c>
       <c r="D23" s="70">
         <f>+IF('Carga Tiempos'!D23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!D23,'Carga Tiempos'!D23-MIN('Carga Tiempos'!$C23:$F23))</f>
-        <v>0</v>
+        <v>1.0914351851852013E-5</v>
       </c>
       <c r="E23" s="70">
         <f>+IF('Carga Tiempos'!E23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!E23,'Carga Tiempos'!E23-MIN('Carga Tiempos'!$C23:$F23))</f>
-        <v>0</v>
+        <v>3.3391203703703881E-5</v>
       </c>
       <c r="F23" s="60">
         <f>+IF('Carga Tiempos'!F23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!F23,'Carga Tiempos'!F23-MIN('Carga Tiempos'!$C23:$F23))</f>
-        <v>0</v>
+        <v>6.1273148148148189E-5</v>
       </c>
       <c r="G23" s="58"/>
       <c r="H23" s="58"/>
@@ -14230,9 +14440,9 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="107"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" s="69">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
@@ -14262,9 +14472,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="108"/>
+      <c r="A25" s="112"/>
       <c r="B25" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C25" s="71">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
@@ -14294,11 +14504,11 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="111" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="69">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
@@ -14328,9 +14538,9 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="107"/>
+      <c r="A27" s="111"/>
       <c r="B27" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -14360,9 +14570,9 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="107"/>
+      <c r="A28" s="111"/>
       <c r="B28" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" s="69">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -14392,11 +14602,11 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="110" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" s="70">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -14426,9 +14636,9 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="107"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="69">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -14458,9 +14668,9 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="108"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" s="71">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -14565,29 +14775,34 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34573353-DC88-4E7A-8BA7-3DB24B9880AA}">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="111" t="s">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
+      <c r="K1" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14598,24 +14813,28 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="109" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="110"/>
-      <c r="M2" s="109" t="s">
+      <c r="K2" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="N2" s="110"/>
-      <c r="O2" s="109" t="s">
+      <c r="L2" s="96"/>
+      <c r="M2" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="109" t="s">
+      <c r="N2" s="96"/>
+      <c r="O2" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="110"/>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="P2" s="96"/>
+      <c r="Q2" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="96"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -14632,26 +14851,30 @@
       <c r="L3" s="81">
         <v>1.2731481481481483E-3</v>
       </c>
-      <c r="M3" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="N3" s="84">
+      <c r="M3" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="77">
+        <v>1.2796759259259259E-3</v>
+      </c>
+      <c r="O3" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
-      <c r="O3" s="86" t="s">
-        <v>84</v>
-      </c>
-      <c r="P3" s="77">
-        <v>1.2796759259259259E-3</v>
-      </c>
-      <c r="Q3" s="86" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="77">
-        <v>1.2796759259259259E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="Q3" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="84">
+        <v>1.4428356481481482E-3</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -14669,25 +14892,29 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="81">
+        <v>86</v>
+      </c>
+      <c r="N4" s="77">
+        <v>1.2429976851851853E-3</v>
+      </c>
+      <c r="O4" s="83" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
-      <c r="O4" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" s="77">
-        <v>1.2429976851851853E-3</v>
-      </c>
       <c r="Q4" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" s="77">
-        <v>1.2429976851851853E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>86</v>
+      </c>
+      <c r="R4" s="81">
+        <v>1.2858101851851852E-3</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -14704,26 +14931,30 @@
       <c r="L5" s="81">
         <v>1.2545601851851852E-3</v>
       </c>
-      <c r="M5" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="81">
+      <c r="M5" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="77">
+        <v>1.2377777777777777E-3</v>
+      </c>
+      <c r="O5" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
-      <c r="O5" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="P5" s="77">
-        <v>1.2377777777777777E-3</v>
-      </c>
-      <c r="Q5" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="77">
-        <v>1.2377777777777777E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="Q5" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="R5" s="81">
+        <v>1.2647453703703703E-3</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -14741,25 +14972,29 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="N6" s="81">
+        <v>88</v>
+      </c>
+      <c r="N6" s="77">
+        <v>1.3249884259259259E-3</v>
+      </c>
+      <c r="O6" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
-      <c r="O6" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="P6" s="77">
-        <v>1.3249884259259259E-3</v>
-      </c>
       <c r="Q6" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="R6" s="77">
-        <v>1.3249884259259259E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>88</v>
+      </c>
+      <c r="R6" s="81">
+        <v>1.2908564814814816E-3</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -14776,26 +15011,30 @@
       <c r="L7" s="81">
         <v>1.260300925925926E-3</v>
       </c>
-      <c r="M7" s="83" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="81">
+      <c r="M7" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="N7" s="77">
+        <v>1.2426273148148149E-3</v>
+      </c>
+      <c r="O7" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
-      <c r="O7" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="P7" s="77">
-        <v>1.2426273148148149E-3</v>
-      </c>
-      <c r="Q7" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="R7" s="77">
-        <v>1.2426273148148149E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="Q7" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="R7" s="81">
+        <v>1.2742476851851851E-3</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -14813,25 +15052,29 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="N8" s="81">
+        <v>90</v>
+      </c>
+      <c r="N8" s="77">
+        <v>1.2478472222222222E-3</v>
+      </c>
+      <c r="O8" s="83" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
-      <c r="O8" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="P8" s="77">
-        <v>1.2478472222222222E-3</v>
-      </c>
       <c r="Q8" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="R8" s="77">
-        <v>1.2478472222222222E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>90</v>
+      </c>
+      <c r="R8" s="81">
+        <v>1.2452199074074073E-3</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -14849,25 +15092,29 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" s="81">
+        <v>91</v>
+      </c>
+      <c r="N9" s="77">
+        <v>1.248275462962963E-3</v>
+      </c>
+      <c r="O9" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
-      <c r="O9" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="77">
-        <v>1.248275462962963E-3</v>
-      </c>
       <c r="Q9" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="R9" s="77">
-        <v>1.248275462962963E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>91</v>
+      </c>
+      <c r="R9" s="81">
+        <v>1.2555324074074075E-3</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -14884,26 +15131,30 @@
       <c r="L10" s="81">
         <v>1.2430787037037037E-3</v>
       </c>
-      <c r="M10" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="N10" s="81">
+      <c r="M10" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="N10" s="77">
+        <v>1.2653240740740741E-3</v>
+      </c>
+      <c r="O10" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
-      <c r="O10" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="P10" s="77">
-        <v>1.2653240740740741E-3</v>
-      </c>
-      <c r="Q10" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="R10" s="77">
-        <v>1.2653240740740741E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="Q10" s="83" t="s">
+        <v>92</v>
+      </c>
+      <c r="R10" s="81">
+        <v>1.2631365740740741E-3</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -14921,25 +15172,29 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="81">
+        <v>93</v>
+      </c>
+      <c r="N11" s="77">
+        <v>1.6837615740740741E-3</v>
+      </c>
+      <c r="O11" s="83" t="s">
+        <v>93</v>
+      </c>
+      <c r="P11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
-      <c r="O11" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="P11" s="77">
-        <v>1.6837615740740741E-3</v>
-      </c>
       <c r="Q11" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="77">
-        <v>1.6837615740740741E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>93</v>
+      </c>
+      <c r="R11" s="81">
+        <v>1.4671412037037036E-3</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -14957,25 +15212,29 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="N12" s="81">
+        <v>94</v>
+      </c>
+      <c r="N12" s="77">
+        <v>1.543287037037037E-3</v>
+      </c>
+      <c r="O12" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="P12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
-      <c r="O12" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="P12" s="77">
-        <v>1.543287037037037E-3</v>
-      </c>
       <c r="Q12" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="R12" s="77">
-        <v>1.543287037037037E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>94</v>
+      </c>
+      <c r="R12" s="81">
+        <v>1.5160185185185185E-3</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -14993,25 +15252,29 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" s="81">
+        <v>95</v>
+      </c>
+      <c r="N13" s="77">
+        <v>1.9202893518518521E-3</v>
+      </c>
+      <c r="O13" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="P13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
-      <c r="O13" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="P13" s="77">
-        <v>1.9202893518518521E-3</v>
-      </c>
       <c r="Q13" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="R13" s="77">
-        <v>1.9202893518518521E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>95</v>
+      </c>
+      <c r="R13" s="81">
+        <v>1.9527199074074074E-3</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -15029,25 +15292,29 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="N14" s="81">
+        <v>96</v>
+      </c>
+      <c r="N14" s="77">
+        <v>1.2480787037037037E-3</v>
+      </c>
+      <c r="O14" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
-      <c r="O14" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="P14" s="77">
-        <v>1.2480787037037037E-3</v>
-      </c>
       <c r="Q14" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="R14" s="77">
-        <v>1.2480787037037037E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>96</v>
+      </c>
+      <c r="R14" s="81">
+        <v>1.2462037037037036E-3</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -15064,26 +15331,30 @@
       <c r="L15" s="81">
         <v>1.236238425925926E-3</v>
       </c>
-      <c r="M15" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="N15" s="81">
+      <c r="M15" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="N15" s="77">
+        <v>1.241701388888889E-3</v>
+      </c>
+      <c r="O15" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
-      <c r="O15" s="87" t="s">
-        <v>96</v>
-      </c>
-      <c r="P15" s="77">
-        <v>1.241701388888889E-3</v>
-      </c>
-      <c r="Q15" s="87" t="s">
-        <v>96</v>
-      </c>
-      <c r="R15" s="77">
-        <v>1.241701388888889E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="Q15" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="R15" s="81">
+        <v>1.2494560185185185E-3</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -15100,26 +15371,30 @@
       <c r="L16" s="81">
         <v>1.2310648148148148E-3</v>
       </c>
-      <c r="M16" s="83" t="s">
-        <v>97</v>
-      </c>
-      <c r="N16" s="81">
+      <c r="M16" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="N16" s="77">
+        <v>1.2480208333333334E-3</v>
+      </c>
+      <c r="O16" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
-      <c r="O16" s="88" t="s">
-        <v>97</v>
-      </c>
-      <c r="P16" s="77">
-        <v>1.2480208333333334E-3</v>
-      </c>
-      <c r="Q16" s="88" t="s">
-        <v>97</v>
-      </c>
-      <c r="R16" s="77">
-        <v>1.2480208333333334E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="Q16" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="R16" s="81">
+        <v>1.2403703703703704E-3</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -15137,25 +15412,30 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="N17" s="82">
+        <v>99</v>
+      </c>
+      <c r="N17" s="80">
+        <v>1.2779629629629629E-3</v>
+      </c>
+      <c r="O17" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
-      <c r="O17" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="P17" s="80">
-        <v>1.2779629629629629E-3</v>
-      </c>
       <c r="Q17" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="R17" s="80">
-        <v>1.2779629629629629E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>99</v>
+      </c>
+      <c r="R17" s="82">
+        <v>1.2507638888888889E-3</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -15174,8 +15454,13 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -15188,26 +15473,31 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="58">
-        <f>+AVERAGE(L3:L10)</f>
-        <v>1.2600376157407408E-3</v>
-      </c>
-      <c r="M19" s="1"/>
+        <f>+AVERAGE(L3:L10,L14:L17)</f>
+        <v>1.2562307098765433E-3</v>
+      </c>
+      <c r="M19" s="75"/>
       <c r="N19" s="58">
-        <f>+AVERAGE(N3:N10)</f>
-        <v>1.2902980324074075E-3</v>
+        <f>+AVERAGE(N3:N10,N14:N17)</f>
+        <v>1.2587731481481482E-3</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="58">
-        <f>+AVERAGE(P3:P10)</f>
-        <v>1.2611892361111109E-3</v>
-      </c>
-      <c r="Q19" s="1"/>
+        <f>+AVERAGE(P3:P10,P14:P17)</f>
+        <v>1.2757648533950618E-3</v>
+      </c>
+      <c r="Q19" s="75"/>
       <c r="R19" s="58">
-        <f>+AVERAGE(R3:R10)</f>
-        <v>1.2611892361111109E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <f>+AVERAGE(R3:R10,R14:R17)</f>
+        <v>1.2757648533950618E-3</v>
+      </c>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -15219,27 +15509,20 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="58">
-        <f>+AVERAGE(L14:L17)</f>
-        <v>1.248616898148148E-3</v>
-      </c>
+      <c r="L20" s="58"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="58">
-        <f>+AVERAGE(N14:N17)</f>
-        <v>1.2466984953703702E-3</v>
-      </c>
+      <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="58">
-        <f>+AVERAGE(P14:P17)</f>
-        <v>1.2539409722222223E-3</v>
-      </c>
+      <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="58">
-        <f>+AVERAGE(R14:R17)</f>
-        <v>1.2539409722222223E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -15251,27 +15534,32 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="58">
+      <c r="L21" s="89">
         <f>+AVERAGE(L19:L20)</f>
-        <v>1.2543272569444444E-3</v>
-      </c>
-      <c r="M21" s="75"/>
-      <c r="N21" s="58">
-        <f>+AVERAGE(N19:N20)</f>
-        <v>1.2684982638888889E-3</v>
-      </c>
-      <c r="O21" s="75"/>
-      <c r="P21" s="58">
-        <f>+AVERAGE(P19:P20)</f>
-        <v>1.2575651041666666E-3</v>
-      </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="58">
-        <f>+AVERAGE(R19:R20)</f>
-        <v>1.2575651041666666E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>1.2562307098765433E-3</v>
+      </c>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91">
+        <f>+SUM(N19-L19)</f>
+        <v>2.5424382716048976E-6</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="91">
+        <f>+SUM(P19-L19)</f>
+        <v>1.9534143518518555E-5</v>
+      </c>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="91">
+        <f>+SUM(R19-L19)</f>
+        <v>1.9534143518518555E-5</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -15283,15 +15571,20 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="58"/>
+      <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -15303,32 +15596,1752 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="89">
-        <f>+AVERAGE(L21:L22)</f>
-        <v>1.2543272569444444E-3</v>
-      </c>
-      <c r="M23" s="90"/>
-      <c r="N23" s="91">
-        <f>+SUM(N21-L21)</f>
-        <v>1.4171006944444474E-5</v>
-      </c>
-      <c r="O23" s="90"/>
-      <c r="P23" s="91">
-        <f>+SUM(P21-L21)</f>
-        <v>3.2378472222221837E-6</v>
-      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-      <c r="R23" s="91">
-        <v>3.2378472222221837E-6</v>
-      </c>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+    </row>
+    <row r="25" spans="1:23" ht="34.5">
+      <c r="A25" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="97"/>
+      <c r="C25" s="97"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="L25" s="97"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="97"/>
+      <c r="P25" s="97"/>
+      <c r="Q25" s="97"/>
+      <c r="R25" s="97"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="96"/>
+      <c r="C26" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="96"/>
+      <c r="E26" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="114"/>
+      <c r="G26" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="96"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="L26" s="96"/>
+      <c r="M26" s="95" t="s">
+        <v>82</v>
+      </c>
+      <c r="N26" s="96"/>
+      <c r="O26" s="113" t="s">
+        <v>83</v>
+      </c>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="R26" s="96"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="119">
+        <v>1</v>
+      </c>
+      <c r="B27" s="120">
+        <v>1.1538888888888888E-3</v>
+      </c>
+      <c r="C27" s="119">
+        <v>1</v>
+      </c>
+      <c r="D27" s="120">
+        <v>1.1476041666666666E-3</v>
+      </c>
+      <c r="E27" s="119">
+        <v>1</v>
+      </c>
+      <c r="F27" s="120">
+        <v>1.1644560185185187E-3</v>
+      </c>
+      <c r="G27" s="121">
+        <v>1</v>
+      </c>
+      <c r="H27" s="122">
+        <v>1.1644560185185187E-3</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="123">
+        <v>1</v>
+      </c>
+      <c r="L27" s="124">
+        <v>1.4355671296296297E-3</v>
+      </c>
+      <c r="M27" s="123">
+        <v>1</v>
+      </c>
+      <c r="N27" s="124">
+        <v>1.4123148148148148E-3</v>
+      </c>
+      <c r="O27" s="115">
+        <v>1</v>
+      </c>
+      <c r="P27" s="116">
+        <v>1.4081597222222223E-3</v>
+      </c>
+      <c r="Q27" s="123">
+        <v>1</v>
+      </c>
+      <c r="R27" s="124">
+        <v>1.4081597222222223E-3</v>
+      </c>
+      <c r="S27" s="94"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" s="119">
+        <v>2</v>
+      </c>
+      <c r="B28" s="120">
+        <v>1.1098379629629629E-3</v>
+      </c>
+      <c r="C28" s="119">
+        <v>2</v>
+      </c>
+      <c r="D28" s="120">
+        <v>1.1111458333333333E-3</v>
+      </c>
+      <c r="E28" s="119">
+        <v>2</v>
+      </c>
+      <c r="F28" s="120">
+        <v>1.1378703703703703E-3</v>
+      </c>
+      <c r="G28" s="121">
+        <v>2</v>
+      </c>
+      <c r="H28" s="122">
+        <v>1.1378703703703703E-3</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="123">
+        <v>2</v>
+      </c>
+      <c r="L28" s="124">
+        <v>1.1143287037037035E-3</v>
+      </c>
+      <c r="M28" s="123">
+        <v>2</v>
+      </c>
+      <c r="N28" s="124">
+        <v>1.1365393518518519E-3</v>
+      </c>
+      <c r="O28" s="115">
+        <v>2</v>
+      </c>
+      <c r="P28" s="116">
+        <v>1.1394212962962964E-3</v>
+      </c>
+      <c r="Q28" s="123">
+        <v>2</v>
+      </c>
+      <c r="R28" s="124">
+        <v>1.1394212962962964E-3</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="119">
+        <v>3</v>
+      </c>
+      <c r="B29" s="120">
+        <v>1.110173611111111E-3</v>
+      </c>
+      <c r="C29" s="119">
+        <v>3</v>
+      </c>
+      <c r="D29" s="120">
+        <v>1.0993171296296296E-3</v>
+      </c>
+      <c r="E29" s="119">
+        <v>3</v>
+      </c>
+      <c r="F29" s="120">
+        <v>1.1312268518518518E-3</v>
+      </c>
+      <c r="G29" s="121">
+        <v>3</v>
+      </c>
+      <c r="H29" s="122">
+        <v>1.1312268518518518E-3</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="123">
+        <v>3</v>
+      </c>
+      <c r="L29" s="124">
+        <v>1.1773726851851852E-3</v>
+      </c>
+      <c r="M29" s="123">
+        <v>3</v>
+      </c>
+      <c r="N29" s="124">
+        <v>1.1328703703703702E-3</v>
+      </c>
+      <c r="O29" s="115">
+        <v>3</v>
+      </c>
+      <c r="P29" s="116">
+        <v>1.1317361111111111E-3</v>
+      </c>
+      <c r="Q29" s="123">
+        <v>3</v>
+      </c>
+      <c r="R29" s="124">
+        <v>1.1317361111111111E-3</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="119">
+        <v>4</v>
+      </c>
+      <c r="B30" s="120">
+        <v>1.1127083333333334E-3</v>
+      </c>
+      <c r="C30" s="119">
+        <v>4</v>
+      </c>
+      <c r="D30" s="120">
+        <v>1.0976736111111111E-3</v>
+      </c>
+      <c r="E30" s="119">
+        <v>4</v>
+      </c>
+      <c r="F30" s="120">
+        <v>1.1532986111111112E-3</v>
+      </c>
+      <c r="G30" s="121">
+        <v>4</v>
+      </c>
+      <c r="H30" s="122">
+        <v>1.1532986111111112E-3</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="123">
+        <v>4</v>
+      </c>
+      <c r="L30" s="124">
+        <v>1.1155787037037037E-3</v>
+      </c>
+      <c r="M30" s="123">
+        <v>4</v>
+      </c>
+      <c r="N30" s="124">
+        <v>1.1118055555555556E-3</v>
+      </c>
+      <c r="O30" s="115">
+        <v>4</v>
+      </c>
+      <c r="P30" s="116">
+        <v>2.0264583333333337E-3</v>
+      </c>
+      <c r="Q30" s="123">
+        <v>4</v>
+      </c>
+      <c r="R30" s="124">
+        <v>2.0264583333333337E-3</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" s="119">
+        <v>5</v>
+      </c>
+      <c r="B31" s="120">
+        <v>1.1121296296296296E-3</v>
+      </c>
+      <c r="C31" s="119">
+        <v>5</v>
+      </c>
+      <c r="D31" s="120">
+        <v>1.1186458333333335E-3</v>
+      </c>
+      <c r="E31" s="119">
+        <v>5</v>
+      </c>
+      <c r="F31" s="120">
+        <v>1.1660416666666668E-3</v>
+      </c>
+      <c r="G31" s="121">
+        <v>5</v>
+      </c>
+      <c r="H31" s="122">
+        <v>1.1660416666666668E-3</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="123">
+        <v>5</v>
+      </c>
+      <c r="L31" s="124">
+        <v>1.1346180555555556E-3</v>
+      </c>
+      <c r="M31" s="123">
+        <v>5</v>
+      </c>
+      <c r="N31" s="124">
+        <v>1.0958333333333334E-3</v>
+      </c>
+      <c r="O31" s="115">
+        <v>5</v>
+      </c>
+      <c r="P31" s="116">
+        <v>1.198900462962963E-3</v>
+      </c>
+      <c r="Q31" s="123">
+        <v>5</v>
+      </c>
+      <c r="R31" s="124">
+        <v>1.198900462962963E-3</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" s="119">
+        <v>6</v>
+      </c>
+      <c r="B32" s="120">
+        <v>1.1231828703703705E-3</v>
+      </c>
+      <c r="C32" s="119">
+        <v>6</v>
+      </c>
+      <c r="D32" s="120">
+        <v>1.1192708333333332E-3</v>
+      </c>
+      <c r="E32" s="119">
+        <v>6</v>
+      </c>
+      <c r="F32" s="120">
+        <v>1.1783333333333333E-3</v>
+      </c>
+      <c r="G32" s="121">
+        <v>6</v>
+      </c>
+      <c r="H32" s="122">
+        <v>1.1783333333333333E-3</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="123">
+        <v>6</v>
+      </c>
+      <c r="L32" s="124">
+        <v>1.1811458333333333E-3</v>
+      </c>
+      <c r="M32" s="123">
+        <v>6</v>
+      </c>
+      <c r="N32" s="124">
+        <v>1.1103587962962964E-3</v>
+      </c>
+      <c r="O32" s="115">
+        <v>6</v>
+      </c>
+      <c r="P32" s="116">
+        <v>1.3676157407407409E-3</v>
+      </c>
+      <c r="Q32" s="123">
+        <v>6</v>
+      </c>
+      <c r="R32" s="124">
+        <v>1.3676157407407409E-3</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" s="119">
+        <v>7</v>
+      </c>
+      <c r="B33" s="120">
+        <v>1.1183564814814815E-3</v>
+      </c>
+      <c r="C33" s="119">
+        <v>7</v>
+      </c>
+      <c r="D33" s="120">
+        <v>1.1119675925925926E-3</v>
+      </c>
+      <c r="E33" s="119">
+        <v>7</v>
+      </c>
+      <c r="F33" s="120">
+        <v>1.1461342592592593E-3</v>
+      </c>
+      <c r="G33" s="121">
+        <v>7</v>
+      </c>
+      <c r="H33" s="122">
+        <v>1.1461342592592593E-3</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="123">
+        <v>7</v>
+      </c>
+      <c r="L33" s="124">
+        <v>1.1964467592592591E-3</v>
+      </c>
+      <c r="M33" s="123">
+        <v>7</v>
+      </c>
+      <c r="N33" s="124">
+        <v>1.1330787037037036E-3</v>
+      </c>
+      <c r="O33" s="115">
+        <v>7</v>
+      </c>
+      <c r="P33" s="116">
+        <v>1.2607407407407407E-3</v>
+      </c>
+      <c r="Q33" s="123">
+        <v>7</v>
+      </c>
+      <c r="R33" s="124">
+        <v>1.2607407407407407E-3</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" s="119">
+        <v>8</v>
+      </c>
+      <c r="B34" s="120">
+        <v>1.124398148148148E-3</v>
+      </c>
+      <c r="C34" s="119">
+        <v>8</v>
+      </c>
+      <c r="D34" s="120">
+        <v>1.1048148148148148E-3</v>
+      </c>
+      <c r="E34" s="119">
+        <v>8</v>
+      </c>
+      <c r="F34" s="120">
+        <v>1.2261226851851851E-3</v>
+      </c>
+      <c r="G34" s="121">
+        <v>8</v>
+      </c>
+      <c r="H34" s="122">
+        <v>1.2261226851851851E-3</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="123">
+        <v>8</v>
+      </c>
+      <c r="L34" s="124">
+        <v>1.1544097222222223E-3</v>
+      </c>
+      <c r="M34" s="123">
+        <v>8</v>
+      </c>
+      <c r="N34" s="124">
+        <v>1.1489930555555554E-3</v>
+      </c>
+      <c r="O34" s="115">
+        <v>8</v>
+      </c>
+      <c r="P34" s="116">
+        <v>1.1238657407407408E-3</v>
+      </c>
+      <c r="Q34" s="123">
+        <v>8</v>
+      </c>
+      <c r="R34" s="124">
+        <v>1.1238657407407408E-3</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="119">
+        <v>9</v>
+      </c>
+      <c r="B35" s="120">
+        <v>1.2592476851851853E-3</v>
+      </c>
+      <c r="C35" s="119">
+        <v>9</v>
+      </c>
+      <c r="D35" s="120">
+        <v>1.0967939814814816E-3</v>
+      </c>
+      <c r="E35" s="119">
+        <v>9</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1.1561111111111112E-3</v>
+      </c>
+      <c r="G35" s="121">
+        <v>9</v>
+      </c>
+      <c r="H35" s="122">
+        <v>1.1561111111111112E-3</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="123">
+        <v>9</v>
+      </c>
+      <c r="L35" s="124">
+        <v>1.2505092592592592E-3</v>
+      </c>
+      <c r="M35" s="123">
+        <v>9</v>
+      </c>
+      <c r="N35" s="124">
+        <v>1.1331134259259261E-3</v>
+      </c>
+      <c r="O35" s="115">
+        <v>9</v>
+      </c>
+      <c r="P35" s="116">
+        <v>1.2741203703703703E-3</v>
+      </c>
+      <c r="Q35" s="123">
+        <v>9</v>
+      </c>
+      <c r="R35" s="124">
+        <v>1.2741203703703703E-3</v>
+      </c>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="119">
+        <v>10</v>
+      </c>
+      <c r="B36" s="120">
+        <v>1.1363194444444444E-3</v>
+      </c>
+      <c r="C36" s="119">
+        <v>10</v>
+      </c>
+      <c r="D36" s="120">
+        <v>1.1534143518518519E-3</v>
+      </c>
+      <c r="E36" s="119">
+        <v>10</v>
+      </c>
+      <c r="F36" s="120">
+        <v>1.1621296296296297E-3</v>
+      </c>
+      <c r="G36" s="121">
+        <v>10</v>
+      </c>
+      <c r="H36" s="122">
+        <v>1.1621296296296297E-3</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="123">
+        <v>10</v>
+      </c>
+      <c r="L36" s="124">
+        <v>1.1465856481481481E-3</v>
+      </c>
+      <c r="M36" s="123">
+        <v>10</v>
+      </c>
+      <c r="N36" s="124">
+        <v>1.1556481481481481E-3</v>
+      </c>
+      <c r="O36" s="115">
+        <v>10</v>
+      </c>
+      <c r="P36" s="116">
+        <v>1.1596180555555557E-3</v>
+      </c>
+      <c r="Q36" s="123">
+        <v>10</v>
+      </c>
+      <c r="R36" s="124">
+        <v>1.1596180555555557E-3</v>
+      </c>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="119">
+        <v>11</v>
+      </c>
+      <c r="B37" s="120">
+        <v>1.3982291666666668E-3</v>
+      </c>
+      <c r="C37" s="119">
+        <v>11</v>
+      </c>
+      <c r="D37" s="120">
+        <v>1.2330902777777778E-3</v>
+      </c>
+      <c r="E37" s="119">
+        <v>11</v>
+      </c>
+      <c r="F37" s="120">
+        <v>1.2419907407407406E-3</v>
+      </c>
+      <c r="G37" s="121">
+        <v>11</v>
+      </c>
+      <c r="H37" s="122">
+        <v>1.2419907407407406E-3</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="123">
+        <v>11</v>
+      </c>
+      <c r="L37" s="124">
+        <v>1.1611226851851852E-3</v>
+      </c>
+      <c r="M37" s="123">
+        <v>11</v>
+      </c>
+      <c r="N37" s="124">
+        <v>1.2279976851851851E-3</v>
+      </c>
+      <c r="O37" s="115">
+        <v>11</v>
+      </c>
+      <c r="P37" s="116">
+        <v>2.1243171296296296E-3</v>
+      </c>
+      <c r="Q37" s="123">
+        <v>11</v>
+      </c>
+      <c r="R37" s="124">
+        <v>2.1243171296296296E-3</v>
+      </c>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="119">
+        <v>12</v>
+      </c>
+      <c r="B38" s="120">
+        <v>1.5461458333333332E-3</v>
+      </c>
+      <c r="C38" s="119">
+        <v>12</v>
+      </c>
+      <c r="D38" s="120">
+        <v>1.9078009259259261E-3</v>
+      </c>
+      <c r="E38" s="119">
+        <v>12</v>
+      </c>
+      <c r="F38" s="120">
+        <v>1.4453819444444444E-3</v>
+      </c>
+      <c r="G38" s="121">
+        <v>12</v>
+      </c>
+      <c r="H38" s="122">
+        <v>1.4453819444444444E-3</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="123">
+        <v>12</v>
+      </c>
+      <c r="L38" s="124">
+        <v>1.3398611111111113E-3</v>
+      </c>
+      <c r="M38" s="123">
+        <v>12</v>
+      </c>
+      <c r="N38" s="124">
+        <v>1.310949074074074E-3</v>
+      </c>
+      <c r="O38" s="115">
+        <v>12</v>
+      </c>
+      <c r="P38" s="116">
+        <v>1.4692245370370371E-3</v>
+      </c>
+      <c r="Q38" s="123">
+        <v>12</v>
+      </c>
+      <c r="R38" s="124">
+        <v>1.4692245370370371E-3</v>
+      </c>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="119">
+        <v>13</v>
+      </c>
+      <c r="B39" s="120">
+        <v>1.2216550925925925E-3</v>
+      </c>
+      <c r="C39" s="119">
+        <v>13</v>
+      </c>
+      <c r="D39" s="120">
+        <v>1.2544560185185185E-3</v>
+      </c>
+      <c r="E39" s="119">
+        <v>13</v>
+      </c>
+      <c r="F39" s="120">
+        <v>1.2557175925925926E-3</v>
+      </c>
+      <c r="G39" s="121">
+        <v>13</v>
+      </c>
+      <c r="H39" s="122">
+        <v>1.2557175925925926E-3</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="123">
+        <v>13</v>
+      </c>
+      <c r="L39" s="124">
+        <v>3.8921759259259257E-3</v>
+      </c>
+      <c r="M39" s="123">
+        <v>13</v>
+      </c>
+      <c r="N39" s="124">
+        <v>4.1754282407407408E-3</v>
+      </c>
+      <c r="O39" s="115">
+        <v>13</v>
+      </c>
+      <c r="P39" s="116">
+        <v>1.6091435185185184E-3</v>
+      </c>
+      <c r="Q39" s="123">
+        <v>13</v>
+      </c>
+      <c r="R39" s="124">
+        <v>1.6091435185185184E-3</v>
+      </c>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="119">
+        <v>14</v>
+      </c>
+      <c r="B40" s="120">
+        <v>1.1457523148148147E-3</v>
+      </c>
+      <c r="C40" s="119">
+        <v>14</v>
+      </c>
+      <c r="D40" s="120">
+        <v>1.1745949074074074E-3</v>
+      </c>
+      <c r="E40" s="119">
+        <v>14</v>
+      </c>
+      <c r="F40" s="120">
+        <v>1.1743055555555556E-3</v>
+      </c>
+      <c r="G40" s="121">
+        <v>14</v>
+      </c>
+      <c r="H40" s="122">
+        <v>1.1743055555555556E-3</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="123">
+        <v>14</v>
+      </c>
+      <c r="L40" s="124">
+        <v>1.1608564814814815E-3</v>
+      </c>
+      <c r="M40" s="123">
+        <v>14</v>
+      </c>
+      <c r="N40" s="124">
+        <v>1.1806365740740742E-3</v>
+      </c>
+      <c r="O40" s="115">
+        <v>14</v>
+      </c>
+      <c r="P40" s="116">
+        <v>1.1635069444444444E-3</v>
+      </c>
+      <c r="Q40" s="123">
+        <v>14</v>
+      </c>
+      <c r="R40" s="124">
+        <v>1.1635069444444444E-3</v>
+      </c>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="119">
+        <v>15</v>
+      </c>
+      <c r="B41" s="120">
+        <v>1.5789930555555557E-3</v>
+      </c>
+      <c r="C41" s="119">
+        <v>15</v>
+      </c>
+      <c r="D41" s="120">
+        <v>1.544236111111111E-3</v>
+      </c>
+      <c r="E41" s="119">
+        <v>15</v>
+      </c>
+      <c r="F41" s="120">
+        <v>1.5701967592592592E-3</v>
+      </c>
+      <c r="G41" s="121">
+        <v>15</v>
+      </c>
+      <c r="H41" s="122">
+        <v>1.5701967592592592E-3</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="123">
+        <v>15</v>
+      </c>
+      <c r="L41" s="124">
+        <v>1.1989930555555556E-3</v>
+      </c>
+      <c r="M41" s="123">
+        <v>15</v>
+      </c>
+      <c r="N41" s="124">
+        <v>1.1869444444444445E-3</v>
+      </c>
+      <c r="O41" s="115">
+        <v>15</v>
+      </c>
+      <c r="P41" s="116">
+        <v>1.1449421296296297E-3</v>
+      </c>
+      <c r="Q41" s="123">
+        <v>15</v>
+      </c>
+      <c r="R41" s="124">
+        <v>1.1449421296296297E-3</v>
+      </c>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="119">
+        <v>16</v>
+      </c>
+      <c r="B42" s="120">
+        <v>1.1158217592592591E-3</v>
+      </c>
+      <c r="C42" s="119">
+        <v>16</v>
+      </c>
+      <c r="D42" s="120">
+        <v>1.1127083333333334E-3</v>
+      </c>
+      <c r="E42" s="119">
+        <v>16</v>
+      </c>
+      <c r="F42" s="120">
+        <v>1.2513888888888889E-3</v>
+      </c>
+      <c r="G42" s="121">
+        <v>16</v>
+      </c>
+      <c r="H42" s="122">
+        <v>1.2513888888888889E-3</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="123">
+        <v>16</v>
+      </c>
+      <c r="L42" s="124">
+        <v>1.1175E-3</v>
+      </c>
+      <c r="M42" s="123">
+        <v>16</v>
+      </c>
+      <c r="N42" s="124">
+        <v>1.1115046296296296E-3</v>
+      </c>
+      <c r="O42" s="115">
+        <v>16</v>
+      </c>
+      <c r="P42" s="116">
+        <v>1.140324074074074E-3</v>
+      </c>
+      <c r="Q42" s="123">
+        <v>16</v>
+      </c>
+      <c r="R42" s="124">
+        <v>1.140324074074074E-3</v>
+      </c>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="119">
+        <v>17</v>
+      </c>
+      <c r="B43" s="120">
+        <v>1.1162731481481481E-3</v>
+      </c>
+      <c r="C43" s="119">
+        <v>17</v>
+      </c>
+      <c r="D43" s="120">
+        <v>1.1204629629629629E-3</v>
+      </c>
+      <c r="E43" s="119">
+        <v>17</v>
+      </c>
+      <c r="F43" s="120">
+        <v>1.1524421296296296E-3</v>
+      </c>
+      <c r="G43" s="121">
+        <v>17</v>
+      </c>
+      <c r="H43" s="122">
+        <v>1.1524421296296296E-3</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="123">
+        <v>17</v>
+      </c>
+      <c r="L43" s="124">
+        <v>1.133587962962963E-3</v>
+      </c>
+      <c r="M43" s="123">
+        <v>17</v>
+      </c>
+      <c r="N43" s="124">
+        <v>1.1427777777777777E-3</v>
+      </c>
+      <c r="O43" s="115">
+        <v>17</v>
+      </c>
+      <c r="P43" s="116">
+        <v>1.1632407407407407E-3</v>
+      </c>
+      <c r="Q43" s="123">
+        <v>17</v>
+      </c>
+      <c r="R43" s="124">
+        <v>1.1632407407407407E-3</v>
+      </c>
+      <c r="S43" s="58"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="119">
+        <v>18</v>
+      </c>
+      <c r="B44" s="120">
+        <v>1.114398148148148E-3</v>
+      </c>
+      <c r="C44" s="119">
+        <v>18</v>
+      </c>
+      <c r="D44" s="120">
+        <v>1.1069444444444445E-3</v>
+      </c>
+      <c r="E44" s="119">
+        <v>18</v>
+      </c>
+      <c r="F44" s="120">
+        <v>1.1676157407407408E-3</v>
+      </c>
+      <c r="G44" s="121">
+        <v>18</v>
+      </c>
+      <c r="H44" s="122">
+        <v>1.1676157407407408E-3</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="123">
+        <v>18</v>
+      </c>
+      <c r="L44" s="124">
+        <v>1.1378240740740741E-3</v>
+      </c>
+      <c r="M44" s="123">
+        <v>18</v>
+      </c>
+      <c r="N44" s="124">
+        <v>1.1362962962962963E-3</v>
+      </c>
+      <c r="O44" s="115">
+        <v>18</v>
+      </c>
+      <c r="P44" s="116">
+        <v>1.1319444444444443E-3</v>
+      </c>
+      <c r="Q44" s="123">
+        <v>18</v>
+      </c>
+      <c r="R44" s="124">
+        <v>1.1319444444444443E-3</v>
+      </c>
+      <c r="S44" s="58"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="119">
+        <v>19</v>
+      </c>
+      <c r="B45" s="120">
+        <v>1.1236805555555555E-3</v>
+      </c>
+      <c r="C45" s="119">
+        <v>19</v>
+      </c>
+      <c r="D45" s="120">
+        <v>1.1092129629629629E-3</v>
+      </c>
+      <c r="E45" s="119">
+        <v>19</v>
+      </c>
+      <c r="F45" s="120">
+        <v>1.1594328703703703E-3</v>
+      </c>
+      <c r="G45" s="121">
+        <v>19</v>
+      </c>
+      <c r="H45" s="122">
+        <v>1.1594328703703703E-3</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="123">
+        <v>19</v>
+      </c>
+      <c r="L45" s="124">
+        <v>1.1439699074074073E-3</v>
+      </c>
+      <c r="M45" s="123">
+        <v>19</v>
+      </c>
+      <c r="N45" s="124">
+        <v>1.1471990740740739E-3</v>
+      </c>
+      <c r="O45" s="115">
+        <v>19</v>
+      </c>
+      <c r="P45" s="116">
+        <v>1.149375E-3</v>
+      </c>
+      <c r="Q45" s="123">
+        <v>19</v>
+      </c>
+      <c r="R45" s="124">
+        <v>1.149375E-3</v>
+      </c>
+      <c r="S45" s="58"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="119">
+        <v>20</v>
+      </c>
+      <c r="B46" s="120">
+        <v>1.1430092592592592E-3</v>
+      </c>
+      <c r="C46" s="119">
+        <v>20</v>
+      </c>
+      <c r="D46" s="120">
+        <v>1.1691319444444444E-3</v>
+      </c>
+      <c r="E46" s="119">
+        <v>20</v>
+      </c>
+      <c r="F46" s="120">
+        <v>1.2307523148148149E-3</v>
+      </c>
+      <c r="G46" s="121">
+        <v>20</v>
+      </c>
+      <c r="H46" s="122">
+        <v>1.2307523148148149E-3</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="125">
+        <v>20</v>
+      </c>
+      <c r="L46" s="126">
+        <v>1.1290277777777778E-3</v>
+      </c>
+      <c r="M46" s="125">
+        <v>20</v>
+      </c>
+      <c r="N46" s="126">
+        <v>1.1019907407407408E-3</v>
+      </c>
+      <c r="O46" s="117">
+        <v>20</v>
+      </c>
+      <c r="P46" s="118">
+        <v>1.1516666666666665E-3</v>
+      </c>
+      <c r="Q46" s="125">
+        <v>20</v>
+      </c>
+      <c r="R46" s="126">
+        <v>1.1516666666666665E-3</v>
+      </c>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" s="1"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="75"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="1"/>
+      <c r="B49" s="58">
+        <f>+AVERAGE(B27:B36,B40:B46)</f>
+        <v>1.1587159586056647E-3</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="58">
+        <f>+AVERAGE(D27:D36,D40:D46)</f>
+        <v>1.1469376361655772E-3</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="58">
+        <f>+AVERAGE(F27:F36,F40:F46)</f>
+        <v>1.1957563997821352E-3</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="58">
+        <f>+AVERAGE(H27:H36,H40:H46)</f>
+        <v>1.1957563997821352E-3</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="58">
+        <f>+AVERAGE(L27:L37,L40:L46)</f>
+        <v>1.1716358024691359E-3</v>
+      </c>
+      <c r="M49" s="1"/>
+      <c r="N49" s="58">
+        <f>+AVERAGE(N27:N37,N40:N46)</f>
+        <v>1.1558834876543207E-3</v>
+      </c>
+      <c r="O49" s="1"/>
+      <c r="P49" s="58">
+        <f>+AVERAGE(P27:P37,P40:P46)</f>
+        <v>1.2922196502057615E-3</v>
+      </c>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="58">
+        <f>+AVERAGE(R27:R37,R40:R46)</f>
+        <v>1.2922196502057615E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="1"/>
+      <c r="B51" s="91">
+        <f>+SUM(B49-D49)</f>
+        <v>1.1778322440087483E-5</v>
+      </c>
+      <c r="C51" s="90"/>
+      <c r="D51" s="58">
+        <v>1.1469376361655772E-3</v>
+      </c>
+      <c r="E51" s="90"/>
+      <c r="F51" s="91">
+        <f>+SUM(F49-D49)</f>
+        <v>4.8818763616557959E-5</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="91">
+        <f>+SUM(H49-D49)</f>
+        <v>4.8818763616557959E-5</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="91">
+        <f>+SUM(L49-N49)</f>
+        <v>1.5752314814815229E-5</v>
+      </c>
+      <c r="M51" s="90"/>
+      <c r="N51" s="58">
+        <v>1.1558834876543207E-3</v>
+      </c>
+      <c r="O51" s="90"/>
+      <c r="P51" s="91">
+        <f>+SUM(P49-N49)</f>
+        <v>1.3633616255144076E-4</v>
+      </c>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="91">
+        <f>+SUM(R49-N49)</f>
+        <v>1.3633616255144076E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="15">
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="M26:N26"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="K1:R1"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B76A17BE-6EA0-4506-951E-9FEFEA8AAF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C257708-D205-496E-A70A-8716091E9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="138" r:id="rId9"/>
+    <pivotCache cacheId="321" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="105">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>FECHA 4</t>
-  </si>
-  <si>
-    <t>Gana pablo por</t>
   </si>
   <si>
     <t>Mendoza</t>
@@ -1189,26 +1186,29 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1217,13 +1217,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1231,12 +1231,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1250,20 +1244,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -5118,7 +5115,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="321" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5769,26 +5766,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105" t="s">
+      <c r="A1" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="105"/>
+      <c r="D1" s="110"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5803,13 +5800,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="92">
+      <c r="A2" s="93">
         <v>1</v>
       </c>
-      <c r="B2" s="92">
+      <c r="B2" s="93">
         <v>25</v>
       </c>
-      <c r="C2" s="92">
+      <c r="C2" s="93">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5847,26 +5844,26 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="102" t="s">
+      <c r="R2" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="102"/>
-      <c r="T2" s="102"/>
-      <c r="U2" s="102"/>
-      <c r="V2" s="102"/>
-      <c r="W2" s="102"/>
-      <c r="X2" s="102"/>
-      <c r="Y2" s="102"/>
-      <c r="Z2" s="102"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="104"/>
+      <c r="Z2" s="104"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="92">
+      <c r="A3" s="93">
         <v>2</v>
       </c>
-      <c r="B3" s="92">
+      <c r="B3" s="93">
         <v>18</v>
       </c>
-      <c r="C3" s="92">
+      <c r="C3" s="93">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -5935,13 +5932,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="92">
+      <c r="A4" s="93">
         <v>3</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="93">
         <v>15</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="93">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -6004,13 +6001,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="92">
+      <c r="A5" s="93">
         <v>4</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="93">
         <v>12</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="93">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -6066,17 +6063,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="102" t="s">
+      <c r="R6" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="102"/>
-      <c r="T6" s="102"/>
-      <c r="U6" s="102"/>
-      <c r="V6" s="102"/>
-      <c r="W6" s="102"/>
-      <c r="X6" s="102"/>
-      <c r="Y6" s="102"/>
-      <c r="Z6" s="102"/>
+      <c r="S6" s="104"/>
+      <c r="T6" s="104"/>
+      <c r="U6" s="104"/>
+      <c r="V6" s="104"/>
+      <c r="W6" s="104"/>
+      <c r="X6" s="104"/>
+      <c r="Y6" s="104"/>
+      <c r="Z6" s="104"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6138,32 +6135,29 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="107">
+      <c r="G8" s="109">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="104"/>
-      <c r="I8" s="107">
+      <c r="H8" s="108"/>
+      <c r="I8" s="109">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="104"/>
-      <c r="K8" s="107">
+      <c r="J8" s="108"/>
+      <c r="K8" s="109">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="104"/>
-      <c r="M8" s="107">
+      <c r="L8" s="108"/>
+      <c r="M8" s="109">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="104"/>
+      <c r="N8" s="108"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="1">
-        <f>+SUM(I8-G8)</f>
-        <v>-2.5</v>
-      </c>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -6195,17 +6189,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="102" t="s">
+      <c r="R9" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="102"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="102"/>
-      <c r="V9" s="102"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="102"/>
-      <c r="Y9" s="102"/>
-      <c r="Z9" s="102"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="104"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="104"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="104"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="104"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6216,26 +6210,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="111">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106">
+      <c r="H10" s="111"/>
+      <c r="I10" s="111">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106">
+      <c r="J10" s="111"/>
+      <c r="K10" s="111">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106">
+      <c r="L10" s="111"/>
+      <c r="M10" s="111">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="106"/>
+      <c r="N10" s="111"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6268,26 +6262,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="98">
+      <c r="G11" s="102">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="99"/>
-      <c r="I11" s="98">
+      <c r="H11" s="103"/>
+      <c r="I11" s="102">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="99"/>
-      <c r="K11" s="98">
+      <c r="J11" s="103"/>
+      <c r="K11" s="102">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="99"/>
-      <c r="M11" s="98">
+      <c r="L11" s="103"/>
+      <c r="M11" s="102">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="99"/>
+      <c r="N11" s="103"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6310,40 +6304,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="98">
+      <c r="G12" s="102">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="99"/>
-      <c r="I12" s="98">
+      <c r="H12" s="103"/>
+      <c r="I12" s="102">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="99"/>
-      <c r="K12" s="98">
+      <c r="J12" s="103"/>
+      <c r="K12" s="102">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="99"/>
-      <c r="M12" s="98">
+      <c r="L12" s="103"/>
+      <c r="M12" s="102">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="99"/>
+      <c r="N12" s="103"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="102" t="s">
+      <c r="R12" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="102"/>
-      <c r="T12" s="102"/>
-      <c r="U12" s="102"/>
-      <c r="V12" s="102"/>
-      <c r="W12" s="102"/>
-      <c r="X12" s="102"/>
-      <c r="Y12" s="102"/>
-      <c r="Z12" s="102"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="104"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="104"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="104"/>
+      <c r="Y12" s="104"/>
+      <c r="Z12" s="104"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6389,17 +6383,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="102" t="s">
+      <c r="F14" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6628,32 +6622,29 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="107">
+      <c r="G21" s="109">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="104"/>
-      <c r="I21" s="103">
+      <c r="H21" s="108"/>
+      <c r="I21" s="107">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="104"/>
-      <c r="K21" s="103">
+      <c r="J21" s="108"/>
+      <c r="K21" s="107">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="104"/>
-      <c r="M21" s="103">
+      <c r="L21" s="108"/>
+      <c r="M21" s="107">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="104"/>
+      <c r="N21" s="108"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1">
-        <f>+SUM(I21-G21)+Q8</f>
-        <v>8.75</v>
-      </c>
+      <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickTop="1">
       <c r="A22" s="1"/>
@@ -6683,26 +6674,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="100">
+      <c r="G23" s="105">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="101"/>
-      <c r="I23" s="100">
+      <c r="H23" s="106"/>
+      <c r="I23" s="105">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="101"/>
-      <c r="K23" s="100">
+      <c r="J23" s="106"/>
+      <c r="K23" s="105">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="101"/>
-      <c r="M23" s="100">
+      <c r="L23" s="106"/>
+      <c r="M23" s="105">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="101"/>
+      <c r="N23" s="106"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6716,26 +6707,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="98">
+      <c r="G24" s="102">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="99"/>
-      <c r="I24" s="98">
+      <c r="H24" s="103"/>
+      <c r="I24" s="102">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="99"/>
-      <c r="K24" s="98">
+      <c r="J24" s="103"/>
+      <c r="K24" s="102">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="99"/>
-      <c r="M24" s="98">
+      <c r="L24" s="103"/>
+      <c r="M24" s="102">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="99"/>
+      <c r="N24" s="103"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6749,26 +6740,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="98">
+      <c r="G25" s="102">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="99"/>
-      <c r="I25" s="98">
+      <c r="H25" s="103"/>
+      <c r="I25" s="102">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="99"/>
-      <c r="K25" s="98">
+      <c r="J25" s="103"/>
+      <c r="K25" s="102">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="99"/>
-      <c r="M25" s="98">
+      <c r="L25" s="103"/>
+      <c r="M25" s="102">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="99"/>
+      <c r="N25" s="103"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6798,17 +6789,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="102" t="s">
+      <c r="F27" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="102"/>
-      <c r="H27" s="102"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="102"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -6889,10 +6880,7 @@
       </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1">
-        <f>+SUM(J29-H29)</f>
-        <v>7</v>
-      </c>
+      <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1"/>
@@ -6933,10 +6921,7 @@
       </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1">
-        <f>+SUM(J30-H30)</f>
-        <v>5.25</v>
-      </c>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="1"/>
@@ -7012,32 +6997,29 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="103">
+      <c r="G34" s="107">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="104"/>
-      <c r="I34" s="103">
+      <c r="H34" s="108"/>
+      <c r="I34" s="107">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="104"/>
-      <c r="K34" s="103">
+      <c r="J34" s="108"/>
+      <c r="K34" s="107">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="104"/>
-      <c r="M34" s="103">
+      <c r="L34" s="108"/>
+      <c r="M34" s="107">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="104"/>
+      <c r="N34" s="108"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1">
-        <f>+SUM(I34-G34)+Q21</f>
-        <v>24</v>
-      </c>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -7069,26 +7051,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="100">
+      <c r="G36" s="105">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="101"/>
-      <c r="I36" s="100">
+      <c r="H36" s="106"/>
+      <c r="I36" s="105">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="101"/>
-      <c r="K36" s="100">
+      <c r="J36" s="106"/>
+      <c r="K36" s="105">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="101"/>
-      <c r="M36" s="100">
+      <c r="L36" s="106"/>
+      <c r="M36" s="105">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="101"/>
+      <c r="N36" s="106"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7103,26 +7085,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="98">
+      <c r="G37" s="102">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="99"/>
-      <c r="I37" s="98">
+      <c r="H37" s="103"/>
+      <c r="I37" s="102">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="99"/>
-      <c r="K37" s="98">
+      <c r="J37" s="103"/>
+      <c r="K37" s="102">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="99"/>
-      <c r="M37" s="98">
+      <c r="L37" s="103"/>
+      <c r="M37" s="102">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="99"/>
+      <c r="N37" s="103"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7137,26 +7119,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="98">
+      <c r="G38" s="102">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="99"/>
-      <c r="I38" s="98">
+      <c r="H38" s="103"/>
+      <c r="I38" s="102">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="99"/>
-      <c r="K38" s="98">
+      <c r="J38" s="103"/>
+      <c r="K38" s="102">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="99"/>
-      <c r="M38" s="98">
+      <c r="L38" s="103"/>
+      <c r="M38" s="102">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="99"/>
+      <c r="N38" s="103"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7188,17 +7170,17 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="102" t="s">
+      <c r="F40" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="102"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="102"/>
-      <c r="L40" s="102"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="102"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="104"/>
+      <c r="N40" s="104"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -7395,9 +7377,7 @@
       <c r="N46" s="5"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
@@ -7409,32 +7389,29 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="103">
+      <c r="G47" s="107">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="104"/>
-      <c r="I47" s="103">
+      <c r="H47" s="108"/>
+      <c r="I47" s="107">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="104"/>
-      <c r="K47" s="103">
+      <c r="J47" s="108"/>
+      <c r="K47" s="107">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="104"/>
-      <c r="M47" s="103">
+      <c r="L47" s="108"/>
+      <c r="M47" s="107">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="104"/>
+      <c r="N47" s="108"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="1">
-        <f>+SUM(I47-G47)+Q34</f>
-        <v>6.75</v>
-      </c>
+      <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
@@ -7466,76 +7443,76 @@
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="100">
+      <c r="G49" s="105">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="101"/>
-      <c r="I49" s="100">
+      <c r="H49" s="106"/>
+      <c r="I49" s="105">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="101"/>
-      <c r="K49" s="100">
+      <c r="J49" s="106"/>
+      <c r="K49" s="105">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="101"/>
-      <c r="M49" s="100">
+      <c r="L49" s="106"/>
+      <c r="M49" s="105">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="101"/>
+      <c r="N49" s="106"/>
     </row>
     <row r="50" spans="6:14">
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="98">
+      <c r="G50" s="102">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="99"/>
-      <c r="I50" s="98">
+      <c r="H50" s="103"/>
+      <c r="I50" s="102">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="99"/>
-      <c r="K50" s="98">
+      <c r="J50" s="103"/>
+      <c r="K50" s="102">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="99"/>
-      <c r="M50" s="98">
+      <c r="L50" s="103"/>
+      <c r="M50" s="102">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="99"/>
+      <c r="N50" s="103"/>
     </row>
     <row r="51" spans="6:14">
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="98">
+      <c r="G51" s="102">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="99"/>
-      <c r="I51" s="98">
+      <c r="H51" s="103"/>
+      <c r="I51" s="102">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="99"/>
-      <c r="K51" s="98">
+      <c r="J51" s="103"/>
+      <c r="K51" s="102">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="99"/>
-      <c r="M51" s="98">
+      <c r="L51" s="103"/>
+      <c r="M51" s="102">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="99"/>
+      <c r="N51" s="103"/>
     </row>
     <row r="52" spans="6:14">
       <c r="F52" s="27"/>
@@ -7549,21 +7526,21 @@
       <c r="N52" s="28"/>
     </row>
     <row r="53" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F53" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="102"/>
-      <c r="H53" s="102"/>
-      <c r="I53" s="102"/>
-      <c r="J53" s="102"/>
-      <c r="K53" s="102"/>
-      <c r="L53" s="102"/>
-      <c r="M53" s="102"/>
-      <c r="N53" s="102"/>
+      <c r="F53" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="104"/>
+      <c r="N53" s="104"/>
     </row>
     <row r="54" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F54" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>4</v>
@@ -7705,26 +7682,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="103">
+      <c r="G60" s="107">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="104"/>
-      <c r="I60" s="103">
+      <c r="H60" s="108"/>
+      <c r="I60" s="107">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="104"/>
-      <c r="K60" s="103">
+      <c r="J60" s="108"/>
+      <c r="K60" s="107">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="104"/>
-      <c r="M60" s="103">
+      <c r="L60" s="108"/>
+      <c r="M60" s="107">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="104"/>
+      <c r="N60" s="108"/>
     </row>
     <row r="61" spans="6:14" ht="15.75" thickTop="1">
       <c r="F61" s="1"/>
@@ -7741,93 +7718,93 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="100">
+      <c r="G62" s="105">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="101"/>
-      <c r="I62" s="100">
+      <c r="H62" s="106"/>
+      <c r="I62" s="105">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="101"/>
-      <c r="K62" s="100">
+      <c r="J62" s="106"/>
+      <c r="K62" s="105">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="101"/>
-      <c r="M62" s="100">
+      <c r="L62" s="106"/>
+      <c r="M62" s="105">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="101"/>
+      <c r="N62" s="106"/>
     </row>
     <row r="63" spans="6:14">
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="98">
+      <c r="G63" s="102">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="99"/>
-      <c r="I63" s="98">
+      <c r="H63" s="103"/>
+      <c r="I63" s="102">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="99"/>
-      <c r="K63" s="98">
+      <c r="J63" s="103"/>
+      <c r="K63" s="102">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="99"/>
-      <c r="M63" s="98">
+      <c r="L63" s="103"/>
+      <c r="M63" s="102">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="99"/>
+      <c r="N63" s="103"/>
     </row>
     <row r="64" spans="6:14">
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="98">
+      <c r="G64" s="102">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="99"/>
-      <c r="I64" s="98">
+      <c r="H64" s="103"/>
+      <c r="I64" s="102">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="99"/>
-      <c r="K64" s="98">
+      <c r="J64" s="103"/>
+      <c r="K64" s="102">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="99"/>
-      <c r="M64" s="98">
+      <c r="L64" s="103"/>
+      <c r="M64" s="102">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="99"/>
+      <c r="N64" s="103"/>
     </row>
     <row r="66" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F66" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="102"/>
-      <c r="H66" s="102"/>
-      <c r="I66" s="102"/>
-      <c r="J66" s="102"/>
-      <c r="K66" s="102"/>
-      <c r="L66" s="102"/>
-      <c r="M66" s="102"/>
-      <c r="N66" s="102"/>
+      <c r="F66" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
+      <c r="J66" s="104"/>
+      <c r="K66" s="104"/>
+      <c r="L66" s="104"/>
+      <c r="M66" s="104"/>
+      <c r="N66" s="104"/>
     </row>
     <row r="67" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F67" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G67" s="8" t="s">
         <v>4</v>
@@ -7969,35 +7946,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="103">
+      <c r="G73" s="107">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="104">
+      <c r="H73" s="108">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="103">
+      <c r="I73" s="107">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="104">
+      <c r="J73" s="108">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="103">
+      <c r="K73" s="107">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="104">
+      <c r="L73" s="108">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="103">
+      <c r="M73" s="107">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="104">
+      <c r="N73" s="108">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -8017,93 +7994,93 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="100">
+      <c r="G75" s="105">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="101"/>
-      <c r="I75" s="100">
+      <c r="H75" s="106"/>
+      <c r="I75" s="105">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="101"/>
-      <c r="K75" s="100">
+      <c r="J75" s="106"/>
+      <c r="K75" s="105">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="101"/>
-      <c r="M75" s="100">
+      <c r="L75" s="106"/>
+      <c r="M75" s="105">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="101"/>
+      <c r="N75" s="106"/>
     </row>
     <row r="76" spans="6:14">
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="98">
+      <c r="G76" s="102">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="99"/>
-      <c r="I76" s="98">
+      <c r="H76" s="103"/>
+      <c r="I76" s="102">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="99"/>
-      <c r="K76" s="98">
+      <c r="J76" s="103"/>
+      <c r="K76" s="102">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="99"/>
-      <c r="M76" s="98">
+      <c r="L76" s="103"/>
+      <c r="M76" s="102">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="99"/>
+      <c r="N76" s="103"/>
     </row>
     <row r="77" spans="6:14">
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="98">
+      <c r="G77" s="102">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="99"/>
-      <c r="I77" s="98">
+      <c r="H77" s="103"/>
+      <c r="I77" s="102">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="99"/>
-      <c r="K77" s="98">
+      <c r="J77" s="103"/>
+      <c r="K77" s="102">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="99"/>
-      <c r="M77" s="98">
+      <c r="L77" s="103"/>
+      <c r="M77" s="102">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="99"/>
+      <c r="N77" s="103"/>
     </row>
     <row r="79" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F79" s="102" t="s">
-        <v>30</v>
-      </c>
-      <c r="G79" s="102"/>
-      <c r="H79" s="102"/>
-      <c r="I79" s="102"/>
-      <c r="J79" s="102"/>
-      <c r="K79" s="102"/>
-      <c r="L79" s="102"/>
-      <c r="M79" s="102"/>
-      <c r="N79" s="102"/>
+      <c r="F79" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="104"/>
+      <c r="H79" s="104"/>
+      <c r="I79" s="104"/>
+      <c r="J79" s="104"/>
+      <c r="K79" s="104"/>
+      <c r="L79" s="104"/>
+      <c r="M79" s="104"/>
+      <c r="N79" s="104"/>
     </row>
     <row r="80" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F80" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>4</v>
@@ -8295,35 +8272,35 @@
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="103">
+      <c r="G86" s="107">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="104">
+      <c r="H86" s="108">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="103">
+      <c r="I86" s="107">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="104">
+      <c r="J86" s="108">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="103">
+      <c r="K86" s="107">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="L86" s="104">
+      <c r="L86" s="108">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>21</v>
       </c>
-      <c r="M86" s="103">
+      <c r="M86" s="107">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
-      <c r="N86" s="104">
+      <c r="N86" s="108">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>33.75</v>
       </c>
@@ -8363,26 +8340,26 @@
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="100">
+      <c r="G88" s="105">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="101"/>
-      <c r="I88" s="100">
+      <c r="H88" s="106"/>
+      <c r="I88" s="105">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="101"/>
-      <c r="K88" s="100">
+      <c r="J88" s="106"/>
+      <c r="K88" s="105">
         <f>+SUM(K86,K75)</f>
         <v>169.75</v>
       </c>
-      <c r="L88" s="101"/>
-      <c r="M88" s="100">
+      <c r="L88" s="106"/>
+      <c r="M88" s="105">
         <f>+SUM(M86,M75)</f>
         <v>212.25</v>
       </c>
-      <c r="N88" s="101"/>
+      <c r="N88" s="106"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -8398,26 +8375,26 @@
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="98">
+      <c r="G89" s="102">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="99"/>
-      <c r="I89" s="98">
+      <c r="H89" s="103"/>
+      <c r="I89" s="102">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="99"/>
-      <c r="K89" s="98">
+      <c r="J89" s="103"/>
+      <c r="K89" s="102">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L89" s="99"/>
-      <c r="M89" s="98">
+      <c r="L89" s="103"/>
+      <c r="M89" s="102">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N89" s="99"/>
+      <c r="N89" s="103"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -8433,26 +8410,26 @@
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="98">
+      <c r="G90" s="102">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="99"/>
-      <c r="I90" s="98">
+      <c r="H90" s="103"/>
+      <c r="I90" s="102">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="99"/>
-      <c r="K90" s="98">
+      <c r="J90" s="103"/>
+      <c r="K90" s="102">
         <f>+SUM(K89+K77-K50)</f>
         <v>0</v>
       </c>
-      <c r="L90" s="99"/>
-      <c r="M90" s="98">
+      <c r="L90" s="103"/>
+      <c r="M90" s="102">
         <f>+SUM(M89+M77-M50)</f>
         <v>70</v>
       </c>
-      <c r="N90" s="99"/>
+      <c r="N90" s="103"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -8465,17 +8442,17 @@
       <c r="X90" s="1"/>
     </row>
     <row r="92" spans="6:24">
-      <c r="F92" s="102" t="s">
-        <v>32</v>
-      </c>
-      <c r="G92" s="102"/>
-      <c r="H92" s="102"/>
-      <c r="I92" s="102"/>
-      <c r="J92" s="102"/>
-      <c r="K92" s="102"/>
-      <c r="L92" s="102"/>
-      <c r="M92" s="102"/>
-      <c r="N92" s="102"/>
+      <c r="F92" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="G92" s="104"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="104"/>
+      <c r="J92" s="104"/>
+      <c r="K92" s="104"/>
+      <c r="L92" s="104"/>
+      <c r="M92" s="104"/>
+      <c r="N92" s="104"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -8489,7 +8466,7 @@
     </row>
     <row r="93" spans="6:24" ht="16.5" customHeight="1">
       <c r="F93" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>4</v>
@@ -8671,35 +8648,35 @@
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="103">
+      <c r="G99" s="107">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="104">
+      <c r="H99" s="108">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="103">
+      <c r="I99" s="107">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="104">
+      <c r="J99" s="108">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="103">
+      <c r="K99" s="107">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="L99" s="104">
+      <c r="L99" s="108">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="M99" s="103">
+      <c r="M99" s="107">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-      <c r="N99" s="104">
+      <c r="N99" s="108">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
@@ -8719,91 +8696,91 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="100">
+      <c r="G101" s="105">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="101"/>
-      <c r="I101" s="100">
+      <c r="H101" s="106"/>
+      <c r="I101" s="105">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="101"/>
-      <c r="K101" s="100">
+      <c r="J101" s="106"/>
+      <c r="K101" s="105">
         <f>+SUM(K99,K88)</f>
         <v>193.75</v>
       </c>
-      <c r="L101" s="101"/>
-      <c r="M101" s="100">
+      <c r="L101" s="106"/>
+      <c r="M101" s="105">
         <f>+SUM(M99,M88)</f>
         <v>235.5</v>
       </c>
-      <c r="N101" s="101"/>
+      <c r="N101" s="106"/>
     </row>
     <row r="102" spans="6:14">
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="98">
+      <c r="G102" s="102">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="99"/>
-      <c r="I102" s="98">
+      <c r="H102" s="103"/>
+      <c r="I102" s="102">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="99"/>
-      <c r="K102" s="98">
+      <c r="J102" s="103"/>
+      <c r="K102" s="102">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="99"/>
-      <c r="M102" s="98">
+      <c r="L102" s="103"/>
+      <c r="M102" s="102">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="99"/>
+      <c r="N102" s="103"/>
     </row>
     <row r="103" spans="6:14">
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="98">
+      <c r="G103" s="102">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="99"/>
-      <c r="I103" s="98">
+      <c r="H103" s="103"/>
+      <c r="I103" s="102">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="99"/>
-      <c r="K103" s="98">
+      <c r="J103" s="103"/>
+      <c r="K103" s="102">
         <f>+SUM(K102+K90-K63)</f>
         <v>10</v>
       </c>
-      <c r="L103" s="99"/>
-      <c r="M103" s="98">
+      <c r="L103" s="103"/>
+      <c r="M103" s="102">
         <f>+SUM(M102+M90-M63)</f>
         <v>30</v>
       </c>
-      <c r="N103" s="99"/>
+      <c r="N103" s="103"/>
     </row>
     <row r="105" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F105" s="102"/>
-      <c r="G105" s="102"/>
-      <c r="H105" s="102"/>
-      <c r="I105" s="102"/>
-      <c r="J105" s="102"/>
-      <c r="K105" s="102"/>
-      <c r="L105" s="102"/>
-      <c r="M105" s="102"/>
-      <c r="N105" s="102"/>
+      <c r="F105" s="104"/>
+      <c r="G105" s="104"/>
+      <c r="H105" s="104"/>
+      <c r="I105" s="104"/>
+      <c r="J105" s="104"/>
+      <c r="K105" s="104"/>
+      <c r="L105" s="104"/>
+      <c r="M105" s="104"/>
+      <c r="N105" s="104"/>
     </row>
     <row r="106" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F106" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>4</v>
@@ -8923,17 +8900,17 @@
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="103"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="103"/>
-      <c r="J112" s="104"/>
-      <c r="K112" s="103"/>
-      <c r="L112" s="104">
+      <c r="G112" s="107"/>
+      <c r="H112" s="108"/>
+      <c r="I112" s="107"/>
+      <c r="J112" s="108"/>
+      <c r="K112" s="107"/>
+      <c r="L112" s="108">
         <f>+SUM(L107:L111)</f>
         <v>0</v>
       </c>
-      <c r="M112" s="103"/>
-      <c r="N112" s="104">
+      <c r="M112" s="107"/>
+      <c r="N112" s="108">
         <f>+SUM(N107:N111)</f>
         <v>0</v>
       </c>
@@ -8953,67 +8930,67 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="100"/>
-      <c r="H114" s="101"/>
-      <c r="I114" s="100"/>
-      <c r="J114" s="101"/>
-      <c r="K114" s="100"/>
-      <c r="L114" s="101"/>
-      <c r="M114" s="100"/>
-      <c r="N114" s="101"/>
+      <c r="G114" s="105"/>
+      <c r="H114" s="106"/>
+      <c r="I114" s="105"/>
+      <c r="J114" s="106"/>
+      <c r="K114" s="105"/>
+      <c r="L114" s="106"/>
+      <c r="M114" s="105"/>
+      <c r="N114" s="106"/>
     </row>
     <row r="115" spans="6:14">
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="98" t="str">
+      <c r="G115" s="102" t="str">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H115" s="99"/>
-      <c r="I115" s="98" t="str">
+      <c r="H115" s="103"/>
+      <c r="I115" s="102" t="str">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J115" s="99"/>
-      <c r="K115" s="100"/>
-      <c r="L115" s="101"/>
-      <c r="M115" s="100"/>
-      <c r="N115" s="101"/>
+      <c r="J115" s="103"/>
+      <c r="K115" s="105"/>
+      <c r="L115" s="106"/>
+      <c r="M115" s="105"/>
+      <c r="N115" s="106"/>
     </row>
     <row r="116" spans="6:14">
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="98"/>
-      <c r="H116" s="99"/>
-      <c r="I116" s="98"/>
-      <c r="J116" s="99"/>
-      <c r="K116" s="100" t="str">
+      <c r="G116" s="102"/>
+      <c r="H116" s="103"/>
+      <c r="I116" s="102"/>
+      <c r="J116" s="103"/>
+      <c r="K116" s="105" t="str">
         <f>+IF($K107=1,"40Kg",IF($K107=2,"20Kg",IF($K107=3,"10Kg",IF($K107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L116" s="101"/>
-      <c r="M116" s="100" t="str">
+      <c r="L116" s="106"/>
+      <c r="M116" s="105" t="str">
         <f>+IF($M107=1,"40Kg",IF($M107=2,"20Kg",IF($M107=3,"10Kg",IF($M107=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N116" s="101"/>
+      <c r="N116" s="106"/>
     </row>
     <row r="118" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F118" s="102"/>
-      <c r="G118" s="102"/>
-      <c r="H118" s="102"/>
-      <c r="I118" s="102"/>
-      <c r="J118" s="102"/>
-      <c r="K118" s="102"/>
-      <c r="L118" s="102"/>
-      <c r="M118" s="102"/>
-      <c r="N118" s="102"/>
+      <c r="F118" s="104"/>
+      <c r="G118" s="104"/>
+      <c r="H118" s="104"/>
+      <c r="I118" s="104"/>
+      <c r="J118" s="104"/>
+      <c r="K118" s="104"/>
+      <c r="L118" s="104"/>
+      <c r="M118" s="104"/>
+      <c r="N118" s="104"/>
     </row>
     <row r="119" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="F119" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>4</v>
@@ -9133,23 +9110,23 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="103"/>
-      <c r="H125" s="104">
+      <c r="G125" s="107"/>
+      <c r="H125" s="108">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="103"/>
-      <c r="J125" s="104">
+      <c r="I125" s="107"/>
+      <c r="J125" s="108">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="103"/>
-      <c r="L125" s="104">
+      <c r="K125" s="107"/>
+      <c r="L125" s="108">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="103"/>
-      <c r="N125" s="104">
+      <c r="M125" s="107"/>
+      <c r="N125" s="108">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -9169,73 +9146,225 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="100">
+      <c r="G127" s="105">
         <f>H125</f>
         <v>0</v>
       </c>
-      <c r="H127" s="101"/>
-      <c r="I127" s="100">
+      <c r="H127" s="106"/>
+      <c r="I127" s="105">
         <f>J125</f>
         <v>0</v>
       </c>
-      <c r="J127" s="101"/>
-      <c r="K127" s="100">
+      <c r="J127" s="106"/>
+      <c r="K127" s="105">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="101"/>
-      <c r="M127" s="100">
+      <c r="L127" s="106"/>
+      <c r="M127" s="105">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="101"/>
+      <c r="N127" s="106"/>
     </row>
     <row r="128" spans="6:14">
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="98" t="str">
+      <c r="G128" s="102" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="99"/>
-      <c r="I128" s="98" t="str">
+      <c r="H128" s="103"/>
+      <c r="I128" s="102" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J128" s="99"/>
-      <c r="K128" s="100"/>
-      <c r="L128" s="101"/>
-      <c r="M128" s="100"/>
-      <c r="N128" s="101"/>
+      <c r="J128" s="103"/>
+      <c r="K128" s="105"/>
+      <c r="L128" s="106"/>
+      <c r="M128" s="105"/>
+      <c r="N128" s="106"/>
     </row>
     <row r="129" spans="6:14">
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="98" t="e">
+      <c r="G129" s="102" t="e">
         <f>+SUM(G128+G116-G89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H129" s="99"/>
-      <c r="I129" s="98" t="e">
+      <c r="H129" s="103"/>
+      <c r="I129" s="102" t="e">
         <f>+SUM(I128+I116-I89)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J129" s="99"/>
-      <c r="K129" s="100" t="str">
+      <c r="J129" s="103"/>
+      <c r="K129" s="105" t="str">
         <f>+IF($K120=1,"40Kg",IF($K120=2,"20Kg",IF($K120=3,"10Kg",IF($K120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="L129" s="101"/>
-      <c r="M129" s="100" t="str">
+      <c r="L129" s="106"/>
+      <c r="M129" s="105" t="str">
         <f>+IF($M120=1,"40Kg",IF($M120=2,"20Kg",IF($M120=3,"10Kg",IF($M120=4,"0Kg",""))))</f>
         <v/>
       </c>
-      <c r="N129" s="101"/>
+      <c r="N129" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="176">
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="G77:H77"/>
     <mergeCell ref="I77:J77"/>
     <mergeCell ref="K77:L77"/>
@@ -9260,158 +9389,6 @@
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9434,13 +9411,13 @@
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="A1" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>37</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>38</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -9448,23 +9425,23 @@
       <c r="G1" s="29"/>
       <c r="H1" s="34"/>
       <c r="I1" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="K1" s="36" t="s">
         <v>37</v>
-      </c>
-      <c r="K1" s="36" t="s">
-        <v>38</v>
       </c>
       <c r="L1" s="29"/>
       <c r="M1" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="O1" s="52" t="s">
         <v>40</v>
-      </c>
-      <c r="O1" s="52" t="s">
-        <v>41</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
@@ -9757,7 +9734,7 @@
       <c r="L7" s="29"/>
       <c r="M7" s="29"/>
       <c r="N7" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O7" s="29"/>
       <c r="P7" s="29"/>
@@ -10385,57 +10362,57 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="112" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="105" t="s">
+      <c r="B2" s="110"/>
+      <c r="C2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="101" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1">
         <f>Hoja1!G3</f>
@@ -10457,40 +10434,40 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="101"/>
+      <c r="B4" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="108"/>
-      <c r="B4" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C4" s="1">
         <f>Hoja1!G4</f>
@@ -10511,7 +10488,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10555,11 +10532,11 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="101" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1">
         <f>Hoja1!G16</f>
@@ -10580,7 +10557,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10624,9 +10601,9 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="108"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1">
         <f>Hoja1!G17</f>
@@ -10647,7 +10624,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10691,11 +10668,11 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="108" t="s">
+      <c r="A7" s="101" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1">
         <f>Hoja1!G29</f>
@@ -10716,7 +10693,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10760,9 +10737,9 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="108"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1">
         <f>Hoja1!G30</f>
@@ -10795,11 +10772,11 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="108" t="s">
+      <c r="A9" s="101" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1">
         <f>Hoja1!G42</f>
@@ -10832,9 +10809,9 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="108"/>
+      <c r="A10" s="101"/>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1">
         <f>Hoja1!G43</f>
@@ -10867,11 +10844,11 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="108" t="s">
-        <v>61</v>
+      <c r="A11" s="101" t="s">
+        <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1">
         <f>Hoja1!G55</f>
@@ -10904,9 +10881,9 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="108"/>
+      <c r="A12" s="101"/>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1">
         <f>Hoja1!G56</f>
@@ -10939,11 +10916,11 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="108" t="s">
-        <v>62</v>
+      <c r="A13" s="101" t="s">
+        <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1">
         <f>Hoja1!G68</f>
@@ -10976,9 +10953,9 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="108"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1">
         <f>Hoja1!G69</f>
@@ -11011,11 +10988,11 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="108" t="s">
-        <v>63</v>
+      <c r="A15" s="101" t="s">
+        <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1">
         <f>Hoja1!G81</f>
@@ -11048,9 +11025,9 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="108"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1">
         <f>Hoja1!G82</f>
@@ -11083,11 +11060,11 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="108" t="s">
-        <v>64</v>
+      <c r="A17" s="101" t="s">
+        <v>63</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1">
         <f>Hoja1!G94</f>
@@ -11108,9 +11085,9 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="108"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="1">
         <f>Hoja1!G95</f>
@@ -11131,9 +11108,9 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="108"/>
+      <c r="A19" s="101"/>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1">
         <f>Hoja1!G109</f>
@@ -11154,9 +11131,9 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="108"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1">
         <f>Hoja1!G110</f>
@@ -11177,9 +11154,9 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="108"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1">
         <f>Hoja1!G122</f>
@@ -11200,9 +11177,9 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="108"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1">
         <f>Hoja1!G123</f>
@@ -11224,7 +11201,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -11246,352 +11223,352 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
+      <c r="A25" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="110"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="110"/>
+      <c r="C26" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="93" t="s">
+      <c r="D26" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="93" t="s">
+      <c r="E26" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="93" t="s">
+      <c r="F26" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="93" t="s">
-        <v>48</v>
-      </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="108" t="s">
+      <c r="A27" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="105">
+      <c r="B27" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="110">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="105">
+      <c r="D27" s="110">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="105">
+      <c r="E27" s="110">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="105">
+      <c r="F27" s="110">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="105"/>
+      <c r="G27" s="110"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="108" t="s">
+      <c r="A29" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="105">
+      <c r="B29" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="110">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="105">
+      <c r="D29" s="110">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="105">
+      <c r="E29" s="110">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="105">
+      <c r="F29" s="110">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="105"/>
+      <c r="G29" s="110"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="108" t="s">
+      <c r="A31" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="105">
+      <c r="B31" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="110">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="105">
+      <c r="D31" s="110">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="105">
+      <c r="E31" s="110">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="105">
+      <c r="F31" s="110">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="105"/>
+      <c r="G31" s="110"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="108"/>
-      <c r="B32" s="108"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="108" t="s">
+      <c r="A33" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="105">
+      <c r="B33" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="110">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="105">
+      <c r="D33" s="110">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="105">
+      <c r="E33" s="110">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="105">
+      <c r="F33" s="110">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="105"/>
+      <c r="G33" s="110"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="108"/>
-      <c r="B34" s="108"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="110"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="108" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="105">
+      <c r="A35" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="110">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="105">
+      <c r="D35" s="110">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="105">
+      <c r="E35" s="110">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="105">
+      <c r="F35" s="110">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="105"/>
+      <c r="G35" s="110"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="108"/>
-      <c r="B36" s="108"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="101"/>
+      <c r="C36" s="110"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="110"/>
+      <c r="G36" s="110"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="108" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="105">
+      <c r="A37" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="110">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="105">
+      <c r="D37" s="110">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="105">
+      <c r="E37" s="110">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="105">
+      <c r="F37" s="110">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="105"/>
+      <c r="G37" s="110"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="108"/>
-      <c r="B38" s="108"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
+      <c r="A38" s="101"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="110"/>
+      <c r="G38" s="110"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="105">
+      <c r="A39" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="110">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="105">
+      <c r="D39" s="110">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="105">
+      <c r="E39" s="110">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="105">
+      <c r="F39" s="110">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="105"/>
+      <c r="G39" s="110"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="108"/>
-      <c r="B40" s="108"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
+      <c r="A40" s="101"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="110"/>
+      <c r="G40" s="110"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="105">
+      <c r="A41" s="101" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="110">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="105">
+      <c r="D41" s="110">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="105">
+      <c r="E41" s="110">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="105">
+      <c r="F41" s="110">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="105"/>
+      <c r="G41" s="110"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="108"/>
-      <c r="B42" s="108"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
+      <c r="A42" s="101"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="110"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="108"/>
-      <c r="B43" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="105">
+      <c r="A43" s="101"/>
+      <c r="B43" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="110">
         <f>Hoja1!H109</f>
         <v>0</v>
       </c>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
+      <c r="D43" s="110"/>
+      <c r="E43" s="110"/>
+      <c r="F43" s="110"/>
+      <c r="G43" s="110"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="108"/>
-      <c r="B44" s="108"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
+      <c r="A44" s="101"/>
+      <c r="B44" s="101"/>
+      <c r="C44" s="110"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="110"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="108"/>
-      <c r="B45" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="105">
+      <c r="A45" s="101"/>
+      <c r="B45" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="110">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
+      <c r="D45" s="110"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="110"/>
+      <c r="G45" s="110"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="108"/>
-      <c r="B46" s="108"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
+      <c r="A46" s="101"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="110"/>
+      <c r="D46" s="110"/>
+      <c r="E46" s="110"/>
+      <c r="F46" s="110"/>
+      <c r="G46" s="110"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -11618,52 +11595,28 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="I1:S2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
@@ -11680,28 +11633,52 @@
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="I1:S2"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11718,25 +11695,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -12205,7 +12182,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
@@ -12233,7 +12210,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -12261,7 +12238,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -12289,7 +12266,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -12317,7 +12294,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>4</v>
@@ -12345,7 +12322,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -12373,7 +12350,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -12401,7 +12378,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -12429,7 +12406,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>4</v>
@@ -12457,7 +12434,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -12485,7 +12462,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -12513,7 +12490,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -12541,7 +12518,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
@@ -12569,7 +12546,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
@@ -12597,7 +12574,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -12625,7 +12602,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -12652,7 +12629,7 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="105"/>
+      <c r="A34" s="110"/>
       <c r="B34" s="1" t="s">
         <v>4</v>
       </c>
@@ -12678,7 +12655,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="105"/>
+      <c r="A35" s="110"/>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
@@ -12704,7 +12681,7 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="105"/>
+      <c r="A36" s="110"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -12730,7 +12707,7 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="105"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -12756,7 +12733,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="105"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -12782,7 +12759,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="105"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -12808,7 +12785,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="105"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -12834,7 +12811,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="105"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -12883,10 +12860,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -12895,22 +12872,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="C3" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="D3" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="E3" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="F3" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13032,11 +13009,11 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="101" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="58">
         <v>1.0631828703703704E-3</v>
@@ -13055,9 +13032,9 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="108"/>
+      <c r="A3" s="101"/>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="58">
         <v>1.0327314814814815E-3</v>
@@ -13078,9 +13055,9 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="108"/>
+      <c r="A4" s="101"/>
       <c r="B4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="58">
         <v>1.0267824074074075E-3</v>
@@ -13101,11 +13078,11 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="101" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
@@ -13118,9 +13095,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="108"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -13133,9 +13110,9 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="108"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
@@ -13148,11 +13125,11 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="101" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -13165,9 +13142,9 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="108"/>
+      <c r="A9" s="101"/>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="58"/>
       <c r="D9" s="58"/>
@@ -13180,9 +13157,9 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="108"/>
+      <c r="A10" s="101"/>
       <c r="B10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="58">
         <v>8.9045138888888887E-4</v>
@@ -13203,11 +13180,11 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="108" t="s">
+      <c r="A11" s="101" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="58">
         <v>8.6745370370370383E-4</v>
@@ -13228,9 +13205,9 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="108"/>
+      <c r="A12" s="101"/>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -13243,9 +13220,9 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="108"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -13258,11 +13235,11 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="108" t="s">
-        <v>61</v>
+      <c r="A14" s="101" t="s">
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="58">
         <v>8.2178240740740736E-4</v>
@@ -13295,9 +13272,9 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="108"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="58">
         <v>8.1365740740740736E-4</v>
@@ -13328,9 +13305,9 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="108"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="58">
         <v>8.0902777777777787E-4</v>
@@ -13361,11 +13338,11 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="108" t="s">
-        <v>62</v>
+      <c r="A17" s="101" t="s">
+        <v>61</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="58">
         <v>9.2799768518518524E-4</v>
@@ -13391,9 +13368,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="108"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="58">
         <v>9.2737268518518516E-4</v>
@@ -13419,9 +13396,9 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="108"/>
+      <c r="A19" s="101"/>
       <c r="B19" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="58">
         <v>9.2612268518518521E-4</v>
@@ -13447,11 +13424,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="108" t="s">
-        <v>63</v>
+      <c r="A20" s="101" t="s">
+        <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="58">
         <v>1.2464004629629628E-3</v>
@@ -13477,9 +13454,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="108"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="58">
         <v>1.2324652777777779E-3</v>
@@ -13503,9 +13480,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="108"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="58">
         <v>1.2377777777777777E-3</v>
@@ -13529,11 +13506,11 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="108" t="s">
-        <v>64</v>
+      <c r="A23" s="101" t="s">
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="58">
         <v>1.0980555555555555E-3</v>
@@ -13559,9 +13536,9 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="108"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="58"/>
       <c r="D24" s="58"/>
@@ -13579,9 +13556,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="108"/>
+      <c r="A25" s="101"/>
       <c r="B25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" s="58"/>
       <c r="D25" s="58"/>
@@ -13599,8 +13576,8 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="108" t="s">
-        <v>34</v>
+      <c r="A26" s="101" t="s">
+        <v>33</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="58"/>
@@ -13619,7 +13596,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="108"/>
+      <c r="A27" s="101"/>
       <c r="B27" s="1"/>
       <c r="C27" s="58"/>
       <c r="D27" s="58"/>
@@ -13637,7 +13614,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="108"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="1"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
@@ -13655,8 +13632,8 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="108" t="s">
-        <v>35</v>
+      <c r="A29" s="101" t="s">
+        <v>34</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="58"/>
@@ -13675,7 +13652,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="108"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -13693,7 +13670,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="108"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -13754,7 +13731,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -13771,11 +13748,11 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="113" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="69">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -13796,7 +13773,7 @@
       <c r="G2" s="58"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1">
         <f>IF('Carga Tiempos'!H14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!H14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
@@ -13816,9 +13793,9 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="111"/>
+      <c r="A3" s="114"/>
       <c r="B3" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="69">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -13839,7 +13816,7 @@
       <c r="G3" s="58"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1">
         <f>IF('Carga Tiempos'!H15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!H15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
@@ -13859,9 +13836,9 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="111"/>
+      <c r="A4" s="114"/>
       <c r="B4" s="62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="69">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -13882,7 +13859,7 @@
       <c r="G4" s="58"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J4" s="1">
         <f>IF('Carga Tiempos'!H16=MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16),0,'Carga Tiempos'!H16-MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16))</f>
@@ -13902,11 +13879,11 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="113" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="60"/>
@@ -13924,9 +13901,9 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="111"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
@@ -13944,9 +13921,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="112"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="61"/>
@@ -13964,11 +13941,11 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="114" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
@@ -13986,9 +13963,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="111"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="68"/>
@@ -14006,9 +13983,9 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="112"/>
+      <c r="A10" s="115"/>
       <c r="B10" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="71">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -14038,11 +14015,11 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="114" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="69">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -14072,9 +14049,9 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="111"/>
+      <c r="A12" s="114"/>
       <c r="B12" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="68"/>
@@ -14092,9 +14069,9 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="111"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="68"/>
@@ -14112,11 +14089,11 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="110" t="s">
-        <v>61</v>
+      <c r="A14" s="113" t="s">
+        <v>60</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="70">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -14146,9 +14123,9 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="111"/>
+      <c r="A15" s="114"/>
       <c r="B15" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="69">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -14178,9 +14155,9 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="112"/>
+      <c r="A16" s="115"/>
       <c r="B16" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="71">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -14210,11 +14187,11 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="111" t="s">
-        <v>62</v>
+      <c r="A17" s="114" t="s">
+        <v>61</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="69">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -14244,9 +14221,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="111"/>
+      <c r="A18" s="114"/>
       <c r="B18" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="69">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -14276,9 +14253,9 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="111"/>
+      <c r="A19" s="114"/>
       <c r="B19" s="62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="69">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -14308,11 +14285,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="110" t="s">
-        <v>63</v>
+      <c r="A20" s="113" t="s">
+        <v>62</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="70">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -14342,9 +14319,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="111"/>
+      <c r="A21" s="114"/>
       <c r="B21" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="69">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -14374,9 +14351,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="111"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="69">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -14406,11 +14383,11 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="110" t="s">
-        <v>33</v>
+      <c r="A23" s="113" t="s">
+        <v>32</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="70">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
@@ -14440,9 +14417,9 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="111"/>
+      <c r="A24" s="114"/>
       <c r="B24" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="69">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
@@ -14472,9 +14449,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="112"/>
+      <c r="A25" s="115"/>
       <c r="B25" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" s="71">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
@@ -14504,11 +14481,11 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="111" t="s">
-        <v>34</v>
+      <c r="A26" s="114" t="s">
+        <v>33</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="69">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
@@ -14538,9 +14515,9 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="111"/>
+      <c r="A27" s="114"/>
       <c r="B27" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -14570,9 +14547,9 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="111"/>
+      <c r="A28" s="114"/>
       <c r="B28" s="62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" s="69">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -14602,11 +14579,11 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="110" t="s">
-        <v>35</v>
+      <c r="A29" s="113" t="s">
+        <v>34</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C29" s="70">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -14636,9 +14613,9 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="111"/>
+      <c r="A30" s="114"/>
       <c r="B30" s="62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" s="69">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -14668,9 +14645,9 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="112"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C31" s="71">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -14791,16 +14768,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
+      <c r="K1" s="116" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1"/>
@@ -14813,22 +14790,22 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="95" t="s">
+      <c r="K2" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="118"/>
+      <c r="M2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="96"/>
-      <c r="M2" s="95" t="s">
+      <c r="N2" s="118"/>
+      <c r="O2" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="96"/>
-      <c r="O2" s="95" t="s">
+      <c r="P2" s="118"/>
+      <c r="Q2" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="95" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" s="96"/>
+      <c r="R2" s="118"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -14852,19 +14829,19 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="M3" s="86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N3" s="77">
         <v>1.2796759259259259E-3</v>
       </c>
       <c r="O3" s="86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
       <c r="Q3" s="83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R3" s="84">
         <v>1.4428356481481482E-3</v>
@@ -14892,19 +14869,19 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N4" s="77">
         <v>1.2429976851851853E-3</v>
       </c>
       <c r="O4" s="83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
       <c r="Q4" s="83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R4" s="81">
         <v>1.2858101851851852E-3</v>
@@ -14932,19 +14909,19 @@
         <v>1.2545601851851852E-3</v>
       </c>
       <c r="M5" s="87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N5" s="77">
         <v>1.2377777777777777E-3</v>
       </c>
       <c r="O5" s="87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
       <c r="Q5" s="83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R5" s="81">
         <v>1.2647453703703703E-3</v>
@@ -14972,19 +14949,19 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N6" s="77">
         <v>1.3249884259259259E-3</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R6" s="81">
         <v>1.2908564814814816E-3</v>
@@ -15012,19 +14989,19 @@
         <v>1.260300925925926E-3</v>
       </c>
       <c r="M7" s="87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N7" s="77">
         <v>1.2426273148148149E-3</v>
       </c>
       <c r="O7" s="87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
       <c r="Q7" s="83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R7" s="81">
         <v>1.2742476851851851E-3</v>
@@ -15052,19 +15029,19 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N8" s="77">
         <v>1.2478472222222222E-3</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R8" s="81">
         <v>1.2452199074074073E-3</v>
@@ -15092,19 +15069,19 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N9" s="77">
         <v>1.248275462962963E-3</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
       <c r="Q9" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R9" s="81">
         <v>1.2555324074074075E-3</v>
@@ -15132,19 +15109,19 @@
         <v>1.2430787037037037E-3</v>
       </c>
       <c r="M10" s="87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N10" s="77">
         <v>1.2653240740740741E-3</v>
       </c>
       <c r="O10" s="87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
       <c r="Q10" s="83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R10" s="81">
         <v>1.2631365740740741E-3</v>
@@ -15172,19 +15149,19 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N11" s="77">
         <v>1.6837615740740741E-3</v>
       </c>
       <c r="O11" s="83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
       <c r="Q11" s="83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R11" s="81">
         <v>1.4671412037037036E-3</v>
@@ -15212,19 +15189,19 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N12" s="77">
         <v>1.543287037037037E-3</v>
       </c>
       <c r="O12" s="83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
       <c r="Q12" s="83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R12" s="81">
         <v>1.5160185185185185E-3</v>
@@ -15252,19 +15229,19 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N13" s="77">
         <v>1.9202893518518521E-3</v>
       </c>
       <c r="O13" s="83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
       <c r="Q13" s="83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R13" s="81">
         <v>1.9527199074074074E-3</v>
@@ -15292,19 +15269,19 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N14" s="77">
         <v>1.2480787037037037E-3</v>
       </c>
       <c r="O14" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
       <c r="Q14" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R14" s="81">
         <v>1.2462037037037036E-3</v>
@@ -15332,19 +15309,19 @@
         <v>1.236238425925926E-3</v>
       </c>
       <c r="M15" s="87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N15" s="77">
         <v>1.241701388888889E-3</v>
       </c>
       <c r="O15" s="87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
       <c r="Q15" s="83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R15" s="81">
         <v>1.2494560185185185E-3</v>
@@ -15372,19 +15349,19 @@
         <v>1.2310648148148148E-3</v>
       </c>
       <c r="M16" s="88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N16" s="77">
         <v>1.2480208333333334E-3</v>
       </c>
       <c r="O16" s="88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
       <c r="Q16" s="83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R16" s="81">
         <v>1.2403703703703704E-3</v>
@@ -15412,19 +15389,19 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N17" s="80">
         <v>1.2779629629629629E-3</v>
       </c>
       <c r="O17" s="85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
       <c r="Q17" s="85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R17" s="82">
         <v>1.2507638888888889E-3</v>
@@ -15610,28 +15587,28 @@
       <c r="W23" s="1"/>
     </row>
     <row r="25" spans="1:23" ht="34.5">
-      <c r="A25" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
+      <c r="A25" s="116" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="116"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="L25" s="97"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="97"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="97"/>
-      <c r="R25" s="97"/>
+      <c r="K25" s="116" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="116"/>
+      <c r="M25" s="116"/>
+      <c r="N25" s="116"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="116"/>
+      <c r="Q25" s="116"/>
+      <c r="R25" s="116"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -15639,40 +15616,40 @@
       <c r="W25" s="1"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="117" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="118"/>
+      <c r="C26" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="95" t="s">
+      <c r="D26" s="118"/>
+      <c r="E26" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="96"/>
-      <c r="E26" s="113" t="s">
+      <c r="F26" s="120"/>
+      <c r="G26" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="114"/>
-      <c r="G26" s="95" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="96"/>
+      <c r="H26" s="118"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="95" t="s">
+      <c r="K26" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="L26" s="118"/>
+      <c r="M26" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="L26" s="96"/>
-      <c r="M26" s="95" t="s">
+      <c r="N26" s="118"/>
+      <c r="O26" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="N26" s="96"/>
-      <c r="O26" s="113" t="s">
+      <c r="P26" s="120"/>
+      <c r="Q26" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="95" t="s">
-        <v>84</v>
-      </c>
-      <c r="R26" s="96"/>
+      <c r="R26" s="118"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
@@ -15680,28 +15657,28 @@
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="119">
+      <c r="A27" s="121">
         <v>1</v>
       </c>
-      <c r="B27" s="120">
+      <c r="B27" s="122">
         <v>1.1538888888888888E-3</v>
       </c>
-      <c r="C27" s="119">
+      <c r="C27" s="121">
         <v>1</v>
       </c>
-      <c r="D27" s="120">
+      <c r="D27" s="122">
         <v>1.1476041666666666E-3</v>
       </c>
-      <c r="E27" s="119">
+      <c r="E27" s="121">
         <v>1</v>
       </c>
-      <c r="F27" s="120">
+      <c r="F27" s="122">
         <v>1.1644560185185187E-3</v>
       </c>
-      <c r="G27" s="121">
+      <c r="G27" s="99">
         <v>1</v>
       </c>
-      <c r="H27" s="122">
+      <c r="H27" s="100">
         <v>1.1644560185185187E-3</v>
       </c>
       <c r="I27" s="1"/>
@@ -15718,10 +15695,10 @@
       <c r="N27" s="124">
         <v>1.4123148148148148E-3</v>
       </c>
-      <c r="O27" s="115">
+      <c r="O27" s="95">
         <v>1</v>
       </c>
-      <c r="P27" s="116">
+      <c r="P27" s="96">
         <v>1.4081597222222223E-3</v>
       </c>
       <c r="Q27" s="123">
@@ -15730,35 +15707,35 @@
       <c r="R27" s="124">
         <v>1.4081597222222223E-3</v>
       </c>
-      <c r="S27" s="94"/>
+      <c r="S27" s="92"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="119">
+      <c r="A28" s="121">
         <v>2</v>
       </c>
-      <c r="B28" s="120">
+      <c r="B28" s="122">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="C28" s="119">
+      <c r="C28" s="121">
         <v>2</v>
       </c>
-      <c r="D28" s="120">
+      <c r="D28" s="122">
         <v>1.1111458333333333E-3</v>
       </c>
-      <c r="E28" s="119">
+      <c r="E28" s="121">
         <v>2</v>
       </c>
-      <c r="F28" s="120">
+      <c r="F28" s="122">
         <v>1.1378703703703703E-3</v>
       </c>
-      <c r="G28" s="121">
+      <c r="G28" s="99">
         <v>2</v>
       </c>
-      <c r="H28" s="122">
+      <c r="H28" s="100">
         <v>1.1378703703703703E-3</v>
       </c>
       <c r="I28" s="1"/>
@@ -15775,10 +15752,10 @@
       <c r="N28" s="124">
         <v>1.1365393518518519E-3</v>
       </c>
-      <c r="O28" s="115">
+      <c r="O28" s="95">
         <v>2</v>
       </c>
-      <c r="P28" s="116">
+      <c r="P28" s="96">
         <v>1.1394212962962964E-3</v>
       </c>
       <c r="Q28" s="123">
@@ -15794,28 +15771,28 @@
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="119">
+      <c r="A29" s="121">
         <v>3</v>
       </c>
-      <c r="B29" s="120">
+      <c r="B29" s="122">
         <v>1.110173611111111E-3</v>
       </c>
-      <c r="C29" s="119">
+      <c r="C29" s="121">
         <v>3</v>
       </c>
-      <c r="D29" s="120">
+      <c r="D29" s="122">
         <v>1.0993171296296296E-3</v>
       </c>
-      <c r="E29" s="119">
+      <c r="E29" s="121">
         <v>3</v>
       </c>
-      <c r="F29" s="120">
+      <c r="F29" s="122">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="G29" s="121">
+      <c r="G29" s="99">
         <v>3</v>
       </c>
-      <c r="H29" s="122">
+      <c r="H29" s="100">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="I29" s="1"/>
@@ -15832,10 +15809,10 @@
       <c r="N29" s="124">
         <v>1.1328703703703702E-3</v>
       </c>
-      <c r="O29" s="115">
+      <c r="O29" s="95">
         <v>3</v>
       </c>
-      <c r="P29" s="116">
+      <c r="P29" s="96">
         <v>1.1317361111111111E-3</v>
       </c>
       <c r="Q29" s="123">
@@ -15851,28 +15828,28 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="119">
+      <c r="A30" s="121">
         <v>4</v>
       </c>
-      <c r="B30" s="120">
+      <c r="B30" s="122">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="C30" s="119">
+      <c r="C30" s="121">
         <v>4</v>
       </c>
-      <c r="D30" s="120">
+      <c r="D30" s="122">
         <v>1.0976736111111111E-3</v>
       </c>
-      <c r="E30" s="119">
+      <c r="E30" s="121">
         <v>4</v>
       </c>
-      <c r="F30" s="120">
+      <c r="F30" s="122">
         <v>1.1532986111111112E-3</v>
       </c>
-      <c r="G30" s="121">
+      <c r="G30" s="99">
         <v>4</v>
       </c>
-      <c r="H30" s="122">
+      <c r="H30" s="100">
         <v>1.1532986111111112E-3</v>
       </c>
       <c r="I30" s="1"/>
@@ -15889,10 +15866,10 @@
       <c r="N30" s="124">
         <v>1.1118055555555556E-3</v>
       </c>
-      <c r="O30" s="115">
+      <c r="O30" s="95">
         <v>4</v>
       </c>
-      <c r="P30" s="116">
+      <c r="P30" s="96">
         <v>2.0264583333333337E-3</v>
       </c>
       <c r="Q30" s="123">
@@ -15908,28 +15885,28 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="119">
+      <c r="A31" s="121">
         <v>5</v>
       </c>
-      <c r="B31" s="120">
+      <c r="B31" s="122">
         <v>1.1121296296296296E-3</v>
       </c>
-      <c r="C31" s="119">
+      <c r="C31" s="121">
         <v>5</v>
       </c>
-      <c r="D31" s="120">
+      <c r="D31" s="122">
         <v>1.1186458333333335E-3</v>
       </c>
-      <c r="E31" s="119">
+      <c r="E31" s="121">
         <v>5</v>
       </c>
-      <c r="F31" s="120">
+      <c r="F31" s="122">
         <v>1.1660416666666668E-3</v>
       </c>
-      <c r="G31" s="121">
+      <c r="G31" s="99">
         <v>5</v>
       </c>
-      <c r="H31" s="122">
+      <c r="H31" s="100">
         <v>1.1660416666666668E-3</v>
       </c>
       <c r="I31" s="1"/>
@@ -15946,10 +15923,10 @@
       <c r="N31" s="124">
         <v>1.0958333333333334E-3</v>
       </c>
-      <c r="O31" s="115">
+      <c r="O31" s="95">
         <v>5</v>
       </c>
-      <c r="P31" s="116">
+      <c r="P31" s="96">
         <v>1.198900462962963E-3</v>
       </c>
       <c r="Q31" s="123">
@@ -15965,28 +15942,28 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="119">
+      <c r="A32" s="121">
         <v>6</v>
       </c>
-      <c r="B32" s="120">
+      <c r="B32" s="122">
         <v>1.1231828703703705E-3</v>
       </c>
-      <c r="C32" s="119">
+      <c r="C32" s="121">
         <v>6</v>
       </c>
-      <c r="D32" s="120">
+      <c r="D32" s="122">
         <v>1.1192708333333332E-3</v>
       </c>
-      <c r="E32" s="119">
+      <c r="E32" s="121">
         <v>6</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32" s="122">
         <v>1.1783333333333333E-3</v>
       </c>
-      <c r="G32" s="121">
+      <c r="G32" s="99">
         <v>6</v>
       </c>
-      <c r="H32" s="122">
+      <c r="H32" s="100">
         <v>1.1783333333333333E-3</v>
       </c>
       <c r="I32" s="1"/>
@@ -16003,10 +15980,10 @@
       <c r="N32" s="124">
         <v>1.1103587962962964E-3</v>
       </c>
-      <c r="O32" s="115">
+      <c r="O32" s="95">
         <v>6</v>
       </c>
-      <c r="P32" s="116">
+      <c r="P32" s="96">
         <v>1.3676157407407409E-3</v>
       </c>
       <c r="Q32" s="123">
@@ -16022,28 +15999,28 @@
       <c r="W32" s="1"/>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="119">
+      <c r="A33" s="121">
         <v>7</v>
       </c>
-      <c r="B33" s="120">
+      <c r="B33" s="122">
         <v>1.1183564814814815E-3</v>
       </c>
-      <c r="C33" s="119">
+      <c r="C33" s="121">
         <v>7</v>
       </c>
-      <c r="D33" s="120">
+      <c r="D33" s="122">
         <v>1.1119675925925926E-3</v>
       </c>
-      <c r="E33" s="119">
+      <c r="E33" s="121">
         <v>7</v>
       </c>
-      <c r="F33" s="120">
+      <c r="F33" s="122">
         <v>1.1461342592592593E-3</v>
       </c>
-      <c r="G33" s="121">
+      <c r="G33" s="99">
         <v>7</v>
       </c>
-      <c r="H33" s="122">
+      <c r="H33" s="100">
         <v>1.1461342592592593E-3</v>
       </c>
       <c r="I33" s="1"/>
@@ -16060,10 +16037,10 @@
       <c r="N33" s="124">
         <v>1.1330787037037036E-3</v>
       </c>
-      <c r="O33" s="115">
+      <c r="O33" s="95">
         <v>7</v>
       </c>
-      <c r="P33" s="116">
+      <c r="P33" s="96">
         <v>1.2607407407407407E-3</v>
       </c>
       <c r="Q33" s="123">
@@ -16079,28 +16056,28 @@
       <c r="W33" s="1"/>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="119">
+      <c r="A34" s="121">
         <v>8</v>
       </c>
-      <c r="B34" s="120">
+      <c r="B34" s="122">
         <v>1.124398148148148E-3</v>
       </c>
-      <c r="C34" s="119">
+      <c r="C34" s="121">
         <v>8</v>
       </c>
-      <c r="D34" s="120">
+      <c r="D34" s="122">
         <v>1.1048148148148148E-3</v>
       </c>
-      <c r="E34" s="119">
+      <c r="E34" s="121">
         <v>8</v>
       </c>
-      <c r="F34" s="120">
+      <c r="F34" s="122">
         <v>1.2261226851851851E-3</v>
       </c>
-      <c r="G34" s="121">
+      <c r="G34" s="99">
         <v>8</v>
       </c>
-      <c r="H34" s="122">
+      <c r="H34" s="100">
         <v>1.2261226851851851E-3</v>
       </c>
       <c r="I34" s="1"/>
@@ -16117,10 +16094,10 @@
       <c r="N34" s="124">
         <v>1.1489930555555554E-3</v>
       </c>
-      <c r="O34" s="115">
+      <c r="O34" s="95">
         <v>8</v>
       </c>
-      <c r="P34" s="116">
+      <c r="P34" s="96">
         <v>1.1238657407407408E-3</v>
       </c>
       <c r="Q34" s="123">
@@ -16136,28 +16113,28 @@
       <c r="W34" s="1"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="119">
+      <c r="A35" s="121">
         <v>9</v>
       </c>
-      <c r="B35" s="120">
+      <c r="B35" s="122">
         <v>1.2592476851851853E-3</v>
       </c>
-      <c r="C35" s="119">
+      <c r="C35" s="121">
         <v>9</v>
       </c>
-      <c r="D35" s="120">
+      <c r="D35" s="122">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="E35" s="119">
+      <c r="E35" s="121">
         <v>9</v>
       </c>
-      <c r="F35" s="120">
+      <c r="F35" s="122">
         <v>1.1561111111111112E-3</v>
       </c>
-      <c r="G35" s="121">
+      <c r="G35" s="99">
         <v>9</v>
       </c>
-      <c r="H35" s="122">
+      <c r="H35" s="100">
         <v>1.1561111111111112E-3</v>
       </c>
       <c r="I35" s="1"/>
@@ -16174,10 +16151,10 @@
       <c r="N35" s="124">
         <v>1.1331134259259261E-3</v>
       </c>
-      <c r="O35" s="115">
+      <c r="O35" s="95">
         <v>9</v>
       </c>
-      <c r="P35" s="116">
+      <c r="P35" s="96">
         <v>1.2741203703703703E-3</v>
       </c>
       <c r="Q35" s="123">
@@ -16193,28 +16170,28 @@
       <c r="W35" s="1"/>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="119">
+      <c r="A36" s="121">
         <v>10</v>
       </c>
-      <c r="B36" s="120">
+      <c r="B36" s="122">
         <v>1.1363194444444444E-3</v>
       </c>
-      <c r="C36" s="119">
+      <c r="C36" s="121">
         <v>10</v>
       </c>
-      <c r="D36" s="120">
+      <c r="D36" s="122">
         <v>1.1534143518518519E-3</v>
       </c>
-      <c r="E36" s="119">
+      <c r="E36" s="121">
         <v>10</v>
       </c>
-      <c r="F36" s="120">
+      <c r="F36" s="122">
         <v>1.1621296296296297E-3</v>
       </c>
-      <c r="G36" s="121">
+      <c r="G36" s="99">
         <v>10</v>
       </c>
-      <c r="H36" s="122">
+      <c r="H36" s="100">
         <v>1.1621296296296297E-3</v>
       </c>
       <c r="I36" s="1"/>
@@ -16231,10 +16208,10 @@
       <c r="N36" s="124">
         <v>1.1556481481481481E-3</v>
       </c>
-      <c r="O36" s="115">
+      <c r="O36" s="95">
         <v>10</v>
       </c>
-      <c r="P36" s="116">
+      <c r="P36" s="96">
         <v>1.1596180555555557E-3</v>
       </c>
       <c r="Q36" s="123">
@@ -16250,28 +16227,28 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="119">
+      <c r="A37" s="121">
         <v>11</v>
       </c>
-      <c r="B37" s="120">
+      <c r="B37" s="122">
         <v>1.3982291666666668E-3</v>
       </c>
-      <c r="C37" s="119">
+      <c r="C37" s="121">
         <v>11</v>
       </c>
-      <c r="D37" s="120">
+      <c r="D37" s="122">
         <v>1.2330902777777778E-3</v>
       </c>
-      <c r="E37" s="119">
+      <c r="E37" s="121">
         <v>11</v>
       </c>
-      <c r="F37" s="120">
+      <c r="F37" s="122">
         <v>1.2419907407407406E-3</v>
       </c>
-      <c r="G37" s="121">
+      <c r="G37" s="99">
         <v>11</v>
       </c>
-      <c r="H37" s="122">
+      <c r="H37" s="100">
         <v>1.2419907407407406E-3</v>
       </c>
       <c r="I37" s="1"/>
@@ -16288,10 +16265,10 @@
       <c r="N37" s="124">
         <v>1.2279976851851851E-3</v>
       </c>
-      <c r="O37" s="115">
+      <c r="O37" s="95">
         <v>11</v>
       </c>
-      <c r="P37" s="116">
+      <c r="P37" s="96">
         <v>2.1243171296296296E-3</v>
       </c>
       <c r="Q37" s="123">
@@ -16307,28 +16284,28 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="119">
+      <c r="A38" s="121">
         <v>12</v>
       </c>
-      <c r="B38" s="120">
+      <c r="B38" s="122">
         <v>1.5461458333333332E-3</v>
       </c>
-      <c r="C38" s="119">
+      <c r="C38" s="121">
         <v>12</v>
       </c>
-      <c r="D38" s="120">
+      <c r="D38" s="122">
         <v>1.9078009259259261E-3</v>
       </c>
-      <c r="E38" s="119">
+      <c r="E38" s="121">
         <v>12</v>
       </c>
-      <c r="F38" s="120">
+      <c r="F38" s="122">
         <v>1.4453819444444444E-3</v>
       </c>
-      <c r="G38" s="121">
+      <c r="G38" s="99">
         <v>12</v>
       </c>
-      <c r="H38" s="122">
+      <c r="H38" s="100">
         <v>1.4453819444444444E-3</v>
       </c>
       <c r="I38" s="1"/>
@@ -16345,10 +16322,10 @@
       <c r="N38" s="124">
         <v>1.310949074074074E-3</v>
       </c>
-      <c r="O38" s="115">
+      <c r="O38" s="95">
         <v>12</v>
       </c>
-      <c r="P38" s="116">
+      <c r="P38" s="96">
         <v>1.4692245370370371E-3</v>
       </c>
       <c r="Q38" s="123">
@@ -16364,28 +16341,28 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="119">
+      <c r="A39" s="121">
         <v>13</v>
       </c>
-      <c r="B39" s="120">
+      <c r="B39" s="122">
         <v>1.2216550925925925E-3</v>
       </c>
-      <c r="C39" s="119">
+      <c r="C39" s="121">
         <v>13</v>
       </c>
-      <c r="D39" s="120">
+      <c r="D39" s="122">
         <v>1.2544560185185185E-3</v>
       </c>
-      <c r="E39" s="119">
+      <c r="E39" s="121">
         <v>13</v>
       </c>
-      <c r="F39" s="120">
+      <c r="F39" s="122">
         <v>1.2557175925925926E-3</v>
       </c>
-      <c r="G39" s="121">
+      <c r="G39" s="99">
         <v>13</v>
       </c>
-      <c r="H39" s="122">
+      <c r="H39" s="100">
         <v>1.2557175925925926E-3</v>
       </c>
       <c r="I39" s="1"/>
@@ -16402,10 +16379,10 @@
       <c r="N39" s="124">
         <v>4.1754282407407408E-3</v>
       </c>
-      <c r="O39" s="115">
+      <c r="O39" s="95">
         <v>13</v>
       </c>
-      <c r="P39" s="116">
+      <c r="P39" s="96">
         <v>1.6091435185185184E-3</v>
       </c>
       <c r="Q39" s="123">
@@ -16421,28 +16398,28 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="119">
+      <c r="A40" s="121">
         <v>14</v>
       </c>
-      <c r="B40" s="120">
+      <c r="B40" s="122">
         <v>1.1457523148148147E-3</v>
       </c>
-      <c r="C40" s="119">
+      <c r="C40" s="121">
         <v>14</v>
       </c>
-      <c r="D40" s="120">
+      <c r="D40" s="122">
         <v>1.1745949074074074E-3</v>
       </c>
-      <c r="E40" s="119">
+      <c r="E40" s="121">
         <v>14</v>
       </c>
-      <c r="F40" s="120">
+      <c r="F40" s="122">
         <v>1.1743055555555556E-3</v>
       </c>
-      <c r="G40" s="121">
+      <c r="G40" s="99">
         <v>14</v>
       </c>
-      <c r="H40" s="122">
+      <c r="H40" s="100">
         <v>1.1743055555555556E-3</v>
       </c>
       <c r="I40" s="1"/>
@@ -16459,10 +16436,10 @@
       <c r="N40" s="124">
         <v>1.1806365740740742E-3</v>
       </c>
-      <c r="O40" s="115">
+      <c r="O40" s="95">
         <v>14</v>
       </c>
-      <c r="P40" s="116">
+      <c r="P40" s="96">
         <v>1.1635069444444444E-3</v>
       </c>
       <c r="Q40" s="123">
@@ -16478,28 +16455,28 @@
       <c r="W40" s="1"/>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="119">
+      <c r="A41" s="121">
         <v>15</v>
       </c>
-      <c r="B41" s="120">
+      <c r="B41" s="122">
         <v>1.5789930555555557E-3</v>
       </c>
-      <c r="C41" s="119">
+      <c r="C41" s="121">
         <v>15</v>
       </c>
-      <c r="D41" s="120">
+      <c r="D41" s="122">
         <v>1.544236111111111E-3</v>
       </c>
-      <c r="E41" s="119">
+      <c r="E41" s="121">
         <v>15</v>
       </c>
-      <c r="F41" s="120">
+      <c r="F41" s="122">
         <v>1.5701967592592592E-3</v>
       </c>
-      <c r="G41" s="121">
+      <c r="G41" s="99">
         <v>15</v>
       </c>
-      <c r="H41" s="122">
+      <c r="H41" s="100">
         <v>1.5701967592592592E-3</v>
       </c>
       <c r="I41" s="1"/>
@@ -16516,10 +16493,10 @@
       <c r="N41" s="124">
         <v>1.1869444444444445E-3</v>
       </c>
-      <c r="O41" s="115">
+      <c r="O41" s="95">
         <v>15</v>
       </c>
-      <c r="P41" s="116">
+      <c r="P41" s="96">
         <v>1.1449421296296297E-3</v>
       </c>
       <c r="Q41" s="123">
@@ -16535,28 +16512,28 @@
       <c r="W41" s="1"/>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="119">
+      <c r="A42" s="121">
         <v>16</v>
       </c>
-      <c r="B42" s="120">
+      <c r="B42" s="122">
         <v>1.1158217592592591E-3</v>
       </c>
-      <c r="C42" s="119">
+      <c r="C42" s="121">
         <v>16</v>
       </c>
-      <c r="D42" s="120">
+      <c r="D42" s="122">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="E42" s="119">
+      <c r="E42" s="121">
         <v>16</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42" s="122">
         <v>1.2513888888888889E-3</v>
       </c>
-      <c r="G42" s="121">
+      <c r="G42" s="99">
         <v>16</v>
       </c>
-      <c r="H42" s="122">
+      <c r="H42" s="100">
         <v>1.2513888888888889E-3</v>
       </c>
       <c r="I42" s="1"/>
@@ -16573,10 +16550,10 @@
       <c r="N42" s="124">
         <v>1.1115046296296296E-3</v>
       </c>
-      <c r="O42" s="115">
+      <c r="O42" s="95">
         <v>16</v>
       </c>
-      <c r="P42" s="116">
+      <c r="P42" s="96">
         <v>1.140324074074074E-3</v>
       </c>
       <c r="Q42" s="123">
@@ -16592,28 +16569,28 @@
       <c r="W42" s="1"/>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="119">
+      <c r="A43" s="121">
         <v>17</v>
       </c>
-      <c r="B43" s="120">
+      <c r="B43" s="122">
         <v>1.1162731481481481E-3</v>
       </c>
-      <c r="C43" s="119">
+      <c r="C43" s="121">
         <v>17</v>
       </c>
-      <c r="D43" s="120">
+      <c r="D43" s="122">
         <v>1.1204629629629629E-3</v>
       </c>
-      <c r="E43" s="119">
+      <c r="E43" s="121">
         <v>17</v>
       </c>
-      <c r="F43" s="120">
+      <c r="F43" s="122">
         <v>1.1524421296296296E-3</v>
       </c>
-      <c r="G43" s="121">
+      <c r="G43" s="99">
         <v>17</v>
       </c>
-      <c r="H43" s="122">
+      <c r="H43" s="100">
         <v>1.1524421296296296E-3</v>
       </c>
       <c r="I43" s="1"/>
@@ -16630,10 +16607,10 @@
       <c r="N43" s="124">
         <v>1.1427777777777777E-3</v>
       </c>
-      <c r="O43" s="115">
+      <c r="O43" s="95">
         <v>17</v>
       </c>
-      <c r="P43" s="116">
+      <c r="P43" s="96">
         <v>1.1632407407407407E-3</v>
       </c>
       <c r="Q43" s="123">
@@ -16649,28 +16626,28 @@
       <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="119">
+      <c r="A44" s="121">
         <v>18</v>
       </c>
-      <c r="B44" s="120">
+      <c r="B44" s="122">
         <v>1.114398148148148E-3</v>
       </c>
-      <c r="C44" s="119">
+      <c r="C44" s="121">
         <v>18</v>
       </c>
-      <c r="D44" s="120">
+      <c r="D44" s="122">
         <v>1.1069444444444445E-3</v>
       </c>
-      <c r="E44" s="119">
+      <c r="E44" s="121">
         <v>18</v>
       </c>
-      <c r="F44" s="120">
+      <c r="F44" s="122">
         <v>1.1676157407407408E-3</v>
       </c>
-      <c r="G44" s="121">
+      <c r="G44" s="99">
         <v>18</v>
       </c>
-      <c r="H44" s="122">
+      <c r="H44" s="100">
         <v>1.1676157407407408E-3</v>
       </c>
       <c r="I44" s="1"/>
@@ -16687,10 +16664,10 @@
       <c r="N44" s="124">
         <v>1.1362962962962963E-3</v>
       </c>
-      <c r="O44" s="115">
+      <c r="O44" s="95">
         <v>18</v>
       </c>
-      <c r="P44" s="116">
+      <c r="P44" s="96">
         <v>1.1319444444444443E-3</v>
       </c>
       <c r="Q44" s="123">
@@ -16706,28 +16683,28 @@
       <c r="W44" s="1"/>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="119">
+      <c r="A45" s="121">
         <v>19</v>
       </c>
-      <c r="B45" s="120">
+      <c r="B45" s="122">
         <v>1.1236805555555555E-3</v>
       </c>
-      <c r="C45" s="119">
+      <c r="C45" s="121">
         <v>19</v>
       </c>
-      <c r="D45" s="120">
+      <c r="D45" s="122">
         <v>1.1092129629629629E-3</v>
       </c>
-      <c r="E45" s="119">
+      <c r="E45" s="121">
         <v>19</v>
       </c>
-      <c r="F45" s="120">
+      <c r="F45" s="122">
         <v>1.1594328703703703E-3</v>
       </c>
-      <c r="G45" s="121">
+      <c r="G45" s="99">
         <v>19</v>
       </c>
-      <c r="H45" s="122">
+      <c r="H45" s="100">
         <v>1.1594328703703703E-3</v>
       </c>
       <c r="I45" s="1"/>
@@ -16744,10 +16721,10 @@
       <c r="N45" s="124">
         <v>1.1471990740740739E-3</v>
       </c>
-      <c r="O45" s="115">
+      <c r="O45" s="95">
         <v>19</v>
       </c>
-      <c r="P45" s="116">
+      <c r="P45" s="96">
         <v>1.149375E-3</v>
       </c>
       <c r="Q45" s="123">
@@ -16763,28 +16740,28 @@
       <c r="W45" s="1"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="119">
+      <c r="A46" s="121">
         <v>20</v>
       </c>
-      <c r="B46" s="120">
+      <c r="B46" s="122">
         <v>1.1430092592592592E-3</v>
       </c>
-      <c r="C46" s="119">
+      <c r="C46" s="121">
         <v>20</v>
       </c>
-      <c r="D46" s="120">
+      <c r="D46" s="122">
         <v>1.1691319444444444E-3</v>
       </c>
-      <c r="E46" s="119">
+      <c r="E46" s="121">
         <v>20</v>
       </c>
-      <c r="F46" s="120">
+      <c r="F46" s="122">
         <v>1.2307523148148149E-3</v>
       </c>
-      <c r="G46" s="121">
+      <c r="G46" s="99">
         <v>20</v>
       </c>
-      <c r="H46" s="122">
+      <c r="H46" s="100">
         <v>1.2307523148148149E-3</v>
       </c>
       <c r="I46" s="1"/>
@@ -16801,10 +16778,10 @@
       <c r="N46" s="126">
         <v>1.1019907407407408E-3</v>
       </c>
-      <c r="O46" s="117">
+      <c r="O46" s="97">
         <v>20</v>
       </c>
-      <c r="P46" s="118">
+      <c r="P46" s="98">
         <v>1.1516666666666665E-3</v>
       </c>
       <c r="Q46" s="125">
@@ -17327,21 +17304,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:R1"/>
     <mergeCell ref="K25:R25"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="O26:P26"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C257708-D205-496E-A70A-8716091E9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D3C955-CCF6-4AC1-B2D4-EA7CC7C98E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="321" r:id="rId9"/>
+    <pivotCache cacheId="1131" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="111">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -180,10 +180,19 @@
     <t>FECHA 8</t>
   </si>
   <si>
+    <t>Villicum</t>
+  </si>
+  <si>
     <t>FECHA 9</t>
   </si>
   <si>
+    <t>Parana</t>
+  </si>
+  <si>
     <t>FECHA 10</t>
+  </si>
+  <si>
+    <t>pos 2 C1</t>
   </si>
   <si>
     <t>PILOTO</t>
@@ -286,6 +295,9 @@
   </si>
   <si>
     <t>POS C2</t>
+  </si>
+  <si>
+    <t>VILLICUM</t>
   </si>
   <si>
     <t>(Todas)</t>
@@ -395,6 +407,12 @@
   <si>
     <t>Eze C1</t>
   </si>
+  <si>
+    <t>Mejor tiempo</t>
+  </si>
+  <si>
+    <t>VILLICUM C1</t>
+  </si>
 </sst>
 </file>
 
@@ -406,7 +424,7 @@
     <numFmt numFmtId="166" formatCode="mm:ss.000"/>
     <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +483,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1007,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1187,18 +1211,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,13 +1229,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1223,14 +1244,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1259,8 +1283,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1559,10 +1584,10 @@
                   <c:v>287.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>334.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>#N/A</c:v>
+                  <c:v>364.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1681,10 +1706,10 @@
                   <c:v>287.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>302.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>#N/A</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1797,13 +1822,13 @@
                   <c:v>148.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>169.75</c:v>
+                  <c:v>172.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>193.75</c:v>
+                  <c:v>196.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>208.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>#N/A</c:v>
@@ -1919,13 +1944,13 @@
                   <c:v>178.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>212.25</c:v>
+                  <c:v>209.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>235.5</c:v>
+                  <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>#N/A</c:v>
+                  <c:v>247.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>#N/A</c:v>
@@ -5115,7 +5140,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="321" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="1131" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5766,26 +5791,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110" t="s">
+      <c r="A1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="110"/>
+      <c r="D1" s="108"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="104" t="s">
+      <c r="F1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5800,13 +5825,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="93">
+      <c r="A2" s="99">
         <v>1</v>
       </c>
-      <c r="B2" s="93">
+      <c r="B2" s="99">
         <v>25</v>
       </c>
-      <c r="C2" s="93">
+      <c r="C2" s="99">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5842,28 +5867,30 @@
         <v>5</v>
       </c>
       <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
       <c r="Q2" s="1"/>
-      <c r="R2" s="104" t="s">
+      <c r="R2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
-      <c r="U2" s="104"/>
-      <c r="V2" s="104"/>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
-      <c r="Y2" s="104"/>
-      <c r="Z2" s="104"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="105"/>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="105"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="93">
+      <c r="A3" s="99">
         <v>2</v>
       </c>
-      <c r="B3" s="93">
+      <c r="B3" s="99">
         <v>18</v>
       </c>
-      <c r="C3" s="93">
+      <c r="C3" s="99">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -5932,13 +5959,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="93">
+      <c r="A4" s="99">
         <v>3</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="99">
         <v>15</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="99">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -6001,13 +6028,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="93">
+      <c r="A5" s="99">
         <v>4</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="99">
         <v>12</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="99">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -6063,17 +6090,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="104" t="s">
+      <c r="R6" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="104"/>
-      <c r="T6" s="104"/>
-      <c r="U6" s="104"/>
-      <c r="V6" s="104"/>
-      <c r="W6" s="104"/>
-      <c r="X6" s="104"/>
-      <c r="Y6" s="104"/>
-      <c r="Z6" s="104"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="105"/>
+      <c r="Z6" s="105"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6135,26 +6162,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="109">
+      <c r="G8" s="110">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="108"/>
-      <c r="I8" s="109">
+      <c r="H8" s="107"/>
+      <c r="I8" s="110">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109">
+      <c r="J8" s="107"/>
+      <c r="K8" s="110">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="108"/>
-      <c r="M8" s="109">
+      <c r="L8" s="107"/>
+      <c r="M8" s="110">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="108"/>
+      <c r="N8" s="107"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -6189,17 +6216,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="104" t="s">
+      <c r="R9" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="104"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="104"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="104"/>
-      <c r="Y9" s="104"/>
-      <c r="Z9" s="104"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6210,26 +6237,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G10" s="109">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111">
+      <c r="H10" s="109"/>
+      <c r="I10" s="109">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111">
+      <c r="J10" s="109"/>
+      <c r="K10" s="109">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111">
+      <c r="L10" s="109"/>
+      <c r="M10" s="109">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="111"/>
+      <c r="N10" s="109"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6262,26 +6289,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="102">
+      <c r="G11" s="101">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="103"/>
-      <c r="I11" s="102">
+      <c r="H11" s="102"/>
+      <c r="I11" s="101">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="103"/>
-      <c r="K11" s="102">
+      <c r="J11" s="102"/>
+      <c r="K11" s="101">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="102">
+      <c r="L11" s="102"/>
+      <c r="M11" s="101">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="103"/>
+      <c r="N11" s="102"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6304,40 +6331,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="102">
+      <c r="G12" s="101">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="103"/>
-      <c r="I12" s="102">
+      <c r="H12" s="102"/>
+      <c r="I12" s="101">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="103"/>
-      <c r="K12" s="102">
+      <c r="J12" s="102"/>
+      <c r="K12" s="101">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="103"/>
-      <c r="M12" s="102">
+      <c r="L12" s="102"/>
+      <c r="M12" s="101">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="103"/>
+      <c r="N12" s="102"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="104" t="s">
+      <c r="R12" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="104"/>
-      <c r="T12" s="104"/>
-      <c r="U12" s="104"/>
-      <c r="V12" s="104"/>
-      <c r="W12" s="104"/>
-      <c r="X12" s="104"/>
-      <c r="Y12" s="104"/>
-      <c r="Z12" s="104"/>
+      <c r="S12" s="105"/>
+      <c r="T12" s="105"/>
+      <c r="U12" s="105"/>
+      <c r="V12" s="105"/>
+      <c r="W12" s="105"/>
+      <c r="X12" s="105"/>
+      <c r="Y12" s="105"/>
+      <c r="Z12" s="105"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6383,17 +6410,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="104" t="s">
+      <c r="F14" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="104"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="105"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6441,7 +6468,9 @@
         <v>5</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
+      <c r="P15" s="1">
+        <v>40</v>
+      </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -6622,26 +6651,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="109">
+      <c r="G21" s="110">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="108"/>
-      <c r="I21" s="107">
+      <c r="H21" s="107"/>
+      <c r="I21" s="106">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="108"/>
-      <c r="K21" s="107">
+      <c r="J21" s="107"/>
+      <c r="K21" s="106">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="108"/>
-      <c r="M21" s="107">
+      <c r="L21" s="107"/>
+      <c r="M21" s="106">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="108"/>
+      <c r="N21" s="107"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -6674,26 +6703,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="105">
+      <c r="G23" s="103">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="106"/>
-      <c r="I23" s="105">
+      <c r="H23" s="104"/>
+      <c r="I23" s="103">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="106"/>
-      <c r="K23" s="105">
+      <c r="J23" s="104"/>
+      <c r="K23" s="103">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="106"/>
-      <c r="M23" s="105">
+      <c r="L23" s="104"/>
+      <c r="M23" s="103">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="106"/>
+      <c r="N23" s="104"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6707,26 +6736,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="102">
+      <c r="G24" s="101">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="103"/>
-      <c r="I24" s="102">
+      <c r="H24" s="102"/>
+      <c r="I24" s="101">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="103"/>
-      <c r="K24" s="102">
+      <c r="J24" s="102"/>
+      <c r="K24" s="101">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="103"/>
-      <c r="M24" s="102">
+      <c r="L24" s="102"/>
+      <c r="M24" s="101">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="103"/>
+      <c r="N24" s="102"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6740,26 +6769,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="102">
+      <c r="G25" s="101">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="103"/>
-      <c r="I25" s="102">
+      <c r="H25" s="102"/>
+      <c r="I25" s="101">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="103"/>
-      <c r="K25" s="102">
+      <c r="J25" s="102"/>
+      <c r="K25" s="101">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="103"/>
-      <c r="M25" s="102">
+      <c r="L25" s="102"/>
+      <c r="M25" s="101">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="103"/>
+      <c r="N25" s="102"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6789,17 +6818,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="104" t="s">
+      <c r="F27" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="104"/>
-      <c r="H27" s="104"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="104"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="105"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -6838,7 +6867,9 @@
         <v>5</v>
       </c>
       <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
+      <c r="P28" s="1">
+        <v>40</v>
+      </c>
       <c r="Q28" s="1"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" thickTop="1">
@@ -6997,26 +7028,26 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="107">
+      <c r="G34" s="106">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="108"/>
-      <c r="I34" s="107">
+      <c r="H34" s="107"/>
+      <c r="I34" s="106">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="108"/>
-      <c r="K34" s="107">
+      <c r="J34" s="107"/>
+      <c r="K34" s="106">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="108"/>
-      <c r="M34" s="107">
+      <c r="L34" s="107"/>
+      <c r="M34" s="106">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="108"/>
+      <c r="N34" s="107"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -7051,26 +7082,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="105">
+      <c r="G36" s="103">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="106"/>
-      <c r="I36" s="105">
+      <c r="H36" s="104"/>
+      <c r="I36" s="103">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="106"/>
-      <c r="K36" s="105">
+      <c r="J36" s="104"/>
+      <c r="K36" s="103">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="106"/>
-      <c r="M36" s="105">
+      <c r="L36" s="104"/>
+      <c r="M36" s="103">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="106"/>
+      <c r="N36" s="104"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7085,26 +7116,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="102">
+      <c r="G37" s="101">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="103"/>
-      <c r="I37" s="102">
+      <c r="H37" s="102"/>
+      <c r="I37" s="101">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="103"/>
-      <c r="K37" s="102">
+      <c r="J37" s="102"/>
+      <c r="K37" s="101">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="103"/>
-      <c r="M37" s="102">
+      <c r="L37" s="102"/>
+      <c r="M37" s="101">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="103"/>
+      <c r="N37" s="102"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7119,26 +7150,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="102">
+      <c r="G38" s="101">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="103"/>
-      <c r="I38" s="102">
+      <c r="H38" s="102"/>
+      <c r="I38" s="101">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="103"/>
-      <c r="K38" s="102">
+      <c r="J38" s="102"/>
+      <c r="K38" s="101">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="103"/>
-      <c r="M38" s="102">
+      <c r="L38" s="102"/>
+      <c r="M38" s="101">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="103"/>
+      <c r="N38" s="102"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7170,17 +7201,17 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="104" t="s">
+      <c r="F40" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="104"/>
-      <c r="N40" s="104"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="105"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="105"/>
+      <c r="N40" s="105"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -7220,7 +7251,9 @@
         <v>5</v>
       </c>
       <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="P41" s="1">
+        <v>60</v>
+      </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -7389,26 +7422,26 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="107">
+      <c r="G47" s="106">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="108"/>
-      <c r="I47" s="107">
+      <c r="H47" s="107"/>
+      <c r="I47" s="106">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="108"/>
-      <c r="K47" s="107">
+      <c r="J47" s="107"/>
+      <c r="K47" s="106">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="108"/>
-      <c r="M47" s="107">
+      <c r="L47" s="107"/>
+      <c r="M47" s="106">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="108"/>
+      <c r="N47" s="107"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -7439,82 +7472,88 @@
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
     </row>
-    <row r="49" spans="6:14">
+    <row r="49" spans="6:16">
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="105">
+      <c r="G49" s="103">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="106"/>
-      <c r="I49" s="105">
+      <c r="H49" s="104"/>
+      <c r="I49" s="103">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="106"/>
-      <c r="K49" s="105">
+      <c r="J49" s="104"/>
+      <c r="K49" s="103">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="106"/>
-      <c r="M49" s="105">
+      <c r="L49" s="104"/>
+      <c r="M49" s="103">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="106"/>
-    </row>
-    <row r="50" spans="6:14">
+      <c r="N49" s="104"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="6:16">
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="102">
+      <c r="G50" s="101">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="103"/>
-      <c r="I50" s="102">
+      <c r="H50" s="102"/>
+      <c r="I50" s="101">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="103"/>
-      <c r="K50" s="102">
+      <c r="J50" s="102"/>
+      <c r="K50" s="101">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="103"/>
-      <c r="M50" s="102">
+      <c r="L50" s="102"/>
+      <c r="M50" s="101">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="103"/>
-    </row>
-    <row r="51" spans="6:14">
+      <c r="N50" s="102"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+    <row r="51" spans="6:16">
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="102">
+      <c r="G51" s="101">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="103"/>
-      <c r="I51" s="102">
+      <c r="H51" s="102"/>
+      <c r="I51" s="101">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="103"/>
-      <c r="K51" s="102">
+      <c r="J51" s="102"/>
+      <c r="K51" s="101">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="103"/>
-      <c r="M51" s="102">
+      <c r="L51" s="102"/>
+      <c r="M51" s="101">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="103"/>
-    </row>
-    <row r="52" spans="6:14">
+      <c r="N51" s="102"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+    </row>
+    <row r="52" spans="6:16">
       <c r="F52" s="27"/>
       <c r="G52" s="28"/>
       <c r="H52" s="28"/>
@@ -7524,21 +7563,25 @@
       <c r="L52" s="28"/>
       <c r="M52" s="28"/>
       <c r="N52" s="28"/>
-    </row>
-    <row r="53" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F53" s="104" t="s">
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+    </row>
+    <row r="53" spans="6:16" ht="15.75" thickBot="1">
+      <c r="F53" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
-    </row>
-    <row r="54" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="105"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="105"/>
+      <c r="M53" s="105"/>
+      <c r="N53" s="105"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+    </row>
+    <row r="54" spans="6:16" ht="16.5" thickTop="1" thickBot="1">
       <c r="F54" s="13" t="s">
         <v>26</v>
       </c>
@@ -7566,8 +7609,12 @@
       <c r="N54" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O54" s="1"/>
+      <c r="P54" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="6:16" ht="15.75" thickTop="1">
       <c r="F55" s="14" t="s">
         <v>9</v>
       </c>
@@ -7599,8 +7646,10 @@
         <f>+IF(M55=1,$B$2,IF($M55=2,$B$3,IF($M55=3,$B$4,IF($M55=4,$B$5,""))))</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="56" spans="6:14">
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+    </row>
+    <row r="56" spans="6:16">
       <c r="F56" s="11" t="s">
         <v>11</v>
       </c>
@@ -7632,8 +7681,10 @@
         <f>+IF(M56=1,$D$2,IF($M56=2,$D$3,IF($M56=3,$D$4,IF($M56=4,$D$5,""))))</f>
         <v>18.75</v>
       </c>
-    </row>
-    <row r="57" spans="6:14">
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+    </row>
+    <row r="57" spans="6:16">
       <c r="F57" s="11" t="s">
         <v>13</v>
       </c>
@@ -7647,8 +7698,10 @@
       <c r="L57" s="5"/>
       <c r="M57" s="10"/>
       <c r="N57" s="5"/>
-    </row>
-    <row r="58" spans="6:14">
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+    </row>
+    <row r="58" spans="6:16">
       <c r="F58" s="11" t="s">
         <v>14</v>
       </c>
@@ -7662,8 +7715,10 @@
       <c r="L58" s="5"/>
       <c r="M58" s="10"/>
       <c r="N58" s="5"/>
-    </row>
-    <row r="59" spans="6:14">
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+    </row>
+    <row r="59" spans="6:16">
       <c r="F59" s="11" t="s">
         <v>16</v>
       </c>
@@ -7677,33 +7732,37 @@
       <c r="N59" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="6:14" ht="15.75" thickBot="1">
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+    </row>
+    <row r="60" spans="6:16" ht="15.75" thickBot="1">
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="107">
+      <c r="G60" s="106">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="108"/>
-      <c r="I60" s="107">
+      <c r="H60" s="107"/>
+      <c r="I60" s="106">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="108"/>
-      <c r="K60" s="107">
+      <c r="J60" s="107"/>
+      <c r="K60" s="106">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="108"/>
-      <c r="M60" s="107">
+      <c r="L60" s="107"/>
+      <c r="M60" s="106">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="108"/>
-    </row>
-    <row r="61" spans="6:14" ht="15.75" thickTop="1">
+      <c r="N60" s="107"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+    </row>
+    <row r="61" spans="6:16" ht="15.75" thickTop="1">
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -7713,96 +7772,106 @@
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
-    </row>
-    <row r="62" spans="6:14">
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+    </row>
+    <row r="62" spans="6:16">
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="105">
+      <c r="G62" s="103">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="106"/>
-      <c r="I62" s="105">
+      <c r="H62" s="104"/>
+      <c r="I62" s="103">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="106"/>
-      <c r="K62" s="105">
+      <c r="J62" s="104"/>
+      <c r="K62" s="103">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="106"/>
-      <c r="M62" s="105">
+      <c r="L62" s="104"/>
+      <c r="M62" s="103">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="106"/>
-    </row>
-    <row r="63" spans="6:14">
+      <c r="N62" s="104"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+    </row>
+    <row r="63" spans="6:16">
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="102">
+      <c r="G63" s="101">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="103"/>
-      <c r="I63" s="102">
+      <c r="H63" s="102"/>
+      <c r="I63" s="101">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="103"/>
-      <c r="K63" s="102">
+      <c r="J63" s="102"/>
+      <c r="K63" s="101">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="103"/>
-      <c r="M63" s="102">
+      <c r="L63" s="102"/>
+      <c r="M63" s="101">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="103"/>
-    </row>
-    <row r="64" spans="6:14">
+      <c r="N63" s="102"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+    </row>
+    <row r="64" spans="6:16">
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="102">
+      <c r="G64" s="101">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="103"/>
-      <c r="I64" s="102">
+      <c r="H64" s="102"/>
+      <c r="I64" s="101">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="103"/>
-      <c r="K64" s="102">
+      <c r="J64" s="102"/>
+      <c r="K64" s="101">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="103"/>
-      <c r="M64" s="102">
+      <c r="L64" s="102"/>
+      <c r="M64" s="101">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="103"/>
-    </row>
-    <row r="66" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F66" s="104" t="s">
+      <c r="N64" s="102"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+    </row>
+    <row r="66" spans="6:16" ht="15.75" thickBot="1">
+      <c r="F66" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="104"/>
-      <c r="H66" s="104"/>
-      <c r="I66" s="104"/>
-      <c r="J66" s="104"/>
-      <c r="K66" s="104"/>
-      <c r="L66" s="104"/>
-      <c r="M66" s="104"/>
-      <c r="N66" s="104"/>
-    </row>
-    <row r="67" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="G66" s="105"/>
+      <c r="H66" s="105"/>
+      <c r="I66" s="105"/>
+      <c r="J66" s="105"/>
+      <c r="K66" s="105"/>
+      <c r="L66" s="105"/>
+      <c r="M66" s="105"/>
+      <c r="N66" s="105"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+    </row>
+    <row r="67" spans="6:16" ht="16.5" thickTop="1" thickBot="1">
       <c r="F67" s="13" t="s">
         <v>28</v>
       </c>
@@ -7830,8 +7899,12 @@
       <c r="N67" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O67" s="1"/>
+      <c r="P67" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="6:16" ht="15.75" thickTop="1">
       <c r="F68" s="14" t="s">
         <v>9</v>
       </c>
@@ -7863,8 +7936,10 @@
         <f>+IF(M68=1,$B$2,IF($M68=2,$B$3,IF($M68=3,$B$4,IF($M68=4,$B$5,""))))</f>
         <v>18</v>
       </c>
-    </row>
-    <row r="69" spans="6:14">
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+    </row>
+    <row r="69" spans="6:16">
       <c r="F69" s="11" t="s">
         <v>11</v>
       </c>
@@ -7896,8 +7971,10 @@
         <f>+IF(M69=1,$D$2,IF($M69=2,$D$3,IF($M69=3,$D$4,IF($M69=4,$D$5,""))))</f>
         <v>11.25</v>
       </c>
-    </row>
-    <row r="70" spans="6:14">
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+    </row>
+    <row r="70" spans="6:16">
       <c r="F70" s="11" t="s">
         <v>13</v>
       </c>
@@ -7911,8 +7988,10 @@
       <c r="L70" s="5"/>
       <c r="M70" s="10"/>
       <c r="N70" s="5"/>
-    </row>
-    <row r="71" spans="6:14">
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+    </row>
+    <row r="71" spans="6:16">
       <c r="F71" s="11" t="s">
         <v>14</v>
       </c>
@@ -7926,8 +8005,10 @@
       <c r="L71" s="5"/>
       <c r="M71" s="10"/>
       <c r="N71" s="5"/>
-    </row>
-    <row r="72" spans="6:14">
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+    </row>
+    <row r="72" spans="6:16">
       <c r="F72" s="11" t="s">
         <v>16</v>
       </c>
@@ -7941,45 +8022,49 @@
       <c r="L72" s="5"/>
       <c r="M72" s="10"/>
       <c r="N72" s="5"/>
-    </row>
-    <row r="73" spans="6:14" ht="15.75" thickBot="1">
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+    </row>
+    <row r="73" spans="6:16" ht="15.75" thickBot="1">
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="107">
+      <c r="G73" s="106">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="108">
+      <c r="H73" s="107">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="107">
+      <c r="I73" s="106">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="108">
+      <c r="J73" s="107">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="107">
+      <c r="K73" s="106">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="108">
+      <c r="L73" s="107">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="107">
+      <c r="M73" s="106">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="108">
+      <c r="N73" s="107">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-    </row>
-    <row r="74" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+    </row>
+    <row r="74" spans="6:16" ht="15.75" thickTop="1">
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -7989,96 +8074,106 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-    </row>
-    <row r="75" spans="6:14">
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+    </row>
+    <row r="75" spans="6:16">
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="105">
+      <c r="G75" s="103">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="106"/>
-      <c r="I75" s="105">
+      <c r="H75" s="104"/>
+      <c r="I75" s="103">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="106"/>
-      <c r="K75" s="105">
+      <c r="J75" s="104"/>
+      <c r="K75" s="103">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="106"/>
-      <c r="M75" s="105">
+      <c r="L75" s="104"/>
+      <c r="M75" s="103">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="106"/>
-    </row>
-    <row r="76" spans="6:14">
+      <c r="N75" s="104"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+    </row>
+    <row r="76" spans="6:16">
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="102">
+      <c r="G76" s="101">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="103"/>
-      <c r="I76" s="102">
+      <c r="H76" s="102"/>
+      <c r="I76" s="101">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="103"/>
-      <c r="K76" s="102">
+      <c r="J76" s="102"/>
+      <c r="K76" s="101">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="103"/>
-      <c r="M76" s="102">
+      <c r="L76" s="102"/>
+      <c r="M76" s="101">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="103"/>
-    </row>
-    <row r="77" spans="6:14">
+      <c r="N76" s="102"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+    </row>
+    <row r="77" spans="6:16">
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="102">
+      <c r="G77" s="101">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="103"/>
-      <c r="I77" s="102">
+      <c r="H77" s="102"/>
+      <c r="I77" s="101">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="103"/>
-      <c r="K77" s="102">
+      <c r="J77" s="102"/>
+      <c r="K77" s="101">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="103"/>
-      <c r="M77" s="102">
+      <c r="L77" s="102"/>
+      <c r="M77" s="101">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="103"/>
-    </row>
-    <row r="79" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F79" s="104" t="s">
+      <c r="N77" s="102"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+    </row>
+    <row r="79" spans="6:16" ht="15.75" thickBot="1">
+      <c r="F79" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="G79" s="104"/>
-      <c r="H79" s="104"/>
-      <c r="I79" s="104"/>
-      <c r="J79" s="104"/>
-      <c r="K79" s="104"/>
-      <c r="L79" s="104"/>
-      <c r="M79" s="104"/>
-      <c r="N79" s="104"/>
-    </row>
-    <row r="80" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="G79" s="105"/>
+      <c r="H79" s="105"/>
+      <c r="I79" s="105"/>
+      <c r="J79" s="105"/>
+      <c r="K79" s="105"/>
+      <c r="L79" s="105"/>
+      <c r="M79" s="105"/>
+      <c r="N79" s="105"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+    </row>
+    <row r="80" spans="6:16" ht="16.5" thickTop="1" thickBot="1">
       <c r="F80" s="13" t="s">
         <v>30</v>
       </c>
@@ -8106,8 +8201,12 @@
       <c r="N80" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="6:24" ht="15.75" thickTop="1">
+      <c r="O80" s="1"/>
+      <c r="P80" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="6:26" ht="15.75" thickTop="1">
       <c r="F81" s="14" t="s">
         <v>9</v>
       </c>
@@ -8126,18 +8225,18 @@
         <v>18</v>
       </c>
       <c r="K81" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81" s="6">
         <f>+IF(K81=1,$B$2,IF($K81=2,$B$3,IF($K81=3,$B$4,IF($K81=4,$B$5,""))))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M81" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N81" s="6">
         <f>+IF(M81=1,$B$2,IF($M81=2,$B$3,IF($M81=3,$B$4,IF($M81=4,$B$5,""))))</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
@@ -8149,8 +8248,10 @@
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
-    </row>
-    <row r="82" spans="6:24">
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
+    </row>
+    <row r="82" spans="6:26">
       <c r="F82" s="11" t="s">
         <v>11</v>
       </c>
@@ -8192,8 +8293,10 @@
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
-    </row>
-    <row r="83" spans="6:24">
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
+    </row>
+    <row r="83" spans="6:26">
       <c r="F83" s="11" t="s">
         <v>13</v>
       </c>
@@ -8217,8 +8320,10 @@
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
-    </row>
-    <row r="84" spans="6:24">
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+    </row>
+    <row r="84" spans="6:26">
       <c r="F84" s="11" t="s">
         <v>14</v>
       </c>
@@ -8242,8 +8347,10 @@
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
-    </row>
-    <row r="85" spans="6:24">
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+    </row>
+    <row r="85" spans="6:26">
       <c r="F85" s="11" t="s">
         <v>16</v>
       </c>
@@ -8267,42 +8374,44 @@
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
-    </row>
-    <row r="86" spans="6:24" ht="15.75" thickBot="1">
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+    </row>
+    <row r="86" spans="6:26" ht="15.75" thickBot="1">
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="107">
+      <c r="G86" s="106">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="108">
+      <c r="H86" s="107">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="107">
+      <c r="I86" s="106">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="108">
+      <c r="J86" s="107">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="107">
+      <c r="K86" s="106">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
-        <v>21</v>
-      </c>
-      <c r="L86" s="108">
+        <v>24</v>
+      </c>
+      <c r="L86" s="107">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
-        <v>21</v>
-      </c>
-      <c r="M86" s="107">
+        <v>24</v>
+      </c>
+      <c r="M86" s="106">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
-        <v>33.75</v>
-      </c>
-      <c r="N86" s="108">
+        <v>30.75</v>
+      </c>
+      <c r="N86" s="107">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
-        <v>33.75</v>
+        <v>30.75</v>
       </c>
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
@@ -8314,8 +8423,10 @@
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
-    </row>
-    <row r="87" spans="6:24">
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+    </row>
+    <row r="87" spans="6:26">
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -8335,31 +8446,33 @@
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
-    </row>
-    <row r="88" spans="6:24">
+      <c r="Y87" s="1"/>
+      <c r="Z87" s="1"/>
+    </row>
+    <row r="88" spans="6:26">
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="105">
+      <c r="G88" s="103">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="106"/>
-      <c r="I88" s="105">
+      <c r="H88" s="104"/>
+      <c r="I88" s="103">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="106"/>
-      <c r="K88" s="105">
+      <c r="J88" s="104"/>
+      <c r="K88" s="103">
         <f>+SUM(K86,K75)</f>
-        <v>169.75</v>
-      </c>
-      <c r="L88" s="106"/>
-      <c r="M88" s="105">
+        <v>172.75</v>
+      </c>
+      <c r="L88" s="104"/>
+      <c r="M88" s="103">
         <f>+SUM(M86,M75)</f>
-        <v>212.25</v>
-      </c>
-      <c r="N88" s="106"/>
+        <v>209.25</v>
+      </c>
+      <c r="N88" s="104"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -8370,31 +8483,33 @@
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
-    </row>
-    <row r="89" spans="6:24">
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
+    </row>
+    <row r="89" spans="6:26">
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="102">
+      <c r="G89" s="101">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="103"/>
-      <c r="I89" s="102">
+      <c r="H89" s="102"/>
+      <c r="I89" s="101">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="103"/>
-      <c r="K89" s="102">
+      <c r="J89" s="102"/>
+      <c r="K89" s="101">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
-        <v>0</v>
-      </c>
-      <c r="L89" s="103"/>
-      <c r="M89" s="102">
+        <v>10</v>
+      </c>
+      <c r="L89" s="102"/>
+      <c r="M89" s="101">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
-        <v>10</v>
-      </c>
-      <c r="N89" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="N89" s="102"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -8405,31 +8520,33 @@
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
-    </row>
-    <row r="90" spans="6:24">
+      <c r="Y89" s="1"/>
+      <c r="Z89" s="1"/>
+    </row>
+    <row r="90" spans="6:26">
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="102">
+      <c r="G90" s="101">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="103"/>
-      <c r="I90" s="102">
+      <c r="H90" s="102"/>
+      <c r="I90" s="101">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="103"/>
-      <c r="K90" s="102">
+      <c r="J90" s="102"/>
+      <c r="K90" s="101">
         <f>+SUM(K89+K77-K50)</f>
-        <v>0</v>
-      </c>
-      <c r="L90" s="103"/>
-      <c r="M90" s="102">
+        <v>10</v>
+      </c>
+      <c r="L90" s="102"/>
+      <c r="M90" s="101">
         <f>+SUM(M89+M77-M50)</f>
-        <v>70</v>
-      </c>
-      <c r="N90" s="103"/>
+        <v>60</v>
+      </c>
+      <c r="N90" s="102"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -8440,19 +8557,44 @@
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
-    </row>
-    <row r="92" spans="6:24">
-      <c r="F92" s="104" t="s">
+      <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
+    </row>
+    <row r="91" spans="6:26">
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
+    </row>
+    <row r="92" spans="6:26">
+      <c r="F92" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="G92" s="104"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="104"/>
-      <c r="J92" s="104"/>
-      <c r="K92" s="104"/>
-      <c r="L92" s="104"/>
-      <c r="M92" s="104"/>
-      <c r="N92" s="104"/>
+      <c r="G92" s="105"/>
+      <c r="H92" s="105"/>
+      <c r="I92" s="105"/>
+      <c r="J92" s="105"/>
+      <c r="K92" s="105"/>
+      <c r="L92" s="105"/>
+      <c r="M92" s="105"/>
+      <c r="N92" s="105"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -8463,8 +8605,10 @@
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
-    </row>
-    <row r="93" spans="6:24" ht="16.5" customHeight="1">
+      <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
+    </row>
+    <row r="93" spans="6:26" ht="16.5" customHeight="1">
       <c r="F93" s="13" t="s">
         <v>32</v>
       </c>
@@ -8493,7 +8637,9 @@
         <v>5</v>
       </c>
       <c r="O93" s="1"/>
-      <c r="P93" s="1"/>
+      <c r="P93" s="1">
+        <v>60</v>
+      </c>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
@@ -8502,8 +8648,10 @@
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
-    </row>
-    <row r="94" spans="6:24" ht="15.75" customHeight="1">
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
+    </row>
+    <row r="94" spans="6:26" ht="15.75" customHeight="1">
       <c r="F94" s="14" t="s">
         <v>9</v>
       </c>
@@ -8545,8 +8693,10 @@
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
-    </row>
-    <row r="95" spans="6:24">
+      <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
+    </row>
+    <row r="95" spans="6:26">
       <c r="F95" s="11" t="s">
         <v>11</v>
       </c>
@@ -8588,8 +8738,10 @@
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
-    </row>
-    <row r="96" spans="6:24">
+      <c r="Y95" s="1"/>
+      <c r="Z95" s="1"/>
+    </row>
+    <row r="96" spans="6:26">
       <c r="F96" s="11" t="s">
         <v>13</v>
       </c>
@@ -8613,8 +8765,10 @@
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
-    </row>
-    <row r="97" spans="6:14">
+      <c r="Y96" s="1"/>
+      <c r="Z96" s="1"/>
+    </row>
+    <row r="97" spans="6:16">
       <c r="F97" s="11" t="s">
         <v>14</v>
       </c>
@@ -8628,8 +8782,10 @@
       <c r="L97" s="5"/>
       <c r="M97" s="10"/>
       <c r="N97" s="5"/>
-    </row>
-    <row r="98" spans="6:14">
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+    </row>
+    <row r="98" spans="6:16">
       <c r="F98" s="11" t="s">
         <v>16</v>
       </c>
@@ -8643,45 +8799,49 @@
       <c r="L98" s="5"/>
       <c r="M98" s="10"/>
       <c r="N98" s="5"/>
-    </row>
-    <row r="99" spans="6:14" ht="15.75" customHeight="1">
+      <c r="O98" s="1"/>
+      <c r="P98" s="1"/>
+    </row>
+    <row r="99" spans="6:16" ht="15.75" customHeight="1">
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="107">
+      <c r="G99" s="106">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="108">
+      <c r="H99" s="107">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="107">
+      <c r="I99" s="106">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="108">
+      <c r="J99" s="107">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="107">
+      <c r="K99" s="106">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="L99" s="108">
+      <c r="L99" s="107">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="M99" s="107">
+      <c r="M99" s="106">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-      <c r="N99" s="108">
+      <c r="N99" s="107">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-    </row>
-    <row r="100" spans="6:14">
+      <c r="O99" s="1"/>
+      <c r="P99" s="1"/>
+    </row>
+    <row r="100" spans="6:16">
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -8691,96 +8851,108 @@
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
-    </row>
-    <row r="101" spans="6:14">
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+    </row>
+    <row r="101" spans="6:16">
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="105">
+      <c r="G101" s="103">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="106"/>
-      <c r="I101" s="105">
+      <c r="H101" s="104"/>
+      <c r="I101" s="103">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="106"/>
-      <c r="K101" s="105">
+      <c r="J101" s="104"/>
+      <c r="K101" s="103">
         <f>+SUM(K99,K88)</f>
-        <v>193.75</v>
-      </c>
-      <c r="L101" s="106"/>
-      <c r="M101" s="105">
+        <v>196.75</v>
+      </c>
+      <c r="L101" s="104"/>
+      <c r="M101" s="103">
         <f>+SUM(M99,M88)</f>
-        <v>235.5</v>
-      </c>
-      <c r="N101" s="106"/>
-    </row>
-    <row r="102" spans="6:14">
+        <v>232.5</v>
+      </c>
+      <c r="N101" s="104"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+    </row>
+    <row r="102" spans="6:16">
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="102">
+      <c r="G102" s="101">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="103"/>
-      <c r="I102" s="102">
+      <c r="H102" s="102"/>
+      <c r="I102" s="101">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="103"/>
-      <c r="K102" s="102">
+      <c r="J102" s="102"/>
+      <c r="K102" s="101">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="103"/>
-      <c r="M102" s="102">
+      <c r="L102" s="102"/>
+      <c r="M102" s="101">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="103"/>
-    </row>
-    <row r="103" spans="6:14">
+      <c r="N102" s="102"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+    </row>
+    <row r="103" spans="6:16">
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="102">
+      <c r="G103" s="101">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="103"/>
-      <c r="I103" s="102">
+      <c r="H103" s="102"/>
+      <c r="I103" s="101">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="103"/>
-      <c r="K103" s="102">
+      <c r="J103" s="102"/>
+      <c r="K103" s="101">
         <f>+SUM(K102+K90-K63)</f>
-        <v>10</v>
-      </c>
-      <c r="L103" s="103"/>
-      <c r="M103" s="102">
+        <v>20</v>
+      </c>
+      <c r="L103" s="102"/>
+      <c r="M103" s="101">
         <f>+SUM(M102+M90-M63)</f>
-        <v>30</v>
-      </c>
-      <c r="N103" s="103"/>
-    </row>
-    <row r="105" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F105" s="104"/>
-      <c r="G105" s="104"/>
-      <c r="H105" s="104"/>
-      <c r="I105" s="104"/>
-      <c r="J105" s="104"/>
-      <c r="K105" s="104"/>
-      <c r="L105" s="104"/>
-      <c r="M105" s="104"/>
-      <c r="N105" s="104"/>
-    </row>
-    <row r="106" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+        <v>20</v>
+      </c>
+      <c r="N103" s="102"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1"/>
+    </row>
+    <row r="105" spans="6:16" ht="15.75" thickBot="1">
+      <c r="F105" s="105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" s="105"/>
+      <c r="H105" s="105"/>
+      <c r="I105" s="105"/>
+      <c r="J105" s="105"/>
+      <c r="K105" s="105"/>
+      <c r="L105" s="105"/>
+      <c r="M105" s="105"/>
+      <c r="N105" s="105"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+    </row>
+    <row r="106" spans="6:16" ht="16.5" thickTop="1" thickBot="1">
       <c r="F106" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>4</v>
@@ -8806,40 +8978,56 @@
       <c r="N106" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="107" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O106" s="1"/>
+      <c r="P106" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="107" spans="6:16" ht="15.75" thickTop="1">
       <c r="F107" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G107" s="9"/>
-      <c r="H107" s="6" t="str">
+      <c r="G107" s="9">
+        <v>1</v>
+      </c>
+      <c r="H107" s="6">
         <f>+IF(G107=1,$B$2,IF($G107=2,$B$3,IF($G107=3,$B$4,IF($G107=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="I107" s="9"/>
-      <c r="J107" s="6" t="str">
+        <v>25</v>
+      </c>
+      <c r="I107" s="9">
+        <v>3</v>
+      </c>
+      <c r="J107" s="6">
         <f>+IF(I107=1,$B$2,IF($I107=2,$B$3,IF($I107=3,$B$4,IF($I107=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="K107" s="9"/>
-      <c r="L107" s="6" t="str">
+        <v>15</v>
+      </c>
+      <c r="K107" s="9">
+        <v>4</v>
+      </c>
+      <c r="L107" s="6">
         <f>+IF(K107=1,$B$2,IF($K107=2,$B$3,IF($K107=3,$B$4,IF($K107=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="M107" s="9"/>
-      <c r="N107" s="6" t="str">
+        <v>12</v>
+      </c>
+      <c r="M107" s="9">
+        <v>3</v>
+      </c>
+      <c r="N107" s="6">
         <f>+IF(M107=1,$B$2,IF($M107=2,$B$3,IF($M107=3,$B$4,IF($M107=4,$B$5,""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="6:14">
+        <v>15</v>
+      </c>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+    </row>
+    <row r="108" spans="6:16">
       <c r="F108" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G108" s="10"/>
-      <c r="H108" s="5" t="str">
+      <c r="G108" s="10">
+        <v>1</v>
+      </c>
+      <c r="H108" s="5">
         <f>+IF(G108=1,$D$2,IF($G108=2,$D$3,IF($G108=3,$D$4,IF($G108=4,$D$5,""))))</f>
-        <v/>
+        <v>18.75</v>
       </c>
       <c r="I108" s="10"/>
       <c r="J108" s="5" t="str">
@@ -8856,66 +9044,100 @@
         <f>+IF(M108=1,$D$2,IF($M108=2,$D$3,IF($M108=3,$D$4,IF($M108=4,$D$5,""))))</f>
         <v/>
       </c>
-    </row>
-    <row r="109" spans="6:14">
+      <c r="O108" s="1"/>
+      <c r="P108" s="1"/>
+    </row>
+    <row r="109" spans="6:16">
       <c r="F109" s="11" t="s">
         <v>13</v>
       </c>
       <c r="G109" s="10"/>
-      <c r="H109" s="5"/>
+      <c r="H109" s="5">
+        <v>1</v>
+      </c>
       <c r="I109" s="10"/>
       <c r="J109" s="5"/>
       <c r="K109" s="10"/>
       <c r="L109" s="5"/>
       <c r="M109" s="10"/>
       <c r="N109" s="5"/>
-    </row>
-    <row r="110" spans="6:14">
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+    </row>
+    <row r="110" spans="6:16">
       <c r="F110" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="10"/>
-      <c r="H110" s="5"/>
+      <c r="H110" s="5">
+        <v>1</v>
+      </c>
       <c r="I110" s="10"/>
       <c r="J110" s="5"/>
       <c r="K110" s="10"/>
       <c r="L110" s="5"/>
       <c r="M110" s="10"/>
       <c r="N110" s="5"/>
-    </row>
-    <row r="111" spans="6:14">
+      <c r="O110" s="1"/>
+      <c r="P110" s="1"/>
+    </row>
+    <row r="111" spans="6:16">
       <c r="F111" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G111" s="10"/>
-      <c r="H111" s="5"/>
+      <c r="H111" s="5">
+        <v>1</v>
+      </c>
       <c r="I111" s="10"/>
       <c r="J111" s="5"/>
       <c r="K111" s="10"/>
       <c r="L111" s="5"/>
       <c r="M111" s="10"/>
       <c r="N111" s="5"/>
-    </row>
-    <row r="112" spans="6:14" ht="15.75" customHeight="1">
+      <c r="O111" s="1"/>
+      <c r="P111" s="1"/>
+    </row>
+    <row r="112" spans="6:16" ht="15.75" customHeight="1">
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="107"/>
-      <c r="H112" s="108"/>
-      <c r="I112" s="107"/>
-      <c r="J112" s="108"/>
-      <c r="K112" s="107"/>
-      <c r="L112" s="108">
+      <c r="G112" s="106">
+        <f>+SUM(H107:H111)</f>
+        <v>46.75</v>
+      </c>
+      <c r="H112" s="107">
+        <f>+SUM(H107:H111)</f>
+        <v>46.75</v>
+      </c>
+      <c r="I112" s="106">
+        <f>+SUM(J107:J111)</f>
+        <v>15</v>
+      </c>
+      <c r="J112" s="107">
+        <f>+SUM(J107:J111)</f>
+        <v>15</v>
+      </c>
+      <c r="K112" s="106">
         <f>+SUM(L107:L111)</f>
-        <v>0</v>
-      </c>
-      <c r="M112" s="107"/>
-      <c r="N112" s="108">
+        <v>12</v>
+      </c>
+      <c r="L112" s="107">
+        <f>+SUM(L107:L111)</f>
+        <v>12</v>
+      </c>
+      <c r="M112" s="106">
         <f>+SUM(N107:N111)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="6:14">
+        <v>15</v>
+      </c>
+      <c r="N112" s="107">
+        <f>+SUM(N107:N111)</f>
+        <v>15</v>
+      </c>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+    </row>
+    <row r="113" spans="6:23">
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
@@ -8925,72 +9147,143 @@
       <c r="L113" s="1"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
-    </row>
-    <row r="114" spans="6:14">
+      <c r="O113" s="1"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
+      <c r="T113" s="1"/>
+      <c r="U113" s="1"/>
+      <c r="V113" s="1"/>
+      <c r="W113" s="1"/>
+    </row>
+    <row r="114" spans="6:23">
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="105"/>
-      <c r="H114" s="106"/>
-      <c r="I114" s="105"/>
-      <c r="J114" s="106"/>
-      <c r="K114" s="105"/>
-      <c r="L114" s="106"/>
-      <c r="M114" s="105"/>
-      <c r="N114" s="106"/>
-    </row>
-    <row r="115" spans="6:14">
+      <c r="G114" s="103">
+        <f>+SUM(G112,G101)</f>
+        <v>334.25</v>
+      </c>
+      <c r="H114" s="104"/>
+      <c r="I114" s="103">
+        <f>+SUM(I112,I101)</f>
+        <v>302.25</v>
+      </c>
+      <c r="J114" s="104"/>
+      <c r="K114" s="103">
+        <f>+SUM(K112,K101)</f>
+        <v>208.75</v>
+      </c>
+      <c r="L114" s="104"/>
+      <c r="M114" s="103">
+        <f>+SUM(M112,M101)</f>
+        <v>247.5</v>
+      </c>
+      <c r="N114" s="104"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
+      <c r="T114" s="1"/>
+      <c r="U114" s="1"/>
+      <c r="V114" s="1"/>
+      <c r="W114" s="1"/>
+    </row>
+    <row r="115" spans="6:23">
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="102" t="str">
+      <c r="G115" s="101">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="H115" s="103"/>
-      <c r="I115" s="102" t="str">
+        <v>40</v>
+      </c>
+      <c r="H115" s="102"/>
+      <c r="I115" s="101">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="J115" s="103"/>
-      <c r="K115" s="105"/>
-      <c r="L115" s="106"/>
-      <c r="M115" s="105"/>
-      <c r="N115" s="106"/>
-    </row>
-    <row r="116" spans="6:14">
+        <v>10</v>
+      </c>
+      <c r="J115" s="102"/>
+      <c r="K115" s="101">
+        <f>+IF($K107=1,40,IF($K107=2,20,IF($K107=3,10,IF($K107=4,0,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="L115" s="102"/>
+      <c r="M115" s="101">
+        <f>+IF($M107=1,40,IF($M107=2,20,IF($M107=3,10,IF($M107=4,0,""))))</f>
+        <v>10</v>
+      </c>
+      <c r="N115" s="102"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+      <c r="S115" s="1"/>
+      <c r="T115" s="1"/>
+      <c r="U115" s="1"/>
+      <c r="V115" s="1"/>
+      <c r="W115" s="1"/>
+    </row>
+    <row r="116" spans="6:23">
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="102"/>
-      <c r="H116" s="103"/>
-      <c r="I116" s="102"/>
-      <c r="J116" s="103"/>
-      <c r="K116" s="105" t="str">
-        <f>+IF($K107=1,"40Kg",IF($K107=2,"20Kg",IF($K107=3,"10Kg",IF($K107=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="L116" s="106"/>
-      <c r="M116" s="105" t="str">
-        <f>+IF($M107=1,"40Kg",IF($M107=2,"20Kg",IF($M107=3,"10Kg",IF($M107=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="N116" s="106"/>
-    </row>
-    <row r="118" spans="6:14" ht="15.75" thickBot="1">
-      <c r="F118" s="104"/>
-      <c r="G118" s="104"/>
-      <c r="H118" s="104"/>
-      <c r="I118" s="104"/>
-      <c r="J118" s="104"/>
-      <c r="K118" s="104"/>
-      <c r="L118" s="104"/>
-      <c r="M118" s="104"/>
-      <c r="N118" s="104"/>
-    </row>
-    <row r="119" spans="6:14" ht="16.5" thickTop="1" thickBot="1">
+      <c r="G116" s="101">
+        <f>+SUM(G115+G103-G76)</f>
+        <v>100</v>
+      </c>
+      <c r="H116" s="102"/>
+      <c r="I116" s="101">
+        <f>+SUM(I115+I103-I76)</f>
+        <v>70</v>
+      </c>
+      <c r="J116" s="102"/>
+      <c r="K116" s="101">
+        <f>+SUM(K115+K103-K76)</f>
+        <v>20</v>
+      </c>
+      <c r="L116" s="102"/>
+      <c r="M116" s="101">
+        <f>+SUM(M115+M103-M76)</f>
+        <v>10</v>
+      </c>
+      <c r="N116" s="102"/>
+      <c r="O116" s="1"/>
+      <c r="P116" s="1"/>
+      <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+      <c r="S116" s="1"/>
+      <c r="T116" s="1"/>
+      <c r="U116" s="1"/>
+      <c r="V116" s="1"/>
+      <c r="W116" s="1"/>
+    </row>
+    <row r="118" spans="6:23">
+      <c r="F118" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="G118" s="105"/>
+      <c r="H118" s="105"/>
+      <c r="I118" s="105"/>
+      <c r="J118" s="105"/>
+      <c r="K118" s="105"/>
+      <c r="L118" s="105"/>
+      <c r="M118" s="105"/>
+      <c r="N118" s="105"/>
+      <c r="O118" s="1"/>
+      <c r="P118" s="1"/>
+      <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+      <c r="S118" s="1"/>
+      <c r="T118" s="1"/>
+      <c r="U118" s="1"/>
+      <c r="V118" s="1"/>
+      <c r="W118" s="1"/>
+    </row>
+    <row r="119" spans="6:23">
       <c r="F119" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>4</v>
@@ -9016,20 +9309,35 @@
       <c r="N119" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O119" s="1"/>
+      <c r="P119" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+      <c r="S119" s="1"/>
+      <c r="T119" s="1"/>
+      <c r="U119" s="1"/>
+      <c r="V119" s="1"/>
+      <c r="W119" s="1"/>
+    </row>
+    <row r="120" spans="6:23">
       <c r="F120" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G120" s="9"/>
-      <c r="H120" s="6" t="str">
-        <f>+IF(G120=1,$B$2,IF($G120=2,$B$3,IF($G120=3,$B$4,IF($G120=4,$B$5,""))))</f>
-        <v/>
-      </c>
-      <c r="I120" s="9"/>
-      <c r="J120" s="6" t="str">
-        <f>+IF(I120=1,$B$2,IF($I120=2,$B$3,IF($I120=3,$B$4,IF($I120=4,$B$5,""))))</f>
-        <v/>
+      <c r="G120" s="9">
+        <v>3</v>
+      </c>
+      <c r="H120" s="6">
+        <f>+IF(G120=1,$P$128,IF($G120=2,$P$129,IF($G120=3,$B$4,IF($G120=4,$B$5,""))))</f>
+        <v>15</v>
+      </c>
+      <c r="I120" s="9">
+        <v>1</v>
+      </c>
+      <c r="J120" s="6">
+        <f>+IF(I120=1,$P$128,IF($G120=2,$P$129,IF($G120=3,$B$4,IF($G120=4,$B$5,""))))</f>
+        <v>37.5</v>
       </c>
       <c r="K120" s="9"/>
       <c r="L120" s="6" t="str">
@@ -9041,20 +9349,33 @@
         <f>+IF(M120=1,$B$2,IF($M120=2,$B$3,IF($M120=3,$B$4,IF($M120=4,$B$5,""))))</f>
         <v/>
       </c>
-    </row>
-    <row r="121" spans="6:14">
+      <c r="O120" s="1"/>
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="U120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+    </row>
+    <row r="121" spans="6:23">
       <c r="F121" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G121" s="10"/>
-      <c r="H121" s="5" t="str">
-        <f>+IF(G121=1,$D$2,IF($G121=2,$D$3,IF($G121=3,$D$4,IF($G121=4,$D$5,""))))</f>
-        <v/>
-      </c>
-      <c r="I121" s="10"/>
-      <c r="J121" s="5" t="str">
-        <f>+IF(I121=1,$D$2,IF($I121=2,$D$3,IF($I121=3,$D$4,IF($I121=4,$D$5,""))))</f>
-        <v/>
+      <c r="G121" s="10">
+        <v>3</v>
+      </c>
+      <c r="H121" s="6">
+        <f>+IF(G121=1,$Q$128,IF($G121=2,$Q$129,IF($G121=3,$B$4,IF($G121=4,$B$5,""))))</f>
+        <v>15</v>
+      </c>
+      <c r="I121" s="10">
+        <v>2</v>
+      </c>
+      <c r="J121" s="6">
+        <f>+IF(I121=1,$Q$128,IF($I121=2,$Q$129,IF($G121=3,$B$4,IF($G121=4,$B$5,""))))</f>
+        <v>20.25</v>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="5" t="str">
@@ -9066,8 +9387,17 @@
         <f>+IF(M121=1,$D$2,IF($M121=2,$D$3,IF($M121=3,$D$4,IF($M121=4,$D$5,""))))</f>
         <v/>
       </c>
-    </row>
-    <row r="122" spans="6:14">
+      <c r="O121" s="1"/>
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1"/>
+      <c r="T121" s="1"/>
+      <c r="U121" s="1"/>
+      <c r="V121" s="1"/>
+      <c r="W121" s="1"/>
+    </row>
+    <row r="122" spans="6:23">
       <c r="F122" s="11" t="s">
         <v>13</v>
       </c>
@@ -9079,8 +9409,17 @@
       <c r="L122" s="5"/>
       <c r="M122" s="10"/>
       <c r="N122" s="5"/>
-    </row>
-    <row r="123" spans="6:14">
+      <c r="O122" s="1"/>
+      <c r="P122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+      <c r="S122" s="1"/>
+      <c r="T122" s="1"/>
+      <c r="U122" s="1"/>
+      <c r="V122" s="1"/>
+      <c r="W122" s="1"/>
+    </row>
+    <row r="123" spans="6:23">
       <c r="F123" s="11" t="s">
         <v>14</v>
       </c>
@@ -9092,8 +9431,17 @@
       <c r="L123" s="5"/>
       <c r="M123" s="10"/>
       <c r="N123" s="5"/>
-    </row>
-    <row r="124" spans="6:14">
+      <c r="O123" s="1"/>
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
+      <c r="T123" s="1"/>
+      <c r="U123" s="1"/>
+      <c r="V123" s="1"/>
+      <c r="W123" s="1"/>
+    </row>
+    <row r="124" spans="6:23">
       <c r="F124" s="11" t="s">
         <v>16</v>
       </c>
@@ -9105,33 +9453,57 @@
       <c r="L124" s="5"/>
       <c r="M124" s="10"/>
       <c r="N124" s="5"/>
-    </row>
-    <row r="125" spans="6:14" ht="15.75" thickBot="1">
+      <c r="O124" s="1"/>
+      <c r="P124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="1"/>
+      <c r="T124" s="1"/>
+      <c r="U124" s="1"/>
+      <c r="V124" s="1"/>
+      <c r="W124" s="1"/>
+    </row>
+    <row r="125" spans="6:23" ht="15.75" customHeight="1">
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="107"/>
-      <c r="H125" s="108">
+      <c r="G125" s="106">
+        <f>+SUM(H120:H121)</f>
+        <v>30</v>
+      </c>
+      <c r="H125" s="107">
         <f>+SUM(H120:H124)</f>
-        <v>0</v>
-      </c>
-      <c r="I125" s="107"/>
-      <c r="J125" s="108">
+        <v>30</v>
+      </c>
+      <c r="I125" s="106">
+        <f>+SUM(J120:J121)</f>
+        <v>57.75</v>
+      </c>
+      <c r="J125" s="107">
         <f>+SUM(J120:J124)</f>
-        <v>0</v>
-      </c>
-      <c r="K125" s="107"/>
-      <c r="L125" s="108">
+        <v>57.75</v>
+      </c>
+      <c r="K125" s="106"/>
+      <c r="L125" s="107">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="107"/>
-      <c r="N125" s="108">
+      <c r="M125" s="106"/>
+      <c r="N125" s="107">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="6:14" ht="15.75" thickTop="1">
+      <c r="O125" s="1"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
+      <c r="V125" s="1"/>
+      <c r="W125" s="1"/>
+    </row>
+    <row r="126" spans="6:23">
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
@@ -9141,182 +9513,186 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
-    </row>
-    <row r="127" spans="6:14">
+      <c r="O126" s="1"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
+      <c r="T126" s="1"/>
+      <c r="U126" s="1"/>
+      <c r="V126" s="1"/>
+      <c r="W126" s="1"/>
+    </row>
+    <row r="127" spans="6:23">
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="105">
-        <f>H125</f>
-        <v>0</v>
-      </c>
-      <c r="H127" s="106"/>
-      <c r="I127" s="105">
-        <f>J125</f>
-        <v>0</v>
-      </c>
-      <c r="J127" s="106"/>
-      <c r="K127" s="105">
+      <c r="G127" s="103">
+        <f>+SUM(G125,G114)</f>
+        <v>364.25</v>
+      </c>
+      <c r="H127" s="104"/>
+      <c r="I127" s="103">
+        <f>+SUM(I125,I114)</f>
+        <v>360</v>
+      </c>
+      <c r="J127" s="104"/>
+      <c r="K127" s="103">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="106"/>
-      <c r="M127" s="105">
+      <c r="L127" s="104"/>
+      <c r="M127" s="103">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="106"/>
-    </row>
-    <row r="128" spans="6:14">
+      <c r="N127" s="104"/>
+      <c r="O127" s="1"/>
+      <c r="P127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R127" s="1"/>
+      <c r="S127" s="1"/>
+      <c r="T127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U127" s="1"/>
+      <c r="V127" s="1"/>
+      <c r="W127" s="1"/>
+    </row>
+    <row r="128" spans="6:23">
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="102" t="str">
+      <c r="G128" s="101">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="H128" s="103"/>
-      <c r="I128" s="102" t="str">
+        <v>10</v>
+      </c>
+      <c r="H128" s="102"/>
+      <c r="I128" s="101">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
-        <v/>
-      </c>
-      <c r="J128" s="103"/>
-      <c r="K128" s="105"/>
-      <c r="L128" s="106"/>
-      <c r="M128" s="105"/>
-      <c r="N128" s="106"/>
-    </row>
-    <row r="129" spans="6:14">
+        <v>40</v>
+      </c>
+      <c r="J128" s="102"/>
+      <c r="K128" s="103"/>
+      <c r="L128" s="104"/>
+      <c r="M128" s="103"/>
+      <c r="N128" s="104"/>
+      <c r="O128" s="1"/>
+      <c r="P128" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>27</v>
+      </c>
+      <c r="R128" s="1"/>
+      <c r="S128" s="1"/>
+      <c r="T128" s="1">
+        <v>28.13</v>
+      </c>
+      <c r="U128" s="1"/>
+      <c r="V128" s="1"/>
+      <c r="W128" s="1">
+        <f>+SUM(P128-T128)</f>
+        <v>9.370000000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="6:23">
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="102" t="e">
-        <f>+SUM(G128+G116-G89)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H129" s="103"/>
-      <c r="I129" s="102" t="e">
-        <f>+SUM(I128+I116-I89)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J129" s="103"/>
-      <c r="K129" s="105" t="str">
-        <f>+IF($K120=1,"40Kg",IF($K120=2,"20Kg",IF($K120=3,"10Kg",IF($K120=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="L129" s="106"/>
-      <c r="M129" s="105" t="str">
-        <f>+IF($M120=1,"40Kg",IF($M120=2,"20Kg",IF($M120=3,"10Kg",IF($M120=4,"0Kg",""))))</f>
-        <v/>
-      </c>
-      <c r="N129" s="106"/>
+      <c r="G129" s="101">
+        <f>G116</f>
+        <v>100</v>
+      </c>
+      <c r="H129" s="102"/>
+      <c r="I129" s="101">
+        <f t="shared" ref="I129:N129" si="19">I116</f>
+        <v>70</v>
+      </c>
+      <c r="J129" s="102"/>
+      <c r="K129" s="101">
+        <f t="shared" ref="K129:N129" si="20">K116</f>
+        <v>20</v>
+      </c>
+      <c r="L129" s="102"/>
+      <c r="M129" s="101">
+        <f t="shared" ref="M129:N129" si="21">M116</f>
+        <v>10</v>
+      </c>
+      <c r="N129" s="102"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1">
+        <v>28.125</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>20.25</v>
+      </c>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1">
+        <v>20.25</v>
+      </c>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1">
+        <f>+SUM(P129-T129)</f>
+        <v>7.875</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="176">
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="R2:Z2"/>
+    <mergeCell ref="R6:Z6"/>
+    <mergeCell ref="R9:Z9"/>
+    <mergeCell ref="R12:Z12"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="F66:N66"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="I11:J11"/>
@@ -9341,54 +9717,110 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="R2:Z2"/>
-    <mergeCell ref="R6:Z6"/>
-    <mergeCell ref="R9:Z9"/>
-    <mergeCell ref="R12:Z12"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="F66:N66"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9411,13 +9843,13 @@
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="A1" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -9425,23 +9857,23 @@
       <c r="G1" s="29"/>
       <c r="H1" s="34"/>
       <c r="I1" s="35" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L1" s="29"/>
       <c r="M1" s="50" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N1" s="51" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O1" s="52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
@@ -9458,12 +9890,12 @@
         <v>4</v>
       </c>
       <c r="B2" s="17">
-        <f>+SUM(Hoja1!$G8,Hoja1!$G21,Hoja1!$G34,Hoja1!$G47,Hoja1!$G60,Hoja1!G73,Hoja1!G86,Hoja1!G99)</f>
-        <v>287.5</v>
+        <f>+SUM(Hoja1!$G8,Hoja1!$G21,Hoja1!$G34,Hoja1!$G47,Hoja1!$G60,Hoja1!G73,Hoja1!G86,Hoja1!G99,Hoja1!G112)</f>
+        <v>334.25</v>
       </c>
       <c r="C2" s="25">
         <f>INDEX(Hoja1!$G$1:$G$250, (COUNTIF(DATOS!$J$4:$S$4, "&gt;0")-1)*13 + 12)</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1">
         <f>_xlfn.RANK.EQ(B2, $B$2:$B$5) + COUNTIF($B$2:B2, B2) - 1</f>
@@ -9484,11 +9916,11 @@
       </c>
       <c r="J2" s="31">
         <f>INDEX($B$2:$B$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>287.5</v>
+        <v>334.25</v>
       </c>
       <c r="K2" s="43">
         <f>INDEX($C$2:$C$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L2" s="29"/>
       <c r="M2" s="47">
@@ -9497,7 +9929,7 @@
       </c>
       <c r="N2" s="48">
         <f>J2 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.76871657754010692</v>
+        <v>0.89371657754010692</v>
       </c>
       <c r="O2" s="49">
         <f>SUM(DATOS!D27:D46)</f>
@@ -9518,12 +9950,12 @@
         <v>6</v>
       </c>
       <c r="B3" s="21">
-        <f>+SUM(Hoja1!$I8,Hoja1!$I21,Hoja1!$I34,Hoja1!$I47,Hoja1!$I60,Hoja1!I73,Hoja1!I86,Hoja1!I99)</f>
-        <v>287.25</v>
+        <f>+SUM(Hoja1!$I8,Hoja1!$I21,Hoja1!$I34,Hoja1!$I47,Hoja1!$I60,Hoja1!I73,Hoja1!I86,Hoja1!I99,Hoja1!I112)</f>
+        <v>302.25</v>
       </c>
       <c r="C3" s="25">
         <f>INDEX(Hoja1!$I$1:$I$250, (COUNTIF(DATOS!$J$5:$S$5, "&gt;0")-1)*13 + 12)</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D3" s="1">
         <f>_xlfn.RANK.EQ(B3, $B$2:$B$5) + COUNTIF($B$2:B3, B3) - 1</f>
@@ -9544,11 +9976,11 @@
       </c>
       <c r="J3" s="31">
         <f t="shared" ref="J3:J5" si="1">INDEX($B$2:$B$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>287.25</v>
+        <v>302.25</v>
       </c>
       <c r="K3" s="43">
         <f t="shared" ref="K3:K5" si="2">INDEX($C$2:$C$5, MATCH(H3, $D$2:$D$5, 0))</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L3" s="29"/>
       <c r="M3" s="45">
@@ -9557,11 +9989,11 @@
       </c>
       <c r="N3" s="39">
         <f>J3 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.76804812834224601</v>
+        <v>0.8081550802139037</v>
       </c>
       <c r="O3" s="41">
         <f>+SUM(DATOS!C27:C46)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="29"/>
       <c r="Q3" s="29"/>
@@ -9578,12 +10010,12 @@
         <v>7</v>
       </c>
       <c r="B4" s="21">
-        <f>+SUM(Hoja1!K8,Hoja1!K21,Hoja1!K34,Hoja1!K47,Hoja1!K60,Hoja1!K73,Hoja1!K86,Hoja1!K99)</f>
-        <v>193.75</v>
+        <f>+SUM(Hoja1!K8,Hoja1!K21,Hoja1!K34,Hoja1!K47,Hoja1!K60,Hoja1!K73,Hoja1!K86,Hoja1!K99,,Hoja1!K112)</f>
+        <v>208.75</v>
       </c>
       <c r="C4" s="25">
         <f>INDEX(Hoja1!$K$1:$K$250, (COUNTIF(DATOS!$J$6:$S$6, "&gt;0")-1)*13 + 12)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1">
         <f>_xlfn.RANK.EQ(B4, $B$2:$B$5) + COUNTIF($B$2:B4, B4) - 1</f>
@@ -9591,7 +10023,7 @@
       </c>
       <c r="E4" s="1">
         <f>+AVERAGEIF(DATOS!E$3:E$22, "&gt;0")</f>
-        <v>3.5</v>
+        <v>3.4375</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="29"/>
@@ -9604,20 +10036,20 @@
       </c>
       <c r="J4" s="31">
         <f t="shared" si="1"/>
-        <v>235.5</v>
+        <v>247.5</v>
       </c>
       <c r="K4" s="43">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I4, $A$2:$A$5, 0))</f>
-        <v>2.6875</v>
+        <v>2.75</v>
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.6296791443850267</v>
+        <v>0.66176470588235292</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -9638,12 +10070,12 @@
         <v>8</v>
       </c>
       <c r="B5" s="20">
-        <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86,Hoja1!M99)</f>
-        <v>235.5</v>
+        <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86,Hoja1!M99,,Hoja1!M112)</f>
+        <v>247.5</v>
       </c>
       <c r="C5" s="26">
         <f>INDEX(Hoja1!$M$1:$M$250, (COUNTIF(DATOS!$J$7:$S$7, "&gt;0")-1)*13 + 12)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1">
         <f>_xlfn.RANK.EQ(B5, $B$2:$B$5) + COUNTIF($B$2:B5, B5) - 1</f>
@@ -9651,7 +10083,7 @@
       </c>
       <c r="E5" s="1">
         <f>+AVERAGEIF(DATOS!F$3:F$22, "&gt;0")</f>
-        <v>2.6875</v>
+        <v>2.75</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="29"/>
@@ -9664,20 +10096,20 @@
       </c>
       <c r="J5" s="33">
         <f t="shared" si="1"/>
-        <v>193.75</v>
+        <v>208.75</v>
       </c>
       <c r="K5" s="44">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" s="29"/>
       <c r="M5" s="46">
         <f>INDEX($E$2:$E$5, MATCH(I5, $A$2:$A$5, 0))</f>
-        <v>3.5</v>
+        <v>3.4375</v>
       </c>
       <c r="N5" s="40">
         <f>J5 / (COUNTIFS(DATOS!F3:F22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.51804812834224601</v>
+        <v>0.5581550802139037</v>
       </c>
       <c r="O5" s="42">
         <f>+SUM(DATOS!F27:F46)</f>
@@ -9734,7 +10166,7 @@
       <c r="L7" s="29"/>
       <c r="M7" s="29"/>
       <c r="N7" s="29" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O7" s="29"/>
       <c r="P7" s="29"/>
@@ -10363,7 +10795,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="112" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -10377,21 +10809,21 @@
       <c r="S1" s="112"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="110" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="110"/>
+      <c r="A2" s="108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="108"/>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -10408,11 +10840,11 @@
       <c r="S2" s="112"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="111" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1">
         <f>Hoja1!G3</f>
@@ -10434,40 +10866,40 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="101"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1">
         <f>Hoja1!G4</f>
@@ -10488,7 +10920,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10522,21 +10954,21 @@
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(H1)-1)*13 + 10))</f>
         <v>287.5</v>
       </c>
-      <c r="R4" s="1" t="e">
+      <c r="R4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S4" s="1" t="e">
+        <v>334.25</v>
+      </c>
+      <c r="S4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>364.25</v>
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="111" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1">
         <f>Hoja1!G16</f>
@@ -10557,7 +10989,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10591,19 +11023,19 @@
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(H1)-1)*13 + 10))</f>
         <v>287.25</v>
       </c>
-      <c r="R5" s="1" t="e">
+      <c r="R5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S5" s="1" t="e">
+        <v>302.25</v>
+      </c>
+      <c r="S5" s="1">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(J1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="101"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1">
         <f>Hoja1!G17</f>
@@ -10624,7 +11056,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10652,15 +11084,15 @@
       </c>
       <c r="P6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(G1)-1)*13 + 10))</f>
-        <v>169.75</v>
+        <v>172.75</v>
       </c>
       <c r="Q6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>193.75</v>
-      </c>
-      <c r="R6" s="1" t="e">
+        <v>196.75</v>
+      </c>
+      <c r="R6" s="1">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>208.75</v>
       </c>
       <c r="S6" s="1" t="e">
         <f>IF(INDEX(Hoja1!$K$1:$K$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$K$1:$K$250, (COLUMN(J1)-1)*13 + 10))</f>
@@ -10668,11 +11100,11 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="111" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1">
         <f>Hoja1!G29</f>
@@ -10693,7 +11125,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(A1)-1)*13 + 10))</f>
@@ -10721,15 +11153,15 @@
       </c>
       <c r="P7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(G1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(G1)-1)*13 + 10))</f>
-        <v>212.25</v>
+        <v>209.25</v>
       </c>
       <c r="Q7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(H1)-1)*13 + 10))</f>
-        <v>235.5</v>
-      </c>
-      <c r="R7" s="1" t="e">
+        <v>232.5</v>
+      </c>
+      <c r="R7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>#N/A</v>
+        <v>247.5</v>
       </c>
       <c r="S7" s="1" t="e">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(J1)-1)*13 + 10))</f>
@@ -10737,9 +11169,9 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="101"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1">
         <f>Hoja1!G30</f>
@@ -10772,11 +11204,11 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="111" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1">
         <f>Hoja1!G42</f>
@@ -10809,9 +11241,9 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="101"/>
+      <c r="A10" s="111"/>
       <c r="B10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1">
         <f>Hoja1!G43</f>
@@ -10844,11 +11276,11 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="101" t="s">
-        <v>60</v>
+      <c r="A11" s="111" t="s">
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1">
         <f>Hoja1!G55</f>
@@ -10881,9 +11313,9 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="101"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1">
         <f>Hoja1!G56</f>
@@ -10916,11 +11348,11 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="101" t="s">
-        <v>61</v>
+      <c r="A13" s="111" t="s">
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1">
         <f>Hoja1!G68</f>
@@ -10953,9 +11385,9 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="101"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" s="1">
         <f>Hoja1!G69</f>
@@ -10988,11 +11420,11 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="101" t="s">
-        <v>62</v>
+      <c r="A15" s="111" t="s">
+        <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1">
         <f>Hoja1!G81</f>
@@ -11004,11 +11436,11 @@
       </c>
       <c r="E15" s="1">
         <f>Hoja1!K81</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="1">
         <f>Hoja1!M81</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -11025,9 +11457,9 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="101"/>
+      <c r="A16" s="111"/>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1">
         <f>Hoja1!G82</f>
@@ -11060,11 +11492,11 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="101" t="s">
-        <v>63</v>
+      <c r="A17" s="111" t="s">
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1">
         <f>Hoja1!G94</f>
@@ -11085,9 +11517,9 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="101"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1">
         <f>Hoja1!G95</f>
@@ -11108,9 +11540,9 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="101"/>
+      <c r="A19" s="111"/>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1">
         <f>Hoja1!G109</f>
@@ -11131,9 +11563,9 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="101"/>
+      <c r="A20" s="111"/>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C20" s="1">
         <f>Hoja1!G110</f>
@@ -11154,9 +11586,9 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="101"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <f>Hoja1!G122</f>
@@ -11177,9 +11609,9 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="101"/>
+      <c r="A22" s="111"/>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1">
         <f>Hoja1!G123</f>
@@ -11201,7 +11633,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -11223,352 +11655,352 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="110"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
+      <c r="A25" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="108"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="110" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="110"/>
-      <c r="C26" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="94" t="s">
+      <c r="A26" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="94" t="s">
+      <c r="B26" s="108"/>
+      <c r="C26" s="100" t="s">
         <v>47</v>
       </c>
+      <c r="D26" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="100" t="s">
+        <v>50</v>
+      </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="101" t="s">
+      <c r="A27" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="110">
+      <c r="B27" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="108">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="110">
+      <c r="D27" s="108">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="110">
+      <c r="E27" s="108">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="110">
+      <c r="F27" s="108">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="110"/>
+      <c r="G27" s="108"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="101"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="110">
+      <c r="B29" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="108">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="110">
+      <c r="D29" s="108">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="110">
+      <c r="E29" s="108">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="110">
+      <c r="F29" s="108">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="110"/>
+      <c r="G29" s="108"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="101"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
+      <c r="A30" s="111"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="101" t="s">
+      <c r="A31" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="110">
+      <c r="B31" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="108">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="110">
+      <c r="D31" s="108">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="110">
+      <c r="E31" s="108">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="110">
+      <c r="F31" s="108">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="110"/>
+      <c r="G31" s="108"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="101"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
-      <c r="G32" s="110"/>
+      <c r="A32" s="111"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="101" t="s">
+      <c r="A33" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="110">
+      <c r="B33" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="108">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="110">
+      <c r="D33" s="108">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="110">
+      <c r="E33" s="108">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="110">
+      <c r="F33" s="108">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="110"/>
+      <c r="G33" s="108"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="101"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="110"/>
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="110"/>
-      <c r="G34" s="110"/>
+      <c r="A34" s="111"/>
+      <c r="B34" s="111"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="110">
+      <c r="A35" s="111" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="108">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="110">
+      <c r="D35" s="108">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="110">
+      <c r="E35" s="108">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="110">
+      <c r="F35" s="108">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="110"/>
+      <c r="G35" s="108"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="101"/>
-      <c r="B36" s="101"/>
-      <c r="C36" s="110"/>
-      <c r="D36" s="110"/>
-      <c r="E36" s="110"/>
-      <c r="F36" s="110"/>
-      <c r="G36" s="110"/>
+      <c r="A36" s="111"/>
+      <c r="B36" s="111"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="101" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="110">
+      <c r="A37" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="108">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="110">
+      <c r="D37" s="108">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="110">
+      <c r="E37" s="108">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="110">
+      <c r="F37" s="108">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="110"/>
+      <c r="G37" s="108"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="101"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
+      <c r="A38" s="111"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="101" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="101" t="s">
+      <c r="A39" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="110">
+      <c r="B39" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="108">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="110">
+      <c r="D39" s="108">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="110">
+      <c r="E39" s="108">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="110">
+      <c r="F39" s="108">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="110"/>
+      <c r="G39" s="108"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="101"/>
-      <c r="B40" s="101"/>
-      <c r="C40" s="110"/>
-      <c r="D40" s="110"/>
-      <c r="E40" s="110"/>
-      <c r="F40" s="110"/>
-      <c r="G40" s="110"/>
+      <c r="A40" s="111"/>
+      <c r="B40" s="111"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="101" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="110">
+      <c r="A41" s="111" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="108">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="110">
+      <c r="D41" s="108">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="110">
+      <c r="E41" s="108">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="110">
+      <c r="F41" s="108">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="110"/>
+      <c r="G41" s="108"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="101"/>
-      <c r="B42" s="101"/>
-      <c r="C42" s="110"/>
-      <c r="D42" s="110"/>
-      <c r="E42" s="110"/>
-      <c r="F42" s="110"/>
-      <c r="G42" s="110"/>
+      <c r="A42" s="111"/>
+      <c r="B42" s="111"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="101"/>
-      <c r="B43" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="110">
+      <c r="A43" s="111"/>
+      <c r="B43" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="108">
         <f>Hoja1!H109</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="110"/>
-      <c r="E43" s="110"/>
-      <c r="F43" s="110"/>
-      <c r="G43" s="110"/>
+        <v>1</v>
+      </c>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="101"/>
-      <c r="B44" s="101"/>
-      <c r="C44" s="110"/>
-      <c r="D44" s="110"/>
-      <c r="E44" s="110"/>
-      <c r="F44" s="110"/>
-      <c r="G44" s="110"/>
+      <c r="A44" s="111"/>
+      <c r="B44" s="111"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="101"/>
-      <c r="B45" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="110">
+      <c r="A45" s="111"/>
+      <c r="B45" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="108">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="110"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="110"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="101"/>
-      <c r="B46" s="101"/>
-      <c r="C46" s="110"/>
-      <c r="D46" s="110"/>
-      <c r="E46" s="110"/>
-      <c r="F46" s="110"/>
-      <c r="G46" s="110"/>
+      <c r="A46" s="111"/>
+      <c r="B46" s="111"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -11577,7 +12009,7 @@
       <c r="B47" s="1"/>
       <c r="C47" s="1">
         <f>+SUM(C27:C46)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" ref="D47:F47" si="1">+SUM(D27:D46)</f>
@@ -11595,12 +12027,68 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
@@ -11617,68 +12105,12 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11695,25 +12127,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -12182,7 +12614,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="57" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
@@ -12210,7 +12642,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="57" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -12238,7 +12670,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="57" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -12266,7 +12698,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="57" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -12294,7 +12726,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>4</v>
@@ -12322,7 +12754,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -12350,7 +12782,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -12378,7 +12810,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
@@ -12406,7 +12838,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>4</v>
@@ -12434,7 +12866,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -12462,7 +12894,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -12481,7 +12913,7 @@
       </c>
       <c r="F28" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A27)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A27)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A27)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A27)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A27)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A27)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A27)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A27)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -12490,7 +12922,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
@@ -12509,7 +12941,7 @@
       </c>
       <c r="F29" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A28)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A28)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A28)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A28)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A28)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A28)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A28)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A28)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -12518,7 +12950,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
@@ -12546,7 +12978,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
@@ -12574,7 +13006,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -12602,7 +13034,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
@@ -12629,33 +13061,37 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="110"/>
+      <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="B34" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C34" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A33)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 6, CHOOSE(MOD(ROW(A33)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A33)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G34" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="110"/>
+      <c r="A35" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
@@ -12671,9 +13107,9 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A34)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F35" s="1" t="str">
+      <c r="F35" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A34)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A34)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G35" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A34)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A34)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -12681,7 +13117,9 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="110"/>
+      <c r="A36" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
@@ -12697,9 +13135,9 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A35)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F36" s="1" t="str">
+      <c r="F36" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A35)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A35)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G36" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A35)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A35)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -12707,7 +13145,9 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="110"/>
+      <c r="A37" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
@@ -12723,9 +13163,9 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A36)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F37" s="1" t="str">
+      <c r="F37" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G37" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -12733,7 +13173,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="110"/>
+      <c r="A38" s="108"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -12749,17 +13189,17 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A37)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="1" t="str">
+      <c r="F38" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G38" s="1" t="str">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="110"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -12775,17 +13215,17 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A38)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="1" t="str">
+      <c r="F39" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
-      </c>
-      <c r="G39" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="110"/>
+      <c r="A40" s="108"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -12811,7 +13251,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="110"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -12837,8 +13277,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A34:A37"/>
+  <mergeCells count="1">
     <mergeCell ref="A38:A41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12860,10 +13299,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="53" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -12872,22 +13311,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="94" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="94" t="s">
         <v>74</v>
       </c>
+      <c r="B3" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="100" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="100" t="s">
+        <v>78</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -13009,11 +13448,11 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="111" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" s="58">
         <v>1.0631828703703704E-3</v>
@@ -13032,9 +13471,9 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="101"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3" s="58">
         <v>1.0327314814814815E-3</v>
@@ -13055,9 +13494,9 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="101"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4" s="58">
         <v>1.0267824074074075E-3</v>
@@ -13078,11 +13517,11 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="111" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
@@ -13095,9 +13534,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="101"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -13110,9 +13549,9 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="101"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
@@ -13125,11 +13564,11 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="111" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -13142,9 +13581,9 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="101"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" s="58"/>
       <c r="D9" s="58"/>
@@ -13157,9 +13596,9 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="101"/>
+      <c r="A10" s="111"/>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C10" s="58">
         <v>8.9045138888888887E-4</v>
@@ -13180,11 +13619,11 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="111" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" s="58">
         <v>8.6745370370370383E-4</v>
@@ -13205,9 +13644,9 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="101"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -13220,9 +13659,9 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="101"/>
+      <c r="A13" s="111"/>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -13235,11 +13674,11 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="101" t="s">
-        <v>60</v>
+      <c r="A14" s="111" t="s">
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" s="58">
         <v>8.2178240740740736E-4</v>
@@ -13256,7 +13695,7 @@
       <c r="G14" s="58"/>
       <c r="H14" s="1" cm="1">
         <f t="array" ref="H14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>1.0041454475308643E-3</v>
+        <v>1.0306134259259259E-3</v>
       </c>
       <c r="I14" s="1" cm="1">
         <f t="array" ref="I14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
@@ -13264,17 +13703,17 @@
       </c>
       <c r="J14" s="1">
         <f t="array" ref="J14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(E$2:E$46&gt;0),E$2:E$46)),0)</f>
-        <v>1.0265000000000001E-3</v>
+        <v>1.0664583333333333E-3</v>
       </c>
       <c r="K14" s="1">
         <f t="array" ref="K14">IFERROR(AVERAGE(IF(($B$2:$B$46="Clasificacion")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>1.0336226851851852E-3</v>
+        <v>1.0595072751322751E-3</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="101"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" s="58">
         <v>8.1365740740740736E-4</v>
@@ -13289,11 +13728,11 @@
       <c r="G15" s="58"/>
       <c r="H15" s="1" cm="1">
         <f t="array" ref="H15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>1.001556712962963E-3</v>
+        <v>1.0206041666666666E-3</v>
       </c>
       <c r="I15" s="1" cm="1">
         <f t="array" ref="I15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
-        <v>1.004369212962963E-3</v>
+        <v>1.0254629629629628E-3</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ref="J15" si="0">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(E$2:E$46&gt;0),E$2:E$46)),0)</f>
@@ -13301,13 +13740,13 @@
       </c>
       <c r="K15" s="1" cm="1">
         <f t="array" ref="K15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>1.0111313657407406E-3</v>
+        <v>1.035150462962963E-3</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="101"/>
+      <c r="A16" s="111"/>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" s="58">
         <v>8.0902777777777787E-4</v>
@@ -13322,11 +13761,11 @@
       <c r="G16" s="58"/>
       <c r="H16" s="1">
         <f t="array" ref="H16">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 2")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>9.7803240740740728E-4</v>
+        <v>1.0007484567901234E-3</v>
       </c>
       <c r="I16" s="1">
         <f t="array" ref="I16">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 2")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
-        <v>9.7885416666666672E-4</v>
+        <v>9.983506944444445E-4</v>
       </c>
       <c r="J16" s="1">
         <f>IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 2")*(E$2:E$46&gt;0),E$2:E$46)),0)</f>
@@ -13334,15 +13773,15 @@
       </c>
       <c r="K16" s="1" cm="1">
         <f t="array" ref="K16">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 2")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>9.8515740740740747E-4</v>
+        <v>1.0082754629629632E-3</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="101" t="s">
-        <v>61</v>
+      <c r="A17" s="111" t="s">
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C17" s="58">
         <v>9.2799768518518524E-4</v>
@@ -13368,9 +13807,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="101"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" s="58">
         <v>9.2737268518518516E-4</v>
@@ -13396,9 +13835,9 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="101"/>
+      <c r="A19" s="111"/>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19" s="58">
         <v>9.2612268518518521E-4</v>
@@ -13424,11 +13863,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="101" t="s">
-        <v>62</v>
+      <c r="A20" s="111" t="s">
+        <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20" s="58">
         <v>1.2464004629629628E-3</v>
@@ -13454,9 +13893,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="101"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21" s="58">
         <v>1.2324652777777779E-3</v>
@@ -13480,9 +13919,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="101"/>
+      <c r="A22" s="111"/>
       <c r="B22" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22" s="58">
         <v>1.2377777777777777E-3</v>
@@ -13506,11 +13945,11 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="101" t="s">
-        <v>63</v>
+      <c r="A23" s="111" t="s">
+        <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" s="58">
         <v>1.0980555555555555E-3</v>
@@ -13536,14 +13975,22 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="101"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
+        <v>81</v>
+      </c>
+      <c r="C24" s="122">
+        <v>1.0967939814814816E-3</v>
+      </c>
+      <c r="D24" s="122">
+        <v>1.1098379629629629E-3</v>
+      </c>
+      <c r="E24" s="122">
+        <v>1.1312268518518518E-3</v>
+      </c>
+      <c r="F24" s="122">
+        <v>1.1312268518518518E-3</v>
+      </c>
       <c r="G24" s="58"/>
       <c r="H24" s="58"/>
       <c r="I24" s="58"/>
@@ -13556,14 +14003,22 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="101"/>
+      <c r="A25" s="111"/>
       <c r="B25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
+        <v>82</v>
+      </c>
+      <c r="C25" s="58">
+        <v>1.1143287037037035E-3</v>
+      </c>
+      <c r="D25" s="58">
+        <v>1.0958333333333334E-3</v>
+      </c>
+      <c r="E25" s="58">
+        <v>1.1238657407407408E-3</v>
+      </c>
+      <c r="F25" s="58">
+        <v>1.1238657407407408E-3</v>
+      </c>
       <c r="G25" s="58"/>
       <c r="H25" s="58"/>
       <c r="I25" s="58"/>
@@ -13576,14 +14031,22 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="58"/>
+      <c r="B26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="58">
+        <v>1.1894212962962963E-3</v>
+      </c>
       <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
+      <c r="E26" s="58">
+        <v>1.26625E-3</v>
+      </c>
+      <c r="F26" s="58">
+        <v>1.2148148148148148E-3</v>
+      </c>
       <c r="G26" s="58"/>
       <c r="H26" s="58"/>
       <c r="I26" s="58"/>
@@ -13596,8 +14059,10 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="101"/>
-      <c r="B27" s="1"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="C27" s="58"/>
       <c r="D27" s="58"/>
       <c r="E27" s="58"/>
@@ -13614,8 +14079,10 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="101"/>
-      <c r="B28" s="1"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="E28" s="58"/>
@@ -13632,8 +14099,8 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="101" t="s">
-        <v>34</v>
+      <c r="A29" s="111" t="s">
+        <v>36</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="58"/>
@@ -13652,7 +14119,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="101"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -13670,7 +14137,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="101"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -13731,7 +14198,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -13752,7 +14219,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" s="69">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -13773,19 +14240,19 @@
       <c r="G2" s="58"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1">
         <f>IF('Carga Tiempos'!H14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!H14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>0</v>
+        <v>2.5206404320987554E-5</v>
       </c>
       <c r="K2" s="1">
         <f>IF('Carga Tiempos'!I14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!I14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>1.261574074074099E-6</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
         <f>IF('Carga Tiempos'!K14=MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14),0,'Carga Tiempos'!K14-MIN('Carga Tiempos'!$H14,'Carga Tiempos'!$I14,'Carga Tiempos'!$K14))</f>
-        <v>2.9477237654320894E-5</v>
+        <v>5.4100253527336779E-5</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -13795,7 +14262,7 @@
     <row r="3" spans="1:16">
       <c r="A3" s="114"/>
       <c r="B3" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3" s="69">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -13816,7 +14283,7 @@
       <c r="G3" s="58"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1">
         <f>IF('Carga Tiempos'!H15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!H15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
@@ -13824,11 +14291,11 @@
       </c>
       <c r="K3" s="58">
         <f>IF('Carga Tiempos'!I15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!I15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>2.8124999999999938E-6</v>
+        <v>4.8587962962962084E-6</v>
       </c>
       <c r="L3" s="1">
         <f>IF('Carga Tiempos'!K15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!K15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>9.5746527777776196E-6</v>
+        <v>1.4546296296296356E-5</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -13838,7 +14305,7 @@
     <row r="4" spans="1:16">
       <c r="A4" s="114"/>
       <c r="B4" s="62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4" s="69">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -13859,19 +14326,19 @@
       <c r="G4" s="58"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J4" s="1">
         <f>IF('Carga Tiempos'!H16=MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16),0,'Carga Tiempos'!H16-MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16))</f>
-        <v>0</v>
+        <v>2.3977623456788912E-6</v>
       </c>
       <c r="K4" s="1">
         <f>IF('Carga Tiempos'!I16=MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16),0,'Carga Tiempos'!I16-MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16))</f>
-        <v>8.217592592594386E-7</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1">
         <f>IF('Carga Tiempos'!K16=MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16),0,'Carga Tiempos'!K16-MIN('Carga Tiempos'!$H16,'Carga Tiempos'!$I16,'Carga Tiempos'!$K16))</f>
-        <v>7.1250000000001867E-6</v>
+        <v>9.9247685185187024E-6</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -13883,7 +14350,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="60"/>
@@ -13903,7 +14370,7 @@
     <row r="6" spans="1:16">
       <c r="A6" s="114"/>
       <c r="B6" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
@@ -13923,7 +14390,7 @@
     <row r="7" spans="1:16">
       <c r="A7" s="115"/>
       <c r="B7" s="66" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="61"/>
@@ -13945,7 +14412,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
@@ -13965,7 +14432,7 @@
     <row r="9" spans="1:16">
       <c r="A9" s="114"/>
       <c r="B9" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="68"/>
@@ -13985,7 +14452,7 @@
     <row r="10" spans="1:16">
       <c r="A10" s="115"/>
       <c r="B10" s="66" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C10" s="71">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -14019,7 +14486,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" s="69">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -14051,7 +14518,7 @@
     <row r="12" spans="1:16">
       <c r="A12" s="114"/>
       <c r="B12" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="68"/>
@@ -14071,7 +14538,7 @@
     <row r="13" spans="1:16">
       <c r="A13" s="114"/>
       <c r="B13" s="62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="68"/>
@@ -14090,10 +14557,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="113" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" s="70">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -14125,7 +14592,7 @@
     <row r="15" spans="1:16">
       <c r="A15" s="114"/>
       <c r="B15" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" s="69">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -14157,7 +14624,7 @@
     <row r="16" spans="1:16">
       <c r="A16" s="115"/>
       <c r="B16" s="66" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" s="71">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -14188,10 +14655,10 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="114" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C17" s="69">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -14223,7 +14690,7 @@
     <row r="18" spans="1:16">
       <c r="A18" s="114"/>
       <c r="B18" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" s="69">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -14255,7 +14722,7 @@
     <row r="19" spans="1:16">
       <c r="A19" s="114"/>
       <c r="B19" s="62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19" s="69">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -14286,10 +14753,10 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="113" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20" s="70">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -14321,7 +14788,7 @@
     <row r="21" spans="1:16">
       <c r="A21" s="114"/>
       <c r="B21" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21" s="69">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -14353,7 +14820,7 @@
     <row r="22" spans="1:16">
       <c r="A22" s="114"/>
       <c r="B22" s="62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22" s="69">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -14384,10 +14851,10 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="113" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" s="70">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
@@ -14419,23 +14886,23 @@
     <row r="24" spans="1:16">
       <c r="A24" s="114"/>
       <c r="B24" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C24" s="69">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
-        <v>0</v>
+        <v>1.0967939814814816E-3</v>
       </c>
       <c r="D24" s="68">
         <f>+IF('Carga Tiempos'!D24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!D24,'Carga Tiempos'!D24-MIN('Carga Tiempos'!$C24:$F24))</f>
-        <v>0</v>
+        <v>1.3043981481481283E-5</v>
       </c>
       <c r="E24" s="63">
         <f>+IF('Carga Tiempos'!E24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!E24,'Carga Tiempos'!E24-MIN('Carga Tiempos'!$C24:$F24))</f>
-        <v>0</v>
+        <v>3.4432870370370216E-5</v>
       </c>
       <c r="F24" s="68">
         <f>+IF('Carga Tiempos'!F24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!F24,'Carga Tiempos'!F24-MIN('Carga Tiempos'!$C24:$F24))</f>
-        <v>0</v>
+        <v>3.4432870370370216E-5</v>
       </c>
       <c r="G24" s="58"/>
       <c r="H24" s="58"/>
@@ -14451,23 +14918,23 @@
     <row r="25" spans="1:16">
       <c r="A25" s="115"/>
       <c r="B25" s="66" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C25" s="71">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
-        <v>0</v>
+        <v>1.8495370370370107E-5</v>
       </c>
       <c r="D25" s="61">
         <f>+IF('Carga Tiempos'!D25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!D25,'Carga Tiempos'!D25-MIN('Carga Tiempos'!$C25:$F25))</f>
-        <v>0</v>
+        <v>1.0958333333333334E-3</v>
       </c>
       <c r="E25" s="67">
         <f>+IF('Carga Tiempos'!E25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!E25,'Carga Tiempos'!E25-MIN('Carga Tiempos'!$C25:$F25))</f>
-        <v>0</v>
+        <v>2.803240740740739E-5</v>
       </c>
       <c r="F25" s="61">
         <f>+IF('Carga Tiempos'!F25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!F25,'Carga Tiempos'!F25-MIN('Carga Tiempos'!$C25:$F25))</f>
-        <v>0</v>
+        <v>2.803240740740739E-5</v>
       </c>
       <c r="G25" s="58"/>
       <c r="H25" s="58"/>
@@ -14482,26 +14949,26 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="114" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C26" s="69">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="69">
+        <v>1.1894212962962963E-3</v>
+      </c>
+      <c r="D26" s="70">
         <f>+IF('Carga Tiempos'!D26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!D26,'Carga Tiempos'!D26-MIN('Carga Tiempos'!$C26:$F26))</f>
-        <v>0</v>
+        <v>-1.1894212962962963E-3</v>
       </c>
       <c r="E26" s="69">
         <f>+IF('Carga Tiempos'!E26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!E26,'Carga Tiempos'!E26-MIN('Carga Tiempos'!$C26:$F26))</f>
-        <v>0</v>
+        <v>7.6828703703703738E-5</v>
       </c>
       <c r="F26" s="68">
         <f>+IF('Carga Tiempos'!F26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!F26,'Carga Tiempos'!F26-MIN('Carga Tiempos'!$C26:$F26))</f>
-        <v>0</v>
+        <v>2.539351851851856E-5</v>
       </c>
       <c r="G26" s="58"/>
       <c r="H26" s="58"/>
@@ -14517,7 +14984,7 @@
     <row r="27" spans="1:16">
       <c r="A27" s="114"/>
       <c r="B27" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -14549,7 +15016,7 @@
     <row r="28" spans="1:16">
       <c r="A28" s="114"/>
       <c r="B28" s="62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C28" s="69">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -14580,10 +15047,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="113" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C29" s="70">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -14615,7 +15082,7 @@
     <row r="30" spans="1:16">
       <c r="A30" s="114"/>
       <c r="B30" s="62" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C30" s="69">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -14647,7 +15114,7 @@
     <row r="31" spans="1:16">
       <c r="A31" s="115"/>
       <c r="B31" s="66" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C31" s="71">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -14752,13 +15219,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34573353-DC88-4E7A-8BA7-3DB24B9880AA}">
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -14769,7 +15237,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
       <c r="K1" s="116" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L1" s="116"/>
       <c r="M1" s="116"/>
@@ -14791,19 +15259,19 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="117" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L2" s="118"/>
       <c r="M2" s="117" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N2" s="118"/>
       <c r="O2" s="117" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P2" s="118"/>
       <c r="Q2" s="117" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R2" s="118"/>
       <c r="S2" s="1"/>
@@ -14829,19 +15297,19 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="M3" s="86" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N3" s="77">
         <v>1.2796759259259259E-3</v>
       </c>
       <c r="O3" s="86" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
       <c r="Q3" s="83" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R3" s="84">
         <v>1.4428356481481482E-3</v>
@@ -14869,19 +15337,19 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N4" s="77">
         <v>1.2429976851851853E-3</v>
       </c>
       <c r="O4" s="83" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="P4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
       <c r="Q4" s="83" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="R4" s="81">
         <v>1.2858101851851852E-3</v>
@@ -14909,19 +15377,19 @@
         <v>1.2545601851851852E-3</v>
       </c>
       <c r="M5" s="87" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N5" s="77">
         <v>1.2377777777777777E-3</v>
       </c>
       <c r="O5" s="87" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
       <c r="Q5" s="83" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="R5" s="81">
         <v>1.2647453703703703E-3</v>
@@ -14949,19 +15417,19 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N6" s="77">
         <v>1.3249884259259259E-3</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="R6" s="81">
         <v>1.2908564814814816E-3</v>
@@ -14989,19 +15457,19 @@
         <v>1.260300925925926E-3</v>
       </c>
       <c r="M7" s="87" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N7" s="77">
         <v>1.2426273148148149E-3</v>
       </c>
       <c r="O7" s="87" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
       <c r="Q7" s="83" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R7" s="81">
         <v>1.2742476851851851E-3</v>
@@ -15029,19 +15497,19 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N8" s="77">
         <v>1.2478472222222222E-3</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="P8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="R8" s="81">
         <v>1.2452199074074073E-3</v>
@@ -15069,19 +15537,19 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N9" s="77">
         <v>1.248275462962963E-3</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
       <c r="Q9" s="83" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="R9" s="81">
         <v>1.2555324074074075E-3</v>
@@ -15109,19 +15577,19 @@
         <v>1.2430787037037037E-3</v>
       </c>
       <c r="M10" s="87" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N10" s="77">
         <v>1.2653240740740741E-3</v>
       </c>
       <c r="O10" s="87" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
       <c r="Q10" s="83" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="R10" s="81">
         <v>1.2631365740740741E-3</v>
@@ -15149,19 +15617,19 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N11" s="77">
         <v>1.6837615740740741E-3</v>
       </c>
       <c r="O11" s="83" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
       <c r="Q11" s="83" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R11" s="81">
         <v>1.4671412037037036E-3</v>
@@ -15189,19 +15657,19 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N12" s="77">
         <v>1.543287037037037E-3</v>
       </c>
       <c r="O12" s="83" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="P12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
       <c r="Q12" s="83" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="R12" s="81">
         <v>1.5160185185185185E-3</v>
@@ -15229,19 +15697,19 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N13" s="77">
         <v>1.9202893518518521E-3</v>
       </c>
       <c r="O13" s="83" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="P13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
       <c r="Q13" s="83" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R13" s="81">
         <v>1.9527199074074074E-3</v>
@@ -15269,19 +15737,19 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N14" s="77">
         <v>1.2480787037037037E-3</v>
       </c>
       <c r="O14" s="83" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
       <c r="Q14" s="83" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="R14" s="81">
         <v>1.2462037037037036E-3</v>
@@ -15309,19 +15777,19 @@
         <v>1.236238425925926E-3</v>
       </c>
       <c r="M15" s="87" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N15" s="77">
         <v>1.241701388888889E-3</v>
       </c>
       <c r="O15" s="87" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
       <c r="Q15" s="83" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R15" s="81">
         <v>1.2494560185185185E-3</v>
@@ -15349,19 +15817,19 @@
         <v>1.2310648148148148E-3</v>
       </c>
       <c r="M16" s="88" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N16" s="77">
         <v>1.2480208333333334E-3</v>
       </c>
       <c r="O16" s="88" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="P16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
       <c r="Q16" s="83" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="R16" s="81">
         <v>1.2403703703703704E-3</v>
@@ -15389,19 +15857,19 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N17" s="80">
         <v>1.2779629629629629E-3</v>
       </c>
       <c r="O17" s="85" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
       <c r="Q17" s="85" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="R17" s="82">
         <v>1.2507638888888889E-3</v>
@@ -15588,7 +16056,7 @@
     </row>
     <row r="25" spans="1:23" ht="34.5">
       <c r="A25" s="116" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B25" s="116"/>
       <c r="C25" s="116"/>
@@ -15600,7 +16068,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="116" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L25" s="116"/>
       <c r="M25" s="116"/>
@@ -15617,37 +16085,37 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="117" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B26" s="118"/>
       <c r="C26" s="117" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26" s="118"/>
       <c r="E26" s="119" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F26" s="120"/>
       <c r="G26" s="117" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H26" s="118"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="117" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L26" s="118"/>
       <c r="M26" s="117" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N26" s="118"/>
       <c r="O26" s="119" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P26" s="120"/>
       <c r="Q26" s="117" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R26" s="118"/>
       <c r="S26" s="1"/>
@@ -15657,54 +16125,54 @@
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="121">
+      <c r="A27" s="123">
         <v>1</v>
       </c>
       <c r="B27" s="122">
         <v>1.1538888888888888E-3</v>
       </c>
-      <c r="C27" s="121">
+      <c r="C27" s="123">
         <v>1</v>
       </c>
       <c r="D27" s="122">
         <v>1.1476041666666666E-3</v>
       </c>
-      <c r="E27" s="121">
+      <c r="E27" s="123">
         <v>1</v>
       </c>
       <c r="F27" s="122">
         <v>1.1644560185185187E-3</v>
       </c>
-      <c r="G27" s="99">
+      <c r="G27" s="97">
         <v>1</v>
       </c>
-      <c r="H27" s="100">
+      <c r="H27" s="98">
         <v>1.1644560185185187E-3</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="123">
+      <c r="K27" s="124">
         <v>1</v>
       </c>
-      <c r="L27" s="124">
+      <c r="L27" s="125">
         <v>1.4355671296296297E-3</v>
       </c>
-      <c r="M27" s="123">
+      <c r="M27" s="124">
         <v>1</v>
       </c>
-      <c r="N27" s="124">
+      <c r="N27" s="125">
         <v>1.4123148148148148E-3</v>
       </c>
-      <c r="O27" s="95">
+      <c r="O27" s="93">
         <v>1</v>
       </c>
-      <c r="P27" s="96">
+      <c r="P27" s="94">
         <v>1.4081597222222223E-3</v>
       </c>
-      <c r="Q27" s="123">
+      <c r="Q27" s="124">
         <v>1</v>
       </c>
-      <c r="R27" s="124">
+      <c r="R27" s="125">
         <v>1.4081597222222223E-3</v>
       </c>
       <c r="S27" s="92"/>
@@ -15714,54 +16182,54 @@
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="121">
+      <c r="A28" s="123">
         <v>2</v>
       </c>
       <c r="B28" s="122">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="C28" s="121">
+      <c r="C28" s="123">
         <v>2</v>
       </c>
       <c r="D28" s="122">
         <v>1.1111458333333333E-3</v>
       </c>
-      <c r="E28" s="121">
+      <c r="E28" s="123">
         <v>2</v>
       </c>
       <c r="F28" s="122">
         <v>1.1378703703703703E-3</v>
       </c>
-      <c r="G28" s="99">
+      <c r="G28" s="97">
         <v>2</v>
       </c>
-      <c r="H28" s="100">
+      <c r="H28" s="98">
         <v>1.1378703703703703E-3</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="123">
+      <c r="K28" s="124">
         <v>2</v>
       </c>
-      <c r="L28" s="124">
+      <c r="L28" s="125">
         <v>1.1143287037037035E-3</v>
       </c>
-      <c r="M28" s="123">
+      <c r="M28" s="124">
         <v>2</v>
       </c>
-      <c r="N28" s="124">
+      <c r="N28" s="125">
         <v>1.1365393518518519E-3</v>
       </c>
-      <c r="O28" s="95">
+      <c r="O28" s="93">
         <v>2</v>
       </c>
-      <c r="P28" s="96">
+      <c r="P28" s="94">
         <v>1.1394212962962964E-3</v>
       </c>
-      <c r="Q28" s="123">
+      <c r="Q28" s="124">
         <v>2</v>
       </c>
-      <c r="R28" s="124">
+      <c r="R28" s="125">
         <v>1.1394212962962964E-3</v>
       </c>
       <c r="S28" s="1"/>
@@ -15771,54 +16239,54 @@
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="121">
+      <c r="A29" s="123">
         <v>3</v>
       </c>
       <c r="B29" s="122">
         <v>1.110173611111111E-3</v>
       </c>
-      <c r="C29" s="121">
+      <c r="C29" s="123">
         <v>3</v>
       </c>
       <c r="D29" s="122">
         <v>1.0993171296296296E-3</v>
       </c>
-      <c r="E29" s="121">
+      <c r="E29" s="123">
         <v>3</v>
       </c>
       <c r="F29" s="122">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="G29" s="99">
+      <c r="G29" s="97">
         <v>3</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="98">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="123">
+      <c r="K29" s="124">
         <v>3</v>
       </c>
-      <c r="L29" s="124">
+      <c r="L29" s="125">
         <v>1.1773726851851852E-3</v>
       </c>
-      <c r="M29" s="123">
+      <c r="M29" s="124">
         <v>3</v>
       </c>
-      <c r="N29" s="124">
+      <c r="N29" s="125">
         <v>1.1328703703703702E-3</v>
       </c>
-      <c r="O29" s="95">
+      <c r="O29" s="93">
         <v>3</v>
       </c>
-      <c r="P29" s="96">
+      <c r="P29" s="94">
         <v>1.1317361111111111E-3</v>
       </c>
-      <c r="Q29" s="123">
+      <c r="Q29" s="124">
         <v>3</v>
       </c>
-      <c r="R29" s="124">
+      <c r="R29" s="125">
         <v>1.1317361111111111E-3</v>
       </c>
       <c r="S29" s="1"/>
@@ -15828,54 +16296,54 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="121">
+      <c r="A30" s="123">
         <v>4</v>
       </c>
       <c r="B30" s="122">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="C30" s="121">
+      <c r="C30" s="123">
         <v>4</v>
       </c>
       <c r="D30" s="122">
         <v>1.0976736111111111E-3</v>
       </c>
-      <c r="E30" s="121">
+      <c r="E30" s="123">
         <v>4</v>
       </c>
       <c r="F30" s="122">
         <v>1.1532986111111112E-3</v>
       </c>
-      <c r="G30" s="99">
+      <c r="G30" s="97">
         <v>4</v>
       </c>
-      <c r="H30" s="100">
+      <c r="H30" s="98">
         <v>1.1532986111111112E-3</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="123">
+      <c r="K30" s="124">
         <v>4</v>
       </c>
-      <c r="L30" s="124">
+      <c r="L30" s="125">
         <v>1.1155787037037037E-3</v>
       </c>
-      <c r="M30" s="123">
+      <c r="M30" s="124">
         <v>4</v>
       </c>
-      <c r="N30" s="124">
+      <c r="N30" s="125">
         <v>1.1118055555555556E-3</v>
       </c>
-      <c r="O30" s="95">
+      <c r="O30" s="93">
         <v>4</v>
       </c>
-      <c r="P30" s="96">
+      <c r="P30" s="94">
         <v>2.0264583333333337E-3</v>
       </c>
-      <c r="Q30" s="123">
+      <c r="Q30" s="124">
         <v>4</v>
       </c>
-      <c r="R30" s="124">
+      <c r="R30" s="125">
         <v>2.0264583333333337E-3</v>
       </c>
       <c r="S30" s="1"/>
@@ -15885,54 +16353,54 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="121">
+      <c r="A31" s="123">
         <v>5</v>
       </c>
       <c r="B31" s="122">
         <v>1.1121296296296296E-3</v>
       </c>
-      <c r="C31" s="121">
+      <c r="C31" s="123">
         <v>5</v>
       </c>
       <c r="D31" s="122">
         <v>1.1186458333333335E-3</v>
       </c>
-      <c r="E31" s="121">
+      <c r="E31" s="123">
         <v>5</v>
       </c>
       <c r="F31" s="122">
         <v>1.1660416666666668E-3</v>
       </c>
-      <c r="G31" s="99">
+      <c r="G31" s="97">
         <v>5</v>
       </c>
-      <c r="H31" s="100">
+      <c r="H31" s="98">
         <v>1.1660416666666668E-3</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="123">
+      <c r="K31" s="124">
         <v>5</v>
       </c>
-      <c r="L31" s="124">
+      <c r="L31" s="125">
         <v>1.1346180555555556E-3</v>
       </c>
-      <c r="M31" s="123">
+      <c r="M31" s="124">
         <v>5</v>
       </c>
-      <c r="N31" s="124">
+      <c r="N31" s="125">
         <v>1.0958333333333334E-3</v>
       </c>
-      <c r="O31" s="95">
+      <c r="O31" s="93">
         <v>5</v>
       </c>
-      <c r="P31" s="96">
+      <c r="P31" s="94">
         <v>1.198900462962963E-3</v>
       </c>
-      <c r="Q31" s="123">
+      <c r="Q31" s="124">
         <v>5</v>
       </c>
-      <c r="R31" s="124">
+      <c r="R31" s="125">
         <v>1.198900462962963E-3</v>
       </c>
       <c r="S31" s="1"/>
@@ -15942,54 +16410,54 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="121">
+      <c r="A32" s="123">
         <v>6</v>
       </c>
       <c r="B32" s="122">
         <v>1.1231828703703705E-3</v>
       </c>
-      <c r="C32" s="121">
+      <c r="C32" s="123">
         <v>6</v>
       </c>
       <c r="D32" s="122">
         <v>1.1192708333333332E-3</v>
       </c>
-      <c r="E32" s="121">
+      <c r="E32" s="123">
         <v>6</v>
       </c>
       <c r="F32" s="122">
         <v>1.1783333333333333E-3</v>
       </c>
-      <c r="G32" s="99">
+      <c r="G32" s="97">
         <v>6</v>
       </c>
-      <c r="H32" s="100">
+      <c r="H32" s="98">
         <v>1.1783333333333333E-3</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="123">
+      <c r="K32" s="124">
         <v>6</v>
       </c>
-      <c r="L32" s="124">
+      <c r="L32" s="125">
         <v>1.1811458333333333E-3</v>
       </c>
-      <c r="M32" s="123">
+      <c r="M32" s="124">
         <v>6</v>
       </c>
-      <c r="N32" s="124">
+      <c r="N32" s="125">
         <v>1.1103587962962964E-3</v>
       </c>
-      <c r="O32" s="95">
+      <c r="O32" s="93">
         <v>6</v>
       </c>
-      <c r="P32" s="96">
+      <c r="P32" s="94">
         <v>1.3676157407407409E-3</v>
       </c>
-      <c r="Q32" s="123">
+      <c r="Q32" s="124">
         <v>6</v>
       </c>
-      <c r="R32" s="124">
+      <c r="R32" s="125">
         <v>1.3676157407407409E-3</v>
       </c>
       <c r="S32" s="1"/>
@@ -15999,54 +16467,54 @@
       <c r="W32" s="1"/>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="121">
+      <c r="A33" s="123">
         <v>7</v>
       </c>
       <c r="B33" s="122">
         <v>1.1183564814814815E-3</v>
       </c>
-      <c r="C33" s="121">
+      <c r="C33" s="123">
         <v>7</v>
       </c>
       <c r="D33" s="122">
         <v>1.1119675925925926E-3</v>
       </c>
-      <c r="E33" s="121">
+      <c r="E33" s="123">
         <v>7</v>
       </c>
       <c r="F33" s="122">
         <v>1.1461342592592593E-3</v>
       </c>
-      <c r="G33" s="99">
+      <c r="G33" s="97">
         <v>7</v>
       </c>
-      <c r="H33" s="100">
+      <c r="H33" s="98">
         <v>1.1461342592592593E-3</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="123">
+      <c r="K33" s="124">
         <v>7</v>
       </c>
-      <c r="L33" s="124">
+      <c r="L33" s="125">
         <v>1.1964467592592591E-3</v>
       </c>
-      <c r="M33" s="123">
+      <c r="M33" s="124">
         <v>7</v>
       </c>
-      <c r="N33" s="124">
+      <c r="N33" s="125">
         <v>1.1330787037037036E-3</v>
       </c>
-      <c r="O33" s="95">
+      <c r="O33" s="93">
         <v>7</v>
       </c>
-      <c r="P33" s="96">
+      <c r="P33" s="94">
         <v>1.2607407407407407E-3</v>
       </c>
-      <c r="Q33" s="123">
+      <c r="Q33" s="124">
         <v>7</v>
       </c>
-      <c r="R33" s="124">
+      <c r="R33" s="125">
         <v>1.2607407407407407E-3</v>
       </c>
       <c r="S33" s="1"/>
@@ -16056,54 +16524,54 @@
       <c r="W33" s="1"/>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="121">
+      <c r="A34" s="123">
         <v>8</v>
       </c>
       <c r="B34" s="122">
         <v>1.124398148148148E-3</v>
       </c>
-      <c r="C34" s="121">
+      <c r="C34" s="123">
         <v>8</v>
       </c>
       <c r="D34" s="122">
         <v>1.1048148148148148E-3</v>
       </c>
-      <c r="E34" s="121">
+      <c r="E34" s="123">
         <v>8</v>
       </c>
       <c r="F34" s="122">
         <v>1.2261226851851851E-3</v>
       </c>
-      <c r="G34" s="99">
+      <c r="G34" s="97">
         <v>8</v>
       </c>
-      <c r="H34" s="100">
+      <c r="H34" s="98">
         <v>1.2261226851851851E-3</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="123">
+      <c r="K34" s="124">
         <v>8</v>
       </c>
-      <c r="L34" s="124">
+      <c r="L34" s="125">
         <v>1.1544097222222223E-3</v>
       </c>
-      <c r="M34" s="123">
+      <c r="M34" s="124">
         <v>8</v>
       </c>
-      <c r="N34" s="124">
+      <c r="N34" s="125">
         <v>1.1489930555555554E-3</v>
       </c>
-      <c r="O34" s="95">
+      <c r="O34" s="93">
         <v>8</v>
       </c>
-      <c r="P34" s="96">
+      <c r="P34" s="94">
         <v>1.1238657407407408E-3</v>
       </c>
-      <c r="Q34" s="123">
+      <c r="Q34" s="124">
         <v>8</v>
       </c>
-      <c r="R34" s="124">
+      <c r="R34" s="125">
         <v>1.1238657407407408E-3</v>
       </c>
       <c r="S34" s="1"/>
@@ -16113,54 +16581,54 @@
       <c r="W34" s="1"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="121">
+      <c r="A35" s="123">
         <v>9</v>
       </c>
       <c r="B35" s="122">
         <v>1.2592476851851853E-3</v>
       </c>
-      <c r="C35" s="121">
+      <c r="C35" s="123">
         <v>9</v>
       </c>
       <c r="D35" s="122">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="E35" s="121">
+      <c r="E35" s="123">
         <v>9</v>
       </c>
       <c r="F35" s="122">
         <v>1.1561111111111112E-3</v>
       </c>
-      <c r="G35" s="99">
+      <c r="G35" s="97">
         <v>9</v>
       </c>
-      <c r="H35" s="100">
+      <c r="H35" s="98">
         <v>1.1561111111111112E-3</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="123">
+      <c r="K35" s="124">
         <v>9</v>
       </c>
-      <c r="L35" s="124">
+      <c r="L35" s="125">
         <v>1.2505092592592592E-3</v>
       </c>
-      <c r="M35" s="123">
+      <c r="M35" s="124">
         <v>9</v>
       </c>
-      <c r="N35" s="124">
+      <c r="N35" s="125">
         <v>1.1331134259259261E-3</v>
       </c>
-      <c r="O35" s="95">
+      <c r="O35" s="93">
         <v>9</v>
       </c>
-      <c r="P35" s="96">
+      <c r="P35" s="94">
         <v>1.2741203703703703E-3</v>
       </c>
-      <c r="Q35" s="123">
+      <c r="Q35" s="124">
         <v>9</v>
       </c>
-      <c r="R35" s="124">
+      <c r="R35" s="125">
         <v>1.2741203703703703E-3</v>
       </c>
       <c r="S35" s="1"/>
@@ -16170,54 +16638,54 @@
       <c r="W35" s="1"/>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="121">
+      <c r="A36" s="123">
         <v>10</v>
       </c>
       <c r="B36" s="122">
         <v>1.1363194444444444E-3</v>
       </c>
-      <c r="C36" s="121">
+      <c r="C36" s="123">
         <v>10</v>
       </c>
       <c r="D36" s="122">
         <v>1.1534143518518519E-3</v>
       </c>
-      <c r="E36" s="121">
+      <c r="E36" s="123">
         <v>10</v>
       </c>
       <c r="F36" s="122">
         <v>1.1621296296296297E-3</v>
       </c>
-      <c r="G36" s="99">
+      <c r="G36" s="97">
         <v>10</v>
       </c>
-      <c r="H36" s="100">
+      <c r="H36" s="98">
         <v>1.1621296296296297E-3</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="123">
+      <c r="K36" s="124">
         <v>10</v>
       </c>
-      <c r="L36" s="124">
+      <c r="L36" s="125">
         <v>1.1465856481481481E-3</v>
       </c>
-      <c r="M36" s="123">
+      <c r="M36" s="124">
         <v>10</v>
       </c>
-      <c r="N36" s="124">
+      <c r="N36" s="125">
         <v>1.1556481481481481E-3</v>
       </c>
-      <c r="O36" s="95">
+      <c r="O36" s="93">
         <v>10</v>
       </c>
-      <c r="P36" s="96">
+      <c r="P36" s="94">
         <v>1.1596180555555557E-3</v>
       </c>
-      <c r="Q36" s="123">
+      <c r="Q36" s="124">
         <v>10</v>
       </c>
-      <c r="R36" s="124">
+      <c r="R36" s="125">
         <v>1.1596180555555557E-3</v>
       </c>
       <c r="S36" s="1"/>
@@ -16227,54 +16695,54 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="121">
+      <c r="A37" s="123">
         <v>11</v>
       </c>
       <c r="B37" s="122">
         <v>1.3982291666666668E-3</v>
       </c>
-      <c r="C37" s="121">
+      <c r="C37" s="123">
         <v>11</v>
       </c>
       <c r="D37" s="122">
         <v>1.2330902777777778E-3</v>
       </c>
-      <c r="E37" s="121">
+      <c r="E37" s="123">
         <v>11</v>
       </c>
       <c r="F37" s="122">
         <v>1.2419907407407406E-3</v>
       </c>
-      <c r="G37" s="99">
+      <c r="G37" s="97">
         <v>11</v>
       </c>
-      <c r="H37" s="100">
+      <c r="H37" s="98">
         <v>1.2419907407407406E-3</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="123">
+      <c r="K37" s="124">
         <v>11</v>
       </c>
-      <c r="L37" s="124">
+      <c r="L37" s="125">
         <v>1.1611226851851852E-3</v>
       </c>
-      <c r="M37" s="123">
+      <c r="M37" s="124">
         <v>11</v>
       </c>
-      <c r="N37" s="124">
+      <c r="N37" s="125">
         <v>1.2279976851851851E-3</v>
       </c>
-      <c r="O37" s="95">
+      <c r="O37" s="93">
         <v>11</v>
       </c>
-      <c r="P37" s="96">
+      <c r="P37" s="94">
         <v>2.1243171296296296E-3</v>
       </c>
-      <c r="Q37" s="123">
+      <c r="Q37" s="124">
         <v>11</v>
       </c>
-      <c r="R37" s="124">
+      <c r="R37" s="125">
         <v>2.1243171296296296E-3</v>
       </c>
       <c r="S37" s="1"/>
@@ -16284,54 +16752,54 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="121">
+      <c r="A38" s="123">
         <v>12</v>
       </c>
       <c r="B38" s="122">
         <v>1.5461458333333332E-3</v>
       </c>
-      <c r="C38" s="121">
+      <c r="C38" s="123">
         <v>12</v>
       </c>
       <c r="D38" s="122">
         <v>1.9078009259259261E-3</v>
       </c>
-      <c r="E38" s="121">
+      <c r="E38" s="123">
         <v>12</v>
       </c>
       <c r="F38" s="122">
         <v>1.4453819444444444E-3</v>
       </c>
-      <c r="G38" s="99">
+      <c r="G38" s="97">
         <v>12</v>
       </c>
-      <c r="H38" s="100">
+      <c r="H38" s="98">
         <v>1.4453819444444444E-3</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="123">
+      <c r="K38" s="124">
         <v>12</v>
       </c>
-      <c r="L38" s="124">
+      <c r="L38" s="125">
         <v>1.3398611111111113E-3</v>
       </c>
-      <c r="M38" s="123">
+      <c r="M38" s="124">
         <v>12</v>
       </c>
-      <c r="N38" s="124">
+      <c r="N38" s="125">
         <v>1.310949074074074E-3</v>
       </c>
-      <c r="O38" s="95">
+      <c r="O38" s="93">
         <v>12</v>
       </c>
-      <c r="P38" s="96">
+      <c r="P38" s="94">
         <v>1.4692245370370371E-3</v>
       </c>
-      <c r="Q38" s="123">
+      <c r="Q38" s="124">
         <v>12</v>
       </c>
-      <c r="R38" s="124">
+      <c r="R38" s="125">
         <v>1.4692245370370371E-3</v>
       </c>
       <c r="S38" s="1"/>
@@ -16341,54 +16809,54 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="121">
+      <c r="A39" s="123">
         <v>13</v>
       </c>
       <c r="B39" s="122">
         <v>1.2216550925925925E-3</v>
       </c>
-      <c r="C39" s="121">
+      <c r="C39" s="123">
         <v>13</v>
       </c>
       <c r="D39" s="122">
         <v>1.2544560185185185E-3</v>
       </c>
-      <c r="E39" s="121">
+      <c r="E39" s="123">
         <v>13</v>
       </c>
       <c r="F39" s="122">
         <v>1.2557175925925926E-3</v>
       </c>
-      <c r="G39" s="99">
+      <c r="G39" s="97">
         <v>13</v>
       </c>
-      <c r="H39" s="100">
+      <c r="H39" s="98">
         <v>1.2557175925925926E-3</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="123">
+      <c r="K39" s="124">
         <v>13</v>
       </c>
-      <c r="L39" s="124">
+      <c r="L39" s="125">
         <v>3.8921759259259257E-3</v>
       </c>
-      <c r="M39" s="123">
+      <c r="M39" s="124">
         <v>13</v>
       </c>
-      <c r="N39" s="124">
+      <c r="N39" s="125">
         <v>4.1754282407407408E-3</v>
       </c>
-      <c r="O39" s="95">
+      <c r="O39" s="93">
         <v>13</v>
       </c>
-      <c r="P39" s="96">
+      <c r="P39" s="94">
         <v>1.6091435185185184E-3</v>
       </c>
-      <c r="Q39" s="123">
+      <c r="Q39" s="124">
         <v>13</v>
       </c>
-      <c r="R39" s="124">
+      <c r="R39" s="125">
         <v>1.6091435185185184E-3</v>
       </c>
       <c r="S39" s="1"/>
@@ -16398,54 +16866,54 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="121">
+      <c r="A40" s="123">
         <v>14</v>
       </c>
       <c r="B40" s="122">
         <v>1.1457523148148147E-3</v>
       </c>
-      <c r="C40" s="121">
+      <c r="C40" s="123">
         <v>14</v>
       </c>
       <c r="D40" s="122">
         <v>1.1745949074074074E-3</v>
       </c>
-      <c r="E40" s="121">
+      <c r="E40" s="123">
         <v>14</v>
       </c>
       <c r="F40" s="122">
         <v>1.1743055555555556E-3</v>
       </c>
-      <c r="G40" s="99">
+      <c r="G40" s="97">
         <v>14</v>
       </c>
-      <c r="H40" s="100">
+      <c r="H40" s="98">
         <v>1.1743055555555556E-3</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="123">
+      <c r="K40" s="124">
         <v>14</v>
       </c>
-      <c r="L40" s="124">
+      <c r="L40" s="125">
         <v>1.1608564814814815E-3</v>
       </c>
-      <c r="M40" s="123">
+      <c r="M40" s="124">
         <v>14</v>
       </c>
-      <c r="N40" s="124">
+      <c r="N40" s="125">
         <v>1.1806365740740742E-3</v>
       </c>
-      <c r="O40" s="95">
+      <c r="O40" s="93">
         <v>14</v>
       </c>
-      <c r="P40" s="96">
+      <c r="P40" s="94">
         <v>1.1635069444444444E-3</v>
       </c>
-      <c r="Q40" s="123">
+      <c r="Q40" s="124">
         <v>14</v>
       </c>
-      <c r="R40" s="124">
+      <c r="R40" s="125">
         <v>1.1635069444444444E-3</v>
       </c>
       <c r="S40" s="1"/>
@@ -16455,54 +16923,54 @@
       <c r="W40" s="1"/>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="121">
+      <c r="A41" s="123">
         <v>15</v>
       </c>
       <c r="B41" s="122">
         <v>1.5789930555555557E-3</v>
       </c>
-      <c r="C41" s="121">
+      <c r="C41" s="123">
         <v>15</v>
       </c>
       <c r="D41" s="122">
         <v>1.544236111111111E-3</v>
       </c>
-      <c r="E41" s="121">
+      <c r="E41" s="123">
         <v>15</v>
       </c>
       <c r="F41" s="122">
         <v>1.5701967592592592E-3</v>
       </c>
-      <c r="G41" s="99">
+      <c r="G41" s="97">
         <v>15</v>
       </c>
-      <c r="H41" s="100">
+      <c r="H41" s="98">
         <v>1.5701967592592592E-3</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="123">
+      <c r="K41" s="124">
         <v>15</v>
       </c>
-      <c r="L41" s="124">
+      <c r="L41" s="125">
         <v>1.1989930555555556E-3</v>
       </c>
-      <c r="M41" s="123">
+      <c r="M41" s="124">
         <v>15</v>
       </c>
-      <c r="N41" s="124">
+      <c r="N41" s="125">
         <v>1.1869444444444445E-3</v>
       </c>
-      <c r="O41" s="95">
+      <c r="O41" s="93">
         <v>15</v>
       </c>
-      <c r="P41" s="96">
+      <c r="P41" s="94">
         <v>1.1449421296296297E-3</v>
       </c>
-      <c r="Q41" s="123">
+      <c r="Q41" s="124">
         <v>15</v>
       </c>
-      <c r="R41" s="124">
+      <c r="R41" s="125">
         <v>1.1449421296296297E-3</v>
       </c>
       <c r="S41" s="1"/>
@@ -16512,54 +16980,54 @@
       <c r="W41" s="1"/>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="121">
+      <c r="A42" s="123">
         <v>16</v>
       </c>
       <c r="B42" s="122">
         <v>1.1158217592592591E-3</v>
       </c>
-      <c r="C42" s="121">
+      <c r="C42" s="123">
         <v>16</v>
       </c>
       <c r="D42" s="122">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="E42" s="121">
+      <c r="E42" s="123">
         <v>16</v>
       </c>
       <c r="F42" s="122">
         <v>1.2513888888888889E-3</v>
       </c>
-      <c r="G42" s="99">
+      <c r="G42" s="97">
         <v>16</v>
       </c>
-      <c r="H42" s="100">
+      <c r="H42" s="98">
         <v>1.2513888888888889E-3</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="123">
+      <c r="K42" s="124">
         <v>16</v>
       </c>
-      <c r="L42" s="124">
+      <c r="L42" s="125">
         <v>1.1175E-3</v>
       </c>
-      <c r="M42" s="123">
+      <c r="M42" s="124">
         <v>16</v>
       </c>
-      <c r="N42" s="124">
+      <c r="N42" s="125">
         <v>1.1115046296296296E-3</v>
       </c>
-      <c r="O42" s="95">
+      <c r="O42" s="93">
         <v>16</v>
       </c>
-      <c r="P42" s="96">
+      <c r="P42" s="94">
         <v>1.140324074074074E-3</v>
       </c>
-      <c r="Q42" s="123">
+      <c r="Q42" s="124">
         <v>16</v>
       </c>
-      <c r="R42" s="124">
+      <c r="R42" s="125">
         <v>1.140324074074074E-3</v>
       </c>
       <c r="S42" s="1"/>
@@ -16569,54 +17037,54 @@
       <c r="W42" s="1"/>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="121">
+      <c r="A43" s="123">
         <v>17</v>
       </c>
       <c r="B43" s="122">
         <v>1.1162731481481481E-3</v>
       </c>
-      <c r="C43" s="121">
+      <c r="C43" s="123">
         <v>17</v>
       </c>
       <c r="D43" s="122">
         <v>1.1204629629629629E-3</v>
       </c>
-      <c r="E43" s="121">
+      <c r="E43" s="123">
         <v>17</v>
       </c>
       <c r="F43" s="122">
         <v>1.1524421296296296E-3</v>
       </c>
-      <c r="G43" s="99">
+      <c r="G43" s="97">
         <v>17</v>
       </c>
-      <c r="H43" s="100">
+      <c r="H43" s="98">
         <v>1.1524421296296296E-3</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="123">
+      <c r="K43" s="124">
         <v>17</v>
       </c>
-      <c r="L43" s="124">
+      <c r="L43" s="125">
         <v>1.133587962962963E-3</v>
       </c>
-      <c r="M43" s="123">
+      <c r="M43" s="124">
         <v>17</v>
       </c>
-      <c r="N43" s="124">
+      <c r="N43" s="125">
         <v>1.1427777777777777E-3</v>
       </c>
-      <c r="O43" s="95">
+      <c r="O43" s="93">
         <v>17</v>
       </c>
-      <c r="P43" s="96">
+      <c r="P43" s="94">
         <v>1.1632407407407407E-3</v>
       </c>
-      <c r="Q43" s="123">
+      <c r="Q43" s="124">
         <v>17</v>
       </c>
-      <c r="R43" s="124">
+      <c r="R43" s="125">
         <v>1.1632407407407407E-3</v>
       </c>
       <c r="S43" s="58"/>
@@ -16626,54 +17094,54 @@
       <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="121">
+      <c r="A44" s="123">
         <v>18</v>
       </c>
       <c r="B44" s="122">
         <v>1.114398148148148E-3</v>
       </c>
-      <c r="C44" s="121">
+      <c r="C44" s="123">
         <v>18</v>
       </c>
       <c r="D44" s="122">
         <v>1.1069444444444445E-3</v>
       </c>
-      <c r="E44" s="121">
+      <c r="E44" s="123">
         <v>18</v>
       </c>
       <c r="F44" s="122">
         <v>1.1676157407407408E-3</v>
       </c>
-      <c r="G44" s="99">
+      <c r="G44" s="97">
         <v>18</v>
       </c>
-      <c r="H44" s="100">
+      <c r="H44" s="98">
         <v>1.1676157407407408E-3</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="123">
+      <c r="K44" s="124">
         <v>18</v>
       </c>
-      <c r="L44" s="124">
+      <c r="L44" s="125">
         <v>1.1378240740740741E-3</v>
       </c>
-      <c r="M44" s="123">
+      <c r="M44" s="124">
         <v>18</v>
       </c>
-      <c r="N44" s="124">
+      <c r="N44" s="125">
         <v>1.1362962962962963E-3</v>
       </c>
-      <c r="O44" s="95">
+      <c r="O44" s="93">
         <v>18</v>
       </c>
-      <c r="P44" s="96">
+      <c r="P44" s="94">
         <v>1.1319444444444443E-3</v>
       </c>
-      <c r="Q44" s="123">
+      <c r="Q44" s="124">
         <v>18</v>
       </c>
-      <c r="R44" s="124">
+      <c r="R44" s="125">
         <v>1.1319444444444443E-3</v>
       </c>
       <c r="S44" s="58"/>
@@ -16683,54 +17151,54 @@
       <c r="W44" s="1"/>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="121">
+      <c r="A45" s="123">
         <v>19</v>
       </c>
       <c r="B45" s="122">
         <v>1.1236805555555555E-3</v>
       </c>
-      <c r="C45" s="121">
+      <c r="C45" s="123">
         <v>19</v>
       </c>
       <c r="D45" s="122">
         <v>1.1092129629629629E-3</v>
       </c>
-      <c r="E45" s="121">
+      <c r="E45" s="123">
         <v>19</v>
       </c>
       <c r="F45" s="122">
         <v>1.1594328703703703E-3</v>
       </c>
-      <c r="G45" s="99">
+      <c r="G45" s="97">
         <v>19</v>
       </c>
-      <c r="H45" s="100">
+      <c r="H45" s="98">
         <v>1.1594328703703703E-3</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="123">
+      <c r="K45" s="124">
         <v>19</v>
       </c>
-      <c r="L45" s="124">
+      <c r="L45" s="125">
         <v>1.1439699074074073E-3</v>
       </c>
-      <c r="M45" s="123">
+      <c r="M45" s="124">
         <v>19</v>
       </c>
-      <c r="N45" s="124">
+      <c r="N45" s="125">
         <v>1.1471990740740739E-3</v>
       </c>
-      <c r="O45" s="95">
+      <c r="O45" s="93">
         <v>19</v>
       </c>
-      <c r="P45" s="96">
+      <c r="P45" s="94">
         <v>1.149375E-3</v>
       </c>
-      <c r="Q45" s="123">
+      <c r="Q45" s="124">
         <v>19</v>
       </c>
-      <c r="R45" s="124">
+      <c r="R45" s="125">
         <v>1.149375E-3</v>
       </c>
       <c r="S45" s="58"/>
@@ -16740,54 +17208,54 @@
       <c r="W45" s="1"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="121">
+      <c r="A46" s="123">
         <v>20</v>
       </c>
       <c r="B46" s="122">
         <v>1.1430092592592592E-3</v>
       </c>
-      <c r="C46" s="121">
+      <c r="C46" s="123">
         <v>20</v>
       </c>
       <c r="D46" s="122">
         <v>1.1691319444444444E-3</v>
       </c>
-      <c r="E46" s="121">
+      <c r="E46" s="123">
         <v>20</v>
       </c>
       <c r="F46" s="122">
         <v>1.2307523148148149E-3</v>
       </c>
-      <c r="G46" s="99">
+      <c r="G46" s="97">
         <v>20</v>
       </c>
-      <c r="H46" s="100">
+      <c r="H46" s="98">
         <v>1.2307523148148149E-3</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="125">
+      <c r="K46" s="126">
         <v>20</v>
       </c>
-      <c r="L46" s="126">
+      <c r="L46" s="127">
         <v>1.1290277777777778E-3</v>
       </c>
-      <c r="M46" s="125">
+      <c r="M46" s="126">
         <v>20</v>
       </c>
-      <c r="N46" s="126">
+      <c r="N46" s="127">
         <v>1.1019907407407408E-3</v>
       </c>
-      <c r="O46" s="97">
+      <c r="O46" s="95">
         <v>20</v>
       </c>
-      <c r="P46" s="98">
+      <c r="P46" s="96">
         <v>1.1516666666666665E-3</v>
       </c>
-      <c r="Q46" s="125">
+      <c r="Q46" s="126">
         <v>20</v>
       </c>
-      <c r="R46" s="126">
+      <c r="R46" s="127">
         <v>1.1516666666666665E-3</v>
       </c>
       <c r="S46" s="1"/>
@@ -16973,24 +17441,52 @@
       <c r="R52" s="1"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
+      <c r="A53" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="58">
+        <f>+SMALL(B27:B46,1)</f>
+        <v>1.1098379629629629E-3</v>
+      </c>
       <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="D53" s="58">
+        <f>+SMALL(D27:D46,1)</f>
+        <v>1.0967939814814816E-3</v>
+      </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="F53" s="58">
+        <f>+SMALL(F27:F46,1)</f>
+        <v>1.1312268518518518E-3</v>
+      </c>
       <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="H53" s="58">
+        <f>+SMALL(H27:H46,1)</f>
+        <v>1.1312268518518518E-3</v>
+      </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
+      <c r="K53" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="L53" s="58">
+        <f>+SMALL(L27:L46,1)</f>
+        <v>1.1143287037037035E-3</v>
+      </c>
       <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
+      <c r="N53" s="58">
+        <f>+SMALL(N27:N46,1)</f>
+        <v>1.0958333333333334E-3</v>
+      </c>
       <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
+      <c r="P53" s="58">
+        <f>+SMALL(P27:P46,1)</f>
+        <v>1.1238657407407408E-3</v>
+      </c>
       <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
+      <c r="R53" s="58">
+        <f>+SMALL(R27:R46,1)</f>
+        <v>1.1238657407407408E-3</v>
+      </c>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="1"/>
@@ -17032,15 +17528,17 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
     </row>
-    <row r="56" spans="1:18">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+    <row r="56" spans="1:18" ht="34.5">
+      <c r="A56" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="116"/>
+      <c r="C56" s="116"/>
+      <c r="D56" s="116"/>
+      <c r="E56" s="116"/>
+      <c r="F56" s="116"/>
+      <c r="G56" s="116"/>
+      <c r="H56" s="116"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -17053,14 +17551,22 @@
       <c r="R56" s="1"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="A57" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" s="118"/>
+      <c r="C57" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="118"/>
+      <c r="E57" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="120"/>
+      <c r="G57" s="117" t="s">
+        <v>108</v>
+      </c>
+      <c r="H57" s="118"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -17075,12 +17581,20 @@
     <row r="58" spans="1:18">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+      <c r="C58" s="123">
+        <v>1</v>
+      </c>
+      <c r="D58" s="58">
+        <v>1.9520833333333332E-3</v>
+      </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
+      <c r="G58" s="123">
+        <v>1</v>
+      </c>
+      <c r="H58" s="122">
+        <v>1.9796875000000001E-3</v>
+      </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -17095,12 +17609,20 @@
     <row r="59" spans="1:18">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+      <c r="C59" s="123">
+        <v>2</v>
+      </c>
+      <c r="D59" s="58">
+        <v>1.1939004629629628E-3</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="G59" s="123">
+        <v>2</v>
+      </c>
+      <c r="H59" s="122">
+        <v>1.2236342592592594E-3</v>
+      </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -17115,12 +17637,20 @@
     <row r="60" spans="1:18">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+      <c r="C60" s="123">
+        <v>3</v>
+      </c>
+      <c r="D60" s="58">
+        <v>1.1949652777777779E-3</v>
+      </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="G60" s="123">
+        <v>3</v>
+      </c>
+      <c r="H60" s="122">
+        <v>1.2050810185185185E-3</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -17135,12 +17665,20 @@
     <row r="61" spans="1:18">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
+      <c r="C61" s="123">
+        <v>4</v>
+      </c>
+      <c r="D61" s="58">
+        <v>1.1942129629629631E-3</v>
+      </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+      <c r="G61" s="123">
+        <v>4</v>
+      </c>
+      <c r="H61" s="122">
+        <v>1.2027199074074073E-3</v>
+      </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -17155,12 +17693,20 @@
     <row r="62" spans="1:18">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="C62" s="123">
+        <v>5</v>
+      </c>
+      <c r="D62" s="58">
+        <v>1.1978819444444443E-3</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
+      <c r="G62" s="123">
+        <v>5</v>
+      </c>
+      <c r="H62" s="122">
+        <v>1.1896412037037036E-3</v>
+      </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -17175,12 +17721,20 @@
     <row r="63" spans="1:18">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+      <c r="C63" s="123">
+        <v>6</v>
+      </c>
+      <c r="D63" s="58">
+        <v>1.1956712962962962E-3</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
+      <c r="G63" s="123">
+        <v>6</v>
+      </c>
+      <c r="H63" s="122">
+        <v>1.2009606481481483E-3</v>
+      </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -17195,12 +17749,20 @@
     <row r="64" spans="1:18">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+      <c r="C64" s="123">
+        <v>7</v>
+      </c>
+      <c r="D64" s="58">
+        <v>1.1767824074074074E-3</v>
+      </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
+      <c r="G64" s="123">
+        <v>7</v>
+      </c>
+      <c r="H64" s="122">
+        <v>1.1911805555555556E-3</v>
+      </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -17215,110 +17777,239 @@
     <row r="65" spans="1:8">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="C65" s="123">
+        <v>8</v>
+      </c>
+      <c r="D65" s="58">
+        <v>1.204861111111111E-3</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
+      <c r="G65" s="123">
+        <v>8</v>
+      </c>
+      <c r="H65" s="122">
+        <v>1.1953125E-3</v>
+      </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
+      <c r="C66" s="123">
+        <v>9</v>
+      </c>
+      <c r="D66" s="58">
+        <v>1.2104166666666667E-3</v>
+      </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
+      <c r="G66" s="123">
+        <v>9</v>
+      </c>
+      <c r="H66" s="122">
+        <v>1.2066550925925925E-3</v>
+      </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="C67" s="123">
+        <v>10</v>
+      </c>
+      <c r="D67" s="58">
+        <v>1.5151504629629629E-3</v>
+      </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
+      <c r="G67" s="123">
+        <v>10</v>
+      </c>
+      <c r="H67" s="122">
+        <v>1.4534606481481482E-3</v>
+      </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+      <c r="C68" s="123">
+        <v>11</v>
+      </c>
+      <c r="D68" s="58">
+        <v>1.9391203703703703E-3</v>
+      </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
+      <c r="G68" s="123">
+        <v>11</v>
+      </c>
+      <c r="H68" s="122">
+        <v>1.9292013888888887E-3</v>
+      </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="C69" s="123">
+        <v>12</v>
+      </c>
+      <c r="D69" s="58">
+        <v>1.1987847222222222E-3</v>
+      </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="G69" s="123">
+        <v>12</v>
+      </c>
+      <c r="H69" s="122">
+        <v>1.2021874999999999E-3</v>
+      </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
+      <c r="C70" s="123">
+        <v>13</v>
+      </c>
+      <c r="D70" s="58">
+        <v>1.2125462962962964E-3</v>
+      </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
+      <c r="G70" s="123">
+        <v>13</v>
+      </c>
+      <c r="H70" s="122">
+        <v>1.2077546296296296E-3</v>
+      </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+      <c r="C71" s="123">
+        <v>14</v>
+      </c>
+      <c r="D71" s="58">
+        <v>1.2050694444444444E-3</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
+      <c r="G71" s="123">
+        <v>14</v>
+      </c>
+      <c r="H71" s="122">
+        <v>1.2092245370370371E-3</v>
+      </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="C72" s="123">
+        <v>15</v>
+      </c>
+      <c r="D72" s="58">
+        <v>1.1976967592592592E-3</v>
+      </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
+      <c r="G72" s="123">
+        <v>15</v>
+      </c>
+      <c r="H72" s="122">
+        <v>1.2027314814814815E-3</v>
+      </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
+      <c r="C73" s="123">
+        <v>16</v>
+      </c>
+      <c r="D73" s="58">
+        <v>1.2089351851851851E-3</v>
+      </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
+      <c r="G73" s="123">
+        <v>16</v>
+      </c>
+      <c r="H73" s="122">
+        <v>1.1990972222222223E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="123"/>
+      <c r="H74" s="121"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="123"/>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1"/>
+      <c r="B76" s="58" t="e">
+        <f>+AVERAGE(B54:B63,B67:B73)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="58">
+        <f>+AVERAGE(D54:D66,D69:D73)</f>
+        <v>1.2531291335978834E-3</v>
+      </c>
+      <c r="E76" s="1"/>
+      <c r="F76" s="58" t="e">
+        <f>+AVERAGE(F54:F63,F67:F73)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G76" s="123"/>
+      <c r="H76" s="58">
+        <f>+AVERAGE(H58:H66,H69:H73)</f>
+        <v>1.2582762896825397E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="123"/>
+      <c r="H77" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="20">
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:R1"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="M26:N26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D3C955-CCF6-4AC1-B2D4-EA7CC7C98E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BB64967-D6A7-45CE-9CAC-9ED2A3EC7410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="111">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -418,11 +418,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0&quot;Kg&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mm:ss.000"/>
     <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
+    <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1031,7 +1032,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1284,6 +1285,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -13728,7 +13730,7 @@
       <c r="G15" s="58"/>
       <c r="H15" s="1" cm="1">
         <f t="array" ref="H15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>1.0206041666666666E-3</v>
+        <v>1.0593583278218695E-3</v>
       </c>
       <c r="I15" s="1" cm="1">
         <f t="array" ref="I15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
@@ -13740,7 +13742,7 @@
       </c>
       <c r="K15" s="1" cm="1">
         <f t="array" ref="K15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>1.035150462962963E-3</v>
+        <v>1.072338100749559E-3</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -13979,16 +13981,16 @@
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="122">
+      <c r="C24" s="123">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="D24" s="122">
+      <c r="D24" s="123">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="E24" s="122">
+      <c r="E24" s="123">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="F24" s="122">
+      <c r="F24" s="123">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G24" s="58"/>
@@ -14063,10 +14065,14 @@
       <c r="B27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="58"/>
+      <c r="C27" s="58">
+        <v>1.2531291335978834E-3</v>
+      </c>
       <c r="D27" s="58"/>
       <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
+      <c r="F27" s="58">
+        <v>1.2582762896825397E-3</v>
+      </c>
       <c r="G27" s="58"/>
       <c r="H27" s="58"/>
       <c r="I27" s="58"/>
@@ -14287,15 +14293,15 @@
       </c>
       <c r="J3" s="1">
         <f>IF('Carga Tiempos'!H15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!H15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>0</v>
+        <v>3.3895364858906691E-5</v>
       </c>
       <c r="K3" s="58">
         <f>IF('Carga Tiempos'!I15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!I15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>4.8587962962962084E-6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1">
         <f>IF('Carga Tiempos'!K15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!K15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>1.4546296296296356E-5</v>
+        <v>4.6875137786596193E-5</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -14988,19 +14994,19 @@
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>0</v>
+        <v>1.2531291335978834E-3</v>
       </c>
       <c r="D27" s="68">
         <f>+IF('Carga Tiempos'!D27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!D27,'Carga Tiempos'!D27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>0</v>
+        <v>-1.2531291335978834E-3</v>
       </c>
       <c r="E27" s="63">
         <f>+IF('Carga Tiempos'!E27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!E27,'Carga Tiempos'!E27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>0</v>
+        <v>-1.2531291335978834E-3</v>
       </c>
       <c r="F27" s="68">
         <f>+IF('Carga Tiempos'!F27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!F27,'Carga Tiempos'!F27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>0</v>
+        <v>5.1471560846563184E-6</v>
       </c>
       <c r="G27" s="58"/>
       <c r="H27" s="58"/>
@@ -15219,10 +15225,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34573353-DC88-4E7A-8BA7-3DB24B9880AA}">
-  <dimension ref="A1:W77"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
@@ -16125,22 +16132,22 @@
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="123">
+      <c r="A27" s="124">
         <v>1</v>
       </c>
-      <c r="B27" s="122">
+      <c r="B27" s="123">
         <v>1.1538888888888888E-3</v>
       </c>
-      <c r="C27" s="123">
+      <c r="C27" s="124">
         <v>1</v>
       </c>
-      <c r="D27" s="122">
+      <c r="D27" s="123">
         <v>1.1476041666666666E-3</v>
       </c>
-      <c r="E27" s="123">
+      <c r="E27" s="124">
         <v>1</v>
       </c>
-      <c r="F27" s="122">
+      <c r="F27" s="123">
         <v>1.1644560185185187E-3</v>
       </c>
       <c r="G27" s="97">
@@ -16151,16 +16158,16 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="124">
+      <c r="K27" s="125">
         <v>1</v>
       </c>
-      <c r="L27" s="125">
+      <c r="L27" s="126">
         <v>1.4355671296296297E-3</v>
       </c>
-      <c r="M27" s="124">
+      <c r="M27" s="125">
         <v>1</v>
       </c>
-      <c r="N27" s="125">
+      <c r="N27" s="126">
         <v>1.4123148148148148E-3</v>
       </c>
       <c r="O27" s="93">
@@ -16169,10 +16176,10 @@
       <c r="P27" s="94">
         <v>1.4081597222222223E-3</v>
       </c>
-      <c r="Q27" s="124">
+      <c r="Q27" s="125">
         <v>1</v>
       </c>
-      <c r="R27" s="125">
+      <c r="R27" s="126">
         <v>1.4081597222222223E-3</v>
       </c>
       <c r="S27" s="92"/>
@@ -16182,22 +16189,22 @@
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="123">
+      <c r="A28" s="124">
         <v>2</v>
       </c>
-      <c r="B28" s="122">
+      <c r="B28" s="123">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="C28" s="123">
+      <c r="C28" s="124">
         <v>2</v>
       </c>
-      <c r="D28" s="122">
+      <c r="D28" s="123">
         <v>1.1111458333333333E-3</v>
       </c>
-      <c r="E28" s="123">
+      <c r="E28" s="124">
         <v>2</v>
       </c>
-      <c r="F28" s="122">
+      <c r="F28" s="123">
         <v>1.1378703703703703E-3</v>
       </c>
       <c r="G28" s="97">
@@ -16208,16 +16215,16 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="124">
+      <c r="K28" s="125">
         <v>2</v>
       </c>
-      <c r="L28" s="125">
+      <c r="L28" s="126">
         <v>1.1143287037037035E-3</v>
       </c>
-      <c r="M28" s="124">
+      <c r="M28" s="125">
         <v>2</v>
       </c>
-      <c r="N28" s="125">
+      <c r="N28" s="126">
         <v>1.1365393518518519E-3</v>
       </c>
       <c r="O28" s="93">
@@ -16226,10 +16233,10 @@
       <c r="P28" s="94">
         <v>1.1394212962962964E-3</v>
       </c>
-      <c r="Q28" s="124">
+      <c r="Q28" s="125">
         <v>2</v>
       </c>
-      <c r="R28" s="125">
+      <c r="R28" s="126">
         <v>1.1394212962962964E-3</v>
       </c>
       <c r="S28" s="1"/>
@@ -16239,22 +16246,22 @@
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="123">
+      <c r="A29" s="124">
         <v>3</v>
       </c>
-      <c r="B29" s="122">
+      <c r="B29" s="123">
         <v>1.110173611111111E-3</v>
       </c>
-      <c r="C29" s="123">
+      <c r="C29" s="124">
         <v>3</v>
       </c>
-      <c r="D29" s="122">
+      <c r="D29" s="123">
         <v>1.0993171296296296E-3</v>
       </c>
-      <c r="E29" s="123">
+      <c r="E29" s="124">
         <v>3</v>
       </c>
-      <c r="F29" s="122">
+      <c r="F29" s="123">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G29" s="97">
@@ -16265,16 +16272,16 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="124">
+      <c r="K29" s="125">
         <v>3</v>
       </c>
-      <c r="L29" s="125">
+      <c r="L29" s="126">
         <v>1.1773726851851852E-3</v>
       </c>
-      <c r="M29" s="124">
+      <c r="M29" s="125">
         <v>3</v>
       </c>
-      <c r="N29" s="125">
+      <c r="N29" s="126">
         <v>1.1328703703703702E-3</v>
       </c>
       <c r="O29" s="93">
@@ -16283,10 +16290,10 @@
       <c r="P29" s="94">
         <v>1.1317361111111111E-3</v>
       </c>
-      <c r="Q29" s="124">
+      <c r="Q29" s="125">
         <v>3</v>
       </c>
-      <c r="R29" s="125">
+      <c r="R29" s="126">
         <v>1.1317361111111111E-3</v>
       </c>
       <c r="S29" s="1"/>
@@ -16296,22 +16303,22 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="123">
+      <c r="A30" s="124">
         <v>4</v>
       </c>
-      <c r="B30" s="122">
+      <c r="B30" s="123">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="C30" s="123">
+      <c r="C30" s="124">
         <v>4</v>
       </c>
-      <c r="D30" s="122">
+      <c r="D30" s="123">
         <v>1.0976736111111111E-3</v>
       </c>
-      <c r="E30" s="123">
+      <c r="E30" s="124">
         <v>4</v>
       </c>
-      <c r="F30" s="122">
+      <c r="F30" s="123">
         <v>1.1532986111111112E-3</v>
       </c>
       <c r="G30" s="97">
@@ -16322,16 +16329,16 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="124">
+      <c r="K30" s="125">
         <v>4</v>
       </c>
-      <c r="L30" s="125">
+      <c r="L30" s="126">
         <v>1.1155787037037037E-3</v>
       </c>
-      <c r="M30" s="124">
+      <c r="M30" s="125">
         <v>4</v>
       </c>
-      <c r="N30" s="125">
+      <c r="N30" s="126">
         <v>1.1118055555555556E-3</v>
       </c>
       <c r="O30" s="93">
@@ -16340,10 +16347,10 @@
       <c r="P30" s="94">
         <v>2.0264583333333337E-3</v>
       </c>
-      <c r="Q30" s="124">
+      <c r="Q30" s="125">
         <v>4</v>
       </c>
-      <c r="R30" s="125">
+      <c r="R30" s="126">
         <v>2.0264583333333337E-3</v>
       </c>
       <c r="S30" s="1"/>
@@ -16353,22 +16360,22 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="123">
+      <c r="A31" s="124">
         <v>5</v>
       </c>
-      <c r="B31" s="122">
+      <c r="B31" s="123">
         <v>1.1121296296296296E-3</v>
       </c>
-      <c r="C31" s="123">
+      <c r="C31" s="124">
         <v>5</v>
       </c>
-      <c r="D31" s="122">
+      <c r="D31" s="123">
         <v>1.1186458333333335E-3</v>
       </c>
-      <c r="E31" s="123">
+      <c r="E31" s="124">
         <v>5</v>
       </c>
-      <c r="F31" s="122">
+      <c r="F31" s="123">
         <v>1.1660416666666668E-3</v>
       </c>
       <c r="G31" s="97">
@@ -16379,16 +16386,16 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="124">
+      <c r="K31" s="125">
         <v>5</v>
       </c>
-      <c r="L31" s="125">
+      <c r="L31" s="126">
         <v>1.1346180555555556E-3</v>
       </c>
-      <c r="M31" s="124">
+      <c r="M31" s="125">
         <v>5</v>
       </c>
-      <c r="N31" s="125">
+      <c r="N31" s="126">
         <v>1.0958333333333334E-3</v>
       </c>
       <c r="O31" s="93">
@@ -16397,10 +16404,10 @@
       <c r="P31" s="94">
         <v>1.198900462962963E-3</v>
       </c>
-      <c r="Q31" s="124">
+      <c r="Q31" s="125">
         <v>5</v>
       </c>
-      <c r="R31" s="125">
+      <c r="R31" s="126">
         <v>1.198900462962963E-3</v>
       </c>
       <c r="S31" s="1"/>
@@ -16410,22 +16417,22 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="123">
+      <c r="A32" s="124">
         <v>6</v>
       </c>
-      <c r="B32" s="122">
+      <c r="B32" s="123">
         <v>1.1231828703703705E-3</v>
       </c>
-      <c r="C32" s="123">
+      <c r="C32" s="124">
         <v>6</v>
       </c>
-      <c r="D32" s="122">
+      <c r="D32" s="123">
         <v>1.1192708333333332E-3</v>
       </c>
-      <c r="E32" s="123">
+      <c r="E32" s="124">
         <v>6</v>
       </c>
-      <c r="F32" s="122">
+      <c r="F32" s="123">
         <v>1.1783333333333333E-3</v>
       </c>
       <c r="G32" s="97">
@@ -16436,16 +16443,16 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="124">
+      <c r="K32" s="125">
         <v>6</v>
       </c>
-      <c r="L32" s="125">
+      <c r="L32" s="126">
         <v>1.1811458333333333E-3</v>
       </c>
-      <c r="M32" s="124">
+      <c r="M32" s="125">
         <v>6</v>
       </c>
-      <c r="N32" s="125">
+      <c r="N32" s="126">
         <v>1.1103587962962964E-3</v>
       </c>
       <c r="O32" s="93">
@@ -16454,10 +16461,10 @@
       <c r="P32" s="94">
         <v>1.3676157407407409E-3</v>
       </c>
-      <c r="Q32" s="124">
+      <c r="Q32" s="125">
         <v>6</v>
       </c>
-      <c r="R32" s="125">
+      <c r="R32" s="126">
         <v>1.3676157407407409E-3</v>
       </c>
       <c r="S32" s="1"/>
@@ -16467,22 +16474,22 @@
       <c r="W32" s="1"/>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="123">
+      <c r="A33" s="124">
         <v>7</v>
       </c>
-      <c r="B33" s="122">
+      <c r="B33" s="123">
         <v>1.1183564814814815E-3</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="124">
         <v>7</v>
       </c>
-      <c r="D33" s="122">
+      <c r="D33" s="123">
         <v>1.1119675925925926E-3</v>
       </c>
-      <c r="E33" s="123">
+      <c r="E33" s="124">
         <v>7</v>
       </c>
-      <c r="F33" s="122">
+      <c r="F33" s="123">
         <v>1.1461342592592593E-3</v>
       </c>
       <c r="G33" s="97">
@@ -16493,16 +16500,16 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="124">
+      <c r="K33" s="125">
         <v>7</v>
       </c>
-      <c r="L33" s="125">
+      <c r="L33" s="126">
         <v>1.1964467592592591E-3</v>
       </c>
-      <c r="M33" s="124">
+      <c r="M33" s="125">
         <v>7</v>
       </c>
-      <c r="N33" s="125">
+      <c r="N33" s="126">
         <v>1.1330787037037036E-3</v>
       </c>
       <c r="O33" s="93">
@@ -16511,10 +16518,10 @@
       <c r="P33" s="94">
         <v>1.2607407407407407E-3</v>
       </c>
-      <c r="Q33" s="124">
+      <c r="Q33" s="125">
         <v>7</v>
       </c>
-      <c r="R33" s="125">
+      <c r="R33" s="126">
         <v>1.2607407407407407E-3</v>
       </c>
       <c r="S33" s="1"/>
@@ -16524,22 +16531,22 @@
       <c r="W33" s="1"/>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="123">
+      <c r="A34" s="124">
         <v>8</v>
       </c>
-      <c r="B34" s="122">
+      <c r="B34" s="123">
         <v>1.124398148148148E-3</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="124">
         <v>8</v>
       </c>
-      <c r="D34" s="122">
+      <c r="D34" s="123">
         <v>1.1048148148148148E-3</v>
       </c>
-      <c r="E34" s="123">
+      <c r="E34" s="124">
         <v>8</v>
       </c>
-      <c r="F34" s="122">
+      <c r="F34" s="123">
         <v>1.2261226851851851E-3</v>
       </c>
       <c r="G34" s="97">
@@ -16550,16 +16557,16 @@
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="124">
+      <c r="K34" s="125">
         <v>8</v>
       </c>
-      <c r="L34" s="125">
+      <c r="L34" s="126">
         <v>1.1544097222222223E-3</v>
       </c>
-      <c r="M34" s="124">
+      <c r="M34" s="125">
         <v>8</v>
       </c>
-      <c r="N34" s="125">
+      <c r="N34" s="126">
         <v>1.1489930555555554E-3</v>
       </c>
       <c r="O34" s="93">
@@ -16568,10 +16575,10 @@
       <c r="P34" s="94">
         <v>1.1238657407407408E-3</v>
       </c>
-      <c r="Q34" s="124">
+      <c r="Q34" s="125">
         <v>8</v>
       </c>
-      <c r="R34" s="125">
+      <c r="R34" s="126">
         <v>1.1238657407407408E-3</v>
       </c>
       <c r="S34" s="1"/>
@@ -16581,22 +16588,22 @@
       <c r="W34" s="1"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="123">
+      <c r="A35" s="124">
         <v>9</v>
       </c>
-      <c r="B35" s="122">
+      <c r="B35" s="123">
         <v>1.2592476851851853E-3</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="124">
         <v>9</v>
       </c>
-      <c r="D35" s="122">
+      <c r="D35" s="123">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="E35" s="123">
+      <c r="E35" s="124">
         <v>9</v>
       </c>
-      <c r="F35" s="122">
+      <c r="F35" s="123">
         <v>1.1561111111111112E-3</v>
       </c>
       <c r="G35" s="97">
@@ -16607,16 +16614,16 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="124">
+      <c r="K35" s="125">
         <v>9</v>
       </c>
-      <c r="L35" s="125">
+      <c r="L35" s="126">
         <v>1.2505092592592592E-3</v>
       </c>
-      <c r="M35" s="124">
+      <c r="M35" s="125">
         <v>9</v>
       </c>
-      <c r="N35" s="125">
+      <c r="N35" s="126">
         <v>1.1331134259259261E-3</v>
       </c>
       <c r="O35" s="93">
@@ -16625,10 +16632,10 @@
       <c r="P35" s="94">
         <v>1.2741203703703703E-3</v>
       </c>
-      <c r="Q35" s="124">
+      <c r="Q35" s="125">
         <v>9</v>
       </c>
-      <c r="R35" s="125">
+      <c r="R35" s="126">
         <v>1.2741203703703703E-3</v>
       </c>
       <c r="S35" s="1"/>
@@ -16638,22 +16645,22 @@
       <c r="W35" s="1"/>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="123">
+      <c r="A36" s="124">
         <v>10</v>
       </c>
-      <c r="B36" s="122">
+      <c r="B36" s="123">
         <v>1.1363194444444444E-3</v>
       </c>
-      <c r="C36" s="123">
+      <c r="C36" s="124">
         <v>10</v>
       </c>
-      <c r="D36" s="122">
+      <c r="D36" s="123">
         <v>1.1534143518518519E-3</v>
       </c>
-      <c r="E36" s="123">
+      <c r="E36" s="124">
         <v>10</v>
       </c>
-      <c r="F36" s="122">
+      <c r="F36" s="123">
         <v>1.1621296296296297E-3</v>
       </c>
       <c r="G36" s="97">
@@ -16664,16 +16671,16 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="124">
+      <c r="K36" s="125">
         <v>10</v>
       </c>
-      <c r="L36" s="125">
+      <c r="L36" s="126">
         <v>1.1465856481481481E-3</v>
       </c>
-      <c r="M36" s="124">
+      <c r="M36" s="125">
         <v>10</v>
       </c>
-      <c r="N36" s="125">
+      <c r="N36" s="126">
         <v>1.1556481481481481E-3</v>
       </c>
       <c r="O36" s="93">
@@ -16682,10 +16689,10 @@
       <c r="P36" s="94">
         <v>1.1596180555555557E-3</v>
       </c>
-      <c r="Q36" s="124">
+      <c r="Q36" s="125">
         <v>10</v>
       </c>
-      <c r="R36" s="125">
+      <c r="R36" s="126">
         <v>1.1596180555555557E-3</v>
       </c>
       <c r="S36" s="1"/>
@@ -16695,22 +16702,22 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="123">
+      <c r="A37" s="124">
         <v>11</v>
       </c>
-      <c r="B37" s="122">
+      <c r="B37" s="123">
         <v>1.3982291666666668E-3</v>
       </c>
-      <c r="C37" s="123">
+      <c r="C37" s="124">
         <v>11</v>
       </c>
-      <c r="D37" s="122">
+      <c r="D37" s="123">
         <v>1.2330902777777778E-3</v>
       </c>
-      <c r="E37" s="123">
+      <c r="E37" s="124">
         <v>11</v>
       </c>
-      <c r="F37" s="122">
+      <c r="F37" s="123">
         <v>1.2419907407407406E-3</v>
       </c>
       <c r="G37" s="97">
@@ -16721,16 +16728,16 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="124">
+      <c r="K37" s="125">
         <v>11</v>
       </c>
-      <c r="L37" s="125">
+      <c r="L37" s="126">
         <v>1.1611226851851852E-3</v>
       </c>
-      <c r="M37" s="124">
+      <c r="M37" s="125">
         <v>11</v>
       </c>
-      <c r="N37" s="125">
+      <c r="N37" s="126">
         <v>1.2279976851851851E-3</v>
       </c>
       <c r="O37" s="93">
@@ -16739,10 +16746,10 @@
       <c r="P37" s="94">
         <v>2.1243171296296296E-3</v>
       </c>
-      <c r="Q37" s="124">
+      <c r="Q37" s="125">
         <v>11</v>
       </c>
-      <c r="R37" s="125">
+      <c r="R37" s="126">
         <v>2.1243171296296296E-3</v>
       </c>
       <c r="S37" s="1"/>
@@ -16752,22 +16759,22 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="123">
+      <c r="A38" s="124">
         <v>12</v>
       </c>
-      <c r="B38" s="122">
+      <c r="B38" s="123">
         <v>1.5461458333333332E-3</v>
       </c>
-      <c r="C38" s="123">
+      <c r="C38" s="124">
         <v>12</v>
       </c>
-      <c r="D38" s="122">
+      <c r="D38" s="123">
         <v>1.9078009259259261E-3</v>
       </c>
-      <c r="E38" s="123">
+      <c r="E38" s="124">
         <v>12</v>
       </c>
-      <c r="F38" s="122">
+      <c r="F38" s="123">
         <v>1.4453819444444444E-3</v>
       </c>
       <c r="G38" s="97">
@@ -16778,16 +16785,16 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="124">
+      <c r="K38" s="125">
         <v>12</v>
       </c>
-      <c r="L38" s="125">
+      <c r="L38" s="126">
         <v>1.3398611111111113E-3</v>
       </c>
-      <c r="M38" s="124">
+      <c r="M38" s="125">
         <v>12</v>
       </c>
-      <c r="N38" s="125">
+      <c r="N38" s="126">
         <v>1.310949074074074E-3</v>
       </c>
       <c r="O38" s="93">
@@ -16796,10 +16803,10 @@
       <c r="P38" s="94">
         <v>1.4692245370370371E-3</v>
       </c>
-      <c r="Q38" s="124">
+      <c r="Q38" s="125">
         <v>12</v>
       </c>
-      <c r="R38" s="125">
+      <c r="R38" s="126">
         <v>1.4692245370370371E-3</v>
       </c>
       <c r="S38" s="1"/>
@@ -16809,22 +16816,22 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="123">
+      <c r="A39" s="124">
         <v>13</v>
       </c>
-      <c r="B39" s="122">
+      <c r="B39" s="123">
         <v>1.2216550925925925E-3</v>
       </c>
-      <c r="C39" s="123">
+      <c r="C39" s="124">
         <v>13</v>
       </c>
-      <c r="D39" s="122">
+      <c r="D39" s="123">
         <v>1.2544560185185185E-3</v>
       </c>
-      <c r="E39" s="123">
+      <c r="E39" s="124">
         <v>13</v>
       </c>
-      <c r="F39" s="122">
+      <c r="F39" s="123">
         <v>1.2557175925925926E-3</v>
       </c>
       <c r="G39" s="97">
@@ -16835,16 +16842,16 @@
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="124">
+      <c r="K39" s="125">
         <v>13</v>
       </c>
-      <c r="L39" s="125">
+      <c r="L39" s="126">
         <v>3.8921759259259257E-3</v>
       </c>
-      <c r="M39" s="124">
+      <c r="M39" s="125">
         <v>13</v>
       </c>
-      <c r="N39" s="125">
+      <c r="N39" s="126">
         <v>4.1754282407407408E-3</v>
       </c>
       <c r="O39" s="93">
@@ -16853,10 +16860,10 @@
       <c r="P39" s="94">
         <v>1.6091435185185184E-3</v>
       </c>
-      <c r="Q39" s="124">
+      <c r="Q39" s="125">
         <v>13</v>
       </c>
-      <c r="R39" s="125">
+      <c r="R39" s="126">
         <v>1.6091435185185184E-3</v>
       </c>
       <c r="S39" s="1"/>
@@ -16866,22 +16873,22 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="123">
+      <c r="A40" s="124">
         <v>14</v>
       </c>
-      <c r="B40" s="122">
+      <c r="B40" s="123">
         <v>1.1457523148148147E-3</v>
       </c>
-      <c r="C40" s="123">
+      <c r="C40" s="124">
         <v>14</v>
       </c>
-      <c r="D40" s="122">
+      <c r="D40" s="123">
         <v>1.1745949074074074E-3</v>
       </c>
-      <c r="E40" s="123">
+      <c r="E40" s="124">
         <v>14</v>
       </c>
-      <c r="F40" s="122">
+      <c r="F40" s="123">
         <v>1.1743055555555556E-3</v>
       </c>
       <c r="G40" s="97">
@@ -16892,16 +16899,16 @@
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="124">
+      <c r="K40" s="125">
         <v>14</v>
       </c>
-      <c r="L40" s="125">
+      <c r="L40" s="126">
         <v>1.1608564814814815E-3</v>
       </c>
-      <c r="M40" s="124">
+      <c r="M40" s="125">
         <v>14</v>
       </c>
-      <c r="N40" s="125">
+      <c r="N40" s="126">
         <v>1.1806365740740742E-3</v>
       </c>
       <c r="O40" s="93">
@@ -16910,10 +16917,10 @@
       <c r="P40" s="94">
         <v>1.1635069444444444E-3</v>
       </c>
-      <c r="Q40" s="124">
+      <c r="Q40" s="125">
         <v>14</v>
       </c>
-      <c r="R40" s="125">
+      <c r="R40" s="126">
         <v>1.1635069444444444E-3</v>
       </c>
       <c r="S40" s="1"/>
@@ -16923,22 +16930,22 @@
       <c r="W40" s="1"/>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="123">
+      <c r="A41" s="124">
         <v>15</v>
       </c>
-      <c r="B41" s="122">
+      <c r="B41" s="123">
         <v>1.5789930555555557E-3</v>
       </c>
-      <c r="C41" s="123">
+      <c r="C41" s="124">
         <v>15</v>
       </c>
-      <c r="D41" s="122">
+      <c r="D41" s="123">
         <v>1.544236111111111E-3</v>
       </c>
-      <c r="E41" s="123">
+      <c r="E41" s="124">
         <v>15</v>
       </c>
-      <c r="F41" s="122">
+      <c r="F41" s="123">
         <v>1.5701967592592592E-3</v>
       </c>
       <c r="G41" s="97">
@@ -16949,16 +16956,16 @@
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="124">
+      <c r="K41" s="125">
         <v>15</v>
       </c>
-      <c r="L41" s="125">
+      <c r="L41" s="126">
         <v>1.1989930555555556E-3</v>
       </c>
-      <c r="M41" s="124">
+      <c r="M41" s="125">
         <v>15</v>
       </c>
-      <c r="N41" s="125">
+      <c r="N41" s="126">
         <v>1.1869444444444445E-3</v>
       </c>
       <c r="O41" s="93">
@@ -16967,10 +16974,10 @@
       <c r="P41" s="94">
         <v>1.1449421296296297E-3</v>
       </c>
-      <c r="Q41" s="124">
+      <c r="Q41" s="125">
         <v>15</v>
       </c>
-      <c r="R41" s="125">
+      <c r="R41" s="126">
         <v>1.1449421296296297E-3</v>
       </c>
       <c r="S41" s="1"/>
@@ -16980,22 +16987,22 @@
       <c r="W41" s="1"/>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="123">
+      <c r="A42" s="124">
         <v>16</v>
       </c>
-      <c r="B42" s="122">
+      <c r="B42" s="123">
         <v>1.1158217592592591E-3</v>
       </c>
-      <c r="C42" s="123">
+      <c r="C42" s="124">
         <v>16</v>
       </c>
-      <c r="D42" s="122">
+      <c r="D42" s="123">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="E42" s="123">
+      <c r="E42" s="124">
         <v>16</v>
       </c>
-      <c r="F42" s="122">
+      <c r="F42" s="123">
         <v>1.2513888888888889E-3</v>
       </c>
       <c r="G42" s="97">
@@ -17006,16 +17013,16 @@
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="124">
+      <c r="K42" s="125">
         <v>16</v>
       </c>
-      <c r="L42" s="125">
+      <c r="L42" s="126">
         <v>1.1175E-3</v>
       </c>
-      <c r="M42" s="124">
+      <c r="M42" s="125">
         <v>16</v>
       </c>
-      <c r="N42" s="125">
+      <c r="N42" s="126">
         <v>1.1115046296296296E-3</v>
       </c>
       <c r="O42" s="93">
@@ -17024,10 +17031,10 @@
       <c r="P42" s="94">
         <v>1.140324074074074E-3</v>
       </c>
-      <c r="Q42" s="124">
+      <c r="Q42" s="125">
         <v>16</v>
       </c>
-      <c r="R42" s="125">
+      <c r="R42" s="126">
         <v>1.140324074074074E-3</v>
       </c>
       <c r="S42" s="1"/>
@@ -17037,22 +17044,22 @@
       <c r="W42" s="1"/>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="123">
+      <c r="A43" s="124">
         <v>17</v>
       </c>
-      <c r="B43" s="122">
+      <c r="B43" s="123">
         <v>1.1162731481481481E-3</v>
       </c>
-      <c r="C43" s="123">
+      <c r="C43" s="124">
         <v>17</v>
       </c>
-      <c r="D43" s="122">
+      <c r="D43" s="123">
         <v>1.1204629629629629E-3</v>
       </c>
-      <c r="E43" s="123">
+      <c r="E43" s="124">
         <v>17</v>
       </c>
-      <c r="F43" s="122">
+      <c r="F43" s="123">
         <v>1.1524421296296296E-3</v>
       </c>
       <c r="G43" s="97">
@@ -17063,16 +17070,16 @@
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="124">
+      <c r="K43" s="125">
         <v>17</v>
       </c>
-      <c r="L43" s="125">
+      <c r="L43" s="126">
         <v>1.133587962962963E-3</v>
       </c>
-      <c r="M43" s="124">
+      <c r="M43" s="125">
         <v>17</v>
       </c>
-      <c r="N43" s="125">
+      <c r="N43" s="126">
         <v>1.1427777777777777E-3</v>
       </c>
       <c r="O43" s="93">
@@ -17081,10 +17088,10 @@
       <c r="P43" s="94">
         <v>1.1632407407407407E-3</v>
       </c>
-      <c r="Q43" s="124">
+      <c r="Q43" s="125">
         <v>17</v>
       </c>
-      <c r="R43" s="125">
+      <c r="R43" s="126">
         <v>1.1632407407407407E-3</v>
       </c>
       <c r="S43" s="58"/>
@@ -17094,22 +17101,22 @@
       <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="123">
+      <c r="A44" s="124">
         <v>18</v>
       </c>
-      <c r="B44" s="122">
+      <c r="B44" s="123">
         <v>1.114398148148148E-3</v>
       </c>
-      <c r="C44" s="123">
+      <c r="C44" s="124">
         <v>18</v>
       </c>
-      <c r="D44" s="122">
+      <c r="D44" s="123">
         <v>1.1069444444444445E-3</v>
       </c>
-      <c r="E44" s="123">
+      <c r="E44" s="124">
         <v>18</v>
       </c>
-      <c r="F44" s="122">
+      <c r="F44" s="123">
         <v>1.1676157407407408E-3</v>
       </c>
       <c r="G44" s="97">
@@ -17120,16 +17127,16 @@
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="124">
+      <c r="K44" s="125">
         <v>18</v>
       </c>
-      <c r="L44" s="125">
+      <c r="L44" s="126">
         <v>1.1378240740740741E-3</v>
       </c>
-      <c r="M44" s="124">
+      <c r="M44" s="125">
         <v>18</v>
       </c>
-      <c r="N44" s="125">
+      <c r="N44" s="126">
         <v>1.1362962962962963E-3</v>
       </c>
       <c r="O44" s="93">
@@ -17138,10 +17145,10 @@
       <c r="P44" s="94">
         <v>1.1319444444444443E-3</v>
       </c>
-      <c r="Q44" s="124">
+      <c r="Q44" s="125">
         <v>18</v>
       </c>
-      <c r="R44" s="125">
+      <c r="R44" s="126">
         <v>1.1319444444444443E-3</v>
       </c>
       <c r="S44" s="58"/>
@@ -17151,22 +17158,22 @@
       <c r="W44" s="1"/>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="123">
+      <c r="A45" s="124">
         <v>19</v>
       </c>
-      <c r="B45" s="122">
+      <c r="B45" s="123">
         <v>1.1236805555555555E-3</v>
       </c>
-      <c r="C45" s="123">
+      <c r="C45" s="124">
         <v>19</v>
       </c>
-      <c r="D45" s="122">
+      <c r="D45" s="123">
         <v>1.1092129629629629E-3</v>
       </c>
-      <c r="E45" s="123">
+      <c r="E45" s="124">
         <v>19</v>
       </c>
-      <c r="F45" s="122">
+      <c r="F45" s="123">
         <v>1.1594328703703703E-3</v>
       </c>
       <c r="G45" s="97">
@@ -17177,16 +17184,16 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="124">
+      <c r="K45" s="125">
         <v>19</v>
       </c>
-      <c r="L45" s="125">
+      <c r="L45" s="126">
         <v>1.1439699074074073E-3</v>
       </c>
-      <c r="M45" s="124">
+      <c r="M45" s="125">
         <v>19</v>
       </c>
-      <c r="N45" s="125">
+      <c r="N45" s="126">
         <v>1.1471990740740739E-3</v>
       </c>
       <c r="O45" s="93">
@@ -17195,10 +17202,10 @@
       <c r="P45" s="94">
         <v>1.149375E-3</v>
       </c>
-      <c r="Q45" s="124">
+      <c r="Q45" s="125">
         <v>19</v>
       </c>
-      <c r="R45" s="125">
+      <c r="R45" s="126">
         <v>1.149375E-3</v>
       </c>
       <c r="S45" s="58"/>
@@ -17208,22 +17215,22 @@
       <c r="W45" s="1"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="123">
+      <c r="A46" s="124">
         <v>20</v>
       </c>
-      <c r="B46" s="122">
+      <c r="B46" s="123">
         <v>1.1430092592592592E-3</v>
       </c>
-      <c r="C46" s="123">
+      <c r="C46" s="124">
         <v>20</v>
       </c>
-      <c r="D46" s="122">
+      <c r="D46" s="123">
         <v>1.1691319444444444E-3</v>
       </c>
-      <c r="E46" s="123">
+      <c r="E46" s="124">
         <v>20</v>
       </c>
-      <c r="F46" s="122">
+      <c r="F46" s="123">
         <v>1.2307523148148149E-3</v>
       </c>
       <c r="G46" s="97">
@@ -17234,16 +17241,16 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="126">
+      <c r="K46" s="127">
         <v>20</v>
       </c>
-      <c r="L46" s="127">
+      <c r="L46" s="128">
         <v>1.1290277777777778E-3</v>
       </c>
-      <c r="M46" s="126">
+      <c r="M46" s="127">
         <v>20</v>
       </c>
-      <c r="N46" s="127">
+      <c r="N46" s="128">
         <v>1.1019907407407408E-3</v>
       </c>
       <c r="O46" s="95">
@@ -17252,10 +17259,10 @@
       <c r="P46" s="96">
         <v>1.1516666666666665E-3</v>
       </c>
-      <c r="Q46" s="126">
+      <c r="Q46" s="127">
         <v>20</v>
       </c>
-      <c r="R46" s="127">
+      <c r="R46" s="128">
         <v>1.1516666666666665E-3</v>
       </c>
       <c r="S46" s="1"/>
@@ -17581,7 +17588,7 @@
     <row r="58" spans="1:18">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="123">
+      <c r="C58" s="124">
         <v>1</v>
       </c>
       <c r="D58" s="58">
@@ -17589,10 +17596,10 @@
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="123">
+      <c r="G58" s="124">
         <v>1</v>
       </c>
-      <c r="H58" s="122">
+      <c r="H58" s="123">
         <v>1.9796875000000001E-3</v>
       </c>
       <c r="I58" s="1"/>
@@ -17609,7 +17616,7 @@
     <row r="59" spans="1:18">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="123">
+      <c r="C59" s="124">
         <v>2</v>
       </c>
       <c r="D59" s="58">
@@ -17617,10 +17624,10 @@
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="123">
+      <c r="G59" s="124">
         <v>2</v>
       </c>
-      <c r="H59" s="122">
+      <c r="H59" s="123">
         <v>1.2236342592592594E-3</v>
       </c>
       <c r="I59" s="1"/>
@@ -17637,7 +17644,7 @@
     <row r="60" spans="1:18">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="123">
+      <c r="C60" s="124">
         <v>3</v>
       </c>
       <c r="D60" s="58">
@@ -17645,10 +17652,10 @@
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="123">
+      <c r="G60" s="124">
         <v>3</v>
       </c>
-      <c r="H60" s="122">
+      <c r="H60" s="123">
         <v>1.2050810185185185E-3</v>
       </c>
       <c r="I60" s="1"/>
@@ -17665,7 +17672,7 @@
     <row r="61" spans="1:18">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="123">
+      <c r="C61" s="124">
         <v>4</v>
       </c>
       <c r="D61" s="58">
@@ -17673,10 +17680,10 @@
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="123">
+      <c r="G61" s="124">
         <v>4</v>
       </c>
-      <c r="H61" s="122">
+      <c r="H61" s="123">
         <v>1.2027199074074073E-3</v>
       </c>
       <c r="I61" s="1"/>
@@ -17693,7 +17700,7 @@
     <row r="62" spans="1:18">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="123">
+      <c r="C62" s="124">
         <v>5</v>
       </c>
       <c r="D62" s="58">
@@ -17701,10 +17708,10 @@
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="123">
+      <c r="G62" s="124">
         <v>5</v>
       </c>
-      <c r="H62" s="122">
+      <c r="H62" s="123">
         <v>1.1896412037037036E-3</v>
       </c>
       <c r="I62" s="1"/>
@@ -17721,7 +17728,7 @@
     <row r="63" spans="1:18">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="123">
+      <c r="C63" s="124">
         <v>6</v>
       </c>
       <c r="D63" s="58">
@@ -17729,10 +17736,10 @@
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="123">
+      <c r="G63" s="124">
         <v>6</v>
       </c>
-      <c r="H63" s="122">
+      <c r="H63" s="123">
         <v>1.2009606481481483E-3</v>
       </c>
       <c r="I63" s="1"/>
@@ -17749,7 +17756,7 @@
     <row r="64" spans="1:18">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="123">
+      <c r="C64" s="124">
         <v>7</v>
       </c>
       <c r="D64" s="58">
@@ -17757,10 +17764,10 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="123">
+      <c r="G64" s="124">
         <v>7</v>
       </c>
-      <c r="H64" s="122">
+      <c r="H64" s="123">
         <v>1.1911805555555556E-3</v>
       </c>
       <c r="I64" s="1"/>
@@ -17777,7 +17784,7 @@
     <row r="65" spans="1:8">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="123">
+      <c r="C65" s="124">
         <v>8</v>
       </c>
       <c r="D65" s="58">
@@ -17785,17 +17792,17 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="123">
+      <c r="G65" s="124">
         <v>8</v>
       </c>
-      <c r="H65" s="122">
+      <c r="H65" s="123">
         <v>1.1953125E-3</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="123">
+      <c r="C66" s="124">
         <v>9</v>
       </c>
       <c r="D66" s="58">
@@ -17803,17 +17810,17 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="123">
+      <c r="G66" s="124">
         <v>9</v>
       </c>
-      <c r="H66" s="122">
+      <c r="H66" s="123">
         <v>1.2066550925925925E-3</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="123">
+      <c r="C67" s="124">
         <v>10</v>
       </c>
       <c r="D67" s="58">
@@ -17821,17 +17828,17 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="123">
+      <c r="G67" s="124">
         <v>10</v>
       </c>
-      <c r="H67" s="122">
+      <c r="H67" s="123">
         <v>1.4534606481481482E-3</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="123">
+      <c r="C68" s="124">
         <v>11</v>
       </c>
       <c r="D68" s="58">
@@ -17839,17 +17846,17 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="123">
+      <c r="G68" s="124">
         <v>11</v>
       </c>
-      <c r="H68" s="122">
+      <c r="H68" s="123">
         <v>1.9292013888888887E-3</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="123">
+      <c r="C69" s="124">
         <v>12</v>
       </c>
       <c r="D69" s="58">
@@ -17857,17 +17864,17 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="123">
+      <c r="G69" s="124">
         <v>12</v>
       </c>
-      <c r="H69" s="122">
+      <c r="H69" s="123">
         <v>1.2021874999999999E-3</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="123">
+      <c r="C70" s="124">
         <v>13</v>
       </c>
       <c r="D70" s="58">
@@ -17875,17 +17882,17 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="123">
+      <c r="G70" s="124">
         <v>13</v>
       </c>
-      <c r="H70" s="122">
+      <c r="H70" s="123">
         <v>1.2077546296296296E-3</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="123">
+      <c r="C71" s="124">
         <v>14</v>
       </c>
       <c r="D71" s="58">
@@ -17893,17 +17900,17 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="123">
+      <c r="G71" s="124">
         <v>14</v>
       </c>
-      <c r="H71" s="122">
+      <c r="H71" s="123">
         <v>1.2092245370370371E-3</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="123">
+      <c r="C72" s="124">
         <v>15</v>
       </c>
       <c r="D72" s="58">
@@ -17911,17 +17918,17 @@
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="123">
+      <c r="G72" s="124">
         <v>15</v>
       </c>
-      <c r="H72" s="122">
+      <c r="H72" s="123">
         <v>1.2027314814814815E-3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="123">
+      <c r="C73" s="124">
         <v>16</v>
       </c>
       <c r="D73" s="58">
@@ -17929,10 +17936,10 @@
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="123">
+      <c r="G73" s="124">
         <v>16</v>
       </c>
-      <c r="H73" s="122">
+      <c r="H73" s="123">
         <v>1.1990972222222223E-3</v>
       </c>
     </row>
@@ -17943,7 +17950,7 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="123"/>
+      <c r="G74" s="124"/>
       <c r="H74" s="121"/>
     </row>
     <row r="75" spans="1:8">
@@ -17953,7 +17960,7 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="123"/>
+      <c r="G75" s="124"/>
       <c r="H75" s="1"/>
     </row>
     <row r="76" spans="1:8">
@@ -17972,7 +17979,7 @@
         <f>+AVERAGE(F54:F63,F67:F73)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G76" s="123"/>
+      <c r="G76" s="124"/>
       <c r="H76" s="58">
         <f>+AVERAGE(H58:H66,H69:H73)</f>
         <v>1.2582762896825397E-3</v>
@@ -17985,8 +17992,41 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="123"/>
+      <c r="G77" s="124"/>
       <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="58">
+        <v>1.2531291335978834E-3</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="122">
+        <f>+SUM(H76-D76)</f>
+        <v>5.1471560846563184E-6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="58">
+        <f>+SMALL(D58:D73,1)</f>
+        <v>1.1767824074074074E-3</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="58">
+        <f>+SMALL(H58:H73,1)</f>
+        <v>1.1896412037037036E-3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BB64967-D6A7-45CE-9CAC-9ED2A3EC7410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C5AD90D-6419-4358-8086-15C7128998D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -425,7 +425,7 @@
     <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
     <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,6 +490,14 @@
       <color theme="1"/>
       <name val="Google Sans"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1032,7 +1040,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1286,6 +1294,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1589,7 +1603,7 @@
                   <c:v>334.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>364.25</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1711,7 +1725,7 @@
                   <c:v>302.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>360</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8937,7 +8951,7 @@
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
     </row>
-    <row r="105" spans="6:16" ht="15.75" thickBot="1">
+    <row r="105" spans="6:16">
       <c r="F105" s="105" t="s">
         <v>33</v>
       </c>
@@ -8952,7 +8966,7 @@
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
     </row>
-    <row r="106" spans="6:16" ht="16.5" thickTop="1" thickBot="1">
+    <row r="106" spans="6:16">
       <c r="F106" s="13" t="s">
         <v>34</v>
       </c>
@@ -8985,7 +8999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="6:16" ht="15.75" thickTop="1">
+    <row r="107" spans="6:16">
       <c r="F107" s="14" t="s">
         <v>9</v>
       </c>
@@ -9327,19 +9341,15 @@
       <c r="F120" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G120" s="9">
-        <v>3</v>
-      </c>
-      <c r="H120" s="6">
+      <c r="G120" s="9"/>
+      <c r="H120" s="6" t="str">
         <f>+IF(G120=1,$P$128,IF($G120=2,$P$129,IF($G120=3,$B$4,IF($G120=4,$B$5,""))))</f>
-        <v>15</v>
-      </c>
-      <c r="I120" s="9">
-        <v>1</v>
-      </c>
-      <c r="J120" s="6">
+        <v/>
+      </c>
+      <c r="I120" s="9"/>
+      <c r="J120" s="6" t="str">
         <f>+IF(I120=1,$P$128,IF($G120=2,$P$129,IF($G120=3,$B$4,IF($G120=4,$B$5,""))))</f>
-        <v>37.5</v>
+        <v/>
       </c>
       <c r="K120" s="9"/>
       <c r="L120" s="6" t="str">
@@ -9365,19 +9375,15 @@
       <c r="F121" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G121" s="10">
-        <v>3</v>
-      </c>
-      <c r="H121" s="6">
+      <c r="G121" s="10"/>
+      <c r="H121" s="6" t="str">
         <f>+IF(G121=1,$Q$128,IF($G121=2,$Q$129,IF($G121=3,$B$4,IF($G121=4,$B$5,""))))</f>
-        <v>15</v>
-      </c>
-      <c r="I121" s="10">
-        <v>2</v>
-      </c>
-      <c r="J121" s="6">
+        <v/>
+      </c>
+      <c r="I121" s="10"/>
+      <c r="J121" s="6" t="str">
         <f>+IF(I121=1,$Q$128,IF($I121=2,$Q$129,IF($G121=3,$B$4,IF($G121=4,$B$5,""))))</f>
-        <v>20.25</v>
+        <v/>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="5" t="str">
@@ -9471,19 +9477,19 @@
       </c>
       <c r="G125" s="106">
         <f>+SUM(H120:H121)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H125" s="107">
         <f>+SUM(H120:H124)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I125" s="106">
         <f>+SUM(J120:J121)</f>
-        <v>57.75</v>
+        <v>0</v>
       </c>
       <c r="J125" s="107">
         <f>+SUM(J120:J124)</f>
-        <v>57.75</v>
+        <v>0</v>
       </c>
       <c r="K125" s="106"/>
       <c r="L125" s="107">
@@ -9529,15 +9535,9 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="103">
-        <f>+SUM(G125,G114)</f>
-        <v>364.25</v>
-      </c>
+      <c r="G127" s="103"/>
       <c r="H127" s="104"/>
-      <c r="I127" s="103">
-        <f>+SUM(I125,I114)</f>
-        <v>360</v>
-      </c>
+      <c r="I127" s="103"/>
       <c r="J127" s="104"/>
       <c r="K127" s="103">
         <f>L125</f>
@@ -9569,16 +9569,16 @@
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="101">
+      <c r="G128" s="101" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="H128" s="102"/>
-      <c r="I128" s="101">
+      <c r="I128" s="123" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
-        <v>40</v>
-      </c>
-      <c r="J128" s="102"/>
+        <v/>
+      </c>
+      <c r="J128" s="124"/>
       <c r="K128" s="103"/>
       <c r="L128" s="104"/>
       <c r="M128" s="103"/>
@@ -10960,9 +10960,9 @@
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10))</f>
         <v>334.25</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="1" t="e">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10))</f>
-        <v>364.25</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -11029,9 +11029,9 @@
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(I1)-1)*13 + 10))</f>
         <v>302.25</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="1" t="e">
         <f>IF(INDEX(Hoja1!$I$1:$I$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$I$1:$I$250, (COLUMN(J1)-1)*13 + 10))</f>
-        <v>360</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -13191,13 +13191,13 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A37)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>3</v>
-      </c>
-      <c r="G38" s="1">
+        <v/>
+      </c>
+      <c r="G38" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A37)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -13217,13 +13217,13 @@
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A38)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>1</v>
-      </c>
-      <c r="G39" s="1">
+        <v/>
+      </c>
+      <c r="G39" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A38)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -13730,7 +13730,7 @@
       <c r="G15" s="58"/>
       <c r="H15" s="1" cm="1">
         <f t="array" ref="H15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(C$2:C$46&gt;0),C$2:C$46)),0)</f>
-        <v>1.0593583278218695E-3</v>
+        <v>1.0466338734567901E-3</v>
       </c>
       <c r="I15" s="1" cm="1">
         <f t="array" ref="I15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(D$2:D$46&gt;0),D$2:D$46)),0)</f>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="K15" s="1" cm="1">
         <f t="array" ref="K15">IFERROR(AVERAGE(IF(($B$2:$B$46="VR Carrera 1")*(F$2:F$46&gt;0),F$2:F$46)),0)</f>
-        <v>1.072338100749559E-3</v>
+        <v>1.0608989197530864E-3</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -13981,16 +13981,16 @@
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="123">
+      <c r="C24" s="125">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="D24" s="123">
+      <c r="D24" s="125">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="E24" s="123">
+      <c r="E24" s="125">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="F24" s="123">
+      <c r="F24" s="125">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G24" s="58"/>
@@ -14066,12 +14066,12 @@
         <v>81</v>
       </c>
       <c r="C27" s="58">
-        <v>1.2531291335978834E-3</v>
+        <v>1.1767824074074074E-3</v>
       </c>
       <c r="D27" s="58"/>
       <c r="E27" s="58"/>
       <c r="F27" s="58">
-        <v>1.2582762896825397E-3</v>
+        <v>1.1896412037037036E-3</v>
       </c>
       <c r="G27" s="58"/>
       <c r="H27" s="58"/>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="J3" s="1">
         <f>IF('Carga Tiempos'!H15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!H15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>3.3895364858906691E-5</v>
+        <v>2.1170910493827294E-5</v>
       </c>
       <c r="K3" s="58">
         <f>IF('Carga Tiempos'!I15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!I15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="L3" s="1">
         <f>IF('Carga Tiempos'!K15=MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15),0,'Carga Tiempos'!K15-MIN('Carga Tiempos'!$H15,'Carga Tiempos'!$I15,'Carga Tiempos'!$K15))</f>
-        <v>4.6875137786596193E-5</v>
+        <v>3.5435956790123586E-5</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -14994,19 +14994,19 @@
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>1.2531291335978834E-3</v>
+        <v>1.1767824074074074E-3</v>
       </c>
       <c r="D27" s="68">
         <f>+IF('Carga Tiempos'!D27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!D27,'Carga Tiempos'!D27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>-1.2531291335978834E-3</v>
+        <v>-1.1767824074074074E-3</v>
       </c>
       <c r="E27" s="63">
         <f>+IF('Carga Tiempos'!E27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!E27,'Carga Tiempos'!E27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>-1.2531291335978834E-3</v>
+        <v>-1.1767824074074074E-3</v>
       </c>
       <c r="F27" s="68">
         <f>+IF('Carga Tiempos'!F27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!F27,'Carga Tiempos'!F27-MIN('Carga Tiempos'!$C27:$F27))</f>
-        <v>5.1471560846563184E-6</v>
+        <v>1.2858796296296186E-5</v>
       </c>
       <c r="G27" s="58"/>
       <c r="H27" s="58"/>
@@ -16132,22 +16132,22 @@
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="124">
+      <c r="A27" s="126">
         <v>1</v>
       </c>
-      <c r="B27" s="123">
+      <c r="B27" s="125">
         <v>1.1538888888888888E-3</v>
       </c>
-      <c r="C27" s="124">
+      <c r="C27" s="126">
         <v>1</v>
       </c>
-      <c r="D27" s="123">
+      <c r="D27" s="125">
         <v>1.1476041666666666E-3</v>
       </c>
-      <c r="E27" s="124">
+      <c r="E27" s="126">
         <v>1</v>
       </c>
-      <c r="F27" s="123">
+      <c r="F27" s="125">
         <v>1.1644560185185187E-3</v>
       </c>
       <c r="G27" s="97">
@@ -16158,16 +16158,16 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="125">
+      <c r="K27" s="127">
         <v>1</v>
       </c>
-      <c r="L27" s="126">
+      <c r="L27" s="128">
         <v>1.4355671296296297E-3</v>
       </c>
-      <c r="M27" s="125">
+      <c r="M27" s="127">
         <v>1</v>
       </c>
-      <c r="N27" s="126">
+      <c r="N27" s="128">
         <v>1.4123148148148148E-3</v>
       </c>
       <c r="O27" s="93">
@@ -16176,10 +16176,10 @@
       <c r="P27" s="94">
         <v>1.4081597222222223E-3</v>
       </c>
-      <c r="Q27" s="125">
+      <c r="Q27" s="127">
         <v>1</v>
       </c>
-      <c r="R27" s="126">
+      <c r="R27" s="128">
         <v>1.4081597222222223E-3</v>
       </c>
       <c r="S27" s="92"/>
@@ -16189,22 +16189,22 @@
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="124">
+      <c r="A28" s="126">
         <v>2</v>
       </c>
-      <c r="B28" s="123">
+      <c r="B28" s="125">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="C28" s="124">
+      <c r="C28" s="126">
         <v>2</v>
       </c>
-      <c r="D28" s="123">
+      <c r="D28" s="125">
         <v>1.1111458333333333E-3</v>
       </c>
-      <c r="E28" s="124">
+      <c r="E28" s="126">
         <v>2</v>
       </c>
-      <c r="F28" s="123">
+      <c r="F28" s="125">
         <v>1.1378703703703703E-3</v>
       </c>
       <c r="G28" s="97">
@@ -16215,16 +16215,16 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="125">
+      <c r="K28" s="127">
         <v>2</v>
       </c>
-      <c r="L28" s="126">
+      <c r="L28" s="128">
         <v>1.1143287037037035E-3</v>
       </c>
-      <c r="M28" s="125">
+      <c r="M28" s="127">
         <v>2</v>
       </c>
-      <c r="N28" s="126">
+      <c r="N28" s="128">
         <v>1.1365393518518519E-3</v>
       </c>
       <c r="O28" s="93">
@@ -16233,10 +16233,10 @@
       <c r="P28" s="94">
         <v>1.1394212962962964E-3</v>
       </c>
-      <c r="Q28" s="125">
+      <c r="Q28" s="127">
         <v>2</v>
       </c>
-      <c r="R28" s="126">
+      <c r="R28" s="128">
         <v>1.1394212962962964E-3</v>
       </c>
       <c r="S28" s="1"/>
@@ -16246,22 +16246,22 @@
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="124">
+      <c r="A29" s="126">
         <v>3</v>
       </c>
-      <c r="B29" s="123">
+      <c r="B29" s="125">
         <v>1.110173611111111E-3</v>
       </c>
-      <c r="C29" s="124">
+      <c r="C29" s="126">
         <v>3</v>
       </c>
-      <c r="D29" s="123">
+      <c r="D29" s="125">
         <v>1.0993171296296296E-3</v>
       </c>
-      <c r="E29" s="124">
+      <c r="E29" s="126">
         <v>3</v>
       </c>
-      <c r="F29" s="123">
+      <c r="F29" s="125">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G29" s="97">
@@ -16272,16 +16272,16 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="125">
+      <c r="K29" s="127">
         <v>3</v>
       </c>
-      <c r="L29" s="126">
+      <c r="L29" s="128">
         <v>1.1773726851851852E-3</v>
       </c>
-      <c r="M29" s="125">
+      <c r="M29" s="127">
         <v>3</v>
       </c>
-      <c r="N29" s="126">
+      <c r="N29" s="128">
         <v>1.1328703703703702E-3</v>
       </c>
       <c r="O29" s="93">
@@ -16290,10 +16290,10 @@
       <c r="P29" s="94">
         <v>1.1317361111111111E-3</v>
       </c>
-      <c r="Q29" s="125">
+      <c r="Q29" s="127">
         <v>3</v>
       </c>
-      <c r="R29" s="126">
+      <c r="R29" s="128">
         <v>1.1317361111111111E-3</v>
       </c>
       <c r="S29" s="1"/>
@@ -16303,22 +16303,22 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="124">
+      <c r="A30" s="126">
         <v>4</v>
       </c>
-      <c r="B30" s="123">
+      <c r="B30" s="125">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="C30" s="124">
+      <c r="C30" s="126">
         <v>4</v>
       </c>
-      <c r="D30" s="123">
+      <c r="D30" s="125">
         <v>1.0976736111111111E-3</v>
       </c>
-      <c r="E30" s="124">
+      <c r="E30" s="126">
         <v>4</v>
       </c>
-      <c r="F30" s="123">
+      <c r="F30" s="125">
         <v>1.1532986111111112E-3</v>
       </c>
       <c r="G30" s="97">
@@ -16329,16 +16329,16 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="125">
+      <c r="K30" s="127">
         <v>4</v>
       </c>
-      <c r="L30" s="126">
+      <c r="L30" s="128">
         <v>1.1155787037037037E-3</v>
       </c>
-      <c r="M30" s="125">
+      <c r="M30" s="127">
         <v>4</v>
       </c>
-      <c r="N30" s="126">
+      <c r="N30" s="128">
         <v>1.1118055555555556E-3</v>
       </c>
       <c r="O30" s="93">
@@ -16347,10 +16347,10 @@
       <c r="P30" s="94">
         <v>2.0264583333333337E-3</v>
       </c>
-      <c r="Q30" s="125">
+      <c r="Q30" s="127">
         <v>4</v>
       </c>
-      <c r="R30" s="126">
+      <c r="R30" s="128">
         <v>2.0264583333333337E-3</v>
       </c>
       <c r="S30" s="1"/>
@@ -16360,22 +16360,22 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="124">
+      <c r="A31" s="126">
         <v>5</v>
       </c>
-      <c r="B31" s="123">
+      <c r="B31" s="125">
         <v>1.1121296296296296E-3</v>
       </c>
-      <c r="C31" s="124">
+      <c r="C31" s="126">
         <v>5</v>
       </c>
-      <c r="D31" s="123">
+      <c r="D31" s="125">
         <v>1.1186458333333335E-3</v>
       </c>
-      <c r="E31" s="124">
+      <c r="E31" s="126">
         <v>5</v>
       </c>
-      <c r="F31" s="123">
+      <c r="F31" s="125">
         <v>1.1660416666666668E-3</v>
       </c>
       <c r="G31" s="97">
@@ -16386,16 +16386,16 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="125">
+      <c r="K31" s="127">
         <v>5</v>
       </c>
-      <c r="L31" s="126">
+      <c r="L31" s="128">
         <v>1.1346180555555556E-3</v>
       </c>
-      <c r="M31" s="125">
+      <c r="M31" s="127">
         <v>5</v>
       </c>
-      <c r="N31" s="126">
+      <c r="N31" s="128">
         <v>1.0958333333333334E-3</v>
       </c>
       <c r="O31" s="93">
@@ -16404,10 +16404,10 @@
       <c r="P31" s="94">
         <v>1.198900462962963E-3</v>
       </c>
-      <c r="Q31" s="125">
+      <c r="Q31" s="127">
         <v>5</v>
       </c>
-      <c r="R31" s="126">
+      <c r="R31" s="128">
         <v>1.198900462962963E-3</v>
       </c>
       <c r="S31" s="1"/>
@@ -16417,22 +16417,22 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="124">
+      <c r="A32" s="126">
         <v>6</v>
       </c>
-      <c r="B32" s="123">
+      <c r="B32" s="125">
         <v>1.1231828703703705E-3</v>
       </c>
-      <c r="C32" s="124">
+      <c r="C32" s="126">
         <v>6</v>
       </c>
-      <c r="D32" s="123">
+      <c r="D32" s="125">
         <v>1.1192708333333332E-3</v>
       </c>
-      <c r="E32" s="124">
+      <c r="E32" s="126">
         <v>6</v>
       </c>
-      <c r="F32" s="123">
+      <c r="F32" s="125">
         <v>1.1783333333333333E-3</v>
       </c>
       <c r="G32" s="97">
@@ -16443,16 +16443,16 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="125">
+      <c r="K32" s="127">
         <v>6</v>
       </c>
-      <c r="L32" s="126">
+      <c r="L32" s="128">
         <v>1.1811458333333333E-3</v>
       </c>
-      <c r="M32" s="125">
+      <c r="M32" s="127">
         <v>6</v>
       </c>
-      <c r="N32" s="126">
+      <c r="N32" s="128">
         <v>1.1103587962962964E-3</v>
       </c>
       <c r="O32" s="93">
@@ -16461,10 +16461,10 @@
       <c r="P32" s="94">
         <v>1.3676157407407409E-3</v>
       </c>
-      <c r="Q32" s="125">
+      <c r="Q32" s="127">
         <v>6</v>
       </c>
-      <c r="R32" s="126">
+      <c r="R32" s="128">
         <v>1.3676157407407409E-3</v>
       </c>
       <c r="S32" s="1"/>
@@ -16474,22 +16474,22 @@
       <c r="W32" s="1"/>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="124">
+      <c r="A33" s="126">
         <v>7</v>
       </c>
-      <c r="B33" s="123">
+      <c r="B33" s="125">
         <v>1.1183564814814815E-3</v>
       </c>
-      <c r="C33" s="124">
+      <c r="C33" s="126">
         <v>7</v>
       </c>
-      <c r="D33" s="123">
+      <c r="D33" s="125">
         <v>1.1119675925925926E-3</v>
       </c>
-      <c r="E33" s="124">
+      <c r="E33" s="126">
         <v>7</v>
       </c>
-      <c r="F33" s="123">
+      <c r="F33" s="125">
         <v>1.1461342592592593E-3</v>
       </c>
       <c r="G33" s="97">
@@ -16500,16 +16500,16 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="125">
+      <c r="K33" s="127">
         <v>7</v>
       </c>
-      <c r="L33" s="126">
+      <c r="L33" s="128">
         <v>1.1964467592592591E-3</v>
       </c>
-      <c r="M33" s="125">
+      <c r="M33" s="127">
         <v>7</v>
       </c>
-      <c r="N33" s="126">
+      <c r="N33" s="128">
         <v>1.1330787037037036E-3</v>
       </c>
       <c r="O33" s="93">
@@ -16518,10 +16518,10 @@
       <c r="P33" s="94">
         <v>1.2607407407407407E-3</v>
       </c>
-      <c r="Q33" s="125">
+      <c r="Q33" s="127">
         <v>7</v>
       </c>
-      <c r="R33" s="126">
+      <c r="R33" s="128">
         <v>1.2607407407407407E-3</v>
       </c>
       <c r="S33" s="1"/>
@@ -16531,22 +16531,22 @@
       <c r="W33" s="1"/>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="124">
+      <c r="A34" s="126">
         <v>8</v>
       </c>
-      <c r="B34" s="123">
+      <c r="B34" s="125">
         <v>1.124398148148148E-3</v>
       </c>
-      <c r="C34" s="124">
+      <c r="C34" s="126">
         <v>8</v>
       </c>
-      <c r="D34" s="123">
+      <c r="D34" s="125">
         <v>1.1048148148148148E-3</v>
       </c>
-      <c r="E34" s="124">
+      <c r="E34" s="126">
         <v>8</v>
       </c>
-      <c r="F34" s="123">
+      <c r="F34" s="125">
         <v>1.2261226851851851E-3</v>
       </c>
       <c r="G34" s="97">
@@ -16557,16 +16557,16 @@
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="125">
+      <c r="K34" s="127">
         <v>8</v>
       </c>
-      <c r="L34" s="126">
+      <c r="L34" s="128">
         <v>1.1544097222222223E-3</v>
       </c>
-      <c r="M34" s="125">
+      <c r="M34" s="127">
         <v>8</v>
       </c>
-      <c r="N34" s="126">
+      <c r="N34" s="128">
         <v>1.1489930555555554E-3</v>
       </c>
       <c r="O34" s="93">
@@ -16575,10 +16575,10 @@
       <c r="P34" s="94">
         <v>1.1238657407407408E-3</v>
       </c>
-      <c r="Q34" s="125">
+      <c r="Q34" s="127">
         <v>8</v>
       </c>
-      <c r="R34" s="126">
+      <c r="R34" s="128">
         <v>1.1238657407407408E-3</v>
       </c>
       <c r="S34" s="1"/>
@@ -16588,22 +16588,22 @@
       <c r="W34" s="1"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="124">
+      <c r="A35" s="126">
         <v>9</v>
       </c>
-      <c r="B35" s="123">
+      <c r="B35" s="125">
         <v>1.2592476851851853E-3</v>
       </c>
-      <c r="C35" s="124">
+      <c r="C35" s="126">
         <v>9</v>
       </c>
-      <c r="D35" s="123">
+      <c r="D35" s="125">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="E35" s="124">
+      <c r="E35" s="126">
         <v>9</v>
       </c>
-      <c r="F35" s="123">
+      <c r="F35" s="125">
         <v>1.1561111111111112E-3</v>
       </c>
       <c r="G35" s="97">
@@ -16614,16 +16614,16 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="125">
+      <c r="K35" s="127">
         <v>9</v>
       </c>
-      <c r="L35" s="126">
+      <c r="L35" s="128">
         <v>1.2505092592592592E-3</v>
       </c>
-      <c r="M35" s="125">
+      <c r="M35" s="127">
         <v>9</v>
       </c>
-      <c r="N35" s="126">
+      <c r="N35" s="128">
         <v>1.1331134259259261E-3</v>
       </c>
       <c r="O35" s="93">
@@ -16632,10 +16632,10 @@
       <c r="P35" s="94">
         <v>1.2741203703703703E-3</v>
       </c>
-      <c r="Q35" s="125">
+      <c r="Q35" s="127">
         <v>9</v>
       </c>
-      <c r="R35" s="126">
+      <c r="R35" s="128">
         <v>1.2741203703703703E-3</v>
       </c>
       <c r="S35" s="1"/>
@@ -16645,22 +16645,22 @@
       <c r="W35" s="1"/>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="124">
+      <c r="A36" s="126">
         <v>10</v>
       </c>
-      <c r="B36" s="123">
+      <c r="B36" s="125">
         <v>1.1363194444444444E-3</v>
       </c>
-      <c r="C36" s="124">
+      <c r="C36" s="126">
         <v>10</v>
       </c>
-      <c r="D36" s="123">
+      <c r="D36" s="125">
         <v>1.1534143518518519E-3</v>
       </c>
-      <c r="E36" s="124">
+      <c r="E36" s="126">
         <v>10</v>
       </c>
-      <c r="F36" s="123">
+      <c r="F36" s="125">
         <v>1.1621296296296297E-3</v>
       </c>
       <c r="G36" s="97">
@@ -16671,16 +16671,16 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="125">
+      <c r="K36" s="127">
         <v>10</v>
       </c>
-      <c r="L36" s="126">
+      <c r="L36" s="128">
         <v>1.1465856481481481E-3</v>
       </c>
-      <c r="M36" s="125">
+      <c r="M36" s="127">
         <v>10</v>
       </c>
-      <c r="N36" s="126">
+      <c r="N36" s="128">
         <v>1.1556481481481481E-3</v>
       </c>
       <c r="O36" s="93">
@@ -16689,10 +16689,10 @@
       <c r="P36" s="94">
         <v>1.1596180555555557E-3</v>
       </c>
-      <c r="Q36" s="125">
+      <c r="Q36" s="127">
         <v>10</v>
       </c>
-      <c r="R36" s="126">
+      <c r="R36" s="128">
         <v>1.1596180555555557E-3</v>
       </c>
       <c r="S36" s="1"/>
@@ -16702,22 +16702,22 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="124">
+      <c r="A37" s="126">
         <v>11</v>
       </c>
-      <c r="B37" s="123">
+      <c r="B37" s="125">
         <v>1.3982291666666668E-3</v>
       </c>
-      <c r="C37" s="124">
+      <c r="C37" s="126">
         <v>11</v>
       </c>
-      <c r="D37" s="123">
+      <c r="D37" s="125">
         <v>1.2330902777777778E-3</v>
       </c>
-      <c r="E37" s="124">
+      <c r="E37" s="126">
         <v>11</v>
       </c>
-      <c r="F37" s="123">
+      <c r="F37" s="125">
         <v>1.2419907407407406E-3</v>
       </c>
       <c r="G37" s="97">
@@ -16728,16 +16728,16 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="125">
+      <c r="K37" s="127">
         <v>11</v>
       </c>
-      <c r="L37" s="126">
+      <c r="L37" s="128">
         <v>1.1611226851851852E-3</v>
       </c>
-      <c r="M37" s="125">
+      <c r="M37" s="127">
         <v>11</v>
       </c>
-      <c r="N37" s="126">
+      <c r="N37" s="128">
         <v>1.2279976851851851E-3</v>
       </c>
       <c r="O37" s="93">
@@ -16746,10 +16746,10 @@
       <c r="P37" s="94">
         <v>2.1243171296296296E-3</v>
       </c>
-      <c r="Q37" s="125">
+      <c r="Q37" s="127">
         <v>11</v>
       </c>
-      <c r="R37" s="126">
+      <c r="R37" s="128">
         <v>2.1243171296296296E-3</v>
       </c>
       <c r="S37" s="1"/>
@@ -16759,22 +16759,22 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="124">
+      <c r="A38" s="126">
         <v>12</v>
       </c>
-      <c r="B38" s="123">
+      <c r="B38" s="125">
         <v>1.5461458333333332E-3</v>
       </c>
-      <c r="C38" s="124">
+      <c r="C38" s="126">
         <v>12</v>
       </c>
-      <c r="D38" s="123">
+      <c r="D38" s="125">
         <v>1.9078009259259261E-3</v>
       </c>
-      <c r="E38" s="124">
+      <c r="E38" s="126">
         <v>12</v>
       </c>
-      <c r="F38" s="123">
+      <c r="F38" s="125">
         <v>1.4453819444444444E-3</v>
       </c>
       <c r="G38" s="97">
@@ -16785,16 +16785,16 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="125">
+      <c r="K38" s="127">
         <v>12</v>
       </c>
-      <c r="L38" s="126">
+      <c r="L38" s="128">
         <v>1.3398611111111113E-3</v>
       </c>
-      <c r="M38" s="125">
+      <c r="M38" s="127">
         <v>12</v>
       </c>
-      <c r="N38" s="126">
+      <c r="N38" s="128">
         <v>1.310949074074074E-3</v>
       </c>
       <c r="O38" s="93">
@@ -16803,10 +16803,10 @@
       <c r="P38" s="94">
         <v>1.4692245370370371E-3</v>
       </c>
-      <c r="Q38" s="125">
+      <c r="Q38" s="127">
         <v>12</v>
       </c>
-      <c r="R38" s="126">
+      <c r="R38" s="128">
         <v>1.4692245370370371E-3</v>
       </c>
       <c r="S38" s="1"/>
@@ -16816,22 +16816,22 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="124">
+      <c r="A39" s="126">
         <v>13</v>
       </c>
-      <c r="B39" s="123">
+      <c r="B39" s="125">
         <v>1.2216550925925925E-3</v>
       </c>
-      <c r="C39" s="124">
+      <c r="C39" s="126">
         <v>13</v>
       </c>
-      <c r="D39" s="123">
+      <c r="D39" s="125">
         <v>1.2544560185185185E-3</v>
       </c>
-      <c r="E39" s="124">
+      <c r="E39" s="126">
         <v>13</v>
       </c>
-      <c r="F39" s="123">
+      <c r="F39" s="125">
         <v>1.2557175925925926E-3</v>
       </c>
       <c r="G39" s="97">
@@ -16842,16 +16842,16 @@
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="125">
+      <c r="K39" s="127">
         <v>13</v>
       </c>
-      <c r="L39" s="126">
+      <c r="L39" s="128">
         <v>3.8921759259259257E-3</v>
       </c>
-      <c r="M39" s="125">
+      <c r="M39" s="127">
         <v>13</v>
       </c>
-      <c r="N39" s="126">
+      <c r="N39" s="128">
         <v>4.1754282407407408E-3</v>
       </c>
       <c r="O39" s="93">
@@ -16860,10 +16860,10 @@
       <c r="P39" s="94">
         <v>1.6091435185185184E-3</v>
       </c>
-      <c r="Q39" s="125">
+      <c r="Q39" s="127">
         <v>13</v>
       </c>
-      <c r="R39" s="126">
+      <c r="R39" s="128">
         <v>1.6091435185185184E-3</v>
       </c>
       <c r="S39" s="1"/>
@@ -16873,22 +16873,22 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23">
-      <c r="A40" s="124">
+      <c r="A40" s="126">
         <v>14</v>
       </c>
-      <c r="B40" s="123">
+      <c r="B40" s="125">
         <v>1.1457523148148147E-3</v>
       </c>
-      <c r="C40" s="124">
+      <c r="C40" s="126">
         <v>14</v>
       </c>
-      <c r="D40" s="123">
+      <c r="D40" s="125">
         <v>1.1745949074074074E-3</v>
       </c>
-      <c r="E40" s="124">
+      <c r="E40" s="126">
         <v>14</v>
       </c>
-      <c r="F40" s="123">
+      <c r="F40" s="125">
         <v>1.1743055555555556E-3</v>
       </c>
       <c r="G40" s="97">
@@ -16899,16 +16899,16 @@
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="125">
+      <c r="K40" s="127">
         <v>14</v>
       </c>
-      <c r="L40" s="126">
+      <c r="L40" s="128">
         <v>1.1608564814814815E-3</v>
       </c>
-      <c r="M40" s="125">
+      <c r="M40" s="127">
         <v>14</v>
       </c>
-      <c r="N40" s="126">
+      <c r="N40" s="128">
         <v>1.1806365740740742E-3</v>
       </c>
       <c r="O40" s="93">
@@ -16917,10 +16917,10 @@
       <c r="P40" s="94">
         <v>1.1635069444444444E-3</v>
       </c>
-      <c r="Q40" s="125">
+      <c r="Q40" s="127">
         <v>14</v>
       </c>
-      <c r="R40" s="126">
+      <c r="R40" s="128">
         <v>1.1635069444444444E-3</v>
       </c>
       <c r="S40" s="1"/>
@@ -16930,22 +16930,22 @@
       <c r="W40" s="1"/>
     </row>
     <row r="41" spans="1:23">
-      <c r="A41" s="124">
+      <c r="A41" s="126">
         <v>15</v>
       </c>
-      <c r="B41" s="123">
+      <c r="B41" s="125">
         <v>1.5789930555555557E-3</v>
       </c>
-      <c r="C41" s="124">
+      <c r="C41" s="126">
         <v>15</v>
       </c>
-      <c r="D41" s="123">
+      <c r="D41" s="125">
         <v>1.544236111111111E-3</v>
       </c>
-      <c r="E41" s="124">
+      <c r="E41" s="126">
         <v>15</v>
       </c>
-      <c r="F41" s="123">
+      <c r="F41" s="125">
         <v>1.5701967592592592E-3</v>
       </c>
       <c r="G41" s="97">
@@ -16956,16 +16956,16 @@
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="125">
+      <c r="K41" s="127">
         <v>15</v>
       </c>
-      <c r="L41" s="126">
+      <c r="L41" s="128">
         <v>1.1989930555555556E-3</v>
       </c>
-      <c r="M41" s="125">
+      <c r="M41" s="127">
         <v>15</v>
       </c>
-      <c r="N41" s="126">
+      <c r="N41" s="128">
         <v>1.1869444444444445E-3</v>
       </c>
       <c r="O41" s="93">
@@ -16974,10 +16974,10 @@
       <c r="P41" s="94">
         <v>1.1449421296296297E-3</v>
       </c>
-      <c r="Q41" s="125">
+      <c r="Q41" s="127">
         <v>15</v>
       </c>
-      <c r="R41" s="126">
+      <c r="R41" s="128">
         <v>1.1449421296296297E-3</v>
       </c>
       <c r="S41" s="1"/>
@@ -16987,22 +16987,22 @@
       <c r="W41" s="1"/>
     </row>
     <row r="42" spans="1:23">
-      <c r="A42" s="124">
+      <c r="A42" s="126">
         <v>16</v>
       </c>
-      <c r="B42" s="123">
+      <c r="B42" s="125">
         <v>1.1158217592592591E-3</v>
       </c>
-      <c r="C42" s="124">
+      <c r="C42" s="126">
         <v>16</v>
       </c>
-      <c r="D42" s="123">
+      <c r="D42" s="125">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="E42" s="124">
+      <c r="E42" s="126">
         <v>16</v>
       </c>
-      <c r="F42" s="123">
+      <c r="F42" s="125">
         <v>1.2513888888888889E-3</v>
       </c>
       <c r="G42" s="97">
@@ -17013,16 +17013,16 @@
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="125">
+      <c r="K42" s="127">
         <v>16</v>
       </c>
-      <c r="L42" s="126">
+      <c r="L42" s="128">
         <v>1.1175E-3</v>
       </c>
-      <c r="M42" s="125">
+      <c r="M42" s="127">
         <v>16</v>
       </c>
-      <c r="N42" s="126">
+      <c r="N42" s="128">
         <v>1.1115046296296296E-3</v>
       </c>
       <c r="O42" s="93">
@@ -17031,10 +17031,10 @@
       <c r="P42" s="94">
         <v>1.140324074074074E-3</v>
       </c>
-      <c r="Q42" s="125">
+      <c r="Q42" s="127">
         <v>16</v>
       </c>
-      <c r="R42" s="126">
+      <c r="R42" s="128">
         <v>1.140324074074074E-3</v>
       </c>
       <c r="S42" s="1"/>
@@ -17044,22 +17044,22 @@
       <c r="W42" s="1"/>
     </row>
     <row r="43" spans="1:23">
-      <c r="A43" s="124">
+      <c r="A43" s="126">
         <v>17</v>
       </c>
-      <c r="B43" s="123">
+      <c r="B43" s="125">
         <v>1.1162731481481481E-3</v>
       </c>
-      <c r="C43" s="124">
+      <c r="C43" s="126">
         <v>17</v>
       </c>
-      <c r="D43" s="123">
+      <c r="D43" s="125">
         <v>1.1204629629629629E-3</v>
       </c>
-      <c r="E43" s="124">
+      <c r="E43" s="126">
         <v>17</v>
       </c>
-      <c r="F43" s="123">
+      <c r="F43" s="125">
         <v>1.1524421296296296E-3</v>
       </c>
       <c r="G43" s="97">
@@ -17070,16 +17070,16 @@
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="125">
+      <c r="K43" s="127">
         <v>17</v>
       </c>
-      <c r="L43" s="126">
+      <c r="L43" s="128">
         <v>1.133587962962963E-3</v>
       </c>
-      <c r="M43" s="125">
+      <c r="M43" s="127">
         <v>17</v>
       </c>
-      <c r="N43" s="126">
+      <c r="N43" s="128">
         <v>1.1427777777777777E-3</v>
       </c>
       <c r="O43" s="93">
@@ -17088,10 +17088,10 @@
       <c r="P43" s="94">
         <v>1.1632407407407407E-3</v>
       </c>
-      <c r="Q43" s="125">
+      <c r="Q43" s="127">
         <v>17</v>
       </c>
-      <c r="R43" s="126">
+      <c r="R43" s="128">
         <v>1.1632407407407407E-3</v>
       </c>
       <c r="S43" s="58"/>
@@ -17101,22 +17101,22 @@
       <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23">
-      <c r="A44" s="124">
+      <c r="A44" s="126">
         <v>18</v>
       </c>
-      <c r="B44" s="123">
+      <c r="B44" s="125">
         <v>1.114398148148148E-3</v>
       </c>
-      <c r="C44" s="124">
+      <c r="C44" s="126">
         <v>18</v>
       </c>
-      <c r="D44" s="123">
+      <c r="D44" s="125">
         <v>1.1069444444444445E-3</v>
       </c>
-      <c r="E44" s="124">
+      <c r="E44" s="126">
         <v>18</v>
       </c>
-      <c r="F44" s="123">
+      <c r="F44" s="125">
         <v>1.1676157407407408E-3</v>
       </c>
       <c r="G44" s="97">
@@ -17127,16 +17127,16 @@
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="125">
+      <c r="K44" s="127">
         <v>18</v>
       </c>
-      <c r="L44" s="126">
+      <c r="L44" s="128">
         <v>1.1378240740740741E-3</v>
       </c>
-      <c r="M44" s="125">
+      <c r="M44" s="127">
         <v>18</v>
       </c>
-      <c r="N44" s="126">
+      <c r="N44" s="128">
         <v>1.1362962962962963E-3</v>
       </c>
       <c r="O44" s="93">
@@ -17145,10 +17145,10 @@
       <c r="P44" s="94">
         <v>1.1319444444444443E-3</v>
       </c>
-      <c r="Q44" s="125">
+      <c r="Q44" s="127">
         <v>18</v>
       </c>
-      <c r="R44" s="126">
+      <c r="R44" s="128">
         <v>1.1319444444444443E-3</v>
       </c>
       <c r="S44" s="58"/>
@@ -17158,22 +17158,22 @@
       <c r="W44" s="1"/>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="124">
+      <c r="A45" s="126">
         <v>19</v>
       </c>
-      <c r="B45" s="123">
+      <c r="B45" s="125">
         <v>1.1236805555555555E-3</v>
       </c>
-      <c r="C45" s="124">
+      <c r="C45" s="126">
         <v>19</v>
       </c>
-      <c r="D45" s="123">
+      <c r="D45" s="125">
         <v>1.1092129629629629E-3</v>
       </c>
-      <c r="E45" s="124">
+      <c r="E45" s="126">
         <v>19</v>
       </c>
-      <c r="F45" s="123">
+      <c r="F45" s="125">
         <v>1.1594328703703703E-3</v>
       </c>
       <c r="G45" s="97">
@@ -17184,16 +17184,16 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="125">
+      <c r="K45" s="127">
         <v>19</v>
       </c>
-      <c r="L45" s="126">
+      <c r="L45" s="128">
         <v>1.1439699074074073E-3</v>
       </c>
-      <c r="M45" s="125">
+      <c r="M45" s="127">
         <v>19</v>
       </c>
-      <c r="N45" s="126">
+      <c r="N45" s="128">
         <v>1.1471990740740739E-3</v>
       </c>
       <c r="O45" s="93">
@@ -17202,10 +17202,10 @@
       <c r="P45" s="94">
         <v>1.149375E-3</v>
       </c>
-      <c r="Q45" s="125">
+      <c r="Q45" s="127">
         <v>19</v>
       </c>
-      <c r="R45" s="126">
+      <c r="R45" s="128">
         <v>1.149375E-3</v>
       </c>
       <c r="S45" s="58"/>
@@ -17215,22 +17215,22 @@
       <c r="W45" s="1"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="124">
+      <c r="A46" s="126">
         <v>20</v>
       </c>
-      <c r="B46" s="123">
+      <c r="B46" s="125">
         <v>1.1430092592592592E-3</v>
       </c>
-      <c r="C46" s="124">
+      <c r="C46" s="126">
         <v>20</v>
       </c>
-      <c r="D46" s="123">
+      <c r="D46" s="125">
         <v>1.1691319444444444E-3</v>
       </c>
-      <c r="E46" s="124">
+      <c r="E46" s="126">
         <v>20</v>
       </c>
-      <c r="F46" s="123">
+      <c r="F46" s="125">
         <v>1.2307523148148149E-3</v>
       </c>
       <c r="G46" s="97">
@@ -17241,16 +17241,16 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="127">
+      <c r="K46" s="129">
         <v>20</v>
       </c>
-      <c r="L46" s="128">
+      <c r="L46" s="130">
         <v>1.1290277777777778E-3</v>
       </c>
-      <c r="M46" s="127">
+      <c r="M46" s="129">
         <v>20</v>
       </c>
-      <c r="N46" s="128">
+      <c r="N46" s="130">
         <v>1.1019907407407408E-3</v>
       </c>
       <c r="O46" s="95">
@@ -17259,10 +17259,10 @@
       <c r="P46" s="96">
         <v>1.1516666666666665E-3</v>
       </c>
-      <c r="Q46" s="127">
+      <c r="Q46" s="129">
         <v>20</v>
       </c>
-      <c r="R46" s="128">
+      <c r="R46" s="130">
         <v>1.1516666666666665E-3</v>
       </c>
       <c r="S46" s="1"/>
@@ -17588,7 +17588,7 @@
     <row r="58" spans="1:18">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="124">
+      <c r="C58" s="126">
         <v>1</v>
       </c>
       <c r="D58" s="58">
@@ -17596,10 +17596,10 @@
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="124">
+      <c r="G58" s="126">
         <v>1</v>
       </c>
-      <c r="H58" s="123">
+      <c r="H58" s="125">
         <v>1.9796875000000001E-3</v>
       </c>
       <c r="I58" s="1"/>
@@ -17616,7 +17616,7 @@
     <row r="59" spans="1:18">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="124">
+      <c r="C59" s="126">
         <v>2</v>
       </c>
       <c r="D59" s="58">
@@ -17624,10 +17624,10 @@
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="124">
+      <c r="G59" s="126">
         <v>2</v>
       </c>
-      <c r="H59" s="123">
+      <c r="H59" s="125">
         <v>1.2236342592592594E-3</v>
       </c>
       <c r="I59" s="1"/>
@@ -17644,7 +17644,7 @@
     <row r="60" spans="1:18">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="124">
+      <c r="C60" s="126">
         <v>3</v>
       </c>
       <c r="D60" s="58">
@@ -17652,10 +17652,10 @@
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="124">
+      <c r="G60" s="126">
         <v>3</v>
       </c>
-      <c r="H60" s="123">
+      <c r="H60" s="125">
         <v>1.2050810185185185E-3</v>
       </c>
       <c r="I60" s="1"/>
@@ -17672,7 +17672,7 @@
     <row r="61" spans="1:18">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="124">
+      <c r="C61" s="126">
         <v>4</v>
       </c>
       <c r="D61" s="58">
@@ -17680,10 +17680,10 @@
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="124">
+      <c r="G61" s="126">
         <v>4</v>
       </c>
-      <c r="H61" s="123">
+      <c r="H61" s="125">
         <v>1.2027199074074073E-3</v>
       </c>
       <c r="I61" s="1"/>
@@ -17700,7 +17700,7 @@
     <row r="62" spans="1:18">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="124">
+      <c r="C62" s="126">
         <v>5</v>
       </c>
       <c r="D62" s="58">
@@ -17708,10 +17708,10 @@
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="124">
+      <c r="G62" s="126">
         <v>5</v>
       </c>
-      <c r="H62" s="123">
+      <c r="H62" s="125">
         <v>1.1896412037037036E-3</v>
       </c>
       <c r="I62" s="1"/>
@@ -17728,7 +17728,7 @@
     <row r="63" spans="1:18">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="124">
+      <c r="C63" s="126">
         <v>6</v>
       </c>
       <c r="D63" s="58">
@@ -17736,10 +17736,10 @@
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="124">
+      <c r="G63" s="126">
         <v>6</v>
       </c>
-      <c r="H63" s="123">
+      <c r="H63" s="125">
         <v>1.2009606481481483E-3</v>
       </c>
       <c r="I63" s="1"/>
@@ -17756,7 +17756,7 @@
     <row r="64" spans="1:18">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="124">
+      <c r="C64" s="126">
         <v>7</v>
       </c>
       <c r="D64" s="58">
@@ -17764,10 +17764,10 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="124">
+      <c r="G64" s="126">
         <v>7</v>
       </c>
-      <c r="H64" s="123">
+      <c r="H64" s="125">
         <v>1.1911805555555556E-3</v>
       </c>
       <c r="I64" s="1"/>
@@ -17784,7 +17784,7 @@
     <row r="65" spans="1:8">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="124">
+      <c r="C65" s="126">
         <v>8</v>
       </c>
       <c r="D65" s="58">
@@ -17792,17 +17792,17 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="124">
+      <c r="G65" s="126">
         <v>8</v>
       </c>
-      <c r="H65" s="123">
+      <c r="H65" s="125">
         <v>1.1953125E-3</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="124">
+      <c r="C66" s="126">
         <v>9</v>
       </c>
       <c r="D66" s="58">
@@ -17810,17 +17810,17 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="124">
+      <c r="G66" s="126">
         <v>9</v>
       </c>
-      <c r="H66" s="123">
+      <c r="H66" s="125">
         <v>1.2066550925925925E-3</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="124">
+      <c r="C67" s="126">
         <v>10</v>
       </c>
       <c r="D67" s="58">
@@ -17828,17 +17828,17 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="124">
+      <c r="G67" s="126">
         <v>10</v>
       </c>
-      <c r="H67" s="123">
+      <c r="H67" s="125">
         <v>1.4534606481481482E-3</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="124">
+      <c r="C68" s="126">
         <v>11</v>
       </c>
       <c r="D68" s="58">
@@ -17846,17 +17846,17 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="124">
+      <c r="G68" s="126">
         <v>11</v>
       </c>
-      <c r="H68" s="123">
+      <c r="H68" s="125">
         <v>1.9292013888888887E-3</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="124">
+      <c r="C69" s="126">
         <v>12</v>
       </c>
       <c r="D69" s="58">
@@ -17864,17 +17864,17 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="124">
+      <c r="G69" s="126">
         <v>12</v>
       </c>
-      <c r="H69" s="123">
+      <c r="H69" s="125">
         <v>1.2021874999999999E-3</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="124">
+      <c r="C70" s="126">
         <v>13</v>
       </c>
       <c r="D70" s="58">
@@ -17882,17 +17882,17 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="124">
+      <c r="G70" s="126">
         <v>13</v>
       </c>
-      <c r="H70" s="123">
+      <c r="H70" s="125">
         <v>1.2077546296296296E-3</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="124">
+      <c r="C71" s="126">
         <v>14</v>
       </c>
       <c r="D71" s="58">
@@ -17900,17 +17900,17 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="124">
+      <c r="G71" s="126">
         <v>14</v>
       </c>
-      <c r="H71" s="123">
+      <c r="H71" s="125">
         <v>1.2092245370370371E-3</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="124">
+      <c r="C72" s="126">
         <v>15</v>
       </c>
       <c r="D72" s="58">
@@ -17918,17 +17918,17 @@
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="124">
+      <c r="G72" s="126">
         <v>15</v>
       </c>
-      <c r="H72" s="123">
+      <c r="H72" s="125">
         <v>1.2027314814814815E-3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="124">
+      <c r="C73" s="126">
         <v>16</v>
       </c>
       <c r="D73" s="58">
@@ -17936,10 +17936,10 @@
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="124">
+      <c r="G73" s="126">
         <v>16</v>
       </c>
-      <c r="H73" s="123">
+      <c r="H73" s="125">
         <v>1.1990972222222223E-3</v>
       </c>
     </row>
@@ -17950,7 +17950,7 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="124"/>
+      <c r="G74" s="126"/>
       <c r="H74" s="121"/>
     </row>
     <row r="75" spans="1:8">
@@ -17960,7 +17960,7 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="124"/>
+      <c r="G75" s="126"/>
       <c r="H75" s="1"/>
     </row>
     <row r="76" spans="1:8">
@@ -17979,7 +17979,7 @@
         <f>+AVERAGE(F54:F63,F67:F73)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G76" s="124"/>
+      <c r="G76" s="126"/>
       <c r="H76" s="58">
         <f>+AVERAGE(H58:H66,H69:H73)</f>
         <v>1.2582762896825397E-3</v>
@@ -17992,7 +17992,7 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="124"/>
+      <c r="G77" s="126"/>
       <c r="H77" s="1"/>
     </row>
     <row r="78" spans="1:8">

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C5AD90D-6419-4358-8086-15C7128998D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED576A2-E280-4847-A37E-F965F430434F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1131" r:id="rId9"/>
+    <pivotCache cacheId="24" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="119">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -321,6 +321,9 @@
     <t>Suma de POLE</t>
   </si>
   <si>
+    <t>Exe</t>
+  </si>
+  <si>
     <t>Clasificacion</t>
   </si>
   <si>
@@ -390,6 +393,9 @@
     <t>15</t>
   </si>
   <si>
+    <t>Carrera</t>
+  </si>
+  <si>
     <t>ROSARIO C1</t>
   </si>
   <si>
@@ -408,22 +414,41 @@
     <t>Eze C1</t>
   </si>
   <si>
+    <t>PROMEDIO</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>VILLICUM C1</t>
+  </si>
+  <si>
+    <t>Toay</t>
+  </si>
+  <si>
     <t>Mejor tiempo</t>
   </si>
   <si>
-    <t>VILLICUM C1</t>
+    <t>Promedio total</t>
+  </si>
+  <si>
+    <t>Dif promedio</t>
+  </si>
+  <si>
+    <t>Dif. record</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0&quot;Kg&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mm:ss.000"/>
     <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
     <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
+    <numFmt numFmtId="169" formatCode="&quot;+ &quot;s.000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1040,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1226,10 +1251,36 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1238,13 +1289,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1253,13 +1304,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1276,29 +1333,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2850,7 +2884,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -2950,7 +2984,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -3050,13 +3084,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.1428571428571428</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4285714285714284</c:v>
+                  <c:v>2.7777777777777777</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.4285714285714284</c:v>
+                  <c:v>3.3333333333333335</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
@@ -3150,16 +3184,16 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1.8571428571428572</c:v>
+                  <c:v>1.6666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7142857142857144</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5714285714285716</c:v>
+                  <c:v>3.625</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8571428571428572</c:v>
+                  <c:v>1.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3250,7 +3284,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4742,19 +4776,22 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46230.104097800926" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46242.104577546299" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G41" sheet="Comparativa"/>
   </cacheSource>
   <cacheFields count="7">
     <cacheField name="FECHA" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
+      <sharedItems containsBlank="1" count="10">
         <s v="CABALEN"/>
         <s v="LA PLATA"/>
         <s v="SAN JORGE"/>
         <s v="TOAY"/>
         <s v="MENDOZA"/>
         <s v="CALAFATE"/>
+        <s v="TERMAS"/>
+        <s v="ROSARIO"/>
+        <s v="VILLICUM"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -5032,7 +5069,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="4"/>
+    <n v="3"/>
     <n v="4"/>
   </r>
   <r>
@@ -5041,11 +5078,83 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="3"/>
+    <n v="4"/>
     <n v="1"/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <s v=""/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <s v=""/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <s v=""/>
+  </r>
+  <r>
+    <x v="9"/>
     <x v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -5054,7 +5163,7 @@
     <s v=""/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="9"/>
     <x v="1"/>
     <n v="0"/>
     <n v="0"/>
@@ -5063,7 +5172,7 @@
     <s v=""/>
   </r>
   <r>
-    <x v="6"/>
+    <x v="9"/>
     <x v="2"/>
     <n v="0"/>
     <n v="0"/>
@@ -5072,79 +5181,7 @@
     <s v=""/>
   </r>
   <r>
-    <x v="6"/>
-    <x v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v=""/>
-    <s v=""/>
-  </r>
-  <r>
-    <x v="6"/>
+    <x v="9"/>
     <x v="3"/>
     <n v="0"/>
     <n v="0"/>
@@ -5156,18 +5193,21 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="1131" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="8">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="4"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="9"/>
+        <item x="5"/>
         <item x="6"/>
-        <item x="5"/>
+        <item x="7"/>
+        <item x="8"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -5483,14 +5523,17 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1">
-      <items count="7">
+      <items count="10">
         <i x="0" s="1"/>
         <i x="5" s="1"/>
         <i x="1" s="1"/>
         <i x="4" s="1"/>
+        <i x="7" s="1"/>
         <i x="2" s="1"/>
+        <i x="6" s="1"/>
         <i x="3" s="1"/>
-        <i x="6" s="1"/>
+        <i x="8" s="1"/>
+        <i x="9" s="1"/>
       </items>
     </tabular>
   </data>
@@ -5807,26 +5850,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="108"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="105" t="s">
+      <c r="F1" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5841,13 +5884,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="99">
+      <c r="A2" s="105">
         <v>1</v>
       </c>
-      <c r="B2" s="99">
+      <c r="B2" s="105">
         <v>25</v>
       </c>
-      <c r="C2" s="99">
+      <c r="C2" s="105">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5887,26 +5930,26 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1"/>
-      <c r="R2" s="105" t="s">
+      <c r="R2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="115"/>
+      <c r="W2" s="115"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="115"/>
+      <c r="Z2" s="115"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="99">
+      <c r="A3" s="105">
         <v>2</v>
       </c>
-      <c r="B3" s="99">
+      <c r="B3" s="105">
         <v>18</v>
       </c>
-      <c r="C3" s="99">
+      <c r="C3" s="105">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -5975,13 +6018,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="99">
+      <c r="A4" s="105">
         <v>3</v>
       </c>
-      <c r="B4" s="99">
+      <c r="B4" s="105">
         <v>15</v>
       </c>
-      <c r="C4" s="99">
+      <c r="C4" s="105">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -6044,13 +6087,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="99">
+      <c r="A5" s="105">
         <v>4</v>
       </c>
-      <c r="B5" s="99">
+      <c r="B5" s="105">
         <v>12</v>
       </c>
-      <c r="C5" s="99">
+      <c r="C5" s="105">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -6106,17 +6149,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="105" t="s">
+      <c r="R6" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="105"/>
-      <c r="T6" s="105"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="105"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="105"/>
-      <c r="Y6" s="105"/>
-      <c r="Z6" s="105"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6178,26 +6221,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="110">
+      <c r="G8" s="120">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="110">
+      <c r="H8" s="119"/>
+      <c r="I8" s="120">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="107"/>
-      <c r="K8" s="110">
+      <c r="J8" s="119"/>
+      <c r="K8" s="120">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="107"/>
-      <c r="M8" s="110">
+      <c r="L8" s="119"/>
+      <c r="M8" s="120">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="107"/>
+      <c r="N8" s="119"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -6232,17 +6275,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="105" t="s">
+      <c r="R9" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
+      <c r="S9" s="115"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
+      <c r="V9" s="115"/>
+      <c r="W9" s="115"/>
+      <c r="X9" s="115"/>
+      <c r="Y9" s="115"/>
+      <c r="Z9" s="115"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6253,26 +6296,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="109">
+      <c r="G10" s="122">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109">
+      <c r="H10" s="122"/>
+      <c r="I10" s="122">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109">
+      <c r="J10" s="122"/>
+      <c r="K10" s="122">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109">
+      <c r="L10" s="122"/>
+      <c r="M10" s="122">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="109"/>
+      <c r="N10" s="122"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6305,26 +6348,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="101">
+      <c r="G11" s="113">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="102"/>
-      <c r="I11" s="101">
+      <c r="H11" s="114"/>
+      <c r="I11" s="113">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="102"/>
-      <c r="K11" s="101">
+      <c r="J11" s="114"/>
+      <c r="K11" s="113">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="101">
+      <c r="L11" s="114"/>
+      <c r="M11" s="113">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="102"/>
+      <c r="N11" s="114"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6347,40 +6390,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="101">
+      <c r="G12" s="113">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="102"/>
-      <c r="I12" s="101">
+      <c r="H12" s="114"/>
+      <c r="I12" s="113">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="102"/>
-      <c r="K12" s="101">
+      <c r="J12" s="114"/>
+      <c r="K12" s="113">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="102"/>
-      <c r="M12" s="101">
+      <c r="L12" s="114"/>
+      <c r="M12" s="113">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="102"/>
+      <c r="N12" s="114"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="105" t="s">
+      <c r="R12" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="105"/>
-      <c r="T12" s="105"/>
-      <c r="U12" s="105"/>
-      <c r="V12" s="105"/>
-      <c r="W12" s="105"/>
-      <c r="X12" s="105"/>
-      <c r="Y12" s="105"/>
-      <c r="Z12" s="105"/>
+      <c r="S12" s="115"/>
+      <c r="T12" s="115"/>
+      <c r="U12" s="115"/>
+      <c r="V12" s="115"/>
+      <c r="W12" s="115"/>
+      <c r="X12" s="115"/>
+      <c r="Y12" s="115"/>
+      <c r="Z12" s="115"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6426,17 +6469,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="105" t="s">
+      <c r="F14" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="115"/>
+      <c r="N14" s="115"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6667,26 +6710,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="110">
+      <c r="G21" s="120">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="107"/>
-      <c r="I21" s="106">
+      <c r="H21" s="119"/>
+      <c r="I21" s="118">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="107"/>
-      <c r="K21" s="106">
+      <c r="J21" s="119"/>
+      <c r="K21" s="118">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="107"/>
-      <c r="M21" s="106">
+      <c r="L21" s="119"/>
+      <c r="M21" s="118">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="107"/>
+      <c r="N21" s="119"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -6719,26 +6762,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="103">
+      <c r="G23" s="116">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="104"/>
-      <c r="I23" s="103">
+      <c r="H23" s="117"/>
+      <c r="I23" s="116">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="104"/>
-      <c r="K23" s="103">
+      <c r="J23" s="117"/>
+      <c r="K23" s="116">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="104"/>
-      <c r="M23" s="103">
+      <c r="L23" s="117"/>
+      <c r="M23" s="116">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="104"/>
+      <c r="N23" s="117"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6752,26 +6795,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="101">
+      <c r="G24" s="113">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="102"/>
-      <c r="I24" s="101">
+      <c r="H24" s="114"/>
+      <c r="I24" s="113">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="102"/>
-      <c r="K24" s="101">
+      <c r="J24" s="114"/>
+      <c r="K24" s="113">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="102"/>
-      <c r="M24" s="101">
+      <c r="L24" s="114"/>
+      <c r="M24" s="113">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="102"/>
+      <c r="N24" s="114"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6785,26 +6828,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="101">
+      <c r="G25" s="113">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="102"/>
-      <c r="I25" s="101">
+      <c r="H25" s="114"/>
+      <c r="I25" s="113">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="102"/>
-      <c r="K25" s="101">
+      <c r="J25" s="114"/>
+      <c r="K25" s="113">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="102"/>
-      <c r="M25" s="101">
+      <c r="L25" s="114"/>
+      <c r="M25" s="113">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="102"/>
+      <c r="N25" s="114"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6834,17 +6877,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="105" t="s">
+      <c r="F27" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="105"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="115"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -7044,26 +7087,26 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="106">
+      <c r="G34" s="118">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="107"/>
-      <c r="I34" s="106">
+      <c r="H34" s="119"/>
+      <c r="I34" s="118">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="107"/>
-      <c r="K34" s="106">
+      <c r="J34" s="119"/>
+      <c r="K34" s="118">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="107"/>
-      <c r="M34" s="106">
+      <c r="L34" s="119"/>
+      <c r="M34" s="118">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="107"/>
+      <c r="N34" s="119"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -7098,26 +7141,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="103">
+      <c r="G36" s="116">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="104"/>
-      <c r="I36" s="103">
+      <c r="H36" s="117"/>
+      <c r="I36" s="116">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="104"/>
-      <c r="K36" s="103">
+      <c r="J36" s="117"/>
+      <c r="K36" s="116">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="104"/>
-      <c r="M36" s="103">
+      <c r="L36" s="117"/>
+      <c r="M36" s="116">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="104"/>
+      <c r="N36" s="117"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7132,26 +7175,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="101">
+      <c r="G37" s="113">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="102"/>
-      <c r="I37" s="101">
+      <c r="H37" s="114"/>
+      <c r="I37" s="113">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="102"/>
-      <c r="K37" s="101">
+      <c r="J37" s="114"/>
+      <c r="K37" s="113">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="102"/>
-      <c r="M37" s="101">
+      <c r="L37" s="114"/>
+      <c r="M37" s="113">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="102"/>
+      <c r="N37" s="114"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7166,26 +7209,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="101">
+      <c r="G38" s="113">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="102"/>
-      <c r="I38" s="101">
+      <c r="H38" s="114"/>
+      <c r="I38" s="113">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="102"/>
-      <c r="K38" s="101">
+      <c r="J38" s="114"/>
+      <c r="K38" s="113">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="102"/>
-      <c r="M38" s="101">
+      <c r="L38" s="114"/>
+      <c r="M38" s="113">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="102"/>
+      <c r="N38" s="114"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7217,17 +7260,17 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="105" t="s">
+      <c r="F40" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="105"/>
-      <c r="M40" s="105"/>
-      <c r="N40" s="105"/>
+      <c r="G40" s="115"/>
+      <c r="H40" s="115"/>
+      <c r="I40" s="115"/>
+      <c r="J40" s="115"/>
+      <c r="K40" s="115"/>
+      <c r="L40" s="115"/>
+      <c r="M40" s="115"/>
+      <c r="N40" s="115"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -7438,26 +7481,26 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="106">
+      <c r="G47" s="118">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="107"/>
-      <c r="I47" s="106">
+      <c r="H47" s="119"/>
+      <c r="I47" s="118">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="107"/>
-      <c r="K47" s="106">
+      <c r="J47" s="119"/>
+      <c r="K47" s="118">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="107"/>
-      <c r="M47" s="106">
+      <c r="L47" s="119"/>
+      <c r="M47" s="118">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="107"/>
+      <c r="N47" s="119"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -7492,26 +7535,26 @@
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="103">
+      <c r="G49" s="116">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="104"/>
-      <c r="I49" s="103">
+      <c r="H49" s="117"/>
+      <c r="I49" s="116">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="104"/>
-      <c r="K49" s="103">
+      <c r="J49" s="117"/>
+      <c r="K49" s="116">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="104"/>
-      <c r="M49" s="103">
+      <c r="L49" s="117"/>
+      <c r="M49" s="116">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="104"/>
+      <c r="N49" s="117"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
     </row>
@@ -7519,26 +7562,26 @@
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="101">
+      <c r="G50" s="113">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="102"/>
-      <c r="I50" s="101">
+      <c r="H50" s="114"/>
+      <c r="I50" s="113">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="102"/>
-      <c r="K50" s="101">
+      <c r="J50" s="114"/>
+      <c r="K50" s="113">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="102"/>
-      <c r="M50" s="101">
+      <c r="L50" s="114"/>
+      <c r="M50" s="113">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="102"/>
+      <c r="N50" s="114"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
     </row>
@@ -7546,26 +7589,26 @@
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="101">
+      <c r="G51" s="113">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="102"/>
-      <c r="I51" s="101">
+      <c r="H51" s="114"/>
+      <c r="I51" s="113">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="102"/>
-      <c r="K51" s="101">
+      <c r="J51" s="114"/>
+      <c r="K51" s="113">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="102"/>
-      <c r="M51" s="101">
+      <c r="L51" s="114"/>
+      <c r="M51" s="113">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="102"/>
+      <c r="N51" s="114"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
     </row>
@@ -7583,17 +7626,17 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F53" s="105" t="s">
+      <c r="F53" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="G53" s="105"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="105"/>
-      <c r="K53" s="105"/>
-      <c r="L53" s="105"/>
-      <c r="M53" s="105"/>
-      <c r="N53" s="105"/>
+      <c r="G53" s="115"/>
+      <c r="H53" s="115"/>
+      <c r="I53" s="115"/>
+      <c r="J53" s="115"/>
+      <c r="K53" s="115"/>
+      <c r="L53" s="115"/>
+      <c r="M53" s="115"/>
+      <c r="N53" s="115"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
     </row>
@@ -7755,26 +7798,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="106">
+      <c r="G60" s="118">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="107"/>
-      <c r="I60" s="106">
+      <c r="H60" s="119"/>
+      <c r="I60" s="118">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="107"/>
-      <c r="K60" s="106">
+      <c r="J60" s="119"/>
+      <c r="K60" s="118">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="107"/>
-      <c r="M60" s="106">
+      <c r="L60" s="119"/>
+      <c r="M60" s="118">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="107"/>
+      <c r="N60" s="119"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
     </row>
@@ -7795,26 +7838,26 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="103">
+      <c r="G62" s="116">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="104"/>
-      <c r="I62" s="103">
+      <c r="H62" s="117"/>
+      <c r="I62" s="116">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="104"/>
-      <c r="K62" s="103">
+      <c r="J62" s="117"/>
+      <c r="K62" s="116">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="104"/>
-      <c r="M62" s="103">
+      <c r="L62" s="117"/>
+      <c r="M62" s="116">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="104"/>
+      <c r="N62" s="117"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
     </row>
@@ -7822,26 +7865,26 @@
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="101">
+      <c r="G63" s="113">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="102"/>
-      <c r="I63" s="101">
+      <c r="H63" s="114"/>
+      <c r="I63" s="113">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="102"/>
-      <c r="K63" s="101">
+      <c r="J63" s="114"/>
+      <c r="K63" s="113">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="102"/>
-      <c r="M63" s="101">
+      <c r="L63" s="114"/>
+      <c r="M63" s="113">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="102"/>
+      <c r="N63" s="114"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
     </row>
@@ -7849,41 +7892,41 @@
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="101">
+      <c r="G64" s="113">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="102"/>
-      <c r="I64" s="101">
+      <c r="H64" s="114"/>
+      <c r="I64" s="113">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="102"/>
-      <c r="K64" s="101">
+      <c r="J64" s="114"/>
+      <c r="K64" s="113">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="102"/>
-      <c r="M64" s="101">
+      <c r="L64" s="114"/>
+      <c r="M64" s="113">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="102"/>
+      <c r="N64" s="114"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
     </row>
     <row r="66" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F66" s="105" t="s">
+      <c r="F66" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="105"/>
-      <c r="H66" s="105"/>
-      <c r="I66" s="105"/>
-      <c r="J66" s="105"/>
-      <c r="K66" s="105"/>
-      <c r="L66" s="105"/>
-      <c r="M66" s="105"/>
-      <c r="N66" s="105"/>
+      <c r="G66" s="115"/>
+      <c r="H66" s="115"/>
+      <c r="I66" s="115"/>
+      <c r="J66" s="115"/>
+      <c r="K66" s="115"/>
+      <c r="L66" s="115"/>
+      <c r="M66" s="115"/>
+      <c r="N66" s="115"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
     </row>
@@ -8045,35 +8088,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="106">
+      <c r="G73" s="118">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="107">
+      <c r="H73" s="119">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="106">
+      <c r="I73" s="118">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="107">
+      <c r="J73" s="119">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="106">
+      <c r="K73" s="118">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="107">
+      <c r="L73" s="119">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="106">
+      <c r="M73" s="118">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="107">
+      <c r="N73" s="119">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -8097,26 +8140,26 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="103">
+      <c r="G75" s="116">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="104"/>
-      <c r="I75" s="103">
+      <c r="H75" s="117"/>
+      <c r="I75" s="116">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="104"/>
-      <c r="K75" s="103">
+      <c r="J75" s="117"/>
+      <c r="K75" s="116">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="104"/>
-      <c r="M75" s="103">
+      <c r="L75" s="117"/>
+      <c r="M75" s="116">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="104"/>
+      <c r="N75" s="117"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
     </row>
@@ -8124,26 +8167,26 @@
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="101">
+      <c r="G76" s="113">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="102"/>
-      <c r="I76" s="101">
+      <c r="H76" s="114"/>
+      <c r="I76" s="113">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="102"/>
-      <c r="K76" s="101">
+      <c r="J76" s="114"/>
+      <c r="K76" s="113">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="102"/>
-      <c r="M76" s="101">
+      <c r="L76" s="114"/>
+      <c r="M76" s="113">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="102"/>
+      <c r="N76" s="114"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
     </row>
@@ -8151,41 +8194,41 @@
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="101">
+      <c r="G77" s="113">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="102"/>
-      <c r="I77" s="101">
+      <c r="H77" s="114"/>
+      <c r="I77" s="113">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="102"/>
-      <c r="K77" s="101">
+      <c r="J77" s="114"/>
+      <c r="K77" s="113">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="102"/>
-      <c r="M77" s="101">
+      <c r="L77" s="114"/>
+      <c r="M77" s="113">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="102"/>
+      <c r="N77" s="114"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
     </row>
     <row r="79" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F79" s="105" t="s">
+      <c r="F79" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="G79" s="105"/>
-      <c r="H79" s="105"/>
-      <c r="I79" s="105"/>
-      <c r="J79" s="105"/>
-      <c r="K79" s="105"/>
-      <c r="L79" s="105"/>
-      <c r="M79" s="105"/>
-      <c r="N79" s="105"/>
+      <c r="G79" s="115"/>
+      <c r="H79" s="115"/>
+      <c r="I79" s="115"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="115"/>
+      <c r="L79" s="115"/>
+      <c r="M79" s="115"/>
+      <c r="N79" s="115"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
     </row>
@@ -8397,35 +8440,35 @@
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="106">
+      <c r="G86" s="118">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="107">
+      <c r="H86" s="119">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="106">
+      <c r="I86" s="118">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="107">
+      <c r="J86" s="119">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="106">
+      <c r="K86" s="118">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="L86" s="107">
+      <c r="L86" s="119">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="M86" s="106">
+      <c r="M86" s="118">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
-      <c r="N86" s="107">
+      <c r="N86" s="119">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
@@ -8469,26 +8512,26 @@
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="103">
+      <c r="G88" s="116">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="104"/>
-      <c r="I88" s="103">
+      <c r="H88" s="117"/>
+      <c r="I88" s="116">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="104"/>
-      <c r="K88" s="103">
+      <c r="J88" s="117"/>
+      <c r="K88" s="116">
         <f>+SUM(K86,K75)</f>
         <v>172.75</v>
       </c>
-      <c r="L88" s="104"/>
-      <c r="M88" s="103">
+      <c r="L88" s="117"/>
+      <c r="M88" s="116">
         <f>+SUM(M86,M75)</f>
         <v>209.25</v>
       </c>
-      <c r="N88" s="104"/>
+      <c r="N88" s="117"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -8506,26 +8549,26 @@
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="101">
+      <c r="G89" s="113">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="102"/>
-      <c r="I89" s="101">
+      <c r="H89" s="114"/>
+      <c r="I89" s="113">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="102"/>
-      <c r="K89" s="101">
+      <c r="J89" s="114"/>
+      <c r="K89" s="113">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L89" s="102"/>
-      <c r="M89" s="101">
+      <c r="L89" s="114"/>
+      <c r="M89" s="113">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N89" s="102"/>
+      <c r="N89" s="114"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -8543,26 +8586,26 @@
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="101">
+      <c r="G90" s="113">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="102"/>
-      <c r="I90" s="101">
+      <c r="H90" s="114"/>
+      <c r="I90" s="113">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="102"/>
-      <c r="K90" s="101">
+      <c r="J90" s="114"/>
+      <c r="K90" s="113">
         <f>+SUM(K89+K77-K50)</f>
         <v>10</v>
       </c>
-      <c r="L90" s="102"/>
-      <c r="M90" s="101">
+      <c r="L90" s="114"/>
+      <c r="M90" s="113">
         <f>+SUM(M89+M77-M50)</f>
         <v>60</v>
       </c>
-      <c r="N90" s="102"/>
+      <c r="N90" s="114"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -8600,17 +8643,17 @@
       <c r="Z91" s="1"/>
     </row>
     <row r="92" spans="6:26">
-      <c r="F92" s="105" t="s">
+      <c r="F92" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="G92" s="105"/>
-      <c r="H92" s="105"/>
-      <c r="I92" s="105"/>
-      <c r="J92" s="105"/>
-      <c r="K92" s="105"/>
-      <c r="L92" s="105"/>
-      <c r="M92" s="105"/>
-      <c r="N92" s="105"/>
+      <c r="G92" s="115"/>
+      <c r="H92" s="115"/>
+      <c r="I92" s="115"/>
+      <c r="J92" s="115"/>
+      <c r="K92" s="115"/>
+      <c r="L92" s="115"/>
+      <c r="M92" s="115"/>
+      <c r="N92" s="115"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -8822,35 +8865,35 @@
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="106">
+      <c r="G99" s="118">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="107">
+      <c r="H99" s="119">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="106">
+      <c r="I99" s="118">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="107">
+      <c r="J99" s="119">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="106">
+      <c r="K99" s="118">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="L99" s="107">
+      <c r="L99" s="119">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="M99" s="106">
+      <c r="M99" s="118">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-      <c r="N99" s="107">
+      <c r="N99" s="119">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
@@ -8874,26 +8917,26 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="103">
+      <c r="G101" s="116">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="104"/>
-      <c r="I101" s="103">
+      <c r="H101" s="117"/>
+      <c r="I101" s="116">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="104"/>
-      <c r="K101" s="103">
+      <c r="J101" s="117"/>
+      <c r="K101" s="116">
         <f>+SUM(K99,K88)</f>
         <v>196.75</v>
       </c>
-      <c r="L101" s="104"/>
-      <c r="M101" s="103">
+      <c r="L101" s="117"/>
+      <c r="M101" s="116">
         <f>+SUM(M99,M88)</f>
         <v>232.5</v>
       </c>
-      <c r="N101" s="104"/>
+      <c r="N101" s="117"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
     </row>
@@ -8901,26 +8944,26 @@
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="101">
+      <c r="G102" s="113">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="102"/>
-      <c r="I102" s="101">
+      <c r="H102" s="114"/>
+      <c r="I102" s="113">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="102"/>
-      <c r="K102" s="101">
+      <c r="J102" s="114"/>
+      <c r="K102" s="113">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="102"/>
-      <c r="M102" s="101">
+      <c r="L102" s="114"/>
+      <c r="M102" s="113">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="102"/>
+      <c r="N102" s="114"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
     </row>
@@ -8928,41 +8971,41 @@
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="101">
+      <c r="G103" s="113">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="102"/>
-      <c r="I103" s="101">
+      <c r="H103" s="114"/>
+      <c r="I103" s="113">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="102"/>
-      <c r="K103" s="101">
+      <c r="J103" s="114"/>
+      <c r="K103" s="113">
         <f>+SUM(K102+K90-K63)</f>
         <v>20</v>
       </c>
-      <c r="L103" s="102"/>
-      <c r="M103" s="101">
+      <c r="L103" s="114"/>
+      <c r="M103" s="113">
         <f>+SUM(M102+M90-M63)</f>
         <v>20</v>
       </c>
-      <c r="N103" s="102"/>
+      <c r="N103" s="114"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
     </row>
     <row r="105" spans="6:16">
-      <c r="F105" s="105" t="s">
+      <c r="F105" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="G105" s="105"/>
-      <c r="H105" s="105"/>
-      <c r="I105" s="105"/>
-      <c r="J105" s="105"/>
-      <c r="K105" s="105"/>
-      <c r="L105" s="105"/>
-      <c r="M105" s="105"/>
-      <c r="N105" s="105"/>
+      <c r="G105" s="115"/>
+      <c r="H105" s="115"/>
+      <c r="I105" s="115"/>
+      <c r="J105" s="115"/>
+      <c r="K105" s="115"/>
+      <c r="L105" s="115"/>
+      <c r="M105" s="115"/>
+      <c r="N105" s="115"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
     </row>
@@ -9118,35 +9161,35 @@
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="106">
+      <c r="G112" s="118">
         <f>+SUM(H107:H111)</f>
         <v>46.75</v>
       </c>
-      <c r="H112" s="107">
+      <c r="H112" s="119">
         <f>+SUM(H107:H111)</f>
         <v>46.75</v>
       </c>
-      <c r="I112" s="106">
+      <c r="I112" s="118">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="J112" s="107">
+      <c r="J112" s="119">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="K112" s="106">
+      <c r="K112" s="118">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="L112" s="107">
+      <c r="L112" s="119">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="M112" s="106">
+      <c r="M112" s="118">
         <f>+SUM(N107:N111)</f>
         <v>15</v>
       </c>
-      <c r="N112" s="107">
+      <c r="N112" s="119">
         <f>+SUM(N107:N111)</f>
         <v>15</v>
       </c>
@@ -9177,26 +9220,26 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="103">
+      <c r="G114" s="116">
         <f>+SUM(G112,G101)</f>
         <v>334.25</v>
       </c>
-      <c r="H114" s="104"/>
-      <c r="I114" s="103">
+      <c r="H114" s="117"/>
+      <c r="I114" s="116">
         <f>+SUM(I112,I101)</f>
         <v>302.25</v>
       </c>
-      <c r="J114" s="104"/>
-      <c r="K114" s="103">
+      <c r="J114" s="117"/>
+      <c r="K114" s="116">
         <f>+SUM(K112,K101)</f>
         <v>208.75</v>
       </c>
-      <c r="L114" s="104"/>
-      <c r="M114" s="103">
+      <c r="L114" s="117"/>
+      <c r="M114" s="116">
         <f>+SUM(M112,M101)</f>
         <v>247.5</v>
       </c>
-      <c r="N114" s="104"/>
+      <c r="N114" s="117"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
@@ -9211,26 +9254,26 @@
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="101">
+      <c r="G115" s="113">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H115" s="102"/>
-      <c r="I115" s="101">
+      <c r="H115" s="114"/>
+      <c r="I115" s="113">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J115" s="102"/>
-      <c r="K115" s="101">
+      <c r="J115" s="114"/>
+      <c r="K115" s="113">
         <f>+IF($K107=1,40,IF($K107=2,20,IF($K107=3,10,IF($K107=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L115" s="102"/>
-      <c r="M115" s="101">
+      <c r="L115" s="114"/>
+      <c r="M115" s="113">
         <f>+IF($M107=1,40,IF($M107=2,20,IF($M107=3,10,IF($M107=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N115" s="102"/>
+      <c r="N115" s="114"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
@@ -9245,26 +9288,26 @@
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="101">
+      <c r="G116" s="113">
         <f>+SUM(G115+G103-G76)</f>
         <v>100</v>
       </c>
-      <c r="H116" s="102"/>
-      <c r="I116" s="101">
+      <c r="H116" s="114"/>
+      <c r="I116" s="113">
         <f>+SUM(I115+I103-I76)</f>
         <v>70</v>
       </c>
-      <c r="J116" s="102"/>
-      <c r="K116" s="101">
+      <c r="J116" s="114"/>
+      <c r="K116" s="113">
         <f>+SUM(K115+K103-K76)</f>
         <v>20</v>
       </c>
-      <c r="L116" s="102"/>
-      <c r="M116" s="101">
+      <c r="L116" s="114"/>
+      <c r="M116" s="113">
         <f>+SUM(M115+M103-M76)</f>
         <v>10</v>
       </c>
-      <c r="N116" s="102"/>
+      <c r="N116" s="114"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
@@ -9276,17 +9319,17 @@
       <c r="W116" s="1"/>
     </row>
     <row r="118" spans="6:23">
-      <c r="F118" s="105" t="s">
+      <c r="F118" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="G118" s="105"/>
-      <c r="H118" s="105"/>
-      <c r="I118" s="105"/>
-      <c r="J118" s="105"/>
-      <c r="K118" s="105"/>
-      <c r="L118" s="105"/>
-      <c r="M118" s="105"/>
-      <c r="N118" s="105"/>
+      <c r="G118" s="115"/>
+      <c r="H118" s="115"/>
+      <c r="I118" s="115"/>
+      <c r="J118" s="115"/>
+      <c r="K118" s="115"/>
+      <c r="L118" s="115"/>
+      <c r="M118" s="115"/>
+      <c r="N118" s="115"/>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
@@ -9475,29 +9518,29 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="106">
+      <c r="G125" s="118">
         <f>+SUM(H120:H121)</f>
         <v>0</v>
       </c>
-      <c r="H125" s="107">
+      <c r="H125" s="119">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="106">
+      <c r="I125" s="118">
         <f>+SUM(J120:J121)</f>
         <v>0</v>
       </c>
-      <c r="J125" s="107">
+      <c r="J125" s="119">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="106"/>
-      <c r="L125" s="107">
+      <c r="K125" s="118"/>
+      <c r="L125" s="119">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="106"/>
-      <c r="N125" s="107">
+      <c r="M125" s="118"/>
+      <c r="N125" s="119">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -9535,20 +9578,20 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="103"/>
-      <c r="H127" s="104"/>
-      <c r="I127" s="103"/>
-      <c r="J127" s="104"/>
-      <c r="K127" s="103">
+      <c r="G127" s="116"/>
+      <c r="H127" s="117"/>
+      <c r="I127" s="116"/>
+      <c r="J127" s="117"/>
+      <c r="K127" s="116">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="104"/>
-      <c r="M127" s="103">
+      <c r="L127" s="117"/>
+      <c r="M127" s="116">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="104"/>
+      <c r="N127" s="117"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1" t="s">
         <v>9</v>
@@ -9569,20 +9612,20 @@
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="101" t="str">
+      <c r="G128" s="113" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="102"/>
+      <c r="H128" s="114"/>
       <c r="I128" s="123" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
       <c r="J128" s="124"/>
-      <c r="K128" s="103"/>
-      <c r="L128" s="104"/>
-      <c r="M128" s="103"/>
-      <c r="N128" s="104"/>
+      <c r="K128" s="116"/>
+      <c r="L128" s="117"/>
+      <c r="M128" s="116"/>
+      <c r="N128" s="117"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1">
         <v>37.5</v>
@@ -9606,26 +9649,26 @@
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="101">
+      <c r="G129" s="113">
         <f>G116</f>
         <v>100</v>
       </c>
-      <c r="H129" s="102"/>
-      <c r="I129" s="101">
+      <c r="H129" s="114"/>
+      <c r="I129" s="113">
         <f t="shared" ref="I129:N129" si="19">I116</f>
         <v>70</v>
       </c>
-      <c r="J129" s="102"/>
-      <c r="K129" s="101">
+      <c r="J129" s="114"/>
+      <c r="K129" s="113">
         <f t="shared" ref="K129:N129" si="20">K116</f>
         <v>20</v>
       </c>
-      <c r="L129" s="102"/>
-      <c r="M129" s="101">
+      <c r="L129" s="114"/>
+      <c r="M129" s="113">
         <f t="shared" ref="M129:N129" si="21">M116</f>
         <v>10</v>
       </c>
-      <c r="N129" s="102"/>
+      <c r="N129" s="114"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1">
         <v>28.125</v>
@@ -9640,13 +9683,165 @@
       </c>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
-      <c r="W129" s="1">
+      <c r="W129" s="101">
         <f>+SUM(P129-T129)</f>
         <v>7.875</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="176">
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="G77:H77"/>
     <mergeCell ref="I77:J77"/>
     <mergeCell ref="K77:L77"/>
@@ -9671,158 +9866,6 @@
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9837,7 +9880,8 @@
   <dimension ref="A1:X35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="11.42578125" customWidth="1"/>
+    <col min="1" max="4" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
     <col min="6" max="12" width="11.42578125"/>
     <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -10796,25 +10840,25 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="126"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="108"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
@@ -10829,20 +10873,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="125" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10899,7 +10943,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="111"/>
+      <c r="A4" s="125"/>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
@@ -10966,7 +11010,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="125" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -11035,7 +11079,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="111"/>
+      <c r="A6" s="125"/>
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
@@ -11102,7 +11146,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="125" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -11171,7 +11215,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="111"/>
+      <c r="A8" s="125"/>
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
@@ -11206,7 +11250,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="125" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -11243,7 +11287,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="111"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
@@ -11278,7 +11322,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="125" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -11315,7 +11359,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="111"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
@@ -11350,7 +11394,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="125" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -11387,7 +11431,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="111"/>
+      <c r="A14" s="125"/>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
@@ -11422,7 +11466,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="125" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -11459,7 +11503,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="111"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
@@ -11494,7 +11538,7 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="125" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -11519,7 +11563,7 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="111"/>
+      <c r="A18" s="125"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
@@ -11542,7 +11586,7 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="111"/>
+      <c r="A19" s="125"/>
       <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
@@ -11565,7 +11609,7 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="111"/>
+      <c r="A20" s="125"/>
       <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
@@ -11588,7 +11632,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="111"/>
+      <c r="A21" s="125"/>
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
@@ -11611,7 +11655,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="111"/>
+      <c r="A22" s="125"/>
       <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
@@ -11657,352 +11701,352 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="108" t="s">
+      <c r="A25" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="108"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="108" t="s">
+      <c r="A26" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="108"/>
-      <c r="C26" s="100" t="s">
+      <c r="B26" s="121"/>
+      <c r="C26" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="100" t="s">
+      <c r="D26" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="100" t="s">
+      <c r="E26" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="100" t="s">
+      <c r="F26" s="104" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="111" t="s">
+      <c r="A27" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="108">
+      <c r="C27" s="121">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="108">
+      <c r="D27" s="121">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="108">
+      <c r="E27" s="121">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="108">
+      <c r="F27" s="121">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="108"/>
+      <c r="G27" s="121"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="111"/>
-      <c r="B28" s="111"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
+      <c r="A28" s="125"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="121"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="121"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="111" t="s">
+      <c r="A29" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="111" t="s">
+      <c r="B29" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="108">
+      <c r="C29" s="121">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="108">
+      <c r="D29" s="121">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="108">
+      <c r="E29" s="121">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="108">
+      <c r="F29" s="121">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="108"/>
+      <c r="G29" s="121"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="111"/>
-      <c r="B30" s="111"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
+      <c r="A30" s="125"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="121"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="121"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="111" t="s">
+      <c r="A31" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="111" t="s">
+      <c r="B31" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="108">
+      <c r="C31" s="121">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="108">
+      <c r="D31" s="121">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="108">
+      <c r="E31" s="121">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="108">
+      <c r="F31" s="121">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="108"/>
+      <c r="G31" s="121"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="111"/>
-      <c r="B32" s="111"/>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
+      <c r="A32" s="125"/>
+      <c r="B32" s="125"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="121"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="111" t="s">
+      <c r="A33" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="111" t="s">
+      <c r="B33" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C33" s="121">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="108">
+      <c r="D33" s="121">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="108">
+      <c r="E33" s="121">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="108">
+      <c r="F33" s="121">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="108"/>
+      <c r="G33" s="121"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="111"/>
-      <c r="B34" s="111"/>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
+      <c r="A34" s="125"/>
+      <c r="B34" s="125"/>
+      <c r="C34" s="121"/>
+      <c r="D34" s="121"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="121"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="111" t="s">
+      <c r="A35" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="108">
+      <c r="C35" s="121">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="121">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="108">
+      <c r="E35" s="121">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="108">
+      <c r="F35" s="121">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="108"/>
+      <c r="G35" s="121"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="111"/>
-      <c r="B36" s="111"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
+      <c r="A36" s="125"/>
+      <c r="B36" s="125"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="121"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="121"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="111" t="s">
+      <c r="A37" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="111" t="s">
+      <c r="B37" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="108">
+      <c r="C37" s="121">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="108">
+      <c r="D37" s="121">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="108">
+      <c r="E37" s="121">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="108">
+      <c r="F37" s="121">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="108"/>
+      <c r="G37" s="121"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="111"/>
-      <c r="B38" s="111"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
+      <c r="A38" s="125"/>
+      <c r="B38" s="125"/>
+      <c r="C38" s="121"/>
+      <c r="D38" s="121"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="121"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="111" t="s">
+      <c r="B39" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="108">
+      <c r="C39" s="121">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="108">
+      <c r="D39" s="121">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="108">
+      <c r="E39" s="121">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="108">
+      <c r="F39" s="121">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="108"/>
+      <c r="G39" s="121"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="111"/>
-      <c r="B40" s="111"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="108"/>
-      <c r="F40" s="108"/>
-      <c r="G40" s="108"/>
+      <c r="A40" s="125"/>
+      <c r="B40" s="125"/>
+      <c r="C40" s="121"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="111" t="s">
+      <c r="A41" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="111" t="s">
+      <c r="B41" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="108">
+      <c r="C41" s="121">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="108">
+      <c r="D41" s="121">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="108">
+      <c r="E41" s="121">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="108">
+      <c r="F41" s="121">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="108"/>
+      <c r="G41" s="121"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="111"/>
-      <c r="B42" s="111"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
+      <c r="A42" s="125"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="121"/>
+      <c r="D42" s="121"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="121"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="111"/>
-      <c r="B43" s="111" t="s">
+      <c r="A43" s="125"/>
+      <c r="B43" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="108">
+      <c r="C43" s="121">
         <f>Hoja1!H109</f>
         <v>1</v>
       </c>
-      <c r="D43" s="108"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="121"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="111"/>
-      <c r="B44" s="111"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
+      <c r="A44" s="125"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="121"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="121"/>
+      <c r="F44" s="121"/>
+      <c r="G44" s="121"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="111"/>
-      <c r="B45" s="111" t="s">
+      <c r="A45" s="125"/>
+      <c r="B45" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="108">
+      <c r="C45" s="121">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="108"/>
-      <c r="E45" s="108"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="108"/>
+      <c r="D45" s="121"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="121"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="111"/>
-      <c r="B46" s="111"/>
-      <c r="C46" s="108"/>
-      <c r="D46" s="108"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
+      <c r="A46" s="125"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="121"/>
+      <c r="D46" s="121"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="121"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -12029,52 +12073,28 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="I1:S2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
@@ -12091,28 +12111,52 @@
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="I1:S2"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13175,7 +13219,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="108"/>
+      <c r="A38" s="121"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -13201,7 +13245,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="108"/>
+      <c r="A39" s="121"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -13227,7 +13271,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="108"/>
+      <c r="A40" s="121"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -13253,7 +13297,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="108"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -13315,16 +13359,16 @@
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="104" t="s">
         <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -13336,19 +13380,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="55">
+        <v>4</v>
+      </c>
+      <c r="D4" s="56">
         <v>2</v>
       </c>
-      <c r="D4" s="56">
-        <v>2.1428571428571428</v>
-      </c>
       <c r="E4" s="56">
-        <v>1.8571428571428572</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F4" s="55">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -13362,10 +13406,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="56">
-        <v>2.4285714285714284</v>
+        <v>2.7777777777777777</v>
       </c>
       <c r="E5" s="56">
-        <v>2.7142857142857144</v>
+        <v>2.75</v>
       </c>
       <c r="F5" s="55">
         <v>0</v>
@@ -13382,10 +13426,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="56">
-        <v>3.4285714285714284</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="E6" s="56">
-        <v>3.5714285714285716</v>
+        <v>3.625</v>
       </c>
       <c r="F6" s="55">
         <v>0</v>
@@ -13405,7 +13449,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="56">
-        <v>1.8571428571428572</v>
+        <v>1.875</v>
       </c>
       <c r="F7" s="55">
         <v>2</v>
@@ -13440,7 +13484,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -13450,11 +13494,11 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="125" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" s="58">
         <v>1.0631828703703704E-3</v>
@@ -13473,9 +13517,9 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="111"/>
+      <c r="A3" s="125"/>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="58">
         <v>1.0327314814814815E-3</v>
@@ -13496,9 +13540,9 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="111"/>
+      <c r="A4" s="125"/>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="58">
         <v>1.0267824074074075E-3</v>
@@ -13519,11 +13563,11 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="125" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="58"/>
@@ -13536,9 +13580,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="111"/>
+      <c r="A6" s="125"/>
       <c r="B6" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -13551,9 +13595,9 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="111"/>
+      <c r="A7" s="125"/>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
@@ -13566,11 +13610,11 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="125" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="58"/>
@@ -13583,9 +13627,9 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="111"/>
+      <c r="A9" s="125"/>
       <c r="B9" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="58"/>
       <c r="D9" s="58"/>
@@ -13598,9 +13642,9 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="111"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="58">
         <v>8.9045138888888887E-4</v>
@@ -13621,11 +13665,11 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="125" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="58">
         <v>8.6745370370370383E-4</v>
@@ -13646,9 +13690,9 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="111"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -13661,9 +13705,9 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="111"/>
+      <c r="A13" s="125"/>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -13676,11 +13720,11 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="125" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="58">
         <v>8.2178240740740736E-4</v>
@@ -13713,9 +13757,9 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="111"/>
+      <c r="A15" s="125"/>
       <c r="B15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" s="58">
         <v>8.1365740740740736E-4</v>
@@ -13746,9 +13790,9 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="111"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="58">
         <v>8.0902777777777787E-4</v>
@@ -13779,11 +13823,11 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="125" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" s="58">
         <v>9.2799768518518524E-4</v>
@@ -13809,9 +13853,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="111"/>
+      <c r="A18" s="125"/>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="58">
         <v>9.2737268518518516E-4</v>
@@ -13837,9 +13881,9 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="111"/>
+      <c r="A19" s="125"/>
       <c r="B19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="58">
         <v>9.2612268518518521E-4</v>
@@ -13865,11 +13909,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="125" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="58">
         <v>1.2464004629629628E-3</v>
@@ -13895,9 +13939,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="111"/>
+      <c r="A21" s="125"/>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="58">
         <v>1.2324652777777779E-3</v>
@@ -13921,9 +13965,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="111"/>
+      <c r="A22" s="125"/>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="58">
         <v>1.2377777777777777E-3</v>
@@ -13947,11 +13991,11 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="111" t="s">
+      <c r="A23" s="125" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="58">
         <v>1.0980555555555555E-3</v>
@@ -13977,20 +14021,20 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="111"/>
+      <c r="A24" s="125"/>
       <c r="B24" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="125">
+        <v>82</v>
+      </c>
+      <c r="C24" s="130">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="D24" s="125">
+      <c r="D24" s="130">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="E24" s="125">
+      <c r="E24" s="130">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="F24" s="125">
+      <c r="F24" s="130">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G24" s="58"/>
@@ -14005,9 +14049,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="111"/>
+      <c r="A25" s="125"/>
       <c r="B25" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="58">
         <v>1.1143287037037035E-3</v>
@@ -14033,11 +14077,11 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="111" t="s">
-        <v>33</v>
+      <c r="A26" s="125" t="s">
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="58">
         <v>1.1894212962962963E-3</v>
@@ -14061,9 +14105,9 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="111"/>
+      <c r="A27" s="125"/>
       <c r="B27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="58">
         <v>1.1767824074074074E-3</v>
@@ -14085,9 +14129,9 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="111"/>
+      <c r="A28" s="125"/>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
@@ -14105,8 +14149,8 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="111" t="s">
-        <v>36</v>
+      <c r="A29" s="125" t="s">
+        <v>21</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="58"/>
@@ -14125,7 +14169,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="111"/>
+      <c r="A30" s="125"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -14143,7 +14187,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="111"/>
+      <c r="A31" s="125"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -14204,7 +14248,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -14221,11 +14265,11 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="127" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" s="69">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -14266,9 +14310,9 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="114"/>
+      <c r="A3" s="128"/>
       <c r="B3" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="69">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -14309,9 +14353,9 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="114"/>
+      <c r="A4" s="128"/>
       <c r="B4" s="62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="69">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -14352,11 +14396,11 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="127" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="60"/>
@@ -14374,9 +14418,9 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="114"/>
+      <c r="A6" s="128"/>
       <c r="B6" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
@@ -14394,9 +14438,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="115"/>
+      <c r="A7" s="129"/>
       <c r="B7" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="61"/>
@@ -14414,11 +14458,11 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="128" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
@@ -14436,9 +14480,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="114"/>
+      <c r="A9" s="128"/>
       <c r="B9" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="68"/>
@@ -14456,9 +14500,9 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="115"/>
+      <c r="A10" s="129"/>
       <c r="B10" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="71">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -14488,11 +14532,11 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="114" t="s">
+      <c r="A11" s="128" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="69">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -14522,9 +14566,9 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="114"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="68"/>
@@ -14542,9 +14586,9 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="114"/>
+      <c r="A13" s="128"/>
       <c r="B13" s="62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="68"/>
@@ -14562,11 +14606,11 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="127" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="70">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -14596,9 +14640,9 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="114"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" s="69">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -14628,9 +14672,9 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="115"/>
+      <c r="A16" s="129"/>
       <c r="B16" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="71">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -14660,11 +14704,11 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="128" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" s="69">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -14694,9 +14738,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="114"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="69">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -14726,9 +14770,9 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="114"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="69">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -14758,11 +14802,11 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="127" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="70">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -14792,9 +14836,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="114"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="69">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -14824,9 +14868,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="114"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="69">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -14856,11 +14900,11 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="127" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="70">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
@@ -14890,9 +14934,9 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="114"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="69">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
@@ -14922,9 +14966,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="115"/>
+      <c r="A25" s="129"/>
       <c r="B25" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="71">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
@@ -14954,11 +14998,11 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="128" t="s">
         <v>72</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="69">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
@@ -14988,9 +15032,9 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="114"/>
+      <c r="A27" s="128"/>
       <c r="B27" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="69">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -15020,9 +15064,9 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="114"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="69">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -15052,11 +15096,11 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="127" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="70">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -15086,9 +15130,9 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="114"/>
+      <c r="A30" s="128"/>
       <c r="B30" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="69">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -15118,9 +15162,9 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="115"/>
+      <c r="A31" s="129"/>
       <c r="B31" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="71">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -15225,16 +15269,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34573353-DC88-4E7A-8BA7-3DB24B9880AA}">
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:X115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
@@ -15243,16 +15289,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="116" t="s">
+      <c r="K1" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1"/>
@@ -15265,22 +15311,22 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="117" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="118"/>
-      <c r="M2" s="117" t="s">
+      <c r="K2" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="118"/>
-      <c r="O2" s="117" t="s">
+      <c r="L2" s="108"/>
+      <c r="M2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="P2" s="118"/>
-      <c r="Q2" s="117" t="s">
+      <c r="N2" s="108"/>
+      <c r="O2" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="118"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="107" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" s="108"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -15304,19 +15350,19 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="M3" s="86" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" s="77">
         <v>1.2796759259259259E-3</v>
       </c>
       <c r="O3" s="86" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
       <c r="Q3" s="83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R3" s="84">
         <v>1.4428356481481482E-3</v>
@@ -15344,19 +15390,19 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N4" s="77">
         <v>1.2429976851851853E-3</v>
       </c>
       <c r="O4" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
       <c r="Q4" s="83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R4" s="81">
         <v>1.2858101851851852E-3</v>
@@ -15384,19 +15430,19 @@
         <v>1.2545601851851852E-3</v>
       </c>
       <c r="M5" s="87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N5" s="77">
         <v>1.2377777777777777E-3</v>
       </c>
       <c r="O5" s="87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
       <c r="Q5" s="83" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R5" s="81">
         <v>1.2647453703703703E-3</v>
@@ -15424,19 +15470,19 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" s="77">
         <v>1.3249884259259259E-3</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R6" s="81">
         <v>1.2908564814814816E-3</v>
@@ -15464,19 +15510,19 @@
         <v>1.260300925925926E-3</v>
       </c>
       <c r="M7" s="87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="77">
         <v>1.2426273148148149E-3</v>
       </c>
       <c r="O7" s="87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
       <c r="Q7" s="83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R7" s="81">
         <v>1.2742476851851851E-3</v>
@@ -15504,19 +15550,19 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N8" s="77">
         <v>1.2478472222222222E-3</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R8" s="81">
         <v>1.2452199074074073E-3</v>
@@ -15544,19 +15590,19 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N9" s="77">
         <v>1.248275462962963E-3</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
       <c r="Q9" s="83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" s="81">
         <v>1.2555324074074075E-3</v>
@@ -15584,19 +15630,19 @@
         <v>1.2430787037037037E-3</v>
       </c>
       <c r="M10" s="87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N10" s="77">
         <v>1.2653240740740741E-3</v>
       </c>
       <c r="O10" s="87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
       <c r="Q10" s="83" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R10" s="81">
         <v>1.2631365740740741E-3</v>
@@ -15624,19 +15670,19 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11" s="77">
         <v>1.6837615740740741E-3</v>
       </c>
       <c r="O11" s="83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
       <c r="Q11" s="83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R11" s="81">
         <v>1.4671412037037036E-3</v>
@@ -15664,19 +15710,19 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N12" s="77">
         <v>1.543287037037037E-3</v>
       </c>
       <c r="O12" s="83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
       <c r="Q12" s="83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R12" s="81">
         <v>1.5160185185185185E-3</v>
@@ -15704,19 +15750,19 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N13" s="77">
         <v>1.9202893518518521E-3</v>
       </c>
       <c r="O13" s="83" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
       <c r="Q13" s="83" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R13" s="81">
         <v>1.9527199074074074E-3</v>
@@ -15744,19 +15790,19 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N14" s="77">
         <v>1.2480787037037037E-3</v>
       </c>
       <c r="O14" s="83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
       <c r="Q14" s="83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R14" s="81">
         <v>1.2462037037037036E-3</v>
@@ -15784,19 +15830,19 @@
         <v>1.236238425925926E-3</v>
       </c>
       <c r="M15" s="87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N15" s="77">
         <v>1.241701388888889E-3</v>
       </c>
       <c r="O15" s="87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
       <c r="Q15" s="83" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R15" s="81">
         <v>1.2494560185185185E-3</v>
@@ -15824,19 +15870,19 @@
         <v>1.2310648148148148E-3</v>
       </c>
       <c r="M16" s="88" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N16" s="77">
         <v>1.2480208333333334E-3</v>
       </c>
       <c r="O16" s="88" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
       <c r="Q16" s="83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R16" s="81">
         <v>1.2403703703703704E-3</v>
@@ -15846,7 +15892,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -15864,19 +15910,19 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N17" s="80">
         <v>1.2779629629629629E-3</v>
       </c>
       <c r="O17" s="85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
       <c r="Q17" s="85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R17" s="82">
         <v>1.2507638888888889E-3</v>
@@ -15886,8 +15932,9 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="X17" s="1"/>
+    </row>
+    <row r="18" spans="1:24">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -15911,8 +15958,9 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="X18" s="1"/>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -15948,8 +15996,9 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="X19" s="1"/>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -15973,8 +16022,9 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="X20" s="1"/>
+    </row>
+    <row r="21" spans="1:24">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -16010,8 +16060,9 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="X21" s="1"/>
+    </row>
+    <row r="22" spans="1:24">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -16035,8 +16086,9 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="X22" s="1"/>
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -16060,1251 +16112,1313 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
-    </row>
-    <row r="25" spans="1:23" ht="34.5">
-      <c r="A25" s="116" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="116"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="116"/>
+      <c r="X23" s="1"/>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+    </row>
+    <row r="25" spans="1:24" ht="34.5">
+      <c r="A25" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="106"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="116" t="s">
-        <v>104</v>
-      </c>
-      <c r="L25" s="116"/>
-      <c r="M25" s="116"/>
-      <c r="N25" s="116"/>
-      <c r="O25" s="116"/>
-      <c r="P25" s="116"/>
-      <c r="Q25" s="116"/>
-      <c r="R25" s="116"/>
+      <c r="K25" s="106" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="106"/>
+      <c r="R25" s="106"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
-    </row>
-    <row r="26" spans="1:23">
-      <c r="A26" s="117" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="118"/>
-      <c r="C26" s="117" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="119" t="s">
+      <c r="X25" s="1"/>
+    </row>
+    <row r="26" spans="1:24" s="1" customFormat="1">
+      <c r="A26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="112"/>
+      <c r="C26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="112"/>
+      <c r="E26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="112"/>
+      <c r="G26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="112"/>
+      <c r="K26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="112"/>
+      <c r="M26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="N26" s="112"/>
+      <c r="O26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="R26" s="112"/>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="120"/>
-      <c r="G26" s="117" t="s">
+      <c r="B27" s="108"/>
+      <c r="C27" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="118"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="117" t="s">
-        <v>84</v>
-      </c>
-      <c r="L26" s="118"/>
-      <c r="M26" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="N26" s="118"/>
-      <c r="O26" s="119" t="s">
-        <v>86</v>
-      </c>
-      <c r="P26" s="120"/>
-      <c r="Q26" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="R26" s="118"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-    </row>
-    <row r="27" spans="1:23">
-      <c r="A27" s="126">
-        <v>1</v>
-      </c>
-      <c r="B27" s="125">
-        <v>1.1538888888888888E-3</v>
-      </c>
-      <c r="C27" s="126">
-        <v>1</v>
-      </c>
-      <c r="D27" s="125">
-        <v>1.1476041666666666E-3</v>
-      </c>
-      <c r="E27" s="126">
-        <v>1</v>
-      </c>
-      <c r="F27" s="125">
-        <v>1.1644560185185187E-3</v>
-      </c>
-      <c r="G27" s="97">
-        <v>1</v>
-      </c>
-      <c r="H27" s="98">
-        <v>1.1644560185185187E-3</v>
-      </c>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" s="110"/>
+      <c r="G27" s="107" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="108"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="127">
-        <v>1</v>
-      </c>
-      <c r="L27" s="128">
-        <v>1.4355671296296297E-3</v>
-      </c>
-      <c r="M27" s="127">
-        <v>1</v>
-      </c>
-      <c r="N27" s="128">
-        <v>1.4123148148148148E-3</v>
-      </c>
-      <c r="O27" s="93">
-        <v>1</v>
-      </c>
-      <c r="P27" s="94">
-        <v>1.4081597222222223E-3</v>
-      </c>
-      <c r="Q27" s="127">
-        <v>1</v>
-      </c>
-      <c r="R27" s="128">
-        <v>1.4081597222222223E-3</v>
-      </c>
-      <c r="S27" s="92"/>
+      <c r="K27" s="107" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" s="108"/>
+      <c r="M27" s="107" t="s">
+        <v>86</v>
+      </c>
+      <c r="N27" s="108"/>
+      <c r="O27" s="109" t="s">
+        <v>87</v>
+      </c>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="107" t="s">
+        <v>88</v>
+      </c>
+      <c r="R27" s="108"/>
+      <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:23">
-      <c r="A28" s="126">
-        <v>2</v>
-      </c>
-      <c r="B28" s="125">
-        <v>1.1098379629629629E-3</v>
-      </c>
-      <c r="C28" s="126">
-        <v>2</v>
-      </c>
-      <c r="D28" s="125">
-        <v>1.1111458333333333E-3</v>
-      </c>
-      <c r="E28" s="126">
-        <v>2</v>
-      </c>
-      <c r="F28" s="125">
-        <v>1.1378703703703703E-3</v>
+      <c r="X27" s="1"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" s="131">
+        <v>1</v>
+      </c>
+      <c r="B28" s="130">
+        <v>1.1538888888888888E-3</v>
+      </c>
+      <c r="C28" s="131">
+        <v>1</v>
+      </c>
+      <c r="D28" s="130">
+        <v>1.1476041666666666E-3</v>
+      </c>
+      <c r="E28" s="131">
+        <v>1</v>
+      </c>
+      <c r="F28" s="130">
+        <v>1.1644560185185187E-3</v>
       </c>
       <c r="G28" s="97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="98">
-        <v>1.1378703703703703E-3</v>
+        <v>1.1644560185185187E-3</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="127">
-        <v>2</v>
-      </c>
-      <c r="L28" s="128">
-        <v>1.1143287037037035E-3</v>
-      </c>
-      <c r="M28" s="127">
-        <v>2</v>
-      </c>
-      <c r="N28" s="128">
-        <v>1.1365393518518519E-3</v>
+      <c r="K28" s="132">
+        <v>1</v>
+      </c>
+      <c r="L28" s="133">
+        <v>1.4355671296296297E-3</v>
+      </c>
+      <c r="M28" s="132">
+        <v>1</v>
+      </c>
+      <c r="N28" s="133">
+        <v>1.4123148148148148E-3</v>
       </c>
       <c r="O28" s="93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" s="94">
-        <v>1.1394212962962964E-3</v>
-      </c>
-      <c r="Q28" s="127">
-        <v>2</v>
-      </c>
-      <c r="R28" s="128">
-        <v>1.1394212962962964E-3</v>
-      </c>
-      <c r="S28" s="1"/>
+        <v>1.4081597222222223E-3</v>
+      </c>
+      <c r="Q28" s="132">
+        <v>1</v>
+      </c>
+      <c r="R28" s="133">
+        <v>1.4081597222222223E-3</v>
+      </c>
+      <c r="S28" s="92"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-    </row>
-    <row r="29" spans="1:23">
-      <c r="A29" s="126">
-        <v>3</v>
-      </c>
-      <c r="B29" s="125">
-        <v>1.110173611111111E-3</v>
-      </c>
-      <c r="C29" s="126">
-        <v>3</v>
-      </c>
-      <c r="D29" s="125">
-        <v>1.0993171296296296E-3</v>
-      </c>
-      <c r="E29" s="126">
-        <v>3</v>
-      </c>
-      <c r="F29" s="125">
-        <v>1.1312268518518518E-3</v>
+      <c r="X28" s="1"/>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29" s="131">
+        <v>2</v>
+      </c>
+      <c r="B29" s="130">
+        <v>1.1098379629629629E-3</v>
+      </c>
+      <c r="C29" s="131">
+        <v>2</v>
+      </c>
+      <c r="D29" s="130">
+        <v>1.1111458333333333E-3</v>
+      </c>
+      <c r="E29" s="131">
+        <v>2</v>
+      </c>
+      <c r="F29" s="130">
+        <v>1.1378703703703703E-3</v>
       </c>
       <c r="G29" s="97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="98">
-        <v>1.1312268518518518E-3</v>
+        <v>1.1378703703703703E-3</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="127">
-        <v>3</v>
-      </c>
-      <c r="L29" s="128">
-        <v>1.1773726851851852E-3</v>
-      </c>
-      <c r="M29" s="127">
-        <v>3</v>
-      </c>
-      <c r="N29" s="128">
-        <v>1.1328703703703702E-3</v>
+      <c r="K29" s="132">
+        <v>2</v>
+      </c>
+      <c r="L29" s="133">
+        <v>1.1143287037037035E-3</v>
+      </c>
+      <c r="M29" s="132">
+        <v>2</v>
+      </c>
+      <c r="N29" s="133">
+        <v>1.1365393518518519E-3</v>
       </c>
       <c r="O29" s="93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" s="94">
-        <v>1.1317361111111111E-3</v>
-      </c>
-      <c r="Q29" s="127">
-        <v>3</v>
-      </c>
-      <c r="R29" s="128">
-        <v>1.1317361111111111E-3</v>
+        <v>1.1394212962962964E-3</v>
+      </c>
+      <c r="Q29" s="132">
+        <v>2</v>
+      </c>
+      <c r="R29" s="133">
+        <v>1.1394212962962964E-3</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-    </row>
-    <row r="30" spans="1:23">
-      <c r="A30" s="126">
-        <v>4</v>
-      </c>
-      <c r="B30" s="125">
-        <v>1.1127083333333334E-3</v>
-      </c>
-      <c r="C30" s="126">
-        <v>4</v>
-      </c>
-      <c r="D30" s="125">
-        <v>1.0976736111111111E-3</v>
-      </c>
-      <c r="E30" s="126">
-        <v>4</v>
-      </c>
-      <c r="F30" s="125">
-        <v>1.1532986111111112E-3</v>
+      <c r="X29" s="1"/>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30" s="131">
+        <v>3</v>
+      </c>
+      <c r="B30" s="130">
+        <v>1.110173611111111E-3</v>
+      </c>
+      <c r="C30" s="131">
+        <v>3</v>
+      </c>
+      <c r="D30" s="130">
+        <v>1.0993171296296296E-3</v>
+      </c>
+      <c r="E30" s="131">
+        <v>3</v>
+      </c>
+      <c r="F30" s="130">
+        <v>1.1312268518518518E-3</v>
       </c>
       <c r="G30" s="97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="98">
-        <v>1.1532986111111112E-3</v>
+        <v>1.1312268518518518E-3</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="127">
-        <v>4</v>
-      </c>
-      <c r="L30" s="128">
-        <v>1.1155787037037037E-3</v>
-      </c>
-      <c r="M30" s="127">
-        <v>4</v>
-      </c>
-      <c r="N30" s="128">
-        <v>1.1118055555555556E-3</v>
+      <c r="K30" s="132">
+        <v>3</v>
+      </c>
+      <c r="L30" s="133">
+        <v>1.1773726851851852E-3</v>
+      </c>
+      <c r="M30" s="132">
+        <v>3</v>
+      </c>
+      <c r="N30" s="133">
+        <v>1.1328703703703702E-3</v>
       </c>
       <c r="O30" s="93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" s="94">
-        <v>2.0264583333333337E-3</v>
-      </c>
-      <c r="Q30" s="127">
-        <v>4</v>
-      </c>
-      <c r="R30" s="128">
-        <v>2.0264583333333337E-3</v>
+        <v>1.1317361111111111E-3</v>
+      </c>
+      <c r="Q30" s="132">
+        <v>3</v>
+      </c>
+      <c r="R30" s="133">
+        <v>1.1317361111111111E-3</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-    </row>
-    <row r="31" spans="1:23">
-      <c r="A31" s="126">
-        <v>5</v>
-      </c>
-      <c r="B31" s="125">
-        <v>1.1121296296296296E-3</v>
-      </c>
-      <c r="C31" s="126">
-        <v>5</v>
-      </c>
-      <c r="D31" s="125">
-        <v>1.1186458333333335E-3</v>
-      </c>
-      <c r="E31" s="126">
-        <v>5</v>
-      </c>
-      <c r="F31" s="125">
-        <v>1.1660416666666668E-3</v>
+      <c r="X30" s="1"/>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" s="131">
+        <v>4</v>
+      </c>
+      <c r="B31" s="130">
+        <v>1.1127083333333334E-3</v>
+      </c>
+      <c r="C31" s="131">
+        <v>4</v>
+      </c>
+      <c r="D31" s="130">
+        <v>1.0976736111111111E-3</v>
+      </c>
+      <c r="E31" s="131">
+        <v>4</v>
+      </c>
+      <c r="F31" s="130">
+        <v>1.1532986111111112E-3</v>
       </c>
       <c r="G31" s="97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" s="98">
-        <v>1.1660416666666668E-3</v>
+        <v>1.1532986111111112E-3</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="127">
-        <v>5</v>
-      </c>
-      <c r="L31" s="128">
-        <v>1.1346180555555556E-3</v>
-      </c>
-      <c r="M31" s="127">
-        <v>5</v>
-      </c>
-      <c r="N31" s="128">
-        <v>1.0958333333333334E-3</v>
+      <c r="K31" s="132">
+        <v>4</v>
+      </c>
+      <c r="L31" s="133">
+        <v>1.1155787037037037E-3</v>
+      </c>
+      <c r="M31" s="132">
+        <v>4</v>
+      </c>
+      <c r="N31" s="133">
+        <v>1.1118055555555556E-3</v>
       </c>
       <c r="O31" s="93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P31" s="94">
-        <v>1.198900462962963E-3</v>
-      </c>
-      <c r="Q31" s="127">
-        <v>5</v>
-      </c>
-      <c r="R31" s="128">
-        <v>1.198900462962963E-3</v>
+        <v>2.0264583333333337E-3</v>
+      </c>
+      <c r="Q31" s="132">
+        <v>4</v>
+      </c>
+      <c r="R31" s="133">
+        <v>2.0264583333333337E-3</v>
       </c>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
-    </row>
-    <row r="32" spans="1:23">
-      <c r="A32" s="126">
-        <v>6</v>
-      </c>
-      <c r="B32" s="125">
-        <v>1.1231828703703705E-3</v>
-      </c>
-      <c r="C32" s="126">
-        <v>6</v>
-      </c>
-      <c r="D32" s="125">
-        <v>1.1192708333333332E-3</v>
-      </c>
-      <c r="E32" s="126">
-        <v>6</v>
-      </c>
-      <c r="F32" s="125">
-        <v>1.1783333333333333E-3</v>
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="A32" s="131">
+        <v>5</v>
+      </c>
+      <c r="B32" s="130">
+        <v>1.1121296296296296E-3</v>
+      </c>
+      <c r="C32" s="131">
+        <v>5</v>
+      </c>
+      <c r="D32" s="130">
+        <v>1.1186458333333335E-3</v>
+      </c>
+      <c r="E32" s="131">
+        <v>5</v>
+      </c>
+      <c r="F32" s="130">
+        <v>1.1660416666666668E-3</v>
       </c>
       <c r="G32" s="97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32" s="98">
-        <v>1.1783333333333333E-3</v>
+        <v>1.1660416666666668E-3</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="127">
-        <v>6</v>
-      </c>
-      <c r="L32" s="128">
-        <v>1.1811458333333333E-3</v>
-      </c>
-      <c r="M32" s="127">
-        <v>6</v>
-      </c>
-      <c r="N32" s="128">
-        <v>1.1103587962962964E-3</v>
+      <c r="K32" s="132">
+        <v>5</v>
+      </c>
+      <c r="L32" s="133">
+        <v>1.1346180555555556E-3</v>
+      </c>
+      <c r="M32" s="132">
+        <v>5</v>
+      </c>
+      <c r="N32" s="133">
+        <v>1.0958333333333334E-3</v>
       </c>
       <c r="O32" s="93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P32" s="94">
-        <v>1.3676157407407409E-3</v>
-      </c>
-      <c r="Q32" s="127">
-        <v>6</v>
-      </c>
-      <c r="R32" s="128">
-        <v>1.3676157407407409E-3</v>
+        <v>1.198900462962963E-3</v>
+      </c>
+      <c r="Q32" s="132">
+        <v>5</v>
+      </c>
+      <c r="R32" s="133">
+        <v>1.198900462962963E-3</v>
       </c>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
-    </row>
-    <row r="33" spans="1:23">
-      <c r="A33" s="126">
-        <v>7</v>
-      </c>
-      <c r="B33" s="125">
-        <v>1.1183564814814815E-3</v>
-      </c>
-      <c r="C33" s="126">
-        <v>7</v>
-      </c>
-      <c r="D33" s="125">
-        <v>1.1119675925925926E-3</v>
-      </c>
-      <c r="E33" s="126">
-        <v>7</v>
-      </c>
-      <c r="F33" s="125">
-        <v>1.1461342592592593E-3</v>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24">
+      <c r="A33" s="131">
+        <v>6</v>
+      </c>
+      <c r="B33" s="130">
+        <v>1.1231828703703705E-3</v>
+      </c>
+      <c r="C33" s="131">
+        <v>6</v>
+      </c>
+      <c r="D33" s="130">
+        <v>1.1192708333333332E-3</v>
+      </c>
+      <c r="E33" s="131">
+        <v>6</v>
+      </c>
+      <c r="F33" s="130">
+        <v>1.1783333333333333E-3</v>
       </c>
       <c r="G33" s="97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H33" s="98">
-        <v>1.1461342592592593E-3</v>
+        <v>1.1783333333333333E-3</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="127">
-        <v>7</v>
-      </c>
-      <c r="L33" s="128">
-        <v>1.1964467592592591E-3</v>
-      </c>
-      <c r="M33" s="127">
-        <v>7</v>
-      </c>
-      <c r="N33" s="128">
-        <v>1.1330787037037036E-3</v>
+      <c r="K33" s="132">
+        <v>6</v>
+      </c>
+      <c r="L33" s="133">
+        <v>1.1811458333333333E-3</v>
+      </c>
+      <c r="M33" s="132">
+        <v>6</v>
+      </c>
+      <c r="N33" s="133">
+        <v>1.1103587962962964E-3</v>
       </c>
       <c r="O33" s="93">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P33" s="94">
-        <v>1.2607407407407407E-3</v>
-      </c>
-      <c r="Q33" s="127">
-        <v>7</v>
-      </c>
-      <c r="R33" s="128">
-        <v>1.2607407407407407E-3</v>
+        <v>1.3676157407407409E-3</v>
+      </c>
+      <c r="Q33" s="132">
+        <v>6</v>
+      </c>
+      <c r="R33" s="133">
+        <v>1.3676157407407409E-3</v>
       </c>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
-    </row>
-    <row r="34" spans="1:23">
-      <c r="A34" s="126">
-        <v>8</v>
-      </c>
-      <c r="B34" s="125">
-        <v>1.124398148148148E-3</v>
-      </c>
-      <c r="C34" s="126">
-        <v>8</v>
-      </c>
-      <c r="D34" s="125">
-        <v>1.1048148148148148E-3</v>
-      </c>
-      <c r="E34" s="126">
-        <v>8</v>
-      </c>
-      <c r="F34" s="125">
-        <v>1.2261226851851851E-3</v>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24">
+      <c r="A34" s="131">
+        <v>7</v>
+      </c>
+      <c r="B34" s="130">
+        <v>1.1183564814814815E-3</v>
+      </c>
+      <c r="C34" s="131">
+        <v>7</v>
+      </c>
+      <c r="D34" s="130">
+        <v>1.1119675925925926E-3</v>
+      </c>
+      <c r="E34" s="131">
+        <v>7</v>
+      </c>
+      <c r="F34" s="130">
+        <v>1.1461342592592593E-3</v>
       </c>
       <c r="G34" s="97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34" s="98">
-        <v>1.2261226851851851E-3</v>
+        <v>1.1461342592592593E-3</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="127">
-        <v>8</v>
-      </c>
-      <c r="L34" s="128">
-        <v>1.1544097222222223E-3</v>
-      </c>
-      <c r="M34" s="127">
-        <v>8</v>
-      </c>
-      <c r="N34" s="128">
-        <v>1.1489930555555554E-3</v>
+      <c r="K34" s="132">
+        <v>7</v>
+      </c>
+      <c r="L34" s="133">
+        <v>1.1964467592592591E-3</v>
+      </c>
+      <c r="M34" s="132">
+        <v>7</v>
+      </c>
+      <c r="N34" s="133">
+        <v>1.1330787037037036E-3</v>
       </c>
       <c r="O34" s="93">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P34" s="94">
-        <v>1.1238657407407408E-3</v>
-      </c>
-      <c r="Q34" s="127">
-        <v>8</v>
-      </c>
-      <c r="R34" s="128">
-        <v>1.1238657407407408E-3</v>
+        <v>1.2607407407407407E-3</v>
+      </c>
+      <c r="Q34" s="132">
+        <v>7</v>
+      </c>
+      <c r="R34" s="133">
+        <v>1.2607407407407407E-3</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
-    </row>
-    <row r="35" spans="1:23">
-      <c r="A35" s="126">
-        <v>9</v>
-      </c>
-      <c r="B35" s="125">
-        <v>1.2592476851851853E-3</v>
-      </c>
-      <c r="C35" s="126">
-        <v>9</v>
-      </c>
-      <c r="D35" s="125">
-        <v>1.0967939814814816E-3</v>
-      </c>
-      <c r="E35" s="126">
-        <v>9</v>
-      </c>
-      <c r="F35" s="125">
-        <v>1.1561111111111112E-3</v>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24">
+      <c r="A35" s="131">
+        <v>8</v>
+      </c>
+      <c r="B35" s="130">
+        <v>1.124398148148148E-3</v>
+      </c>
+      <c r="C35" s="131">
+        <v>8</v>
+      </c>
+      <c r="D35" s="130">
+        <v>1.1048148148148148E-3</v>
+      </c>
+      <c r="E35" s="131">
+        <v>8</v>
+      </c>
+      <c r="F35" s="130">
+        <v>1.2261226851851851E-3</v>
       </c>
       <c r="G35" s="97">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H35" s="98">
-        <v>1.1561111111111112E-3</v>
+        <v>1.2261226851851851E-3</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="127">
-        <v>9</v>
-      </c>
-      <c r="L35" s="128">
-        <v>1.2505092592592592E-3</v>
-      </c>
-      <c r="M35" s="127">
-        <v>9</v>
-      </c>
-      <c r="N35" s="128">
-        <v>1.1331134259259261E-3</v>
+      <c r="K35" s="132">
+        <v>8</v>
+      </c>
+      <c r="L35" s="133">
+        <v>1.1544097222222223E-3</v>
+      </c>
+      <c r="M35" s="132">
+        <v>8</v>
+      </c>
+      <c r="N35" s="133">
+        <v>1.1489930555555554E-3</v>
       </c>
       <c r="O35" s="93">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P35" s="94">
-        <v>1.2741203703703703E-3</v>
-      </c>
-      <c r="Q35" s="127">
-        <v>9</v>
-      </c>
-      <c r="R35" s="128">
-        <v>1.2741203703703703E-3</v>
+        <v>1.1238657407407408E-3</v>
+      </c>
+      <c r="Q35" s="132">
+        <v>8</v>
+      </c>
+      <c r="R35" s="133">
+        <v>1.1238657407407408E-3</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="126">
-        <v>10</v>
-      </c>
-      <c r="B36" s="125">
-        <v>1.1363194444444444E-3</v>
-      </c>
-      <c r="C36" s="126">
-        <v>10</v>
-      </c>
-      <c r="D36" s="125">
-        <v>1.1534143518518519E-3</v>
-      </c>
-      <c r="E36" s="126">
-        <v>10</v>
-      </c>
-      <c r="F36" s="125">
-        <v>1.1621296296296297E-3</v>
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="1:24">
+      <c r="A36" s="131">
+        <v>9</v>
+      </c>
+      <c r="B36" s="130">
+        <v>1.2592476851851853E-3</v>
+      </c>
+      <c r="C36" s="131">
+        <v>9</v>
+      </c>
+      <c r="D36" s="130">
+        <v>1.0967939814814816E-3</v>
+      </c>
+      <c r="E36" s="131">
+        <v>9</v>
+      </c>
+      <c r="F36" s="130">
+        <v>1.1561111111111112E-3</v>
       </c>
       <c r="G36" s="97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H36" s="98">
-        <v>1.1621296296296297E-3</v>
+        <v>1.1561111111111112E-3</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="127">
-        <v>10</v>
-      </c>
-      <c r="L36" s="128">
-        <v>1.1465856481481481E-3</v>
-      </c>
-      <c r="M36" s="127">
-        <v>10</v>
-      </c>
-      <c r="N36" s="128">
-        <v>1.1556481481481481E-3</v>
+      <c r="K36" s="132">
+        <v>9</v>
+      </c>
+      <c r="L36" s="133">
+        <v>1.2505092592592592E-3</v>
+      </c>
+      <c r="M36" s="132">
+        <v>9</v>
+      </c>
+      <c r="N36" s="133">
+        <v>1.1331134259259261E-3</v>
       </c>
       <c r="O36" s="93">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P36" s="94">
-        <v>1.1596180555555557E-3</v>
-      </c>
-      <c r="Q36" s="127">
-        <v>10</v>
-      </c>
-      <c r="R36" s="128">
-        <v>1.1596180555555557E-3</v>
+        <v>1.2741203703703703E-3</v>
+      </c>
+      <c r="Q36" s="132">
+        <v>9</v>
+      </c>
+      <c r="R36" s="133">
+        <v>1.2741203703703703E-3</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="126">
-        <v>11</v>
-      </c>
-      <c r="B37" s="125">
-        <v>1.3982291666666668E-3</v>
-      </c>
-      <c r="C37" s="126">
-        <v>11</v>
-      </c>
-      <c r="D37" s="125">
-        <v>1.2330902777777778E-3</v>
-      </c>
-      <c r="E37" s="126">
-        <v>11</v>
-      </c>
-      <c r="F37" s="125">
-        <v>1.2419907407407406E-3</v>
+      <c r="X36" s="1"/>
+    </row>
+    <row r="37" spans="1:24">
+      <c r="A37" s="131">
+        <v>10</v>
+      </c>
+      <c r="B37" s="130">
+        <v>1.1363194444444444E-3</v>
+      </c>
+      <c r="C37" s="131">
+        <v>10</v>
+      </c>
+      <c r="D37" s="130">
+        <v>1.1534143518518519E-3</v>
+      </c>
+      <c r="E37" s="131">
+        <v>10</v>
+      </c>
+      <c r="F37" s="130">
+        <v>1.1621296296296297E-3</v>
       </c>
       <c r="G37" s="97">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H37" s="98">
-        <v>1.2419907407407406E-3</v>
+        <v>1.1621296296296297E-3</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="127">
-        <v>11</v>
-      </c>
-      <c r="L37" s="128">
-        <v>1.1611226851851852E-3</v>
-      </c>
-      <c r="M37" s="127">
-        <v>11</v>
-      </c>
-      <c r="N37" s="128">
-        <v>1.2279976851851851E-3</v>
+      <c r="K37" s="132">
+        <v>10</v>
+      </c>
+      <c r="L37" s="133">
+        <v>1.1465856481481481E-3</v>
+      </c>
+      <c r="M37" s="132">
+        <v>10</v>
+      </c>
+      <c r="N37" s="133">
+        <v>1.1556481481481481E-3</v>
       </c>
       <c r="O37" s="93">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P37" s="94">
-        <v>2.1243171296296296E-3</v>
-      </c>
-      <c r="Q37" s="127">
-        <v>11</v>
-      </c>
-      <c r="R37" s="128">
-        <v>2.1243171296296296E-3</v>
+        <v>1.1596180555555557E-3</v>
+      </c>
+      <c r="Q37" s="132">
+        <v>10</v>
+      </c>
+      <c r="R37" s="133">
+        <v>1.1596180555555557E-3</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
-    </row>
-    <row r="38" spans="1:23">
-      <c r="A38" s="126">
-        <v>12</v>
-      </c>
-      <c r="B38" s="125">
-        <v>1.5461458333333332E-3</v>
-      </c>
-      <c r="C38" s="126">
-        <v>12</v>
-      </c>
-      <c r="D38" s="125">
-        <v>1.9078009259259261E-3</v>
-      </c>
-      <c r="E38" s="126">
-        <v>12</v>
-      </c>
-      <c r="F38" s="125">
-        <v>1.4453819444444444E-3</v>
+      <c r="X37" s="1"/>
+    </row>
+    <row r="38" spans="1:24">
+      <c r="A38" s="131">
+        <v>11</v>
+      </c>
+      <c r="B38" s="130">
+        <v>1.3982291666666668E-3</v>
+      </c>
+      <c r="C38" s="131">
+        <v>11</v>
+      </c>
+      <c r="D38" s="130">
+        <v>1.2330902777777778E-3</v>
+      </c>
+      <c r="E38" s="131">
+        <v>11</v>
+      </c>
+      <c r="F38" s="130">
+        <v>1.2419907407407406E-3</v>
       </c>
       <c r="G38" s="97">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H38" s="98">
-        <v>1.4453819444444444E-3</v>
+        <v>1.2419907407407406E-3</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="127">
-        <v>12</v>
-      </c>
-      <c r="L38" s="128">
-        <v>1.3398611111111113E-3</v>
-      </c>
-      <c r="M38" s="127">
-        <v>12</v>
-      </c>
-      <c r="N38" s="128">
-        <v>1.310949074074074E-3</v>
+      <c r="K38" s="132">
+        <v>11</v>
+      </c>
+      <c r="L38" s="133">
+        <v>1.1611226851851852E-3</v>
+      </c>
+      <c r="M38" s="132">
+        <v>11</v>
+      </c>
+      <c r="N38" s="133">
+        <v>1.2279976851851851E-3</v>
       </c>
       <c r="O38" s="93">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P38" s="94">
-        <v>1.4692245370370371E-3</v>
-      </c>
-      <c r="Q38" s="127">
-        <v>12</v>
-      </c>
-      <c r="R38" s="128">
-        <v>1.4692245370370371E-3</v>
+        <v>2.1243171296296296E-3</v>
+      </c>
+      <c r="Q38" s="132">
+        <v>11</v>
+      </c>
+      <c r="R38" s="133">
+        <v>2.1243171296296296E-3</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="126">
-        <v>13</v>
-      </c>
-      <c r="B39" s="125">
-        <v>1.2216550925925925E-3</v>
-      </c>
-      <c r="C39" s="126">
-        <v>13</v>
-      </c>
-      <c r="D39" s="125">
-        <v>1.2544560185185185E-3</v>
-      </c>
-      <c r="E39" s="126">
-        <v>13</v>
-      </c>
-      <c r="F39" s="125">
-        <v>1.2557175925925926E-3</v>
+      <c r="X38" s="1"/>
+    </row>
+    <row r="39" spans="1:24">
+      <c r="A39" s="131">
+        <v>12</v>
+      </c>
+      <c r="B39" s="130">
+        <v>1.5461458333333332E-3</v>
+      </c>
+      <c r="C39" s="131">
+        <v>12</v>
+      </c>
+      <c r="D39" s="130">
+        <v>1.9078009259259261E-3</v>
+      </c>
+      <c r="E39" s="131">
+        <v>12</v>
+      </c>
+      <c r="F39" s="130">
+        <v>1.4453819444444444E-3</v>
       </c>
       <c r="G39" s="97">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="98">
-        <v>1.2557175925925926E-3</v>
+        <v>1.4453819444444444E-3</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="127">
-        <v>13</v>
-      </c>
-      <c r="L39" s="128">
-        <v>3.8921759259259257E-3</v>
-      </c>
-      <c r="M39" s="127">
-        <v>13</v>
-      </c>
-      <c r="N39" s="128">
-        <v>4.1754282407407408E-3</v>
+      <c r="K39" s="132">
+        <v>12</v>
+      </c>
+      <c r="L39" s="133">
+        <v>1.3398611111111113E-3</v>
+      </c>
+      <c r="M39" s="132">
+        <v>12</v>
+      </c>
+      <c r="N39" s="133">
+        <v>1.310949074074074E-3</v>
       </c>
       <c r="O39" s="93">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P39" s="94">
-        <v>1.6091435185185184E-3</v>
-      </c>
-      <c r="Q39" s="127">
-        <v>13</v>
-      </c>
-      <c r="R39" s="128">
-        <v>1.6091435185185184E-3</v>
+        <v>1.4692245370370371E-3</v>
+      </c>
+      <c r="Q39" s="132">
+        <v>12</v>
+      </c>
+      <c r="R39" s="133">
+        <v>1.4692245370370371E-3</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="126">
-        <v>14</v>
-      </c>
-      <c r="B40" s="125">
-        <v>1.1457523148148147E-3</v>
-      </c>
-      <c r="C40" s="126">
-        <v>14</v>
-      </c>
-      <c r="D40" s="125">
-        <v>1.1745949074074074E-3</v>
-      </c>
-      <c r="E40" s="126">
-        <v>14</v>
-      </c>
-      <c r="F40" s="125">
-        <v>1.1743055555555556E-3</v>
+      <c r="X39" s="1"/>
+    </row>
+    <row r="40" spans="1:24">
+      <c r="A40" s="131">
+        <v>13</v>
+      </c>
+      <c r="B40" s="130">
+        <v>1.2216550925925925E-3</v>
+      </c>
+      <c r="C40" s="131">
+        <v>13</v>
+      </c>
+      <c r="D40" s="130">
+        <v>1.2544560185185185E-3</v>
+      </c>
+      <c r="E40" s="131">
+        <v>13</v>
+      </c>
+      <c r="F40" s="130">
+        <v>1.2557175925925926E-3</v>
       </c>
       <c r="G40" s="97">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="98">
-        <v>1.1743055555555556E-3</v>
+        <v>1.2557175925925926E-3</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="127">
-        <v>14</v>
-      </c>
-      <c r="L40" s="128">
-        <v>1.1608564814814815E-3</v>
-      </c>
-      <c r="M40" s="127">
-        <v>14</v>
-      </c>
-      <c r="N40" s="128">
-        <v>1.1806365740740742E-3</v>
+      <c r="K40" s="132">
+        <v>13</v>
+      </c>
+      <c r="L40" s="133">
+        <v>3.8921759259259257E-3</v>
+      </c>
+      <c r="M40" s="132">
+        <v>13</v>
+      </c>
+      <c r="N40" s="133">
+        <v>4.1754282407407408E-3</v>
       </c>
       <c r="O40" s="93">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P40" s="94">
-        <v>1.1635069444444444E-3</v>
-      </c>
-      <c r="Q40" s="127">
-        <v>14</v>
-      </c>
-      <c r="R40" s="128">
-        <v>1.1635069444444444E-3</v>
+        <v>1.6091435185185184E-3</v>
+      </c>
+      <c r="Q40" s="132">
+        <v>13</v>
+      </c>
+      <c r="R40" s="133">
+        <v>1.6091435185185184E-3</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="126">
-        <v>15</v>
-      </c>
-      <c r="B41" s="125">
-        <v>1.5789930555555557E-3</v>
-      </c>
-      <c r="C41" s="126">
-        <v>15</v>
-      </c>
-      <c r="D41" s="125">
-        <v>1.544236111111111E-3</v>
-      </c>
-      <c r="E41" s="126">
-        <v>15</v>
-      </c>
-      <c r="F41" s="125">
-        <v>1.5701967592592592E-3</v>
+      <c r="X40" s="1"/>
+    </row>
+    <row r="41" spans="1:24">
+      <c r="A41" s="131">
+        <v>14</v>
+      </c>
+      <c r="B41" s="130">
+        <v>1.1457523148148147E-3</v>
+      </c>
+      <c r="C41" s="131">
+        <v>14</v>
+      </c>
+      <c r="D41" s="130">
+        <v>1.1745949074074074E-3</v>
+      </c>
+      <c r="E41" s="131">
+        <v>14</v>
+      </c>
+      <c r="F41" s="130">
+        <v>1.1743055555555556E-3</v>
       </c>
       <c r="G41" s="97">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" s="98">
-        <v>1.5701967592592592E-3</v>
+        <v>1.1743055555555556E-3</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="127">
-        <v>15</v>
-      </c>
-      <c r="L41" s="128">
-        <v>1.1989930555555556E-3</v>
-      </c>
-      <c r="M41" s="127">
-        <v>15</v>
-      </c>
-      <c r="N41" s="128">
-        <v>1.1869444444444445E-3</v>
+      <c r="K41" s="132">
+        <v>14</v>
+      </c>
+      <c r="L41" s="133">
+        <v>1.1608564814814815E-3</v>
+      </c>
+      <c r="M41" s="132">
+        <v>14</v>
+      </c>
+      <c r="N41" s="133">
+        <v>1.1806365740740742E-3</v>
       </c>
       <c r="O41" s="93">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P41" s="94">
-        <v>1.1449421296296297E-3</v>
-      </c>
-      <c r="Q41" s="127">
-        <v>15</v>
-      </c>
-      <c r="R41" s="128">
-        <v>1.1449421296296297E-3</v>
+        <v>1.1635069444444444E-3</v>
+      </c>
+      <c r="Q41" s="132">
+        <v>14</v>
+      </c>
+      <c r="R41" s="133">
+        <v>1.1635069444444444E-3</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="126">
-        <v>16</v>
-      </c>
-      <c r="B42" s="125">
-        <v>1.1158217592592591E-3</v>
-      </c>
-      <c r="C42" s="126">
-        <v>16</v>
-      </c>
-      <c r="D42" s="125">
-        <v>1.1127083333333334E-3</v>
-      </c>
-      <c r="E42" s="126">
-        <v>16</v>
-      </c>
-      <c r="F42" s="125">
-        <v>1.2513888888888889E-3</v>
+      <c r="X41" s="1"/>
+    </row>
+    <row r="42" spans="1:24">
+      <c r="A42" s="131">
+        <v>15</v>
+      </c>
+      <c r="B42" s="130">
+        <v>1.5789930555555557E-3</v>
+      </c>
+      <c r="C42" s="131">
+        <v>15</v>
+      </c>
+      <c r="D42" s="130">
+        <v>1.544236111111111E-3</v>
+      </c>
+      <c r="E42" s="131">
+        <v>15</v>
+      </c>
+      <c r="F42" s="130">
+        <v>1.5701967592592592E-3</v>
       </c>
       <c r="G42" s="97">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H42" s="98">
-        <v>1.2513888888888889E-3</v>
+        <v>1.5701967592592592E-3</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="127">
-        <v>16</v>
-      </c>
-      <c r="L42" s="128">
-        <v>1.1175E-3</v>
-      </c>
-      <c r="M42" s="127">
-        <v>16</v>
-      </c>
-      <c r="N42" s="128">
-        <v>1.1115046296296296E-3</v>
+      <c r="K42" s="132">
+        <v>15</v>
+      </c>
+      <c r="L42" s="133">
+        <v>1.1989930555555556E-3</v>
+      </c>
+      <c r="M42" s="132">
+        <v>15</v>
+      </c>
+      <c r="N42" s="133">
+        <v>1.1869444444444445E-3</v>
       </c>
       <c r="O42" s="93">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P42" s="94">
-        <v>1.140324074074074E-3</v>
-      </c>
-      <c r="Q42" s="127">
-        <v>16</v>
-      </c>
-      <c r="R42" s="128">
-        <v>1.140324074074074E-3</v>
+        <v>1.1449421296296297E-3</v>
+      </c>
+      <c r="Q42" s="132">
+        <v>15</v>
+      </c>
+      <c r="R42" s="133">
+        <v>1.1449421296296297E-3</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="126">
-        <v>17</v>
-      </c>
-      <c r="B43" s="125">
-        <v>1.1162731481481481E-3</v>
-      </c>
-      <c r="C43" s="126">
-        <v>17</v>
-      </c>
-      <c r="D43" s="125">
-        <v>1.1204629629629629E-3</v>
-      </c>
-      <c r="E43" s="126">
-        <v>17</v>
-      </c>
-      <c r="F43" s="125">
-        <v>1.1524421296296296E-3</v>
+      <c r="X42" s="1"/>
+    </row>
+    <row r="43" spans="1:24">
+      <c r="A43" s="131">
+        <v>16</v>
+      </c>
+      <c r="B43" s="130">
+        <v>1.1158217592592591E-3</v>
+      </c>
+      <c r="C43" s="131">
+        <v>16</v>
+      </c>
+      <c r="D43" s="130">
+        <v>1.1127083333333334E-3</v>
+      </c>
+      <c r="E43" s="131">
+        <v>16</v>
+      </c>
+      <c r="F43" s="130">
+        <v>1.2513888888888889E-3</v>
       </c>
       <c r="G43" s="97">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H43" s="98">
-        <v>1.1524421296296296E-3</v>
+        <v>1.2513888888888889E-3</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="127">
-        <v>17</v>
-      </c>
-      <c r="L43" s="128">
-        <v>1.133587962962963E-3</v>
-      </c>
-      <c r="M43" s="127">
-        <v>17</v>
-      </c>
-      <c r="N43" s="128">
-        <v>1.1427777777777777E-3</v>
+      <c r="K43" s="132">
+        <v>16</v>
+      </c>
+      <c r="L43" s="133">
+        <v>1.1175E-3</v>
+      </c>
+      <c r="M43" s="132">
+        <v>16</v>
+      </c>
+      <c r="N43" s="133">
+        <v>1.1115046296296296E-3</v>
       </c>
       <c r="O43" s="93">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P43" s="94">
-        <v>1.1632407407407407E-3</v>
-      </c>
-      <c r="Q43" s="127">
-        <v>17</v>
-      </c>
-      <c r="R43" s="128">
-        <v>1.1632407407407407E-3</v>
-      </c>
-      <c r="S43" s="58"/>
+        <v>1.140324074074074E-3</v>
+      </c>
+      <c r="Q43" s="132">
+        <v>16</v>
+      </c>
+      <c r="R43" s="133">
+        <v>1.140324074074074E-3</v>
+      </c>
+      <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="126">
-        <v>18</v>
-      </c>
-      <c r="B44" s="125">
-        <v>1.114398148148148E-3</v>
-      </c>
-      <c r="C44" s="126">
-        <v>18</v>
-      </c>
-      <c r="D44" s="125">
-        <v>1.1069444444444445E-3</v>
-      </c>
-      <c r="E44" s="126">
-        <v>18</v>
-      </c>
-      <c r="F44" s="125">
-        <v>1.1676157407407408E-3</v>
+      <c r="X43" s="1"/>
+    </row>
+    <row r="44" spans="1:24">
+      <c r="A44" s="131">
+        <v>17</v>
+      </c>
+      <c r="B44" s="130">
+        <v>1.1162731481481481E-3</v>
+      </c>
+      <c r="C44" s="131">
+        <v>17</v>
+      </c>
+      <c r="D44" s="130">
+        <v>1.1204629629629629E-3</v>
+      </c>
+      <c r="E44" s="131">
+        <v>17</v>
+      </c>
+      <c r="F44" s="130">
+        <v>1.1524421296296296E-3</v>
       </c>
       <c r="G44" s="97">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H44" s="98">
-        <v>1.1676157407407408E-3</v>
+        <v>1.1524421296296296E-3</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="127">
-        <v>18</v>
-      </c>
-      <c r="L44" s="128">
-        <v>1.1378240740740741E-3</v>
-      </c>
-      <c r="M44" s="127">
-        <v>18</v>
-      </c>
-      <c r="N44" s="128">
-        <v>1.1362962962962963E-3</v>
+      <c r="K44" s="132">
+        <v>17</v>
+      </c>
+      <c r="L44" s="133">
+        <v>1.133587962962963E-3</v>
+      </c>
+      <c r="M44" s="132">
+        <v>17</v>
+      </c>
+      <c r="N44" s="133">
+        <v>1.1427777777777777E-3</v>
       </c>
       <c r="O44" s="93">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P44" s="94">
-        <v>1.1319444444444443E-3</v>
-      </c>
-      <c r="Q44" s="127">
-        <v>18</v>
-      </c>
-      <c r="R44" s="128">
-        <v>1.1319444444444443E-3</v>
+        <v>1.1632407407407407E-3</v>
+      </c>
+      <c r="Q44" s="132">
+        <v>17</v>
+      </c>
+      <c r="R44" s="133">
+        <v>1.1632407407407407E-3</v>
       </c>
       <c r="S44" s="58"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="126">
-        <v>19</v>
-      </c>
-      <c r="B45" s="125">
-        <v>1.1236805555555555E-3</v>
-      </c>
-      <c r="C45" s="126">
-        <v>19</v>
-      </c>
-      <c r="D45" s="125">
-        <v>1.1092129629629629E-3</v>
-      </c>
-      <c r="E45" s="126">
-        <v>19</v>
-      </c>
-      <c r="F45" s="125">
-        <v>1.1594328703703703E-3</v>
+      <c r="X44" s="1"/>
+    </row>
+    <row r="45" spans="1:24">
+      <c r="A45" s="131">
+        <v>18</v>
+      </c>
+      <c r="B45" s="130">
+        <v>1.114398148148148E-3</v>
+      </c>
+      <c r="C45" s="131">
+        <v>18</v>
+      </c>
+      <c r="D45" s="130">
+        <v>1.1069444444444445E-3</v>
+      </c>
+      <c r="E45" s="131">
+        <v>18</v>
+      </c>
+      <c r="F45" s="130">
+        <v>1.1676157407407408E-3</v>
       </c>
       <c r="G45" s="97">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" s="98">
-        <v>1.1594328703703703E-3</v>
+        <v>1.1676157407407408E-3</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="127">
-        <v>19</v>
-      </c>
-      <c r="L45" s="128">
-        <v>1.1439699074074073E-3</v>
-      </c>
-      <c r="M45" s="127">
-        <v>19</v>
-      </c>
-      <c r="N45" s="128">
-        <v>1.1471990740740739E-3</v>
+      <c r="K45" s="132">
+        <v>18</v>
+      </c>
+      <c r="L45" s="133">
+        <v>1.1378240740740741E-3</v>
+      </c>
+      <c r="M45" s="132">
+        <v>18</v>
+      </c>
+      <c r="N45" s="133">
+        <v>1.1362962962962963E-3</v>
       </c>
       <c r="O45" s="93">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P45" s="94">
-        <v>1.149375E-3</v>
-      </c>
-      <c r="Q45" s="127">
-        <v>19</v>
-      </c>
-      <c r="R45" s="128">
-        <v>1.149375E-3</v>
+        <v>1.1319444444444443E-3</v>
+      </c>
+      <c r="Q45" s="132">
+        <v>18</v>
+      </c>
+      <c r="R45" s="133">
+        <v>1.1319444444444443E-3</v>
       </c>
       <c r="S45" s="58"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="126">
-        <v>20</v>
-      </c>
-      <c r="B46" s="125">
-        <v>1.1430092592592592E-3</v>
-      </c>
-      <c r="C46" s="126">
-        <v>20</v>
-      </c>
-      <c r="D46" s="125">
-        <v>1.1691319444444444E-3</v>
-      </c>
-      <c r="E46" s="126">
-        <v>20</v>
-      </c>
-      <c r="F46" s="125">
-        <v>1.2307523148148149E-3</v>
+      <c r="X45" s="1"/>
+    </row>
+    <row r="46" spans="1:24">
+      <c r="A46" s="131">
+        <v>19</v>
+      </c>
+      <c r="B46" s="130">
+        <v>1.1236805555555555E-3</v>
+      </c>
+      <c r="C46" s="131">
+        <v>19</v>
+      </c>
+      <c r="D46" s="130">
+        <v>1.1092129629629629E-3</v>
+      </c>
+      <c r="E46" s="131">
+        <v>19</v>
+      </c>
+      <c r="F46" s="130">
+        <v>1.1594328703703703E-3</v>
       </c>
       <c r="G46" s="97">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H46" s="98">
-        <v>1.2307523148148149E-3</v>
+        <v>1.1594328703703703E-3</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="129">
-        <v>20</v>
-      </c>
-      <c r="L46" s="130">
-        <v>1.1290277777777778E-3</v>
-      </c>
-      <c r="M46" s="129">
-        <v>20</v>
-      </c>
-      <c r="N46" s="130">
-        <v>1.1019907407407408E-3</v>
-      </c>
-      <c r="O46" s="95">
-        <v>20</v>
-      </c>
-      <c r="P46" s="96">
-        <v>1.1516666666666665E-3</v>
-      </c>
-      <c r="Q46" s="129">
-        <v>20</v>
-      </c>
-      <c r="R46" s="130">
-        <v>1.1516666666666665E-3</v>
-      </c>
-      <c r="S46" s="1"/>
+      <c r="K46" s="132">
+        <v>19</v>
+      </c>
+      <c r="L46" s="133">
+        <v>1.1439699074074073E-3</v>
+      </c>
+      <c r="M46" s="132">
+        <v>19</v>
+      </c>
+      <c r="N46" s="133">
+        <v>1.1471990740740739E-3</v>
+      </c>
+      <c r="O46" s="93">
+        <v>19</v>
+      </c>
+      <c r="P46" s="94">
+        <v>1.149375E-3</v>
+      </c>
+      <c r="Q46" s="132">
+        <v>19</v>
+      </c>
+      <c r="R46" s="133">
+        <v>1.149375E-3</v>
+      </c>
+      <c r="S46" s="58"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="1"/>
-      <c r="B47" s="89"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="90"/>
-      <c r="F47" s="91"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="91"/>
+      <c r="X46" s="1"/>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47" s="131">
+        <v>20</v>
+      </c>
+      <c r="B47" s="130">
+        <v>1.1430092592592592E-3</v>
+      </c>
+      <c r="C47" s="131">
+        <v>20</v>
+      </c>
+      <c r="D47" s="130">
+        <v>1.1691319444444444E-3</v>
+      </c>
+      <c r="E47" s="131">
+        <v>20</v>
+      </c>
+      <c r="F47" s="130">
+        <v>1.2307523148148149E-3</v>
+      </c>
+      <c r="G47" s="97">
+        <v>20</v>
+      </c>
+      <c r="H47" s="98">
+        <v>1.2307523148148149E-3</v>
+      </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
+      <c r="K47" s="134">
+        <v>20</v>
+      </c>
+      <c r="L47" s="135">
+        <v>1.1290277777777778E-3</v>
+      </c>
+      <c r="M47" s="134">
+        <v>20</v>
+      </c>
+      <c r="N47" s="135">
+        <v>1.1019907407407408E-3</v>
+      </c>
+      <c r="O47" s="95">
+        <v>20</v>
+      </c>
+      <c r="P47" s="96">
+        <v>1.1516666666666665E-3</v>
+      </c>
+      <c r="Q47" s="134">
+        <v>20</v>
+      </c>
+      <c r="R47" s="135">
+        <v>1.1516666666666665E-3</v>
+      </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
-      <c r="U47" s="75"/>
+      <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="X47" s="1"/>
+    </row>
+    <row r="48" spans="1:24">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="91"/>
+      <c r="E48" s="90"/>
+      <c r="F48" s="91"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+      <c r="H48" s="91"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -17317,205 +17431,246 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
+      <c r="U48" s="75"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="X48" s="1"/>
+    </row>
+    <row r="49" spans="1:24">
       <c r="A49" s="1"/>
-      <c r="B49" s="58">
-        <f>+AVERAGE(B27:B36,B40:B46)</f>
-        <v>1.1587159586056647E-3</v>
-      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="58">
-        <f>+AVERAGE(D27:D36,D40:D46)</f>
-        <v>1.1469376361655772E-3</v>
-      </c>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="58">
-        <f>+AVERAGE(F27:F36,F40:F46)</f>
-        <v>1.1957563997821352E-3</v>
-      </c>
+      <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="58">
-        <f>+AVERAGE(H27:H36,H40:H46)</f>
-        <v>1.1957563997821352E-3</v>
-      </c>
+      <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="58">
-        <f>+AVERAGE(L27:L37,L40:L46)</f>
-        <v>1.1716358024691359E-3</v>
-      </c>
+      <c r="L49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="N49" s="58">
-        <f>+AVERAGE(N27:N37,N40:N46)</f>
-        <v>1.1558834876543207E-3</v>
-      </c>
+      <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="P49" s="58">
-        <f>+AVERAGE(P27:P37,P40:P46)</f>
-        <v>1.2922196502057615E-3</v>
-      </c>
+      <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-      <c r="R49" s="58">
-        <f>+AVERAGE(R27:R37,R40:R46)</f>
-        <v>1.2922196502057615E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+    </row>
+    <row r="50" spans="1:24">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="58">
+        <f>+AVERAGE(B28:B37,B41:B47)</f>
+        <v>1.1587159586056647E-3</v>
+      </c>
       <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+      <c r="D50" s="58">
+        <f>+AVERAGE(D28:D37,D41:D47)</f>
+        <v>1.1469376361655772E-3</v>
+      </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="F50" s="58">
+        <f>+AVERAGE(F28:F37,F41:F47)</f>
+        <v>1.1957563997821352E-3</v>
+      </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+      <c r="H50" s="58">
+        <f>+AVERAGE(H28:H37,H41:H47)</f>
+        <v>1.1957563997821352E-3</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L50" s="58">
+        <f>+AVERAGE(L28:L38,L41:L47)</f>
+        <v>1.1716358024691359E-3</v>
+      </c>
       <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
+      <c r="N50" s="58">
+        <f>+AVERAGE(N28:N38,N41:N47)</f>
+        <v>1.1558834876543207E-3</v>
+      </c>
       <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
+      <c r="P50" s="58">
+        <f>+AVERAGE(P28:P38,P41:P47)</f>
+        <v>1.2922196502057615E-3</v>
+      </c>
       <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="R50" s="58">
+        <f>+AVERAGE(R28:R38,R41:R47)</f>
+        <v>1.2922196502057615E-3</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+    </row>
+    <row r="51" spans="1:24">
       <c r="A51" s="1"/>
-      <c r="B51" s="91">
-        <f>+SUM(B49-D49)</f>
-        <v>1.1778322440087483E-5</v>
-      </c>
-      <c r="C51" s="90"/>
-      <c r="D51" s="58">
-        <v>1.1469376361655772E-3</v>
-      </c>
-      <c r="E51" s="90"/>
-      <c r="F51" s="91">
-        <f>+SUM(F49-D49)</f>
-        <v>4.8818763616557959E-5</v>
-      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="91">
-        <f>+SUM(H49-D49)</f>
-        <v>4.8818763616557959E-5</v>
-      </c>
+      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="91">
-        <f>+SUM(L49-N49)</f>
-        <v>1.5752314814815229E-5</v>
-      </c>
-      <c r="M51" s="90"/>
-      <c r="N51" s="58">
-        <v>1.1558834876543207E-3</v>
-      </c>
-      <c r="O51" s="90"/>
-      <c r="P51" s="91">
-        <f>+SUM(P49-N49)</f>
-        <v>1.3633616255144076E-4</v>
-      </c>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
-      <c r="R51" s="91">
-        <f>+SUM(R49-N49)</f>
-        <v>1.3633616255144076E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+    </row>
+    <row r="52" spans="1:24">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="B52" s="91">
+        <f>+SUM(B50-D50)</f>
+        <v>1.1778322440087483E-5</v>
+      </c>
+      <c r="C52" s="90"/>
+      <c r="D52" s="58">
+        <v>1.1469376361655772E-3</v>
+      </c>
+      <c r="E52" s="90"/>
+      <c r="F52" s="91">
+        <f>+SUM(F50-D50)</f>
+        <v>4.8818763616557959E-5</v>
+      </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="H52" s="91">
+        <f>+SUM(H50-D50)</f>
+        <v>4.8818763616557959E-5</v>
+      </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
+      <c r="L52" s="91">
+        <f>+SUM(L50-N50)</f>
+        <v>1.5752314814815229E-5</v>
+      </c>
+      <c r="M52" s="90"/>
+      <c r="N52" s="58">
+        <v>1.1558834876543207E-3</v>
+      </c>
+      <c r="O52" s="90"/>
+      <c r="P52" s="91">
+        <f>+SUM(P50-N50)</f>
+        <v>1.3633616255144076E-4</v>
+      </c>
       <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-    </row>
-    <row r="53" spans="1:18">
-      <c r="A53" s="90" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="58">
-        <f>+SMALL(B27:B46,1)</f>
-        <v>1.1098379629629629E-3</v>
-      </c>
+      <c r="R52" s="91">
+        <f>+SUM(R50-N50)</f>
+        <v>1.3633616255144076E-4</v>
+      </c>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+    </row>
+    <row r="53" spans="1:24">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="58">
-        <f>+SMALL(D27:D46,1)</f>
-        <v>1.0967939814814816E-3</v>
-      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="58">
-        <f>+SMALL(F27:F46,1)</f>
-        <v>1.1312268518518518E-3</v>
-      </c>
+      <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="58">
-        <f>+SMALL(H27:H46,1)</f>
-        <v>1.1312268518518518E-3</v>
-      </c>
+      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="90" t="s">
-        <v>109</v>
-      </c>
-      <c r="L53" s="58">
-        <f>+SMALL(L27:L46,1)</f>
-        <v>1.1143287037037035E-3</v>
-      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1"/>
-      <c r="N53" s="58">
-        <f>+SMALL(N27:N46,1)</f>
-        <v>1.0958333333333334E-3</v>
-      </c>
+      <c r="N53" s="1"/>
       <c r="O53" s="1"/>
-      <c r="P53" s="58">
-        <f>+SMALL(P27:P46,1)</f>
-        <v>1.1238657407407408E-3</v>
-      </c>
+      <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
-      <c r="R53" s="58">
-        <f>+SMALL(R27:R46,1)</f>
-        <v>1.1238657407407408E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+    </row>
+    <row r="54" spans="1:24">
+      <c r="A54" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="58">
+        <f>+SMALL(B28:B47,1)</f>
+        <v>1.1098379629629629E-3</v>
+      </c>
       <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="D54" s="58">
+        <f>+SMALL(D28:D47,1)</f>
+        <v>1.0967939814814816E-3</v>
+      </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="58">
+        <f>+SMALL(F28:F47,1)</f>
+        <v>1.1312268518518518E-3</v>
+      </c>
       <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="H54" s="58">
+        <f>+SMALL(H28:H47,1)</f>
+        <v>1.1312268518518518E-3</v>
+      </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="K54" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="L54" s="58">
+        <f>+SMALL(L28:L47,1)</f>
+        <v>1.1143287037037035E-3</v>
+      </c>
       <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
+      <c r="N54" s="58">
+        <f>+SMALL(N28:N47,1)</f>
+        <v>1.0958333333333334E-3</v>
+      </c>
       <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
+      <c r="P54" s="58">
+        <f>+SMALL(P28:P47,1)</f>
+        <v>1.1238657407407408E-3</v>
+      </c>
       <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="R54" s="58">
+        <f>+SMALL(R28:R47,1)</f>
+        <v>1.1238657407407408E-3</v>
+      </c>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+    </row>
+    <row r="55" spans="1:24">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -17534,18 +17689,22 @@
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
-    </row>
-    <row r="56" spans="1:18" ht="34.5">
-      <c r="A56" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="116"/>
-      <c r="C56" s="116"/>
-      <c r="D56" s="116"/>
-      <c r="E56" s="116"/>
-      <c r="F56" s="116"/>
-      <c r="G56" s="116"/>
-      <c r="H56" s="116"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+    </row>
+    <row r="56" spans="1:24">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -17556,500 +17715,1983 @@
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57" s="117" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="118"/>
-      <c r="C57" s="117" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" s="118"/>
-      <c r="E57" s="119" t="s">
-        <v>107</v>
-      </c>
-      <c r="F57" s="120"/>
-      <c r="G57" s="117" t="s">
-        <v>108</v>
-      </c>
-      <c r="H57" s="118"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+    </row>
+    <row r="57" spans="1:24" ht="34.5">
+      <c r="A57" s="106" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="106"/>
+      <c r="C57" s="106"/>
+      <c r="D57" s="106"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="106"/>
+      <c r="H57" s="106"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-    </row>
-    <row r="58" spans="1:18">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="126">
-        <v>1</v>
-      </c>
-      <c r="D58" s="58">
-        <v>1.9520833333333332E-3</v>
-      </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="126">
-        <v>1</v>
-      </c>
-      <c r="H58" s="125">
-        <v>1.9796875000000001E-3</v>
-      </c>
+      <c r="K57" s="106" t="s">
+        <v>114</v>
+      </c>
+      <c r="L57" s="106"/>
+      <c r="M57" s="106"/>
+      <c r="N57" s="106"/>
+      <c r="O57" s="106"/>
+      <c r="P57" s="106"/>
+      <c r="Q57" s="106"/>
+      <c r="R57" s="106"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+    </row>
+    <row r="58" spans="1:24">
+      <c r="A58" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="108"/>
+      <c r="C58" s="107" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="108"/>
+      <c r="E58" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="F58" s="110"/>
+      <c r="G58" s="107" t="s">
+        <v>110</v>
+      </c>
+      <c r="H58" s="108"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="K58" s="107"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="108"/>
+      <c r="O58" s="109"/>
+      <c r="P58" s="110"/>
+      <c r="Q58" s="107" t="s">
+        <v>80</v>
+      </c>
+      <c r="R58" s="108"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+    </row>
+    <row r="59" spans="1:24">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="126">
-        <v>2</v>
+      <c r="C59" s="131">
+        <v>1</v>
       </c>
       <c r="D59" s="58">
-        <v>1.1939004629629628E-3</v>
+        <v>1.9520833333333332E-3</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="126">
-        <v>2</v>
-      </c>
-      <c r="H59" s="125">
-        <v>1.2236342592592594E-3</v>
+      <c r="G59" s="131">
+        <v>1</v>
+      </c>
+      <c r="H59" s="130">
+        <v>1.9796875000000001E-3</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
+      <c r="M59" s="1">
+        <v>1</v>
+      </c>
+      <c r="N59" s="58">
+        <v>1.4361342592592592E-3</v>
+      </c>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="Q59" s="1">
+        <v>1</v>
+      </c>
+      <c r="R59" s="58">
+        <v>1.4263888888888889E-3</v>
+      </c>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+    </row>
+    <row r="60" spans="1:24">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="126">
-        <v>3</v>
+      <c r="C60" s="131">
+        <v>2</v>
       </c>
       <c r="D60" s="58">
-        <v>1.1949652777777779E-3</v>
+        <v>1.1939004629629628E-3</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="126">
-        <v>3</v>
-      </c>
-      <c r="H60" s="125">
-        <v>1.2050810185185185E-3</v>
+      <c r="G60" s="131">
+        <v>2</v>
+      </c>
+      <c r="H60" s="130">
+        <v>1.2236342592592594E-3</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
+      <c r="M60" s="1">
+        <v>2</v>
+      </c>
+      <c r="N60" s="58">
+        <v>9.4768518518518509E-4</v>
+      </c>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="Q60" s="1">
+        <v>2</v>
+      </c>
+      <c r="R60" s="58">
+        <v>9.1004629629629628E-4</v>
+      </c>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+    </row>
+    <row r="61" spans="1:24">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="126">
-        <v>4</v>
+      <c r="C61" s="131">
+        <v>3</v>
       </c>
       <c r="D61" s="58">
-        <v>1.1942129629629631E-3</v>
+        <v>1.1949652777777779E-3</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="126">
-        <v>4</v>
-      </c>
-      <c r="H61" s="125">
-        <v>1.2027199074074073E-3</v>
+      <c r="G61" s="131">
+        <v>3</v>
+      </c>
+      <c r="H61" s="130">
+        <v>1.2050810185185185E-3</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
+      <c r="M61" s="1">
+        <v>3</v>
+      </c>
+      <c r="N61" s="58">
+        <v>8.3365740740740752E-4</v>
+      </c>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
-    <row r="62" spans="1:18">
+      <c r="Q61" s="1">
+        <v>3</v>
+      </c>
+      <c r="R61" s="58">
+        <v>8.2151620370370364E-4</v>
+      </c>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+    </row>
+    <row r="62" spans="1:24">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="126">
-        <v>5</v>
+      <c r="C62" s="131">
+        <v>4</v>
       </c>
       <c r="D62" s="58">
-        <v>1.1978819444444443E-3</v>
+        <v>1.1942129629629631E-3</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="126">
-        <v>5</v>
-      </c>
-      <c r="H62" s="125">
-        <v>1.1896412037037036E-3</v>
+      <c r="G62" s="131">
+        <v>4</v>
+      </c>
+      <c r="H62" s="130">
+        <v>1.2027199074074073E-3</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
+      <c r="M62" s="1">
+        <v>4</v>
+      </c>
+      <c r="N62" s="58">
+        <v>8.2813657407407413E-4</v>
+      </c>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-    </row>
-    <row r="63" spans="1:18">
+      <c r="Q62" s="1">
+        <v>4</v>
+      </c>
+      <c r="R62" s="58">
+        <v>8.2106481481481483E-4</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+    </row>
+    <row r="63" spans="1:24">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="126">
-        <v>6</v>
+      <c r="C63" s="131">
+        <v>5</v>
       </c>
       <c r="D63" s="58">
-        <v>1.1956712962962962E-3</v>
+        <v>1.1978819444444443E-3</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="126">
-        <v>6</v>
-      </c>
-      <c r="H63" s="125">
-        <v>1.2009606481481483E-3</v>
+      <c r="G63" s="131">
+        <v>5</v>
+      </c>
+      <c r="H63" s="130">
+        <v>1.1896412037037036E-3</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
+      <c r="M63" s="1">
+        <v>5</v>
+      </c>
+      <c r="N63" s="58">
+        <v>8.2803240740740743E-4</v>
+      </c>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-    </row>
-    <row r="64" spans="1:18">
+      <c r="Q63" s="1">
+        <v>5</v>
+      </c>
+      <c r="R63" s="58">
+        <v>8.2216435185185181E-4</v>
+      </c>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+    </row>
+    <row r="64" spans="1:24">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="126">
-        <v>7</v>
+      <c r="C64" s="131">
+        <v>6</v>
       </c>
       <c r="D64" s="58">
-        <v>1.1767824074074074E-3</v>
+        <v>1.1956712962962962E-3</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="126">
-        <v>7</v>
-      </c>
-      <c r="H64" s="125">
-        <v>1.1911805555555556E-3</v>
+      <c r="G64" s="131">
+        <v>6</v>
+      </c>
+      <c r="H64" s="130">
+        <v>1.2009606481481483E-3</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
+      <c r="M64" s="1">
+        <v>6</v>
+      </c>
+      <c r="N64" s="58">
+        <v>8.3063657407407402E-4</v>
+      </c>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="Q64" s="1">
+        <v>6</v>
+      </c>
+      <c r="R64" s="58">
+        <v>8.4766203703703707E-4</v>
+      </c>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+    </row>
+    <row r="65" spans="1:24">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="126">
-        <v>8</v>
+      <c r="C65" s="131">
+        <v>7</v>
       </c>
       <c r="D65" s="58">
-        <v>1.204861111111111E-3</v>
+        <v>1.1767824074074074E-3</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="126">
-        <v>8</v>
-      </c>
-      <c r="H65" s="125">
-        <v>1.1953125E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="G65" s="131">
+        <v>7</v>
+      </c>
+      <c r="H65" s="130">
+        <v>1.1911805555555556E-3</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1">
+        <v>7</v>
+      </c>
+      <c r="N65" s="58">
+        <v>8.3038194444444446E-4</v>
+      </c>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1">
+        <v>7</v>
+      </c>
+      <c r="R65" s="58">
+        <v>8.2127314814814812E-4</v>
+      </c>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+    </row>
+    <row r="66" spans="1:24">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="126">
-        <v>9</v>
+      <c r="C66" s="131">
+        <v>8</v>
       </c>
       <c r="D66" s="58">
-        <v>1.2104166666666667E-3</v>
+        <v>1.204861111111111E-3</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="126">
-        <v>9</v>
-      </c>
-      <c r="H66" s="125">
-        <v>1.2066550925925925E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="G66" s="131">
+        <v>8</v>
+      </c>
+      <c r="H66" s="130">
+        <v>1.1953125E-3</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1">
+        <v>8</v>
+      </c>
+      <c r="N66" s="58">
+        <v>8.2754629629629628E-4</v>
+      </c>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1">
+        <v>8</v>
+      </c>
+      <c r="R66" s="58">
+        <v>8.2086805555555559E-4</v>
+      </c>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+    </row>
+    <row r="67" spans="1:24">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="126">
-        <v>10</v>
+      <c r="C67" s="131">
+        <v>9</v>
       </c>
       <c r="D67" s="58">
-        <v>1.5151504629629629E-3</v>
+        <v>1.2104166666666667E-3</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="126">
-        <v>10</v>
-      </c>
-      <c r="H67" s="125">
-        <v>1.4534606481481482E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="G67" s="131">
+        <v>9</v>
+      </c>
+      <c r="H67" s="130">
+        <v>1.2066550925925925E-3</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1">
+        <v>9</v>
+      </c>
+      <c r="N67" s="58">
+        <v>8.3032407407407404E-4</v>
+      </c>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1">
+        <v>9</v>
+      </c>
+      <c r="R67" s="58">
+        <v>8.1811342592592591E-4</v>
+      </c>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+    </row>
+    <row r="68" spans="1:24">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="126">
-        <v>11</v>
+      <c r="C68" s="131">
+        <v>10</v>
       </c>
       <c r="D68" s="58">
-        <v>1.9391203703703703E-3</v>
+        <v>1.5151504629629629E-3</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="126">
-        <v>11</v>
-      </c>
-      <c r="H68" s="125">
-        <v>1.9292013888888887E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="G68" s="131">
+        <v>10</v>
+      </c>
+      <c r="H68" s="130">
+        <v>1.4534606481481482E-3</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1">
+        <v>10</v>
+      </c>
+      <c r="N68" s="58">
+        <v>8.3142361111111123E-4</v>
+      </c>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1">
+        <v>10</v>
+      </c>
+      <c r="R68" s="58">
+        <v>8.1762731481481487E-4</v>
+      </c>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+    </row>
+    <row r="69" spans="1:24">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="126">
-        <v>12</v>
+      <c r="C69" s="131">
+        <v>11</v>
       </c>
       <c r="D69" s="58">
-        <v>1.1987847222222222E-3</v>
+        <v>1.9391203703703703E-3</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="126">
-        <v>12</v>
-      </c>
-      <c r="H69" s="125">
-        <v>1.2021874999999999E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="G69" s="131">
+        <v>11</v>
+      </c>
+      <c r="H69" s="130">
+        <v>1.9292013888888887E-3</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1">
+        <v>11</v>
+      </c>
+      <c r="N69" s="58">
+        <v>8.480671296296296E-4</v>
+      </c>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1">
+        <v>11</v>
+      </c>
+      <c r="R69" s="58">
+        <v>8.2513888888888893E-4</v>
+      </c>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+    </row>
+    <row r="70" spans="1:24">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="126">
-        <v>13</v>
+      <c r="C70" s="131">
+        <v>12</v>
       </c>
       <c r="D70" s="58">
-        <v>1.2125462962962964E-3</v>
+        <v>1.1987847222222222E-3</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="126">
-        <v>13</v>
-      </c>
-      <c r="H70" s="125">
-        <v>1.2077546296296296E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="G70" s="131">
+        <v>12</v>
+      </c>
+      <c r="H70" s="130">
+        <v>1.2021874999999999E-3</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1">
+        <v>12</v>
+      </c>
+      <c r="N70" s="58">
+        <v>8.3438657407407398E-4</v>
+      </c>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1">
+        <v>12</v>
+      </c>
+      <c r="R70" s="58">
+        <v>9.9265046296296297E-4</v>
+      </c>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+    </row>
+    <row r="71" spans="1:24">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="126">
-        <v>14</v>
+      <c r="C71" s="131">
+        <v>13</v>
       </c>
       <c r="D71" s="58">
-        <v>1.2050694444444444E-3</v>
+        <v>1.2125462962962964E-3</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="126">
-        <v>14</v>
-      </c>
-      <c r="H71" s="125">
-        <v>1.2092245370370371E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="G71" s="131">
+        <v>13</v>
+      </c>
+      <c r="H71" s="130">
+        <v>1.2077546296296296E-3</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1">
+        <v>13</v>
+      </c>
+      <c r="N71" s="58">
+        <v>8.3318287037037031E-4</v>
+      </c>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1">
+        <v>13</v>
+      </c>
+      <c r="R71" s="58">
+        <v>8.3115740740740741E-4</v>
+      </c>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+    </row>
+    <row r="72" spans="1:24">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="126">
-        <v>15</v>
+      <c r="C72" s="131">
+        <v>14</v>
       </c>
       <c r="D72" s="58">
-        <v>1.1976967592592592E-3</v>
+        <v>1.2050694444444444E-3</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="126">
-        <v>15</v>
-      </c>
-      <c r="H72" s="125">
-        <v>1.2027314814814815E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="G72" s="131">
+        <v>14</v>
+      </c>
+      <c r="H72" s="130">
+        <v>1.2092245370370371E-3</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1">
+        <v>14</v>
+      </c>
+      <c r="N72" s="58">
+        <v>8.3377314814814816E-4</v>
+      </c>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1">
+        <v>14</v>
+      </c>
+      <c r="R72" s="58">
+        <v>8.1944444444444437E-4</v>
+      </c>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+    </row>
+    <row r="73" spans="1:24">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="126">
-        <v>16</v>
+      <c r="C73" s="131">
+        <v>15</v>
       </c>
       <c r="D73" s="58">
-        <v>1.2089351851851851E-3</v>
+        <v>1.1976967592592592E-3</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="126">
-        <v>16</v>
-      </c>
-      <c r="H73" s="125">
-        <v>1.1990972222222223E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="15.75">
+      <c r="G73" s="131">
+        <v>15</v>
+      </c>
+      <c r="H73" s="130">
+        <v>1.2027314814814815E-3</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1">
+        <v>15</v>
+      </c>
+      <c r="N73" s="58">
+        <v>8.3221064814814822E-4</v>
+      </c>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1">
+        <v>15</v>
+      </c>
+      <c r="R73" s="58">
+        <v>8.2342592592592602E-4</v>
+      </c>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+    </row>
+    <row r="74" spans="1:24">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
+      <c r="C74" s="131">
+        <v>16</v>
+      </c>
+      <c r="D74" s="58">
+        <v>1.2089351851851851E-3</v>
+      </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="126"/>
-      <c r="H74" s="121"/>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="G74" s="131">
+        <v>16</v>
+      </c>
+      <c r="H74" s="130">
+        <v>1.2106712962962963E-3</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1">
+        <v>16</v>
+      </c>
+      <c r="N74" s="58">
+        <v>8.2762731481481489E-4</v>
+      </c>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1">
+        <v>16</v>
+      </c>
+      <c r="R74" s="58">
+        <v>8.1971064814814819E-4</v>
+      </c>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+    </row>
+    <row r="75" spans="1:24" ht="15.75">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="126"/>
-      <c r="H75" s="1"/>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="G75" s="131"/>
+      <c r="H75" s="99"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1">
+        <v>17</v>
+      </c>
+      <c r="N75" s="58">
+        <v>8.4262731481481482E-4</v>
+      </c>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1">
+        <v>17</v>
+      </c>
+      <c r="R75" s="58">
+        <v>8.3310185185185191E-4</v>
+      </c>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+    </row>
+    <row r="76" spans="1:24">
       <c r="A76" s="1"/>
-      <c r="B76" s="58" t="e">
-        <f>+AVERAGE(B54:B63,B67:B73)</f>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="131"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1">
+        <v>18</v>
+      </c>
+      <c r="N76" s="58">
+        <v>8.3070601851851849E-4</v>
+      </c>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1">
+        <v>18</v>
+      </c>
+      <c r="R76" s="58">
+        <v>8.2271990740740743E-4</v>
+      </c>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+    </row>
+    <row r="77" spans="1:24">
+      <c r="A77" s="1"/>
+      <c r="B77" s="58" t="e">
+        <f>+AVERAGE(B55:B64,B68:B74)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="58">
-        <f>+AVERAGE(D54:D66,D69:D73)</f>
+      <c r="C77" s="1"/>
+      <c r="D77" s="58">
+        <f>+AVERAGE(D55:D67,D70:D74)</f>
         <v>1.2531291335978834E-3</v>
       </c>
-      <c r="E76" s="1"/>
-      <c r="F76" s="58" t="e">
-        <f>+AVERAGE(F54:F63,F67:F73)</f>
+      <c r="E77" s="1"/>
+      <c r="F77" s="58" t="e">
+        <f>+AVERAGE(F55:F64,F68:F74)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G76" s="126"/>
-      <c r="H76" s="58">
-        <f>+AVERAGE(H58:H66,H69:H73)</f>
-        <v>1.2582762896825397E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="126"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="G77" s="131"/>
+      <c r="H77" s="58">
+        <f>+AVERAGE(H59:H67,H70:H74)</f>
+        <v>1.2591030092592593E-3</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="58"/>
+      <c r="M77" s="1">
+        <v>19</v>
+      </c>
+      <c r="N77" s="58">
+        <v>8.292361111111111E-4</v>
+      </c>
+      <c r="O77" s="1"/>
+      <c r="P77" s="58"/>
+      <c r="Q77" s="1">
+        <v>19</v>
+      </c>
+      <c r="R77" s="58">
+        <v>8.2199074074074065E-4</v>
+      </c>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+    </row>
+    <row r="78" spans="1:24">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="58">
-        <v>1.2531291335978834E-3</v>
-      </c>
+      <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="122">
-        <f>+SUM(H76-D76)</f>
-        <v>5.1471560846563184E-6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="90" t="s">
-        <v>109</v>
-      </c>
+      <c r="G78" s="131"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1">
+        <v>20</v>
+      </c>
+      <c r="N78" s="58">
+        <v>8.3160879629629633E-4</v>
+      </c>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1">
+        <v>20</v>
+      </c>
+      <c r="R78" s="58">
+        <v>8.2870370370370368E-4</v>
+      </c>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+    </row>
+    <row r="79" spans="1:24">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="58">
+        <v>1.2531291335978834E-3</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="100">
+        <f>+SUM(H77-D77)</f>
+        <v>5.9738756613759211E-6</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1">
+        <v>21</v>
+      </c>
+      <c r="N79" s="58">
+        <v>8.294444444444445E-4</v>
+      </c>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1">
+        <v>21</v>
+      </c>
+      <c r="R79" s="58">
+        <v>8.2164351851851843E-4</v>
+      </c>
+      <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+    </row>
+    <row r="80" spans="1:24">
+      <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="58">
-        <f>+SMALL(D58:D73,1)</f>
-        <v>1.1767824074074074E-3</v>
-      </c>
+      <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="58">
-        <f>+SMALL(H58:H73,1)</f>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1">
+        <v>22</v>
+      </c>
+      <c r="N80" s="58">
+        <v>8.3431712962962973E-4</v>
+      </c>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1">
+        <v>22</v>
+      </c>
+      <c r="R80" s="58">
+        <v>8.227662037037037E-4</v>
+      </c>
+      <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+    </row>
+    <row r="81" spans="1:24">
+      <c r="A81" s="90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="58">
+        <f>+SMALL(D59:D74,1)</f>
+        <v>1.1767824074074074E-3</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="58">
+        <f>+SMALL(H59:H74,1)</f>
         <v>1.1896412037037036E-3</v>
       </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="90"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1">
+        <v>23</v>
+      </c>
+      <c r="N81" s="58">
+        <v>8.2590277777777783E-4</v>
+      </c>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1">
+        <v>23</v>
+      </c>
+      <c r="R81" s="58">
+        <v>8.2003472222222222E-4</v>
+      </c>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+    </row>
+    <row r="82" spans="1:24">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1">
+        <v>24</v>
+      </c>
+      <c r="N82" s="58">
+        <v>8.2978009259259257E-4</v>
+      </c>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1">
+        <v>24</v>
+      </c>
+      <c r="R82" s="58">
+        <v>8.2083333333333335E-4</v>
+      </c>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+    </row>
+    <row r="83" spans="1:24">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1">
+        <v>25</v>
+      </c>
+      <c r="N83" s="58">
+        <v>8.2966435185185172E-4</v>
+      </c>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1">
+        <v>25</v>
+      </c>
+      <c r="R83" s="58">
+        <v>8.3520833333333342E-4</v>
+      </c>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+    </row>
+    <row r="84" spans="1:24">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+    </row>
+    <row r="85" spans="1:24">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="N85" s="58">
+        <f>+AVERAGE(N59:N83)</f>
+        <v>8.6065972222222208E-4</v>
+      </c>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="58">
+        <f>+AVERAGE(R59:R83)</f>
+        <v>8.58610185185185E-4</v>
+      </c>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+    </row>
+    <row r="86" spans="1:24">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="90"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+    </row>
+    <row r="87" spans="1:24">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="N87" s="102">
+        <f>+SUM(N85-R85)</f>
+        <v>2.0495370370370806E-6</v>
+      </c>
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="58">
+        <f>+AVERAGE(R61:R85)</f>
+        <v>8.328095679012345E-4</v>
+      </c>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="1"/>
+      <c r="V87" s="1"/>
+      <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+    </row>
+    <row r="88" spans="1:24">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="90"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+    </row>
+    <row r="89" spans="1:24">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="N89" s="58">
+        <f>+SMALL(N59:N83,1)</f>
+        <v>8.2590277777777783E-4</v>
+      </c>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="58">
+        <f>+SMALL(R59:R83,1)</f>
+        <v>8.1762731481481487E-4</v>
+      </c>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
+      <c r="V89" s="1"/>
+      <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+    </row>
+    <row r="90" spans="1:24">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="90"/>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+    </row>
+    <row r="91" spans="1:24">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="N91" s="103">
+        <f>+SUM(N89-R89)</f>
+        <v>8.2754629629629671E-6</v>
+      </c>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="58">
+        <f>+SMALL(R61:R85,1)</f>
+        <v>8.1762731481481487E-4</v>
+      </c>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+    </row>
+    <row r="92" spans="1:24">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+    </row>
+    <row r="93" spans="1:24">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+    </row>
+    <row r="94" spans="1:24">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+    </row>
+    <row r="95" spans="1:24">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1"/>
+      <c r="V95" s="1"/>
+      <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+    </row>
+    <row r="96" spans="1:24">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1"/>
+      <c r="V96" s="1"/>
+      <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
+    </row>
+    <row r="97" spans="1:24">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1"/>
+      <c r="V97" s="1"/>
+      <c r="W97" s="1"/>
+      <c r="X97" s="1"/>
+    </row>
+    <row r="98" spans="1:24">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="1"/>
+      <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="1"/>
+      <c r="U98" s="1"/>
+      <c r="V98" s="1"/>
+      <c r="W98" s="1"/>
+      <c r="X98" s="1"/>
+    </row>
+    <row r="99" spans="1:24">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="1"/>
+      <c r="U99" s="1"/>
+      <c r="V99" s="1"/>
+      <c r="W99" s="1"/>
+      <c r="X99" s="1"/>
+    </row>
+    <row r="100" spans="1:24">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+    </row>
+    <row r="101" spans="1:24">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="1"/>
+      <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+    </row>
+    <row r="102" spans="1:24">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1"/>
+      <c r="V102" s="1"/>
+      <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+    </row>
+    <row r="103" spans="1:24">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1"/>
+      <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="1"/>
+      <c r="U103" s="1"/>
+      <c r="V103" s="1"/>
+      <c r="W103" s="1"/>
+      <c r="X103" s="1"/>
+    </row>
+    <row r="104" spans="1:24">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1"/>
+      <c r="V104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+    </row>
+    <row r="105" spans="1:24">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+    </row>
+    <row r="106" spans="1:24">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+    </row>
+    <row r="107" spans="1:24">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
+      <c r="V107" s="1"/>
+      <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+    </row>
+    <row r="108" spans="1:24">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="1"/>
+      <c r="P108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
+      <c r="T108" s="1"/>
+      <c r="U108" s="1"/>
+      <c r="V108" s="1"/>
+      <c r="W108" s="1"/>
+      <c r="X108" s="1"/>
+    </row>
+    <row r="109" spans="1:24">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+    </row>
+    <row r="110" spans="1:24">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="O110" s="1"/>
+      <c r="P110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1"/>
+      <c r="V110" s="1"/>
+      <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+    </row>
+    <row r="111" spans="1:24">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1"/>
+      <c r="O111" s="1"/>
+      <c r="P111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1"/>
+      <c r="V111" s="1"/>
+      <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+    </row>
+    <row r="112" spans="1:24">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
+      <c r="V112" s="1"/>
+      <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+    </row>
+    <row r="113" spans="1:24">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="N113" s="1"/>
+      <c r="O113" s="1"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
+      <c r="T113" s="1"/>
+      <c r="U113" s="1"/>
+      <c r="V113" s="1"/>
+      <c r="W113" s="1"/>
+      <c r="X113" s="1"/>
+    </row>
+    <row r="114" spans="1:24">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+      <c r="N114" s="1"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
+      <c r="T114" s="1"/>
+      <c r="U114" s="1"/>
+      <c r="V114" s="1"/>
+      <c r="W114" s="1"/>
+      <c r="X114" s="1"/>
+    </row>
+    <row r="115" spans="1:24">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="N115" s="1"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+      <c r="S115" s="1"/>
+      <c r="T115" s="1"/>
+      <c r="U115" s="1"/>
+      <c r="V115" s="1"/>
+      <c r="W115" s="1"/>
+      <c r="X115" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="M26:N26"/>
+  <mergeCells count="33">
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:R58"/>
+    <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED576A2-E280-4847-A37E-F965F430434F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F042D5E-8133-4D6A-B16E-0999DA7B8957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,7 +417,7 @@
     <t>PROMEDIO</t>
   </si>
   <si>
-    <t>Record</t>
+    <t>Mejor tiempo</t>
   </si>
   <si>
     <t>VILLICUM C1</t>
@@ -426,13 +426,13 @@
     <t>Toay</t>
   </si>
   <si>
-    <t>Mejor tiempo</t>
-  </si>
-  <si>
     <t>Promedio total</t>
   </si>
   <si>
     <t>Dif promedio</t>
+  </si>
+  <si>
+    <t>Record</t>
   </si>
   <si>
     <t>Dif. record</t>
@@ -17467,23 +17467,23 @@
         <v>111</v>
       </c>
       <c r="B50" s="58">
-        <f>+AVERAGE(B28:B37,B41:B47)</f>
-        <v>1.1587159586056647E-3</v>
+        <f>+AVERAGE(B28:B38,B43:B47)</f>
+        <v>1.1482284432870371E-3</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="58">
-        <f>+AVERAGE(D28:D37,D41:D47)</f>
-        <v>1.1469376361655772E-3</v>
+        <f>+AVERAGE(D28:D38,D43:D47)</f>
+        <v>1.1257624421296296E-3</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="58">
-        <f>+AVERAGE(F28:F37,F41:F47)</f>
-        <v>1.1957563997821352E-3</v>
+        <f>+AVERAGE(F28:F38,F43:F47)</f>
+        <v>1.1765842013888889E-3</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="58">
-        <f>+AVERAGE(H28:H37,H41:H47)</f>
-        <v>1.1957563997821352E-3</v>
+        <f>+AVERAGE(H28:H38,H43:H47)</f>
+        <v>1.1765842013888889E-3</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -17546,21 +17546,21 @@
       <c r="A52" s="1"/>
       <c r="B52" s="91">
         <f>+SUM(B50-D50)</f>
-        <v>1.1778322440087483E-5</v>
+        <v>2.2466001157407569E-5</v>
       </c>
       <c r="C52" s="90"/>
       <c r="D52" s="58">
-        <v>1.1469376361655772E-3</v>
+        <v>1.1257624421296296E-3</v>
       </c>
       <c r="E52" s="90"/>
       <c r="F52" s="91">
         <f>+SUM(F50-D50)</f>
-        <v>4.8818763616557959E-5</v>
+        <v>5.0821759259259353E-5</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="91">
         <f>+SUM(H50-D50)</f>
-        <v>4.8818763616557959E-5</v>
+        <v>5.0821759259259353E-5</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -18685,7 +18685,7 @@
     </row>
     <row r="81" spans="1:24">
       <c r="A81" s="90" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -18833,7 +18833,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N85" s="58">
         <f>+AVERAGE(N59:N83)</f>
@@ -18893,7 +18893,7 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N87" s="102">
         <f>+SUM(N85-R85)</f>
@@ -18953,7 +18953,7 @@
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="90" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N89" s="58">
         <f>+SMALL(N59:N83,1)</f>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F042D5E-8133-4D6A-B16E-0999DA7B8957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFC9D96D-D57C-484B-93F4-9D7E75432918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="24" r:id="rId9"/>
+    <pivotCache cacheId="200" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="119">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -282,6 +282,9 @@
     <t>ROSARIO</t>
   </si>
   <si>
+    <t>VILLICUM</t>
+  </si>
+  <si>
     <t>Total victorias</t>
   </si>
   <si>
@@ -295,9 +298,6 @@
   </si>
   <si>
     <t>POS C2</t>
-  </si>
-  <si>
-    <t>VILLICUM</t>
   </si>
   <si>
     <t>(Todas)</t>
@@ -1257,10 +1257,10 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1634,7 +1634,7 @@
                   <c:v>287.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>334.25</c:v>
+                  <c:v>314.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>#N/A</c:v>
@@ -2228,7 +2228,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Campeonato TC2000 (1).xlsx]Grafico Dinamico!TablaDinámica1</c:name>
+    <c:name>[Campeonato TC2000.xlsx]Grafico Dinamico!TablaDinámica1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -5193,7 +5193,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="200" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5884,13 +5884,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="105">
+      <c r="A2" s="104">
         <v>1</v>
       </c>
-      <c r="B2" s="105">
+      <c r="B2" s="104">
         <v>25</v>
       </c>
-      <c r="C2" s="105">
+      <c r="C2" s="104">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5943,13 +5943,13 @@
       <c r="Z2" s="115"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="105">
+      <c r="A3" s="104">
         <v>2</v>
       </c>
-      <c r="B3" s="105">
+      <c r="B3" s="104">
         <v>18</v>
       </c>
-      <c r="C3" s="105">
+      <c r="C3" s="104">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -6018,13 +6018,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="105">
+      <c r="A4" s="104">
         <v>3</v>
       </c>
-      <c r="B4" s="105">
+      <c r="B4" s="104">
         <v>15</v>
       </c>
-      <c r="C4" s="105">
+      <c r="C4" s="104">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -6087,13 +6087,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="105">
+      <c r="A5" s="104">
         <v>4</v>
       </c>
-      <c r="B5" s="105">
+      <c r="B5" s="104">
         <v>12</v>
       </c>
-      <c r="C5" s="105">
+      <c r="C5" s="104">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -8827,7 +8827,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="6:16">
+    <row r="97" spans="6:23">
       <c r="F97" s="11" t="s">
         <v>14</v>
       </c>
@@ -8843,8 +8843,15 @@
       <c r="N97" s="5"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
-    </row>
-    <row r="98" spans="6:16">
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1"/>
+      <c r="V97" s="1"/>
+      <c r="W97" s="1"/>
+    </row>
+    <row r="98" spans="6:23">
       <c r="F98" s="11" t="s">
         <v>16</v>
       </c>
@@ -8860,8 +8867,15 @@
       <c r="N98" s="5"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
-    </row>
-    <row r="99" spans="6:16" ht="15.75" customHeight="1">
+      <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="1"/>
+      <c r="U98" s="1"/>
+      <c r="V98" s="1"/>
+      <c r="W98" s="1"/>
+    </row>
+    <row r="99" spans="6:23" ht="15.75" customHeight="1">
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
@@ -8899,8 +8913,15 @@
       </c>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
-    </row>
-    <row r="100" spans="6:16">
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="1"/>
+      <c r="U99" s="1"/>
+      <c r="V99" s="1"/>
+      <c r="W99" s="1"/>
+    </row>
+    <row r="100" spans="6:23">
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -8912,8 +8933,15 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
       <c r="P100" s="1"/>
-    </row>
-    <row r="101" spans="6:16">
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+    </row>
+    <row r="101" spans="6:23">
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
@@ -8939,8 +8967,15 @@
       <c r="N101" s="117"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
-    </row>
-    <row r="102" spans="6:16">
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="1"/>
+      <c r="W101" s="1"/>
+    </row>
+    <row r="102" spans="6:23">
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
@@ -8966,8 +9001,15 @@
       <c r="N102" s="114"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
-    </row>
-    <row r="103" spans="6:16">
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1"/>
+      <c r="V102" s="1"/>
+      <c r="W102" s="1"/>
+    </row>
+    <row r="103" spans="6:23">
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
@@ -8993,8 +9035,15 @@
       <c r="N103" s="114"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
-    </row>
-    <row r="105" spans="6:16">
+      <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="1"/>
+      <c r="U103" s="1"/>
+      <c r="V103" s="1"/>
+      <c r="W103" s="101"/>
+    </row>
+    <row r="105" spans="6:23">
       <c r="F105" s="115" t="s">
         <v>33</v>
       </c>
@@ -9008,8 +9057,15 @@
       <c r="N105" s="115"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
-    </row>
-    <row r="106" spans="6:16">
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+    </row>
+    <row r="106" spans="6:23">
       <c r="F106" s="13" t="s">
         <v>34</v>
       </c>
@@ -9041,8 +9097,15 @@
       <c r="P106" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="107" spans="6:16">
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+    </row>
+    <row r="107" spans="6:23">
       <c r="F107" s="14" t="s">
         <v>9</v>
       </c>
@@ -9076,17 +9139,22 @@
       </c>
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
-    </row>
-    <row r="108" spans="6:16">
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
+      <c r="V107" s="1"/>
+      <c r="W107" s="1"/>
+    </row>
+    <row r="108" spans="6:23">
       <c r="F108" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G108" s="10">
-        <v>1</v>
-      </c>
-      <c r="H108" s="5">
+      <c r="G108" s="10"/>
+      <c r="H108" s="5" t="str">
         <f>+IF(G108=1,$D$2,IF($G108=2,$D$3,IF($G108=3,$D$4,IF($G108=4,$D$5,""))))</f>
-        <v>18.75</v>
+        <v/>
       </c>
       <c r="I108" s="10"/>
       <c r="J108" s="5" t="str">
@@ -9105,8 +9173,15 @@
       </c>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
-    </row>
-    <row r="109" spans="6:16">
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
+      <c r="T108" s="1"/>
+      <c r="U108" s="1"/>
+      <c r="V108" s="1"/>
+      <c r="W108" s="1"/>
+    </row>
+    <row r="109" spans="6:23">
       <c r="F109" s="11" t="s">
         <v>13</v>
       </c>
@@ -9122,8 +9197,15 @@
       <c r="N109" s="5"/>
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
-    </row>
-    <row r="110" spans="6:16">
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+    </row>
+    <row r="110" spans="6:23">
       <c r="F110" s="11" t="s">
         <v>14</v>
       </c>
@@ -9139,15 +9221,20 @@
       <c r="N110" s="5"/>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
-    </row>
-    <row r="111" spans="6:16">
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1"/>
+      <c r="V110" s="1"/>
+      <c r="W110" s="1"/>
+    </row>
+    <row r="111" spans="6:23">
       <c r="F111" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G111" s="10"/>
-      <c r="H111" s="5">
-        <v>1</v>
-      </c>
+      <c r="H111" s="5"/>
       <c r="I111" s="10"/>
       <c r="J111" s="5"/>
       <c r="K111" s="10"/>
@@ -9156,18 +9243,25 @@
       <c r="N111" s="5"/>
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
-    </row>
-    <row r="112" spans="6:16" ht="15.75" customHeight="1">
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1"/>
+      <c r="V111" s="1"/>
+      <c r="W111" s="1"/>
+    </row>
+    <row r="112" spans="6:23" ht="15.75" customHeight="1">
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G112" s="118">
         <f>+SUM(H107:H111)</f>
-        <v>46.75</v>
+        <v>27</v>
       </c>
       <c r="H112" s="119">
         <f>+SUM(H107:H111)</f>
-        <v>46.75</v>
+        <v>27</v>
       </c>
       <c r="I112" s="118">
         <f>+SUM(J107:J111)</f>
@@ -9195,6 +9289,13 @@
       </c>
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
+      <c r="V112" s="1"/>
+      <c r="W112" s="1"/>
     </row>
     <row r="113" spans="6:23">
       <c r="F113" s="1"/>
@@ -9222,7 +9323,7 @@
       </c>
       <c r="G114" s="116">
         <f>+SUM(G112,G101)</f>
-        <v>334.25</v>
+        <v>314.5</v>
       </c>
       <c r="H114" s="117"/>
       <c r="I114" s="116">
@@ -9880,8 +9981,7 @@
   <dimension ref="A1:X35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="1" max="5" width="11.42578125" customWidth="1"/>
     <col min="6" max="12" width="11.42578125"/>
     <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -9937,7 +10037,7 @@
       </c>
       <c r="B2" s="17">
         <f>+SUM(Hoja1!$G8,Hoja1!$G21,Hoja1!$G34,Hoja1!$G47,Hoja1!$G60,Hoja1!G73,Hoja1!G86,Hoja1!G99,Hoja1!G112)</f>
-        <v>334.25</v>
+        <v>314.5</v>
       </c>
       <c r="C2" s="25">
         <f>INDEX(Hoja1!$G$1:$G$250, (COUNTIF(DATOS!$J$4:$S$4, "&gt;0")-1)*13 + 12)</f>
@@ -9949,7 +10049,7 @@
       </c>
       <c r="E2" s="1">
         <f>+AVERAGEIF(DATOS!C$3:C$22, "&gt;0")</f>
-        <v>1.9375</v>
+        <v>1.8823529411764706</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="29"/>
@@ -9962,7 +10062,7 @@
       </c>
       <c r="J2" s="31">
         <f>INDEX($B$2:$B$5, MATCH(H2, $D$2:$D$5, 0))</f>
-        <v>334.25</v>
+        <v>314.5</v>
       </c>
       <c r="K2" s="43">
         <f>INDEX($C$2:$C$5, MATCH(H2, $D$2:$D$5, 0))</f>
@@ -9971,11 +10071,11 @@
       <c r="L2" s="29"/>
       <c r="M2" s="47">
         <f>INDEX($E$2:$E$5, MATCH(I2, $A$2:$A$5, 0))</f>
-        <v>1.9375</v>
+        <v>1.8823529411764706</v>
       </c>
       <c r="N2" s="48">
         <f>J2 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.89371657754010692</v>
+        <v>0.74747474747474751</v>
       </c>
       <c r="O2" s="49">
         <f>SUM(DATOS!D27:D46)</f>
@@ -10009,7 +10109,7 @@
       </c>
       <c r="E3" s="1">
         <f>+AVERAGEIF(DATOS!D$3:D$22, "&gt;0")</f>
-        <v>1.875</v>
+        <v>1.9411764705882353</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="29"/>
@@ -10031,11 +10131,11 @@
       <c r="L3" s="29"/>
       <c r="M3" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I3, $A$2:$A$5, 0))</f>
-        <v>1.875</v>
+        <v>1.9411764705882353</v>
       </c>
       <c r="N3" s="39">
         <f>J3 / (COUNTIFS(DATOS!D3:D22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.8081550802139037</v>
+        <v>0.71836007130124779</v>
       </c>
       <c r="O3" s="41">
         <f>+SUM(DATOS!C27:C46)</f>
@@ -10069,7 +10169,7 @@
       </c>
       <c r="E4" s="1">
         <f>+AVERAGEIF(DATOS!E$3:E$22, "&gt;0")</f>
-        <v>3.4375</v>
+        <v>3.4705882352941178</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="29"/>
@@ -10091,11 +10191,11 @@
       <c r="L4" s="1"/>
       <c r="M4" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I4, $A$2:$A$5, 0))</f>
-        <v>2.75</v>
+        <v>2.7647058823529411</v>
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.66176470588235292</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -10129,7 +10229,7 @@
       </c>
       <c r="E5" s="1">
         <f>+AVERAGEIF(DATOS!F$3:F$22, "&gt;0")</f>
-        <v>2.75</v>
+        <v>2.7647058823529411</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="29"/>
@@ -10151,11 +10251,11 @@
       <c r="L5" s="29"/>
       <c r="M5" s="46">
         <f>INDEX($E$2:$E$5, MATCH(I5, $A$2:$A$5, 0))</f>
-        <v>3.4375</v>
+        <v>3.4705882352941178</v>
       </c>
       <c r="N5" s="40">
         <f>J5 / (COUNTIFS(DATOS!F3:F22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.5581550802139037</v>
+        <v>0.49613784907902553</v>
       </c>
       <c r="O5" s="42">
         <f>+SUM(DATOS!F27:F46)</f>
@@ -11002,7 +11102,7 @@
       </c>
       <c r="R4" s="1">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>334.25</v>
+        <v>314.5</v>
       </c>
       <c r="S4" s="1" t="e">
         <f>IF(INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$G$1:$G$250, (COLUMN(J1)-1)*13 + 10))</f>
@@ -11586,25 +11686,27 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="125"/>
+      <c r="A19" s="125" t="s">
+        <v>67</v>
+      </c>
       <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="1">
-        <f>Hoja1!G109</f>
-        <v>0</v>
+        <f>Hoja1!G107</f>
+        <v>1</v>
       </c>
       <c r="D19" s="1">
-        <f>Hoja1!I109</f>
-        <v>0</v>
+        <f>Hoja1!I107</f>
+        <v>3</v>
       </c>
       <c r="E19" s="1">
-        <f>Hoja1!K109</f>
-        <v>0</v>
+        <f>Hoja1!K107</f>
+        <v>4</v>
       </c>
       <c r="F19" s="1">
-        <f>Hoja1!M109</f>
-        <v>0</v>
+        <f>Hoja1!M107</f>
+        <v>3</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -11679,12 +11781,12 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
         <f>+COUNTIF(C3:C22,1)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" ref="D24:F24" si="0">+COUNTIF(D3:D22,1)</f>
@@ -11716,16 +11818,16 @@
         <v>46</v>
       </c>
       <c r="B26" s="121"/>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="104" t="s">
+      <c r="D26" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="104" t="s">
+      <c r="E26" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="104" t="s">
+      <c r="F26" s="105" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="1"/>
@@ -11735,7 +11837,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="121">
         <f>Hoja1!H5</f>
@@ -11769,7 +11871,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="121">
         <f>Hoja1!H18</f>
@@ -11803,7 +11905,7 @@
         <v>18</v>
       </c>
       <c r="B31" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="121">
         <f>Hoja1!H31</f>
@@ -11837,7 +11939,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C33" s="121">
         <f>Hoja1!H44</f>
@@ -11871,7 +11973,7 @@
         <v>63</v>
       </c>
       <c r="B35" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="121">
         <f>Hoja1!H57</f>
@@ -11905,7 +12007,7 @@
         <v>64</v>
       </c>
       <c r="B37" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C37" s="121">
         <f>Hoja1!H70</f>
@@ -11939,7 +12041,7 @@
         <v>65</v>
       </c>
       <c r="B39" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39" s="121">
         <f>Hoja1!H83</f>
@@ -11973,7 +12075,7 @@
         <v>66</v>
       </c>
       <c r="B41" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41" s="121">
         <f>Hoja1!H96</f>
@@ -12003,9 +12105,11 @@
       <c r="G42" s="121"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="125"/>
+      <c r="A43" s="125" t="s">
+        <v>67</v>
+      </c>
       <c r="B43" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" s="121">
         <f>Hoja1!H109</f>
@@ -12028,7 +12132,7 @@
     <row r="45" spans="1:7">
       <c r="A45" s="125"/>
       <c r="B45" s="125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="121">
         <f>Hoja1!H122</f>
@@ -12179,19 +12283,19 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -13108,7 +13212,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>4</v>
@@ -13123,20 +13227,20 @@
       </c>
       <c r="E34" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 7, CHOOSE(MOD(ROW(A33)-1,4)+1, 8, 10, 12, 14))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13)))</f>
         <v>1</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A33)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -13164,7 +13268,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -13192,7 +13296,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
@@ -13359,16 +13463,16 @@
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="104" t="s">
+      <c r="D3" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E3" s="105" t="s">
         <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -14078,7 +14182,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="125" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>81</v>
@@ -14999,7 +15103,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="128" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B26" s="62" t="s">
         <v>81</v>
@@ -15285,7 +15389,7 @@
     <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
@@ -16155,7 +16259,7 @@
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
       <c r="H25" s="106"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="101"/>
       <c r="J25" s="1"/>
       <c r="K25" s="106" t="s">
         <v>106</v>
@@ -16537,7 +16641,10 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
+      <c r="W32" s="58">
+        <f>+SUM(D52*1.15)</f>
+        <v>1.2835391865079365E-3</v>
+      </c>
       <c r="X32" s="1"/>
     </row>
     <row r="33" spans="1:24">
@@ -16711,7 +16818,10 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
+      <c r="W35" s="58">
+        <f>+SUM(F50*1.05)</f>
+        <v>1.2315920138888891E-3</v>
+      </c>
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="1:24">
@@ -16885,7 +16995,7 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
+      <c r="W38" s="58"/>
       <c r="X38" s="1"/>
     </row>
     <row r="39" spans="1:24">
@@ -16943,7 +17053,10 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
+      <c r="W39" s="58">
+        <f>+SUM(F54*1.1)</f>
+        <v>1.2443495370370371E-3</v>
+      </c>
       <c r="X39" s="1"/>
     </row>
     <row r="40" spans="1:24">
@@ -17349,8 +17462,13 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
+      <c r="W46" s="58">
+        <v>1.0964814814814813E-3</v>
+      </c>
+      <c r="X46" s="58">
+        <f>+SUM(W46*1.05)</f>
+        <v>1.1513055555555554E-3</v>
+      </c>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="131">
@@ -17408,7 +17526,10 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
+      <c r="X47" s="58">
+        <f>+SUM(W46*1.7)</f>
+        <v>1.8640185185185181E-3</v>
+      </c>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="1"/>
@@ -17467,23 +17588,23 @@
         <v>111</v>
       </c>
       <c r="B50" s="58">
-        <f>+AVERAGE(B28:B38,B43:B47)</f>
-        <v>1.1482284432870371E-3</v>
+        <f>+AVERAGE(B28:B36,B43:B47)</f>
+        <v>1.1312218915343914E-3</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="58">
-        <f>+AVERAGE(D28:D38,D43:D47)</f>
-        <v>1.1257624421296296E-3</v>
+        <f>+AVERAGE(D28:D36,D43:D47)</f>
+        <v>1.1161210317460319E-3</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="58">
-        <f>+AVERAGE(F28:F38,F43:F47)</f>
-        <v>1.1765842013888889E-3</v>
+        <f>+AVERAGE(F28:F36,F43:F47)</f>
+        <v>1.1729447751322752E-3</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="58">
-        <f>+AVERAGE(H28:H38,H43:H47)</f>
-        <v>1.1765842013888889E-3</v>
+        <f>+AVERAGE(H28:H36,H43:H47)</f>
+        <v>1.1729447751322752E-3</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -17546,21 +17667,21 @@
       <c r="A52" s="1"/>
       <c r="B52" s="91">
         <f>+SUM(B50-D50)</f>
-        <v>2.2466001157407569E-5</v>
+        <v>1.5100859788359528E-5</v>
       </c>
       <c r="C52" s="90"/>
       <c r="D52" s="58">
-        <v>1.1257624421296296E-3</v>
+        <v>1.1161210317460319E-3</v>
       </c>
       <c r="E52" s="90"/>
       <c r="F52" s="91">
         <f>+SUM(F50-D50)</f>
-        <v>5.0821759259259353E-5</v>
+        <v>5.6823743386243304E-5</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="91">
         <f>+SUM(H50-D50)</f>
-        <v>5.0821759259259353E-5</v>
+        <v>5.6823743386243304E-5</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -18531,7 +18652,9 @@
       <c r="X76" s="1"/>
     </row>
     <row r="77" spans="1:24">
-      <c r="A77" s="1"/>
+      <c r="A77" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="B77" s="58" t="e">
         <f>+AVERAGE(B55:B64,B68:B74)</f>
         <v>#DIV/0!</v>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFC9D96D-D57C-484B-93F4-9D7E75432918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A96C6C-CB6D-4769-B436-B7CDA0BD7C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="200" r:id="rId9"/>
+    <pivotCache cacheId="324" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1065,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1262,8 +1262,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1277,61 +1325,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2000,7 +2003,7 @@
                   <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>247.5</c:v>
+                  <c:v>250.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>#N/A</c:v>
@@ -5193,7 +5196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="200" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="324" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5850,14 +5853,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="121"/>
+      <c r="D1" s="108"/>
       <c r="E1" s="1"/>
       <c r="F1" s="115" t="s">
         <v>2</v>
@@ -6221,26 +6224,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="120">
+      <c r="G8" s="119">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="120">
+      <c r="H8" s="117"/>
+      <c r="I8" s="119">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="119"/>
-      <c r="K8" s="120">
+      <c r="J8" s="117"/>
+      <c r="K8" s="119">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="119"/>
-      <c r="M8" s="120">
+      <c r="L8" s="117"/>
+      <c r="M8" s="119">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="119"/>
+      <c r="N8" s="117"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -6296,26 +6299,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="122">
+      <c r="G10" s="118">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122">
+      <c r="H10" s="118"/>
+      <c r="I10" s="118">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122">
+      <c r="J10" s="118"/>
+      <c r="K10" s="118">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122">
+      <c r="L10" s="118"/>
+      <c r="M10" s="118">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="122"/>
+      <c r="N10" s="118"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6348,26 +6351,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="113">
+      <c r="G11" s="109">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="114"/>
-      <c r="I11" s="113">
+      <c r="H11" s="110"/>
+      <c r="I11" s="109">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="114"/>
-      <c r="K11" s="113">
+      <c r="J11" s="110"/>
+      <c r="K11" s="109">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="114"/>
-      <c r="M11" s="113">
+      <c r="L11" s="110"/>
+      <c r="M11" s="109">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="114"/>
+      <c r="N11" s="110"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6390,26 +6393,26 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="113">
+      <c r="G12" s="109">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="114"/>
-      <c r="I12" s="113">
+      <c r="H12" s="110"/>
+      <c r="I12" s="109">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="114"/>
-      <c r="K12" s="113">
+      <c r="J12" s="110"/>
+      <c r="K12" s="109">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="114"/>
-      <c r="M12" s="113">
+      <c r="L12" s="110"/>
+      <c r="M12" s="109">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="114"/>
+      <c r="N12" s="110"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -6710,26 +6713,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="120">
+      <c r="G21" s="119">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="119"/>
-      <c r="I21" s="118">
+      <c r="H21" s="117"/>
+      <c r="I21" s="116">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="119"/>
-      <c r="K21" s="118">
+      <c r="J21" s="117"/>
+      <c r="K21" s="116">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="118">
+      <c r="L21" s="117"/>
+      <c r="M21" s="116">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="119"/>
+      <c r="N21" s="117"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -6762,26 +6765,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="116">
+      <c r="G23" s="113">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="117"/>
-      <c r="I23" s="116">
+      <c r="H23" s="114"/>
+      <c r="I23" s="113">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="117"/>
-      <c r="K23" s="116">
+      <c r="J23" s="114"/>
+      <c r="K23" s="113">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="117"/>
-      <c r="M23" s="116">
+      <c r="L23" s="114"/>
+      <c r="M23" s="113">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="117"/>
+      <c r="N23" s="114"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6795,26 +6798,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="113">
+      <c r="G24" s="109">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="114"/>
-      <c r="I24" s="113">
+      <c r="H24" s="110"/>
+      <c r="I24" s="109">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="114"/>
-      <c r="K24" s="113">
+      <c r="J24" s="110"/>
+      <c r="K24" s="109">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="114"/>
-      <c r="M24" s="113">
+      <c r="L24" s="110"/>
+      <c r="M24" s="109">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="114"/>
+      <c r="N24" s="110"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6828,26 +6831,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="113">
+      <c r="G25" s="109">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="114"/>
-      <c r="I25" s="113">
+      <c r="H25" s="110"/>
+      <c r="I25" s="109">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="114"/>
-      <c r="K25" s="113">
+      <c r="J25" s="110"/>
+      <c r="K25" s="109">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="114"/>
-      <c r="M25" s="113">
+      <c r="L25" s="110"/>
+      <c r="M25" s="109">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="114"/>
+      <c r="N25" s="110"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -7087,26 +7090,26 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="118">
+      <c r="G34" s="116">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="119"/>
-      <c r="I34" s="118">
+      <c r="H34" s="117"/>
+      <c r="I34" s="116">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="119"/>
-      <c r="K34" s="118">
+      <c r="J34" s="117"/>
+      <c r="K34" s="116">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="119"/>
-      <c r="M34" s="118">
+      <c r="L34" s="117"/>
+      <c r="M34" s="116">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="119"/>
+      <c r="N34" s="117"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -7141,26 +7144,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="116">
+      <c r="G36" s="113">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="117"/>
-      <c r="I36" s="116">
+      <c r="H36" s="114"/>
+      <c r="I36" s="113">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="117"/>
-      <c r="K36" s="116">
+      <c r="J36" s="114"/>
+      <c r="K36" s="113">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="117"/>
-      <c r="M36" s="116">
+      <c r="L36" s="114"/>
+      <c r="M36" s="113">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="117"/>
+      <c r="N36" s="114"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7175,26 +7178,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="113">
+      <c r="G37" s="109">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="114"/>
-      <c r="I37" s="113">
+      <c r="H37" s="110"/>
+      <c r="I37" s="109">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="114"/>
-      <c r="K37" s="113">
+      <c r="J37" s="110"/>
+      <c r="K37" s="109">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="114"/>
-      <c r="M37" s="113">
+      <c r="L37" s="110"/>
+      <c r="M37" s="109">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="114"/>
+      <c r="N37" s="110"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7209,26 +7212,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="113">
+      <c r="G38" s="109">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="114"/>
-      <c r="I38" s="113">
+      <c r="H38" s="110"/>
+      <c r="I38" s="109">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="114"/>
-      <c r="K38" s="113">
+      <c r="J38" s="110"/>
+      <c r="K38" s="109">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="114"/>
-      <c r="M38" s="113">
+      <c r="L38" s="110"/>
+      <c r="M38" s="109">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="114"/>
+      <c r="N38" s="110"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7481,26 +7484,26 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="118">
+      <c r="G47" s="116">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="119"/>
-      <c r="I47" s="118">
+      <c r="H47" s="117"/>
+      <c r="I47" s="116">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="119"/>
-      <c r="K47" s="118">
+      <c r="J47" s="117"/>
+      <c r="K47" s="116">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="119"/>
-      <c r="M47" s="118">
+      <c r="L47" s="117"/>
+      <c r="M47" s="116">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="119"/>
+      <c r="N47" s="117"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -7535,26 +7538,26 @@
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="116">
+      <c r="G49" s="113">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="117"/>
-      <c r="I49" s="116">
+      <c r="H49" s="114"/>
+      <c r="I49" s="113">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="117"/>
-      <c r="K49" s="116">
+      <c r="J49" s="114"/>
+      <c r="K49" s="113">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="117"/>
-      <c r="M49" s="116">
+      <c r="L49" s="114"/>
+      <c r="M49" s="113">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="117"/>
+      <c r="N49" s="114"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
     </row>
@@ -7562,26 +7565,26 @@
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="113">
+      <c r="G50" s="109">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="114"/>
-      <c r="I50" s="113">
+      <c r="H50" s="110"/>
+      <c r="I50" s="109">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="114"/>
-      <c r="K50" s="113">
+      <c r="J50" s="110"/>
+      <c r="K50" s="109">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="114"/>
-      <c r="M50" s="113">
+      <c r="L50" s="110"/>
+      <c r="M50" s="109">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="114"/>
+      <c r="N50" s="110"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
     </row>
@@ -7589,26 +7592,26 @@
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="113">
+      <c r="G51" s="109">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="114"/>
-      <c r="I51" s="113">
+      <c r="H51" s="110"/>
+      <c r="I51" s="109">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="114"/>
-      <c r="K51" s="113">
+      <c r="J51" s="110"/>
+      <c r="K51" s="109">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="114"/>
-      <c r="M51" s="113">
+      <c r="L51" s="110"/>
+      <c r="M51" s="109">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="114"/>
+      <c r="N51" s="110"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
     </row>
@@ -7798,26 +7801,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="118">
+      <c r="G60" s="116">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="119"/>
-      <c r="I60" s="118">
+      <c r="H60" s="117"/>
+      <c r="I60" s="116">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="119"/>
-      <c r="K60" s="118">
+      <c r="J60" s="117"/>
+      <c r="K60" s="116">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="119"/>
-      <c r="M60" s="118">
+      <c r="L60" s="117"/>
+      <c r="M60" s="116">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="119"/>
+      <c r="N60" s="117"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
     </row>
@@ -7838,26 +7841,26 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="116">
+      <c r="G62" s="113">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="117"/>
-      <c r="I62" s="116">
+      <c r="H62" s="114"/>
+      <c r="I62" s="113">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="117"/>
-      <c r="K62" s="116">
+      <c r="J62" s="114"/>
+      <c r="K62" s="113">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="117"/>
-      <c r="M62" s="116">
+      <c r="L62" s="114"/>
+      <c r="M62" s="113">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="117"/>
+      <c r="N62" s="114"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
     </row>
@@ -7865,26 +7868,26 @@
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="113">
+      <c r="G63" s="109">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="114"/>
-      <c r="I63" s="113">
+      <c r="H63" s="110"/>
+      <c r="I63" s="109">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="114"/>
-      <c r="K63" s="113">
+      <c r="J63" s="110"/>
+      <c r="K63" s="109">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="114"/>
-      <c r="M63" s="113">
+      <c r="L63" s="110"/>
+      <c r="M63" s="109">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="114"/>
+      <c r="N63" s="110"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
     </row>
@@ -7892,26 +7895,26 @@
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="113">
+      <c r="G64" s="109">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="114"/>
-      <c r="I64" s="113">
+      <c r="H64" s="110"/>
+      <c r="I64" s="109">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="114"/>
-      <c r="K64" s="113">
+      <c r="J64" s="110"/>
+      <c r="K64" s="109">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="114"/>
-      <c r="M64" s="113">
+      <c r="L64" s="110"/>
+      <c r="M64" s="109">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="114"/>
+      <c r="N64" s="110"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
     </row>
@@ -8088,35 +8091,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="118">
+      <c r="G73" s="116">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="119">
+      <c r="H73" s="117">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="118">
+      <c r="I73" s="116">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="119">
+      <c r="J73" s="117">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="118">
+      <c r="K73" s="116">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="119">
+      <c r="L73" s="117">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="118">
+      <c r="M73" s="116">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="119">
+      <c r="N73" s="117">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -8140,26 +8143,26 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="116">
+      <c r="G75" s="113">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="117"/>
-      <c r="I75" s="116">
+      <c r="H75" s="114"/>
+      <c r="I75" s="113">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="117"/>
-      <c r="K75" s="116">
+      <c r="J75" s="114"/>
+      <c r="K75" s="113">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="117"/>
-      <c r="M75" s="116">
+      <c r="L75" s="114"/>
+      <c r="M75" s="113">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="117"/>
+      <c r="N75" s="114"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
     </row>
@@ -8167,26 +8170,26 @@
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="113">
+      <c r="G76" s="109">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="114"/>
-      <c r="I76" s="113">
+      <c r="H76" s="110"/>
+      <c r="I76" s="109">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="114"/>
-      <c r="K76" s="113">
+      <c r="J76" s="110"/>
+      <c r="K76" s="109">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="114"/>
-      <c r="M76" s="113">
+      <c r="L76" s="110"/>
+      <c r="M76" s="109">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="114"/>
+      <c r="N76" s="110"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
     </row>
@@ -8194,26 +8197,26 @@
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="113">
+      <c r="G77" s="109">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="114"/>
-      <c r="I77" s="113">
+      <c r="H77" s="110"/>
+      <c r="I77" s="109">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="114"/>
-      <c r="K77" s="113">
+      <c r="J77" s="110"/>
+      <c r="K77" s="109">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="114"/>
-      <c r="M77" s="113">
+      <c r="L77" s="110"/>
+      <c r="M77" s="109">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="114"/>
+      <c r="N77" s="110"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
     </row>
@@ -8440,35 +8443,35 @@
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="118">
+      <c r="G86" s="116">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="119">
+      <c r="H86" s="117">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="118">
+      <c r="I86" s="116">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="119">
+      <c r="J86" s="117">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="118">
+      <c r="K86" s="116">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="L86" s="119">
+      <c r="L86" s="117">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="M86" s="118">
+      <c r="M86" s="116">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
-      <c r="N86" s="119">
+      <c r="N86" s="117">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
@@ -8512,26 +8515,26 @@
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="116">
+      <c r="G88" s="113">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="117"/>
-      <c r="I88" s="116">
+      <c r="H88" s="114"/>
+      <c r="I88" s="113">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="117"/>
-      <c r="K88" s="116">
+      <c r="J88" s="114"/>
+      <c r="K88" s="113">
         <f>+SUM(K86,K75)</f>
         <v>172.75</v>
       </c>
-      <c r="L88" s="117"/>
-      <c r="M88" s="116">
+      <c r="L88" s="114"/>
+      <c r="M88" s="113">
         <f>+SUM(M86,M75)</f>
         <v>209.25</v>
       </c>
-      <c r="N88" s="117"/>
+      <c r="N88" s="114"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -8549,26 +8552,26 @@
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="113">
+      <c r="G89" s="109">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="114"/>
-      <c r="I89" s="113">
+      <c r="H89" s="110"/>
+      <c r="I89" s="109">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="114"/>
-      <c r="K89" s="113">
+      <c r="J89" s="110"/>
+      <c r="K89" s="109">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L89" s="114"/>
-      <c r="M89" s="113">
+      <c r="L89" s="110"/>
+      <c r="M89" s="109">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N89" s="114"/>
+      <c r="N89" s="110"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -8586,26 +8589,26 @@
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="113">
+      <c r="G90" s="109">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="114"/>
-      <c r="I90" s="113">
+      <c r="H90" s="110"/>
+      <c r="I90" s="109">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="114"/>
-      <c r="K90" s="113">
+      <c r="J90" s="110"/>
+      <c r="K90" s="109">
         <f>+SUM(K89+K77-K50)</f>
         <v>10</v>
       </c>
-      <c r="L90" s="114"/>
-      <c r="M90" s="113">
+      <c r="L90" s="110"/>
+      <c r="M90" s="109">
         <f>+SUM(M89+M77-M50)</f>
         <v>60</v>
       </c>
-      <c r="N90" s="114"/>
+      <c r="N90" s="110"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -8879,35 +8882,35 @@
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="118">
+      <c r="G99" s="116">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="119">
+      <c r="H99" s="117">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="118">
+      <c r="I99" s="116">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="119">
+      <c r="J99" s="117">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="118">
+      <c r="K99" s="116">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="L99" s="119">
+      <c r="L99" s="117">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="M99" s="118">
+      <c r="M99" s="116">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-      <c r="N99" s="119">
+      <c r="N99" s="117">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
@@ -8945,26 +8948,26 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="116">
+      <c r="G101" s="113">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="117"/>
-      <c r="I101" s="116">
+      <c r="H101" s="114"/>
+      <c r="I101" s="113">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="117"/>
-      <c r="K101" s="116">
+      <c r="J101" s="114"/>
+      <c r="K101" s="113">
         <f>+SUM(K99,K88)</f>
         <v>196.75</v>
       </c>
-      <c r="L101" s="117"/>
-      <c r="M101" s="116">
+      <c r="L101" s="114"/>
+      <c r="M101" s="113">
         <f>+SUM(M99,M88)</f>
         <v>232.5</v>
       </c>
-      <c r="N101" s="117"/>
+      <c r="N101" s="114"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
@@ -8979,26 +8982,26 @@
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="113">
+      <c r="G102" s="109">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="114"/>
-      <c r="I102" s="113">
+      <c r="H102" s="110"/>
+      <c r="I102" s="109">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="114"/>
-      <c r="K102" s="113">
+      <c r="J102" s="110"/>
+      <c r="K102" s="109">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="114"/>
-      <c r="M102" s="113">
+      <c r="L102" s="110"/>
+      <c r="M102" s="109">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="114"/>
+      <c r="N102" s="110"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
@@ -9013,26 +9016,26 @@
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="113">
+      <c r="G103" s="109">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="114"/>
-      <c r="I103" s="113">
+      <c r="H103" s="110"/>
+      <c r="I103" s="109">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="114"/>
-      <c r="K103" s="113">
+      <c r="J103" s="110"/>
+      <c r="K103" s="109">
         <f>+SUM(K102+K90-K63)</f>
         <v>20</v>
       </c>
-      <c r="L103" s="114"/>
-      <c r="M103" s="113">
+      <c r="L103" s="110"/>
+      <c r="M103" s="109">
         <f>+SUM(M102+M90-M63)</f>
         <v>20</v>
       </c>
-      <c r="N103" s="114"/>
+      <c r="N103" s="110"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
@@ -9131,11 +9134,11 @@
         <v>12</v>
       </c>
       <c r="M107" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N107" s="6">
         <f>+IF(M107=1,$B$2,IF($M107=2,$B$3,IF($M107=3,$B$4,IF($M107=4,$B$5,""))))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
@@ -9166,7 +9169,7 @@
         <f>+IF(K108=1,$D$2,IF($K108=2,$D$3,IF($K108=3,$D$4,IF($K108=4,$D$5,""))))</f>
         <v/>
       </c>
-      <c r="M108" s="10"/>
+      <c r="M108" s="130"/>
       <c r="N108" s="5" t="str">
         <f>+IF(M108=1,$D$2,IF($M108=2,$D$3,IF($M108=3,$D$4,IF($M108=4,$D$5,""))))</f>
         <v/>
@@ -9255,37 +9258,37 @@
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="118">
+      <c r="G112" s="116">
         <f>+SUM(H107:H111)</f>
         <v>27</v>
       </c>
-      <c r="H112" s="119">
+      <c r="H112" s="117">
         <f>+SUM(H107:H111)</f>
         <v>27</v>
       </c>
-      <c r="I112" s="118">
+      <c r="I112" s="116">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="J112" s="119">
+      <c r="J112" s="117">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="K112" s="118">
+      <c r="K112" s="116">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="L112" s="119">
+      <c r="L112" s="117">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="M112" s="118">
+      <c r="M112" s="116">
         <f>+SUM(N107:N111)</f>
-        <v>15</v>
-      </c>
-      <c r="N112" s="119">
+        <v>18</v>
+      </c>
+      <c r="N112" s="117">
         <f>+SUM(N107:N111)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
@@ -9321,33 +9324,41 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="116">
+      <c r="G114" s="113">
         <f>+SUM(G112,G101)</f>
         <v>314.5</v>
       </c>
-      <c r="H114" s="117"/>
-      <c r="I114" s="116">
+      <c r="H114" s="114"/>
+      <c r="I114" s="113">
         <f>+SUM(I112,I101)</f>
         <v>302.25</v>
       </c>
-      <c r="J114" s="117"/>
-      <c r="K114" s="116">
+      <c r="J114" s="114"/>
+      <c r="K114" s="113">
         <f>+SUM(K112,K101)</f>
         <v>208.75</v>
       </c>
-      <c r="L114" s="117"/>
-      <c r="M114" s="116">
+      <c r="L114" s="114"/>
+      <c r="M114" s="113">
         <f>+SUM(M112,M101)</f>
-        <v>247.5</v>
-      </c>
-      <c r="N114" s="117"/>
+        <v>250.5</v>
+      </c>
+      <c r="N114" s="114"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
-      <c r="R114" s="1"/>
-      <c r="S114" s="1"/>
+      <c r="R114" s="1">
+        <v>348.5</v>
+      </c>
+      <c r="S114" s="1">
+        <f>+SUM(R114+21.5)</f>
+        <v>370</v>
+      </c>
       <c r="T114" s="1"/>
-      <c r="U114" s="1"/>
+      <c r="U114" s="1">
+        <f>+SUM(S114-46.75)</f>
+        <v>323.25</v>
+      </c>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
     </row>
@@ -9355,26 +9366,26 @@
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="113">
+      <c r="G115" s="109">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H115" s="114"/>
-      <c r="I115" s="113">
+      <c r="H115" s="110"/>
+      <c r="I115" s="109">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J115" s="114"/>
-      <c r="K115" s="113">
+      <c r="J115" s="110"/>
+      <c r="K115" s="109">
         <f>+IF($K107=1,40,IF($K107=2,20,IF($K107=3,10,IF($K107=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L115" s="114"/>
-      <c r="M115" s="113">
+      <c r="L115" s="110"/>
+      <c r="M115" s="109">
         <f>+IF($M107=1,40,IF($M107=2,20,IF($M107=3,10,IF($M107=4,0,""))))</f>
-        <v>10</v>
-      </c>
-      <c r="N115" s="114"/>
+        <v>20</v>
+      </c>
+      <c r="N115" s="110"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
@@ -9389,26 +9400,26 @@
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="113">
+      <c r="G116" s="109">
         <f>+SUM(G115+G103-G76)</f>
         <v>100</v>
       </c>
-      <c r="H116" s="114"/>
-      <c r="I116" s="113">
+      <c r="H116" s="110"/>
+      <c r="I116" s="109">
         <f>+SUM(I115+I103-I76)</f>
         <v>70</v>
       </c>
-      <c r="J116" s="114"/>
-      <c r="K116" s="113">
+      <c r="J116" s="110"/>
+      <c r="K116" s="109">
         <f>+SUM(K115+K103-K76)</f>
         <v>20</v>
       </c>
-      <c r="L116" s="114"/>
-      <c r="M116" s="113">
+      <c r="L116" s="110"/>
+      <c r="M116" s="109">
         <f>+SUM(M115+M103-M76)</f>
-        <v>10</v>
-      </c>
-      <c r="N116" s="114"/>
+        <v>20</v>
+      </c>
+      <c r="N116" s="110"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
@@ -9619,29 +9630,29 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="118">
+      <c r="G125" s="116">
         <f>+SUM(H120:H121)</f>
         <v>0</v>
       </c>
-      <c r="H125" s="119">
+      <c r="H125" s="117">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="118">
+      <c r="I125" s="116">
         <f>+SUM(J120:J121)</f>
         <v>0</v>
       </c>
-      <c r="J125" s="119">
+      <c r="J125" s="117">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="118"/>
-      <c r="L125" s="119">
+      <c r="K125" s="116"/>
+      <c r="L125" s="117">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="118"/>
-      <c r="N125" s="119">
+      <c r="M125" s="116"/>
+      <c r="N125" s="117">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -9679,20 +9690,20 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="116"/>
-      <c r="H127" s="117"/>
-      <c r="I127" s="116"/>
-      <c r="J127" s="117"/>
-      <c r="K127" s="116">
+      <c r="G127" s="113"/>
+      <c r="H127" s="114"/>
+      <c r="I127" s="113"/>
+      <c r="J127" s="114"/>
+      <c r="K127" s="113">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="117"/>
-      <c r="M127" s="116">
+      <c r="L127" s="114"/>
+      <c r="M127" s="113">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="117"/>
+      <c r="N127" s="114"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1" t="s">
         <v>9</v>
@@ -9713,20 +9724,20 @@
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="113" t="str">
+      <c r="G128" s="109" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="114"/>
-      <c r="I128" s="123" t="str">
+      <c r="H128" s="110"/>
+      <c r="I128" s="111" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J128" s="124"/>
-      <c r="K128" s="116"/>
-      <c r="L128" s="117"/>
-      <c r="M128" s="116"/>
-      <c r="N128" s="117"/>
+      <c r="J128" s="112"/>
+      <c r="K128" s="113"/>
+      <c r="L128" s="114"/>
+      <c r="M128" s="113"/>
+      <c r="N128" s="114"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1">
         <v>37.5</v>
@@ -9750,26 +9761,26 @@
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="113">
+      <c r="G129" s="109">
         <f>G116</f>
         <v>100</v>
       </c>
-      <c r="H129" s="114"/>
-      <c r="I129" s="113">
+      <c r="H129" s="110"/>
+      <c r="I129" s="109">
         <f t="shared" ref="I129:N129" si="19">I116</f>
         <v>70</v>
       </c>
-      <c r="J129" s="114"/>
-      <c r="K129" s="113">
+      <c r="J129" s="110"/>
+      <c r="K129" s="109">
         <f t="shared" ref="K129:N129" si="20">K116</f>
         <v>20</v>
       </c>
-      <c r="L129" s="114"/>
-      <c r="M129" s="113">
+      <c r="L129" s="110"/>
+      <c r="M129" s="109">
         <f t="shared" ref="M129:N129" si="21">M116</f>
-        <v>10</v>
-      </c>
-      <c r="N129" s="114"/>
+        <v>20</v>
+      </c>
+      <c r="N129" s="110"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1">
         <v>28.125</v>
@@ -9791,110 +9802,54 @@
     </row>
   </sheetData>
   <mergeCells count="176">
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="R2:Z2"/>
+    <mergeCell ref="R6:Z6"/>
+    <mergeCell ref="R9:Z9"/>
+    <mergeCell ref="R12:Z12"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="F66:N66"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="I11:J11"/>
@@ -9919,54 +9874,110 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="R2:Z2"/>
-    <mergeCell ref="R6:Z6"/>
-    <mergeCell ref="R9:Z9"/>
-    <mergeCell ref="R12:Z12"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="F66:N66"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10182,20 +10193,20 @@
       </c>
       <c r="J4" s="31">
         <f t="shared" si="1"/>
-        <v>247.5</v>
+        <v>250.5</v>
       </c>
       <c r="K4" s="43">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="45">
         <f>INDEX($E$2:$E$5, MATCH(I4, $A$2:$A$5, 0))</f>
-        <v>2.7647058823529411</v>
+        <v>2.7058823529411766</v>
       </c>
       <c r="N4" s="39">
         <f>J4 / (COUNTIFS(DATOS!E3:E22, "&gt;0",DATOS!$B$3:$B$22, "CARRERA 1") * 46.75)</f>
-        <v>0.58823529411764708</v>
+        <v>0.59536541889483063</v>
       </c>
       <c r="O4" s="41">
         <f>+SUM(DATOS!E27:E46)</f>
@@ -10217,11 +10228,11 @@
       </c>
       <c r="B5" s="20">
         <f>+SUM(Hoja1!M8,Hoja1!M21,Hoja1!M34,Hoja1!M47,Hoja1!M60,Hoja1!M73,Hoja1!M86,Hoja1!M99,,Hoja1!M112)</f>
-        <v>247.5</v>
+        <v>250.5</v>
       </c>
       <c r="C5" s="26">
         <f>INDEX(Hoja1!$M$1:$M$250, (COUNTIF(DATOS!$J$7:$S$7, "&gt;0")-1)*13 + 12)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
         <f>_xlfn.RANK.EQ(B5, $B$2:$B$5) + COUNTIF($B$2:B5, B5) - 1</f>
@@ -10229,7 +10240,7 @@
       </c>
       <c r="E5" s="1">
         <f>+AVERAGEIF(DATOS!F$3:F$22, "&gt;0")</f>
-        <v>2.7647058823529411</v>
+        <v>2.7058823529411766</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="29"/>
@@ -10940,25 +10951,25 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="126" t="s">
+      <c r="I1" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="121"/>
+      <c r="B2" s="108"/>
       <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
@@ -10973,20 +10984,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="126"/>
-      <c r="P2" s="126"/>
-      <c r="Q2" s="126"/>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="106" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11043,7 +11054,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="125"/>
+      <c r="A4" s="106"/>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
@@ -11110,7 +11121,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="106" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -11179,7 +11190,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="125"/>
+      <c r="A6" s="106"/>
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
@@ -11246,7 +11257,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="106" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -11307,7 +11318,7 @@
       </c>
       <c r="R7" s="1">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(I1)-1)*13 + 10))</f>
-        <v>247.5</v>
+        <v>250.5</v>
       </c>
       <c r="S7" s="1" t="e">
         <f>IF(INDEX(Hoja1!$M$1:$M$250, (COLUMN(J1)-1)*13 + 10)=0, NA(), INDEX(Hoja1!$M$1:$M$250, (COLUMN(J1)-1)*13 + 10))</f>
@@ -11315,7 +11326,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="125"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
@@ -11350,7 +11361,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="106" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -11387,7 +11398,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="125"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
@@ -11422,7 +11433,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="125" t="s">
+      <c r="A11" s="106" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -11459,7 +11470,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="125"/>
+      <c r="A12" s="106"/>
       <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
@@ -11494,7 +11505,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="125" t="s">
+      <c r="A13" s="106" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -11531,7 +11542,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="125"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
@@ -11566,7 +11577,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="106" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -11603,7 +11614,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="125"/>
+      <c r="A16" s="106"/>
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
@@ -11638,7 +11649,7 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="125" t="s">
+      <c r="A17" s="106" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -11663,7 +11674,7 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="125"/>
+      <c r="A18" s="106"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
@@ -11686,7 +11697,7 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="125" t="s">
+      <c r="A19" s="106" t="s">
         <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -11706,12 +11717,12 @@
       </c>
       <c r="F19" s="1">
         <f>Hoja1!M107</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="125"/>
+      <c r="A20" s="106"/>
       <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
@@ -11734,7 +11745,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="125"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
@@ -11757,7 +11768,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="125"/>
+      <c r="A22" s="106"/>
       <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
@@ -11803,21 +11814,21 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="121" t="s">
+      <c r="A25" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="121" t="s">
+      <c r="A26" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="121"/>
+      <c r="B26" s="108"/>
       <c r="C26" s="105" t="s">
         <v>47</v>
       </c>
@@ -11833,324 +11844,324 @@
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="121">
+      <c r="C27" s="108">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="121">
+      <c r="D27" s="108">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="121">
+      <c r="E27" s="108">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="121">
+      <c r="F27" s="108">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="121"/>
+      <c r="G27" s="108"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="125"/>
-      <c r="B28" s="125"/>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="121"/>
-      <c r="G28" s="121"/>
+      <c r="A28" s="106"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="125" t="s">
+      <c r="A29" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="125" t="s">
+      <c r="B29" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="121">
+      <c r="C29" s="108">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="121">
+      <c r="D29" s="108">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="121">
+      <c r="E29" s="108">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="121">
+      <c r="F29" s="108">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="121"/>
+      <c r="G29" s="108"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="125"/>
-      <c r="B30" s="125"/>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="125" t="s">
+      <c r="A31" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="125" t="s">
+      <c r="B31" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="121">
+      <c r="C31" s="108">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="121">
+      <c r="D31" s="108">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="121">
+      <c r="E31" s="108">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="121">
+      <c r="F31" s="108">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="121"/>
+      <c r="G31" s="108"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="125"/>
-      <c r="B32" s="125"/>
-      <c r="C32" s="121"/>
-      <c r="D32" s="121"/>
-      <c r="E32" s="121"/>
-      <c r="F32" s="121"/>
-      <c r="G32" s="121"/>
+      <c r="A32" s="106"/>
+      <c r="B32" s="106"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="125" t="s">
+      <c r="A33" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="125" t="s">
+      <c r="B33" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="121">
+      <c r="C33" s="108">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="121">
+      <c r="D33" s="108">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="121">
+      <c r="E33" s="108">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="121">
+      <c r="F33" s="108">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="121"/>
+      <c r="G33" s="108"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="125"/>
-      <c r="B34" s="125"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="121"/>
-      <c r="E34" s="121"/>
-      <c r="F34" s="121"/>
-      <c r="G34" s="121"/>
+      <c r="A34" s="106"/>
+      <c r="B34" s="106"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="125" t="s">
+      <c r="B35" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="121">
+      <c r="C35" s="108">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="121">
+      <c r="D35" s="108">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="121">
+      <c r="E35" s="108">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="121">
+      <c r="F35" s="108">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="121"/>
+      <c r="G35" s="108"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="125"/>
-      <c r="B36" s="125"/>
-      <c r="C36" s="121"/>
-      <c r="D36" s="121"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="121"/>
-      <c r="G36" s="121"/>
+      <c r="A36" s="106"/>
+      <c r="B36" s="106"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="125" t="s">
+      <c r="A37" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="125" t="s">
+      <c r="B37" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="121">
+      <c r="C37" s="108">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="121">
+      <c r="D37" s="108">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="121">
+      <c r="E37" s="108">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="121">
+      <c r="F37" s="108">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="121"/>
+      <c r="G37" s="108"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="125"/>
-      <c r="B38" s="125"/>
-      <c r="C38" s="121"/>
-      <c r="D38" s="121"/>
-      <c r="E38" s="121"/>
-      <c r="F38" s="121"/>
-      <c r="G38" s="121"/>
+      <c r="A38" s="106"/>
+      <c r="B38" s="106"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="125" t="s">
+      <c r="A39" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="125" t="s">
+      <c r="B39" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="121">
+      <c r="C39" s="108">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="121">
+      <c r="D39" s="108">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="121">
+      <c r="E39" s="108">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="121">
+      <c r="F39" s="108">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="121"/>
+      <c r="G39" s="108"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="125"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="121"/>
-      <c r="D40" s="121"/>
-      <c r="E40" s="121"/>
-      <c r="F40" s="121"/>
-      <c r="G40" s="121"/>
+      <c r="A40" s="106"/>
+      <c r="B40" s="106"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="125" t="s">
+      <c r="A41" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="125" t="s">
+      <c r="B41" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="121">
+      <c r="C41" s="108">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="121">
+      <c r="D41" s="108">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="121">
+      <c r="E41" s="108">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="121">
+      <c r="F41" s="108">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="121"/>
+      <c r="G41" s="108"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="125"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="121"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="121"/>
-      <c r="G42" s="121"/>
+      <c r="A42" s="106"/>
+      <c r="B42" s="106"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="125" t="s">
+      <c r="A43" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="125" t="s">
+      <c r="B43" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="121">
+      <c r="C43" s="108">
         <f>Hoja1!H109</f>
         <v>1</v>
       </c>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="121"/>
-      <c r="G43" s="121"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="125"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="121"/>
-      <c r="D44" s="121"/>
-      <c r="E44" s="121"/>
-      <c r="F44" s="121"/>
-      <c r="G44" s="121"/>
+      <c r="A44" s="106"/>
+      <c r="B44" s="106"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="125"/>
-      <c r="B45" s="125" t="s">
+      <c r="A45" s="106"/>
+      <c r="B45" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="121">
+      <c r="C45" s="108">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="121"/>
-      <c r="E45" s="121"/>
-      <c r="F45" s="121"/>
-      <c r="G45" s="121"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="125"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="121"/>
-      <c r="D46" s="121"/>
-      <c r="E46" s="121"/>
-      <c r="F46" s="121"/>
-      <c r="G46" s="121"/>
+      <c r="A46" s="106"/>
+      <c r="B46" s="106"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -12177,12 +12188,68 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
@@ -12199,68 +12266,12 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13315,7 +13326,7 @@
       </c>
       <c r="F37" s="1">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 3, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1" t="str">
         <f>IF(INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13))=0, "", INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 4, CHOOSE(MOD(ROW(A36)-1,4)+1, 7, 9, 11, 13)))</f>
@@ -13323,7 +13334,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="121"/>
+      <c r="A38" s="108"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -13349,7 +13360,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="121"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -13375,7 +13386,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="121"/>
+      <c r="A40" s="108"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -13401,7 +13412,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="121"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -13598,7 +13609,7 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="106" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -13621,7 +13632,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="125"/>
+      <c r="A3" s="106"/>
       <c r="B3" s="1" t="s">
         <v>82</v>
       </c>
@@ -13644,7 +13655,7 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="125"/>
+      <c r="A4" s="106"/>
       <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
@@ -13667,7 +13678,7 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="106" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -13684,7 +13695,7 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="125"/>
+      <c r="A6" s="106"/>
       <c r="B6" s="1" t="s">
         <v>82</v>
       </c>
@@ -13699,7 +13710,7 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="125"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="1" t="s">
         <v>83</v>
       </c>
@@ -13714,7 +13725,7 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="106" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -13731,7 +13742,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="125"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
@@ -13746,7 +13757,7 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="125"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
@@ -13769,7 +13780,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="125" t="s">
+      <c r="A11" s="106" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -13794,7 +13805,7 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="125"/>
+      <c r="A12" s="106"/>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
@@ -13809,7 +13820,7 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="125"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="1" t="s">
         <v>83</v>
       </c>
@@ -13824,7 +13835,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="106" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -13861,7 +13872,7 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="125"/>
+      <c r="A15" s="106"/>
       <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
@@ -13894,7 +13905,7 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="125"/>
+      <c r="A16" s="106"/>
       <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
@@ -13927,7 +13938,7 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="125" t="s">
+      <c r="A17" s="106" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -13957,7 +13968,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="125"/>
+      <c r="A18" s="106"/>
       <c r="B18" s="1" t="s">
         <v>82</v>
       </c>
@@ -13985,7 +13996,7 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="125"/>
+      <c r="A19" s="106"/>
       <c r="B19" s="1" t="s">
         <v>83</v>
       </c>
@@ -14013,7 +14024,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="106" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -14043,7 +14054,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="125"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="1" t="s">
         <v>82</v>
       </c>
@@ -14069,7 +14080,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="125"/>
+      <c r="A22" s="106"/>
       <c r="B22" s="1" t="s">
         <v>83</v>
       </c>
@@ -14095,7 +14106,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="125" t="s">
+      <c r="A23" s="106" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -14125,20 +14136,20 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="125"/>
+      <c r="A24" s="106"/>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="130">
+      <c r="C24" s="131">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="D24" s="130">
+      <c r="D24" s="131">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="E24" s="130">
+      <c r="E24" s="131">
         <v>1.1312268518518518E-3</v>
       </c>
-      <c r="F24" s="130">
+      <c r="F24" s="131">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G24" s="58"/>
@@ -14153,7 +14164,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="125"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="1" t="s">
         <v>83</v>
       </c>
@@ -14181,7 +14192,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="125" t="s">
+      <c r="A26" s="106" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -14209,7 +14220,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="125"/>
+      <c r="A27" s="106"/>
       <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
@@ -14233,7 +14244,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="125"/>
+      <c r="A28" s="106"/>
       <c r="B28" s="1" t="s">
         <v>83</v>
       </c>
@@ -14253,7 +14264,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="125" t="s">
+      <c r="A29" s="106" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="1"/>
@@ -14273,7 +14284,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="125"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="1"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -14291,7 +14302,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="125"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="1"/>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -14369,7 +14380,7 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
@@ -14414,7 +14425,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="128"/>
+      <c r="A3" s="121"/>
       <c r="B3" s="62" t="s">
         <v>82</v>
       </c>
@@ -14457,7 +14468,7 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="128"/>
+      <c r="A4" s="121"/>
       <c r="B4" s="62" t="s">
         <v>83</v>
       </c>
@@ -14500,7 +14511,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="120" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
@@ -14522,7 +14533,7 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="128"/>
+      <c r="A6" s="121"/>
       <c r="B6" s="62" t="s">
         <v>82</v>
       </c>
@@ -14542,7 +14553,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="129"/>
+      <c r="A7" s="122"/>
       <c r="B7" s="66" t="s">
         <v>83</v>
       </c>
@@ -14562,7 +14573,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="128" t="s">
+      <c r="A8" s="121" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
@@ -14584,7 +14595,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="128"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="62" t="s">
         <v>82</v>
       </c>
@@ -14604,7 +14615,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="129"/>
+      <c r="A10" s="122"/>
       <c r="B10" s="66" t="s">
         <v>83</v>
       </c>
@@ -14636,7 +14647,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="128" t="s">
+      <c r="A11" s="121" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
@@ -14670,7 +14681,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="128"/>
+      <c r="A12" s="121"/>
       <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
@@ -14690,7 +14701,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="128"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="62" t="s">
         <v>83</v>
       </c>
@@ -14710,7 +14721,7 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="120" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="64" t="s">
@@ -14744,7 +14755,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="128"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="62" t="s">
         <v>82</v>
       </c>
@@ -14776,7 +14787,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="129"/>
+      <c r="A16" s="122"/>
       <c r="B16" s="66" t="s">
         <v>83</v>
       </c>
@@ -14808,7 +14819,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="128" t="s">
+      <c r="A17" s="121" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="62" t="s">
@@ -14842,7 +14853,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="128"/>
+      <c r="A18" s="121"/>
       <c r="B18" s="62" t="s">
         <v>82</v>
       </c>
@@ -14874,7 +14885,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="128"/>
+      <c r="A19" s="121"/>
       <c r="B19" s="62" t="s">
         <v>83</v>
       </c>
@@ -14906,7 +14917,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="120" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="64" t="s">
@@ -14940,7 +14951,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="128"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="62" t="s">
         <v>82</v>
       </c>
@@ -14972,7 +14983,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="128"/>
+      <c r="A22" s="121"/>
       <c r="B22" s="62" t="s">
         <v>83</v>
       </c>
@@ -15004,7 +15015,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="127" t="s">
+      <c r="A23" s="120" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -15038,7 +15049,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="128"/>
+      <c r="A24" s="121"/>
       <c r="B24" s="62" t="s">
         <v>82</v>
       </c>
@@ -15070,7 +15081,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="129"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="66" t="s">
         <v>83</v>
       </c>
@@ -15102,7 +15113,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="128" t="s">
+      <c r="A26" s="121" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="62" t="s">
@@ -15136,7 +15147,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="128"/>
+      <c r="A27" s="121"/>
       <c r="B27" s="62" t="s">
         <v>82</v>
       </c>
@@ -15168,7 +15179,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="128"/>
+      <c r="A28" s="121"/>
       <c r="B28" s="62" t="s">
         <v>83</v>
       </c>
@@ -15200,7 +15211,7 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="127" t="s">
+      <c r="A29" s="120" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="64" t="s">
@@ -15234,7 +15245,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="128"/>
+      <c r="A30" s="121"/>
       <c r="B30" s="62" t="s">
         <v>82</v>
       </c>
@@ -15266,7 +15277,7 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="129"/>
+      <c r="A31" s="122"/>
       <c r="B31" s="66" t="s">
         <v>83</v>
       </c>
@@ -15393,16 +15404,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1"/>
@@ -15415,22 +15426,22 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="107" t="s">
+      <c r="K2" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="108"/>
-      <c r="M2" s="107" t="s">
+      <c r="L2" s="124"/>
+      <c r="M2" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="N2" s="108"/>
-      <c r="O2" s="107" t="s">
+      <c r="N2" s="124"/>
+      <c r="O2" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="107" t="s">
+      <c r="P2" s="124"/>
+      <c r="Q2" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="108"/>
+      <c r="R2" s="124"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -16249,28 +16260,28 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="1:24" ht="34.5">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="127" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
       <c r="I25" s="101"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="106" t="s">
+      <c r="K25" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="106"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="127"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -16279,74 +16290,74 @@
       <c r="X25" s="1"/>
     </row>
     <row r="26" spans="1:24" s="1" customFormat="1">
-      <c r="A26" s="111" t="s">
+      <c r="A26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="112"/>
-      <c r="C26" s="111" t="s">
+      <c r="B26" s="129"/>
+      <c r="C26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="112"/>
-      <c r="E26" s="111" t="s">
+      <c r="D26" s="129"/>
+      <c r="E26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="112"/>
-      <c r="G26" s="111" t="s">
+      <c r="F26" s="129"/>
+      <c r="G26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="112"/>
-      <c r="K26" s="111" t="s">
+      <c r="H26" s="129"/>
+      <c r="K26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="L26" s="112"/>
-      <c r="M26" s="111" t="s">
+      <c r="L26" s="129"/>
+      <c r="M26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="N26" s="112"/>
-      <c r="O26" s="111" t="s">
+      <c r="N26" s="129"/>
+      <c r="O26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="111" t="s">
+      <c r="P26" s="129"/>
+      <c r="Q26" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="R26" s="112"/>
+      <c r="R26" s="129"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="107" t="s">
+      <c r="A27" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="108"/>
-      <c r="C27" s="107" t="s">
+      <c r="B27" s="124"/>
+      <c r="C27" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="108"/>
-      <c r="E27" s="109" t="s">
+      <c r="D27" s="124"/>
+      <c r="E27" s="125" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="110"/>
-      <c r="G27" s="107" t="s">
+      <c r="F27" s="126"/>
+      <c r="G27" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="H27" s="108"/>
+      <c r="H27" s="124"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="107" t="s">
+      <c r="K27" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="108"/>
-      <c r="M27" s="107" t="s">
+      <c r="L27" s="124"/>
+      <c r="M27" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="N27" s="108"/>
-      <c r="O27" s="109" t="s">
+      <c r="N27" s="124"/>
+      <c r="O27" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="107" t="s">
+      <c r="P27" s="126"/>
+      <c r="Q27" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="R27" s="108"/>
+      <c r="R27" s="124"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -16355,22 +16366,22 @@
       <c r="X27" s="1"/>
     </row>
     <row r="28" spans="1:24">
-      <c r="A28" s="131">
+      <c r="A28" s="132">
         <v>1</v>
       </c>
-      <c r="B28" s="130">
+      <c r="B28" s="131">
         <v>1.1538888888888888E-3</v>
       </c>
-      <c r="C28" s="131">
+      <c r="C28" s="132">
         <v>1</v>
       </c>
-      <c r="D28" s="130">
+      <c r="D28" s="131">
         <v>1.1476041666666666E-3</v>
       </c>
-      <c r="E28" s="131">
+      <c r="E28" s="132">
         <v>1</v>
       </c>
-      <c r="F28" s="130">
+      <c r="F28" s="131">
         <v>1.1644560185185187E-3</v>
       </c>
       <c r="G28" s="97">
@@ -16381,16 +16392,16 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="132">
+      <c r="K28" s="133">
         <v>1</v>
       </c>
-      <c r="L28" s="133">
+      <c r="L28" s="134">
         <v>1.4355671296296297E-3</v>
       </c>
-      <c r="M28" s="132">
+      <c r="M28" s="133">
         <v>1</v>
       </c>
-      <c r="N28" s="133">
+      <c r="N28" s="134">
         <v>1.4123148148148148E-3</v>
       </c>
       <c r="O28" s="93">
@@ -16399,10 +16410,10 @@
       <c r="P28" s="94">
         <v>1.4081597222222223E-3</v>
       </c>
-      <c r="Q28" s="132">
+      <c r="Q28" s="133">
         <v>1</v>
       </c>
-      <c r="R28" s="133">
+      <c r="R28" s="134">
         <v>1.4081597222222223E-3</v>
       </c>
       <c r="S28" s="92"/>
@@ -16413,22 +16424,22 @@
       <c r="X28" s="1"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" s="131">
+      <c r="A29" s="132">
         <v>2</v>
       </c>
-      <c r="B29" s="130">
+      <c r="B29" s="131">
         <v>1.1098379629629629E-3</v>
       </c>
-      <c r="C29" s="131">
+      <c r="C29" s="132">
         <v>2</v>
       </c>
-      <c r="D29" s="130">
+      <c r="D29" s="131">
         <v>1.1111458333333333E-3</v>
       </c>
-      <c r="E29" s="131">
+      <c r="E29" s="132">
         <v>2</v>
       </c>
-      <c r="F29" s="130">
+      <c r="F29" s="131">
         <v>1.1378703703703703E-3</v>
       </c>
       <c r="G29" s="97">
@@ -16439,16 +16450,16 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="132">
+      <c r="K29" s="133">
         <v>2</v>
       </c>
-      <c r="L29" s="133">
+      <c r="L29" s="134">
         <v>1.1143287037037035E-3</v>
       </c>
-      <c r="M29" s="132">
+      <c r="M29" s="133">
         <v>2</v>
       </c>
-      <c r="N29" s="133">
+      <c r="N29" s="134">
         <v>1.1365393518518519E-3</v>
       </c>
       <c r="O29" s="93">
@@ -16457,10 +16468,10 @@
       <c r="P29" s="94">
         <v>1.1394212962962964E-3</v>
       </c>
-      <c r="Q29" s="132">
+      <c r="Q29" s="133">
         <v>2</v>
       </c>
-      <c r="R29" s="133">
+      <c r="R29" s="134">
         <v>1.1394212962962964E-3</v>
       </c>
       <c r="S29" s="1"/>
@@ -16471,22 +16482,22 @@
       <c r="X29" s="1"/>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" s="131">
+      <c r="A30" s="132">
         <v>3</v>
       </c>
-      <c r="B30" s="130">
+      <c r="B30" s="131">
         <v>1.110173611111111E-3</v>
       </c>
-      <c r="C30" s="131">
+      <c r="C30" s="132">
         <v>3</v>
       </c>
-      <c r="D30" s="130">
+      <c r="D30" s="131">
         <v>1.0993171296296296E-3</v>
       </c>
-      <c r="E30" s="131">
+      <c r="E30" s="132">
         <v>3</v>
       </c>
-      <c r="F30" s="130">
+      <c r="F30" s="131">
         <v>1.1312268518518518E-3</v>
       </c>
       <c r="G30" s="97">
@@ -16497,16 +16508,16 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="132">
+      <c r="K30" s="133">
         <v>3</v>
       </c>
-      <c r="L30" s="133">
+      <c r="L30" s="134">
         <v>1.1773726851851852E-3</v>
       </c>
-      <c r="M30" s="132">
+      <c r="M30" s="133">
         <v>3</v>
       </c>
-      <c r="N30" s="133">
+      <c r="N30" s="134">
         <v>1.1328703703703702E-3</v>
       </c>
       <c r="O30" s="93">
@@ -16515,10 +16526,10 @@
       <c r="P30" s="94">
         <v>1.1317361111111111E-3</v>
       </c>
-      <c r="Q30" s="132">
+      <c r="Q30" s="133">
         <v>3</v>
       </c>
-      <c r="R30" s="133">
+      <c r="R30" s="134">
         <v>1.1317361111111111E-3</v>
       </c>
       <c r="S30" s="1"/>
@@ -16529,22 +16540,22 @@
       <c r="X30" s="1"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="131">
+      <c r="A31" s="132">
         <v>4</v>
       </c>
-      <c r="B31" s="130">
+      <c r="B31" s="131">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="C31" s="131">
+      <c r="C31" s="132">
         <v>4</v>
       </c>
-      <c r="D31" s="130">
+      <c r="D31" s="131">
         <v>1.0976736111111111E-3</v>
       </c>
-      <c r="E31" s="131">
+      <c r="E31" s="132">
         <v>4</v>
       </c>
-      <c r="F31" s="130">
+      <c r="F31" s="131">
         <v>1.1532986111111112E-3</v>
       </c>
       <c r="G31" s="97">
@@ -16555,16 +16566,16 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="132">
+      <c r="K31" s="133">
         <v>4</v>
       </c>
-      <c r="L31" s="133">
+      <c r="L31" s="134">
         <v>1.1155787037037037E-3</v>
       </c>
-      <c r="M31" s="132">
+      <c r="M31" s="133">
         <v>4</v>
       </c>
-      <c r="N31" s="133">
+      <c r="N31" s="134">
         <v>1.1118055555555556E-3</v>
       </c>
       <c r="O31" s="93">
@@ -16573,10 +16584,10 @@
       <c r="P31" s="94">
         <v>2.0264583333333337E-3</v>
       </c>
-      <c r="Q31" s="132">
+      <c r="Q31" s="133">
         <v>4</v>
       </c>
-      <c r="R31" s="133">
+      <c r="R31" s="134">
         <v>2.0264583333333337E-3</v>
       </c>
       <c r="S31" s="1"/>
@@ -16587,22 +16598,22 @@
       <c r="X31" s="1"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="131">
+      <c r="A32" s="132">
         <v>5</v>
       </c>
-      <c r="B32" s="130">
+      <c r="B32" s="131">
         <v>1.1121296296296296E-3</v>
       </c>
-      <c r="C32" s="131">
+      <c r="C32" s="132">
         <v>5</v>
       </c>
-      <c r="D32" s="130">
+      <c r="D32" s="131">
         <v>1.1186458333333335E-3</v>
       </c>
-      <c r="E32" s="131">
+      <c r="E32" s="132">
         <v>5</v>
       </c>
-      <c r="F32" s="130">
+      <c r="F32" s="131">
         <v>1.1660416666666668E-3</v>
       </c>
       <c r="G32" s="97">
@@ -16613,16 +16624,16 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="132">
+      <c r="K32" s="133">
         <v>5</v>
       </c>
-      <c r="L32" s="133">
+      <c r="L32" s="134">
         <v>1.1346180555555556E-3</v>
       </c>
-      <c r="M32" s="132">
+      <c r="M32" s="133">
         <v>5</v>
       </c>
-      <c r="N32" s="133">
+      <c r="N32" s="134">
         <v>1.0958333333333334E-3</v>
       </c>
       <c r="O32" s="93">
@@ -16631,10 +16642,10 @@
       <c r="P32" s="94">
         <v>1.198900462962963E-3</v>
       </c>
-      <c r="Q32" s="132">
+      <c r="Q32" s="133">
         <v>5</v>
       </c>
-      <c r="R32" s="133">
+      <c r="R32" s="134">
         <v>1.198900462962963E-3</v>
       </c>
       <c r="S32" s="1"/>
@@ -16648,22 +16659,22 @@
       <c r="X32" s="1"/>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" s="131">
+      <c r="A33" s="132">
         <v>6</v>
       </c>
-      <c r="B33" s="130">
+      <c r="B33" s="131">
         <v>1.1231828703703705E-3</v>
       </c>
-      <c r="C33" s="131">
+      <c r="C33" s="132">
         <v>6</v>
       </c>
-      <c r="D33" s="130">
+      <c r="D33" s="131">
         <v>1.1192708333333332E-3</v>
       </c>
-      <c r="E33" s="131">
+      <c r="E33" s="132">
         <v>6</v>
       </c>
-      <c r="F33" s="130">
+      <c r="F33" s="131">
         <v>1.1783333333333333E-3</v>
       </c>
       <c r="G33" s="97">
@@ -16674,16 +16685,16 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="132">
+      <c r="K33" s="133">
         <v>6</v>
       </c>
-      <c r="L33" s="133">
+      <c r="L33" s="134">
         <v>1.1811458333333333E-3</v>
       </c>
-      <c r="M33" s="132">
+      <c r="M33" s="133">
         <v>6</v>
       </c>
-      <c r="N33" s="133">
+      <c r="N33" s="134">
         <v>1.1103587962962964E-3</v>
       </c>
       <c r="O33" s="93">
@@ -16692,10 +16703,10 @@
       <c r="P33" s="94">
         <v>1.3676157407407409E-3</v>
       </c>
-      <c r="Q33" s="132">
+      <c r="Q33" s="133">
         <v>6</v>
       </c>
-      <c r="R33" s="133">
+      <c r="R33" s="134">
         <v>1.3676157407407409E-3</v>
       </c>
       <c r="S33" s="1"/>
@@ -16706,22 +16717,22 @@
       <c r="X33" s="1"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="131">
+      <c r="A34" s="132">
         <v>7</v>
       </c>
-      <c r="B34" s="130">
+      <c r="B34" s="131">
         <v>1.1183564814814815E-3</v>
       </c>
-      <c r="C34" s="131">
+      <c r="C34" s="132">
         <v>7</v>
       </c>
-      <c r="D34" s="130">
+      <c r="D34" s="131">
         <v>1.1119675925925926E-3</v>
       </c>
-      <c r="E34" s="131">
+      <c r="E34" s="132">
         <v>7</v>
       </c>
-      <c r="F34" s="130">
+      <c r="F34" s="131">
         <v>1.1461342592592593E-3</v>
       </c>
       <c r="G34" s="97">
@@ -16732,16 +16743,16 @@
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="132">
+      <c r="K34" s="133">
         <v>7</v>
       </c>
-      <c r="L34" s="133">
+      <c r="L34" s="134">
         <v>1.1964467592592591E-3</v>
       </c>
-      <c r="M34" s="132">
+      <c r="M34" s="133">
         <v>7</v>
       </c>
-      <c r="N34" s="133">
+      <c r="N34" s="134">
         <v>1.1330787037037036E-3</v>
       </c>
       <c r="O34" s="93">
@@ -16750,10 +16761,10 @@
       <c r="P34" s="94">
         <v>1.2607407407407407E-3</v>
       </c>
-      <c r="Q34" s="132">
+      <c r="Q34" s="133">
         <v>7</v>
       </c>
-      <c r="R34" s="133">
+      <c r="R34" s="134">
         <v>1.2607407407407407E-3</v>
       </c>
       <c r="S34" s="1"/>
@@ -16764,22 +16775,22 @@
       <c r="X34" s="1"/>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="131">
+      <c r="A35" s="132">
         <v>8</v>
       </c>
-      <c r="B35" s="130">
+      <c r="B35" s="131">
         <v>1.124398148148148E-3</v>
       </c>
-      <c r="C35" s="131">
+      <c r="C35" s="132">
         <v>8</v>
       </c>
-      <c r="D35" s="130">
+      <c r="D35" s="131">
         <v>1.1048148148148148E-3</v>
       </c>
-      <c r="E35" s="131">
+      <c r="E35" s="132">
         <v>8</v>
       </c>
-      <c r="F35" s="130">
+      <c r="F35" s="131">
         <v>1.2261226851851851E-3</v>
       </c>
       <c r="G35" s="97">
@@ -16790,16 +16801,16 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="132">
+      <c r="K35" s="133">
         <v>8</v>
       </c>
-      <c r="L35" s="133">
+      <c r="L35" s="134">
         <v>1.1544097222222223E-3</v>
       </c>
-      <c r="M35" s="132">
+      <c r="M35" s="133">
         <v>8</v>
       </c>
-      <c r="N35" s="133">
+      <c r="N35" s="134">
         <v>1.1489930555555554E-3</v>
       </c>
       <c r="O35" s="93">
@@ -16808,10 +16819,10 @@
       <c r="P35" s="94">
         <v>1.1238657407407408E-3</v>
       </c>
-      <c r="Q35" s="132">
+      <c r="Q35" s="133">
         <v>8</v>
       </c>
-      <c r="R35" s="133">
+      <c r="R35" s="134">
         <v>1.1238657407407408E-3</v>
       </c>
       <c r="S35" s="1"/>
@@ -16825,22 +16836,22 @@
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="1:24">
-      <c r="A36" s="131">
+      <c r="A36" s="132">
         <v>9</v>
       </c>
-      <c r="B36" s="130">
+      <c r="B36" s="131">
         <v>1.2592476851851853E-3</v>
       </c>
-      <c r="C36" s="131">
+      <c r="C36" s="132">
         <v>9</v>
       </c>
-      <c r="D36" s="130">
+      <c r="D36" s="131">
         <v>1.0967939814814816E-3</v>
       </c>
-      <c r="E36" s="131">
+      <c r="E36" s="132">
         <v>9</v>
       </c>
-      <c r="F36" s="130">
+      <c r="F36" s="131">
         <v>1.1561111111111112E-3</v>
       </c>
       <c r="G36" s="97">
@@ -16851,16 +16862,16 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="132">
+      <c r="K36" s="133">
         <v>9</v>
       </c>
-      <c r="L36" s="133">
+      <c r="L36" s="134">
         <v>1.2505092592592592E-3</v>
       </c>
-      <c r="M36" s="132">
+      <c r="M36" s="133">
         <v>9</v>
       </c>
-      <c r="N36" s="133">
+      <c r="N36" s="134">
         <v>1.1331134259259261E-3</v>
       </c>
       <c r="O36" s="93">
@@ -16869,10 +16880,10 @@
       <c r="P36" s="94">
         <v>1.2741203703703703E-3</v>
       </c>
-      <c r="Q36" s="132">
+      <c r="Q36" s="133">
         <v>9</v>
       </c>
-      <c r="R36" s="133">
+      <c r="R36" s="134">
         <v>1.2741203703703703E-3</v>
       </c>
       <c r="S36" s="1"/>
@@ -16883,22 +16894,22 @@
       <c r="X36" s="1"/>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="131">
+      <c r="A37" s="132">
         <v>10</v>
       </c>
-      <c r="B37" s="130">
+      <c r="B37" s="131">
         <v>1.1363194444444444E-3</v>
       </c>
-      <c r="C37" s="131">
+      <c r="C37" s="132">
         <v>10</v>
       </c>
-      <c r="D37" s="130">
+      <c r="D37" s="131">
         <v>1.1534143518518519E-3</v>
       </c>
-      <c r="E37" s="131">
+      <c r="E37" s="132">
         <v>10</v>
       </c>
-      <c r="F37" s="130">
+      <c r="F37" s="131">
         <v>1.1621296296296297E-3</v>
       </c>
       <c r="G37" s="97">
@@ -16909,16 +16920,16 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="132">
+      <c r="K37" s="133">
         <v>10</v>
       </c>
-      <c r="L37" s="133">
+      <c r="L37" s="134">
         <v>1.1465856481481481E-3</v>
       </c>
-      <c r="M37" s="132">
+      <c r="M37" s="133">
         <v>10</v>
       </c>
-      <c r="N37" s="133">
+      <c r="N37" s="134">
         <v>1.1556481481481481E-3</v>
       </c>
       <c r="O37" s="93">
@@ -16927,10 +16938,10 @@
       <c r="P37" s="94">
         <v>1.1596180555555557E-3</v>
       </c>
-      <c r="Q37" s="132">
+      <c r="Q37" s="133">
         <v>10</v>
       </c>
-      <c r="R37" s="133">
+      <c r="R37" s="134">
         <v>1.1596180555555557E-3</v>
       </c>
       <c r="S37" s="1"/>
@@ -16941,22 +16952,22 @@
       <c r="X37" s="1"/>
     </row>
     <row r="38" spans="1:24">
-      <c r="A38" s="131">
+      <c r="A38" s="132">
         <v>11</v>
       </c>
-      <c r="B38" s="130">
+      <c r="B38" s="131">
         <v>1.3982291666666668E-3</v>
       </c>
-      <c r="C38" s="131">
+      <c r="C38" s="132">
         <v>11</v>
       </c>
-      <c r="D38" s="130">
+      <c r="D38" s="131">
         <v>1.2330902777777778E-3</v>
       </c>
-      <c r="E38" s="131">
+      <c r="E38" s="132">
         <v>11</v>
       </c>
-      <c r="F38" s="130">
+      <c r="F38" s="131">
         <v>1.2419907407407406E-3</v>
       </c>
       <c r="G38" s="97">
@@ -16967,16 +16978,16 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="132">
+      <c r="K38" s="133">
         <v>11</v>
       </c>
-      <c r="L38" s="133">
+      <c r="L38" s="134">
         <v>1.1611226851851852E-3</v>
       </c>
-      <c r="M38" s="132">
+      <c r="M38" s="133">
         <v>11</v>
       </c>
-      <c r="N38" s="133">
+      <c r="N38" s="134">
         <v>1.2279976851851851E-3</v>
       </c>
       <c r="O38" s="93">
@@ -16985,10 +16996,10 @@
       <c r="P38" s="94">
         <v>2.1243171296296296E-3</v>
       </c>
-      <c r="Q38" s="132">
+      <c r="Q38" s="133">
         <v>11</v>
       </c>
-      <c r="R38" s="133">
+      <c r="R38" s="134">
         <v>2.1243171296296296E-3</v>
       </c>
       <c r="S38" s="1"/>
@@ -16999,22 +17010,22 @@
       <c r="X38" s="1"/>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="131">
+      <c r="A39" s="132">
         <v>12</v>
       </c>
-      <c r="B39" s="130">
+      <c r="B39" s="131">
         <v>1.5461458333333332E-3</v>
       </c>
-      <c r="C39" s="131">
+      <c r="C39" s="132">
         <v>12</v>
       </c>
-      <c r="D39" s="130">
+      <c r="D39" s="131">
         <v>1.9078009259259261E-3</v>
       </c>
-      <c r="E39" s="131">
+      <c r="E39" s="132">
         <v>12</v>
       </c>
-      <c r="F39" s="130">
+      <c r="F39" s="131">
         <v>1.4453819444444444E-3</v>
       </c>
       <c r="G39" s="97">
@@ -17025,16 +17036,16 @@
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="132">
+      <c r="K39" s="133">
         <v>12</v>
       </c>
-      <c r="L39" s="133">
+      <c r="L39" s="134">
         <v>1.3398611111111113E-3</v>
       </c>
-      <c r="M39" s="132">
+      <c r="M39" s="133">
         <v>12</v>
       </c>
-      <c r="N39" s="133">
+      <c r="N39" s="134">
         <v>1.310949074074074E-3</v>
       </c>
       <c r="O39" s="93">
@@ -17043,10 +17054,10 @@
       <c r="P39" s="94">
         <v>1.4692245370370371E-3</v>
       </c>
-      <c r="Q39" s="132">
+      <c r="Q39" s="133">
         <v>12</v>
       </c>
-      <c r="R39" s="133">
+      <c r="R39" s="134">
         <v>1.4692245370370371E-3</v>
       </c>
       <c r="S39" s="1"/>
@@ -17060,22 +17071,22 @@
       <c r="X39" s="1"/>
     </row>
     <row r="40" spans="1:24">
-      <c r="A40" s="131">
+      <c r="A40" s="132">
         <v>13</v>
       </c>
-      <c r="B40" s="130">
+      <c r="B40" s="131">
         <v>1.2216550925925925E-3</v>
       </c>
-      <c r="C40" s="131">
+      <c r="C40" s="132">
         <v>13</v>
       </c>
-      <c r="D40" s="130">
+      <c r="D40" s="131">
         <v>1.2544560185185185E-3</v>
       </c>
-      <c r="E40" s="131">
+      <c r="E40" s="132">
         <v>13</v>
       </c>
-      <c r="F40" s="130">
+      <c r="F40" s="131">
         <v>1.2557175925925926E-3</v>
       </c>
       <c r="G40" s="97">
@@ -17086,16 +17097,16 @@
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="132">
+      <c r="K40" s="133">
         <v>13</v>
       </c>
-      <c r="L40" s="133">
+      <c r="L40" s="134">
         <v>3.8921759259259257E-3</v>
       </c>
-      <c r="M40" s="132">
+      <c r="M40" s="133">
         <v>13</v>
       </c>
-      <c r="N40" s="133">
+      <c r="N40" s="134">
         <v>4.1754282407407408E-3</v>
       </c>
       <c r="O40" s="93">
@@ -17104,10 +17115,10 @@
       <c r="P40" s="94">
         <v>1.6091435185185184E-3</v>
       </c>
-      <c r="Q40" s="132">
+      <c r="Q40" s="133">
         <v>13</v>
       </c>
-      <c r="R40" s="133">
+      <c r="R40" s="134">
         <v>1.6091435185185184E-3</v>
       </c>
       <c r="S40" s="1"/>
@@ -17118,22 +17129,22 @@
       <c r="X40" s="1"/>
     </row>
     <row r="41" spans="1:24">
-      <c r="A41" s="131">
+      <c r="A41" s="132">
         <v>14</v>
       </c>
-      <c r="B41" s="130">
+      <c r="B41" s="131">
         <v>1.1457523148148147E-3</v>
       </c>
-      <c r="C41" s="131">
+      <c r="C41" s="132">
         <v>14</v>
       </c>
-      <c r="D41" s="130">
+      <c r="D41" s="131">
         <v>1.1745949074074074E-3</v>
       </c>
-      <c r="E41" s="131">
+      <c r="E41" s="132">
         <v>14</v>
       </c>
-      <c r="F41" s="130">
+      <c r="F41" s="131">
         <v>1.1743055555555556E-3</v>
       </c>
       <c r="G41" s="97">
@@ -17144,16 +17155,16 @@
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="132">
+      <c r="K41" s="133">
         <v>14</v>
       </c>
-      <c r="L41" s="133">
+      <c r="L41" s="134">
         <v>1.1608564814814815E-3</v>
       </c>
-      <c r="M41" s="132">
+      <c r="M41" s="133">
         <v>14</v>
       </c>
-      <c r="N41" s="133">
+      <c r="N41" s="134">
         <v>1.1806365740740742E-3</v>
       </c>
       <c r="O41" s="93">
@@ -17162,10 +17173,10 @@
       <c r="P41" s="94">
         <v>1.1635069444444444E-3</v>
       </c>
-      <c r="Q41" s="132">
+      <c r="Q41" s="133">
         <v>14</v>
       </c>
-      <c r="R41" s="133">
+      <c r="R41" s="134">
         <v>1.1635069444444444E-3</v>
       </c>
       <c r="S41" s="1"/>
@@ -17176,22 +17187,22 @@
       <c r="X41" s="1"/>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" s="131">
+      <c r="A42" s="132">
         <v>15</v>
       </c>
-      <c r="B42" s="130">
+      <c r="B42" s="131">
         <v>1.5789930555555557E-3</v>
       </c>
-      <c r="C42" s="131">
+      <c r="C42" s="132">
         <v>15</v>
       </c>
-      <c r="D42" s="130">
+      <c r="D42" s="131">
         <v>1.544236111111111E-3</v>
       </c>
-      <c r="E42" s="131">
+      <c r="E42" s="132">
         <v>15</v>
       </c>
-      <c r="F42" s="130">
+      <c r="F42" s="131">
         <v>1.5701967592592592E-3</v>
       </c>
       <c r="G42" s="97">
@@ -17202,16 +17213,16 @@
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="132">
+      <c r="K42" s="133">
         <v>15</v>
       </c>
-      <c r="L42" s="133">
+      <c r="L42" s="134">
         <v>1.1989930555555556E-3</v>
       </c>
-      <c r="M42" s="132">
+      <c r="M42" s="133">
         <v>15</v>
       </c>
-      <c r="N42" s="133">
+      <c r="N42" s="134">
         <v>1.1869444444444445E-3</v>
       </c>
       <c r="O42" s="93">
@@ -17220,10 +17231,10 @@
       <c r="P42" s="94">
         <v>1.1449421296296297E-3</v>
       </c>
-      <c r="Q42" s="132">
+      <c r="Q42" s="133">
         <v>15</v>
       </c>
-      <c r="R42" s="133">
+      <c r="R42" s="134">
         <v>1.1449421296296297E-3</v>
       </c>
       <c r="S42" s="1"/>
@@ -17234,22 +17245,22 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="1:24">
-      <c r="A43" s="131">
+      <c r="A43" s="132">
         <v>16</v>
       </c>
-      <c r="B43" s="130">
+      <c r="B43" s="131">
         <v>1.1158217592592591E-3</v>
       </c>
-      <c r="C43" s="131">
+      <c r="C43" s="132">
         <v>16</v>
       </c>
-      <c r="D43" s="130">
+      <c r="D43" s="131">
         <v>1.1127083333333334E-3</v>
       </c>
-      <c r="E43" s="131">
+      <c r="E43" s="132">
         <v>16</v>
       </c>
-      <c r="F43" s="130">
+      <c r="F43" s="131">
         <v>1.2513888888888889E-3</v>
       </c>
       <c r="G43" s="97">
@@ -17260,16 +17271,16 @@
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="132">
+      <c r="K43" s="133">
         <v>16</v>
       </c>
-      <c r="L43" s="133">
+      <c r="L43" s="134">
         <v>1.1175E-3</v>
       </c>
-      <c r="M43" s="132">
+      <c r="M43" s="133">
         <v>16</v>
       </c>
-      <c r="N43" s="133">
+      <c r="N43" s="134">
         <v>1.1115046296296296E-3</v>
       </c>
       <c r="O43" s="93">
@@ -17278,10 +17289,10 @@
       <c r="P43" s="94">
         <v>1.140324074074074E-3</v>
       </c>
-      <c r="Q43" s="132">
+      <c r="Q43" s="133">
         <v>16</v>
       </c>
-      <c r="R43" s="133">
+      <c r="R43" s="134">
         <v>1.140324074074074E-3</v>
       </c>
       <c r="S43" s="1"/>
@@ -17292,22 +17303,22 @@
       <c r="X43" s="1"/>
     </row>
     <row r="44" spans="1:24">
-      <c r="A44" s="131">
+      <c r="A44" s="132">
         <v>17</v>
       </c>
-      <c r="B44" s="130">
+      <c r="B44" s="131">
         <v>1.1162731481481481E-3</v>
       </c>
-      <c r="C44" s="131">
+      <c r="C44" s="132">
         <v>17</v>
       </c>
-      <c r="D44" s="130">
+      <c r="D44" s="131">
         <v>1.1204629629629629E-3</v>
       </c>
-      <c r="E44" s="131">
+      <c r="E44" s="132">
         <v>17</v>
       </c>
-      <c r="F44" s="130">
+      <c r="F44" s="131">
         <v>1.1524421296296296E-3</v>
       </c>
       <c r="G44" s="97">
@@ -17318,16 +17329,16 @@
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="132">
+      <c r="K44" s="133">
         <v>17</v>
       </c>
-      <c r="L44" s="133">
+      <c r="L44" s="134">
         <v>1.133587962962963E-3</v>
       </c>
-      <c r="M44" s="132">
+      <c r="M44" s="133">
         <v>17</v>
       </c>
-      <c r="N44" s="133">
+      <c r="N44" s="134">
         <v>1.1427777777777777E-3</v>
       </c>
       <c r="O44" s="93">
@@ -17336,10 +17347,10 @@
       <c r="P44" s="94">
         <v>1.1632407407407407E-3</v>
       </c>
-      <c r="Q44" s="132">
+      <c r="Q44" s="133">
         <v>17</v>
       </c>
-      <c r="R44" s="133">
+      <c r="R44" s="134">
         <v>1.1632407407407407E-3</v>
       </c>
       <c r="S44" s="58"/>
@@ -17350,22 +17361,22 @@
       <c r="X44" s="1"/>
     </row>
     <row r="45" spans="1:24">
-      <c r="A45" s="131">
+      <c r="A45" s="132">
         <v>18</v>
       </c>
-      <c r="B45" s="130">
+      <c r="B45" s="131">
         <v>1.114398148148148E-3</v>
       </c>
-      <c r="C45" s="131">
+      <c r="C45" s="132">
         <v>18</v>
       </c>
-      <c r="D45" s="130">
+      <c r="D45" s="131">
         <v>1.1069444444444445E-3</v>
       </c>
-      <c r="E45" s="131">
+      <c r="E45" s="132">
         <v>18</v>
       </c>
-      <c r="F45" s="130">
+      <c r="F45" s="131">
         <v>1.1676157407407408E-3</v>
       </c>
       <c r="G45" s="97">
@@ -17376,16 +17387,16 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="132">
+      <c r="K45" s="133">
         <v>18</v>
       </c>
-      <c r="L45" s="133">
+      <c r="L45" s="134">
         <v>1.1378240740740741E-3</v>
       </c>
-      <c r="M45" s="132">
+      <c r="M45" s="133">
         <v>18</v>
       </c>
-      <c r="N45" s="133">
+      <c r="N45" s="134">
         <v>1.1362962962962963E-3</v>
       </c>
       <c r="O45" s="93">
@@ -17394,10 +17405,10 @@
       <c r="P45" s="94">
         <v>1.1319444444444443E-3</v>
       </c>
-      <c r="Q45" s="132">
+      <c r="Q45" s="133">
         <v>18</v>
       </c>
-      <c r="R45" s="133">
+      <c r="R45" s="134">
         <v>1.1319444444444443E-3</v>
       </c>
       <c r="S45" s="58"/>
@@ -17408,22 +17419,22 @@
       <c r="X45" s="1"/>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" s="131">
+      <c r="A46" s="132">
         <v>19</v>
       </c>
-      <c r="B46" s="130">
+      <c r="B46" s="131">
         <v>1.1236805555555555E-3</v>
       </c>
-      <c r="C46" s="131">
+      <c r="C46" s="132">
         <v>19</v>
       </c>
-      <c r="D46" s="130">
+      <c r="D46" s="131">
         <v>1.1092129629629629E-3</v>
       </c>
-      <c r="E46" s="131">
+      <c r="E46" s="132">
         <v>19</v>
       </c>
-      <c r="F46" s="130">
+      <c r="F46" s="131">
         <v>1.1594328703703703E-3</v>
       </c>
       <c r="G46" s="97">
@@ -17434,16 +17445,16 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="132">
+      <c r="K46" s="133">
         <v>19</v>
       </c>
-      <c r="L46" s="133">
+      <c r="L46" s="134">
         <v>1.1439699074074073E-3</v>
       </c>
-      <c r="M46" s="132">
+      <c r="M46" s="133">
         <v>19</v>
       </c>
-      <c r="N46" s="133">
+      <c r="N46" s="134">
         <v>1.1471990740740739E-3</v>
       </c>
       <c r="O46" s="93">
@@ -17452,10 +17463,10 @@
       <c r="P46" s="94">
         <v>1.149375E-3</v>
       </c>
-      <c r="Q46" s="132">
+      <c r="Q46" s="133">
         <v>19</v>
       </c>
-      <c r="R46" s="133">
+      <c r="R46" s="134">
         <v>1.149375E-3</v>
       </c>
       <c r="S46" s="58"/>
@@ -17471,22 +17482,22 @@
       </c>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="131">
+      <c r="A47" s="132">
         <v>20</v>
       </c>
-      <c r="B47" s="130">
+      <c r="B47" s="131">
         <v>1.1430092592592592E-3</v>
       </c>
-      <c r="C47" s="131">
+      <c r="C47" s="132">
         <v>20</v>
       </c>
-      <c r="D47" s="130">
+      <c r="D47" s="131">
         <v>1.1691319444444444E-3</v>
       </c>
-      <c r="E47" s="131">
+      <c r="E47" s="132">
         <v>20</v>
       </c>
-      <c r="F47" s="130">
+      <c r="F47" s="131">
         <v>1.2307523148148149E-3</v>
       </c>
       <c r="G47" s="97">
@@ -17497,16 +17508,16 @@
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="134">
+      <c r="K47" s="135">
         <v>20</v>
       </c>
-      <c r="L47" s="135">
+      <c r="L47" s="136">
         <v>1.1290277777777778E-3</v>
       </c>
-      <c r="M47" s="134">
+      <c r="M47" s="135">
         <v>20</v>
       </c>
-      <c r="N47" s="135">
+      <c r="N47" s="136">
         <v>1.1019907407407408E-3</v>
       </c>
       <c r="O47" s="95">
@@ -17515,10 +17526,10 @@
       <c r="P47" s="96">
         <v>1.1516666666666665E-3</v>
       </c>
-      <c r="Q47" s="134">
+      <c r="Q47" s="135">
         <v>20</v>
       </c>
-      <c r="R47" s="135">
+      <c r="R47" s="136">
         <v>1.1516666666666665E-3</v>
       </c>
       <c r="S47" s="1"/>
@@ -17844,28 +17855,28 @@
       <c r="X56" s="1"/>
     </row>
     <row r="57" spans="1:24" ht="34.5">
-      <c r="A57" s="106" t="s">
+      <c r="A57" s="127" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="106"/>
-      <c r="C57" s="106"/>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
+      <c r="B57" s="127"/>
+      <c r="C57" s="127"/>
+      <c r="D57" s="127"/>
+      <c r="E57" s="127"/>
+      <c r="F57" s="127"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="127"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="106" t="s">
+      <c r="K57" s="127" t="s">
         <v>114</v>
       </c>
-      <c r="L57" s="106"/>
-      <c r="M57" s="106"/>
-      <c r="N57" s="106"/>
-      <c r="O57" s="106"/>
-      <c r="P57" s="106"/>
-      <c r="Q57" s="106"/>
-      <c r="R57" s="106"/>
+      <c r="L57" s="127"/>
+      <c r="M57" s="127"/>
+      <c r="N57" s="127"/>
+      <c r="O57" s="127"/>
+      <c r="P57" s="127"/>
+      <c r="Q57" s="127"/>
+      <c r="R57" s="127"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
@@ -17874,36 +17885,36 @@
       <c r="X57" s="1"/>
     </row>
     <row r="58" spans="1:24">
-      <c r="A58" s="107" t="s">
+      <c r="A58" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="108"/>
-      <c r="C58" s="107" t="s">
+      <c r="B58" s="124"/>
+      <c r="C58" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="D58" s="108"/>
-      <c r="E58" s="109" t="s">
+      <c r="D58" s="124"/>
+      <c r="E58" s="125" t="s">
         <v>109</v>
       </c>
-      <c r="F58" s="110"/>
-      <c r="G58" s="107" t="s">
+      <c r="F58" s="126"/>
+      <c r="G58" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="H58" s="108"/>
+      <c r="H58" s="124"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="107"/>
-      <c r="L58" s="108"/>
-      <c r="M58" s="107" t="s">
+      <c r="K58" s="123"/>
+      <c r="L58" s="124"/>
+      <c r="M58" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="108"/>
-      <c r="O58" s="109"/>
-      <c r="P58" s="110"/>
-      <c r="Q58" s="107" t="s">
+      <c r="N58" s="124"/>
+      <c r="O58" s="125"/>
+      <c r="P58" s="126"/>
+      <c r="Q58" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="R58" s="108"/>
+      <c r="R58" s="124"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
@@ -17914,7 +17925,7 @@
     <row r="59" spans="1:24">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="131">
+      <c r="C59" s="132">
         <v>1</v>
       </c>
       <c r="D59" s="58">
@@ -17922,10 +17933,10 @@
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="131">
+      <c r="G59" s="132">
         <v>1</v>
       </c>
-      <c r="H59" s="130">
+      <c r="H59" s="131">
         <v>1.9796875000000001E-3</v>
       </c>
       <c r="I59" s="1"/>
@@ -17956,7 +17967,7 @@
     <row r="60" spans="1:24">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="131">
+      <c r="C60" s="132">
         <v>2</v>
       </c>
       <c r="D60" s="58">
@@ -17964,10 +17975,10 @@
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="131">
+      <c r="G60" s="132">
         <v>2</v>
       </c>
-      <c r="H60" s="130">
+      <c r="H60" s="131">
         <v>1.2236342592592594E-3</v>
       </c>
       <c r="I60" s="1"/>
@@ -17998,7 +18009,7 @@
     <row r="61" spans="1:24">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="131">
+      <c r="C61" s="132">
         <v>3</v>
       </c>
       <c r="D61" s="58">
@@ -18006,10 +18017,10 @@
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="131">
+      <c r="G61" s="132">
         <v>3</v>
       </c>
-      <c r="H61" s="130">
+      <c r="H61" s="131">
         <v>1.2050810185185185E-3</v>
       </c>
       <c r="I61" s="1"/>
@@ -18040,7 +18051,7 @@
     <row r="62" spans="1:24">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="131">
+      <c r="C62" s="132">
         <v>4</v>
       </c>
       <c r="D62" s="58">
@@ -18048,10 +18059,10 @@
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="131">
+      <c r="G62" s="132">
         <v>4</v>
       </c>
-      <c r="H62" s="130">
+      <c r="H62" s="131">
         <v>1.2027199074074073E-3</v>
       </c>
       <c r="I62" s="1"/>
@@ -18082,7 +18093,7 @@
     <row r="63" spans="1:24">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="131">
+      <c r="C63" s="132">
         <v>5</v>
       </c>
       <c r="D63" s="58">
@@ -18090,10 +18101,10 @@
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="131">
+      <c r="G63" s="132">
         <v>5</v>
       </c>
-      <c r="H63" s="130">
+      <c r="H63" s="131">
         <v>1.1896412037037036E-3</v>
       </c>
       <c r="I63" s="1"/>
@@ -18124,7 +18135,7 @@
     <row r="64" spans="1:24">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="131">
+      <c r="C64" s="132">
         <v>6</v>
       </c>
       <c r="D64" s="58">
@@ -18132,10 +18143,10 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="131">
+      <c r="G64" s="132">
         <v>6</v>
       </c>
-      <c r="H64" s="130">
+      <c r="H64" s="131">
         <v>1.2009606481481483E-3</v>
       </c>
       <c r="I64" s="1"/>
@@ -18166,7 +18177,7 @@
     <row r="65" spans="1:24">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="131">
+      <c r="C65" s="132">
         <v>7</v>
       </c>
       <c r="D65" s="58">
@@ -18174,10 +18185,10 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="131">
+      <c r="G65" s="132">
         <v>7</v>
       </c>
-      <c r="H65" s="130">
+      <c r="H65" s="131">
         <v>1.1911805555555556E-3</v>
       </c>
       <c r="I65" s="1"/>
@@ -18208,7 +18219,7 @@
     <row r="66" spans="1:24">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="131">
+      <c r="C66" s="132">
         <v>8</v>
       </c>
       <c r="D66" s="58">
@@ -18216,10 +18227,10 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="131">
+      <c r="G66" s="132">
         <v>8</v>
       </c>
-      <c r="H66" s="130">
+      <c r="H66" s="131">
         <v>1.1953125E-3</v>
       </c>
       <c r="I66" s="1"/>
@@ -18250,7 +18261,7 @@
     <row r="67" spans="1:24">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="131">
+      <c r="C67" s="132">
         <v>9</v>
       </c>
       <c r="D67" s="58">
@@ -18258,10 +18269,10 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="131">
+      <c r="G67" s="132">
         <v>9</v>
       </c>
-      <c r="H67" s="130">
+      <c r="H67" s="131">
         <v>1.2066550925925925E-3</v>
       </c>
       <c r="I67" s="1"/>
@@ -18292,7 +18303,7 @@
     <row r="68" spans="1:24">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="131">
+      <c r="C68" s="132">
         <v>10</v>
       </c>
       <c r="D68" s="58">
@@ -18300,10 +18311,10 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="131">
+      <c r="G68" s="132">
         <v>10</v>
       </c>
-      <c r="H68" s="130">
+      <c r="H68" s="131">
         <v>1.4534606481481482E-3</v>
       </c>
       <c r="I68" s="1"/>
@@ -18334,7 +18345,7 @@
     <row r="69" spans="1:24">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="131">
+      <c r="C69" s="132">
         <v>11</v>
       </c>
       <c r="D69" s="58">
@@ -18342,10 +18353,10 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="131">
+      <c r="G69" s="132">
         <v>11</v>
       </c>
-      <c r="H69" s="130">
+      <c r="H69" s="131">
         <v>1.9292013888888887E-3</v>
       </c>
       <c r="I69" s="1"/>
@@ -18376,7 +18387,7 @@
     <row r="70" spans="1:24">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="131">
+      <c r="C70" s="132">
         <v>12</v>
       </c>
       <c r="D70" s="58">
@@ -18384,10 +18395,10 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="131">
+      <c r="G70" s="132">
         <v>12</v>
       </c>
-      <c r="H70" s="130">
+      <c r="H70" s="131">
         <v>1.2021874999999999E-3</v>
       </c>
       <c r="I70" s="1"/>
@@ -18418,7 +18429,7 @@
     <row r="71" spans="1:24">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="131">
+      <c r="C71" s="132">
         <v>13</v>
       </c>
       <c r="D71" s="58">
@@ -18426,10 +18437,10 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="131">
+      <c r="G71" s="132">
         <v>13</v>
       </c>
-      <c r="H71" s="130">
+      <c r="H71" s="131">
         <v>1.2077546296296296E-3</v>
       </c>
       <c r="I71" s="1"/>
@@ -18460,7 +18471,7 @@
     <row r="72" spans="1:24">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="131">
+      <c r="C72" s="132">
         <v>14</v>
       </c>
       <c r="D72" s="58">
@@ -18468,10 +18479,10 @@
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="131">
+      <c r="G72" s="132">
         <v>14</v>
       </c>
-      <c r="H72" s="130">
+      <c r="H72" s="131">
         <v>1.2092245370370371E-3</v>
       </c>
       <c r="I72" s="1"/>
@@ -18502,7 +18513,7 @@
     <row r="73" spans="1:24">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="131">
+      <c r="C73" s="132">
         <v>15</v>
       </c>
       <c r="D73" s="58">
@@ -18510,10 +18521,10 @@
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="131">
+      <c r="G73" s="132">
         <v>15</v>
       </c>
-      <c r="H73" s="130">
+      <c r="H73" s="131">
         <v>1.2027314814814815E-3</v>
       </c>
       <c r="I73" s="1"/>
@@ -18544,7 +18555,7 @@
     <row r="74" spans="1:24">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="131">
+      <c r="C74" s="132">
         <v>16</v>
       </c>
       <c r="D74" s="58">
@@ -18552,10 +18563,10 @@
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="131">
+      <c r="G74" s="132">
         <v>16</v>
       </c>
-      <c r="H74" s="130">
+      <c r="H74" s="131">
         <v>1.2106712962962963E-3</v>
       </c>
       <c r="I74" s="1"/>
@@ -18590,7 +18601,7 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="131"/>
+      <c r="G75" s="132"/>
       <c r="H75" s="99"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -18624,7 +18635,7 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="131"/>
+      <c r="G76" s="132"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -18669,7 +18680,7 @@
         <f>+AVERAGE(F55:F64,F68:F74)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G77" s="131"/>
+      <c r="G77" s="132"/>
       <c r="H77" s="58">
         <f>+AVERAGE(H59:H67,H70:H74)</f>
         <v>1.2591030092592593E-3</v>
@@ -18706,7 +18717,7 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="131"/>
+      <c r="G78" s="132"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -19782,11 +19793,25 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="M58:N58"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:R58"/>
-    <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:R1"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="G27:H27"/>
@@ -19796,25 +19821,11 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:R58"/>
+    <mergeCell ref="K57:R57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Torneo.xlsx
+++ b/Torneo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A96C6C-CB6D-4769-B436-B7CDA0BD7C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{466A214B-B300-4F32-988A-1AEE9CE9257C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="324" r:id="rId9"/>
+    <pivotCache cacheId="58" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="133">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -333,7 +333,49 @@
     <t>VR Carrera 2</t>
   </si>
   <si>
+    <t>01:53.487</t>
+  </si>
+  <si>
+    <t>01:54.074</t>
+  </si>
+  <si>
+    <t>01:54.108</t>
+  </si>
+  <si>
+    <t>01:54.187</t>
+  </si>
+  <si>
+    <t>01:54.319</t>
+  </si>
+  <si>
+    <t>01:54.910</t>
+  </si>
+  <si>
+    <t>Adrian Saldias</t>
+  </si>
+  <si>
+    <t>Jesuan Anit</t>
+  </si>
+  <si>
+    <t>Federico Oris</t>
+  </si>
+  <si>
+    <t>agus_iraldi92</t>
+  </si>
+  <si>
+    <t>Gabriel Juarez</t>
+  </si>
+  <si>
+    <t>Ale Charvey</t>
+  </si>
+  <si>
+    <t>TERMAS TN</t>
+  </si>
+  <si>
     <t>Columna1</t>
+  </si>
+  <si>
+    <t>Termas TN</t>
   </si>
   <si>
     <t>Pablo C2</t>
@@ -1256,6 +1298,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1265,16 +1310,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1283,26 +1346,8 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1312,6 +1357,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1325,16 +1373,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5196,7 +5238,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="324" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0400-000000000000}" name="TablaDinámica1" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:F7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -5853,26 +5895,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="108"/>
+      <c r="D1" s="116"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="115" t="s">
+      <c r="F1" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -5887,13 +5929,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="104">
+      <c r="A2" s="105">
         <v>1</v>
       </c>
-      <c r="B2" s="104">
+      <c r="B2" s="105">
         <v>25</v>
       </c>
-      <c r="C2" s="104">
+      <c r="C2" s="105">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -5933,26 +5975,26 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1"/>
-      <c r="R2" s="115" t="s">
+      <c r="R2" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="115"/>
-      <c r="T2" s="115"/>
-      <c r="U2" s="115"/>
-      <c r="V2" s="115"/>
-      <c r="W2" s="115"/>
-      <c r="X2" s="115"/>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="104">
+      <c r="A3" s="105">
         <v>2</v>
       </c>
-      <c r="B3" s="104">
+      <c r="B3" s="105">
         <v>18</v>
       </c>
-      <c r="C3" s="104">
+      <c r="C3" s="105">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -6021,13 +6063,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="104">
+      <c r="A4" s="105">
         <v>3</v>
       </c>
-      <c r="B4" s="104">
+      <c r="B4" s="105">
         <v>15</v>
       </c>
-      <c r="C4" s="104">
+      <c r="C4" s="105">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -6090,13 +6132,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="104">
+      <c r="A5" s="105">
         <v>4</v>
       </c>
-      <c r="B5" s="104">
+      <c r="B5" s="105">
         <v>12</v>
       </c>
-      <c r="C5" s="104">
+      <c r="C5" s="105">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -6152,17 +6194,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="115" t="s">
+      <c r="R6" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="115"/>
-      <c r="T6" s="115"/>
-      <c r="U6" s="115"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="115"/>
-      <c r="X6" s="115"/>
-      <c r="Y6" s="115"/>
-      <c r="Z6" s="115"/>
+      <c r="S6" s="110"/>
+      <c r="T6" s="110"/>
+      <c r="U6" s="110"/>
+      <c r="V6" s="110"/>
+      <c r="W6" s="110"/>
+      <c r="X6" s="110"/>
+      <c r="Y6" s="110"/>
+      <c r="Z6" s="110"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -6224,26 +6266,26 @@
       <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="119">
+      <c r="G8" s="115">
         <f>+SUM(H3:H7)</f>
         <v>39.25</v>
       </c>
-      <c r="H8" s="117"/>
-      <c r="I8" s="119">
+      <c r="H8" s="114"/>
+      <c r="I8" s="115">
         <f>+SUM(J3:J7)</f>
         <v>36.75</v>
       </c>
-      <c r="J8" s="117"/>
-      <c r="K8" s="119">
+      <c r="J8" s="114"/>
+      <c r="K8" s="115">
         <f>+SUM(L3:L7)</f>
         <v>21</v>
       </c>
-      <c r="L8" s="117"/>
-      <c r="M8" s="119">
+      <c r="L8" s="114"/>
+      <c r="M8" s="115">
         <f>+SUM(N3:N7)</f>
         <v>28.5</v>
       </c>
-      <c r="N8" s="117"/>
+      <c r="N8" s="114"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -6278,17 +6320,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="115" t="s">
+      <c r="R9" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="115"/>
-      <c r="T9" s="115"/>
-      <c r="U9" s="115"/>
-      <c r="V9" s="115"/>
-      <c r="W9" s="115"/>
-      <c r="X9" s="115"/>
-      <c r="Y9" s="115"/>
-      <c r="Z9" s="115"/>
+      <c r="S9" s="110"/>
+      <c r="T9" s="110"/>
+      <c r="U9" s="110"/>
+      <c r="V9" s="110"/>
+      <c r="W9" s="110"/>
+      <c r="X9" s="110"/>
+      <c r="Y9" s="110"/>
+      <c r="Z9" s="110"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -6299,26 +6341,26 @@
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="118">
+      <c r="G10" s="117">
         <f>G8</f>
         <v>39.25</v>
       </c>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118">
+      <c r="H10" s="117"/>
+      <c r="I10" s="117">
         <f>I8</f>
         <v>36.75</v>
       </c>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118">
+      <c r="J10" s="117"/>
+      <c r="K10" s="117">
         <f>K8</f>
         <v>21</v>
       </c>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118">
+      <c r="L10" s="117"/>
+      <c r="M10" s="117">
         <f>M8</f>
         <v>28.5</v>
       </c>
-      <c r="N10" s="118"/>
+      <c r="N10" s="117"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6351,26 +6393,26 @@
       <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="108">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="109">
+      <c r="H11" s="109"/>
+      <c r="I11" s="108">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J11" s="110"/>
-      <c r="K11" s="109">
+      <c r="J11" s="109"/>
+      <c r="K11" s="108">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="110"/>
-      <c r="M11" s="109">
+      <c r="L11" s="109"/>
+      <c r="M11" s="108">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N11" s="110"/>
+      <c r="N11" s="109"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6393,40 +6435,40 @@
       <c r="F12" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="109">
+      <c r="G12" s="108">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H12" s="110"/>
-      <c r="I12" s="109">
+      <c r="H12" s="109"/>
+      <c r="I12" s="108">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J12" s="110"/>
-      <c r="K12" s="109">
+      <c r="J12" s="109"/>
+      <c r="K12" s="108">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="110"/>
-      <c r="M12" s="109">
+      <c r="L12" s="109"/>
+      <c r="M12" s="108">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="N12" s="110"/>
+      <c r="N12" s="109"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="115" t="s">
+      <c r="R12" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="S12" s="115"/>
-      <c r="T12" s="115"/>
-      <c r="U12" s="115"/>
-      <c r="V12" s="115"/>
-      <c r="W12" s="115"/>
-      <c r="X12" s="115"/>
-      <c r="Y12" s="115"/>
-      <c r="Z12" s="115"/>
+      <c r="S12" s="110"/>
+      <c r="T12" s="110"/>
+      <c r="U12" s="110"/>
+      <c r="V12" s="110"/>
+      <c r="W12" s="110"/>
+      <c r="X12" s="110"/>
+      <c r="Y12" s="110"/>
+      <c r="Z12" s="110"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -6472,17 +6514,17 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="115" t="s">
+      <c r="F14" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -6713,26 +6755,26 @@
       <c r="F21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="119">
+      <c r="G21" s="115">
         <f>+SUM(H16:H20)</f>
         <v>25.5</v>
       </c>
-      <c r="H21" s="117"/>
-      <c r="I21" s="116">
+      <c r="H21" s="114"/>
+      <c r="I21" s="113">
         <f>+SUM(J16:J20)</f>
         <v>36.75</v>
       </c>
-      <c r="J21" s="117"/>
-      <c r="K21" s="116">
+      <c r="J21" s="114"/>
+      <c r="K21" s="113">
         <f>+SUM(L16:L20)</f>
         <v>36.25</v>
       </c>
-      <c r="L21" s="117"/>
-      <c r="M21" s="116">
+      <c r="L21" s="114"/>
+      <c r="M21" s="113">
         <f>+SUM(N16:N20)</f>
         <v>27</v>
       </c>
-      <c r="N21" s="117"/>
+      <c r="N21" s="114"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -6765,26 +6807,26 @@
       <c r="F23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="113">
+      <c r="G23" s="111">
         <f>+SUM(G21+G10)</f>
         <v>64.75</v>
       </c>
-      <c r="H23" s="114"/>
-      <c r="I23" s="113">
+      <c r="H23" s="112"/>
+      <c r="I23" s="111">
         <f>+SUM(I21+I10)</f>
         <v>73.5</v>
       </c>
-      <c r="J23" s="114"/>
-      <c r="K23" s="113">
+      <c r="J23" s="112"/>
+      <c r="K23" s="111">
         <f>+SUM(K21+K10)</f>
         <v>57.25</v>
       </c>
-      <c r="L23" s="114"/>
-      <c r="M23" s="113">
+      <c r="L23" s="112"/>
+      <c r="M23" s="111">
         <f>+SUM(M21+M10)</f>
         <v>55.5</v>
       </c>
-      <c r="N23" s="114"/>
+      <c r="N23" s="112"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -6798,26 +6840,26 @@
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="109">
+      <c r="G24" s="108">
         <f>+IF($G16=1,40,IF($G16=2,20,IF($G16=3,10,IF($G16=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="110"/>
-      <c r="I24" s="109">
+      <c r="H24" s="109"/>
+      <c r="I24" s="108">
         <f>+IF($I16=1,40,IF($I16=2,20,IF($I16=3,10,IF($I16=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J24" s="110"/>
-      <c r="K24" s="109">
+      <c r="J24" s="109"/>
+      <c r="K24" s="108">
         <f>+IF($K16=1,40,IF($K16=2,20,IF($K16=3,10,IF($K16=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="L24" s="110"/>
-      <c r="M24" s="109">
+      <c r="L24" s="109"/>
+      <c r="M24" s="108">
         <f>+IF($M16=1,40,IF($M16=2,20,IF($M16=3,10,IF($M16=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N24" s="110"/>
+      <c r="N24" s="109"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -6831,26 +6873,26 @@
       <c r="F25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="109">
+      <c r="G25" s="108">
         <f>+SUM(G24+G12)</f>
         <v>40</v>
       </c>
-      <c r="H25" s="110"/>
-      <c r="I25" s="109">
+      <c r="H25" s="109"/>
+      <c r="I25" s="108">
         <f>+SUM(I24+I12)</f>
         <v>30</v>
       </c>
-      <c r="J25" s="110"/>
-      <c r="K25" s="109">
+      <c r="J25" s="109"/>
+      <c r="K25" s="108">
         <f>+SUM(K24+K12)</f>
         <v>40</v>
       </c>
-      <c r="L25" s="110"/>
-      <c r="M25" s="109">
+      <c r="L25" s="109"/>
+      <c r="M25" s="108">
         <f>+SUM(M24+M12)</f>
         <v>30</v>
       </c>
-      <c r="N25" s="110"/>
+      <c r="N25" s="109"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -6880,17 +6922,17 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="115" t="s">
+      <c r="F27" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="115"/>
-      <c r="N27" s="115"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="110"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -7090,26 +7132,26 @@
       <c r="F34" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="116">
+      <c r="G34" s="113">
         <f>+SUM(H29:H33)</f>
         <v>31.5</v>
       </c>
-      <c r="H34" s="117"/>
-      <c r="I34" s="116">
+      <c r="H34" s="114"/>
+      <c r="I34" s="113">
         <f>+SUM(J29:J33)</f>
         <v>46.75</v>
       </c>
-      <c r="J34" s="117"/>
-      <c r="K34" s="116">
+      <c r="J34" s="114"/>
+      <c r="K34" s="113">
         <f>+SUM(L29:L33)</f>
         <v>26.25</v>
       </c>
-      <c r="L34" s="117"/>
-      <c r="M34" s="116">
+      <c r="L34" s="114"/>
+      <c r="M34" s="113">
         <f>+SUM(N29:N33)</f>
         <v>21</v>
       </c>
-      <c r="N34" s="117"/>
+      <c r="N34" s="114"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -7144,26 +7186,26 @@
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="113">
+      <c r="G36" s="111">
         <f>+SUM(G34,G23)</f>
         <v>96.25</v>
       </c>
-      <c r="H36" s="114"/>
-      <c r="I36" s="113">
+      <c r="H36" s="112"/>
+      <c r="I36" s="111">
         <f>+SUM(I34,I23)</f>
         <v>120.25</v>
       </c>
-      <c r="J36" s="114"/>
-      <c r="K36" s="113">
+      <c r="J36" s="112"/>
+      <c r="K36" s="111">
         <f>+SUM(K34,K23)</f>
         <v>83.5</v>
       </c>
-      <c r="L36" s="114"/>
-      <c r="M36" s="113">
+      <c r="L36" s="112"/>
+      <c r="M36" s="111">
         <f>+SUM(M34,M23)</f>
         <v>76.5</v>
       </c>
-      <c r="N36" s="114"/>
+      <c r="N36" s="112"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -7178,26 +7220,26 @@
       <c r="F37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="109">
+      <c r="G37" s="108">
         <f>+IF($G29=1,40,IF($G29=2,20,IF($G29=3,10,IF($G29=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H37" s="110"/>
-      <c r="I37" s="109">
+      <c r="H37" s="109"/>
+      <c r="I37" s="108">
         <f>+IF($I29=1,40,IF($I29=2,20,IF($I29=3,10,IF($I29=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J37" s="110"/>
-      <c r="K37" s="109">
+      <c r="J37" s="109"/>
+      <c r="K37" s="108">
         <f>+IF($K29=1,40,IF($K29=2,20,IF($K29=3,10,IF($K29=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L37" s="110"/>
-      <c r="M37" s="109">
+      <c r="L37" s="109"/>
+      <c r="M37" s="108">
         <f>+IF($M29=1,40,IF($M29=2,20,IF($M29=3,10,IF($M29=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="110"/>
+      <c r="N37" s="109"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -7212,26 +7254,26 @@
       <c r="F38" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="109">
+      <c r="G38" s="108">
         <f>+SUM(G37+G25)</f>
         <v>60</v>
       </c>
-      <c r="H38" s="110"/>
-      <c r="I38" s="109">
+      <c r="H38" s="109"/>
+      <c r="I38" s="108">
         <f>+SUM(I37+I25)</f>
         <v>70</v>
       </c>
-      <c r="J38" s="110"/>
-      <c r="K38" s="109">
+      <c r="J38" s="109"/>
+      <c r="K38" s="108">
         <f>+SUM(K37+K25)</f>
         <v>50</v>
       </c>
-      <c r="L38" s="110"/>
-      <c r="M38" s="109">
+      <c r="L38" s="109"/>
+      <c r="M38" s="108">
         <f>+SUM(M37+M25)</f>
         <v>30</v>
       </c>
-      <c r="N38" s="110"/>
+      <c r="N38" s="109"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -7263,17 +7305,17 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="115" t="s">
+      <c r="F40" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="115"/>
-      <c r="H40" s="115"/>
-      <c r="I40" s="115"/>
-      <c r="J40" s="115"/>
-      <c r="K40" s="115"/>
-      <c r="L40" s="115"/>
-      <c r="M40" s="115"/>
-      <c r="N40" s="115"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="110"/>
+      <c r="I40" s="110"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="110"/>
+      <c r="L40" s="110"/>
+      <c r="M40" s="110"/>
+      <c r="N40" s="110"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -7484,26 +7526,26 @@
       <c r="F47" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="116">
+      <c r="G47" s="113">
         <f>+SUM(H42:H46)</f>
         <v>45.75</v>
       </c>
-      <c r="H47" s="117"/>
-      <c r="I47" s="116">
+      <c r="H47" s="114"/>
+      <c r="I47" s="113">
         <f t="shared" ref="I47" si="0">+SUM(J42:J46)</f>
         <v>28.5</v>
       </c>
-      <c r="J47" s="117"/>
-      <c r="K47" s="116">
+      <c r="J47" s="114"/>
+      <c r="K47" s="113">
         <f t="shared" ref="K47" si="1">+SUM(L42:L46)</f>
         <v>23.25</v>
       </c>
-      <c r="L47" s="117"/>
-      <c r="M47" s="116">
+      <c r="L47" s="114"/>
+      <c r="M47" s="113">
         <f t="shared" ref="M47" si="2">+SUM(N42:N46)</f>
         <v>28</v>
       </c>
-      <c r="N47" s="117"/>
+      <c r="N47" s="114"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -7538,26 +7580,26 @@
       <c r="F49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="113">
+      <c r="G49" s="111">
         <f>+SUM(G47,G36)</f>
         <v>142</v>
       </c>
-      <c r="H49" s="114"/>
-      <c r="I49" s="113">
+      <c r="H49" s="112"/>
+      <c r="I49" s="111">
         <f>+SUM(I47,I36)</f>
         <v>148.75</v>
       </c>
-      <c r="J49" s="114"/>
-      <c r="K49" s="113">
+      <c r="J49" s="112"/>
+      <c r="K49" s="111">
         <f>+SUM(K47,K36)</f>
         <v>106.75</v>
       </c>
-      <c r="L49" s="114"/>
-      <c r="M49" s="113">
+      <c r="L49" s="112"/>
+      <c r="M49" s="111">
         <f>+SUM(M47,M36)</f>
         <v>104.5</v>
       </c>
-      <c r="N49" s="114"/>
+      <c r="N49" s="112"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
     </row>
@@ -7565,26 +7607,26 @@
       <c r="F50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="109">
+      <c r="G50" s="108">
         <f>+IF($G42=1,40,IF($G42=2,20,IF($G42=3,10,IF($G42=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H50" s="110"/>
-      <c r="I50" s="109">
+      <c r="H50" s="109"/>
+      <c r="I50" s="108">
         <f>+IF($I42=1,40,IF($I42=2,20,IF($I42=3,10,IF($I42=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J50" s="110"/>
-      <c r="K50" s="109">
+      <c r="J50" s="109"/>
+      <c r="K50" s="108">
         <f>+IF($K42=1,40,IF($K42=2,20,IF($K42=3,10,IF($K42=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="110"/>
-      <c r="M50" s="109">
+      <c r="L50" s="109"/>
+      <c r="M50" s="108">
         <f>+IF($M42=1,40,IF($M42=2,20,IF($M42=3,10,IF($M42=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N50" s="110"/>
+      <c r="N50" s="109"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
     </row>
@@ -7592,26 +7634,26 @@
       <c r="F51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="109">
+      <c r="G51" s="108">
         <f>+SUM(G50+G38-G11)</f>
         <v>60</v>
       </c>
-      <c r="H51" s="110"/>
-      <c r="I51" s="109">
+      <c r="H51" s="109"/>
+      <c r="I51" s="108">
         <f>+SUM(I50+I38-I11)</f>
         <v>60</v>
       </c>
-      <c r="J51" s="110"/>
-      <c r="K51" s="109">
+      <c r="J51" s="109"/>
+      <c r="K51" s="108">
         <f>+SUM(K50+K38-K11)</f>
         <v>50</v>
       </c>
-      <c r="L51" s="110"/>
-      <c r="M51" s="109">
+      <c r="L51" s="109"/>
+      <c r="M51" s="108">
         <f>+SUM(M50+M38-M11)</f>
         <v>40</v>
       </c>
-      <c r="N51" s="110"/>
+      <c r="N51" s="109"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
     </row>
@@ -7629,17 +7671,17 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F53" s="115" t="s">
+      <c r="F53" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="G53" s="115"/>
-      <c r="H53" s="115"/>
-      <c r="I53" s="115"/>
-      <c r="J53" s="115"/>
-      <c r="K53" s="115"/>
-      <c r="L53" s="115"/>
-      <c r="M53" s="115"/>
-      <c r="N53" s="115"/>
+      <c r="G53" s="110"/>
+      <c r="H53" s="110"/>
+      <c r="I53" s="110"/>
+      <c r="J53" s="110"/>
+      <c r="K53" s="110"/>
+      <c r="L53" s="110"/>
+      <c r="M53" s="110"/>
+      <c r="N53" s="110"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
     </row>
@@ -7801,26 +7843,26 @@
       <c r="F60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="116">
+      <c r="G60" s="113">
         <f>+SUM(H55:H59)</f>
         <v>30.5</v>
       </c>
-      <c r="H60" s="117"/>
-      <c r="I60" s="116">
+      <c r="H60" s="114"/>
+      <c r="I60" s="113">
         <f>+SUM(J55:J59)</f>
         <v>29.25</v>
       </c>
-      <c r="J60" s="117"/>
-      <c r="K60" s="116">
+      <c r="J60" s="114"/>
+      <c r="K60" s="113">
         <f t="shared" ref="K60" si="3">+SUM(L55:L59)</f>
         <v>21</v>
       </c>
-      <c r="L60" s="117"/>
-      <c r="M60" s="116">
+      <c r="L60" s="114"/>
+      <c r="M60" s="113">
         <f t="shared" ref="M60" si="4">+SUM(N55:N59)</f>
         <v>44.75</v>
       </c>
-      <c r="N60" s="117"/>
+      <c r="N60" s="114"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
     </row>
@@ -7841,26 +7883,26 @@
       <c r="F62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="113">
+      <c r="G62" s="111">
         <f>+SUM(G60,G49)</f>
         <v>172.5</v>
       </c>
-      <c r="H62" s="114"/>
-      <c r="I62" s="113">
+      <c r="H62" s="112"/>
+      <c r="I62" s="111">
         <f t="shared" ref="I62" si="5">+SUM(I60,I49)</f>
         <v>178</v>
       </c>
-      <c r="J62" s="114"/>
-      <c r="K62" s="113">
+      <c r="J62" s="112"/>
+      <c r="K62" s="111">
         <f t="shared" ref="K62" si="6">+SUM(K60,K49)</f>
         <v>127.75</v>
       </c>
-      <c r="L62" s="114"/>
-      <c r="M62" s="113">
+      <c r="L62" s="112"/>
+      <c r="M62" s="111">
         <f t="shared" ref="M62" si="7">+SUM(M60,M49)</f>
         <v>149.25</v>
       </c>
-      <c r="N62" s="114"/>
+      <c r="N62" s="112"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
     </row>
@@ -7868,26 +7910,26 @@
       <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="109">
+      <c r="G63" s="108">
         <f>+IF($G55=1,40,IF($G55=2,20,IF($G55=3,10,IF($G55=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H63" s="110"/>
-      <c r="I63" s="109">
+      <c r="H63" s="109"/>
+      <c r="I63" s="108">
         <f>+IF($I55=1,40,IF($I55=2,20,IF($I55=3,10,IF($I55=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J63" s="110"/>
-      <c r="K63" s="109">
+      <c r="J63" s="109"/>
+      <c r="K63" s="108">
         <f>+IF($K55=1,40,IF($K55=2,20,IF($K55=3,10,IF($K55=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="110"/>
-      <c r="M63" s="109">
+      <c r="L63" s="109"/>
+      <c r="M63" s="108">
         <f>+IF($M55=1,40,IF($M55=2,20,IF($M55=3,10,IF($M55=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="N63" s="110"/>
+      <c r="N63" s="109"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
     </row>
@@ -7895,41 +7937,41 @@
       <c r="F64" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="109">
+      <c r="G64" s="108">
         <f>+SUM(G63+G51-G24)</f>
         <v>70</v>
       </c>
-      <c r="H64" s="110"/>
-      <c r="I64" s="109">
+      <c r="H64" s="109"/>
+      <c r="I64" s="108">
         <f>+SUM(I63+I51-I24)</f>
         <v>70</v>
       </c>
-      <c r="J64" s="110"/>
-      <c r="K64" s="109">
+      <c r="J64" s="109"/>
+      <c r="K64" s="108">
         <f>+SUM(K63+K51-K24)</f>
         <v>10</v>
       </c>
-      <c r="L64" s="110"/>
-      <c r="M64" s="109">
+      <c r="L64" s="109"/>
+      <c r="M64" s="108">
         <f>+SUM(M63+M51-M24)</f>
         <v>60</v>
       </c>
-      <c r="N64" s="110"/>
+      <c r="N64" s="109"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
     </row>
     <row r="66" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F66" s="115" t="s">
+      <c r="F66" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="115"/>
-      <c r="H66" s="115"/>
-      <c r="I66" s="115"/>
-      <c r="J66" s="115"/>
-      <c r="K66" s="115"/>
-      <c r="L66" s="115"/>
-      <c r="M66" s="115"/>
-      <c r="N66" s="115"/>
+      <c r="G66" s="110"/>
+      <c r="H66" s="110"/>
+      <c r="I66" s="110"/>
+      <c r="J66" s="110"/>
+      <c r="K66" s="110"/>
+      <c r="L66" s="110"/>
+      <c r="M66" s="110"/>
+      <c r="N66" s="110"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
     </row>
@@ -8091,35 +8133,35 @@
       <c r="F73" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G73" s="116">
+      <c r="G73" s="113">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="H73" s="117">
+      <c r="H73" s="114">
         <f>+SUM(H68:H72)</f>
         <v>34.75</v>
       </c>
-      <c r="I73" s="116">
+      <c r="I73" s="113">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="J73" s="117">
+      <c r="J73" s="114">
         <f>+SUM(J68:J72)</f>
         <v>40.5</v>
       </c>
-      <c r="K73" s="116">
+      <c r="K73" s="113">
         <f>+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="L73" s="117">
+      <c r="L73" s="114">
         <f t="shared" ref="L73" si="8">+SUM(L68:L72)</f>
         <v>21</v>
       </c>
-      <c r="M73" s="116">
+      <c r="M73" s="113">
         <f t="shared" ref="M73" si="9">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
-      <c r="N73" s="117">
+      <c r="N73" s="114">
         <f t="shared" ref="N73" si="10">+SUM(N68:N72)</f>
         <v>29.25</v>
       </c>
@@ -8143,26 +8185,26 @@
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="113">
+      <c r="G75" s="111">
         <f>+SUM(G73,G62)</f>
         <v>207.25</v>
       </c>
-      <c r="H75" s="114"/>
-      <c r="I75" s="113">
+      <c r="H75" s="112"/>
+      <c r="I75" s="111">
         <f>+SUM(I73,I62)</f>
         <v>218.5</v>
       </c>
-      <c r="J75" s="114"/>
-      <c r="K75" s="113">
+      <c r="J75" s="112"/>
+      <c r="K75" s="111">
         <f>+SUM(K73,K62)</f>
         <v>148.75</v>
       </c>
-      <c r="L75" s="114"/>
-      <c r="M75" s="113">
+      <c r="L75" s="112"/>
+      <c r="M75" s="111">
         <f>+SUM(M73,M62)</f>
         <v>178.5</v>
       </c>
-      <c r="N75" s="114"/>
+      <c r="N75" s="112"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
     </row>
@@ -8170,26 +8212,26 @@
       <c r="F76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="109">
+      <c r="G76" s="108">
         <f>+IF($G68=1,40,IF($G68=2,20,IF($G68=3,10,IF($G68=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H76" s="110"/>
-      <c r="I76" s="109">
+      <c r="H76" s="109"/>
+      <c r="I76" s="108">
         <f>+IF($I68=1,40,IF($I68=2,20,IF($I68=3,10,IF($I68=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J76" s="110"/>
-      <c r="K76" s="109">
+      <c r="J76" s="109"/>
+      <c r="K76" s="108">
         <f>+IF($K68=1,40,IF($K68=2,20,IF($K68=3,10,IF($K68=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="110"/>
-      <c r="M76" s="109">
+      <c r="L76" s="109"/>
+      <c r="M76" s="108">
         <f>+IF($M68=1,40,IF($M68=2,20,IF($M68=3,10,IF($M68=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N76" s="110"/>
+      <c r="N76" s="109"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
     </row>
@@ -8197,41 +8239,41 @@
       <c r="F77" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="109">
+      <c r="G77" s="108">
         <f>+SUM(G76+G64-G37)</f>
         <v>60</v>
       </c>
-      <c r="H77" s="110"/>
-      <c r="I77" s="109">
+      <c r="H77" s="109"/>
+      <c r="I77" s="108">
         <f>+SUM(I76+I64-I37)</f>
         <v>70</v>
       </c>
-      <c r="J77" s="110"/>
-      <c r="K77" s="109">
+      <c r="J77" s="109"/>
+      <c r="K77" s="108">
         <f>+SUM(K76+K64-K37)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="110"/>
-      <c r="M77" s="109">
+      <c r="L77" s="109"/>
+      <c r="M77" s="108">
         <f>+SUM(M76+M64-M37)</f>
         <v>80</v>
       </c>
-      <c r="N77" s="110"/>
+      <c r="N77" s="109"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
     </row>
     <row r="79" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F79" s="115" t="s">
+      <c r="F79" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="G79" s="115"/>
-      <c r="H79" s="115"/>
-      <c r="I79" s="115"/>
-      <c r="J79" s="115"/>
-      <c r="K79" s="115"/>
-      <c r="L79" s="115"/>
-      <c r="M79" s="115"/>
-      <c r="N79" s="115"/>
+      <c r="G79" s="110"/>
+      <c r="H79" s="110"/>
+      <c r="I79" s="110"/>
+      <c r="J79" s="110"/>
+      <c r="K79" s="110"/>
+      <c r="L79" s="110"/>
+      <c r="M79" s="110"/>
+      <c r="N79" s="110"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
     </row>
@@ -8443,35 +8485,35 @@
       <c r="F86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="116">
+      <c r="G86" s="113">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="H86" s="117">
+      <c r="H86" s="114">
         <f>+SUM(H81:H85)</f>
         <v>40.5</v>
       </c>
-      <c r="I86" s="116">
+      <c r="I86" s="113">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="J86" s="117">
+      <c r="J86" s="114">
         <f>+SUM(J81:J85)</f>
         <v>30.25</v>
       </c>
-      <c r="K86" s="116">
+      <c r="K86" s="113">
         <f t="shared" ref="K86:N86" si="11">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="L86" s="117">
+      <c r="L86" s="114">
         <f t="shared" ref="L86" si="12">+SUM(L81:L85)</f>
         <v>24</v>
       </c>
-      <c r="M86" s="116">
+      <c r="M86" s="113">
         <f t="shared" ref="M86:N86" si="13">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
-      <c r="N86" s="117">
+      <c r="N86" s="114">
         <f t="shared" ref="N86" si="14">+SUM(N81:N85)</f>
         <v>30.75</v>
       </c>
@@ -8515,26 +8557,26 @@
       <c r="F88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="113">
+      <c r="G88" s="111">
         <f>+SUM(G86,G75)</f>
         <v>247.75</v>
       </c>
-      <c r="H88" s="114"/>
-      <c r="I88" s="113">
+      <c r="H88" s="112"/>
+      <c r="I88" s="111">
         <f>+SUM(I86,I75)</f>
         <v>248.75</v>
       </c>
-      <c r="J88" s="114"/>
-      <c r="K88" s="113">
+      <c r="J88" s="112"/>
+      <c r="K88" s="111">
         <f>+SUM(K86,K75)</f>
         <v>172.75</v>
       </c>
-      <c r="L88" s="114"/>
-      <c r="M88" s="113">
+      <c r="L88" s="112"/>
+      <c r="M88" s="111">
         <f>+SUM(M86,M75)</f>
         <v>209.25</v>
       </c>
-      <c r="N88" s="114"/>
+      <c r="N88" s="112"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -8552,26 +8594,26 @@
       <c r="F89" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="109">
+      <c r="G89" s="108">
         <f>+IF($G81=1,40,IF($G81=2,20,IF($G81=3,10,IF($G81=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H89" s="110"/>
-      <c r="I89" s="109">
+      <c r="H89" s="109"/>
+      <c r="I89" s="108">
         <f>+IF($I81=1,40,IF($I81=2,20,IF($I81=3,10,IF($I81=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="J89" s="110"/>
-      <c r="K89" s="109">
+      <c r="J89" s="109"/>
+      <c r="K89" s="108">
         <f>+IF($K81=1,40,IF($K81=2,20,IF($K81=3,10,IF($K81=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L89" s="110"/>
-      <c r="M89" s="109">
+      <c r="L89" s="109"/>
+      <c r="M89" s="108">
         <f>+IF($M81=1,40,IF($M81=2,20,IF($M81=3,10,IF($M81=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N89" s="110"/>
+      <c r="N89" s="109"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -8589,26 +8631,26 @@
       <c r="F90" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="109">
+      <c r="G90" s="108">
         <f>+SUM(G89+G77-G50)</f>
         <v>60</v>
       </c>
-      <c r="H90" s="110"/>
-      <c r="I90" s="109">
+      <c r="H90" s="109"/>
+      <c r="I90" s="108">
         <f>+SUM(I89+I77-I50)</f>
         <v>80</v>
       </c>
-      <c r="J90" s="110"/>
-      <c r="K90" s="109">
+      <c r="J90" s="109"/>
+      <c r="K90" s="108">
         <f>+SUM(K89+K77-K50)</f>
         <v>10</v>
       </c>
-      <c r="L90" s="110"/>
-      <c r="M90" s="109">
+      <c r="L90" s="109"/>
+      <c r="M90" s="108">
         <f>+SUM(M89+M77-M50)</f>
         <v>60</v>
       </c>
-      <c r="N90" s="110"/>
+      <c r="N90" s="109"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -8646,17 +8688,17 @@
       <c r="Z91" s="1"/>
     </row>
     <row r="92" spans="6:26">
-      <c r="F92" s="115" t="s">
+      <c r="F92" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="G92" s="115"/>
-      <c r="H92" s="115"/>
-      <c r="I92" s="115"/>
-      <c r="J92" s="115"/>
-      <c r="K92" s="115"/>
-      <c r="L92" s="115"/>
-      <c r="M92" s="115"/>
-      <c r="N92" s="115"/>
+      <c r="G92" s="110"/>
+      <c r="H92" s="110"/>
+      <c r="I92" s="110"/>
+      <c r="J92" s="110"/>
+      <c r="K92" s="110"/>
+      <c r="L92" s="110"/>
+      <c r="M92" s="110"/>
+      <c r="N92" s="110"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -8882,35 +8924,35 @@
       <c r="F99" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G99" s="116">
+      <c r="G99" s="113">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="H99" s="117">
+      <c r="H99" s="114">
         <f>+SUM(H94:H98)</f>
         <v>39.75</v>
       </c>
-      <c r="I99" s="116">
+      <c r="I99" s="113">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="J99" s="117">
+      <c r="J99" s="114">
         <f>+SUM(J94:J98)</f>
         <v>38.5</v>
       </c>
-      <c r="K99" s="116">
+      <c r="K99" s="113">
         <f t="shared" ref="K99" si="15">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="L99" s="117">
+      <c r="L99" s="114">
         <f t="shared" ref="L99" si="16">+SUM(L94:L98)</f>
         <v>24</v>
       </c>
-      <c r="M99" s="116">
+      <c r="M99" s="113">
         <f t="shared" ref="M99" si="17">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
-      <c r="N99" s="117">
+      <c r="N99" s="114">
         <f t="shared" ref="N99" si="18">+SUM(N94:N98)</f>
         <v>23.25</v>
       </c>
@@ -8948,26 +8990,26 @@
       <c r="F101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="113">
+      <c r="G101" s="111">
         <f>+SUM(G99,G88)</f>
         <v>287.5</v>
       </c>
-      <c r="H101" s="114"/>
-      <c r="I101" s="113">
+      <c r="H101" s="112"/>
+      <c r="I101" s="111">
         <f>+SUM(I99,I88)</f>
         <v>287.25</v>
       </c>
-      <c r="J101" s="114"/>
-      <c r="K101" s="113">
+      <c r="J101" s="112"/>
+      <c r="K101" s="111">
         <f>+SUM(K99,K88)</f>
         <v>196.75</v>
       </c>
-      <c r="L101" s="114"/>
-      <c r="M101" s="113">
+      <c r="L101" s="112"/>
+      <c r="M101" s="111">
         <f>+SUM(M99,M88)</f>
         <v>232.5</v>
       </c>
-      <c r="N101" s="114"/>
+      <c r="N101" s="112"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
@@ -8982,26 +9024,26 @@
       <c r="F102" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="109">
+      <c r="G102" s="108">
         <f>+IF($G94=1,40,IF($G94=2,20,IF($G94=3,10,IF($G94=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="H102" s="110"/>
-      <c r="I102" s="109">
+      <c r="H102" s="109"/>
+      <c r="I102" s="108">
         <f>+IF($I94=1,40,IF($I94=2,20,IF($I94=3,10,IF($I94=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J102" s="110"/>
-      <c r="K102" s="109">
+      <c r="J102" s="109"/>
+      <c r="K102" s="108">
         <f>+IF($K94=1,40,IF($K94=2,20,IF($K94=3,10,IF($K94=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="L102" s="110"/>
-      <c r="M102" s="109">
+      <c r="L102" s="109"/>
+      <c r="M102" s="108">
         <f>+IF($M94=1,40,IF($M94=2,20,IF($M94=3,10,IF($M94=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N102" s="110"/>
+      <c r="N102" s="109"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
@@ -9016,26 +9058,26 @@
       <c r="F103" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G103" s="109">
+      <c r="G103" s="108">
         <f>+SUM(G102+G90-G63)</f>
         <v>70</v>
       </c>
-      <c r="H103" s="110"/>
-      <c r="I103" s="109">
+      <c r="H103" s="109"/>
+      <c r="I103" s="108">
         <f>+SUM(I102+I90-I63)</f>
         <v>100</v>
       </c>
-      <c r="J103" s="110"/>
-      <c r="K103" s="109">
+      <c r="J103" s="109"/>
+      <c r="K103" s="108">
         <f>+SUM(K102+K90-K63)</f>
         <v>20</v>
       </c>
-      <c r="L103" s="110"/>
-      <c r="M103" s="109">
+      <c r="L103" s="109"/>
+      <c r="M103" s="108">
         <f>+SUM(M102+M90-M63)</f>
         <v>20</v>
       </c>
-      <c r="N103" s="110"/>
+      <c r="N103" s="109"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
@@ -9047,17 +9089,17 @@
       <c r="W103" s="101"/>
     </row>
     <row r="105" spans="6:23">
-      <c r="F105" s="115" t="s">
+      <c r="F105" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="G105" s="115"/>
-      <c r="H105" s="115"/>
-      <c r="I105" s="115"/>
-      <c r="J105" s="115"/>
-      <c r="K105" s="115"/>
-      <c r="L105" s="115"/>
-      <c r="M105" s="115"/>
-      <c r="N105" s="115"/>
+      <c r="G105" s="110"/>
+      <c r="H105" s="110"/>
+      <c r="I105" s="110"/>
+      <c r="J105" s="110"/>
+      <c r="K105" s="110"/>
+      <c r="L105" s="110"/>
+      <c r="M105" s="110"/>
+      <c r="N105" s="110"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
@@ -9169,7 +9211,7 @@
         <f>+IF(K108=1,$D$2,IF($K108=2,$D$3,IF($K108=3,$D$4,IF($K108=4,$D$5,""))))</f>
         <v/>
       </c>
-      <c r="M108" s="130"/>
+      <c r="M108" s="104"/>
       <c r="N108" s="5" t="str">
         <f>+IF(M108=1,$D$2,IF($M108=2,$D$3,IF($M108=3,$D$4,IF($M108=4,$D$5,""))))</f>
         <v/>
@@ -9258,35 +9300,35 @@
       <c r="F112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G112" s="116">
+      <c r="G112" s="113">
         <f>+SUM(H107:H111)</f>
         <v>27</v>
       </c>
-      <c r="H112" s="117">
+      <c r="H112" s="114">
         <f>+SUM(H107:H111)</f>
         <v>27</v>
       </c>
-      <c r="I112" s="116">
+      <c r="I112" s="113">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="J112" s="117">
+      <c r="J112" s="114">
         <f>+SUM(J107:J111)</f>
         <v>15</v>
       </c>
-      <c r="K112" s="116">
+      <c r="K112" s="113">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="L112" s="117">
+      <c r="L112" s="114">
         <f>+SUM(L107:L111)</f>
         <v>12</v>
       </c>
-      <c r="M112" s="116">
+      <c r="M112" s="113">
         <f>+SUM(N107:N111)</f>
         <v>18</v>
       </c>
-      <c r="N112" s="117">
+      <c r="N112" s="114">
         <f>+SUM(N107:N111)</f>
         <v>18</v>
       </c>
@@ -9324,26 +9366,26 @@
       <c r="F114" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="113">
+      <c r="G114" s="111">
         <f>+SUM(G112,G101)</f>
         <v>314.5</v>
       </c>
-      <c r="H114" s="114"/>
-      <c r="I114" s="113">
+      <c r="H114" s="112"/>
+      <c r="I114" s="111">
         <f>+SUM(I112,I101)</f>
         <v>302.25</v>
       </c>
-      <c r="J114" s="114"/>
-      <c r="K114" s="113">
+      <c r="J114" s="112"/>
+      <c r="K114" s="111">
         <f>+SUM(K112,K101)</f>
         <v>208.75</v>
       </c>
-      <c r="L114" s="114"/>
-      <c r="M114" s="113">
+      <c r="L114" s="112"/>
+      <c r="M114" s="111">
         <f>+SUM(M112,M101)</f>
         <v>250.5</v>
       </c>
-      <c r="N114" s="114"/>
+      <c r="N114" s="112"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
@@ -9366,26 +9408,26 @@
       <c r="F115" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="109">
+      <c r="G115" s="108">
         <f>+IF($G107=1,40,IF($G107=2,20,IF($G107=3,10,IF($G107=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="H115" s="110"/>
-      <c r="I115" s="109">
+      <c r="H115" s="109"/>
+      <c r="I115" s="108">
         <f>+IF($I107=1,40,IF($I107=2,20,IF($I107=3,10,IF($I107=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="J115" s="110"/>
-      <c r="K115" s="109">
+      <c r="J115" s="109"/>
+      <c r="K115" s="108">
         <f>+IF($K107=1,40,IF($K107=2,20,IF($K107=3,10,IF($K107=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="L115" s="110"/>
-      <c r="M115" s="109">
+      <c r="L115" s="109"/>
+      <c r="M115" s="108">
         <f>+IF($M107=1,40,IF($M107=2,20,IF($M107=3,10,IF($M107=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="N115" s="110"/>
+      <c r="N115" s="109"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
@@ -9400,26 +9442,26 @@
       <c r="F116" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="109">
+      <c r="G116" s="108">
         <f>+SUM(G115+G103-G76)</f>
         <v>100</v>
       </c>
-      <c r="H116" s="110"/>
-      <c r="I116" s="109">
+      <c r="H116" s="109"/>
+      <c r="I116" s="108">
         <f>+SUM(I115+I103-I76)</f>
         <v>70</v>
       </c>
-      <c r="J116" s="110"/>
-      <c r="K116" s="109">
+      <c r="J116" s="109"/>
+      <c r="K116" s="108">
         <f>+SUM(K115+K103-K76)</f>
         <v>20</v>
       </c>
-      <c r="L116" s="110"/>
-      <c r="M116" s="109">
+      <c r="L116" s="109"/>
+      <c r="M116" s="108">
         <f>+SUM(M115+M103-M76)</f>
         <v>20</v>
       </c>
-      <c r="N116" s="110"/>
+      <c r="N116" s="109"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
@@ -9431,17 +9473,17 @@
       <c r="W116" s="1"/>
     </row>
     <row r="118" spans="6:23">
-      <c r="F118" s="115" t="s">
+      <c r="F118" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="G118" s="115"/>
-      <c r="H118" s="115"/>
-      <c r="I118" s="115"/>
-      <c r="J118" s="115"/>
-      <c r="K118" s="115"/>
-      <c r="L118" s="115"/>
-      <c r="M118" s="115"/>
-      <c r="N118" s="115"/>
+      <c r="G118" s="110"/>
+      <c r="H118" s="110"/>
+      <c r="I118" s="110"/>
+      <c r="J118" s="110"/>
+      <c r="K118" s="110"/>
+      <c r="L118" s="110"/>
+      <c r="M118" s="110"/>
+      <c r="N118" s="110"/>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
@@ -9630,29 +9672,29 @@
       <c r="F125" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G125" s="116">
+      <c r="G125" s="113">
         <f>+SUM(H120:H121)</f>
         <v>0</v>
       </c>
-      <c r="H125" s="117">
+      <c r="H125" s="114">
         <f>+SUM(H120:H124)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="116">
+      <c r="I125" s="113">
         <f>+SUM(J120:J121)</f>
         <v>0</v>
       </c>
-      <c r="J125" s="117">
+      <c r="J125" s="114">
         <f>+SUM(J120:J124)</f>
         <v>0</v>
       </c>
-      <c r="K125" s="116"/>
-      <c r="L125" s="117">
+      <c r="K125" s="113"/>
+      <c r="L125" s="114">
         <f>+SUM(L120:L124)</f>
         <v>0</v>
       </c>
-      <c r="M125" s="116"/>
-      <c r="N125" s="117">
+      <c r="M125" s="113"/>
+      <c r="N125" s="114">
         <f>+SUM(N120:N124)</f>
         <v>0</v>
       </c>
@@ -9690,20 +9732,20 @@
       <c r="F127" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="113"/>
-      <c r="H127" s="114"/>
-      <c r="I127" s="113"/>
-      <c r="J127" s="114"/>
-      <c r="K127" s="113">
+      <c r="G127" s="111"/>
+      <c r="H127" s="112"/>
+      <c r="I127" s="111"/>
+      <c r="J127" s="112"/>
+      <c r="K127" s="111">
         <f>L125</f>
         <v>0</v>
       </c>
-      <c r="L127" s="114"/>
-      <c r="M127" s="113">
+      <c r="L127" s="112"/>
+      <c r="M127" s="111">
         <f>N125</f>
         <v>0</v>
       </c>
-      <c r="N127" s="114"/>
+      <c r="N127" s="112"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1" t="s">
         <v>9</v>
@@ -9724,20 +9766,20 @@
       <c r="F128" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="109" t="str">
+      <c r="G128" s="108" t="str">
         <f>+IF($G120=1,40,IF($G120=2,20,IF($G120=3,10,IF($G120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="H128" s="110"/>
-      <c r="I128" s="111" t="str">
+      <c r="H128" s="109"/>
+      <c r="I128" s="118" t="str">
         <f>+IF($I120=1,40,IF($I120=2,20,IF($I120=3,10,IF($I120=4,0,""))))</f>
         <v/>
       </c>
-      <c r="J128" s="112"/>
-      <c r="K128" s="113"/>
-      <c r="L128" s="114"/>
-      <c r="M128" s="113"/>
-      <c r="N128" s="114"/>
+      <c r="J128" s="119"/>
+      <c r="K128" s="111"/>
+      <c r="L128" s="112"/>
+      <c r="M128" s="111"/>
+      <c r="N128" s="112"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1">
         <v>37.5</v>
@@ -9761,26 +9803,26 @@
       <c r="F129" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G129" s="109">
+      <c r="G129" s="108">
         <f>G116</f>
         <v>100</v>
       </c>
-      <c r="H129" s="110"/>
-      <c r="I129" s="109">
+      <c r="H129" s="109"/>
+      <c r="I129" s="108">
         <f t="shared" ref="I129:N129" si="19">I116</f>
         <v>70</v>
       </c>
-      <c r="J129" s="110"/>
-      <c r="K129" s="109">
+      <c r="J129" s="109"/>
+      <c r="K129" s="108">
         <f t="shared" ref="K129:N129" si="20">K116</f>
         <v>20</v>
       </c>
-      <c r="L129" s="110"/>
-      <c r="M129" s="109">
+      <c r="L129" s="109"/>
+      <c r="M129" s="108">
         <f t="shared" ref="M129:N129" si="21">M116</f>
         <v>20</v>
       </c>
-      <c r="N129" s="110"/>
+      <c r="N129" s="109"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1">
         <v>28.125</v>
@@ -9802,6 +9844,158 @@
     </row>
   </sheetData>
   <mergeCells count="176">
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="G77:H77"/>
     <mergeCell ref="I77:J77"/>
     <mergeCell ref="K77:L77"/>
@@ -9826,158 +10020,6 @@
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10951,25 +10993,25 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="108"/>
+      <c r="B2" s="116"/>
       <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
@@ -10984,20 +11026,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="107"/>
-      <c r="S2" s="107"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="107" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11054,7 +11096,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="106"/>
+      <c r="A4" s="107"/>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
@@ -11121,7 +11163,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="107" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -11190,7 +11232,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="106"/>
+      <c r="A6" s="107"/>
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
@@ -11257,7 +11299,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="106" t="s">
+      <c r="A7" s="107" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -11326,7 +11368,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="106"/>
+      <c r="A8" s="107"/>
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
@@ -11361,7 +11403,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="107" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -11398,7 +11440,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="106"/>
+      <c r="A10" s="107"/>
       <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
@@ -11433,7 +11475,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="106" t="s">
+      <c r="A11" s="107" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -11470,7 +11512,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="106"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
@@ -11505,7 +11547,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="107" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -11542,7 +11584,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="106"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
@@ -11577,7 +11619,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="106" t="s">
+      <c r="A15" s="107" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -11614,7 +11656,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="106"/>
+      <c r="A16" s="107"/>
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
@@ -11649,7 +11691,7 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="106" t="s">
+      <c r="A17" s="107" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -11674,7 +11716,7 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="106"/>
+      <c r="A18" s="107"/>
       <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
@@ -11697,7 +11739,7 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -11722,7 +11764,7 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="106"/>
+      <c r="A20" s="107"/>
       <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
@@ -11745,7 +11787,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="106"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
@@ -11768,7 +11810,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="106"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
@@ -11814,354 +11856,354 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="108" t="s">
+      <c r="A25" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="108"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="108" t="s">
+      <c r="A26" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="108"/>
-      <c r="C26" s="105" t="s">
+      <c r="B26" s="116"/>
+      <c r="C26" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="105" t="s">
+      <c r="E26" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="105" t="s">
+      <c r="F26" s="106" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="106" t="s">
+      <c r="A27" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="108">
+      <c r="C27" s="116">
         <f>Hoja1!H5</f>
         <v>1</v>
       </c>
-      <c r="D27" s="108">
+      <c r="D27" s="116">
         <f>Hoja1!J5</f>
         <v>0</v>
       </c>
-      <c r="E27" s="108">
+      <c r="E27" s="116">
         <f>Hoja1!L5</f>
         <v>0</v>
       </c>
-      <c r="F27" s="108">
+      <c r="F27" s="116">
         <f>Hoja1!N5</f>
         <v>0</v>
       </c>
-      <c r="G27" s="108"/>
+      <c r="G27" s="116"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="106"/>
-      <c r="B28" s="106"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="116"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="106" t="s">
+      <c r="B29" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="108">
+      <c r="C29" s="116">
         <f>Hoja1!H18</f>
         <v>0</v>
       </c>
-      <c r="D29" s="108">
+      <c r="D29" s="116">
         <f>Hoja1!J18</f>
         <v>1</v>
       </c>
-      <c r="E29" s="108">
+      <c r="E29" s="116">
         <f>Hoja1!L18</f>
         <v>0</v>
       </c>
-      <c r="F29" s="108">
+      <c r="F29" s="116">
         <f>Hoja1!N18</f>
         <v>0</v>
       </c>
-      <c r="G29" s="108"/>
+      <c r="G29" s="116"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="106"/>
-      <c r="B30" s="106"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="107"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="116"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="106" t="s">
+      <c r="A31" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="106" t="s">
+      <c r="B31" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="108">
+      <c r="C31" s="116">
         <f>Hoja1!H31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="108">
+      <c r="D31" s="116">
         <f>Hoja1!J31</f>
         <v>1</v>
       </c>
-      <c r="E31" s="108">
+      <c r="E31" s="116">
         <f>Hoja1!L31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="108">
+      <c r="F31" s="116">
         <f>Hoja1!N31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="108"/>
+      <c r="G31" s="116"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="106"/>
-      <c r="B32" s="106"/>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
+      <c r="A32" s="107"/>
+      <c r="B32" s="107"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="116"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="106" t="s">
+      <c r="A33" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="106" t="s">
+      <c r="B33" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C33" s="116">
         <f>Hoja1!H44</f>
         <v>1</v>
       </c>
-      <c r="D33" s="108">
+      <c r="D33" s="116">
         <f>Hoja1!J44</f>
         <v>0</v>
       </c>
-      <c r="E33" s="108">
+      <c r="E33" s="116">
         <f>Hoja1!L44</f>
         <v>0</v>
       </c>
-      <c r="F33" s="108">
+      <c r="F33" s="116">
         <f>Hoja1!N44</f>
         <v>0</v>
       </c>
-      <c r="G33" s="108"/>
+      <c r="G33" s="116"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="106"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
+      <c r="A34" s="107"/>
+      <c r="B34" s="107"/>
+      <c r="C34" s="116"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="116"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="106" t="s">
+      <c r="A35" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="106" t="s">
+      <c r="B35" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="108">
+      <c r="C35" s="116">
         <f>Hoja1!H57</f>
         <v>1</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="116">
         <f>Hoja1!J57</f>
         <v>0</v>
       </c>
-      <c r="E35" s="108">
+      <c r="E35" s="116">
         <f>Hoja1!L57</f>
         <v>0</v>
       </c>
-      <c r="F35" s="108">
+      <c r="F35" s="116">
         <f>Hoja1!N57</f>
         <v>0</v>
       </c>
-      <c r="G35" s="108"/>
+      <c r="G35" s="116"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="106"/>
-      <c r="B36" s="106"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
+      <c r="A36" s="107"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="116"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="116"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="106" t="s">
+      <c r="B37" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="108">
+      <c r="C37" s="116">
         <f>Hoja1!H70</f>
         <v>1</v>
       </c>
-      <c r="D37" s="108">
+      <c r="D37" s="116">
         <f>Hoja1!J70</f>
         <v>0</v>
       </c>
-      <c r="E37" s="108">
+      <c r="E37" s="116">
         <f>Hoja1!L70</f>
         <v>0</v>
       </c>
-      <c r="F37" s="108">
+      <c r="F37" s="116">
         <f>Hoja1!N70</f>
         <v>0</v>
       </c>
-      <c r="G37" s="108"/>
+      <c r="G37" s="116"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="106"/>
-      <c r="B38" s="106"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="116"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="116"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="106" t="s">
+      <c r="A39" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="106" t="s">
+      <c r="B39" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="108">
+      <c r="C39" s="116">
         <f>Hoja1!H83</f>
         <v>1</v>
       </c>
-      <c r="D39" s="108">
+      <c r="D39" s="116">
         <f>Hoja1!J83</f>
         <v>0</v>
       </c>
-      <c r="E39" s="108">
+      <c r="E39" s="116">
         <f>Hoja1!L83</f>
         <v>0</v>
       </c>
-      <c r="F39" s="108">
+      <c r="F39" s="116">
         <f>Hoja1!N83</f>
         <v>0</v>
       </c>
-      <c r="G39" s="108"/>
+      <c r="G39" s="116"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="106"/>
-      <c r="B40" s="106"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="108"/>
-      <c r="F40" s="108"/>
-      <c r="G40" s="108"/>
+      <c r="A40" s="107"/>
+      <c r="B40" s="107"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="116"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="106" t="s">
+      <c r="A41" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="106" t="s">
+      <c r="B41" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="108">
+      <c r="C41" s="116">
         <f>Hoja1!H96</f>
         <v>1</v>
       </c>
-      <c r="D41" s="108">
+      <c r="D41" s="116">
         <f>Hoja1!J96</f>
         <v>0</v>
       </c>
-      <c r="E41" s="108">
+      <c r="E41" s="116">
         <f>Hoja1!L96</f>
         <v>0</v>
       </c>
-      <c r="F41" s="108">
+      <c r="F41" s="116">
         <f>Hoja1!N96</f>
         <v>0</v>
       </c>
-      <c r="G41" s="108"/>
+      <c r="G41" s="116"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="106"/>
-      <c r="B42" s="106"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="116"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="116"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="106" t="s">
+      <c r="A43" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="106" t="s">
+      <c r="B43" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="108">
+      <c r="C43" s="116">
         <f>Hoja1!H109</f>
         <v>1</v>
       </c>
-      <c r="D43" s="108"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="116"/>
+      <c r="F43" s="116"/>
+      <c r="G43" s="116"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="106"/>
-      <c r="B44" s="106"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
+      <c r="A44" s="107"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="116"/>
+      <c r="D44" s="116"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="116"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="106"/>
-      <c r="B45" s="106" t="s">
+      <c r="A45" s="107"/>
+      <c r="B45" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="108">
+      <c r="C45" s="116">
         <f>Hoja1!H122</f>
         <v>0</v>
       </c>
-      <c r="D45" s="108"/>
-      <c r="E45" s="108"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="108"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="116"/>
+      <c r="F45" s="116"/>
+      <c r="G45" s="116"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="106"/>
-      <c r="B46" s="106"/>
-      <c r="C46" s="108"/>
-      <c r="D46" s="108"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
+      <c r="A46" s="107"/>
+      <c r="B46" s="107"/>
+      <c r="C46" s="116"/>
+      <c r="D46" s="116"/>
+      <c r="E46" s="116"/>
+      <c r="F46" s="116"/>
+      <c r="G46" s="116"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
@@ -12188,52 +12230,28 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="I1:S2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
@@ -12250,28 +12268,52 @@
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="I1:S2"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13334,7 +13376,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="108"/>
+      <c r="A38" s="116"/>
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -13360,7 +13402,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="108"/>
+      <c r="A39" s="116"/>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
@@ -13386,7 +13428,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="108"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
@@ -13412,7 +13454,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="108"/>
+      <c r="A41" s="116"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -13474,16 +13516,16 @@
       <c r="A3" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="D3" s="106" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="105" t="s">
+      <c r="E3" s="106" t="s">
         <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -13587,7 +13629,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -13609,7 +13651,7 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="107" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -13632,7 +13674,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="106"/>
+      <c r="A3" s="107"/>
       <c r="B3" s="1" t="s">
         <v>82</v>
       </c>
@@ -13655,7 +13697,7 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="106"/>
+      <c r="A4" s="107"/>
       <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
@@ -13678,7 +13720,7 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="107" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -13695,7 +13737,7 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="106"/>
+      <c r="A6" s="107"/>
       <c r="B6" s="1" t="s">
         <v>82</v>
       </c>
@@ -13710,7 +13752,7 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="106"/>
+      <c r="A7" s="107"/>
       <c r="B7" s="1" t="s">
         <v>83</v>
       </c>
@@ -13725,7 +13767,7 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="106" t="s">
+      <c r="A8" s="107" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -13742,7 +13784,7 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="106"/>
+      <c r="A9" s="107"/>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
@@ -13757,7 +13799,7 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="106"/>
+      <c r="A10" s="107"/>
       <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
@@ -13780,7 +13822,7 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="106" t="s">
+      <c r="A11" s="107" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -13805,7 +13847,7 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="106"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
@@ -13820,7 +13862,7 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="106"/>
+      <c r="A13" s="107"/>
       <c r="B13" s="1" t="s">
         <v>83</v>
       </c>
@@ -13835,7 +13877,7 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="106" t="s">
+      <c r="A14" s="107" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -13872,7 +13914,7 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="106"/>
+      <c r="A15" s="107"/>
       <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
@@ -13905,7 +13947,7 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="106"/>
+      <c r="A16" s="107"/>
       <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
@@ -13938,7 +13980,7 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="106" t="s">
+      <c r="A17" s="107" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -13968,7 +14010,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="106"/>
+      <c r="A18" s="107"/>
       <c r="B18" s="1" t="s">
         <v>82</v>
       </c>
@@ -13996,7 +14038,7 @@
       <c r="P18" s="74"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="106"/>
+      <c r="A19" s="107"/>
       <c r="B19" s="1" t="s">
         <v>83</v>
       </c>
@@ -14024,7 +14066,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="107" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -14054,7 +14096,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="106"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="1" t="s">
         <v>82</v>
       </c>
@@ -14080,7 +14122,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="106"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="1" t="s">
         <v>83</v>
       </c>
@@ -14106,7 +14148,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="106" t="s">
+      <c r="A23" s="107" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -14136,7 +14178,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="106"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
@@ -14164,7 +14206,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="106"/>
+      <c r="A25" s="107"/>
       <c r="B25" s="1" t="s">
         <v>83</v>
       </c>
@@ -14192,7 +14234,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -14220,7 +14262,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="106"/>
+      <c r="A27" s="107"/>
       <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
@@ -14244,7 +14286,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="106"/>
+      <c r="A28" s="107"/>
       <c r="B28" s="1" t="s">
         <v>83</v>
       </c>
@@ -14264,16 +14306,30 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
+      <c r="B29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>89</v>
+      </c>
       <c r="I29" s="58"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -14284,8 +14340,10 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="106"/>
-      <c r="B30" s="1"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="58"/>
@@ -14302,14 +14360,28 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="106"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
+      <c r="A31" s="107"/>
+      <c r="B31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="I31" s="58"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -14319,8 +14391,55 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="107"/>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="107"/>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A32:A34"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
@@ -14363,7 +14482,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -14380,7 +14499,7 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="121" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
@@ -14425,7 +14544,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="121"/>
+      <c r="A3" s="122"/>
       <c r="B3" s="62" t="s">
         <v>82</v>
       </c>
@@ -14468,7 +14587,7 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="121"/>
+      <c r="A4" s="122"/>
       <c r="B4" s="62" t="s">
         <v>83</v>
       </c>
@@ -14511,7 +14630,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="121" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="64" t="s">
@@ -14533,7 +14652,7 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="121"/>
+      <c r="A6" s="122"/>
       <c r="B6" s="62" t="s">
         <v>82</v>
       </c>
@@ -14553,7 +14672,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="122"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="66" t="s">
         <v>83</v>
       </c>
@@ -14573,7 +14692,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="121" t="s">
+      <c r="A8" s="122" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="64" t="s">
@@ -14595,7 +14714,7 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="121"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="62" t="s">
         <v>82</v>
       </c>
@@ -14615,7 +14734,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="122"/>
+      <c r="A10" s="123"/>
       <c r="B10" s="66" t="s">
         <v>83</v>
       </c>
@@ -14647,7 +14766,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="121" t="s">
+      <c r="A11" s="122" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="64" t="s">
@@ -14681,7 +14800,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="121"/>
+      <c r="A12" s="122"/>
       <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
@@ -14701,7 +14820,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="121"/>
+      <c r="A13" s="122"/>
       <c r="B13" s="62" t="s">
         <v>83</v>
       </c>
@@ -14721,7 +14840,7 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="120" t="s">
+      <c r="A14" s="121" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="64" t="s">
@@ -14755,7 +14874,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="121"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="62" t="s">
         <v>82</v>
       </c>
@@ -14787,7 +14906,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="122"/>
+      <c r="A16" s="123"/>
       <c r="B16" s="66" t="s">
         <v>83</v>
       </c>
@@ -14819,7 +14938,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="122" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="62" t="s">
@@ -14853,7 +14972,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="121"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="62" t="s">
         <v>82</v>
       </c>
@@ -14885,7 +15004,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="121"/>
+      <c r="A19" s="122"/>
       <c r="B19" s="62" t="s">
         <v>83</v>
       </c>
@@ -14917,7 +15036,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="121" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="64" t="s">
@@ -14951,7 +15070,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="121"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="62" t="s">
         <v>82</v>
       </c>
@@ -14983,7 +15102,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="121"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="62" t="s">
         <v>83</v>
       </c>
@@ -15015,7 +15134,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="121" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -15049,7 +15168,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="121"/>
+      <c r="A24" s="122"/>
       <c r="B24" s="62" t="s">
         <v>82</v>
       </c>
@@ -15081,7 +15200,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="122"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="66" t="s">
         <v>83</v>
       </c>
@@ -15113,7 +15232,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="121" t="s">
+      <c r="A26" s="122" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="62" t="s">
@@ -15147,7 +15266,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="121"/>
+      <c r="A27" s="122"/>
       <c r="B27" s="62" t="s">
         <v>82</v>
       </c>
@@ -15179,7 +15298,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="121"/>
+      <c r="A28" s="122"/>
       <c r="B28" s="62" t="s">
         <v>83</v>
       </c>
@@ -15211,27 +15330,27 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="120" t="s">
-        <v>36</v>
+      <c r="A29" s="121" t="s">
+        <v>98</v>
       </c>
       <c r="B29" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="70">
+      <c r="C29" s="70" t="e">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="70">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D29" s="70" t="e">
         <f>+IF('Carga Tiempos'!D29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!D29,'Carga Tiempos'!D29-MIN('Carga Tiempos'!$C29:$F29))</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="70">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E29" s="70" t="e">
         <f>+IF('Carga Tiempos'!E29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!E29,'Carga Tiempos'!E29-MIN('Carga Tiempos'!$C29:$F29))</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="60">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F29" s="60" t="e">
         <f>+IF('Carga Tiempos'!F29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!F29,'Carga Tiempos'!F29-MIN('Carga Tiempos'!$C29:$F29))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G29" s="58"/>
       <c r="H29" s="58"/>
@@ -15245,7 +15364,7 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="121"/>
+      <c r="A30" s="122"/>
       <c r="B30" s="62" t="s">
         <v>82</v>
       </c>
@@ -15277,25 +15396,25 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="122"/>
+      <c r="A31" s="123"/>
       <c r="B31" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="71">
+      <c r="C31" s="71" t="e">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="61">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D31" s="61" t="e">
         <f>+IF('Carga Tiempos'!D31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!D31,'Carga Tiempos'!D31-MIN('Carga Tiempos'!$C31:$F31))</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" s="67" t="e">
         <f>+IF('Carga Tiempos'!E31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!E31,'Carga Tiempos'!E31-MIN('Carga Tiempos'!$C31:$F31))</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="61">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31" s="61" t="e">
         <f>+IF('Carga Tiempos'!F31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!F31,'Carga Tiempos'!F31-MIN('Carga Tiempos'!$C31:$F31))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G31" s="58"/>
       <c r="H31" s="58"/>
@@ -15404,16 +15523,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
-      <c r="K1" s="127" t="s">
+      <c r="K1" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1"/>
@@ -15426,22 +15545,22 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="123" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="124"/>
-      <c r="M2" s="123" t="s">
-        <v>86</v>
-      </c>
-      <c r="N2" s="124"/>
-      <c r="O2" s="123" t="s">
-        <v>87</v>
-      </c>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" s="124"/>
+      <c r="K2" s="125" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" s="126"/>
+      <c r="M2" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="N2" s="126"/>
+      <c r="O2" s="125" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="125" t="s">
+        <v>102</v>
+      </c>
+      <c r="R2" s="126"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -15465,19 +15584,19 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="M3" s="86" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="N3" s="77">
         <v>1.2796759259259259E-3</v>
       </c>
       <c r="O3" s="86" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="P3" s="84">
         <v>1.4428356481481482E-3</v>
       </c>
       <c r="Q3" s="83" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="R3" s="84">
         <v>1.4428356481481482E-3</v>
@@ -15505,19 +15624,19 @@
         <v>1.2580092592592593E-3</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="N4" s="77">
         <v>1.2429976851851853E-3</v>
       </c>
       <c r="O4" s="83" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="P4" s="81">
         <v>1.2858101851851852E-3</v>
       </c>
       <c r="Q4" s="83" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="R4" s="81">
         <v>1.2858101851851852E-3</v>
@@ -15545,19 +15664,19 @@
         <v>1.2545601851851852E-3</v>
       </c>
       <c r="M5" s="87" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="N5" s="77">
         <v>1.2377777777777777E-3</v>
       </c>
       <c r="O5" s="87" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="P5" s="81">
         <v>1.2647453703703703E-3</v>
       </c>
       <c r="Q5" s="83" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="R5" s="81">
         <v>1.2647453703703703E-3</v>
@@ -15585,19 +15704,19 @@
         <v>1.2705902777777778E-3</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="N6" s="77">
         <v>1.3249884259259259E-3</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="P6" s="81">
         <v>1.2908564814814816E-3</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="R6" s="81">
         <v>1.2908564814814816E-3</v>
@@ -15625,19 +15744,19 @@
         <v>1.260300925925926E-3</v>
       </c>
       <c r="M7" s="87" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N7" s="77">
         <v>1.2426273148148149E-3</v>
       </c>
       <c r="O7" s="87" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="P7" s="81">
         <v>1.2742476851851851E-3</v>
       </c>
       <c r="Q7" s="83" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="R7" s="81">
         <v>1.2742476851851851E-3</v>
@@ -15665,19 +15784,19 @@
         <v>1.2778935185185185E-3</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="N8" s="77">
         <v>1.2478472222222222E-3</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="P8" s="81">
         <v>1.2452199074074073E-3</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="R8" s="81">
         <v>1.2452199074074073E-3</v>
@@ -15705,19 +15824,19 @@
         <v>1.2427199074074074E-3</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="N9" s="77">
         <v>1.248275462962963E-3</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="P9" s="81">
         <v>1.2555324074074075E-3</v>
       </c>
       <c r="Q9" s="83" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R9" s="81">
         <v>1.2555324074074075E-3</v>
@@ -15745,19 +15864,19 @@
         <v>1.2430787037037037E-3</v>
       </c>
       <c r="M10" s="87" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="N10" s="77">
         <v>1.2653240740740741E-3</v>
       </c>
       <c r="O10" s="87" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="P10" s="81">
         <v>1.2631365740740741E-3</v>
       </c>
       <c r="Q10" s="83" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="R10" s="81">
         <v>1.2631365740740741E-3</v>
@@ -15785,19 +15904,19 @@
         <v>1.6843518518518518E-3</v>
       </c>
       <c r="M11" s="83" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="N11" s="77">
         <v>1.6837615740740741E-3</v>
       </c>
       <c r="O11" s="83" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="P11" s="81">
         <v>1.4671412037037036E-3</v>
       </c>
       <c r="Q11" s="83" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="R11" s="81">
         <v>1.4671412037037036E-3</v>
@@ -15825,19 +15944,19 @@
         <v>1.5963078703703703E-3</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="N12" s="77">
         <v>1.543287037037037E-3</v>
       </c>
       <c r="O12" s="83" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="P12" s="81">
         <v>1.5160185185185185E-3</v>
       </c>
       <c r="Q12" s="83" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="R12" s="81">
         <v>1.5160185185185185E-3</v>
@@ -15865,19 +15984,19 @@
         <v>1.8983680555555557E-3</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="N13" s="77">
         <v>1.9202893518518521E-3</v>
       </c>
       <c r="O13" s="83" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="P13" s="81">
         <v>1.9527199074074074E-3</v>
       </c>
       <c r="Q13" s="83" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="R13" s="81">
         <v>1.9527199074074074E-3</v>
@@ -15905,19 +16024,19 @@
         <v>1.2470833333333331E-3</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="N14" s="77">
         <v>1.2480787037037037E-3</v>
       </c>
       <c r="O14" s="83" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="P14" s="81">
         <v>1.2462037037037036E-3</v>
       </c>
       <c r="Q14" s="83" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="R14" s="81">
         <v>1.2462037037037036E-3</v>
@@ -15945,19 +16064,19 @@
         <v>1.236238425925926E-3</v>
       </c>
       <c r="M15" s="87" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="N15" s="77">
         <v>1.241701388888889E-3</v>
       </c>
       <c r="O15" s="87" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="P15" s="81">
         <v>1.2494560185185185E-3</v>
       </c>
       <c r="Q15" s="83" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="R15" s="81">
         <v>1.2494560185185185E-3</v>
@@ -15985,19 +16104,19 @@
         <v>1.2310648148148148E-3</v>
       </c>
       <c r="M16" s="88" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="N16" s="77">
         <v>1.2480208333333334E-3</v>
       </c>
       <c r="O16" s="88" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="P16" s="81">
         <v>1.2403703703703704E-3</v>
       </c>
       <c r="Q16" s="83" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="R16" s="81">
         <v>1.2403703703703704E-3</v>
@@ -16025,19 +16144,19 @@
         <v>1.2800810185185185E-3</v>
       </c>
       <c r="M17" s="85" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="N17" s="80">
         <v>1.2779629629629629E-3</v>
       </c>
       <c r="O17" s="85" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="P17" s="82">
         <v>1.2507638888888889E-3</v>
       </c>
       <c r="Q17" s="85" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="R17" s="82">
         <v>1.2507638888888889E-3</v>
@@ -16231,7 +16350,7 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -16243,7 +16362,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -16260,28 +16379,28 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="1:24" ht="34.5">
-      <c r="A25" s="127" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
+      <c r="A25" s="124" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
       <c r="I25" s="101"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="127" t="s">
-        <v>106</v>
-      </c>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="127"/>
+      <c r="K25" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L25" s="124"/>
+      <c r="M25" s="124"/>
+      <c r="N25" s="124"/>
+      <c r="O25" s="124"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="124"/>
+      <c r="R25" s="124"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -16290,74 +16409,74 @@
       <c r="X25" s="1"/>
     </row>
     <row r="26" spans="1:24" s="1" customFormat="1">
-      <c r="A26" s="128" t="s">
+      <c r="A26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="129"/>
-      <c r="C26" s="128" t="s">
+      <c r="B26" s="130"/>
+      <c r="C26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="129"/>
-      <c r="E26" s="128" t="s">
+      <c r="D26" s="130"/>
+      <c r="E26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="129"/>
-      <c r="G26" s="128" t="s">
+      <c r="F26" s="130"/>
+      <c r="G26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="129"/>
-      <c r="K26" s="128" t="s">
+      <c r="H26" s="130"/>
+      <c r="K26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="L26" s="129"/>
-      <c r="M26" s="128" t="s">
+      <c r="L26" s="130"/>
+      <c r="M26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="N26" s="129"/>
-      <c r="O26" s="128" t="s">
+      <c r="N26" s="130"/>
+      <c r="O26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="P26" s="129"/>
-      <c r="Q26" s="128" t="s">
+      <c r="P26" s="130"/>
+      <c r="Q26" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="R26" s="129"/>
+      <c r="R26" s="130"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="123" t="s">
-        <v>107</v>
-      </c>
-      <c r="B27" s="124"/>
-      <c r="C27" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="124"/>
-      <c r="E27" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="126"/>
-      <c r="G27" s="123" t="s">
-        <v>110</v>
-      </c>
-      <c r="H27" s="124"/>
+      <c r="A27" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="126"/>
+      <c r="C27" s="125" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="126"/>
+      <c r="E27" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="128"/>
+      <c r="G27" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="126"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="123" t="s">
-        <v>85</v>
-      </c>
-      <c r="L27" s="124"/>
-      <c r="M27" s="123" t="s">
-        <v>86</v>
-      </c>
-      <c r="N27" s="124"/>
-      <c r="O27" s="125" t="s">
-        <v>87</v>
-      </c>
-      <c r="P27" s="126"/>
-      <c r="Q27" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="R27" s="124"/>
+      <c r="K27" s="125" t="s">
+        <v>99</v>
+      </c>
+      <c r="L27" s="126"/>
+      <c r="M27" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="N27" s="126"/>
+      <c r="O27" s="127" t="s">
+        <v>101</v>
+      </c>
+      <c r="P27" s="128"/>
+      <c r="Q27" s="125" t="s">
+        <v>102</v>
+      </c>
+      <c r="R27" s="126"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -17596,7 +17715,7 @@
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B50" s="58">
         <f>+AVERAGE(B28:B36,B43:B47)</f>
@@ -17620,7 +17739,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="L50" s="58">
         <f>+AVERAGE(L28:L38,L41:L47)</f>
@@ -17750,7 +17869,7 @@
     </row>
     <row r="54" spans="1:24">
       <c r="A54" s="90" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B54" s="58">
         <f>+SMALL(B28:B47,1)</f>
@@ -17774,7 +17893,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="90" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L54" s="58">
         <f>+SMALL(L28:L47,1)</f>
@@ -17855,28 +17974,28 @@
       <c r="X56" s="1"/>
     </row>
     <row r="57" spans="1:24" ht="34.5">
-      <c r="A57" s="127" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="127"/>
-      <c r="C57" s="127"/>
-      <c r="D57" s="127"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="127"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="127"/>
+      <c r="A57" s="124" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="124"/>
+      <c r="C57" s="124"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="124"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="127" t="s">
-        <v>114</v>
-      </c>
-      <c r="L57" s="127"/>
-      <c r="M57" s="127"/>
-      <c r="N57" s="127"/>
-      <c r="O57" s="127"/>
-      <c r="P57" s="127"/>
-      <c r="Q57" s="127"/>
-      <c r="R57" s="127"/>
+      <c r="K57" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="L57" s="124"/>
+      <c r="M57" s="124"/>
+      <c r="N57" s="124"/>
+      <c r="O57" s="124"/>
+      <c r="P57" s="124"/>
+      <c r="Q57" s="124"/>
+      <c r="R57" s="124"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
@@ -17885,36 +18004,36 @@
       <c r="X57" s="1"/>
     </row>
     <row r="58" spans="1:24">
-      <c r="A58" s="123" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58" s="124"/>
-      <c r="C58" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="124"/>
-      <c r="E58" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="F58" s="126"/>
-      <c r="G58" s="123" t="s">
-        <v>110</v>
-      </c>
-      <c r="H58" s="124"/>
+      <c r="A58" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="126"/>
+      <c r="C58" s="125" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="126"/>
+      <c r="E58" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="128"/>
+      <c r="G58" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="H58" s="126"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="123"/>
-      <c r="L58" s="124"/>
-      <c r="M58" s="123" t="s">
+      <c r="K58" s="125"/>
+      <c r="L58" s="126"/>
+      <c r="M58" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="124"/>
-      <c r="O58" s="125"/>
-      <c r="P58" s="126"/>
-      <c r="Q58" s="123" t="s">
+      <c r="N58" s="126"/>
+      <c r="O58" s="127"/>
+      <c r="P58" s="128"/>
+      <c r="Q58" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="R58" s="124"/>
+      <c r="R58" s="126"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
@@ -18664,7 +18783,7 @@
     </row>
     <row r="77" spans="1:24">
       <c r="A77" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B77" s="58" t="e">
         <f>+AVERAGE(B55:B64,B68:B74)</f>
@@ -18819,7 +18938,7 @@
     </row>
     <row r="81" spans="1:24">
       <c r="A81" s="90" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -18967,7 +19086,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="90" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="N85" s="58">
         <f>+AVERAGE(N59:N83)</f>
@@ -19027,7 +19146,7 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="90" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="N87" s="102">
         <f>+SUM(N85-R85)</f>
@@ -19087,7 +19206,7 @@
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="90" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="N89" s="58">
         <f>+SMALL(N59:N83,1)</f>
@@ -19147,7 +19266,7 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="90" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="N91" s="103">
         <f>+SUM(N89-R89)</f>
@@ -19194,14 +19313,16 @@
       <c r="X92" s="1"/>
     </row>
     <row r="93" spans="1:24">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
+      <c r="A93" s="116" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="116"/>
+      <c r="C93" s="116"/>
+      <c r="D93" s="116"/>
+      <c r="E93" s="116"/>
+      <c r="F93" s="116"/>
+      <c r="G93" s="116"/>
+      <c r="H93" s="116"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -19220,14 +19341,14 @@
       <c r="X93" s="1"/>
     </row>
     <row r="94" spans="1:24">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
+      <c r="A94" s="116"/>
+      <c r="B94" s="116"/>
+      <c r="C94" s="116"/>
+      <c r="D94" s="116"/>
+      <c r="E94" s="116"/>
+      <c r="F94" s="116"/>
+      <c r="G94" s="116"/>
+      <c r="H94" s="116"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -19246,12 +19367,24 @@
       <c r="X94" s="1"/>
     </row>
     <row r="95" spans="1:24">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
+      <c r="A95" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -19272,12 +19405,24 @@
       <c r="X95" s="1"/>
     </row>
     <row r="96" spans="1:24">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
+      <c r="A96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -19792,12 +19937,26 @@
       <c r="X115" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="G58:H58"/>
+  <mergeCells count="34">
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:R58"/>
+    <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:R1"/>
     <mergeCell ref="K25:R25"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="Q27:R27"/>
@@ -19807,25 +19966,12 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="O26:P26"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="M58:N58"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:R58"/>
-    <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A93:H94"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
